--- a/docs/ICON_Greater_Houston_Rolodex.xlsx
+++ b/docs/ICON_Greater_Houston_Rolodex.xlsx
@@ -565,7 +565,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated from houston-data.json · build 31 · 2026-09-11 · public render. Do not hand-edit the HTML deck; it regenerates from the same file.</t>
+          <t>Generated from houston-data.json · build 32 · 2026-09-11 · public render. Do not hand-edit the HTML deck; it regenerates from the same file.</t>
         </is>
       </c>
     </row>
@@ -676,12 +676,12 @@
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>Titan fit</t>
+          <t>Printer fit</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>Titan fit why</t>
+          <t>Printer fit why</t>
         </is>
       </c>
       <c r="M6" s="5" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="U24" s="15" t="inlineStr">
         <is>
-          <t>The 300-closings figure and the even-flow description come from a Builder Magazine profile of 2014 performance. The cadence model is on record; the current volume is not. | Individual profiles for the four named leaders were not found. They are named with titles on the firm's own team page, which is the citation. | The volume on file was more than 300 closings a year. HousingWire reports 973 homes and $310 million in 2025, up 17 percent. Titan fit moves from Yes to Partly on that figure.</t>
+          <t>The 300-closings figure and the even-flow description come from a Builder Magazine profile of 2014 performance. The cadence model is on record; the current volume is not. | Individual profiles for the four named leaders were not found. They are named with titles on the firm's own team page, which is the citation. | The volume on file was more than 300 closings a year. HousingWire reports 973 homes and $310 million in 2025, up 17 percent. Printer fit moves from Yes to Partly on that figure.</t>
         </is>
       </c>
       <c r="V24" s="12" t="inlineStr"/>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="U25" s="9" t="inlineStr">
         <is>
-          <t>The 300-closings figure and the even-flow description come from a Builder Magazine profile of 2014 performance. The cadence model is on record; the current volume is not. | Individual profiles for the four named leaders were not found. They are named with titles on the firm's own team page, which is the citation. | The volume on file was more than 300 closings a year. HousingWire reports 973 homes and $310 million in 2025, up 17 percent. Titan fit moves from Yes to Partly on that figure.</t>
+          <t>The 300-closings figure and the even-flow description come from a Builder Magazine profile of 2014 performance. The cadence model is on record; the current volume is not. | Individual profiles for the four named leaders were not found. They are named with titles on the firm's own team page, which is the citation. | The volume on file was more than 300 closings a year. HousingWire reports 973 homes and $310 million in 2025, up 17 percent. Printer fit moves from Yes to Partly on that figure.</t>
         </is>
       </c>
       <c r="V25" s="6" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="U26" s="15" t="inlineStr">
         <is>
-          <t>The 300-closings figure and the even-flow description come from a Builder Magazine profile of 2014 performance. The cadence model is on record; the current volume is not. | Individual profiles for the four named leaders were not found. They are named with titles on the firm's own team page, which is the citation. | The volume on file was more than 300 closings a year. HousingWire reports 973 homes and $310 million in 2025, up 17 percent. Titan fit moves from Yes to Partly on that figure.</t>
+          <t>The 300-closings figure and the even-flow description come from a Builder Magazine profile of 2014 performance. The cadence model is on record; the current volume is not. | Individual profiles for the four named leaders were not found. They are named with titles on the firm's own team page, which is the citation. | The volume on file was more than 300 closings a year. HousingWire reports 973 homes and $310 million in 2025, up 17 percent. Printer fit moves from Yes to Partly on that figure.</t>
         </is>
       </c>
       <c r="V26" s="12" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="U27" s="9" t="inlineStr">
         <is>
-          <t>The 300-closings figure and the even-flow description come from a Builder Magazine profile of 2014 performance. The cadence model is on record; the current volume is not. | Individual profiles for the four named leaders were not found. They are named with titles on the firm's own team page, which is the citation. | The volume on file was more than 300 closings a year. HousingWire reports 973 homes and $310 million in 2025, up 17 percent. Titan fit moves from Yes to Partly on that figure.</t>
+          <t>The 300-closings figure and the even-flow description come from a Builder Magazine profile of 2014 performance. The cadence model is on record; the current volume is not. | Individual profiles for the four named leaders were not found. They are named with titles on the firm's own team page, which is the citation. | The volume on file was more than 300 closings a year. HousingWire reports 973 homes and $310 million in 2025, up 17 percent. Printer fit moves from Yes to Partly on that figure.</t>
         </is>
       </c>
       <c r="V27" s="6" t="inlineStr"/>
@@ -7819,7 +7819,7 @@
       </c>
       <c r="U67" s="9" t="inlineStr">
         <is>
-          <t>The cumulative figure is the firm's own and covers eighteen years. No single-year number is published. | Builder reports 540 closings in 2025 and 552 in 2024. Titan fit moves from Yes to Partly. | No LinkedIn company page exists for the firm, only individual employee profiles.</t>
+          <t>The cumulative figure is the firm's own and covers eighteen years. No single-year number is published. | Builder reports 540 closings in 2025 and 552 in 2024. Printer fit moves from Yes to Partly. | No LinkedIn company page exists for the firm, only individual employee profiles.</t>
         </is>
       </c>
       <c r="V67" s="6" t="inlineStr"/>
@@ -7932,7 +7932,7 @@
       </c>
       <c r="U68" s="15" t="inlineStr">
         <is>
-          <t>The cumulative figure is the firm's own and covers eighteen years. No single-year number is published. | Builder reports 540 closings in 2025 and 552 in 2024. Titan fit moves from Yes to Partly. | No LinkedIn company page exists for the firm, only individual employee profiles.</t>
+          <t>The cumulative figure is the firm's own and covers eighteen years. No single-year number is published. | Builder reports 540 closings in 2025 and 552 in 2024. Printer fit moves from Yes to Partly. | No LinkedIn company page exists for the firm, only individual employee profiles.</t>
         </is>
       </c>
       <c r="V68" s="12" t="inlineStr">
@@ -22195,7 +22195,7 @@
     <row r="197">
       <c r="A197" s="17" t="inlineStr">
         <is>
-          <t>NOTE. A filled LinkedIn cell means the profile was opened or the search result read and the headline named the firm; column W records what was read. Where that test failed the cell is left empty rather than guessed, because a fabricated slug passes visual inspection and then fails in front of the person it names. Column Q searches for the empty ones in your own session. Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both keep a firm in. Only a No takes it out. Holds counts how many of the three are Yes or Partly. Capital is a qualifier, not a count. Source: ICON Greater Houston screen, build 31, 2026-09-11.</t>
+          <t>NOTE. A filled LinkedIn cell means the profile was opened or the search result read and the headline named the firm; column W records what was read. Where that test failed the cell is left empty rather than guessed, because a fabricated slug passes visual inspection and then fails in front of the person it names. Column Q searches for the empty ones in your own session. Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both keep a firm in. Only a No takes it out. Holds counts how many of the three are Yes or Partly. Capital is a qualifier, not a count. Source: ICON Greater Houston screen, build 32, 2026-09-11.</t>
         </is>
       </c>
     </row>

--- a/docs/ICON_Greater_Houston_Rolodex.xlsx
+++ b/docs/ICON_Greater_Houston_Rolodex.xlsx
@@ -565,7 +565,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated from houston-data.json · build 35 · 2026-09-11 · public render. Do not hand-edit the HTML deck; it regenerates from the same file.</t>
+          <t>Generated from houston-data.json · build 36 · 2026-09-11 · public render. Do not hand-edit the HTML deck; it regenerates from the same file.</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,11 @@
           <t>Spring, Harris-Montgomery</t>
         </is>
       </c>
-      <c r="H42" s="12" t="inlineStr"/>
+      <c r="H42" s="12" t="inlineStr">
+        <is>
+          <t>No unit count published; owned by Sekisui House U.S.</t>
+        </is>
+      </c>
       <c r="I42" s="14" t="inlineStr">
         <is>
           <t>Partly</t>
@@ -4927,7 +4931,11 @@
           <t>Spring, Harris-Montgomery</t>
         </is>
       </c>
-      <c r="H43" s="6" t="inlineStr"/>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>No unit count published; owned by Sekisui House U.S.</t>
+        </is>
+      </c>
       <c r="I43" s="8" t="inlineStr">
         <is>
           <t>Partly</t>
@@ -5040,7 +5048,11 @@
           <t>Spring, Harris-Montgomery</t>
         </is>
       </c>
-      <c r="H44" s="12" t="inlineStr"/>
+      <c r="H44" s="12" t="inlineStr">
+        <is>
+          <t>No unit count published; owned by Sekisui House U.S.</t>
+        </is>
+      </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
           <t>Partly</t>
@@ -7033,7 +7045,7 @@
       </c>
       <c r="N61" s="9" t="inlineStr">
         <is>
-          <t>The model is standardisation for entry-level buyers. That is not evidence of paying for an unproven method.</t>
+          <t>The model is standardisation for entry-level buyers. That is not evidence of paying for a method that was new at the time.</t>
         </is>
       </c>
       <c r="O61" s="8" t="inlineStr">
@@ -9469,7 +9481,7 @@
       </c>
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>20 homes and $22 million in 2020, the latest published</t>
+          <t>About 75 homes a year on the firm's own count</t>
         </is>
       </c>
       <c r="I83" s="8" t="inlineStr">
@@ -9582,7 +9594,7 @@
       </c>
       <c r="H84" s="12" t="inlineStr">
         <is>
-          <t>20 homes and $22 million in 2020, the latest published</t>
+          <t>About 75 homes a year on the firm's own count</t>
         </is>
       </c>
       <c r="I84" s="14" t="inlineStr">
@@ -9694,7 +9706,7 @@
       </c>
       <c r="H85" s="6" t="inlineStr">
         <is>
-          <t>20 homes and $22 million in 2020, the latest published</t>
+          <t>About 75 homes a year on the firm's own count</t>
         </is>
       </c>
       <c r="I85" s="8" t="inlineStr">
@@ -11914,7 +11926,11 @@
           <t>Chicago HQ / Katy, Harris</t>
         </is>
       </c>
-      <c r="H105" s="6" t="inlineStr"/>
+      <c r="H105" s="6" t="inlineStr">
+        <is>
+          <t>366 build-to-rent units across two Katy projects</t>
+        </is>
+      </c>
       <c r="I105" s="8" t="inlineStr">
         <is>
           <t>Partly</t>
@@ -12026,7 +12042,11 @@
           <t>Chicago HQ / Katy, Harris</t>
         </is>
       </c>
-      <c r="H106" s="12" t="inlineStr"/>
+      <c r="H106" s="12" t="inlineStr">
+        <is>
+          <t>366 build-to-rent units across two Katy projects</t>
+        </is>
+      </c>
       <c r="I106" s="14" t="inlineStr">
         <is>
           <t>Partly</t>
@@ -12142,7 +12162,11 @@
           <t>Chicago HQ / Katy, Harris</t>
         </is>
       </c>
-      <c r="H107" s="6" t="inlineStr"/>
+      <c r="H107" s="6" t="inlineStr">
+        <is>
+          <t>366 build-to-rent units across two Katy projects</t>
+        </is>
+      </c>
       <c r="I107" s="8" t="inlineStr">
         <is>
           <t>Partly</t>
@@ -12373,19 +12397,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J109" s="9" t="inlineStr"/>
+      <c r="J109" s="9" t="inlineStr">
+        <is>
+          <t>The same wall system, installed again and again across Houston and the coast since 2002.</t>
+        </is>
+      </c>
       <c r="K109" s="8" t="inlineStr">
         <is>
           <t>Partly</t>
         </is>
       </c>
-      <c r="L109" s="9" t="inlineStr"/>
+      <c r="L109" s="9" t="inlineStr">
+        <is>
+          <t>No crew count or homes-a-year figure is published. On the bands, a firm with no published figure is a Partly, and that is the first thing to establish on the call.</t>
+        </is>
+      </c>
       <c r="M109" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N109" s="9" t="inlineStr"/>
+      <c r="N109" s="9" t="inlineStr">
+        <is>
+          <t>Its entire business is a wall method that was new when it adopted it. The crews are trained on twelve form systems and run a twenty-step checklist before every placement.</t>
+        </is>
+      </c>
       <c r="O109" s="8" t="inlineStr">
         <is>
           <t>No</t>
@@ -12469,19 +12505,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J110" s="15" t="inlineStr"/>
+      <c r="J110" s="15" t="inlineStr">
+        <is>
+          <t>Tilt-up and foundation work repeating across four counties from one Houston yard.</t>
+        </is>
+      </c>
       <c r="K110" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L110" s="15" t="inlineStr"/>
+      <c r="L110" s="15" t="inlineStr">
+        <is>
+          <t>150 office and field staff on the firm's own count. That is the only published size in this section, and at that size one or two printers cover a real share of a year's wall.</t>
+        </is>
+      </c>
       <c r="M110" s="14" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N110" s="15" t="inlineStr"/>
+      <c r="N110" s="15" t="inlineStr">
+        <is>
+          <t>No method statement on record. Its published work is conventional tilt-up and foundations.</t>
+        </is>
+      </c>
       <c r="O110" s="14" t="inlineStr">
         <is>
           <t>Partly</t>
@@ -12565,19 +12613,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J111" s="9" t="inlineStr"/>
+      <c r="J111" s="9" t="inlineStr">
+        <is>
+          <t>Tilt-up and foundation work repeating across four counties from one Houston yard.</t>
+        </is>
+      </c>
       <c r="K111" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L111" s="9" t="inlineStr"/>
+      <c r="L111" s="9" t="inlineStr">
+        <is>
+          <t>150 office and field staff on the firm's own count. That is the only published size in this section, and at that size one or two printers cover a real share of a year's wall.</t>
+        </is>
+      </c>
       <c r="M111" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N111" s="9" t="inlineStr"/>
+      <c r="N111" s="9" t="inlineStr">
+        <is>
+          <t>No method statement on record. Its published work is conventional tilt-up and foundations.</t>
+        </is>
+      </c>
       <c r="O111" s="8" t="inlineStr">
         <is>
           <t>Partly</t>
@@ -12661,19 +12721,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J112" s="15" t="inlineStr"/>
+      <c r="J112" s="15" t="inlineStr">
+        <is>
+          <t>Tilt-up and foundation work repeating across four counties from one Houston yard.</t>
+        </is>
+      </c>
       <c r="K112" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L112" s="15" t="inlineStr"/>
+      <c r="L112" s="15" t="inlineStr">
+        <is>
+          <t>150 office and field staff on the firm's own count. That is the only published size in this section, and at that size one or two printers cover a real share of a year's wall.</t>
+        </is>
+      </c>
       <c r="M112" s="14" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N112" s="15" t="inlineStr"/>
+      <c r="N112" s="15" t="inlineStr">
+        <is>
+          <t>No method statement on record. Its published work is conventional tilt-up and foundations.</t>
+        </is>
+      </c>
       <c r="O112" s="14" t="inlineStr">
         <is>
           <t>Partly</t>
@@ -12753,19 +12825,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J113" s="9" t="inlineStr"/>
+      <c r="J113" s="9" t="inlineStr">
+        <is>
+          <t>Tilt-up warehouses, retail centres and schools repeating inside the Houston market.</t>
+        </is>
+      </c>
       <c r="K113" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L113" s="9" t="inlineStr"/>
+      <c r="L113" s="9" t="inlineStr">
+        <is>
+          <t>No crew count or annual volume is published. The one published job runs to 32 panels across four floors. On the bands, a firm with no annual figure is a Partly.</t>
+        </is>
+      </c>
       <c r="M113" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N113" s="9" t="inlineStr"/>
+      <c r="N113" s="9" t="inlineStr">
+        <is>
+          <t>No method statement on record. The 2025 tilt-up award is for execution, not for a new method.</t>
+        </is>
+      </c>
       <c r="O113" s="8" t="inlineStr">
         <is>
           <t>Partly</t>
@@ -12838,19 +12922,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J114" s="15" t="inlineStr"/>
+      <c r="J114" s="15" t="inlineStr">
+        <is>
+          <t>Three standing placement divisions in one metro, so the same work recurs rather than arriving one project at a time.</t>
+        </is>
+      </c>
       <c r="K114" s="14" t="inlineStr">
         <is>
           <t>Partly</t>
         </is>
       </c>
-      <c r="L114" s="15" t="inlineStr"/>
+      <c r="L114" s="15" t="inlineStr">
+        <is>
+          <t>1,500 craftsmen and 975,000 cubic yards a year on the firm's own count. One or two printers would be a line inside the business rather than the business.</t>
+        </is>
+      </c>
       <c r="M114" s="14" t="inlineStr">
         <is>
           <t>Partly</t>
         </is>
       </c>
-      <c r="N114" s="15" t="inlineStr"/>
+      <c r="N114" s="15" t="inlineStr">
+        <is>
+          <t>It owns a fleet of placing booms and multiple complete hydraulic self-jacking formwork systems on its own account. Buying capital equipment to change how concrete gets placed is the habit this count is looking for, though formwork is not a new method.</t>
+        </is>
+      </c>
       <c r="O114" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -12927,19 +13023,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J115" s="9" t="inlineStr"/>
+      <c r="J115" s="9" t="inlineStr">
+        <is>
+          <t>Interior wall and ceiling packages repeating across multifamily and single family work in one metro.</t>
+        </is>
+      </c>
       <c r="K115" s="8" t="inlineStr">
         <is>
           <t>Partly</t>
         </is>
       </c>
-      <c r="L115" s="9" t="inlineStr"/>
+      <c r="L115" s="9" t="inlineStr">
+        <is>
+          <t>No employee count or annual unit figure is published. On the bands, a firm with no published figure is a Partly.</t>
+        </is>
+      </c>
       <c r="M115" s="8" t="inlineStr">
         <is>
           <t>Partly</t>
         </is>
       </c>
-      <c r="N115" s="9" t="inlineStr"/>
+      <c r="N115" s="9" t="inlineStr">
+        <is>
+          <t>It built and staffed a prefabrication plant producing wall panels and interior components offsite, and publishes what that saved on a hospital project. That is paying to move wall work into a factory, which is the nearest thing to the argument for a printer.</t>
+        </is>
+      </c>
       <c r="O115" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -13023,19 +13131,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J116" s="15" t="inlineStr"/>
+      <c r="J116" s="15" t="inlineStr">
+        <is>
+          <t>Interior wall and ceiling packages repeating across multifamily and single family work in one metro.</t>
+        </is>
+      </c>
       <c r="K116" s="14" t="inlineStr">
         <is>
           <t>Partly</t>
         </is>
       </c>
-      <c r="L116" s="15" t="inlineStr"/>
+      <c r="L116" s="15" t="inlineStr">
+        <is>
+          <t>No employee count or annual unit figure is published. On the bands, a firm with no published figure is a Partly.</t>
+        </is>
+      </c>
       <c r="M116" s="14" t="inlineStr">
         <is>
           <t>Partly</t>
         </is>
       </c>
-      <c r="N116" s="15" t="inlineStr"/>
+      <c r="N116" s="15" t="inlineStr">
+        <is>
+          <t>It built and staffed a prefabrication plant producing wall panels and interior components offsite, and publishes what that saved on a hospital project. That is paying to move wall work into a factory, which is the nearest thing to the argument for a printer.</t>
+        </is>
+      </c>
       <c r="O116" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -13119,19 +13239,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J117" s="9" t="inlineStr"/>
+      <c r="J117" s="9" t="inlineStr">
+        <is>
+          <t>Interior wall and ceiling packages repeating across multifamily and single family work in one metro.</t>
+        </is>
+      </c>
       <c r="K117" s="8" t="inlineStr">
         <is>
           <t>Partly</t>
         </is>
       </c>
-      <c r="L117" s="9" t="inlineStr"/>
+      <c r="L117" s="9" t="inlineStr">
+        <is>
+          <t>No employee count or annual unit figure is published. On the bands, a firm with no published figure is a Partly.</t>
+        </is>
+      </c>
       <c r="M117" s="8" t="inlineStr">
         <is>
           <t>Partly</t>
         </is>
       </c>
-      <c r="N117" s="9" t="inlineStr"/>
+      <c r="N117" s="9" t="inlineStr">
+        <is>
+          <t>It built and staffed a prefabrication plant producing wall panels and interior components offsite, and publishes what that saved on a hospital project. That is paying to move wall work into a factory, which is the nearest thing to the argument for a printer.</t>
+        </is>
+      </c>
       <c r="O117" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -13215,19 +13347,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J118" s="15" t="inlineStr"/>
+      <c r="J118" s="15" t="inlineStr">
+        <is>
+          <t>Interior wall and ceiling packages repeating across multifamily and single family work in one metro.</t>
+        </is>
+      </c>
       <c r="K118" s="14" t="inlineStr">
         <is>
           <t>Partly</t>
         </is>
       </c>
-      <c r="L118" s="15" t="inlineStr"/>
+      <c r="L118" s="15" t="inlineStr">
+        <is>
+          <t>No employee count or annual unit figure is published. On the bands, a firm with no published figure is a Partly.</t>
+        </is>
+      </c>
       <c r="M118" s="14" t="inlineStr">
         <is>
           <t>Partly</t>
         </is>
       </c>
-      <c r="N118" s="15" t="inlineStr"/>
+      <c r="N118" s="15" t="inlineStr">
+        <is>
+          <t>It built and staffed a prefabrication plant producing wall panels and interior components offsite, and publishes what that saved on a hospital project. That is paying to move wall work into a factory, which is the nearest thing to the argument for a printer.</t>
+        </is>
+      </c>
       <c r="O118" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -13303,19 +13447,31 @@
           <t>Partly</t>
         </is>
       </c>
-      <c r="J119" s="9" t="inlineStr"/>
+      <c r="J119" s="9" t="inlineStr">
+        <is>
+          <t>Concrete packages recurring across Houston projects under both delivery models.</t>
+        </is>
+      </c>
       <c r="K119" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L119" s="9" t="inlineStr"/>
+      <c r="L119" s="9" t="inlineStr">
+        <is>
+          <t>No crew count, revenue or project size is published. Nothing on the site sizes the work, so on the bands this is a Partly.</t>
+        </is>
+      </c>
       <c r="M119" s="8" t="inlineStr">
         <is>
           <t>Partly</t>
         </is>
       </c>
-      <c r="N119" s="9" t="inlineStr"/>
+      <c r="N119" s="9" t="inlineStr">
+        <is>
+          <t>It bought and staffed a modelling stack, Revit, Tekla, AutoCAD and Navisworks, to plan its pours. A printed wall arrives as a model first, so the habit transfers, though modelling is not itself a building method.</t>
+        </is>
+      </c>
       <c r="O119" s="8" t="inlineStr">
         <is>
           <t>Partly</t>
@@ -13388,19 +13544,31 @@
           <t>Partly</t>
         </is>
       </c>
-      <c r="J120" s="15" t="inlineStr"/>
+      <c r="J120" s="15" t="inlineStr">
+        <is>
+          <t>Design-build projects, each one different.</t>
+        </is>
+      </c>
       <c r="K120" s="14" t="inlineStr">
         <is>
           <t>Partly</t>
         </is>
       </c>
-      <c r="L120" s="15" t="inlineStr"/>
+      <c r="L120" s="15" t="inlineStr">
+        <is>
+          <t>No headcount, revenue or annual project figure is published. On the bands, a firm with no published figure is a Partly.</t>
+        </is>
+      </c>
       <c r="M120" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N120" s="15" t="inlineStr"/>
+      <c r="N120" s="15" t="inlineStr">
+        <is>
+          <t>It engineered and delivered a printed house in Houston in collaboration with a printing contractor, and publishes the project on its own site.</t>
+        </is>
+      </c>
       <c r="O120" s="14" t="inlineStr">
         <is>
           <t>Partly</t>
@@ -13473,19 +13641,31 @@
           <t>Partly</t>
         </is>
       </c>
-      <c r="J121" s="9" t="inlineStr"/>
+      <c r="J121" s="9" t="inlineStr">
+        <is>
+          <t>Commercial buildings across the Gulf Coast. The structures differ project to project.</t>
+        </is>
+      </c>
       <c r="K121" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L121" s="9" t="inlineStr"/>
+      <c r="L121" s="9" t="inlineStr">
+        <is>
+          <t>No revenue, crew count or project count is published. On the bands, a firm with no published figure is a Partly.</t>
+        </is>
+      </c>
       <c r="M121" s="8" t="inlineStr">
         <is>
           <t>Partly</t>
         </is>
       </c>
-      <c r="N121" s="9" t="inlineStr"/>
+      <c r="N121" s="9" t="inlineStr">
+        <is>
+          <t>It carries insulated concrete form construction in its standard menu alongside tilt-wall and masonry, so it has sold and built a concrete wall system rather than only a wood one. No named project is published to date it.</t>
+        </is>
+      </c>
       <c r="O121" s="8" t="inlineStr">
         <is>
           <t>Partly</t>
@@ -13558,19 +13738,31 @@
           <t>Partly</t>
         </is>
       </c>
-      <c r="J122" s="15" t="inlineStr"/>
+      <c r="J122" s="15" t="inlineStr">
+        <is>
+          <t>Industrial and commercial concrete recurring across the east side of the metro.</t>
+        </is>
+      </c>
       <c r="K122" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L122" s="15" t="inlineStr"/>
+      <c r="L122" s="15" t="inlineStr">
+        <is>
+          <t>No crew count, revenue or annual volume is published. On the bands, a firm with no published figure is a Partly.</t>
+        </is>
+      </c>
       <c r="M122" s="14" t="inlineStr">
         <is>
           <t>Partly</t>
         </is>
       </c>
-      <c r="N122" s="15" t="inlineStr"/>
+      <c r="N122" s="15" t="inlineStr">
+        <is>
+          <t>It bought volumetric mixers and stood up its own delivery arm rather than buying ready-mix from a plant. That is paying for a different way to get concrete to a site, though it is not a wall method.</t>
+        </is>
+      </c>
       <c r="O122" s="14" t="inlineStr">
         <is>
           <t>Partly</t>
@@ -13647,19 +13839,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J123" s="9" t="inlineStr"/>
+      <c r="J123" s="9" t="inlineStr">
+        <is>
+          <t>Garden-style and mid-rise apartment buildings repeating across Texas markets from a Houston office.</t>
+        </is>
+      </c>
       <c r="K123" s="8" t="inlineStr">
         <is>
           <t>Partly</t>
         </is>
       </c>
-      <c r="L123" s="9" t="inlineStr"/>
+      <c r="L123" s="9" t="inlineStr">
+        <is>
+          <t>Over 44,000 apartment homes in 45 years, so the wall volume is there. It states that it works through trade partners rather than self-performing, so the machine would sit with a subcontractor rather than with Blazer.</t>
+        </is>
+      </c>
       <c r="M123" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N123" s="9" t="inlineStr"/>
+      <c r="N123" s="9" t="inlineStr">
+        <is>
+          <t>No method statement on record. The only construction-method language on the site is the list of building types it builds.</t>
+        </is>
+      </c>
       <c r="O123" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -13739,19 +13943,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J124" s="15" t="inlineStr"/>
+      <c r="J124" s="15" t="inlineStr">
+        <is>
+          <t>Garden-style and mid-rise apartment buildings repeating across Texas markets from a Houston office.</t>
+        </is>
+      </c>
       <c r="K124" s="14" t="inlineStr">
         <is>
           <t>Partly</t>
         </is>
       </c>
-      <c r="L124" s="15" t="inlineStr"/>
+      <c r="L124" s="15" t="inlineStr">
+        <is>
+          <t>Over 44,000 apartment homes in 45 years, so the wall volume is there. It states that it works through trade partners rather than self-performing, so the machine would sit with a subcontractor rather than with Blazer.</t>
+        </is>
+      </c>
       <c r="M124" s="14" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N124" s="15" t="inlineStr"/>
+      <c r="N124" s="15" t="inlineStr">
+        <is>
+          <t>No method statement on record. The only construction-method language on the site is the list of building types it builds.</t>
+        </is>
+      </c>
       <c r="O124" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -13831,19 +14047,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J125" s="9" t="inlineStr"/>
+      <c r="J125" s="9" t="inlineStr">
+        <is>
+          <t>Garden-style and mid-rise apartment buildings repeating across Texas markets from a Houston office.</t>
+        </is>
+      </c>
       <c r="K125" s="8" t="inlineStr">
         <is>
           <t>Partly</t>
         </is>
       </c>
-      <c r="L125" s="9" t="inlineStr"/>
+      <c r="L125" s="9" t="inlineStr">
+        <is>
+          <t>Over 44,000 apartment homes in 45 years, so the wall volume is there. It states that it works through trade partners rather than self-performing, so the machine would sit with a subcontractor rather than with Blazer.</t>
+        </is>
+      </c>
       <c r="M125" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N125" s="9" t="inlineStr"/>
+      <c r="N125" s="9" t="inlineStr">
+        <is>
+          <t>No method statement on record. The only construction-method language on the site is the list of building types it builds.</t>
+        </is>
+      </c>
       <c r="O125" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -13923,19 +14151,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J126" s="15" t="inlineStr"/>
+      <c r="J126" s="15" t="inlineStr">
+        <is>
+          <t>Garden-style and mid-rise apartment buildings repeating across Texas markets from a Houston office.</t>
+        </is>
+      </c>
       <c r="K126" s="14" t="inlineStr">
         <is>
           <t>Partly</t>
         </is>
       </c>
-      <c r="L126" s="15" t="inlineStr"/>
+      <c r="L126" s="15" t="inlineStr">
+        <is>
+          <t>Over 44,000 apartment homes in 45 years, so the wall volume is there. It states that it works through trade partners rather than self-performing, so the machine would sit with a subcontractor rather than with Blazer.</t>
+        </is>
+      </c>
       <c r="M126" s="14" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N126" s="15" t="inlineStr"/>
+      <c r="N126" s="15" t="inlineStr">
+        <is>
+          <t>No method statement on record. The only construction-method language on the site is the list of building types it builds.</t>
+        </is>
+      </c>
       <c r="O126" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -14015,19 +14255,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J127" s="9" t="inlineStr"/>
+      <c r="J127" s="9" t="inlineStr">
+        <is>
+          <t>Panel production at the top of the metro's range, recurring across institutional and commercial work.</t>
+        </is>
+      </c>
       <c r="K127" s="8" t="inlineStr">
         <is>
           <t>Partly</t>
         </is>
       </c>
-      <c r="L127" s="9" t="inlineStr"/>
+      <c r="L127" s="9" t="inlineStr">
+        <is>
+          <t>The concrete business is large enough that a printer is a line item, and the capital decision sits with a listed parent rather than in Houston.</t>
+        </is>
+      </c>
       <c r="M127" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N127" s="9" t="inlineStr"/>
+      <c r="N127" s="9" t="inlineStr">
+        <is>
+          <t>No method statement on record.</t>
+        </is>
+      </c>
       <c r="O127" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -14107,19 +14359,31 @@
           <t>Partly</t>
         </is>
       </c>
-      <c r="J128" s="15" t="inlineStr"/>
+      <c r="J128" s="15" t="inlineStr">
+        <is>
+          <t>Site and concrete packages recurring across Houston jobs, though the buildings themselves differ.</t>
+        </is>
+      </c>
       <c r="K128" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L128" s="15" t="inlineStr"/>
+      <c r="L128" s="15" t="inlineStr">
+        <is>
+          <t>No crew count, revenue or annual volume is published. On the bands, a firm with no published figure is a Partly.</t>
+        </is>
+      </c>
       <c r="M128" s="14" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N128" s="15" t="inlineStr"/>
+      <c r="N128" s="15" t="inlineStr">
+        <is>
+          <t>No method statement on record.</t>
+        </is>
+      </c>
       <c r="O128" s="14" t="inlineStr">
         <is>
           <t>Partly</t>
@@ -14192,19 +14456,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J129" s="9" t="inlineStr"/>
+      <c r="J129" s="9" t="inlineStr">
+        <is>
+          <t>Panel and deck work recurring across Houston projects for a standing set of general contractors.</t>
+        </is>
+      </c>
       <c r="K129" s="8" t="inlineStr">
         <is>
           <t>Partly</t>
         </is>
       </c>
-      <c r="L129" s="9" t="inlineStr"/>
+      <c r="L129" s="9" t="inlineStr">
+        <is>
+          <t>No crew count or annual volume is published. The one published job runs to 49 panels. On the bands, a firm with no annual figure is a Partly.</t>
+        </is>
+      </c>
       <c r="M129" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N129" s="9" t="inlineStr"/>
+      <c r="N129" s="9" t="inlineStr">
+        <is>
+          <t>No method statement on record.</t>
+        </is>
+      </c>
       <c r="O129" s="8" t="inlineStr">
         <is>
           <t>Partly</t>
@@ -14277,19 +14553,31 @@
           <t>Partly</t>
         </is>
       </c>
-      <c r="J130" s="15" t="inlineStr"/>
+      <c r="J130" s="15" t="inlineStr">
+        <is>
+          <t>Commercial shells and paving across the metro. The published square footages are weighted to paving rather than to wall.</t>
+        </is>
+      </c>
       <c r="K130" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L130" s="15" t="inlineStr"/>
+      <c r="L130" s="15" t="inlineStr">
+        <is>
+          <t>No annual volume is published. The one published wall figure is 12,000 square feet of tilt wall against 155,000 gross square feet of paving on the same job.</t>
+        </is>
+      </c>
       <c r="M130" s="14" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N130" s="15" t="inlineStr"/>
+      <c r="N130" s="15" t="inlineStr">
+        <is>
+          <t>No method statement on record.</t>
+        </is>
+      </c>
       <c r="O130" s="14" t="inlineStr">
         <is>
           <t>Partly</t>
@@ -14362,19 +14650,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J131" s="9" t="inlineStr"/>
+      <c r="J131" s="9" t="inlineStr">
+        <is>
+          <t>Tilt-up buildings recurring across two Texas metros since 1991.</t>
+        </is>
+      </c>
       <c r="K131" s="8" t="inlineStr">
         <is>
           <t>Partly</t>
         </is>
       </c>
-      <c r="L131" s="9" t="inlineStr"/>
+      <c r="L131" s="9" t="inlineStr">
+        <is>
+          <t>Its own pages carry two different completed square footage figures and neither is repeated here, so nothing published sizes a year's work. On the bands that is a Partly.</t>
+        </is>
+      </c>
       <c r="M131" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N131" s="9" t="inlineStr"/>
+      <c r="N131" s="9" t="inlineStr">
+        <is>
+          <t>No method statement on record.</t>
+        </is>
+      </c>
       <c r="O131" s="8" t="inlineStr">
         <is>
           <t>Partly</t>
@@ -14451,19 +14751,31 @@
           <t>Partly</t>
         </is>
       </c>
-      <c r="J132" s="15" t="inlineStr"/>
+      <c r="J132" s="15" t="inlineStr">
+        <is>
+          <t>Commercial concrete and metal buildings recurring across the north side of the metro.</t>
+        </is>
+      </c>
       <c r="K132" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L132" s="15" t="inlineStr"/>
+      <c r="L132" s="15" t="inlineStr">
+        <is>
+          <t>No crew count, revenue or project size is published anywhere on the site. On the bands, a firm with no published figure is a Partly.</t>
+        </is>
+      </c>
       <c r="M132" s="14" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N132" s="15" t="inlineStr"/>
+      <c r="N132" s="15" t="inlineStr">
+        <is>
+          <t>No method statement on record.</t>
+        </is>
+      </c>
       <c r="O132" s="14" t="inlineStr">
         <is>
           <t>Partly</t>
@@ -14543,19 +14855,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J133" s="9" t="inlineStr"/>
+      <c r="J133" s="9" t="inlineStr">
+        <is>
+          <t>Tilt-up panel production repeats inside one metro even when the buildings differ.</t>
+        </is>
+      </c>
       <c r="K133" s="8" t="inlineStr">
         <is>
           <t>Partly</t>
         </is>
       </c>
-      <c r="L133" s="9" t="inlineStr"/>
+      <c r="L133" s="9" t="inlineStr">
+        <is>
+          <t>The firm's own site gives a job range of $500,000 to $15 million. A printer would be one line in a book that size.</t>
+        </is>
+      </c>
       <c r="M133" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N133" s="9" t="inlineStr"/>
+      <c r="N133" s="9" t="inlineStr">
+        <is>
+          <t>No method statement on record. Its published involvement is in concrete standards committees, not in new methods.</t>
+        </is>
+      </c>
       <c r="O133" s="8" t="inlineStr">
         <is>
           <t>Partly</t>
@@ -14628,19 +14952,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J134" s="15" t="inlineStr"/>
+      <c r="J134" s="15" t="inlineStr">
+        <is>
+          <t>Panel and structural concrete work recurring across the Houston market.</t>
+        </is>
+      </c>
       <c r="K134" s="14" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L134" s="15" t="inlineStr"/>
+      <c r="L134" s="15" t="inlineStr">
+        <is>
+          <t>More than 12,500 people across the United States on the firm's own count, and first on a national ranking of concrete specialty contractors. A machine purchase at that size runs through a national desk, which the bands score as a No.</t>
+        </is>
+      </c>
       <c r="M134" s="14" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N134" s="15" t="inlineStr"/>
+      <c r="N134" s="15" t="inlineStr">
+        <is>
+          <t>No method statement on record. Working at the top of the panel size range is difficulty, not a new method.</t>
+        </is>
+      </c>
       <c r="O134" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -14713,19 +15049,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J135" s="9" t="inlineStr"/>
+      <c r="J135" s="9" t="inlineStr">
+        <is>
+          <t>Single family and townhome communities across the north and west of the metro, taking the same wall package community after community.</t>
+        </is>
+      </c>
       <c r="K135" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L135" s="9" t="inlineStr"/>
+      <c r="L135" s="9" t="inlineStr">
+        <is>
+          <t>9,900 homes a year on the firm's own count, company-wide across Florida and Texas, far above what one or two printers cover. It also counts more than 900 subcontractors and no direct field crew, so there is nobody inside the firm to put on a machine.</t>
+        </is>
+      </c>
       <c r="M135" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N135" s="9" t="inlineStr"/>
+      <c r="N135" s="9" t="inlineStr">
+        <is>
+          <t>No method statement on record.</t>
+        </is>
+      </c>
       <c r="O135" s="8" t="inlineStr">
         <is>
           <t>Partly</t>
@@ -14802,19 +15150,31 @@
           <t>Partly</t>
         </is>
       </c>
-      <c r="J136" s="15" t="inlineStr"/>
+      <c r="J136" s="15" t="inlineStr">
+        <is>
+          <t>Eight divisions across commercial, retail, healthcare and multifamily. The buildings differ project to project.</t>
+        </is>
+      </c>
       <c r="K136" s="14" t="inlineStr">
         <is>
           <t>Partly</t>
         </is>
       </c>
-      <c r="L136" s="15" t="inlineStr"/>
+      <c r="L136" s="15" t="inlineStr">
+        <is>
+          <t>No annual volume is published. The one published job runs to 770,640 square feet, and the panels on it were poured by somebody else.</t>
+        </is>
+      </c>
       <c r="M136" s="14" t="inlineStr">
         <is>
           <t>Partly</t>
         </is>
       </c>
-      <c r="N136" s="15" t="inlineStr"/>
+      <c r="N136" s="15" t="inlineStr">
+        <is>
+          <t>It reordered the standard tilt-wall sequence on a 770,640 square foot job, setting a 275-ton lattice boom crane on the perimeter to avoid the slab, and published the result. That is method appetite rather than the purchase of a new method.</t>
+        </is>
+      </c>
       <c r="O136" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -14898,19 +15258,31 @@
           <t>Partly</t>
         </is>
       </c>
-      <c r="J137" s="9" t="inlineStr"/>
+      <c r="J137" s="9" t="inlineStr">
+        <is>
+          <t>Eight divisions across commercial, retail, healthcare and multifamily. The buildings differ project to project.</t>
+        </is>
+      </c>
       <c r="K137" s="8" t="inlineStr">
         <is>
           <t>Partly</t>
         </is>
       </c>
-      <c r="L137" s="9" t="inlineStr"/>
+      <c r="L137" s="9" t="inlineStr">
+        <is>
+          <t>No annual volume is published. The one published job runs to 770,640 square feet, and the panels on it were poured by somebody else.</t>
+        </is>
+      </c>
       <c r="M137" s="8" t="inlineStr">
         <is>
           <t>Partly</t>
         </is>
       </c>
-      <c r="N137" s="9" t="inlineStr"/>
+      <c r="N137" s="9" t="inlineStr">
+        <is>
+          <t>It reordered the standard tilt-wall sequence on a 770,640 square foot job, setting a 275-ton lattice boom crane on the perimeter to avoid the slab, and published the result. That is method appetite rather than the purchase of a new method.</t>
+        </is>
+      </c>
       <c r="O137" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -14994,19 +15366,31 @@
           <t>Partly</t>
         </is>
       </c>
-      <c r="J138" s="15" t="inlineStr"/>
+      <c r="J138" s="15" t="inlineStr">
+        <is>
+          <t>Eight divisions across commercial, retail, healthcare and multifamily. The buildings differ project to project.</t>
+        </is>
+      </c>
       <c r="K138" s="14" t="inlineStr">
         <is>
           <t>Partly</t>
         </is>
       </c>
-      <c r="L138" s="15" t="inlineStr"/>
+      <c r="L138" s="15" t="inlineStr">
+        <is>
+          <t>No annual volume is published. The one published job runs to 770,640 square feet, and the panels on it were poured by somebody else.</t>
+        </is>
+      </c>
       <c r="M138" s="14" t="inlineStr">
         <is>
           <t>Partly</t>
         </is>
       </c>
-      <c r="N138" s="15" t="inlineStr"/>
+      <c r="N138" s="15" t="inlineStr">
+        <is>
+          <t>It reordered the standard tilt-wall sequence on a 770,640 square foot job, setting a 275-ton lattice boom crane on the perimeter to avoid the slab, and published the result. That is method appetite rather than the purchase of a new method.</t>
+        </is>
+      </c>
       <c r="O138" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -15082,19 +15466,31 @@
           <t>Partly</t>
         </is>
       </c>
-      <c r="J139" s="9" t="inlineStr"/>
+      <c r="J139" s="9" t="inlineStr">
+        <is>
+          <t>Commercial and institutional work rather than a repeated plan, so the structure changes project to project.</t>
+        </is>
+      </c>
       <c r="K139" s="8" t="inlineStr">
         <is>
           <t>Partly</t>
         </is>
       </c>
-      <c r="L139" s="9" t="inlineStr"/>
+      <c r="L139" s="9" t="inlineStr">
+        <is>
+          <t>No crew count, revenue or annual volume is published. On the bands, a firm with no published figure is a Partly.</t>
+        </is>
+      </c>
       <c r="M139" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N139" s="9" t="inlineStr"/>
+      <c r="N139" s="9" t="inlineStr">
+        <is>
+          <t>No method statement on record. Owning the equipment and the crews is not the same as having paid for a method that was new at the time.</t>
+        </is>
+      </c>
       <c r="O139" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -15171,19 +15567,31 @@
           <t>Partly</t>
         </is>
       </c>
-      <c r="J140" s="15" t="inlineStr"/>
+      <c r="J140" s="15" t="inlineStr">
+        <is>
+          <t>Commercial and multifamily work across four metros. The buildings differ project to project.</t>
+        </is>
+      </c>
       <c r="K140" s="14" t="inlineStr">
         <is>
           <t>Partly</t>
         </is>
       </c>
-      <c r="L140" s="15" t="inlineStr"/>
+      <c r="L140" s="15" t="inlineStr">
+        <is>
+          <t>No revenue, crew count or project size is published. On the bands, a firm with no published figure is a Partly.</t>
+        </is>
+      </c>
       <c r="M140" s="14" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N140" s="15" t="inlineStr"/>
+      <c r="N140" s="15" t="inlineStr">
+        <is>
+          <t>No method statement on record. The tilt-up award is for execution.</t>
+        </is>
+      </c>
       <c r="O140" s="14" t="inlineStr">
         <is>
           <t>Partly</t>
@@ -15319,7 +15727,7 @@
       </c>
       <c r="U141" s="9" t="inlineStr">
         <is>
-          <t>The Mill square footage and unit count cross-checked across two sources with differing detail. Treat figures as approximate. | The Mill is the hybrid precedent. A 75,000 square foot six-storey office frame in cross-laminated timber, reported as one of Houston's first, alongside 340 apartments and a 14,000 square foot 1890s brick building kept and folded into the new structure. Michael Hsu and EDI on design. One team ran an unproven structural system and an adaptive reuse on the same six-acre site. | Triten and Radom Capital are the same pair across the Heights packing-plant cluster, M-K-T and the Swift BLDG.  | Triten's construction staff below Larry Sloan are construction managers. A Chief Construction Officer is titled to Triten Corporation, a separate Houston company sharing the name. The relationship between the two is unresolved. | No capital signal carries a dollar figure. M-K-T Heights price undisclosed. | LinkedIn URLs unsourced for all four principals.</t>
+          <t>The Mill square footage and unit count cross-checked across two sources with differing detail. Treat figures as approximate. | The Mill is the hybrid precedent. A 75,000 square foot six-storey office frame in cross-laminated timber, reported as one of Houston's first, alongside 340 apartments and a 14,000 square foot 1890s brick building kept and folded into the new structure. Michael Hsu and EDI on design. One team ran an unproven structural system and an adaptive reuse on the same six-acre site. | Triten and Radom Capital are the same pair across the Heights packing-plant cluster, M-K-T and the Swift BLDG. | Triten's construction staff below Larry Sloan are construction managers. A Chief Construction Officer is titled to Triten Corporation, a separate Houston company sharing the name. The relationship between the two is unresolved. | No capital signal carries a dollar figure. M-K-T Heights price undisclosed. | LinkedIn URLs unsourced for all four principals.</t>
         </is>
       </c>
       <c r="V141" s="6" t="inlineStr"/>
@@ -15436,7 +15844,7 @@
       </c>
       <c r="U142" s="15" t="inlineStr">
         <is>
-          <t>The Mill square footage and unit count cross-checked across two sources with differing detail. Treat figures as approximate. | The Mill is the hybrid precedent. A 75,000 square foot six-storey office frame in cross-laminated timber, reported as one of Houston's first, alongside 340 apartments and a 14,000 square foot 1890s brick building kept and folded into the new structure. Michael Hsu and EDI on design. One team ran an unproven structural system and an adaptive reuse on the same six-acre site. | Triten and Radom Capital are the same pair across the Heights packing-plant cluster, M-K-T and the Swift BLDG.  | Triten's construction staff below Larry Sloan are construction managers. A Chief Construction Officer is titled to Triten Corporation, a separate Houston company sharing the name. The relationship between the two is unresolved. | No capital signal carries a dollar figure. M-K-T Heights price undisclosed. | LinkedIn URLs unsourced for all four principals.</t>
+          <t>The Mill square footage and unit count cross-checked across two sources with differing detail. Treat figures as approximate. | The Mill is the hybrid precedent. A 75,000 square foot six-storey office frame in cross-laminated timber, reported as one of Houston's first, alongside 340 apartments and a 14,000 square foot 1890s brick building kept and folded into the new structure. Michael Hsu and EDI on design. One team ran an unproven structural system and an adaptive reuse on the same six-acre site. | Triten and Radom Capital are the same pair across the Heights packing-plant cluster, M-K-T and the Swift BLDG. | Triten's construction staff below Larry Sloan are construction managers. A Chief Construction Officer is titled to Triten Corporation, a separate Houston company sharing the name. The relationship between the two is unresolved. | No capital signal carries a dollar figure. M-K-T Heights price undisclosed. | LinkedIn URLs unsourced for all four principals.</t>
         </is>
       </c>
       <c r="V142" s="12" t="inlineStr"/>
@@ -15553,7 +15961,7 @@
       </c>
       <c r="U143" s="9" t="inlineStr">
         <is>
-          <t>The Mill square footage and unit count cross-checked across two sources with differing detail. Treat figures as approximate. | The Mill is the hybrid precedent. A 75,000 square foot six-storey office frame in cross-laminated timber, reported as one of Houston's first, alongside 340 apartments and a 14,000 square foot 1890s brick building kept and folded into the new structure. Michael Hsu and EDI on design. One team ran an unproven structural system and an adaptive reuse on the same six-acre site. | Triten and Radom Capital are the same pair across the Heights packing-plant cluster, M-K-T and the Swift BLDG.  | Triten's construction staff below Larry Sloan are construction managers. A Chief Construction Officer is titled to Triten Corporation, a separate Houston company sharing the name. The relationship between the two is unresolved. | No capital signal carries a dollar figure. M-K-T Heights price undisclosed. | LinkedIn URLs unsourced for all four principals.</t>
+          <t>The Mill square footage and unit count cross-checked across two sources with differing detail. Treat figures as approximate. | The Mill is the hybrid precedent. A 75,000 square foot six-storey office frame in cross-laminated timber, reported as one of Houston's first, alongside 340 apartments and a 14,000 square foot 1890s brick building kept and folded into the new structure. Michael Hsu and EDI on design. One team ran an unproven structural system and an adaptive reuse on the same six-acre site. | Triten and Radom Capital are the same pair across the Heights packing-plant cluster, M-K-T and the Swift BLDG. | Triten's construction staff below Larry Sloan are construction managers. A Chief Construction Officer is titled to Triten Corporation, a separate Houston company sharing the name. The relationship between the two is unresolved. | No capital signal carries a dollar figure. M-K-T Heights price undisclosed. | LinkedIn URLs unsourced for all four principals.</t>
         </is>
       </c>
       <c r="V143" s="6" t="inlineStr"/>
@@ -15669,7 +16077,7 @@
       </c>
       <c r="U144" s="15" t="inlineStr">
         <is>
-          <t>The Mill square footage and unit count cross-checked across two sources with differing detail. Treat figures as approximate. | The Mill is the hybrid precedent. A 75,000 square foot six-storey office frame in cross-laminated timber, reported as one of Houston's first, alongside 340 apartments and a 14,000 square foot 1890s brick building kept and folded into the new structure. Michael Hsu and EDI on design. One team ran an unproven structural system and an adaptive reuse on the same six-acre site. | Triten and Radom Capital are the same pair across the Heights packing-plant cluster, M-K-T and the Swift BLDG.  | Triten's construction staff below Larry Sloan are construction managers. A Chief Construction Officer is titled to Triten Corporation, a separate Houston company sharing the name. The relationship between the two is unresolved. | No capital signal carries a dollar figure. M-K-T Heights price undisclosed. | LinkedIn URLs unsourced for all four principals.</t>
+          <t>The Mill square footage and unit count cross-checked across two sources with differing detail. Treat figures as approximate. | The Mill is the hybrid precedent. A 75,000 square foot six-storey office frame in cross-laminated timber, reported as one of Houston's first, alongside 340 apartments and a 14,000 square foot 1890s brick building kept and folded into the new structure. Michael Hsu and EDI on design. One team ran an unproven structural system and an adaptive reuse on the same six-acre site. | Triten and Radom Capital are the same pair across the Heights packing-plant cluster, M-K-T and the Swift BLDG. | Triten's construction staff below Larry Sloan are construction managers. A Chief Construction Officer is titled to Triten Corporation, a separate Houston company sharing the name. The relationship between the two is unresolved. | No capital signal carries a dollar figure. M-K-T Heights price undisclosed. | LinkedIn URLs unsourced for all four principals.</t>
         </is>
       </c>
       <c r="V144" s="12" t="inlineStr"/>
@@ -22473,7 +22881,11 @@
           <t>Houston / Katy, Harris-Waller</t>
         </is>
       </c>
-      <c r="H203" s="6" t="inlineStr"/>
+      <c r="H203" s="6" t="inlineStr">
+        <is>
+          <t>Sunterra, 2,303 acres in Katy, fifteen builders</t>
+        </is>
+      </c>
       <c r="I203" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -22573,7 +22985,11 @@
           <t>Houston / Katy, Harris-Waller</t>
         </is>
       </c>
-      <c r="H204" s="12" t="inlineStr"/>
+      <c r="H204" s="12" t="inlineStr">
+        <is>
+          <t>Sunterra, 2,303 acres in Katy, fifteen builders</t>
+        </is>
+      </c>
       <c r="I204" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -22673,7 +23089,11 @@
           <t>Cypress / Montgomery, Harris</t>
         </is>
       </c>
-      <c r="H205" s="6" t="inlineStr"/>
+      <c r="H205" s="6" t="inlineStr">
+        <is>
+          <t>Towne Lake and The Highlands, about 4,000 homes</t>
+        </is>
+      </c>
       <c r="I205" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -22777,7 +23197,11 @@
           <t>Houston / Fort Bend, Montgomery</t>
         </is>
       </c>
-      <c r="H206" s="12" t="inlineStr"/>
+      <c r="H206" s="12" t="inlineStr">
+        <is>
+          <t>Fourteen concurrent Houston masterplans</t>
+        </is>
+      </c>
       <c r="I206" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -22881,7 +23305,11 @@
           <t>San Diego HQ / Katy, Harris</t>
         </is>
       </c>
-      <c r="H207" s="6" t="inlineStr"/>
+      <c r="H207" s="6" t="inlineStr">
+        <is>
+          <t>Elyson, 3,600 acres in Katy</t>
+        </is>
+      </c>
       <c r="I207" s="8" t="inlineStr">
         <is>
           <t>Partly</t>
@@ -23090,7 +23518,11 @@
           <t>Houston / Montgomery, Galveston</t>
         </is>
       </c>
-      <c r="H209" s="6" t="inlineStr"/>
+      <c r="H209" s="6" t="inlineStr">
+        <is>
+          <t>Sells lots inside its own masterplans; Lennar builds</t>
+        </is>
+      </c>
       <c r="I209" s="8" t="inlineStr">
         <is>
           <t>Partly</t>
@@ -26570,7 +27002,7 @@
     <row r="243">
       <c r="A243" s="17" t="inlineStr">
         <is>
-          <t>NOTE. A filled LinkedIn cell means the profile was opened or the search result read and the headline named the firm; column W records what was read. Where that test failed the cell is left empty rather than guessed, because a fabricated slug passes visual inspection and then fails in front of the person it names. Column Q searches for the empty ones in your own session. Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Capital is a qualifier, not a count. Source: ICON Greater Houston screen, build 35, 2026-09-11.</t>
+          <t>NOTE. A filled LinkedIn cell means the profile was opened or the search result read and the headline named the firm; column W records what was read. Where that test failed the cell is left empty rather than guessed, because a fabricated slug passes visual inspection and then fails in front of the person it names. Column Q searches for the empty ones in your own session. Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Capital is a qualifier, not a count. Source: ICON Greater Houston screen, build 36, 2026-09-11.</t>
         </is>
       </c>
     </row>

--- a/docs/ICON_Greater_Houston_Rolodex.xlsx
+++ b/docs/ICON_Greater_Houston_Rolodex.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contacts" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Contacts'!$A$6:$Z$267</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Contacts'!$A$6:$AA$267</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z269"/>
+  <dimension ref="A1:AA269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -553,6 +553,7 @@
     <col width="46" customWidth="1" min="24" max="24"/>
     <col width="42" customWidth="1" min="25" max="25"/>
     <col width="42" customWidth="1" min="26" max="26"/>
+    <col width="70" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -565,7 +566,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated from houston-data.json · build 39 · 2026-09-11 · public render. Do not hand-edit the HTML deck; it regenerates from the same file.</t>
+          <t>Generated from houston-data.json · build 40 · 2026-09-11 · public render. Do not hand-edit the HTML deck; it regenerates from the same file.</t>
         </is>
       </c>
     </row>
@@ -754,6 +755,11 @@
           <t>Leadership page</t>
         </is>
       </c>
+      <c r="AA6" s="5" t="inlineStr">
+        <is>
+          <t>Latest press</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -874,6 +880,11 @@
           <t>https://colekleinbuilders.com/about/</t>
         </is>
       </c>
+      <c r="AA7" s="6" t="inlineStr">
+        <is>
+          <t>2026-02 The Architect's Newspaper. Zuri Gardens, a 3D-printed Texas community, shows promise for attainable housing  https://www.archpaper.com/2026/02/zuri-gardens-3d-printed-texas-community/</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
@@ -994,6 +1005,11 @@
           <t>https://colekleinbuilders.com/about/</t>
         </is>
       </c>
+      <c r="AA8" s="12" t="inlineStr">
+        <is>
+          <t>2026-02 The Architect's Newspaper. Zuri Gardens, a 3D-printed Texas community, shows promise for attainable housing  https://www.archpaper.com/2026/02/zuri-gardens-3d-printed-texas-community/</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -1106,6 +1122,11 @@
       </c>
       <c r="Y9" s="6" t="inlineStr"/>
       <c r="Z9" s="6" t="inlineStr"/>
+      <c r="AA9" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-30 Intelligent Build.tech. Partnership to develop an innovative 3D-printed residential community  https://www.intelligentbuild.tech/2026/04/30/partnership-to-develop-an-innovative-3d-printed-residential-community/</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
@@ -1218,6 +1239,11 @@
       </c>
       <c r="Y10" s="12" t="inlineStr"/>
       <c r="Z10" s="12" t="inlineStr"/>
+      <c r="AA10" s="12" t="inlineStr">
+        <is>
+          <t>2026-04-22 Homes.com. Houston's 3D-printed housing push grows with two new developments  https://www.homes.com/news/houstons-3d-printed-housing-push-grows-with-two-new-developments/647676272/</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -1335,6 +1361,11 @@
           <t>https://wanbridge.com/leadership/</t>
         </is>
       </c>
+      <c r="AA11" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-25 Houston Chronicle. Why Houston's booming build-to-rent sector could slow  https://www.houstonchronicle.com/business/article/houston-build-to-rent-housing-21293194.php</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
@@ -1456,6 +1487,11 @@
           <t>https://wanbridge.com/leadership/</t>
         </is>
       </c>
+      <c r="AA12" s="12" t="inlineStr">
+        <is>
+          <t>2026-04-25 Houston Chronicle. Why Houston's booming build-to-rent sector could slow  https://www.houstonchronicle.com/business/article/houston-build-to-rent-housing-21293194.php</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -1577,6 +1613,11 @@
           <t>https://wanbridge.com/leadership/</t>
         </is>
       </c>
+      <c r="AA13" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-25 Houston Chronicle. Why Houston's booming build-to-rent sector could slow  https://www.houstonchronicle.com/business/article/houston-build-to-rent-housing-21293194.php</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
@@ -1694,6 +1735,7 @@
           <t>https://www.lovettcommercial.com/about</t>
         </is>
       </c>
+      <c r="AA14" s="12" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -1807,6 +1849,11 @@
       <c r="X15" s="6" t="inlineStr"/>
       <c r="Y15" s="6" t="inlineStr"/>
       <c r="Z15" s="6" t="inlineStr"/>
+      <c r="AA15" s="6" t="inlineStr">
+        <is>
+          <t>2013-10-30 Boxer Property. Boxer Announces Executive Leadership Changes, which is where the current titles come from and which puts engineering and construction under the president  https://www.boxerproperty.com/blog/roles-responsibilities-evolve-executives/</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
@@ -1920,6 +1967,11 @@
       <c r="X16" s="12" t="inlineStr"/>
       <c r="Y16" s="12" t="inlineStr"/>
       <c r="Z16" s="12" t="inlineStr"/>
+      <c r="AA16" s="12" t="inlineStr">
+        <is>
+          <t>2013-10-30 Boxer Property. Boxer Announces Executive Leadership Changes, which is where the current titles come from and which puts engineering and construction under the president  https://www.boxerproperty.com/blog/roles-responsibilities-evolve-executives/</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -2024,6 +2076,11 @@
       <c r="X17" s="6" t="inlineStr"/>
       <c r="Y17" s="6" t="inlineStr"/>
       <c r="Z17" s="6" t="inlineStr"/>
+      <c r="AA17" s="6" t="inlineStr">
+        <is>
+          <t>2013-10-30 Boxer Property. Boxer Announces Executive Leadership Changes, which is where the current titles come from and which puts engineering and construction under the president  https://www.boxerproperty.com/blog/roles-responsibilities-evolve-executives/</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
@@ -2128,6 +2185,11 @@
       <c r="X18" s="12" t="inlineStr"/>
       <c r="Y18" s="12" t="inlineStr"/>
       <c r="Z18" s="12" t="inlineStr"/>
+      <c r="AA18" s="12" t="inlineStr">
+        <is>
+          <t>2013-10-30 Boxer Property. Boxer Announces Executive Leadership Changes, which is where the current titles come from and which puts engineering and construction under the president  https://www.boxerproperty.com/blog/roles-responsibilities-evolve-executives/</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -2240,6 +2302,7 @@
       </c>
       <c r="Y19" s="6" t="inlineStr"/>
       <c r="Z19" s="6" t="inlineStr"/>
+      <c r="AA19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
@@ -2360,6 +2423,7 @@
           <t>https://investors.centurycommunities.com/governance/executive-management/default.aspx</t>
         </is>
       </c>
+      <c r="AA20" s="12" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -2477,6 +2541,7 @@
           <t>https://investors.centurycommunities.com/governance/executive-management/default.aspx</t>
         </is>
       </c>
+      <c r="AA21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
@@ -2597,6 +2662,11 @@
           <t>https://www.firstamericahomes.com/about/</t>
         </is>
       </c>
+      <c r="AA22" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-10 CEOWORLD magazine. Danny Signorelli Leads First America Homes Expansion Across Houston and Texas  https://ceoworld.biz/2026/08/10/danny-signorelli-leads-first-america-homes-expansion-across-houston-and-texas/</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -2714,6 +2784,11 @@
           <t>https://www.firstamericahomes.com/about/</t>
         </is>
       </c>
+      <c r="AA23" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10 CEOWORLD magazine. Danny Signorelli Leads First America Homes Expansion Across Houston and Texas  https://ceoworld.biz/2026/08/10/danny-signorelli-leads-first-america-homes-expansion-across-houston-and-texas/</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
@@ -2835,6 +2910,11 @@
           <t>https://www.firstamericahomes.com/about/</t>
         </is>
       </c>
+      <c r="AA24" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-10 CEOWORLD magazine. Danny Signorelli Leads First America Homes Expansion Across Houston and Texas  https://ceoworld.biz/2026/08/10/danny-signorelli-leads-first-america-homes-expansion-across-houston-and-texas/</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -2956,6 +3036,11 @@
           <t>https://www.firstamericahomes.com/about/</t>
         </is>
       </c>
+      <c r="AA25" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10 CEOWORLD magazine. Danny Signorelli Leads First America Homes Expansion Across Houston and Texas  https://ceoworld.biz/2026/08/10/danny-signorelli-leads-first-america-homes-expansion-across-houston-and-texas/</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
@@ -3073,6 +3158,11 @@
           <t>https://www.firstamericahomes.com/about/</t>
         </is>
       </c>
+      <c r="AA26" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-10 CEOWORLD magazine. Danny Signorelli Leads First America Homes Expansion Across Houston and Texas  https://ceoworld.biz/2026/08/10/danny-signorelli-leads-first-america-homes-expansion-across-houston-and-texas/</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -3186,6 +3276,11 @@
       </c>
       <c r="Y27" s="6" t="inlineStr"/>
       <c r="Z27" s="6" t="inlineStr"/>
+      <c r="AA27" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-24 Builder Magazine. How Stylecraft Is Building Bigger While Staying Local  https://www.builderonline.com/builder-100/leadership/how-stylecraft-is-building-bigger-while-staying-local/</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
@@ -3302,6 +3397,11 @@
       </c>
       <c r="Y28" s="12" t="inlineStr"/>
       <c r="Z28" s="12" t="inlineStr"/>
+      <c r="AA28" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-24 Builder Magazine. How Stylecraft Is Building Bigger While Staying Local  https://www.builderonline.com/builder-100/leadership/how-stylecraft-is-building-bigger-while-staying-local/</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -3419,6 +3519,11 @@
       </c>
       <c r="Y29" s="6" t="inlineStr"/>
       <c r="Z29" s="6" t="inlineStr"/>
+      <c r="AA29" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-24 Builder Magazine. How Stylecraft Is Building Bigger While Staying Local  https://www.builderonline.com/builder-100/leadership/how-stylecraft-is-building-bigger-while-staying-local/</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
@@ -3532,6 +3637,11 @@
       </c>
       <c r="Y30" s="12" t="inlineStr"/>
       <c r="Z30" s="12" t="inlineStr"/>
+      <c r="AA30" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-24 Builder Magazine. How Stylecraft Is Building Bigger While Staying Local  https://www.builderonline.com/builder-100/leadership/how-stylecraft-is-building-bigger-while-staying-local/</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -3640,6 +3750,7 @@
       <c r="X31" s="6" t="inlineStr"/>
       <c r="Y31" s="6" t="inlineStr"/>
       <c r="Z31" s="6" t="inlineStr"/>
+      <c r="AA31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
@@ -3744,6 +3855,7 @@
       <c r="X32" s="12" t="inlineStr"/>
       <c r="Y32" s="12" t="inlineStr"/>
       <c r="Z32" s="12" t="inlineStr"/>
+      <c r="AA32" s="12" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -3848,6 +3960,7 @@
       <c r="X33" s="6" t="inlineStr"/>
       <c r="Y33" s="6" t="inlineStr"/>
       <c r="Z33" s="6" t="inlineStr"/>
+      <c r="AA33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
@@ -3956,6 +4069,7 @@
       <c r="X34" s="12" t="inlineStr"/>
       <c r="Y34" s="12" t="inlineStr"/>
       <c r="Z34" s="12" t="inlineStr"/>
+      <c r="AA34" s="12" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -4076,6 +4190,7 @@
           <t>https://avenuecdc.org/about-us/board-staff/</t>
         </is>
       </c>
+      <c r="AA35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
@@ -4193,6 +4308,7 @@
           <t>https://avenuecdc.org/about-us/board-staff/</t>
         </is>
       </c>
+      <c r="AA36" s="12" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -4310,6 +4426,7 @@
           <t>https://avenuecdc.org/about-us/board-staff/</t>
         </is>
       </c>
+      <c r="AA37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
@@ -4431,6 +4548,7 @@
           <t>https://avenuecdc.org/about-us/board-staff/</t>
         </is>
       </c>
+      <c r="AA38" s="12" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -4548,6 +4666,7 @@
           <t>https://suebausa.com/about-us/</t>
         </is>
       </c>
+      <c r="AA39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
@@ -4668,6 +4787,7 @@
           <t>https://suebausa.com/about-us/</t>
         </is>
       </c>
+      <c r="AA40" s="12" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -4789,6 +4909,7 @@
           <t>https://suebausa.com/about-us/</t>
         </is>
       </c>
+      <c r="AA41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
@@ -4906,6 +5027,11 @@
         </is>
       </c>
       <c r="Z42" s="12" t="inlineStr"/>
+      <c r="AA42" s="12" t="inlineStr">
+        <is>
+          <t>Builder Magazine. Chesmar Homes, with the note that Sekisui House U.S. is the 2026 Builder of the Year  https://www.builderonline.com/organization/chesmar-homes/</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -5023,6 +5149,11 @@
         </is>
       </c>
       <c r="Z43" s="6" t="inlineStr"/>
+      <c r="AA43" s="6" t="inlineStr">
+        <is>
+          <t>Builder Magazine. Chesmar Homes, with the note that Sekisui House U.S. is the 2026 Builder of the Year  https://www.builderonline.com/organization/chesmar-homes/</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
@@ -5140,6 +5271,11 @@
         </is>
       </c>
       <c r="Z44" s="12" t="inlineStr"/>
+      <c r="AA44" s="12" t="inlineStr">
+        <is>
+          <t>Builder Magazine. Chesmar Homes, with the note that Sekisui House U.S. is the 2026 Builder of the Year  https://www.builderonline.com/organization/chesmar-homes/</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -5252,6 +5388,7 @@
       </c>
       <c r="Y45" s="6" t="inlineStr"/>
       <c r="Z45" s="6" t="inlineStr"/>
+      <c r="AA45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
@@ -5364,6 +5501,7 @@
       </c>
       <c r="Y46" s="12" t="inlineStr"/>
       <c r="Z46" s="12" t="inlineStr"/>
+      <c r="AA46" s="12" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -5476,6 +5614,7 @@
       </c>
       <c r="Y47" s="6" t="inlineStr"/>
       <c r="Z47" s="6" t="inlineStr"/>
+      <c r="AA47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
@@ -5588,6 +5727,7 @@
       </c>
       <c r="Y48" s="12" t="inlineStr"/>
       <c r="Z48" s="12" t="inlineStr"/>
+      <c r="AA48" s="12" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
@@ -5704,6 +5844,7 @@
       </c>
       <c r="Y49" s="6" t="inlineStr"/>
       <c r="Z49" s="6" t="inlineStr"/>
+      <c r="AA49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
@@ -5813,6 +5954,7 @@
       <c r="X50" s="12" t="inlineStr"/>
       <c r="Y50" s="12" t="inlineStr"/>
       <c r="Z50" s="12" t="inlineStr"/>
+      <c r="AA50" s="12" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -5926,6 +6068,7 @@
       <c r="X51" s="6" t="inlineStr"/>
       <c r="Y51" s="6" t="inlineStr"/>
       <c r="Z51" s="6" t="inlineStr"/>
+      <c r="AA51" s="6" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
@@ -6035,6 +6178,7 @@
       <c r="X52" s="12" t="inlineStr"/>
       <c r="Y52" s="12" t="inlineStr"/>
       <c r="Z52" s="12" t="inlineStr"/>
+      <c r="AA52" s="12" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
@@ -6155,6 +6299,7 @@
           <t>https://housingforhouston.com/leadership/executive-leadership/</t>
         </is>
       </c>
+      <c r="AA53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
@@ -6276,6 +6421,7 @@
           <t>https://housingforhouston.com/leadership/executive-leadership/</t>
         </is>
       </c>
+      <c r="AA54" s="12" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
@@ -6393,6 +6539,7 @@
           <t>https://investors.meritagehomes.com/company-information/management-team</t>
         </is>
       </c>
+      <c r="AA55" s="6" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
@@ -6513,6 +6660,7 @@
           <t>https://investors.meritagehomes.com/company-information/management-team</t>
         </is>
       </c>
+      <c r="AA56" s="12" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
@@ -6633,6 +6781,7 @@
           <t>https://investors.meritagehomes.com/company-information/management-team</t>
         </is>
       </c>
+      <c r="AA57" s="6" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
@@ -6754,6 +6903,7 @@
           <t>https://investors.meritagehomes.com/company-information/management-team</t>
         </is>
       </c>
+      <c r="AA58" s="12" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
@@ -6871,6 +7021,7 @@
           <t>https://investors.meritagehomes.com/company-information/management-team</t>
         </is>
       </c>
+      <c r="AA59" s="6" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="12" t="inlineStr">
@@ -6988,6 +7139,7 @@
           <t>https://investors.meritagehomes.com/company-information/management-team</t>
         </is>
       </c>
+      <c r="AA60" s="12" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
@@ -7100,6 +7252,7 @@
       </c>
       <c r="Y61" s="6" t="inlineStr"/>
       <c r="Z61" s="6" t="inlineStr"/>
+      <c r="AA61" s="6" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
@@ -7220,6 +7373,7 @@
           <t>https://www.camillocompanies.com/about-us</t>
         </is>
       </c>
+      <c r="AA62" s="12" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
@@ -7340,6 +7494,7 @@
           <t>https://www.camillocompanies.com/about-us</t>
         </is>
       </c>
+      <c r="AA63" s="6" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="12" t="inlineStr">
@@ -7460,6 +7615,7 @@
           <t>https://www.camillocompanies.com/about-us</t>
         </is>
       </c>
+      <c r="AA64" s="12" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
@@ -7580,6 +7736,7 @@
           <t>https://www.camillocompanies.com/about-us</t>
         </is>
       </c>
+      <c r="AA65" s="6" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="12" t="inlineStr">
@@ -7700,6 +7857,7 @@
           <t>https://www.c-rock.com/about</t>
         </is>
       </c>
+      <c r="AA66" s="12" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
@@ -7817,6 +7975,7 @@
           <t>https://www.c-rock.com/about</t>
         </is>
       </c>
+      <c r="AA67" s="6" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="12" t="inlineStr">
@@ -7934,6 +8093,7 @@
           <t>https://www.c-rock.com/about</t>
         </is>
       </c>
+      <c r="AA68" s="12" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
@@ -8054,6 +8214,7 @@
           <t>https://www.christophertodd.com/our-story/</t>
         </is>
       </c>
+      <c r="AA69" s="6" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="12" t="inlineStr">
@@ -8174,6 +8335,7 @@
           <t>https://www.christophertodd.com/our-story/</t>
         </is>
       </c>
+      <c r="AA70" s="12" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
@@ -8282,6 +8444,7 @@
       <c r="X71" s="6" t="inlineStr"/>
       <c r="Y71" s="6" t="inlineStr"/>
       <c r="Z71" s="6" t="inlineStr"/>
+      <c r="AA71" s="6" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="12" t="inlineStr">
@@ -8390,6 +8553,7 @@
       <c r="X72" s="12" t="inlineStr"/>
       <c r="Y72" s="12" t="inlineStr"/>
       <c r="Z72" s="12" t="inlineStr"/>
+      <c r="AA72" s="12" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
@@ -8487,6 +8651,7 @@
       <c r="X73" s="6" t="inlineStr"/>
       <c r="Y73" s="6" t="inlineStr"/>
       <c r="Z73" s="6" t="inlineStr"/>
+      <c r="AA73" s="6" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="12" t="inlineStr">
@@ -8595,6 +8760,7 @@
       <c r="X74" s="12" t="inlineStr"/>
       <c r="Y74" s="12" t="inlineStr"/>
       <c r="Z74" s="12" t="inlineStr"/>
+      <c r="AA74" s="12" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
@@ -8699,6 +8865,7 @@
       <c r="X75" s="6" t="inlineStr"/>
       <c r="Y75" s="6" t="inlineStr"/>
       <c r="Z75" s="6" t="inlineStr"/>
+      <c r="AA75" s="6" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="12" t="inlineStr">
@@ -8796,6 +8963,7 @@
       <c r="X76" s="12" t="inlineStr"/>
       <c r="Y76" s="12" t="inlineStr"/>
       <c r="Z76" s="12" t="inlineStr"/>
+      <c r="AA76" s="12" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
@@ -8905,6 +9073,7 @@
       <c r="X77" s="6" t="inlineStr"/>
       <c r="Y77" s="6" t="inlineStr"/>
       <c r="Z77" s="6" t="inlineStr"/>
+      <c r="AA77" s="6" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="12" t="inlineStr">
@@ -9013,6 +9182,7 @@
       <c r="X78" s="12" t="inlineStr"/>
       <c r="Y78" s="12" t="inlineStr"/>
       <c r="Z78" s="12" t="inlineStr"/>
+      <c r="AA78" s="12" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
@@ -9117,6 +9287,7 @@
       <c r="X79" s="6" t="inlineStr"/>
       <c r="Y79" s="6" t="inlineStr"/>
       <c r="Z79" s="6" t="inlineStr"/>
+      <c r="AA79" s="6" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="12" t="inlineStr">
@@ -9229,6 +9400,7 @@
       </c>
       <c r="Y80" s="12" t="inlineStr"/>
       <c r="Z80" s="12" t="inlineStr"/>
+      <c r="AA80" s="12" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
@@ -9342,6 +9514,7 @@
       <c r="X81" s="6" t="inlineStr"/>
       <c r="Y81" s="6" t="inlineStr"/>
       <c r="Z81" s="6" t="inlineStr"/>
+      <c r="AA81" s="6" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="12" t="inlineStr">
@@ -9454,6 +9627,7 @@
       </c>
       <c r="Y82" s="12" t="inlineStr"/>
       <c r="Z82" s="12" t="inlineStr"/>
+      <c r="AA82" s="12" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
@@ -9567,6 +9741,7 @@
       </c>
       <c r="Y83" s="6" t="inlineStr"/>
       <c r="Z83" s="6" t="inlineStr"/>
+      <c r="AA83" s="6" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="12" t="inlineStr">
@@ -9679,6 +9854,7 @@
       </c>
       <c r="Y84" s="12" t="inlineStr"/>
       <c r="Z84" s="12" t="inlineStr"/>
+      <c r="AA84" s="12" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
@@ -9791,6 +9967,7 @@
       </c>
       <c r="Y85" s="6" t="inlineStr"/>
       <c r="Z85" s="6" t="inlineStr"/>
+      <c r="AA85" s="6" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="12" t="inlineStr">
@@ -9908,6 +10085,7 @@
       </c>
       <c r="Y86" s="12" t="inlineStr"/>
       <c r="Z86" s="12" t="inlineStr"/>
+      <c r="AA86" s="12" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
@@ -10021,6 +10199,7 @@
       </c>
       <c r="Y87" s="6" t="inlineStr"/>
       <c r="Z87" s="6" t="inlineStr"/>
+      <c r="AA87" s="6" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="12" t="inlineStr">
@@ -10125,6 +10304,7 @@
       <c r="X88" s="12" t="inlineStr"/>
       <c r="Y88" s="12" t="inlineStr"/>
       <c r="Z88" s="12" t="inlineStr"/>
+      <c r="AA88" s="12" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
@@ -10229,6 +10409,7 @@
       <c r="X89" s="6" t="inlineStr"/>
       <c r="Y89" s="6" t="inlineStr"/>
       <c r="Z89" s="6" t="inlineStr"/>
+      <c r="AA89" s="6" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="12" t="inlineStr">
@@ -10342,6 +10523,7 @@
       <c r="X90" s="12" t="inlineStr"/>
       <c r="Y90" s="12" t="inlineStr"/>
       <c r="Z90" s="12" t="inlineStr"/>
+      <c r="AA90" s="12" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
@@ -10462,6 +10644,7 @@
           <t>https://provident.net/our-team/</t>
         </is>
       </c>
+      <c r="AA91" s="6" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="12" t="inlineStr">
@@ -10582,6 +10765,7 @@
           <t>https://provident.net/our-team/</t>
         </is>
       </c>
+      <c r="AA92" s="12" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
@@ -10695,6 +10879,7 @@
       </c>
       <c r="Y93" s="6" t="inlineStr"/>
       <c r="Z93" s="6" t="inlineStr"/>
+      <c r="AA93" s="6" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="12" t="inlineStr">
@@ -10808,6 +10993,7 @@
       </c>
       <c r="Y94" s="12" t="inlineStr"/>
       <c r="Z94" s="12" t="inlineStr"/>
+      <c r="AA94" s="12" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
@@ -10921,6 +11107,7 @@
         </is>
       </c>
       <c r="Z95" s="6" t="inlineStr"/>
+      <c r="AA95" s="6" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="12" t="inlineStr">
@@ -11034,6 +11221,7 @@
         </is>
       </c>
       <c r="Z96" s="12" t="inlineStr"/>
+      <c r="AA96" s="12" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
@@ -11146,6 +11334,7 @@
       </c>
       <c r="Y97" s="6" t="inlineStr"/>
       <c r="Z97" s="6" t="inlineStr"/>
+      <c r="AA97" s="6" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="12" t="inlineStr">
@@ -11255,6 +11444,7 @@
       <c r="X98" s="12" t="inlineStr"/>
       <c r="Y98" s="12" t="inlineStr"/>
       <c r="Z98" s="12" t="inlineStr"/>
+      <c r="AA98" s="12" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
@@ -11359,6 +11549,7 @@
       <c r="X99" s="6" t="inlineStr"/>
       <c r="Y99" s="6" t="inlineStr"/>
       <c r="Z99" s="6" t="inlineStr"/>
+      <c r="AA99" s="6" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="12" t="inlineStr">
@@ -11468,6 +11659,7 @@
       <c r="X100" s="12" t="inlineStr"/>
       <c r="Y100" s="12" t="inlineStr"/>
       <c r="Z100" s="12" t="inlineStr"/>
+      <c r="AA100" s="12" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
@@ -11580,6 +11772,7 @@
       </c>
       <c r="Y101" s="6" t="inlineStr"/>
       <c r="Z101" s="6" t="inlineStr"/>
+      <c r="AA101" s="6" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="12" t="inlineStr">
@@ -11684,6 +11877,7 @@
       <c r="X102" s="12" t="inlineStr"/>
       <c r="Y102" s="12" t="inlineStr"/>
       <c r="Z102" s="12" t="inlineStr"/>
+      <c r="AA102" s="12" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
@@ -11797,6 +11991,7 @@
       <c r="X103" s="6" t="inlineStr"/>
       <c r="Y103" s="6" t="inlineStr"/>
       <c r="Z103" s="6" t="inlineStr"/>
+      <c r="AA103" s="6" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="12" t="inlineStr">
@@ -11901,6 +12096,7 @@
       <c r="X104" s="12" t="inlineStr"/>
       <c r="Y104" s="12" t="inlineStr"/>
       <c r="Z104" s="12" t="inlineStr"/>
+      <c r="AA104" s="12" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
@@ -12017,6 +12213,7 @@
           <t>https://rskrealestatepartners.com/our-team/</t>
         </is>
       </c>
+      <c r="AA105" s="6" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="12" t="inlineStr">
@@ -12137,6 +12334,7 @@
           <t>https://rskrealestatepartners.com/our-team/</t>
         </is>
       </c>
+      <c r="AA106" s="12" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
@@ -12253,6 +12451,7 @@
           <t>https://rskrealestatepartners.com/our-team/</t>
         </is>
       </c>
+      <c r="AA107" s="6" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="12" t="inlineStr">
@@ -12362,6 +12561,7 @@
       <c r="X108" s="12" t="inlineStr"/>
       <c r="Y108" s="12" t="inlineStr"/>
       <c r="Z108" s="12" t="inlineStr"/>
+      <c r="AA108" s="12" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
@@ -12470,6 +12670,7 @@
       <c r="X109" s="6" t="inlineStr"/>
       <c r="Y109" s="6" t="inlineStr"/>
       <c r="Z109" s="6" t="inlineStr"/>
+      <c r="AA109" s="6" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="12" t="inlineStr">
@@ -12583,6 +12784,7 @@
       <c r="X110" s="12" t="inlineStr"/>
       <c r="Y110" s="12" t="inlineStr"/>
       <c r="Z110" s="12" t="inlineStr"/>
+      <c r="AA110" s="12" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
@@ -12696,6 +12898,7 @@
       <c r="X111" s="6" t="inlineStr"/>
       <c r="Y111" s="6" t="inlineStr"/>
       <c r="Z111" s="6" t="inlineStr"/>
+      <c r="AA111" s="6" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="12" t="inlineStr">
@@ -12804,6 +13007,7 @@
       <c r="X112" s="12" t="inlineStr"/>
       <c r="Y112" s="12" t="inlineStr"/>
       <c r="Z112" s="12" t="inlineStr"/>
+      <c r="AA112" s="12" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="6" t="inlineStr">
@@ -12917,6 +13121,7 @@
       <c r="X113" s="6" t="inlineStr"/>
       <c r="Y113" s="6" t="inlineStr"/>
       <c r="Z113" s="6" t="inlineStr"/>
+      <c r="AA113" s="6" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="12" t="inlineStr">
@@ -13030,6 +13235,7 @@
       <c r="X114" s="12" t="inlineStr"/>
       <c r="Y114" s="12" t="inlineStr"/>
       <c r="Z114" s="12" t="inlineStr"/>
+      <c r="AA114" s="12" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="6" t="inlineStr">
@@ -13143,6 +13349,7 @@
       <c r="X115" s="6" t="inlineStr"/>
       <c r="Y115" s="6" t="inlineStr"/>
       <c r="Z115" s="6" t="inlineStr"/>
+      <c r="AA115" s="6" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="12" t="inlineStr">
@@ -13256,6 +13463,7 @@
       <c r="X116" s="12" t="inlineStr"/>
       <c r="Y116" s="12" t="inlineStr"/>
       <c r="Z116" s="12" t="inlineStr"/>
+      <c r="AA116" s="12" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="6" t="inlineStr">
@@ -13369,6 +13577,7 @@
       <c r="X117" s="6" t="inlineStr"/>
       <c r="Y117" s="6" t="inlineStr"/>
       <c r="Z117" s="6" t="inlineStr"/>
+      <c r="AA117" s="6" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="12" t="inlineStr">
@@ -13477,6 +13686,7 @@
       <c r="X118" s="12" t="inlineStr"/>
       <c r="Y118" s="12" t="inlineStr"/>
       <c r="Z118" s="12" t="inlineStr"/>
+      <c r="AA118" s="12" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="6" t="inlineStr">
@@ -13585,6 +13795,7 @@
       <c r="X119" s="6" t="inlineStr"/>
       <c r="Y119" s="6" t="inlineStr"/>
       <c r="Z119" s="6" t="inlineStr"/>
+      <c r="AA119" s="6" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="12" t="inlineStr">
@@ -13689,6 +13900,7 @@
       <c r="X120" s="12" t="inlineStr"/>
       <c r="Y120" s="12" t="inlineStr"/>
       <c r="Z120" s="12" t="inlineStr"/>
+      <c r="AA120" s="12" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="6" t="inlineStr">
@@ -13802,6 +14014,7 @@
       <c r="X121" s="6" t="inlineStr"/>
       <c r="Y121" s="6" t="inlineStr"/>
       <c r="Z121" s="6" t="inlineStr"/>
+      <c r="AA121" s="6" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="12" t="inlineStr">
@@ -13915,6 +14128,7 @@
       <c r="X122" s="12" t="inlineStr"/>
       <c r="Y122" s="12" t="inlineStr"/>
       <c r="Z122" s="12" t="inlineStr"/>
+      <c r="AA122" s="12" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="6" t="inlineStr">
@@ -14024,6 +14238,7 @@
       <c r="X123" s="6" t="inlineStr"/>
       <c r="Y123" s="6" t="inlineStr"/>
       <c r="Z123" s="6" t="inlineStr"/>
+      <c r="AA123" s="6" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="12" t="inlineStr">
@@ -14137,6 +14352,11 @@
       <c r="X124" s="12" t="inlineStr"/>
       <c r="Y124" s="12" t="inlineStr"/>
       <c r="Z124" s="12" t="inlineStr"/>
+      <c r="AA124" s="12" t="inlineStr">
+        <is>
+          <t>2025-03 Construction In Focus. CIVE, Construction and Design at their Finest  https://constructioninfocus.com/2025/03/cive-construction-and-design-at-their-finest/</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="6" t="inlineStr">
@@ -14250,6 +14470,11 @@
       <c r="X125" s="6" t="inlineStr"/>
       <c r="Y125" s="6" t="inlineStr"/>
       <c r="Z125" s="6" t="inlineStr"/>
+      <c r="AA125" s="6" t="inlineStr">
+        <is>
+          <t>2025-03 Construction In Focus. CIVE, Construction and Design at their Finest  https://constructioninfocus.com/2025/03/cive-construction-and-design-at-their-finest/</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="12" t="inlineStr">
@@ -14358,6 +14583,11 @@
       <c r="X126" s="12" t="inlineStr"/>
       <c r="Y126" s="12" t="inlineStr"/>
       <c r="Z126" s="12" t="inlineStr"/>
+      <c r="AA126" s="12" t="inlineStr">
+        <is>
+          <t>2025-03 Construction In Focus. CIVE, Construction and Design at their Finest  https://constructioninfocus.com/2025/03/cive-construction-and-design-at-their-finest/</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="6" t="inlineStr">
@@ -14471,6 +14701,7 @@
       <c r="X127" s="6" t="inlineStr"/>
       <c r="Y127" s="6" t="inlineStr"/>
       <c r="Z127" s="6" t="inlineStr"/>
+      <c r="AA127" s="6" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="12" t="inlineStr">
@@ -14584,6 +14815,7 @@
       <c r="X128" s="12" t="inlineStr"/>
       <c r="Y128" s="12" t="inlineStr"/>
       <c r="Z128" s="12" t="inlineStr"/>
+      <c r="AA128" s="12" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="6" t="inlineStr">
@@ -14688,6 +14920,7 @@
       <c r="X129" s="6" t="inlineStr"/>
       <c r="Y129" s="6" t="inlineStr"/>
       <c r="Z129" s="6" t="inlineStr"/>
+      <c r="AA129" s="6" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="12" t="inlineStr">
@@ -14792,6 +15025,7 @@
       <c r="X130" s="12" t="inlineStr"/>
       <c r="Y130" s="12" t="inlineStr"/>
       <c r="Z130" s="12" t="inlineStr"/>
+      <c r="AA130" s="12" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="6" t="inlineStr">
@@ -14896,6 +15130,7 @@
       <c r="X131" s="6" t="inlineStr"/>
       <c r="Y131" s="6" t="inlineStr"/>
       <c r="Z131" s="6" t="inlineStr"/>
+      <c r="AA131" s="6" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="12" t="inlineStr">
@@ -15000,6 +15235,7 @@
       <c r="X132" s="12" t="inlineStr"/>
       <c r="Y132" s="12" t="inlineStr"/>
       <c r="Z132" s="12" t="inlineStr"/>
+      <c r="AA132" s="12" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="6" t="inlineStr">
@@ -15104,6 +15340,7 @@
       <c r="X133" s="6" t="inlineStr"/>
       <c r="Y133" s="6" t="inlineStr"/>
       <c r="Z133" s="6" t="inlineStr"/>
+      <c r="AA133" s="6" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="12" t="inlineStr">
@@ -15208,6 +15445,7 @@
       <c r="X134" s="12" t="inlineStr"/>
       <c r="Y134" s="12" t="inlineStr"/>
       <c r="Z134" s="12" t="inlineStr"/>
+      <c r="AA134" s="12" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="6" t="inlineStr">
@@ -15312,6 +15550,7 @@
       <c r="X135" s="6" t="inlineStr"/>
       <c r="Y135" s="6" t="inlineStr"/>
       <c r="Z135" s="6" t="inlineStr"/>
+      <c r="AA135" s="6" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="12" t="inlineStr">
@@ -15420,6 +15659,7 @@
       <c r="X136" s="12" t="inlineStr"/>
       <c r="Y136" s="12" t="inlineStr"/>
       <c r="Z136" s="12" t="inlineStr"/>
+      <c r="AA136" s="12" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="6" t="inlineStr">
@@ -15524,6 +15764,7 @@
       <c r="X137" s="6" t="inlineStr"/>
       <c r="Y137" s="6" t="inlineStr"/>
       <c r="Z137" s="6" t="inlineStr"/>
+      <c r="AA137" s="6" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="12" t="inlineStr">
@@ -15633,6 +15874,7 @@
       <c r="X138" s="12" t="inlineStr"/>
       <c r="Y138" s="12" t="inlineStr"/>
       <c r="Z138" s="12" t="inlineStr"/>
+      <c r="AA138" s="12" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
@@ -15742,6 +15984,7 @@
       <c r="X139" s="6" t="inlineStr"/>
       <c r="Y139" s="6" t="inlineStr"/>
       <c r="Z139" s="6" t="inlineStr"/>
+      <c r="AA139" s="6" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="12" t="inlineStr">
@@ -15846,6 +16089,11 @@
       <c r="X140" s="12" t="inlineStr"/>
       <c r="Y140" s="12" t="inlineStr"/>
       <c r="Z140" s="12" t="inlineStr"/>
+      <c r="AA140" s="12" t="inlineStr">
+        <is>
+          <t>2026 Engineering News-Record. ENR 2026 Top 400 Contractors, where the firm is ranked 72  https://www.enr.com/toplists/2026-Top-400-Contractors-1</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
@@ -15950,6 +16198,11 @@
       <c r="X141" s="6" t="inlineStr"/>
       <c r="Y141" s="6" t="inlineStr"/>
       <c r="Z141" s="6" t="inlineStr"/>
+      <c r="AA141" s="6" t="inlineStr">
+        <is>
+          <t>2026 Engineering News-Record. ENR 2026 Top 400 Contractors, where the firm is ranked 72  https://www.enr.com/toplists/2026-Top-400-Contractors-1</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="12" t="inlineStr">
@@ -16054,6 +16307,11 @@
       <c r="X142" s="12" t="inlineStr"/>
       <c r="Y142" s="12" t="inlineStr"/>
       <c r="Z142" s="12" t="inlineStr"/>
+      <c r="AA142" s="12" t="inlineStr">
+        <is>
+          <t>2026 Engineering News-Record. ENR 2026 Top 400 Contractors, where the firm is ranked 72  https://www.enr.com/toplists/2026-Top-400-Contractors-1</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="6" t="inlineStr">
@@ -16167,6 +16425,11 @@
       <c r="X143" s="6" t="inlineStr"/>
       <c r="Y143" s="6" t="inlineStr"/>
       <c r="Z143" s="6" t="inlineStr"/>
+      <c r="AA143" s="6" t="inlineStr">
+        <is>
+          <t>2026 Engineering News-Record. ENR 2026 Top 400 Contractors, where the firm is ranked 72  https://www.enr.com/toplists/2026-Top-400-Contractors-1</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="12" t="inlineStr">
@@ -16276,6 +16539,11 @@
       <c r="X144" s="12" t="inlineStr"/>
       <c r="Y144" s="12" t="inlineStr"/>
       <c r="Z144" s="12" t="inlineStr"/>
+      <c r="AA144" s="12" t="inlineStr">
+        <is>
+          <t>2026 Engineering News-Record. ENR 2026 Top 400 Contractors, where the firm is ranked 72  https://www.enr.com/toplists/2026-Top-400-Contractors-1</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="6" t="inlineStr">
@@ -16384,6 +16652,7 @@
       <c r="X145" s="6" t="inlineStr"/>
       <c r="Y145" s="6" t="inlineStr"/>
       <c r="Z145" s="6" t="inlineStr"/>
+      <c r="AA145" s="6" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="12" t="inlineStr">
@@ -16488,6 +16757,7 @@
       <c r="X146" s="12" t="inlineStr"/>
       <c r="Y146" s="12" t="inlineStr"/>
       <c r="Z146" s="12" t="inlineStr"/>
+      <c r="AA146" s="12" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="6" t="inlineStr">
@@ -16597,6 +16867,7 @@
       <c r="X147" s="6" t="inlineStr"/>
       <c r="Y147" s="6" t="inlineStr"/>
       <c r="Z147" s="6" t="inlineStr"/>
+      <c r="AA147" s="6" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="12" t="inlineStr">
@@ -16706,6 +16977,7 @@
       <c r="X148" s="12" t="inlineStr"/>
       <c r="Y148" s="12" t="inlineStr"/>
       <c r="Z148" s="12" t="inlineStr"/>
+      <c r="AA148" s="12" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="6" t="inlineStr">
@@ -16815,6 +17087,7 @@
       <c r="X149" s="6" t="inlineStr"/>
       <c r="Y149" s="6" t="inlineStr"/>
       <c r="Z149" s="6" t="inlineStr"/>
+      <c r="AA149" s="6" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="12" t="inlineStr">
@@ -16924,6 +17197,7 @@
       <c r="X150" s="12" t="inlineStr"/>
       <c r="Y150" s="12" t="inlineStr"/>
       <c r="Z150" s="12" t="inlineStr"/>
+      <c r="AA150" s="12" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="6" t="inlineStr">
@@ -17028,6 +17302,7 @@
       <c r="X151" s="6" t="inlineStr"/>
       <c r="Y151" s="6" t="inlineStr"/>
       <c r="Z151" s="6" t="inlineStr"/>
+      <c r="AA151" s="6" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="12" t="inlineStr">
@@ -17132,6 +17407,7 @@
       <c r="X152" s="12" t="inlineStr"/>
       <c r="Y152" s="12" t="inlineStr"/>
       <c r="Z152" s="12" t="inlineStr"/>
+      <c r="AA152" s="12" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="6" t="inlineStr">
@@ -17236,6 +17512,7 @@
       <c r="X153" s="6" t="inlineStr"/>
       <c r="Y153" s="6" t="inlineStr"/>
       <c r="Z153" s="6" t="inlineStr"/>
+      <c r="AA153" s="6" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="12" t="inlineStr">
@@ -17345,6 +17622,7 @@
       <c r="X154" s="12" t="inlineStr"/>
       <c r="Y154" s="12" t="inlineStr"/>
       <c r="Z154" s="12" t="inlineStr"/>
+      <c r="AA154" s="12" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="6" t="inlineStr">
@@ -17454,6 +17732,7 @@
       <c r="X155" s="6" t="inlineStr"/>
       <c r="Y155" s="6" t="inlineStr"/>
       <c r="Z155" s="6" t="inlineStr"/>
+      <c r="AA155" s="6" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="12" t="inlineStr">
@@ -17562,6 +17841,7 @@
       <c r="X156" s="12" t="inlineStr"/>
       <c r="Y156" s="12" t="inlineStr"/>
       <c r="Z156" s="12" t="inlineStr"/>
+      <c r="AA156" s="12" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="6" t="inlineStr">
@@ -17675,6 +17955,7 @@
       <c r="X157" s="6" t="inlineStr"/>
       <c r="Y157" s="6" t="inlineStr"/>
       <c r="Z157" s="6" t="inlineStr"/>
+      <c r="AA157" s="6" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="12" t="inlineStr">
@@ -17772,6 +18053,7 @@
       <c r="X158" s="12" t="inlineStr"/>
       <c r="Y158" s="12" t="inlineStr"/>
       <c r="Z158" s="12" t="inlineStr"/>
+      <c r="AA158" s="12" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="6" t="inlineStr">
@@ -17881,6 +18163,7 @@
       <c r="X159" s="6" t="inlineStr"/>
       <c r="Y159" s="6" t="inlineStr"/>
       <c r="Z159" s="6" t="inlineStr"/>
+      <c r="AA159" s="6" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="12" t="inlineStr">
@@ -17994,6 +18277,11 @@
       <c r="X160" s="12" t="inlineStr"/>
       <c r="Y160" s="12" t="inlineStr"/>
       <c r="Z160" s="12" t="inlineStr"/>
+      <c r="AA160" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21 Construction Owners. Arch-Con Tops Out 330-Unit Artis Montrose Apartment Project  https://www.constructionowners.com/news/arch-con-reaches-topping-out-milestone-on-330-unit-artis-montrose-apartment-project</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="6" t="inlineStr">
@@ -18102,6 +18390,11 @@
       <c r="X161" s="6" t="inlineStr"/>
       <c r="Y161" s="6" t="inlineStr"/>
       <c r="Z161" s="6" t="inlineStr"/>
+      <c r="AA161" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-21 Construction Owners. Arch-Con Tops Out 330-Unit Artis Montrose Apartment Project  https://www.constructionowners.com/news/arch-con-reaches-topping-out-milestone-on-330-unit-artis-montrose-apartment-project</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="12" t="inlineStr">
@@ -18206,6 +18499,11 @@
       <c r="X162" s="12" t="inlineStr"/>
       <c r="Y162" s="12" t="inlineStr"/>
       <c r="Z162" s="12" t="inlineStr"/>
+      <c r="AA162" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-21 Construction Owners. Arch-Con Tops Out 330-Unit Artis Montrose Apartment Project  https://www.constructionowners.com/news/arch-con-reaches-topping-out-milestone-on-330-unit-artis-montrose-apartment-project</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="6" t="inlineStr">
@@ -18314,6 +18612,11 @@
       <c r="X163" s="6" t="inlineStr"/>
       <c r="Y163" s="6" t="inlineStr"/>
       <c r="Z163" s="6" t="inlineStr"/>
+      <c r="AA163" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-21 Construction Owners. Arch-Con Tops Out 330-Unit Artis Montrose Apartment Project  https://www.constructionowners.com/news/arch-con-reaches-topping-out-milestone-on-330-unit-artis-montrose-apartment-project</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="12" t="inlineStr">
@@ -18422,6 +18725,7 @@
       <c r="X164" s="12" t="inlineStr"/>
       <c r="Y164" s="12" t="inlineStr"/>
       <c r="Z164" s="12" t="inlineStr"/>
+      <c r="AA164" s="12" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="6" t="inlineStr">
@@ -18535,6 +18839,7 @@
       <c r="X165" s="6" t="inlineStr"/>
       <c r="Y165" s="6" t="inlineStr"/>
       <c r="Z165" s="6" t="inlineStr"/>
+      <c r="AA165" s="6" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="12" t="inlineStr">
@@ -18643,6 +18948,7 @@
       <c r="X166" s="12" t="inlineStr"/>
       <c r="Y166" s="12" t="inlineStr"/>
       <c r="Z166" s="12" t="inlineStr"/>
+      <c r="AA166" s="12" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="6" t="inlineStr">
@@ -18760,6 +19066,7 @@
           <t>https://www.tritenre.com/team</t>
         </is>
       </c>
+      <c r="AA167" s="6" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="12" t="inlineStr">
@@ -18877,6 +19184,7 @@
           <t>https://www.tritenre.com/team</t>
         </is>
       </c>
+      <c r="AA168" s="12" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="6" t="inlineStr">
@@ -18994,6 +19302,7 @@
           <t>https://www.tritenre.com/team</t>
         </is>
       </c>
+      <c r="AA169" s="6" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="12" t="inlineStr">
@@ -19114,6 +19423,7 @@
           <t>https://www.tritenre.com/team</t>
         </is>
       </c>
+      <c r="AA170" s="12" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="6" t="inlineStr">
@@ -19231,6 +19541,7 @@
           <t>https://www.radomcapital.com/team</t>
         </is>
       </c>
+      <c r="AA171" s="6" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="12" t="inlineStr">
@@ -19348,6 +19659,7 @@
           <t>https://www.radomcapital.com/team</t>
         </is>
       </c>
+      <c r="AA172" s="12" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="6" t="inlineStr">
@@ -19465,6 +19777,7 @@
           <t>https://www.radomcapital.com/team</t>
         </is>
       </c>
+      <c r="AA173" s="6" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="12" t="inlineStr">
@@ -19581,6 +19894,7 @@
           <t>https://www.dealco.net/about/</t>
         </is>
       </c>
+      <c r="AA174" s="12" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="6" t="inlineStr">
@@ -19701,6 +20015,7 @@
           <t>https://cameronmanagement.com/about</t>
         </is>
       </c>
+      <c r="AA175" s="6" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="12" t="inlineStr">
@@ -19821,6 +20136,7 @@
           <t>https://cameronmanagement.com/about</t>
         </is>
       </c>
+      <c r="AA176" s="12" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="6" t="inlineStr">
@@ -19933,6 +20249,7 @@
       </c>
       <c r="Y177" s="6" t="inlineStr"/>
       <c r="Z177" s="6" t="inlineStr"/>
+      <c r="AA177" s="6" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="12" t="inlineStr">
@@ -20046,6 +20363,7 @@
       <c r="X178" s="12" t="inlineStr"/>
       <c r="Y178" s="12" t="inlineStr"/>
       <c r="Z178" s="12" t="inlineStr"/>
+      <c r="AA178" s="12" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="6" t="inlineStr">
@@ -20158,6 +20476,7 @@
       </c>
       <c r="Y179" s="6" t="inlineStr"/>
       <c r="Z179" s="6" t="inlineStr"/>
+      <c r="AA179" s="6" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="12" t="inlineStr">
@@ -20267,6 +20586,7 @@
       <c r="X180" s="12" t="inlineStr"/>
       <c r="Y180" s="12" t="inlineStr"/>
       <c r="Z180" s="12" t="inlineStr"/>
+      <c r="AA180" s="12" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="6" t="inlineStr">
@@ -20387,6 +20707,7 @@
           <t>https://www.midway.team/our-people</t>
         </is>
       </c>
+      <c r="AA181" s="6" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="12" t="inlineStr">
@@ -20504,6 +20825,7 @@
           <t>https://www.midway.team/our-people</t>
         </is>
       </c>
+      <c r="AA182" s="12" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="6" t="inlineStr">
@@ -20624,6 +20946,7 @@
           <t>https://www.midway.team/our-people</t>
         </is>
       </c>
+      <c r="AA183" s="6" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="12" t="inlineStr">
@@ -20745,6 +21068,7 @@
           <t>https://www.midway.team/our-people</t>
         </is>
       </c>
+      <c r="AA184" s="12" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="6" t="inlineStr">
@@ -20862,6 +21186,7 @@
           <t>https://www.midway.team/our-people</t>
         </is>
       </c>
+      <c r="AA185" s="6" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="12" t="inlineStr">
@@ -20974,6 +21299,7 @@
       </c>
       <c r="Y186" s="12" t="inlineStr"/>
       <c r="Z186" s="12" t="inlineStr"/>
+      <c r="AA186" s="12" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="6" t="inlineStr">
@@ -21087,6 +21413,7 @@
       </c>
       <c r="Y187" s="6" t="inlineStr"/>
       <c r="Z187" s="6" t="inlineStr"/>
+      <c r="AA187" s="6" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="12" t="inlineStr">
@@ -21199,6 +21526,7 @@
       </c>
       <c r="Y188" s="12" t="inlineStr"/>
       <c r="Z188" s="12" t="inlineStr"/>
+      <c r="AA188" s="12" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="6" t="inlineStr">
@@ -21312,6 +21640,7 @@
       </c>
       <c r="Y189" s="6" t="inlineStr"/>
       <c r="Z189" s="6" t="inlineStr"/>
+      <c r="AA189" s="6" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="12" t="inlineStr">
@@ -21425,6 +21754,7 @@
       </c>
       <c r="Y190" s="12" t="inlineStr"/>
       <c r="Z190" s="12" t="inlineStr"/>
+      <c r="AA190" s="12" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="6" t="inlineStr">
@@ -21538,6 +21868,7 @@
       </c>
       <c r="Y191" s="6" t="inlineStr"/>
       <c r="Z191" s="6" t="inlineStr"/>
+      <c r="AA191" s="6" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="12" t="inlineStr">
@@ -21651,6 +21982,7 @@
       </c>
       <c r="Y192" s="12" t="inlineStr"/>
       <c r="Z192" s="12" t="inlineStr"/>
+      <c r="AA192" s="12" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="6" t="inlineStr">
@@ -21764,6 +22096,7 @@
       </c>
       <c r="Y193" s="6" t="inlineStr"/>
       <c r="Z193" s="6" t="inlineStr"/>
+      <c r="AA193" s="6" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="12" t="inlineStr">
@@ -21884,6 +22217,7 @@
           <t>https://investor.lgihomes.com/corporate-governance/management</t>
         </is>
       </c>
+      <c r="AA194" s="12" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="6" t="inlineStr">
@@ -22004,6 +22338,7 @@
           <t>https://investor.lgihomes.com/corporate-governance/management</t>
         </is>
       </c>
+      <c r="AA195" s="6" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="12" t="inlineStr">
@@ -22124,6 +22459,7 @@
           <t>https://investor.lgihomes.com/corporate-governance/management</t>
         </is>
       </c>
+      <c r="AA196" s="12" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="6" t="inlineStr">
@@ -22245,6 +22581,7 @@
           <t>https://investor.lgihomes.com/corporate-governance/management</t>
         </is>
       </c>
+      <c r="AA197" s="6" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="12" t="inlineStr">
@@ -22366,6 +22703,7 @@
           <t>https://investor.lgihomes.com/corporate-governance/management</t>
         </is>
       </c>
+      <c r="AA198" s="12" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="6" t="inlineStr">
@@ -22486,6 +22824,7 @@
           <t>https://investors.mihomes.com/investor-relations/officers-directors/default.aspx</t>
         </is>
       </c>
+      <c r="AA199" s="6" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="12" t="inlineStr">
@@ -22606,6 +22945,7 @@
           <t>https://investors.mihomes.com/investor-relations/officers-directors/default.aspx</t>
         </is>
       </c>
+      <c r="AA200" s="12" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="6" t="inlineStr">
@@ -22727,6 +23067,7 @@
           <t>https://investors.mihomes.com/investor-relations/officers-directors/default.aspx</t>
         </is>
       </c>
+      <c r="AA201" s="6" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="12" t="inlineStr">
@@ -22848,6 +23189,7 @@
           <t>https://investors.mihomes.com/investor-relations/officers-directors/default.aspx</t>
         </is>
       </c>
+      <c r="AA202" s="12" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="6" t="inlineStr">
@@ -22968,6 +23310,7 @@
           <t>https://newsroom.taylormorrison.com/Leadership</t>
         </is>
       </c>
+      <c r="AA203" s="6" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="12" t="inlineStr">
@@ -23081,6 +23424,7 @@
           <t>https://newsroom.taylormorrison.com/Leadership</t>
         </is>
       </c>
+      <c r="AA204" s="12" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="6" t="inlineStr">
@@ -23201,6 +23545,7 @@
           <t>https://www.ashtonwoods.com/corporate-info</t>
         </is>
       </c>
+      <c r="AA205" s="6" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="12" t="inlineStr">
@@ -23321,6 +23666,7 @@
           <t>https://www.ashtonwoods.com/corporate-info</t>
         </is>
       </c>
+      <c r="AA206" s="12" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="6" t="inlineStr">
@@ -23441,6 +23787,7 @@
           <t>https://www.ashtonwoods.com/corporate-info</t>
         </is>
       </c>
+      <c r="AA207" s="6" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="12" t="inlineStr">
@@ -23562,6 +23909,7 @@
           <t>https://www.ashtonwoods.com/corporate-info</t>
         </is>
       </c>
+      <c r="AA208" s="12" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="6" t="inlineStr">
@@ -23679,6 +24027,7 @@
           <t>https://www.davidweekleyhomes.com/about-us/meet-the-team</t>
         </is>
       </c>
+      <c r="AA209" s="6" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="12" t="inlineStr">
@@ -23799,6 +24148,7 @@
           <t>https://www.davidweekleyhomes.com/about-us/meet-the-team</t>
         </is>
       </c>
+      <c r="AA210" s="12" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="6" t="inlineStr">
@@ -23919,6 +24269,7 @@
           <t>https://www.davidweekleyhomes.com/about-us/meet-the-team</t>
         </is>
       </c>
+      <c r="AA211" s="6" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="12" t="inlineStr">
@@ -24040,6 +24391,7 @@
           <t>https://www.davidweekleyhomes.com/about-us/meet-the-team</t>
         </is>
       </c>
+      <c r="AA212" s="12" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="6" t="inlineStr">
@@ -24157,6 +24509,7 @@
           <t>https://www.davidweekleyhomes.com/about-us/meet-the-team</t>
         </is>
       </c>
+      <c r="AA213" s="6" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="12" t="inlineStr">
@@ -24274,6 +24627,7 @@
           <t>https://www.davidweekleyhomes.com/about-us/meet-the-team</t>
         </is>
       </c>
+      <c r="AA214" s="12" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="6" t="inlineStr">
@@ -24394,6 +24748,7 @@
           <t>https://www.perryhomes.com/about-perry-homes</t>
         </is>
       </c>
+      <c r="AA215" s="6" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="12" t="inlineStr">
@@ -24514,6 +24869,7 @@
           <t>https://www.perryhomes.com/about-perry-homes</t>
         </is>
       </c>
+      <c r="AA216" s="12" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="6" t="inlineStr">
@@ -24635,6 +24991,7 @@
           <t>https://www.perryhomes.com/about-perry-homes</t>
         </is>
       </c>
+      <c r="AA217" s="6" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="12" t="inlineStr">
@@ -24756,6 +25113,7 @@
           <t>https://www.perryhomes.com/about-perry-homes</t>
         </is>
       </c>
+      <c r="AA218" s="12" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="6" t="inlineStr">
@@ -24876,6 +25234,7 @@
           <t>https://www.drbgroup.com/about</t>
         </is>
       </c>
+      <c r="AA219" s="6" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="12" t="inlineStr">
@@ -25001,6 +25360,7 @@
           <t>https://www.drbgroup.com/about</t>
         </is>
       </c>
+      <c r="AA220" s="12" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="6" t="inlineStr">
@@ -25106,6 +25466,7 @@
           <t>https://www.signorellicompany.com/our-leadership</t>
         </is>
       </c>
+      <c r="AA221" s="6" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="12" t="inlineStr">
@@ -25214,6 +25575,7 @@
           <t>https://www.signorellicompany.com/our-leadership</t>
         </is>
       </c>
+      <c r="AA222" s="12" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="6" t="inlineStr">
@@ -25322,6 +25684,7 @@
           <t>https://www.signorellicompany.com/our-leadership</t>
         </is>
       </c>
+      <c r="AA223" s="6" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="12" t="inlineStr">
@@ -25430,6 +25793,7 @@
           <t>https://www.signorellicompany.com/our-leadership</t>
         </is>
       </c>
+      <c r="AA224" s="12" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="6" t="inlineStr">
@@ -25538,6 +25902,7 @@
           <t>https://investor.howardhughes.com/governance/leadership</t>
         </is>
       </c>
+      <c r="AA225" s="6" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="12" t="inlineStr">
@@ -25646,6 +26011,7 @@
           <t>https://investor.howardhughes.com/governance/leadership</t>
         </is>
       </c>
+      <c r="AA226" s="12" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="6" t="inlineStr">
@@ -25754,6 +26120,7 @@
           <t>https://investor.howardhughes.com/governance/leadership</t>
         </is>
       </c>
+      <c r="AA227" s="6" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="12" t="inlineStr">
@@ -25859,6 +26226,7 @@
           <t>https://investor.howardhughes.com/governance/leadership</t>
         </is>
       </c>
+      <c r="AA228" s="12" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="6" t="inlineStr">
@@ -25963,6 +26331,7 @@
           <t>https://landtejas.com/about-us/our-leadership/</t>
         </is>
       </c>
+      <c r="AA229" s="6" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="12" t="inlineStr">
@@ -26067,6 +26436,7 @@
           <t>https://landtejas.com/about-us/our-leadership/</t>
         </is>
       </c>
+      <c r="AA230" s="12" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="6" t="inlineStr">
@@ -26175,6 +26545,7 @@
           <t>https://caldwellcos.com/our-team</t>
         </is>
       </c>
+      <c r="AA231" s="6" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="12" t="inlineStr">
@@ -26283,6 +26654,7 @@
           <t>https://www.johnsondevelopment.com/our-leaders</t>
         </is>
       </c>
+      <c r="AA232" s="12" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="6" t="inlineStr">
@@ -26387,6 +26759,7 @@
         </is>
       </c>
       <c r="Z233" s="6" t="inlineStr"/>
+      <c r="AA233" s="6" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="12" t="inlineStr">
@@ -26496,6 +26869,7 @@
       <c r="X234" s="12" t="inlineStr"/>
       <c r="Y234" s="12" t="inlineStr"/>
       <c r="Z234" s="12" t="inlineStr"/>
+      <c r="AA234" s="12" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="6" t="inlineStr">
@@ -26616,6 +26990,7 @@
           <t>https://friendswooddevelopment.com/people</t>
         </is>
       </c>
+      <c r="AA235" s="6" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="12" t="inlineStr">
@@ -26724,6 +27099,7 @@
           <t>https://www.newquest.com/about-us/leadership/</t>
         </is>
       </c>
+      <c r="AA236" s="12" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="6" t="inlineStr">
@@ -26832,6 +27208,7 @@
           <t>https://www.newquest.com/about-us/leadership/</t>
         </is>
       </c>
+      <c r="AA237" s="6" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="12" t="inlineStr">
@@ -26940,6 +27317,7 @@
           <t>https://www.newquest.com/about-us/leadership/</t>
         </is>
       </c>
+      <c r="AA238" s="12" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="6" t="inlineStr">
@@ -27048,6 +27426,7 @@
           <t>https://www.newquest.com/about-us/leadership/</t>
         </is>
       </c>
+      <c r="AA239" s="6" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="12" t="inlineStr">
@@ -27156,6 +27535,7 @@
           <t>https://www.frpltd.com/about-fidelis/mission-values</t>
         </is>
       </c>
+      <c r="AA240" s="12" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="6" t="inlineStr">
@@ -27264,6 +27644,7 @@
           <t>https://www.frpltd.com/about-fidelis/mission-values</t>
         </is>
       </c>
+      <c r="AA241" s="6" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="12" t="inlineStr">
@@ -27373,6 +27754,7 @@
           <t>https://www.frpltd.com/about-fidelis/mission-values</t>
         </is>
       </c>
+      <c r="AA242" s="12" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="6" t="inlineStr">
@@ -27477,6 +27859,7 @@
           <t>https://www.hanoverco.com/leadership</t>
         </is>
       </c>
+      <c r="AA243" s="6" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="12" t="inlineStr">
@@ -27581,6 +27964,7 @@
           <t>https://www.hanoverco.com/leadership</t>
         </is>
       </c>
+      <c r="AA244" s="12" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="6" t="inlineStr">
@@ -27685,6 +28069,7 @@
           <t>https://www.hanoverco.com/leadership</t>
         </is>
       </c>
+      <c r="AA245" s="6" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="12" t="inlineStr">
@@ -27789,6 +28174,7 @@
           <t>https://www.hanoverco.com/leadership</t>
         </is>
       </c>
+      <c r="AA246" s="12" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="6" t="inlineStr">
@@ -27894,6 +28280,7 @@
           <t>https://www.hanoverco.com/leadership</t>
         </is>
       </c>
+      <c r="AA247" s="6" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="12" t="inlineStr">
@@ -27999,6 +28386,7 @@
           <t>https://www.hanoverco.com/leadership</t>
         </is>
       </c>
+      <c r="AA248" s="12" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="6" t="inlineStr">
@@ -28104,6 +28492,7 @@
           <t>https://www.hanoverco.com/leadership</t>
         </is>
       </c>
+      <c r="AA249" s="6" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="12" t="inlineStr">
@@ -28212,6 +28601,7 @@
           <t>https://www.read-king.com/team</t>
         </is>
       </c>
+      <c r="AA250" s="12" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="6" t="inlineStr">
@@ -28320,6 +28710,7 @@
           <t>https://www.read-king.com/team</t>
         </is>
       </c>
+      <c r="AA251" s="6" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="12" t="inlineStr">
@@ -28428,6 +28819,7 @@
           <t>https://www.read-king.com/team</t>
         </is>
       </c>
+      <c r="AA252" s="12" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="6" t="inlineStr">
@@ -28533,6 +28925,7 @@
           <t>https://www.read-king.com/team</t>
         </is>
       </c>
+      <c r="AA253" s="6" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="12" t="inlineStr">
@@ -28641,6 +29034,7 @@
           <t>https://investors.camdenliving.com/investors/governance/board-of-directors/default.aspx</t>
         </is>
       </c>
+      <c r="AA254" s="12" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="6" t="inlineStr">
@@ -28749,6 +29143,7 @@
           <t>https://investors.camdenliving.com/investors/governance/board-of-directors/default.aspx</t>
         </is>
       </c>
+      <c r="AA255" s="6" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="12" t="inlineStr">
@@ -28858,6 +29253,7 @@
           <t>https://investors.camdenliving.com/investors/governance/board-of-directors/default.aspx</t>
         </is>
       </c>
+      <c r="AA256" s="12" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="6" t="inlineStr">
@@ -28966,6 +29362,7 @@
           <t>https://www.greystar.com/business/about-greystar/our-leadership</t>
         </is>
       </c>
+      <c r="AA257" s="6" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="12" t="inlineStr">
@@ -29074,6 +29471,7 @@
           <t>https://www.greystar.com/business/about-greystar/our-leadership</t>
         </is>
       </c>
+      <c r="AA258" s="12" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="6" t="inlineStr">
@@ -29182,6 +29580,7 @@
           <t>https://www.dinersteincos.com/about-us</t>
         </is>
       </c>
+      <c r="AA259" s="6" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="12" t="inlineStr">
@@ -29287,6 +29686,7 @@
           <t>https://www.dinersteincos.com/about-us</t>
         </is>
       </c>
+      <c r="AA260" s="12" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="6" t="inlineStr">
@@ -29395,6 +29795,7 @@
           <t>https://www.dinersteincos.com/about-us</t>
         </is>
       </c>
+      <c r="AA261" s="6" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="12" t="inlineStr">
@@ -29503,6 +29904,7 @@
           <t>https://www.dinersteincos.com/about-us</t>
         </is>
       </c>
+      <c r="AA262" s="12" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="6" t="inlineStr">
@@ -29603,6 +30005,7 @@
           <t>https://bakerkatz.com/about-us/</t>
         </is>
       </c>
+      <c r="AA263" s="6" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="12" t="inlineStr">
@@ -29703,6 +30106,7 @@
           <t>https://bakerkatz.com/about-us/</t>
         </is>
       </c>
+      <c r="AA264" s="12" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="6" t="inlineStr">
@@ -29807,6 +30211,7 @@
           <t>https://bakerkatz.com/about-us/</t>
         </is>
       </c>
+      <c r="AA265" s="6" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="12" t="inlineStr">
@@ -29907,6 +30312,7 @@
           <t>https://www.wulfe.com/people</t>
         </is>
       </c>
+      <c r="AA266" s="12" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="6" t="inlineStr">
@@ -30011,16 +30417,17 @@
           <t>https://www.wulfe.com/people</t>
         </is>
       </c>
+      <c r="AA267" s="6" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="17" t="inlineStr">
         <is>
-          <t>NOTE. A filled LinkedIn cell means the profile was opened or the search result read and the headline named the firm; column W records what was read. Where that test failed the cell is left empty rather than guessed, because a fabricated slug passes visual inspection and then fails in front of the person it names. Column Q searches for the empty ones in your own session. Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Capital is a qualifier, not a count. Source: ICON Greater Houston screen, build 39, 2026-09-11.</t>
+          <t>NOTE. A filled LinkedIn cell means the profile was opened or the search result read and the headline named the firm; column W records what was read. Where that test failed the cell is left empty rather than guessed, because a fabricated slug passes visual inspection and then fails in front of the person it names. Column Q searches for the empty ones in your own session. Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Capital is a qualifier, not a count. Source: ICON Greater Houston screen, build 40, 2026-09-11.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:Z267"/>
+  <autoFilter ref="A6:AA267"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/ICON_Greater_Houston_Rolodex.xlsx
+++ b/docs/ICON_Greater_Houston_Rolodex.xlsx
@@ -565,7 +565,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated from houston-data.json · build 41 · 2026-09-11 · public render. Do not hand-edit the HTML deck; it regenerates from the same file.</t>
+          <t>Generated from houston-data.json · build 42 · 2026-09-11 · public render. Do not hand-edit the HTML deck; it regenerates from the same file.</t>
         </is>
       </c>
     </row>
@@ -28877,7 +28877,7 @@
     <row r="266">
       <c r="A266" s="17" t="inlineStr">
         <is>
-          <t>NOTE. A filled LinkedIn cell means the profile was opened or the search result read and the headline named the firm; column W records what was read. Where that test failed the cell is left empty rather than guessed, because a fabricated slug passes visual inspection and then fails in front of the person it names. Column Q searches for the empty ones in your own session. Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Capital is a qualifier, not a count. Source: ICON Greater Houston screen, build 41, 2026-09-11.</t>
+          <t>NOTE. A filled LinkedIn cell means the profile was opened or the search result read and the headline named the firm; column W records what was read. Where that test failed the cell is left empty rather than guessed, because a fabricated slug passes visual inspection and then fails in front of the person it names. Column Q searches for the empty ones in your own session. Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Capital is a qualifier, not a count. Source: ICON Greater Houston screen, build 42, 2026-09-11.</t>
         </is>
       </c>
     </row>

--- a/docs/ICON_Greater_Houston_Rolodex.xlsx
+++ b/docs/ICON_Greater_Houston_Rolodex.xlsx
@@ -565,7 +565,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated from houston-data.json · build 42 · 2026-09-11 · public render. Do not hand-edit the HTML deck; it regenerates from the same file.</t>
+          <t>Generated from houston-data.json · build 43 · 2026-09-11 · public render. Do not hand-edit the HTML deck; it regenerates from the same file.</t>
         </is>
       </c>
     </row>
@@ -6268,7 +6268,7 @@
       </c>
       <c r="T55" s="9" t="inlineStr">
         <is>
-          <t>1,000 homes at Trinity Landing and a sub-110-day cycle held four quarters. No wall-system statement on record.</t>
+          <t>1,000 homes at Trinity Landing and a sub-110-day cycle held four quarters.</t>
         </is>
       </c>
       <c r="U55" s="6" t="inlineStr"/>
@@ -6380,7 +6380,7 @@
       </c>
       <c r="T56" s="15" t="inlineStr">
         <is>
-          <t>1,000 homes at Trinity Landing and a sub-110-day cycle held four quarters. No wall-system statement on record.</t>
+          <t>1,000 homes at Trinity Landing and a sub-110-day cycle held four quarters.</t>
         </is>
       </c>
       <c r="U56" s="12" t="inlineStr"/>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="T57" s="9" t="inlineStr">
         <is>
-          <t>1,000 homes at Trinity Landing and a sub-110-day cycle held four quarters. No wall-system statement on record.</t>
+          <t>1,000 homes at Trinity Landing and a sub-110-day cycle held four quarters.</t>
         </is>
       </c>
       <c r="U57" s="6" t="inlineStr"/>
@@ -6613,7 +6613,7 @@
       </c>
       <c r="T58" s="15" t="inlineStr">
         <is>
-          <t>1,000 homes at Trinity Landing and a sub-110-day cycle held four quarters. No wall-system statement on record.</t>
+          <t>1,000 homes at Trinity Landing and a sub-110-day cycle held four quarters.</t>
         </is>
       </c>
       <c r="U58" s="12" t="inlineStr">
@@ -6730,7 +6730,7 @@
       </c>
       <c r="T59" s="9" t="inlineStr">
         <is>
-          <t>1,000 homes at Trinity Landing and a sub-110-day cycle held four quarters. No wall-system statement on record.</t>
+          <t>1,000 homes at Trinity Landing and a sub-110-day cycle held four quarters.</t>
         </is>
       </c>
       <c r="U59" s="6" t="inlineStr"/>
@@ -6843,7 +6843,7 @@
       </c>
       <c r="T60" s="15" t="inlineStr">
         <is>
-          <t>1,000 homes at Trinity Landing and a sub-110-day cycle held four quarters. No wall-system statement on record.</t>
+          <t>1,000 homes at Trinity Landing and a sub-110-day cycle held four quarters.</t>
         </is>
       </c>
       <c r="U60" s="12" t="inlineStr"/>
@@ -7063,7 +7063,7 @@
       </c>
       <c r="T62" s="15" t="inlineStr">
         <is>
-          <t>10,800 rental homes across 115 communities, built and held. No construction-method statement anywhere.</t>
+          <t>10,800 rental homes across 115 communities, built and held.</t>
         </is>
       </c>
       <c r="U62" s="12" t="inlineStr"/>
@@ -7179,7 +7179,7 @@
       </c>
       <c r="T63" s="9" t="inlineStr">
         <is>
-          <t>10,800 rental homes across 115 communities, built and held. No construction-method statement anywhere.</t>
+          <t>10,800 rental homes across 115 communities, built and held.</t>
         </is>
       </c>
       <c r="U63" s="6" t="inlineStr"/>
@@ -7295,7 +7295,7 @@
       </c>
       <c r="T64" s="15" t="inlineStr">
         <is>
-          <t>10,800 rental homes across 115 communities, built and held. No construction-method statement anywhere.</t>
+          <t>10,800 rental homes across 115 communities, built and held.</t>
         </is>
       </c>
       <c r="U64" s="12" t="inlineStr"/>
@@ -7411,7 +7411,7 @@
       </c>
       <c r="T65" s="9" t="inlineStr">
         <is>
-          <t>10,800 rental homes across 115 communities, built and held. No construction-method statement anywhere.</t>
+          <t>10,800 rental homes across 115 communities, built and held.</t>
         </is>
       </c>
       <c r="U65" s="6" t="inlineStr"/>
@@ -7527,7 +7527,7 @@
       </c>
       <c r="T66" s="15" t="inlineStr">
         <is>
-          <t>20,000 homes since 2004. Daiwa House owns a stake. No published method evidence.</t>
+          <t>20,000 homes since 2004. Daiwa House owns a stake.</t>
         </is>
       </c>
       <c r="U66" s="12" t="inlineStr"/>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="T67" s="9" t="inlineStr">
         <is>
-          <t>20,000 homes since 2004. Daiwa House owns a stake. No published method evidence.</t>
+          <t>20,000 homes since 2004. Daiwa House owns a stake.</t>
         </is>
       </c>
       <c r="U67" s="6" t="inlineStr"/>
@@ -7757,7 +7757,7 @@
       </c>
       <c r="T68" s="15" t="inlineStr">
         <is>
-          <t>20,000 homes since 2004. Daiwa House owns a stake. No published method evidence.</t>
+          <t>20,000 homes since 2004. Daiwa House owns a stake.</t>
         </is>
       </c>
       <c r="U68" s="12" t="inlineStr"/>
@@ -9785,7 +9785,7 @@
       </c>
       <c r="T87" s="9" t="inlineStr">
         <is>
-          <t>Seven plans, ten communities, founded 2020. No closings figure to size it against.</t>
+          <t>Seven plans, ten communities, founded 2020.</t>
         </is>
       </c>
       <c r="U87" s="6" t="inlineStr"/>
@@ -9885,7 +9885,7 @@
       </c>
       <c r="T88" s="15" t="inlineStr">
         <is>
-          <t>Seven plans, ten communities, founded 2020. No closings figure to size it against.</t>
+          <t>Seven plans, ten communities, founded 2020.</t>
         </is>
       </c>
       <c r="U88" s="12" t="inlineStr"/>
@@ -9986,7 +9986,7 @@
       </c>
       <c r="T89" s="9" t="inlineStr">
         <is>
-          <t>Seven plans, ten communities, founded 2020. No closings figure to size it against.</t>
+          <t>Seven plans, ten communities, founded 2020.</t>
         </is>
       </c>
       <c r="U89" s="6" t="inlineStr">
@@ -10327,7 +10327,7 @@
       </c>
       <c r="T92" s="15" t="inlineStr">
         <is>
-          <t>A national platform with a Houston division president who is a licensed engineer. One community identified so far.</t>
+          <t>A national platform with a Houston division president who is a licensed engineer, building in Sunterra.</t>
         </is>
       </c>
       <c r="U92" s="12" t="inlineStr"/>
@@ -10436,7 +10436,7 @@
       </c>
       <c r="T93" s="9" t="inlineStr">
         <is>
-          <t>A national platform with a Houston division president who is a licensed engineer. One community identified so far.</t>
+          <t>A national platform with a Houston division president who is a licensed engineer, building in Sunterra.</t>
         </is>
       </c>
       <c r="U93" s="6" t="inlineStr"/>
@@ -10545,7 +10545,7 @@
       </c>
       <c r="T94" s="15" t="inlineStr">
         <is>
-          <t>Close to 100 communities inside Dream Finders, which bought parent MHI in 2021. Two Houston division presidents are named.</t>
+          <t>Close to 100 communities inside Dream Finders, which bought parent MHI in 2021.</t>
         </is>
       </c>
       <c r="U94" s="12" t="inlineStr"/>
@@ -10654,7 +10654,7 @@
       </c>
       <c r="T95" s="9" t="inlineStr">
         <is>
-          <t>Close to 100 communities inside Dream Finders, which bought parent MHI in 2021. Two Houston division presidents are named.</t>
+          <t>Close to 100 communities inside Dream Finders, which bought parent MHI in 2021.</t>
         </is>
       </c>
       <c r="U95" s="6" t="inlineStr"/>
@@ -10762,7 +10762,7 @@
       </c>
       <c r="T96" s="15" t="inlineStr">
         <is>
-          <t>483 closings in 2025 across more than twenty communities and more than 150 plans. A president is named; no construction or purchasing lead is published.</t>
+          <t>483 closings in 2025 across more than twenty communities and more than 150 plans.</t>
         </is>
       </c>
       <c r="U96" s="12" t="inlineStr"/>
@@ -11402,7 +11402,7 @@
       </c>
       <c r="T102" s="15" t="inlineStr">
         <is>
-          <t>Two Katy duplex projects a mile apart, 366 units. No capital figure and no method evidence.</t>
+          <t>Two Katy duplex projects a mile apart, 366 units.</t>
         </is>
       </c>
       <c r="U102" s="12" t="inlineStr"/>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="T103" s="9" t="inlineStr">
         <is>
-          <t>Two Katy duplex projects a mile apart, 366 units. No capital figure and no method evidence.</t>
+          <t>Two Katy duplex projects a mile apart, 366 units.</t>
         </is>
       </c>
       <c r="U103" s="6" t="inlineStr">
@@ -11638,7 +11638,7 @@
       </c>
       <c r="T104" s="15" t="inlineStr">
         <is>
-          <t>Two Katy duplex projects a mile apart, 366 units. No capital figure and no method evidence.</t>
+          <t>Two Katy duplex projects a mile apart, 366 units.</t>
         </is>
       </c>
       <c r="U104" s="12" t="inlineStr"/>
@@ -19536,7 +19536,7 @@
       </c>
       <c r="T178" s="15" t="inlineStr">
         <is>
-          <t>East River is 60 blocks on one site. No capital figure disclosed and the Parkway relationship is unresolved.</t>
+          <t>East River is 60 blocks on one site, and Midway kept sole development control after selling out of the Parkway joint venture in December 2024.</t>
         </is>
       </c>
       <c r="U178" s="12" t="inlineStr"/>
@@ -19653,7 +19653,7 @@
       </c>
       <c r="T179" s="9" t="inlineStr">
         <is>
-          <t>East River is 60 blocks on one site. No capital figure disclosed and the Parkway relationship is unresolved.</t>
+          <t>East River is 60 blocks on one site, and Midway kept sole development control after selling out of the Parkway joint venture in December 2024.</t>
         </is>
       </c>
       <c r="U179" s="6" t="inlineStr"/>
@@ -19765,7 +19765,7 @@
       </c>
       <c r="T180" s="15" t="inlineStr">
         <is>
-          <t>East River is 60 blocks on one site. No capital figure disclosed and the Parkway relationship is unresolved.</t>
+          <t>East River is 60 blocks on one site, and Midway kept sole development control after selling out of the Parkway joint venture in December 2024.</t>
         </is>
       </c>
       <c r="U180" s="12" t="inlineStr"/>
@@ -19882,7 +19882,7 @@
       </c>
       <c r="T181" s="9" t="inlineStr">
         <is>
-          <t>East River is 60 blocks on one site. No capital figure disclosed and the Parkway relationship is unresolved.</t>
+          <t>East River is 60 blocks on one site, and Midway kept sole development control after selling out of the Parkway joint venture in December 2024.</t>
         </is>
       </c>
       <c r="U181" s="6" t="inlineStr">
@@ -19999,7 +19999,7 @@
       </c>
       <c r="T182" s="15" t="inlineStr">
         <is>
-          <t>East River is 60 blocks on one site. No capital figure disclosed and the Parkway relationship is unresolved.</t>
+          <t>East River is 60 blocks on one site, and Midway kept sole development control after selling out of the Parkway joint venture in December 2024.</t>
         </is>
       </c>
       <c r="U182" s="12" t="inlineStr"/>
@@ -22258,7 +22258,7 @@
       </c>
       <c r="T202" s="15" t="inlineStr">
         <is>
-          <t>14 named Houston communities and a Texas regional president. No firm-specific method evidence found.</t>
+          <t>14 named Houston communities and a Texas regional president.</t>
         </is>
       </c>
       <c r="U202" s="12" t="inlineStr"/>
@@ -22374,7 +22374,7 @@
       </c>
       <c r="T203" s="9" t="inlineStr">
         <is>
-          <t>14 named Houston communities and a Texas regional president. No firm-specific method evidence found.</t>
+          <t>14 named Houston communities and a Texas regional president.</t>
         </is>
       </c>
       <c r="U203" s="6" t="inlineStr"/>
@@ -22490,7 +22490,7 @@
       </c>
       <c r="T204" s="15" t="inlineStr">
         <is>
-          <t>14 named Houston communities and a Texas regional president. No firm-specific method evidence found.</t>
+          <t>14 named Houston communities and a Texas regional president.</t>
         </is>
       </c>
       <c r="U204" s="12" t="inlineStr"/>
@@ -22607,7 +22607,7 @@
       </c>
       <c r="T205" s="9" t="inlineStr">
         <is>
-          <t>14 named Houston communities and a Texas regional president. No firm-specific method evidence found.</t>
+          <t>14 named Houston communities and a Texas regional president.</t>
         </is>
       </c>
       <c r="U205" s="6" t="inlineStr">
@@ -25136,7 +25136,7 @@
       </c>
       <c r="T228" s="15" t="inlineStr">
         <is>
-          <t>Sells lots. Towne Lake and The Highlands carry 4,000 homes across 12 builders. No published method evidence.</t>
+          <t>Sells lots. Towne Lake and The Highlands carry 4,000 homes across 12 builders.</t>
         </is>
       </c>
       <c r="U228" s="12" t="inlineStr"/>
@@ -28877,7 +28877,7 @@
     <row r="266">
       <c r="A266" s="17" t="inlineStr">
         <is>
-          <t>NOTE. A filled LinkedIn cell means the profile was opened or the search result read and the headline named the firm; column W records what was read. Where that test failed the cell is left empty rather than guessed, because a fabricated slug passes visual inspection and then fails in front of the person it names. Column Q searches for the empty ones in your own session. Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Capital is a qualifier, not a count. Source: ICON Greater Houston screen, build 42, 2026-09-11.</t>
+          <t>NOTE. A filled LinkedIn cell means the profile was opened or the search result read and the headline named the firm; column W records what was read. Where that test failed the cell is left empty rather than guessed, because a fabricated slug passes visual inspection and then fails in front of the person it names. Column Q searches for the empty ones in your own session. Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Capital is a qualifier, not a count. Source: ICON Greater Houston screen, build 43, 2026-09-11.</t>
         </is>
       </c>
     </row>

--- a/docs/ICON_Greater_Houston_Rolodex.xlsx
+++ b/docs/ICON_Greater_Houston_Rolodex.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contacts" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Permits" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Contacts'!$A$6:$Z$264</definedName>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -73,6 +74,17 @@
       <color rgb="00FF4F00"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00111111"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -114,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -159,6 +171,11 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -565,7 +582,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated from houston-data.json · build 43 · 2026-09-11 · public render. Do not hand-edit the HTML deck; it regenerates from the same file.</t>
+          <t>Generated from houston-data.json · build 44 · 2026-09-11 · public render. Do not hand-edit the HTML deck; it regenerates from the same file.</t>
         </is>
       </c>
     </row>
@@ -28877,7 +28894,7 @@
     <row r="266">
       <c r="A266" s="17" t="inlineStr">
         <is>
-          <t>NOTE. A filled LinkedIn cell means the profile was opened or the search result read and the headline named the firm; column W records what was read. Where that test failed the cell is left empty rather than guessed, because a fabricated slug passes visual inspection and then fails in front of the person it names. Column Q searches for the empty ones in your own session. Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Capital is a qualifier, not a count. Source: ICON Greater Houston screen, build 43, 2026-09-11.</t>
+          <t>NOTE. A filled LinkedIn cell means the profile was opened or the search result read and the headline named the firm; column W records what was read. Where that test failed the cell is left empty rather than guessed, because a fabricated slug passes visual inspection and then fails in front of the person it names. Column Q searches for the empty ones in your own session. Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Capital is a qualifier, not a count. Source: ICON Greater Houston screen, build 44, 2026-09-11.</t>
         </is>
       </c>
     </row>
@@ -28885,4 +28902,4472 @@
   <autoFilter ref="A6:Z264"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AA130"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
+    <col width="9" customWidth="1" min="19" max="19"/>
+    <col width="9" customWidth="1" min="20" max="20"/>
+    <col width="9" customWidth="1" min="21" max="21"/>
+    <col width="9" customWidth="1" min="22" max="22"/>
+    <col width="9" customWidth="1" min="23" max="23"/>
+    <col width="9" customWidth="1" min="24" max="24"/>
+    <col width="9" customWidth="1" min="25" max="25"/>
+    <col width="9" customWidth="1" min="26" max="26"/>
+    <col width="9" customWidth="1" min="27" max="27"/>
+    <col width="9" customWidth="1" min="28" max="28"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>Single-family units authorised by building permit, Houston-Pasadena-The Woodlands, TX</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Source: HUD SOCDS, republishing the Census Building Permits Survey. An authorisation is not a start, a completion or a closing. Census counts townhouses and row houses as single family. The jurisdictions sum to the counties and the counties sum to the metro exactly, in every year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>County</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C4" s="19" t="n">
+        <v>2001</v>
+      </c>
+      <c r="D4" s="19" t="n">
+        <v>2002</v>
+      </c>
+      <c r="E4" s="19" t="n">
+        <v>2003</v>
+      </c>
+      <c r="F4" s="19" t="n">
+        <v>2004</v>
+      </c>
+      <c r="G4" s="19" t="n">
+        <v>2005</v>
+      </c>
+      <c r="H4" s="19" t="n">
+        <v>2006</v>
+      </c>
+      <c r="I4" s="19" t="n">
+        <v>2007</v>
+      </c>
+      <c r="J4" s="19" t="n">
+        <v>2008</v>
+      </c>
+      <c r="K4" s="19" t="n">
+        <v>2009</v>
+      </c>
+      <c r="L4" s="19" t="n">
+        <v>2010</v>
+      </c>
+      <c r="M4" s="19" t="n">
+        <v>2011</v>
+      </c>
+      <c r="N4" s="19" t="n">
+        <v>2012</v>
+      </c>
+      <c r="O4" s="19" t="n">
+        <v>2013</v>
+      </c>
+      <c r="P4" s="19" t="n">
+        <v>2014</v>
+      </c>
+      <c r="Q4" s="19" t="n">
+        <v>2015</v>
+      </c>
+      <c r="R4" s="19" t="n">
+        <v>2016</v>
+      </c>
+      <c r="S4" s="19" t="n">
+        <v>2017</v>
+      </c>
+      <c r="T4" s="19" t="n">
+        <v>2018</v>
+      </c>
+      <c r="U4" s="19" t="n">
+        <v>2019</v>
+      </c>
+      <c r="V4" s="19" t="n">
+        <v>2020</v>
+      </c>
+      <c r="W4" s="19" t="n">
+        <v>2021</v>
+      </c>
+      <c r="X4" s="19" t="n">
+        <v>2022</v>
+      </c>
+      <c r="Y4" s="19" t="n">
+        <v>2023</v>
+      </c>
+      <c r="Z4" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA4" s="19" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>Harris</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="n">
+        <v>18244</v>
+      </c>
+      <c r="C5" s="20" t="n">
+        <v>20122</v>
+      </c>
+      <c r="D5" s="20" t="n">
+        <v>23052</v>
+      </c>
+      <c r="E5" s="20" t="n">
+        <v>26450</v>
+      </c>
+      <c r="F5" s="20" t="n">
+        <v>28020</v>
+      </c>
+      <c r="G5" s="20" t="n">
+        <v>32465</v>
+      </c>
+      <c r="H5" s="20" t="n">
+        <v>33023</v>
+      </c>
+      <c r="I5" s="20" t="n">
+        <v>23985</v>
+      </c>
+      <c r="J5" s="20" t="n">
+        <v>14823</v>
+      </c>
+      <c r="K5" s="20" t="n">
+        <v>11591</v>
+      </c>
+      <c r="L5" s="20" t="n">
+        <v>11057</v>
+      </c>
+      <c r="M5" s="20" t="n">
+        <v>11107</v>
+      </c>
+      <c r="N5" s="20" t="n">
+        <v>14550</v>
+      </c>
+      <c r="O5" s="20" t="n">
+        <v>16986</v>
+      </c>
+      <c r="P5" s="20" t="n">
+        <v>18533</v>
+      </c>
+      <c r="Q5" s="20" t="n">
+        <v>16721</v>
+      </c>
+      <c r="R5" s="20" t="n">
+        <v>15511</v>
+      </c>
+      <c r="S5" s="20" t="n">
+        <v>16980</v>
+      </c>
+      <c r="T5" s="20" t="n">
+        <v>17732</v>
+      </c>
+      <c r="U5" s="20" t="n">
+        <v>17903</v>
+      </c>
+      <c r="V5" s="20" t="n">
+        <v>20834</v>
+      </c>
+      <c r="W5" s="20" t="n">
+        <v>21260</v>
+      </c>
+      <c r="X5" s="20" t="n">
+        <v>18156</v>
+      </c>
+      <c r="Y5" s="20" t="n">
+        <v>20324</v>
+      </c>
+      <c r="Z5" s="20" t="n">
+        <v>20087</v>
+      </c>
+      <c r="AA5" s="20" t="n">
+        <v>16940</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>Montgomery</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="n">
+        <v>4067</v>
+      </c>
+      <c r="C6" s="20" t="n">
+        <v>3997</v>
+      </c>
+      <c r="D6" s="20" t="n">
+        <v>4497</v>
+      </c>
+      <c r="E6" s="20" t="n">
+        <v>5581</v>
+      </c>
+      <c r="F6" s="20" t="n">
+        <v>6023</v>
+      </c>
+      <c r="G6" s="20" t="n">
+        <v>6586</v>
+      </c>
+      <c r="H6" s="20" t="n">
+        <v>7417</v>
+      </c>
+      <c r="I6" s="20" t="n">
+        <v>5074</v>
+      </c>
+      <c r="J6" s="20" t="n">
+        <v>3583</v>
+      </c>
+      <c r="K6" s="20" t="n">
+        <v>2773</v>
+      </c>
+      <c r="L6" s="20" t="n">
+        <v>2723</v>
+      </c>
+      <c r="M6" s="20" t="n">
+        <v>2795</v>
+      </c>
+      <c r="N6" s="20" t="n">
+        <v>3364</v>
+      </c>
+      <c r="O6" s="20" t="n">
+        <v>4976</v>
+      </c>
+      <c r="P6" s="20" t="n">
+        <v>5511</v>
+      </c>
+      <c r="Q6" s="20" t="n">
+        <v>4970</v>
+      </c>
+      <c r="R6" s="20" t="n">
+        <v>4175</v>
+      </c>
+      <c r="S6" s="20" t="n">
+        <v>5290</v>
+      </c>
+      <c r="T6" s="20" t="n">
+        <v>6663</v>
+      </c>
+      <c r="U6" s="20" t="n">
+        <v>6082</v>
+      </c>
+      <c r="V6" s="20" t="n">
+        <v>8901</v>
+      </c>
+      <c r="W6" s="20" t="n">
+        <v>12227</v>
+      </c>
+      <c r="X6" s="20" t="n">
+        <v>11820</v>
+      </c>
+      <c r="Y6" s="20" t="n">
+        <v>11259</v>
+      </c>
+      <c r="Z6" s="20" t="n">
+        <v>11586</v>
+      </c>
+      <c r="AA6" s="20" t="n">
+        <v>11597</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>Fort Bend</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="n">
+        <v>1063</v>
+      </c>
+      <c r="C7" s="20" t="n">
+        <v>936</v>
+      </c>
+      <c r="D7" s="20" t="n">
+        <v>1130</v>
+      </c>
+      <c r="E7" s="20" t="n">
+        <v>3476</v>
+      </c>
+      <c r="F7" s="20" t="n">
+        <v>3858</v>
+      </c>
+      <c r="G7" s="20" t="n">
+        <v>4097</v>
+      </c>
+      <c r="H7" s="20" t="n">
+        <v>7910</v>
+      </c>
+      <c r="I7" s="20" t="n">
+        <v>7046</v>
+      </c>
+      <c r="J7" s="20" t="n">
+        <v>5689</v>
+      </c>
+      <c r="K7" s="20" t="n">
+        <v>4845</v>
+      </c>
+      <c r="L7" s="20" t="n">
+        <v>4724</v>
+      </c>
+      <c r="M7" s="20" t="n">
+        <v>5110</v>
+      </c>
+      <c r="N7" s="20" t="n">
+        <v>6517</v>
+      </c>
+      <c r="O7" s="20" t="n">
+        <v>7913</v>
+      </c>
+      <c r="P7" s="20" t="n">
+        <v>8465</v>
+      </c>
+      <c r="Q7" s="20" t="n">
+        <v>9096</v>
+      </c>
+      <c r="R7" s="20" t="n">
+        <v>9777</v>
+      </c>
+      <c r="S7" s="20" t="n">
+        <v>7711</v>
+      </c>
+      <c r="T7" s="20" t="n">
+        <v>8949</v>
+      </c>
+      <c r="U7" s="20" t="n">
+        <v>8452</v>
+      </c>
+      <c r="V7" s="20" t="n">
+        <v>11403</v>
+      </c>
+      <c r="W7" s="20" t="n">
+        <v>9938</v>
+      </c>
+      <c r="X7" s="20" t="n">
+        <v>8917</v>
+      </c>
+      <c r="Y7" s="20" t="n">
+        <v>9953</v>
+      </c>
+      <c r="Z7" s="20" t="n">
+        <v>11200</v>
+      </c>
+      <c r="AA7" s="20" t="n">
+        <v>9760</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>Brazoria</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="n">
+        <v>1903</v>
+      </c>
+      <c r="C8" s="20" t="n">
+        <v>2405</v>
+      </c>
+      <c r="D8" s="20" t="n">
+        <v>2738</v>
+      </c>
+      <c r="E8" s="20" t="n">
+        <v>3025</v>
+      </c>
+      <c r="F8" s="20" t="n">
+        <v>3288</v>
+      </c>
+      <c r="G8" s="20" t="n">
+        <v>3989</v>
+      </c>
+      <c r="H8" s="20" t="n">
+        <v>3287</v>
+      </c>
+      <c r="I8" s="20" t="n">
+        <v>2703</v>
+      </c>
+      <c r="J8" s="20" t="n">
+        <v>1977</v>
+      </c>
+      <c r="K8" s="20" t="n">
+        <v>1496</v>
+      </c>
+      <c r="L8" s="20" t="n">
+        <v>1647</v>
+      </c>
+      <c r="M8" s="20" t="n">
+        <v>1562</v>
+      </c>
+      <c r="N8" s="20" t="n">
+        <v>1922</v>
+      </c>
+      <c r="O8" s="20" t="n">
+        <v>1965</v>
+      </c>
+      <c r="P8" s="20" t="n">
+        <v>2466</v>
+      </c>
+      <c r="Q8" s="20" t="n">
+        <v>2975</v>
+      </c>
+      <c r="R8" s="20" t="n">
+        <v>2909</v>
+      </c>
+      <c r="S8" s="20" t="n">
+        <v>3132</v>
+      </c>
+      <c r="T8" s="20" t="n">
+        <v>3365</v>
+      </c>
+      <c r="U8" s="20" t="n">
+        <v>3207</v>
+      </c>
+      <c r="V8" s="20" t="n">
+        <v>3895</v>
+      </c>
+      <c r="W8" s="20" t="n">
+        <v>4455</v>
+      </c>
+      <c r="X8" s="20" t="n">
+        <v>4174</v>
+      </c>
+      <c r="Y8" s="20" t="n">
+        <v>3750</v>
+      </c>
+      <c r="Z8" s="20" t="n">
+        <v>3363</v>
+      </c>
+      <c r="AA8" s="20" t="n">
+        <v>2789</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>Galveston</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="n">
+        <v>2235</v>
+      </c>
+      <c r="C9" s="20" t="n">
+        <v>2441</v>
+      </c>
+      <c r="D9" s="20" t="n">
+        <v>2687</v>
+      </c>
+      <c r="E9" s="20" t="n">
+        <v>2733</v>
+      </c>
+      <c r="F9" s="20" t="n">
+        <v>2995</v>
+      </c>
+      <c r="G9" s="20" t="n">
+        <v>3148</v>
+      </c>
+      <c r="H9" s="20" t="n">
+        <v>2732</v>
+      </c>
+      <c r="I9" s="20" t="n">
+        <v>2587</v>
+      </c>
+      <c r="J9" s="20" t="n">
+        <v>1517</v>
+      </c>
+      <c r="K9" s="20" t="n">
+        <v>1140</v>
+      </c>
+      <c r="L9" s="20" t="n">
+        <v>1731</v>
+      </c>
+      <c r="M9" s="20" t="n">
+        <v>1823</v>
+      </c>
+      <c r="N9" s="20" t="n">
+        <v>1784</v>
+      </c>
+      <c r="O9" s="20" t="n">
+        <v>2176</v>
+      </c>
+      <c r="P9" s="20" t="n">
+        <v>2638</v>
+      </c>
+      <c r="Q9" s="20" t="n">
+        <v>2372</v>
+      </c>
+      <c r="R9" s="20" t="n">
+        <v>2209</v>
+      </c>
+      <c r="S9" s="20" t="n">
+        <v>2095</v>
+      </c>
+      <c r="T9" s="20" t="n">
+        <v>2201</v>
+      </c>
+      <c r="U9" s="20" t="n">
+        <v>2197</v>
+      </c>
+      <c r="V9" s="20" t="n">
+        <v>2926</v>
+      </c>
+      <c r="W9" s="20" t="n">
+        <v>2474</v>
+      </c>
+      <c r="X9" s="20" t="n">
+        <v>2065</v>
+      </c>
+      <c r="Y9" s="20" t="n">
+        <v>2667</v>
+      </c>
+      <c r="Z9" s="20" t="n">
+        <v>3148</v>
+      </c>
+      <c r="AA9" s="20" t="n">
+        <v>2521</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>Liberty</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="n">
+        <v>213</v>
+      </c>
+      <c r="C10" s="20" t="n">
+        <v>212</v>
+      </c>
+      <c r="D10" s="20" t="n">
+        <v>235</v>
+      </c>
+      <c r="E10" s="20" t="n">
+        <v>258</v>
+      </c>
+      <c r="F10" s="20" t="n">
+        <v>263</v>
+      </c>
+      <c r="G10" s="20" t="n">
+        <v>287</v>
+      </c>
+      <c r="H10" s="20" t="n">
+        <v>293</v>
+      </c>
+      <c r="I10" s="20" t="n">
+        <v>251</v>
+      </c>
+      <c r="J10" s="20" t="n">
+        <v>240</v>
+      </c>
+      <c r="K10" s="20" t="n">
+        <v>231</v>
+      </c>
+      <c r="L10" s="20" t="n">
+        <v>193</v>
+      </c>
+      <c r="M10" s="20" t="n">
+        <v>252</v>
+      </c>
+      <c r="N10" s="20" t="n">
+        <v>165</v>
+      </c>
+      <c r="O10" s="20" t="n">
+        <v>175</v>
+      </c>
+      <c r="P10" s="20" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q10" s="20" t="n">
+        <v>306</v>
+      </c>
+      <c r="R10" s="20" t="n">
+        <v>456</v>
+      </c>
+      <c r="S10" s="20" t="n">
+        <v>544</v>
+      </c>
+      <c r="T10" s="20" t="n">
+        <v>722</v>
+      </c>
+      <c r="U10" s="20" t="n">
+        <v>823</v>
+      </c>
+      <c r="V10" s="20" t="n">
+        <v>964</v>
+      </c>
+      <c r="W10" s="20" t="n">
+        <v>1234</v>
+      </c>
+      <c r="X10" s="20" t="n">
+        <v>1558</v>
+      </c>
+      <c r="Y10" s="20" t="n">
+        <v>1295</v>
+      </c>
+      <c r="Z10" s="20" t="n">
+        <v>1319</v>
+      </c>
+      <c r="AA10" s="20" t="n">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>Chambers</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="n">
+        <v>309</v>
+      </c>
+      <c r="C11" s="20" t="n">
+        <v>326</v>
+      </c>
+      <c r="D11" s="20" t="n">
+        <v>270</v>
+      </c>
+      <c r="E11" s="20" t="n">
+        <v>417</v>
+      </c>
+      <c r="F11" s="20" t="n">
+        <v>571</v>
+      </c>
+      <c r="G11" s="20" t="n">
+        <v>517</v>
+      </c>
+      <c r="H11" s="20" t="n">
+        <v>368</v>
+      </c>
+      <c r="I11" s="20" t="n">
+        <v>457</v>
+      </c>
+      <c r="J11" s="20" t="n">
+        <v>316</v>
+      </c>
+      <c r="K11" s="20" t="n">
+        <v>257</v>
+      </c>
+      <c r="L11" s="20" t="n">
+        <v>226</v>
+      </c>
+      <c r="M11" s="20" t="n">
+        <v>216</v>
+      </c>
+      <c r="N11" s="20" t="n">
+        <v>293</v>
+      </c>
+      <c r="O11" s="20" t="n">
+        <v>318</v>
+      </c>
+      <c r="P11" s="20" t="n">
+        <v>377</v>
+      </c>
+      <c r="Q11" s="20" t="n">
+        <v>317</v>
+      </c>
+      <c r="R11" s="20" t="n">
+        <v>295</v>
+      </c>
+      <c r="S11" s="20" t="n">
+        <v>526</v>
+      </c>
+      <c r="T11" s="20" t="n">
+        <v>593</v>
+      </c>
+      <c r="U11" s="20" t="n">
+        <v>792</v>
+      </c>
+      <c r="V11" s="20" t="n">
+        <v>932</v>
+      </c>
+      <c r="W11" s="20" t="n">
+        <v>1052</v>
+      </c>
+      <c r="X11" s="20" t="n">
+        <v>745</v>
+      </c>
+      <c r="Y11" s="20" t="n">
+        <v>582</v>
+      </c>
+      <c r="Z11" s="20" t="n">
+        <v>642</v>
+      </c>
+      <c r="AA11" s="20" t="n">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>San Jacinto</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="20" t="n">
+        <v>13</v>
+      </c>
+      <c r="F12" s="20" t="n">
+        <v>11</v>
+      </c>
+      <c r="G12" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K12" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="N12" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="O12" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="P12" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" s="20" t="n">
+        <v>177</v>
+      </c>
+      <c r="R12" s="20" t="n">
+        <v>265</v>
+      </c>
+      <c r="S12" s="20" t="n">
+        <v>368</v>
+      </c>
+      <c r="T12" s="20" t="n">
+        <v>376</v>
+      </c>
+      <c r="U12" s="20" t="n">
+        <v>394</v>
+      </c>
+      <c r="V12" s="20" t="n">
+        <v>457</v>
+      </c>
+      <c r="W12" s="20" t="n">
+        <v>575</v>
+      </c>
+      <c r="X12" s="20" t="n">
+        <v>586</v>
+      </c>
+      <c r="Y12" s="20" t="n">
+        <v>548</v>
+      </c>
+      <c r="Z12" s="20" t="n">
+        <v>578</v>
+      </c>
+      <c r="AA12" s="20" t="n">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>Waller</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="n">
+        <v>21</v>
+      </c>
+      <c r="C13" s="20" t="n">
+        <v>17</v>
+      </c>
+      <c r="D13" s="20" t="n">
+        <v>31</v>
+      </c>
+      <c r="E13" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="F13" s="20" t="n">
+        <v>46</v>
+      </c>
+      <c r="G13" s="20" t="n">
+        <v>67</v>
+      </c>
+      <c r="H13" s="20" t="n">
+        <v>90</v>
+      </c>
+      <c r="I13" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="J13" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="K13" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="L13" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="M13" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="N13" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="O13" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="P13" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q13" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="R13" s="20" t="n">
+        <v>13</v>
+      </c>
+      <c r="S13" s="20" t="n">
+        <v>36</v>
+      </c>
+      <c r="T13" s="20" t="n">
+        <v>75</v>
+      </c>
+      <c r="U13" s="20" t="n">
+        <v>24</v>
+      </c>
+      <c r="V13" s="20" t="n">
+        <v>31</v>
+      </c>
+      <c r="W13" s="20" t="n">
+        <v>57</v>
+      </c>
+      <c r="X13" s="20" t="n">
+        <v>90</v>
+      </c>
+      <c r="Y13" s="20" t="n">
+        <v>247</v>
+      </c>
+      <c r="Z13" s="20" t="n">
+        <v>368</v>
+      </c>
+      <c r="AA13" s="20" t="n">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="n">
+        <v>114</v>
+      </c>
+      <c r="C14" s="20" t="n">
+        <v>34</v>
+      </c>
+      <c r="D14" s="20" t="n">
+        <v>45</v>
+      </c>
+      <c r="E14" s="20" t="n">
+        <v>45</v>
+      </c>
+      <c r="F14" s="20" t="n">
+        <v>28</v>
+      </c>
+      <c r="G14" s="20" t="n">
+        <v>46</v>
+      </c>
+      <c r="H14" s="20" t="n">
+        <v>39</v>
+      </c>
+      <c r="I14" s="20" t="n">
+        <v>54</v>
+      </c>
+      <c r="J14" s="20" t="n">
+        <v>36</v>
+      </c>
+      <c r="K14" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="L14" s="20" t="n">
+        <v>18</v>
+      </c>
+      <c r="M14" s="20" t="n">
+        <v>17</v>
+      </c>
+      <c r="N14" s="20" t="n">
+        <v>21</v>
+      </c>
+      <c r="O14" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="P14" s="20" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q14" s="20" t="n">
+        <v>19</v>
+      </c>
+      <c r="R14" s="20" t="n">
+        <v>22</v>
+      </c>
+      <c r="S14" s="20" t="n">
+        <v>34</v>
+      </c>
+      <c r="T14" s="20" t="n">
+        <v>211</v>
+      </c>
+      <c r="U14" s="20" t="n">
+        <v>27</v>
+      </c>
+      <c r="V14" s="20" t="n">
+        <v>289</v>
+      </c>
+      <c r="W14" s="20" t="n">
+        <v>43</v>
+      </c>
+      <c r="X14" s="20" t="n">
+        <v>374</v>
+      </c>
+      <c r="Y14" s="20" t="n">
+        <v>367</v>
+      </c>
+      <c r="Z14" s="20" t="n">
+        <v>412</v>
+      </c>
+      <c r="AA14" s="20" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="21" t="inlineStr">
+        <is>
+          <t>Metro total</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="n">
+        <v>28180</v>
+      </c>
+      <c r="C15" s="21" t="n">
+        <v>30496</v>
+      </c>
+      <c r="D15" s="21" t="n">
+        <v>34685</v>
+      </c>
+      <c r="E15" s="21" t="n">
+        <v>42053</v>
+      </c>
+      <c r="F15" s="21" t="n">
+        <v>45103</v>
+      </c>
+      <c r="G15" s="21" t="n">
+        <v>51205</v>
+      </c>
+      <c r="H15" s="21" t="n">
+        <v>55162</v>
+      </c>
+      <c r="I15" s="21" t="n">
+        <v>42217</v>
+      </c>
+      <c r="J15" s="21" t="n">
+        <v>28192</v>
+      </c>
+      <c r="K15" s="21" t="n">
+        <v>22369</v>
+      </c>
+      <c r="L15" s="21" t="n">
+        <v>22330</v>
+      </c>
+      <c r="M15" s="21" t="n">
+        <v>22889</v>
+      </c>
+      <c r="N15" s="21" t="n">
+        <v>28631</v>
+      </c>
+      <c r="O15" s="21" t="n">
+        <v>34548</v>
+      </c>
+      <c r="P15" s="21" t="n">
+        <v>38321</v>
+      </c>
+      <c r="Q15" s="21" t="n">
+        <v>36963</v>
+      </c>
+      <c r="R15" s="21" t="n">
+        <v>35632</v>
+      </c>
+      <c r="S15" s="21" t="n">
+        <v>36716</v>
+      </c>
+      <c r="T15" s="21" t="n">
+        <v>40887</v>
+      </c>
+      <c r="U15" s="21" t="n">
+        <v>39901</v>
+      </c>
+      <c r="V15" s="21" t="n">
+        <v>50632</v>
+      </c>
+      <c r="W15" s="21" t="n">
+        <v>53315</v>
+      </c>
+      <c r="X15" s="21" t="n">
+        <v>48485</v>
+      </c>
+      <c r="Y15" s="21" t="n">
+        <v>50992</v>
+      </c>
+      <c r="Z15" s="21" t="n">
+        <v>52703</v>
+      </c>
+      <c r="AA15" s="21" t="n">
+        <v>46341</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>Permit-issuing jurisdiction</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>County</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D18" s="19" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E18" s="19" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F18" s="19" t="n">
+        <v>2023</v>
+      </c>
+      <c r="G18" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H18" s="19" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="20" t="inlineStr">
+        <is>
+          <t>Harris County Unincorporated Area</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>Harris</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="n">
+        <v>13017</v>
+      </c>
+      <c r="D19" s="20" t="n">
+        <v>12023</v>
+      </c>
+      <c r="E19" s="20" t="n">
+        <v>9645</v>
+      </c>
+      <c r="F19" s="20" t="n">
+        <v>12252</v>
+      </c>
+      <c r="G19" s="20" t="n">
+        <v>12151</v>
+      </c>
+      <c r="H19" s="20" t="n">
+        <v>11014</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>Montgomery County Unincorporated Area</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>Montgomery</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="n">
+        <v>6940</v>
+      </c>
+      <c r="D20" s="20" t="n">
+        <v>9027</v>
+      </c>
+      <c r="E20" s="20" t="n">
+        <v>9131</v>
+      </c>
+      <c r="F20" s="20" t="n">
+        <v>8880</v>
+      </c>
+      <c r="G20" s="20" t="n">
+        <v>8895</v>
+      </c>
+      <c r="H20" s="20" t="n">
+        <v>9056</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="20" t="inlineStr">
+        <is>
+          <t>Fort Bend County Unincorporated Area</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>Fort Bend</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="n">
+        <v>7892</v>
+      </c>
+      <c r="D21" s="20" t="n">
+        <v>5351</v>
+      </c>
+      <c r="E21" s="20" t="n">
+        <v>4741</v>
+      </c>
+      <c r="F21" s="20" t="n">
+        <v>5014</v>
+      </c>
+      <c r="G21" s="20" t="n">
+        <v>6547</v>
+      </c>
+      <c r="H21" s="20" t="n">
+        <v>5673</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="20" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>Harris</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="n">
+        <v>5923</v>
+      </c>
+      <c r="D22" s="20" t="n">
+        <v>7146</v>
+      </c>
+      <c r="E22" s="20" t="n">
+        <v>6800</v>
+      </c>
+      <c r="F22" s="20" t="n">
+        <v>6609</v>
+      </c>
+      <c r="G22" s="20" t="n">
+        <v>6808</v>
+      </c>
+      <c r="H22" s="20" t="n">
+        <v>4774</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="20" t="inlineStr">
+        <is>
+          <t>Fulshear</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>Fort Bend</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="n">
+        <v>2345</v>
+      </c>
+      <c r="D23" s="20" t="n">
+        <v>3008</v>
+      </c>
+      <c r="E23" s="20" t="n">
+        <v>3001</v>
+      </c>
+      <c r="F23" s="20" t="n">
+        <v>3854</v>
+      </c>
+      <c r="G23" s="20" t="n">
+        <v>3970</v>
+      </c>
+      <c r="H23" s="20" t="n">
+        <v>3264</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>Conroe</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>Montgomery</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="n">
+        <v>1545</v>
+      </c>
+      <c r="D24" s="20" t="n">
+        <v>2574</v>
+      </c>
+      <c r="E24" s="20" t="n">
+        <v>1865</v>
+      </c>
+      <c r="F24" s="20" t="n">
+        <v>1814</v>
+      </c>
+      <c r="G24" s="20" t="n">
+        <v>2069</v>
+      </c>
+      <c r="H24" s="20" t="n">
+        <v>1839</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>Liberty County Unincorporated Area</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>Liberty</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="n">
+        <v>776</v>
+      </c>
+      <c r="D25" s="20" t="n">
+        <v>972</v>
+      </c>
+      <c r="E25" s="20" t="n">
+        <v>1261</v>
+      </c>
+      <c r="F25" s="20" t="n">
+        <v>992</v>
+      </c>
+      <c r="G25" s="20" t="n">
+        <v>1128</v>
+      </c>
+      <c r="H25" s="20" t="n">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>League City</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>Galveston</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="n">
+        <v>847</v>
+      </c>
+      <c r="D26" s="20" t="n">
+        <v>388</v>
+      </c>
+      <c r="E26" s="20" t="n">
+        <v>427</v>
+      </c>
+      <c r="F26" s="20" t="n">
+        <v>842</v>
+      </c>
+      <c r="G26" s="20" t="n">
+        <v>928</v>
+      </c>
+      <c r="H26" s="20" t="n">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="20" t="inlineStr">
+        <is>
+          <t>Brazoria County Unincorporated Area</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>Brazoria</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="n">
+        <v>1217</v>
+      </c>
+      <c r="D27" s="20" t="n">
+        <v>1361</v>
+      </c>
+      <c r="E27" s="20" t="n">
+        <v>1644</v>
+      </c>
+      <c r="F27" s="20" t="n">
+        <v>1280</v>
+      </c>
+      <c r="G27" s="20" t="n">
+        <v>1167</v>
+      </c>
+      <c r="H27" s="20" t="n">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>Manvel</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>Brazoria</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="n">
+        <v>774</v>
+      </c>
+      <c r="D28" s="20" t="n">
+        <v>931</v>
+      </c>
+      <c r="E28" s="20" t="n">
+        <v>891</v>
+      </c>
+      <c r="F28" s="20" t="n">
+        <v>686</v>
+      </c>
+      <c r="G28" s="20" t="n">
+        <v>630</v>
+      </c>
+      <c r="H28" s="20" t="n">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>Iowa Colony Village</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>Brazoria</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="n">
+        <v>796</v>
+      </c>
+      <c r="D29" s="20" t="n">
+        <v>759</v>
+      </c>
+      <c r="E29" s="20" t="n">
+        <v>627</v>
+      </c>
+      <c r="F29" s="20" t="n">
+        <v>780</v>
+      </c>
+      <c r="G29" s="20" t="n">
+        <v>883</v>
+      </c>
+      <c r="H29" s="20" t="n">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="20" t="inlineStr">
+        <is>
+          <t>Texas City</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>Galveston</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="n">
+        <v>778</v>
+      </c>
+      <c r="D30" s="20" t="n">
+        <v>829</v>
+      </c>
+      <c r="E30" s="20" t="n">
+        <v>481</v>
+      </c>
+      <c r="F30" s="20" t="n">
+        <v>596</v>
+      </c>
+      <c r="G30" s="20" t="n">
+        <v>974</v>
+      </c>
+      <c r="H30" s="20" t="n">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>San Jacinto County Unincorporated Area</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>San Jacinto</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="n">
+        <v>457</v>
+      </c>
+      <c r="D31" s="20" t="n">
+        <v>573</v>
+      </c>
+      <c r="E31" s="20" t="n">
+        <v>578</v>
+      </c>
+      <c r="F31" s="20" t="n">
+        <v>543</v>
+      </c>
+      <c r="G31" s="20" t="n">
+        <v>569</v>
+      </c>
+      <c r="H31" s="20" t="n">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="20" t="inlineStr">
+        <is>
+          <t>Rosenberg</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>Fort Bend</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="n">
+        <v>355</v>
+      </c>
+      <c r="D32" s="20" t="n">
+        <v>511</v>
+      </c>
+      <c r="E32" s="20" t="n">
+        <v>346</v>
+      </c>
+      <c r="F32" s="20" t="n">
+        <v>385</v>
+      </c>
+      <c r="G32" s="20" t="n">
+        <v>311</v>
+      </c>
+      <c r="H32" s="20" t="n">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="20" t="inlineStr">
+        <is>
+          <t>Chambers County Unincorporated Area</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>Chambers</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="n">
+        <v>665</v>
+      </c>
+      <c r="D33" s="20" t="n">
+        <v>793</v>
+      </c>
+      <c r="E33" s="20" t="n">
+        <v>481</v>
+      </c>
+      <c r="F33" s="20" t="n">
+        <v>382</v>
+      </c>
+      <c r="G33" s="20" t="n">
+        <v>414</v>
+      </c>
+      <c r="H33" s="20" t="n">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="20" t="inlineStr">
+        <is>
+          <t>Tomball</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>Harris</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="n">
+        <v>350</v>
+      </c>
+      <c r="D34" s="20" t="n">
+        <v>448</v>
+      </c>
+      <c r="E34" s="20" t="n">
+        <v>339</v>
+      </c>
+      <c r="F34" s="20" t="n">
+        <v>332</v>
+      </c>
+      <c r="G34" s="20" t="n">
+        <v>345</v>
+      </c>
+      <c r="H34" s="20" t="n">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="20" t="inlineStr">
+        <is>
+          <t>Alvin</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
+        <is>
+          <t>Brazoria</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="n">
+        <v>283</v>
+      </c>
+      <c r="D35" s="20" t="n">
+        <v>345</v>
+      </c>
+      <c r="E35" s="20" t="n">
+        <v>183</v>
+      </c>
+      <c r="F35" s="20" t="n">
+        <v>382</v>
+      </c>
+      <c r="G35" s="20" t="n">
+        <v>282</v>
+      </c>
+      <c r="H35" s="20" t="n">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="20" t="inlineStr">
+        <is>
+          <t>Waller</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>Waller</t>
+        </is>
+      </c>
+      <c r="C36" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D36" s="20" t="n">
+        <v>23</v>
+      </c>
+      <c r="E36" s="20" t="n">
+        <v>64</v>
+      </c>
+      <c r="F36" s="20" t="n">
+        <v>170</v>
+      </c>
+      <c r="G36" s="20" t="n">
+        <v>304</v>
+      </c>
+      <c r="H36" s="20" t="n">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="20" t="inlineStr">
+        <is>
+          <t>Magnolia Town</t>
+        </is>
+      </c>
+      <c r="B37" s="22" t="inlineStr">
+        <is>
+          <t>Montgomery</t>
+        </is>
+      </c>
+      <c r="C37" s="20" t="n">
+        <v>103</v>
+      </c>
+      <c r="D37" s="20" t="n">
+        <v>272</v>
+      </c>
+      <c r="E37" s="20" t="n">
+        <v>493</v>
+      </c>
+      <c r="F37" s="20" t="n">
+        <v>374</v>
+      </c>
+      <c r="G37" s="20" t="n">
+        <v>304</v>
+      </c>
+      <c r="H37" s="20" t="n">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="20" t="inlineStr">
+        <is>
+          <t>Montgomery</t>
+        </is>
+      </c>
+      <c r="B38" s="22" t="inlineStr">
+        <is>
+          <t>Montgomery</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="n">
+        <v>94</v>
+      </c>
+      <c r="D38" s="20" t="n">
+        <v>76</v>
+      </c>
+      <c r="E38" s="20" t="n">
+        <v>98</v>
+      </c>
+      <c r="F38" s="20" t="n">
+        <v>45</v>
+      </c>
+      <c r="G38" s="20" t="n">
+        <v>117</v>
+      </c>
+      <c r="H38" s="20" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="20" t="inlineStr">
+        <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
+      <c r="B39" s="22" t="inlineStr">
+        <is>
+          <t>Galveston</t>
+        </is>
+      </c>
+      <c r="C39" s="20" t="n">
+        <v>62</v>
+      </c>
+      <c r="D39" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="E39" s="20" t="n">
+        <v>63</v>
+      </c>
+      <c r="F39" s="20" t="n">
+        <v>58</v>
+      </c>
+      <c r="G39" s="20" t="n">
+        <v>364</v>
+      </c>
+      <c r="H39" s="20" t="n">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="20" t="inlineStr">
+        <is>
+          <t>Galveston</t>
+        </is>
+      </c>
+      <c r="B40" s="22" t="inlineStr">
+        <is>
+          <t>Galveston</t>
+        </is>
+      </c>
+      <c r="C40" s="20" t="n">
+        <v>237</v>
+      </c>
+      <c r="D40" s="20" t="n">
+        <v>251</v>
+      </c>
+      <c r="E40" s="20" t="n">
+        <v>215</v>
+      </c>
+      <c r="F40" s="20" t="n">
+        <v>289</v>
+      </c>
+      <c r="G40" s="20" t="n">
+        <v>279</v>
+      </c>
+      <c r="H40" s="20" t="n">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="20" t="inlineStr">
+        <is>
+          <t>Baytown</t>
+        </is>
+      </c>
+      <c r="B41" s="22" t="inlineStr">
+        <is>
+          <t>Harris</t>
+        </is>
+      </c>
+      <c r="C41" s="20" t="n">
+        <v>283</v>
+      </c>
+      <c r="D41" s="20" t="n">
+        <v>309</v>
+      </c>
+      <c r="E41" s="20" t="n">
+        <v>154</v>
+      </c>
+      <c r="F41" s="20" t="n">
+        <v>140</v>
+      </c>
+      <c r="G41" s="20" t="n">
+        <v>142</v>
+      </c>
+      <c r="H41" s="20" t="n">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="20" t="inlineStr">
+        <is>
+          <t>Austin County Unincorporated Area</t>
+        </is>
+      </c>
+      <c r="B42" s="22" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="C42" s="20" t="n">
+        <v>260</v>
+      </c>
+      <c r="D42" s="20" t="n">
+        <v>21</v>
+      </c>
+      <c r="E42" s="20" t="n">
+        <v>196</v>
+      </c>
+      <c r="F42" s="20" t="n">
+        <v>196</v>
+      </c>
+      <c r="G42" s="20" t="n">
+        <v>210</v>
+      </c>
+      <c r="H42" s="20" t="n">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="20" t="inlineStr">
+        <is>
+          <t>Galveston County Unincorporated Area</t>
+        </is>
+      </c>
+      <c r="B43" s="22" t="inlineStr">
+        <is>
+          <t>Galveston</t>
+        </is>
+      </c>
+      <c r="C43" s="20" t="n">
+        <v>318</v>
+      </c>
+      <c r="D43" s="20" t="n">
+        <v>344</v>
+      </c>
+      <c r="E43" s="20" t="n">
+        <v>422</v>
+      </c>
+      <c r="F43" s="20" t="n">
+        <v>271</v>
+      </c>
+      <c r="G43" s="20" t="n">
+        <v>166</v>
+      </c>
+      <c r="H43" s="20" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="20" t="inlineStr">
+        <is>
+          <t>Mont Belvieu</t>
+        </is>
+      </c>
+      <c r="B44" s="22" t="inlineStr">
+        <is>
+          <t>Chambers</t>
+        </is>
+      </c>
+      <c r="C44" s="20" t="n">
+        <v>240</v>
+      </c>
+      <c r="D44" s="20" t="n">
+        <v>230</v>
+      </c>
+      <c r="E44" s="20" t="n">
+        <v>209</v>
+      </c>
+      <c r="F44" s="20" t="n">
+        <v>178</v>
+      </c>
+      <c r="G44" s="20" t="n">
+        <v>188</v>
+      </c>
+      <c r="H44" s="20" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="20" t="inlineStr">
+        <is>
+          <t>La Marque</t>
+        </is>
+      </c>
+      <c r="B45" s="22" t="inlineStr">
+        <is>
+          <t>Galveston</t>
+        </is>
+      </c>
+      <c r="C45" s="20" t="n">
+        <v>241</v>
+      </c>
+      <c r="D45" s="20" t="n">
+        <v>225</v>
+      </c>
+      <c r="E45" s="20" t="n">
+        <v>217</v>
+      </c>
+      <c r="F45" s="20" t="n">
+        <v>268</v>
+      </c>
+      <c r="G45" s="20" t="n">
+        <v>105</v>
+      </c>
+      <c r="H45" s="20" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="20" t="inlineStr">
+        <is>
+          <t>Willis</t>
+        </is>
+      </c>
+      <c r="B46" s="22" t="inlineStr">
+        <is>
+          <t>Montgomery</t>
+        </is>
+      </c>
+      <c r="C46" s="20" t="n">
+        <v>96</v>
+      </c>
+      <c r="D46" s="20" t="n">
+        <v>105</v>
+      </c>
+      <c r="E46" s="20" t="n">
+        <v>17</v>
+      </c>
+      <c r="F46" s="20" t="n">
+        <v>80</v>
+      </c>
+      <c r="G46" s="20" t="n">
+        <v>173</v>
+      </c>
+      <c r="H46" s="20" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t>Dayton</t>
+        </is>
+      </c>
+      <c r="B47" s="22" t="inlineStr">
+        <is>
+          <t>Liberty</t>
+        </is>
+      </c>
+      <c r="C47" s="20" t="n">
+        <v>34</v>
+      </c>
+      <c r="D47" s="20" t="n">
+        <v>58</v>
+      </c>
+      <c r="E47" s="20" t="n">
+        <v>80</v>
+      </c>
+      <c r="F47" s="20" t="n">
+        <v>105</v>
+      </c>
+      <c r="G47" s="20" t="n">
+        <v>135</v>
+      </c>
+      <c r="H47" s="20" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="20" t="inlineStr">
+        <is>
+          <t>Katy</t>
+        </is>
+      </c>
+      <c r="B48" s="22" t="inlineStr">
+        <is>
+          <t>Harris</t>
+        </is>
+      </c>
+      <c r="C48" s="20" t="n">
+        <v>576</v>
+      </c>
+      <c r="D48" s="20" t="n">
+        <v>527</v>
+      </c>
+      <c r="E48" s="20" t="n">
+        <v>430</v>
+      </c>
+      <c r="F48" s="20" t="n">
+        <v>390</v>
+      </c>
+      <c r="G48" s="20" t="n">
+        <v>170</v>
+      </c>
+      <c r="H48" s="20" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="20" t="inlineStr">
+        <is>
+          <t>Missouri City</t>
+        </is>
+      </c>
+      <c r="B49" s="22" t="inlineStr">
+        <is>
+          <t>Fort Bend</t>
+        </is>
+      </c>
+      <c r="C49" s="20" t="n">
+        <v>634</v>
+      </c>
+      <c r="D49" s="20" t="n">
+        <v>693</v>
+      </c>
+      <c r="E49" s="20" t="n">
+        <v>421</v>
+      </c>
+      <c r="F49" s="20" t="n">
+        <v>435</v>
+      </c>
+      <c r="G49" s="20" t="n">
+        <v>118</v>
+      </c>
+      <c r="H49" s="20" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="20" t="inlineStr">
+        <is>
+          <t>Kemah</t>
+        </is>
+      </c>
+      <c r="B50" s="22" t="inlineStr">
+        <is>
+          <t>Galveston</t>
+        </is>
+      </c>
+      <c r="C50" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D50" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E50" s="20" t="n">
+        <v>17</v>
+      </c>
+      <c r="F50" s="20" t="n">
+        <v>145</v>
+      </c>
+      <c r="G50" s="20" t="n">
+        <v>131</v>
+      </c>
+      <c r="H50" s="20" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="20" t="inlineStr">
+        <is>
+          <t>Pearland</t>
+        </is>
+      </c>
+      <c r="B51" s="22" t="inlineStr">
+        <is>
+          <t>Brazoria</t>
+        </is>
+      </c>
+      <c r="C51" s="20" t="n">
+        <v>531</v>
+      </c>
+      <c r="D51" s="20" t="n">
+        <v>715</v>
+      </c>
+      <c r="E51" s="20" t="n">
+        <v>338</v>
+      </c>
+      <c r="F51" s="20" t="n">
+        <v>214</v>
+      </c>
+      <c r="G51" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="H51" s="20" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="20" t="inlineStr">
+        <is>
+          <t>Arcola</t>
+        </is>
+      </c>
+      <c r="B52" s="22" t="inlineStr">
+        <is>
+          <t>Fort Bend</t>
+        </is>
+      </c>
+      <c r="C52" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="20" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="20" t="inlineStr">
+        <is>
+          <t>Friendswood</t>
+        </is>
+      </c>
+      <c r="B53" s="22" t="inlineStr">
+        <is>
+          <t>Galveston</t>
+        </is>
+      </c>
+      <c r="C53" s="20" t="n">
+        <v>156</v>
+      </c>
+      <c r="D53" s="20" t="n">
+        <v>81</v>
+      </c>
+      <c r="E53" s="20" t="n">
+        <v>102</v>
+      </c>
+      <c r="F53" s="20" t="n">
+        <v>111</v>
+      </c>
+      <c r="G53" s="20" t="n">
+        <v>130</v>
+      </c>
+      <c r="H53" s="20" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="20" t="inlineStr">
+        <is>
+          <t>Pasadena</t>
+        </is>
+      </c>
+      <c r="B54" s="22" t="inlineStr">
+        <is>
+          <t>Harris</t>
+        </is>
+      </c>
+      <c r="C54" s="20" t="n">
+        <v>144</v>
+      </c>
+      <c r="D54" s="20" t="n">
+        <v>119</v>
+      </c>
+      <c r="E54" s="20" t="n">
+        <v>138</v>
+      </c>
+      <c r="F54" s="20" t="n">
+        <v>109</v>
+      </c>
+      <c r="G54" s="20" t="n">
+        <v>47</v>
+      </c>
+      <c r="H54" s="20" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="20" t="inlineStr">
+        <is>
+          <t>La Porte</t>
+        </is>
+      </c>
+      <c r="B55" s="22" t="inlineStr">
+        <is>
+          <t>Harris</t>
+        </is>
+      </c>
+      <c r="C55" s="20" t="n">
+        <v>255</v>
+      </c>
+      <c r="D55" s="20" t="n">
+        <v>320</v>
+      </c>
+      <c r="E55" s="20" t="n">
+        <v>285</v>
+      </c>
+      <c r="F55" s="20" t="n">
+        <v>154</v>
+      </c>
+      <c r="G55" s="20" t="n">
+        <v>109</v>
+      </c>
+      <c r="H55" s="20" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="20" t="inlineStr">
+        <is>
+          <t>Sealy</t>
+        </is>
+      </c>
+      <c r="B56" s="22" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="C56" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="D56" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="E56" s="20" t="n">
+        <v>147</v>
+      </c>
+      <c r="F56" s="20" t="n">
+        <v>138</v>
+      </c>
+      <c r="G56" s="20" t="n">
+        <v>146</v>
+      </c>
+      <c r="H56" s="20" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="20" t="inlineStr">
+        <is>
+          <t>Bellaire</t>
+        </is>
+      </c>
+      <c r="B57" s="22" t="inlineStr">
+        <is>
+          <t>Harris</t>
+        </is>
+      </c>
+      <c r="C57" s="20" t="n">
+        <v>61</v>
+      </c>
+      <c r="D57" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="E57" s="20" t="n">
+        <v>73</v>
+      </c>
+      <c r="F57" s="20" t="n">
+        <v>51</v>
+      </c>
+      <c r="G57" s="20" t="n">
+        <v>46</v>
+      </c>
+      <c r="H57" s="20" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="20" t="inlineStr">
+        <is>
+          <t>West University Place</t>
+        </is>
+      </c>
+      <c r="B58" s="22" t="inlineStr">
+        <is>
+          <t>Harris</t>
+        </is>
+      </c>
+      <c r="C58" s="20" t="n">
+        <v>45</v>
+      </c>
+      <c r="D58" s="20" t="n">
+        <v>48</v>
+      </c>
+      <c r="E58" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="F58" s="20" t="n">
+        <v>37</v>
+      </c>
+      <c r="G58" s="20" t="n">
+        <v>35</v>
+      </c>
+      <c r="H58" s="20" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="20" t="inlineStr">
+        <is>
+          <t>Hempstead</t>
+        </is>
+      </c>
+      <c r="B59" s="22" t="inlineStr">
+        <is>
+          <t>Waller</t>
+        </is>
+      </c>
+      <c r="C59" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="20" t="n">
+        <v>49</v>
+      </c>
+      <c r="G59" s="20" t="n">
+        <v>52</v>
+      </c>
+      <c r="H59" s="20" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="20" t="inlineStr">
+        <is>
+          <t>Sugar Land</t>
+        </is>
+      </c>
+      <c r="B60" s="22" t="inlineStr">
+        <is>
+          <t>Fort Bend</t>
+        </is>
+      </c>
+      <c r="C60" s="20" t="n">
+        <v>148</v>
+      </c>
+      <c r="D60" s="20" t="n">
+        <v>151</v>
+      </c>
+      <c r="E60" s="20" t="n">
+        <v>136</v>
+      </c>
+      <c r="F60" s="20" t="n">
+        <v>36</v>
+      </c>
+      <c r="G60" s="20" t="n">
+        <v>67</v>
+      </c>
+      <c r="H60" s="20" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="20" t="inlineStr">
+        <is>
+          <t>Beasley</t>
+        </is>
+      </c>
+      <c r="B61" s="22" t="inlineStr">
+        <is>
+          <t>Fort Bend</t>
+        </is>
+      </c>
+      <c r="C61" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" s="20" t="n">
+        <v>13</v>
+      </c>
+      <c r="E61" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="F61" s="20" t="n">
+        <v>41</v>
+      </c>
+      <c r="G61" s="20" t="n">
+        <v>41</v>
+      </c>
+      <c r="H61" s="20" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="20" t="inlineStr">
+        <is>
+          <t>Needville</t>
+        </is>
+      </c>
+      <c r="B62" s="22" t="inlineStr">
+        <is>
+          <t>Fort Bend</t>
+        </is>
+      </c>
+      <c r="C62" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="D62" s="20" t="n">
+        <v>16</v>
+      </c>
+      <c r="E62" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="F62" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="G62" s="20" t="n">
+        <v>11</v>
+      </c>
+      <c r="H62" s="20" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="20" t="inlineStr">
+        <is>
+          <t>Humble</t>
+        </is>
+      </c>
+      <c r="B63" s="22" t="inlineStr">
+        <is>
+          <t>Harris</t>
+        </is>
+      </c>
+      <c r="C63" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D63" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="G63" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="H63" s="20" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="20" t="inlineStr">
+        <is>
+          <t>Dickinson</t>
+        </is>
+      </c>
+      <c r="B64" s="22" t="inlineStr">
+        <is>
+          <t>Galveston</t>
+        </is>
+      </c>
+      <c r="C64" s="20" t="n">
+        <v>176</v>
+      </c>
+      <c r="D64" s="20" t="n">
+        <v>101</v>
+      </c>
+      <c r="E64" s="20" t="n">
+        <v>46</v>
+      </c>
+      <c r="F64" s="20" t="n">
+        <v>52</v>
+      </c>
+      <c r="G64" s="20" t="n">
+        <v>48</v>
+      </c>
+      <c r="H64" s="20" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="20" t="inlineStr">
+        <is>
+          <t>Spring Valley Village</t>
+        </is>
+      </c>
+      <c r="B65" s="22" t="inlineStr">
+        <is>
+          <t>Harris</t>
+        </is>
+      </c>
+      <c r="C65" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="D65" s="20" t="n">
+        <v>31</v>
+      </c>
+      <c r="E65" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="F65" s="20" t="n">
+        <v>19</v>
+      </c>
+      <c r="G65" s="20" t="n">
+        <v>13</v>
+      </c>
+      <c r="H65" s="20" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="20" t="inlineStr">
+        <is>
+          <t>Bellville</t>
+        </is>
+      </c>
+      <c r="B66" s="22" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="C66" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="D66" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E66" s="20" t="n">
+        <v>24</v>
+      </c>
+      <c r="F66" s="20" t="n">
+        <v>31</v>
+      </c>
+      <c r="G66" s="20" t="n">
+        <v>52</v>
+      </c>
+      <c r="H66" s="20" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="20" t="inlineStr">
+        <is>
+          <t>Seabrook</t>
+        </is>
+      </c>
+      <c r="B67" s="22" t="inlineStr">
+        <is>
+          <t>Harris</t>
+        </is>
+      </c>
+      <c r="C67" s="20" t="n">
+        <v>34</v>
+      </c>
+      <c r="D67" s="20" t="n">
+        <v>35</v>
+      </c>
+      <c r="E67" s="20" t="n">
+        <v>39</v>
+      </c>
+      <c r="F67" s="20" t="n">
+        <v>31</v>
+      </c>
+      <c r="G67" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="H67" s="20" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="20" t="inlineStr">
+        <is>
+          <t>Clute</t>
+        </is>
+      </c>
+      <c r="B68" s="22" t="inlineStr">
+        <is>
+          <t>Brazoria</t>
+        </is>
+      </c>
+      <c r="C68" s="20" t="n">
+        <v>46</v>
+      </c>
+      <c r="D68" s="20" t="n">
+        <v>58</v>
+      </c>
+      <c r="E68" s="20" t="n">
+        <v>39</v>
+      </c>
+      <c r="F68" s="20" t="n">
+        <v>46</v>
+      </c>
+      <c r="G68" s="20" t="n">
+        <v>21</v>
+      </c>
+      <c r="H68" s="20" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="20" t="inlineStr">
+        <is>
+          <t>Weston Lakes</t>
+        </is>
+      </c>
+      <c r="B69" s="22" t="inlineStr">
+        <is>
+          <t>Fort Bend</t>
+        </is>
+      </c>
+      <c r="C69" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="20" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="20" t="inlineStr">
+        <is>
+          <t>Hunters Creek Village</t>
+        </is>
+      </c>
+      <c r="B70" s="22" t="inlineStr">
+        <is>
+          <t>Harris</t>
+        </is>
+      </c>
+      <c r="C70" s="20" t="n">
+        <v>11</v>
+      </c>
+      <c r="D70" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="E70" s="20" t="n">
+        <v>22</v>
+      </c>
+      <c r="F70" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="G70" s="20" t="n">
+        <v>16</v>
+      </c>
+      <c r="H70" s="20" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="20" t="inlineStr">
+        <is>
+          <t>Stafford</t>
+        </is>
+      </c>
+      <c r="B71" s="22" t="inlineStr">
+        <is>
+          <t>Fort Bend</t>
+        </is>
+      </c>
+      <c r="C71" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D71" s="20" t="n">
+        <v>49</v>
+      </c>
+      <c r="E71" s="20" t="n">
+        <v>39</v>
+      </c>
+      <c r="F71" s="20" t="n">
+        <v>39</v>
+      </c>
+      <c r="G71" s="20" t="n">
+        <v>29</v>
+      </c>
+      <c r="H71" s="20" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="20" t="inlineStr">
+        <is>
+          <t>Richwood</t>
+        </is>
+      </c>
+      <c r="B72" s="22" t="inlineStr">
+        <is>
+          <t>Brazoria</t>
+        </is>
+      </c>
+      <c r="C72" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="D72" s="20" t="n">
+        <v>19</v>
+      </c>
+      <c r="E72" s="20" t="n">
+        <v>14</v>
+      </c>
+      <c r="F72" s="20" t="n">
+        <v>11</v>
+      </c>
+      <c r="G72" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="H72" s="20" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="20" t="inlineStr">
+        <is>
+          <t>South Houston</t>
+        </is>
+      </c>
+      <c r="B73" s="22" t="inlineStr">
+        <is>
+          <t>Harris</t>
+        </is>
+      </c>
+      <c r="C73" s="20" t="n">
+        <v>17</v>
+      </c>
+      <c r="D73" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="E73" s="20" t="n">
+        <v>26</v>
+      </c>
+      <c r="F73" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="G73" s="20" t="n">
+        <v>16</v>
+      </c>
+      <c r="H73" s="20" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="20" t="inlineStr">
+        <is>
+          <t>Kendleton</t>
+        </is>
+      </c>
+      <c r="B74" s="22" t="inlineStr">
+        <is>
+          <t>Fort Bend</t>
+        </is>
+      </c>
+      <c r="C74" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D74" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E74" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F74" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="G74" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H74" s="20" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="20" t="inlineStr">
+        <is>
+          <t>Surfside Beach</t>
+        </is>
+      </c>
+      <c r="B75" s="22" t="inlineStr">
+        <is>
+          <t>Brazoria</t>
+        </is>
+      </c>
+      <c r="C75" s="20" t="n">
+        <v>37</v>
+      </c>
+      <c r="D75" s="20" t="n">
+        <v>24</v>
+      </c>
+      <c r="E75" s="20" t="n">
+        <v>39</v>
+      </c>
+      <c r="F75" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="G75" s="20" t="n">
+        <v>16</v>
+      </c>
+      <c r="H75" s="20" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="20" t="inlineStr">
+        <is>
+          <t>Bunker Hill Village</t>
+        </is>
+      </c>
+      <c r="B76" s="22" t="inlineStr">
+        <is>
+          <t>Harris</t>
+        </is>
+      </c>
+      <c r="C76" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="D76" s="20" t="n">
+        <v>16</v>
+      </c>
+      <c r="E76" s="20" t="n">
+        <v>16</v>
+      </c>
+      <c r="F76" s="20" t="n">
+        <v>14</v>
+      </c>
+      <c r="G76" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="H76" s="20" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="20" t="inlineStr">
+        <is>
+          <t>Beach City</t>
+        </is>
+      </c>
+      <c r="B77" s="22" t="inlineStr">
+        <is>
+          <t>Chambers</t>
+        </is>
+      </c>
+      <c r="C77" s="20" t="n">
+        <v>14</v>
+      </c>
+      <c r="D77" s="20" t="n">
+        <v>23</v>
+      </c>
+      <c r="E77" s="20" t="n">
+        <v>42</v>
+      </c>
+      <c r="F77" s="20" t="n">
+        <v>16</v>
+      </c>
+      <c r="G77" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="H77" s="20" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="20" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="B78" s="22" t="inlineStr">
+        <is>
+          <t>Fort Bend</t>
+        </is>
+      </c>
+      <c r="C78" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="D78" s="20" t="n">
+        <v>136</v>
+      </c>
+      <c r="E78" s="20" t="n">
+        <v>189</v>
+      </c>
+      <c r="F78" s="20" t="n">
+        <v>126</v>
+      </c>
+      <c r="G78" s="20" t="n">
+        <v>98</v>
+      </c>
+      <c r="H78" s="20" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="20" t="inlineStr">
+        <is>
+          <t>Prairie View</t>
+        </is>
+      </c>
+      <c r="B79" s="22" t="inlineStr">
+        <is>
+          <t>Waller</t>
+        </is>
+      </c>
+      <c r="C79" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D79" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E79" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="F79" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="G79" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="H79" s="20" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="20" t="inlineStr">
+        <is>
+          <t>Jersey Village</t>
+        </is>
+      </c>
+      <c r="B80" s="22" t="inlineStr">
+        <is>
+          <t>Harris</t>
+        </is>
+      </c>
+      <c r="C80" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D80" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E80" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H80" s="20" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="20" t="inlineStr">
+        <is>
+          <t>Oyster Creek</t>
+        </is>
+      </c>
+      <c r="B81" s="22" t="inlineStr">
+        <is>
+          <t>Brazoria</t>
+        </is>
+      </c>
+      <c r="C81" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="D81" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G81" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H81" s="20" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="20" t="inlineStr">
+        <is>
+          <t>Piney Point Village</t>
+        </is>
+      </c>
+      <c r="B82" s="22" t="inlineStr">
+        <is>
+          <t>Harris</t>
+        </is>
+      </c>
+      <c r="C82" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="D82" s="20" t="n">
+        <v>11</v>
+      </c>
+      <c r="E82" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="F82" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="G82" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="H82" s="20" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="20" t="inlineStr">
+        <is>
+          <t>Roman Forest Town</t>
+        </is>
+      </c>
+      <c r="B83" s="22" t="inlineStr">
+        <is>
+          <t>Montgomery</t>
+        </is>
+      </c>
+      <c r="C83" s="20" t="n">
+        <v>19</v>
+      </c>
+      <c r="D83" s="20" t="n">
+        <v>84</v>
+      </c>
+      <c r="E83" s="20" t="n">
+        <v>94</v>
+      </c>
+      <c r="F83" s="20" t="n">
+        <v>24</v>
+      </c>
+      <c r="G83" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H83" s="20" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="20" t="inlineStr">
+        <is>
+          <t>Southside Place</t>
+        </is>
+      </c>
+      <c r="B84" s="22" t="inlineStr">
+        <is>
+          <t>Harris</t>
+        </is>
+      </c>
+      <c r="C84" s="20" t="n">
+        <v>14</v>
+      </c>
+      <c r="D84" s="20" t="n">
+        <v>16</v>
+      </c>
+      <c r="E84" s="20" t="n">
+        <v>13</v>
+      </c>
+      <c r="F84" s="20" t="n">
+        <v>11</v>
+      </c>
+      <c r="G84" s="20" t="n">
+        <v>11</v>
+      </c>
+      <c r="H84" s="20" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="20" t="inlineStr">
+        <is>
+          <t>Cut And Shoot</t>
+        </is>
+      </c>
+      <c r="B85" s="22" t="inlineStr">
+        <is>
+          <t>Montgomery</t>
+        </is>
+      </c>
+      <c r="C85" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F85" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="20" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="20" t="inlineStr">
+        <is>
+          <t>Deer Park</t>
+        </is>
+      </c>
+      <c r="B86" s="22" t="inlineStr">
+        <is>
+          <t>Harris</t>
+        </is>
+      </c>
+      <c r="C86" s="20" t="n">
+        <v>17</v>
+      </c>
+      <c r="D86" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="E86" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F86" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="G86" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="H86" s="20" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="20" t="inlineStr">
+        <is>
+          <t>Hedwig Village</t>
+        </is>
+      </c>
+      <c r="B87" s="22" t="inlineStr">
+        <is>
+          <t>Harris</t>
+        </is>
+      </c>
+      <c r="C87" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="D87" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="E87" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="F87" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="G87" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="H87" s="20" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="20" t="inlineStr">
+        <is>
+          <t>Shepherd</t>
+        </is>
+      </c>
+      <c r="B88" s="22" t="inlineStr">
+        <is>
+          <t>San Jacinto</t>
+        </is>
+      </c>
+      <c r="C88" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E88" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="F88" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="G88" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="H88" s="20" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="20" t="inlineStr">
+        <is>
+          <t>Hilshire Village</t>
+        </is>
+      </c>
+      <c r="B89" s="22" t="inlineStr">
+        <is>
+          <t>Harris</t>
+        </is>
+      </c>
+      <c r="C89" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D89" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E89" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F89" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="G89" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="H89" s="20" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="20" t="inlineStr">
+        <is>
+          <t>Jacinto City</t>
+        </is>
+      </c>
+      <c r="B90" s="22" t="inlineStr">
+        <is>
+          <t>Harris</t>
+        </is>
+      </c>
+      <c r="C90" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="D90" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="E90" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="F90" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="G90" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="H90" s="20" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="20" t="inlineStr">
+        <is>
+          <t>Liberty</t>
+        </is>
+      </c>
+      <c r="B91" s="22" t="inlineStr">
+        <is>
+          <t>Liberty</t>
+        </is>
+      </c>
+      <c r="C91" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="D91" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="E91" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="F91" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="G91" s="20" t="n">
+        <v>11</v>
+      </c>
+      <c r="H91" s="20" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="20" t="inlineStr">
+        <is>
+          <t>Wallis</t>
+        </is>
+      </c>
+      <c r="B92" s="22" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="C92" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="D92" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E92" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F92" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H92" s="20" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="20" t="inlineStr">
+        <is>
+          <t>Holiday Lakes Town</t>
+        </is>
+      </c>
+      <c r="B93" s="22" t="inlineStr">
+        <is>
+          <t>Brazoria</t>
+        </is>
+      </c>
+      <c r="C93" s="20" t="n">
+        <v>13</v>
+      </c>
+      <c r="D93" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E93" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F93" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" s="20" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="20" t="inlineStr">
+        <is>
+          <t>Lake Jackson</t>
+        </is>
+      </c>
+      <c r="B94" s="22" t="inlineStr">
+        <is>
+          <t>Brazoria</t>
+        </is>
+      </c>
+      <c r="C94" s="20" t="n">
+        <v>35</v>
+      </c>
+      <c r="D94" s="20" t="n">
+        <v>21</v>
+      </c>
+      <c r="E94" s="20" t="n">
+        <v>73</v>
+      </c>
+      <c r="F94" s="20" t="n">
+        <v>69</v>
+      </c>
+      <c r="G94" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="H94" s="20" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="20" t="inlineStr">
+        <is>
+          <t>Panorama Village</t>
+        </is>
+      </c>
+      <c r="B95" s="22" t="inlineStr">
+        <is>
+          <t>Montgomery</t>
+        </is>
+      </c>
+      <c r="C95" s="20" t="n">
+        <v>17</v>
+      </c>
+      <c r="D95" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="E95" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F95" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="G95" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="H95" s="20" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="20" t="inlineStr">
+        <is>
+          <t>Webster</t>
+        </is>
+      </c>
+      <c r="B96" s="22" t="inlineStr">
+        <is>
+          <t>Harris</t>
+        </is>
+      </c>
+      <c r="C96" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D96" s="20" t="n">
+        <v>46</v>
+      </c>
+      <c r="E96" s="20" t="n">
+        <v>49</v>
+      </c>
+      <c r="F96" s="20" t="n">
+        <v>79</v>
+      </c>
+      <c r="G96" s="20" t="n">
+        <v>45</v>
+      </c>
+      <c r="H96" s="20" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="20" t="inlineStr">
+        <is>
+          <t>Nassau Bay</t>
+        </is>
+      </c>
+      <c r="B97" s="22" t="inlineStr">
+        <is>
+          <t>Harris</t>
+        </is>
+      </c>
+      <c r="C97" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D97" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="G97" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H97" s="20" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="20" t="inlineStr">
+        <is>
+          <t>Shoreacres</t>
+        </is>
+      </c>
+      <c r="B98" s="22" t="inlineStr">
+        <is>
+          <t>Harris</t>
+        </is>
+      </c>
+      <c r="C98" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D98" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E98" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F98" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H98" s="20" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="20" t="inlineStr">
+        <is>
+          <t>Clear Lake Shores</t>
+        </is>
+      </c>
+      <c r="B99" s="22" t="inlineStr">
+        <is>
+          <t>Galveston</t>
+        </is>
+      </c>
+      <c r="C99" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="D99" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E99" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F99" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="G99" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H99" s="20" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="20" t="inlineStr">
+        <is>
+          <t>El Lago</t>
+        </is>
+      </c>
+      <c r="B100" s="22" t="inlineStr">
+        <is>
+          <t>Harris</t>
+        </is>
+      </c>
+      <c r="C100" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D100" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="H100" s="20" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="20" t="inlineStr">
+        <is>
+          <t>Tiki Island Village</t>
+        </is>
+      </c>
+      <c r="B101" s="22" t="inlineStr">
+        <is>
+          <t>Galveston</t>
+        </is>
+      </c>
+      <c r="C101" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="D101" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="E101" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="F101" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="G101" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="H101" s="20" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="20" t="inlineStr">
+        <is>
+          <t>Anahuac</t>
+        </is>
+      </c>
+      <c r="B102" s="22" t="inlineStr">
+        <is>
+          <t>Chambers</t>
+        </is>
+      </c>
+      <c r="C102" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="D102" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="E102" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="F102" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="G102" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H102" s="20" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="20" t="inlineStr">
+        <is>
+          <t>Freeport</t>
+        </is>
+      </c>
+      <c r="B103" s="22" t="inlineStr">
+        <is>
+          <t>Brazoria</t>
+        </is>
+      </c>
+      <c r="C103" s="20" t="n">
+        <v>16</v>
+      </c>
+      <c r="D103" s="20" t="n">
+        <v>18</v>
+      </c>
+      <c r="E103" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="F103" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="G103" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="H103" s="20" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="20" t="inlineStr">
+        <is>
+          <t>Simonton</t>
+        </is>
+      </c>
+      <c r="B104" s="22" t="inlineStr">
+        <is>
+          <t>Fort Bend</t>
+        </is>
+      </c>
+      <c r="C104" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D104" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="E104" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F104" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H104" s="20" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="20" t="inlineStr">
+        <is>
+          <t>West Columbia</t>
+        </is>
+      </c>
+      <c r="B105" s="22" t="inlineStr">
+        <is>
+          <t>Brazoria</t>
+        </is>
+      </c>
+      <c r="C105" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="D105" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E105" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="F105" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="G105" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="H105" s="20" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="20" t="inlineStr">
+        <is>
+          <t>Woodbranch Village</t>
+        </is>
+      </c>
+      <c r="B106" s="22" t="inlineStr">
+        <is>
+          <t>Montgomery</t>
+        </is>
+      </c>
+      <c r="C106" s="20" t="n">
+        <v>33</v>
+      </c>
+      <c r="D106" s="20" t="n">
+        <v>31</v>
+      </c>
+      <c r="E106" s="20" t="n">
+        <v>29</v>
+      </c>
+      <c r="F106" s="20" t="n">
+        <v>21</v>
+      </c>
+      <c r="G106" s="20" t="n">
+        <v>18</v>
+      </c>
+      <c r="H106" s="20" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="20" t="inlineStr">
+        <is>
+          <t>Brazoria</t>
+        </is>
+      </c>
+      <c r="B107" s="22" t="inlineStr">
+        <is>
+          <t>Brazoria</t>
+        </is>
+      </c>
+      <c r="C107" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="D107" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E107" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F107" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="G107" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="H107" s="20" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="20" t="inlineStr">
+        <is>
+          <t>Brookside Village</t>
+        </is>
+      </c>
+      <c r="B108" s="22" t="inlineStr">
+        <is>
+          <t>Brazoria</t>
+        </is>
+      </c>
+      <c r="C108" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="D108" s="20" t="n">
+        <v>11</v>
+      </c>
+      <c r="E108" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="F108" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="G108" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H108" s="20" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="20" t="inlineStr">
+        <is>
+          <t>Danbury</t>
+        </is>
+      </c>
+      <c r="B109" s="22" t="inlineStr">
+        <is>
+          <t>Brazoria</t>
+        </is>
+      </c>
+      <c r="C109" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D109" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="E109" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F109" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="G109" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H109" s="20" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="20" t="inlineStr">
+        <is>
+          <t>Hardin</t>
+        </is>
+      </c>
+      <c r="B110" s="22" t="inlineStr">
+        <is>
+          <t>Liberty</t>
+        </is>
+      </c>
+      <c r="C110" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D110" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E110" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F110" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H110" s="20" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="20" t="inlineStr">
+        <is>
+          <t>Jamaica Beach Village</t>
+        </is>
+      </c>
+      <c r="B111" s="22" t="inlineStr">
+        <is>
+          <t>Galveston</t>
+        </is>
+      </c>
+      <c r="C111" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="D111" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="E111" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="F111" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="G111" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H111" s="20" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="20" t="inlineStr">
+        <is>
+          <t>Jones Creek Village</t>
+        </is>
+      </c>
+      <c r="B112" s="22" t="inlineStr">
+        <is>
+          <t>Brazoria</t>
+        </is>
+      </c>
+      <c r="C112" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D112" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="E112" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F112" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G112" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" s="20" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="20" t="inlineStr">
+        <is>
+          <t>Old River-Winfree</t>
+        </is>
+      </c>
+      <c r="B113" s="22" t="inlineStr">
+        <is>
+          <t>Chambers</t>
+        </is>
+      </c>
+      <c r="C113" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D113" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F113" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="G113" s="20" t="n">
+        <v>29</v>
+      </c>
+      <c r="H113" s="20" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="20" t="inlineStr">
+        <is>
+          <t>San Felipe Town</t>
+        </is>
+      </c>
+      <c r="B114" s="22" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="C114" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D114" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E114" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F114" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H114" s="20" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="20" t="inlineStr">
+        <is>
+          <t>Sweeny</t>
+        </is>
+      </c>
+      <c r="B115" s="22" t="inlineStr">
+        <is>
+          <t>Brazoria</t>
+        </is>
+      </c>
+      <c r="C115" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="D115" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E115" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="F115" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="G115" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="H115" s="20" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="20" t="inlineStr">
+        <is>
+          <t>Baileys Prairie Village</t>
+        </is>
+      </c>
+      <c r="B116" s="22" t="inlineStr">
+        <is>
+          <t>Brazoria</t>
+        </is>
+      </c>
+      <c r="C116" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="D116" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="E116" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F116" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G116" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H116" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="20" t="inlineStr">
+        <is>
+          <t>Bayou Vista Village</t>
+        </is>
+      </c>
+      <c r="B117" s="22" t="inlineStr">
+        <is>
+          <t>Galveston</t>
+        </is>
+      </c>
+      <c r="C117" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="D117" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="E117" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="F117" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H117" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="20" t="inlineStr">
+        <is>
+          <t>Shenandoah</t>
+        </is>
+      </c>
+      <c r="B118" s="22" t="inlineStr">
+        <is>
+          <t>Montgomery</t>
+        </is>
+      </c>
+      <c r="C118" s="20" t="n">
+        <v>51</v>
+      </c>
+      <c r="D118" s="20" t="n">
+        <v>45</v>
+      </c>
+      <c r="E118" s="20" t="n">
+        <v>86</v>
+      </c>
+      <c r="F118" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="G118" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="20" t="inlineStr">
+        <is>
+          <t>Stagecoach Town</t>
+        </is>
+      </c>
+      <c r="B119" s="22" t="inlineStr">
+        <is>
+          <t>Montgomery</t>
+        </is>
+      </c>
+      <c r="C119" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D119" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E119" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="G119" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H119" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="20" t="inlineStr">
+        <is>
+          <t>Taylor Lake Village</t>
+        </is>
+      </c>
+      <c r="B120" s="22" t="inlineStr">
+        <is>
+          <t>Harris</t>
+        </is>
+      </c>
+      <c r="C120" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D120" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="E120" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="F120" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="G120" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="H120" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="20" t="inlineStr">
+        <is>
+          <t>Angleton</t>
+        </is>
+      </c>
+      <c r="B121" s="22" t="inlineStr">
+        <is>
+          <t>Brazoria</t>
+        </is>
+      </c>
+      <c r="C121" s="20" t="n">
+        <v>83</v>
+      </c>
+      <c r="D121" s="20" t="n">
+        <v>154</v>
+      </c>
+      <c r="E121" s="20" t="n">
+        <v>271</v>
+      </c>
+      <c r="F121" s="20" t="n">
+        <v>231</v>
+      </c>
+      <c r="G121" s="20" t="n">
+        <v>248</v>
+      </c>
+      <c r="H121" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="20" t="inlineStr">
+        <is>
+          <t>Brookshire</t>
+        </is>
+      </c>
+      <c r="B122" s="22" t="inlineStr">
+        <is>
+          <t>Waller</t>
+        </is>
+      </c>
+      <c r="C122" s="20" t="n">
+        <v>22</v>
+      </c>
+      <c r="D122" s="20" t="n">
+        <v>22</v>
+      </c>
+      <c r="E122" s="20" t="n">
+        <v>17</v>
+      </c>
+      <c r="F122" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="G122" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H122" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="20" t="inlineStr">
+        <is>
+          <t>Cleveland</t>
+        </is>
+      </c>
+      <c r="B123" s="22" t="inlineStr">
+        <is>
+          <t>Liberty</t>
+        </is>
+      </c>
+      <c r="C123" s="20" t="n">
+        <v>140</v>
+      </c>
+      <c r="D123" s="20" t="n">
+        <v>190</v>
+      </c>
+      <c r="E123" s="20" t="n">
+        <v>205</v>
+      </c>
+      <c r="F123" s="20" t="n">
+        <v>186</v>
+      </c>
+      <c r="G123" s="20" t="n">
+        <v>43</v>
+      </c>
+      <c r="H123" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="20" t="inlineStr">
+        <is>
+          <t>Galena Park</t>
+        </is>
+      </c>
+      <c r="B124" s="22" t="inlineStr">
+        <is>
+          <t>Harris</t>
+        </is>
+      </c>
+      <c r="C124" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D124" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E124" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F124" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="G124" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="20" t="inlineStr">
+        <is>
+          <t>Hitchcock</t>
+        </is>
+      </c>
+      <c r="B125" s="22" t="inlineStr">
+        <is>
+          <t>Galveston</t>
+        </is>
+      </c>
+      <c r="C125" s="20" t="n">
+        <v>77</v>
+      </c>
+      <c r="D125" s="20" t="n">
+        <v>142</v>
+      </c>
+      <c r="E125" s="20" t="n">
+        <v>38</v>
+      </c>
+      <c r="F125" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="G125" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="H125" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="20" t="inlineStr">
+        <is>
+          <t>Morgans Point</t>
+        </is>
+      </c>
+      <c r="B126" s="22" t="inlineStr">
+        <is>
+          <t>Harris</t>
+        </is>
+      </c>
+      <c r="C126" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D126" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F126" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G126" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="20" t="inlineStr">
+        <is>
+          <t>Oak Ridge North</t>
+        </is>
+      </c>
+      <c r="B127" s="22" t="inlineStr">
+        <is>
+          <t>Montgomery</t>
+        </is>
+      </c>
+      <c r="C127" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D127" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F127" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="G127" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H127" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="20" t="inlineStr">
+        <is>
+          <t>Orchard</t>
+        </is>
+      </c>
+      <c r="B128" s="22" t="inlineStr">
+        <is>
+          <t>Fort Bend</t>
+        </is>
+      </c>
+      <c r="C128" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D128" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F128" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="G128" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H128" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="20" t="inlineStr">
+        <is>
+          <t>Pattison</t>
+        </is>
+      </c>
+      <c r="B129" s="22" t="inlineStr">
+        <is>
+          <t>Waller</t>
+        </is>
+      </c>
+      <c r="C129" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D129" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="E129" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G129" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H129" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="20" t="inlineStr">
+        <is>
+          <t>Quintana Town</t>
+        </is>
+      </c>
+      <c r="B130" s="22" t="inlineStr">
+        <is>
+          <t>Brazoria</t>
+        </is>
+      </c>
+      <c r="C130" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D130" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G130" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/ICON_Greater_Houston_Rolodex.xlsx
+++ b/docs/ICON_Greater_Houston_Rolodex.xlsx
@@ -582,7 +582,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated from houston-data.json · build 44 · 2026-09-11 · public render. Do not hand-edit the HTML deck; it regenerates from the same file.</t>
+          <t>Generated from houston-data.json · build 45 · 2026-09-11 · public render. Do not hand-edit the HTML deck; it regenerates from the same file.</t>
         </is>
       </c>
     </row>
@@ -28894,7 +28894,7 @@
     <row r="266">
       <c r="A266" s="17" t="inlineStr">
         <is>
-          <t>NOTE. A filled LinkedIn cell means the profile was opened or the search result read and the headline named the firm; column W records what was read. Where that test failed the cell is left empty rather than guessed, because a fabricated slug passes visual inspection and then fails in front of the person it names. Column Q searches for the empty ones in your own session. Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Capital is a qualifier, not a count. Source: ICON Greater Houston screen, build 44, 2026-09-11.</t>
+          <t>NOTE. A filled LinkedIn cell means the profile was opened or the search result read and the headline named the firm; column W records what was read. Where that test failed the cell is left empty rather than guessed, because a fabricated slug passes visual inspection and then fails in front of the person it names. Column Q searches for the empty ones in your own session. Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Capital is a qualifier, not a count. Source: ICON Greater Houston screen, build 45, 2026-09-11.</t>
         </is>
       </c>
     </row>

--- a/docs/ICON_Greater_Houston_Rolodex.xlsx
+++ b/docs/ICON_Greater_Houston_Rolodex.xlsx
@@ -582,7 +582,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated from houston-data.json · build 45 · 2026-09-11 · public render. Do not hand-edit the HTML deck; it regenerates from the same file.</t>
+          <t>Generated from houston-data.json · build 46 · 2026-09-11 · public render. Do not hand-edit the HTML deck; it regenerates from the same file.</t>
         </is>
       </c>
     </row>
@@ -28894,7 +28894,7 @@
     <row r="266">
       <c r="A266" s="17" t="inlineStr">
         <is>
-          <t>NOTE. A filled LinkedIn cell means the profile was opened or the search result read and the headline named the firm; column W records what was read. Where that test failed the cell is left empty rather than guessed, because a fabricated slug passes visual inspection and then fails in front of the person it names. Column Q searches for the empty ones in your own session. Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Capital is a qualifier, not a count. Source: ICON Greater Houston screen, build 45, 2026-09-11.</t>
+          <t>NOTE. A filled LinkedIn cell means the profile was opened or the search result read and the headline named the firm; column W records what was read. Where that test failed the cell is left empty rather than guessed, because a fabricated slug passes visual inspection and then fails in front of the person it names. Column Q searches for the empty ones in your own session. Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Capital is a qualifier, not a count. Source: ICON Greater Houston screen, build 46, 2026-09-11.</t>
         </is>
       </c>
     </row>

--- a/docs/ICON_Greater_Houston_Rolodex.xlsx
+++ b/docs/ICON_Greater_Houston_Rolodex.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Permits" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Contacts'!$A$6:$Z$264</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Contacts'!$A$6:$Z$265</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z266"/>
+  <dimension ref="A1:Z267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -582,7 +582,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated from houston-data.json · build 46 · 2026-09-11 · public render. Do not hand-edit the HTML deck; it regenerates from the same file.</t>
+          <t>Generated from houston-data.json · build 48 · 2026-09-11 · public render. Do not hand-edit the HTML deck; it regenerates from the same file.</t>
         </is>
       </c>
     </row>
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>COUNTA($A$7:$A$264)</f>
+        <f>COUNTA($A$7:$A$265)</f>
         <v/>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="D3" s="3">
-        <f>COUNTIF($R$7:$R$264,"ok")</f>
+        <f>COUNTIF($R$7:$R$265,"ok")</f>
         <v/>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="F3" s="3">
-        <f>COUNTIF($R$7:$R$264,"ADD LINKEDIN")</f>
+        <f>COUNTIF($R$7:$R$265,"ADD LINKEDIN")</f>
         <v/>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="H3" s="3">
-        <f>SUMPRODUCT((COUNTIF(OFFSET($B$7,ROW($B$7:$B$264)-ROW($B$7),0,1,1),$B$7:$B$264)&gt;0)*($D$7:$D$264="Strong target")/COUNTIF($B$7:$B$264,$B$7:$B$264&amp;""))</f>
+        <f>SUMPRODUCT((COUNTIF(OFFSET($B$7,ROW($B$7:$B$265)-ROW($B$7),0,1,1),$B$7:$B$265)&gt;0)*($D$7:$D$265="Strong target")/COUNTIF($B$7:$B$265,$B$7:$B$265&amp;""))</f>
         <v/>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="J3" s="3">
-        <f>COUNTIF($V$7:$V$264,"YES")</f>
+        <f>COUNTIF($V$7:$V$265,"YES")</f>
         <v/>
       </c>
     </row>
@@ -24044,17 +24044,17 @@
     <row r="218">
       <c r="A218" s="12" t="inlineStr">
         <is>
-          <t>Danny Signorelli</t>
+          <t>David O'Reilly</t>
         </is>
       </c>
       <c r="B218" s="12" t="inlineStr">
         <is>
-          <t>The Signorelli Company</t>
+          <t>Howard Hughes Holdings Inc.</t>
         </is>
       </c>
       <c r="C218" s="12" t="inlineStr">
         <is>
-          <t>Founder and Chief Executive Officer</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="D218" s="13" t="inlineStr">
@@ -24072,12 +24072,12 @@
       </c>
       <c r="G218" s="12" t="inlineStr">
         <is>
-          <t>The Woodlands HQ / Fort Bend, Liberty</t>
+          <t>The Woodlands HQ / Harris, Montgomery</t>
         </is>
       </c>
       <c r="H218" s="12" t="inlineStr">
         <is>
-          <t>23,000+ paper lots in pipeline</t>
+          <t>1,802 residential acres left to sell</t>
         </is>
       </c>
       <c r="I218" s="14" t="inlineStr">
@@ -24085,59 +24085,74 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J218" s="15" t="inlineStr"/>
+      <c r="J218" s="15" t="inlineStr">
+        <is>
+          <t>Three communities on one metro's edge, 1,802 residential acres still to sell.</t>
+        </is>
+      </c>
       <c r="K218" s="14" t="inlineStr">
         <is>
-          <t>Partly</t>
-        </is>
-      </c>
-      <c r="L218" s="15" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L218" s="15" t="inlineStr">
+        <is>
+          <t>It sells finished lots. The builder who buys them buys the wall.</t>
+        </is>
+      </c>
       <c r="M218" s="14" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N218" s="15" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N218" s="15" t="inlineStr">
+        <is>
+          <t>Financed and opened Greater Houston's first mass timber office building, with low-carbon concrete in the same structure.</t>
+        </is>
+      </c>
       <c r="O218" s="14" t="inlineStr">
         <is>
-          <t>Partly</t>
-        </is>
-      </c>
-      <c r="P218" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/danny-signorelli-6284461b/</t>
-        </is>
-      </c>
-      <c r="Q218" s="12" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P218" s="10" t="inlineStr"/>
+      <c r="Q218" s="12">
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=David%20O%27Reilly%20Howard%20Hughes%20Holdings%20Inc.","search")</f>
+        <v/>
+      </c>
       <c r="R218" s="16">
         <f>IF(P218="","ADD LINKEDIN","ok")</f>
         <v/>
       </c>
       <c r="S218" s="12" t="inlineStr">
         <is>
-          <t>https://www.signorellicompany.com/</t>
+          <t>https://www.howardhughes.com/</t>
         </is>
       </c>
       <c r="T218" s="15" t="inlineStr">
         <is>
-          <t>Sells lots, but owns First America Homes, which holds all three counts. One president runs both.</t>
+          <t>1,802 residential acres left to sell across three communities, and it paid to put up Greater Houston's first mass timber office. It sells lots, so the builder buys the wall.</t>
         </is>
       </c>
       <c r="U218" s="12" t="inlineStr"/>
       <c r="V218" s="15" t="inlineStr">
         <is>
-          <t>CEO, President, The Signorelli Company. Greater Houston.</t>
-        </is>
-      </c>
-      <c r="W218" s="12" t="inlineStr"/>
+          <t>Chief Executive Officer on Howard Hughes's own leadership page.</t>
+        </is>
+      </c>
+      <c r="W218" s="12" t="inlineStr">
+        <is>
+          <t>https://investor.howardhughes.com/governance/leadership</t>
+        </is>
+      </c>
       <c r="X218" s="12" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/signorelli-company</t>
+          <t>https://www.linkedin.com/company/the-howard-hughes-corporation</t>
         </is>
       </c>
       <c r="Y218" s="12" t="inlineStr">
         <is>
-          <t>https://www.signorellicompany.com/our-leadership</t>
+          <t>https://investor.howardhughes.com/governance/leadership</t>
         </is>
       </c>
       <c r="Z218" s="12" t="inlineStr"/>
@@ -24145,17 +24160,17 @@
     <row r="219">
       <c r="A219" s="6" t="inlineStr">
         <is>
-          <t>Jeff Dewese</t>
+          <t>Bill Ackman</t>
         </is>
       </c>
       <c r="B219" s="6" t="inlineStr">
         <is>
-          <t>The Signorelli Company</t>
+          <t>Howard Hughes Holdings Inc.</t>
         </is>
       </c>
       <c r="C219" s="6" t="inlineStr">
         <is>
-          <t>President, Land Division</t>
+          <t>Executive Chairman of the Board</t>
         </is>
       </c>
       <c r="D219" s="7" t="inlineStr">
@@ -24173,12 +24188,12 @@
       </c>
       <c r="G219" s="6" t="inlineStr">
         <is>
-          <t>The Woodlands HQ / Fort Bend, Liberty</t>
+          <t>The Woodlands HQ / Harris, Montgomery</t>
         </is>
       </c>
       <c r="H219" s="6" t="inlineStr">
         <is>
-          <t>23,000+ paper lots in pipeline</t>
+          <t>1,802 residential acres left to sell</t>
         </is>
       </c>
       <c r="I219" s="8" t="inlineStr">
@@ -24186,27 +24201,39 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J219" s="9" t="inlineStr"/>
+      <c r="J219" s="9" t="inlineStr">
+        <is>
+          <t>Three communities on one metro's edge, 1,802 residential acres still to sell.</t>
+        </is>
+      </c>
       <c r="K219" s="8" t="inlineStr">
         <is>
-          <t>Partly</t>
-        </is>
-      </c>
-      <c r="L219" s="9" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L219" s="9" t="inlineStr">
+        <is>
+          <t>It sells finished lots. The builder who buys them buys the wall.</t>
+        </is>
+      </c>
       <c r="M219" s="8" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N219" s="9" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N219" s="9" t="inlineStr">
+        <is>
+          <t>Financed and opened Greater Houston's first mass timber office building, with low-carbon concrete in the same structure.</t>
+        </is>
+      </c>
       <c r="O219" s="8" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P219" s="10" t="inlineStr"/>
       <c r="Q219" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Jeff%20Dewese%20The%20Signorelli%20Company","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Bill%20Ackman%20Howard%20Hughes%20Holdings%20Inc.","search")</f>
         <v/>
       </c>
       <c r="R219" s="11">
@@ -24215,33 +24242,33 @@
       </c>
       <c r="S219" s="6" t="inlineStr">
         <is>
-          <t>https://www.signorellicompany.com/</t>
+          <t>https://www.howardhughes.com/</t>
         </is>
       </c>
       <c r="T219" s="9" t="inlineStr">
         <is>
-          <t>Sells lots, but owns First America Homes, which holds all three counts. One president runs both.</t>
+          <t>1,802 residential acres left to sell across three communities, and it paid to put up Greater Houston's first mass timber office. It sells lots, so the builder buys the wall.</t>
         </is>
       </c>
       <c r="U219" s="6" t="inlineStr"/>
       <c r="V219" s="9" t="inlineStr">
         <is>
-          <t>Signorelli's own bio page. President, Land Division, overseeing land acquisition, planning and construction management for Granger Pines, Cielo and Austin Point.</t>
+          <t>Executive Chairman on Howard Hughes's own leadership page.</t>
         </is>
       </c>
       <c r="W219" s="6" t="inlineStr">
         <is>
-          <t>https://www.signorellicompany.com/our-leadership/15/jeff-dewese</t>
+          <t>https://investor.howardhughes.com/governance/leadership</t>
         </is>
       </c>
       <c r="X219" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/signorelli-company</t>
+          <t>https://www.linkedin.com/company/the-howard-hughes-corporation</t>
         </is>
       </c>
       <c r="Y219" s="6" t="inlineStr">
         <is>
-          <t>https://www.signorellicompany.com/our-leadership</t>
+          <t>https://investor.howardhughes.com/governance/leadership</t>
         </is>
       </c>
       <c r="Z219" s="6" t="inlineStr"/>
@@ -24249,17 +24276,17 @@
     <row r="220">
       <c r="A220" s="12" t="inlineStr">
         <is>
-          <t>Harry Dinham</t>
+          <t>Ryan Israel</t>
         </is>
       </c>
       <c r="B220" s="12" t="inlineStr">
         <is>
-          <t>The Signorelli Company</t>
+          <t>Howard Hughes Holdings Inc.</t>
         </is>
       </c>
       <c r="C220" s="12" t="inlineStr">
         <is>
-          <t>Chief Financial Officer</t>
+          <t>Chief Investment Officer</t>
         </is>
       </c>
       <c r="D220" s="13" t="inlineStr">
@@ -24277,12 +24304,12 @@
       </c>
       <c r="G220" s="12" t="inlineStr">
         <is>
-          <t>The Woodlands HQ / Fort Bend, Liberty</t>
+          <t>The Woodlands HQ / Harris, Montgomery</t>
         </is>
       </c>
       <c r="H220" s="12" t="inlineStr">
         <is>
-          <t>23,000+ paper lots in pipeline</t>
+          <t>1,802 residential acres left to sell</t>
         </is>
       </c>
       <c r="I220" s="14" t="inlineStr">
@@ -24290,27 +24317,39 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J220" s="15" t="inlineStr"/>
+      <c r="J220" s="15" t="inlineStr">
+        <is>
+          <t>Three communities on one metro's edge, 1,802 residential acres still to sell.</t>
+        </is>
+      </c>
       <c r="K220" s="14" t="inlineStr">
         <is>
-          <t>Partly</t>
-        </is>
-      </c>
-      <c r="L220" s="15" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L220" s="15" t="inlineStr">
+        <is>
+          <t>It sells finished lots. The builder who buys them buys the wall.</t>
+        </is>
+      </c>
       <c r="M220" s="14" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N220" s="15" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N220" s="15" t="inlineStr">
+        <is>
+          <t>Financed and opened Greater Houston's first mass timber office building, with low-carbon concrete in the same structure.</t>
+        </is>
+      </c>
       <c r="O220" s="14" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P220" s="10" t="inlineStr"/>
       <c r="Q220" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Harry%20Dinham%20The%20Signorelli%20Company","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Ryan%20Israel%20Howard%20Hughes%20Holdings%20Inc.","search")</f>
         <v/>
       </c>
       <c r="R220" s="16">
@@ -24319,33 +24358,33 @@
       </c>
       <c r="S220" s="12" t="inlineStr">
         <is>
-          <t>https://www.signorellicompany.com/</t>
+          <t>https://www.howardhughes.com/</t>
         </is>
       </c>
       <c r="T220" s="15" t="inlineStr">
         <is>
-          <t>Sells lots, but owns First America Homes, which holds all three counts. One president runs both.</t>
+          <t>1,802 residential acres left to sell across three communities, and it paid to put up Greater Houston's first mass timber office. It sells lots, so the builder buys the wall.</t>
         </is>
       </c>
       <c r="U220" s="12" t="inlineStr"/>
       <c r="V220" s="15" t="inlineStr">
         <is>
-          <t>Signorelli's own bio page. Chief Financial Officer on the executive leadership team.</t>
+          <t>Chief Investment Officer on Howard Hughes's own leadership page.</t>
         </is>
       </c>
       <c r="W220" s="12" t="inlineStr">
         <is>
-          <t>https://www.signorellicompany.com/our-leadership/30/harry-dinham</t>
+          <t>https://investor.howardhughes.com/governance/leadership</t>
         </is>
       </c>
       <c r="X220" s="12" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/signorelli-company</t>
+          <t>https://www.linkedin.com/company/the-howard-hughes-corporation</t>
         </is>
       </c>
       <c r="Y220" s="12" t="inlineStr">
         <is>
-          <t>https://www.signorellicompany.com/our-leadership</t>
+          <t>https://investor.howardhughes.com/governance/leadership</t>
         </is>
       </c>
       <c r="Z220" s="12" t="inlineStr"/>
@@ -24353,17 +24392,17 @@
     <row r="221">
       <c r="A221" s="6" t="inlineStr">
         <is>
-          <t>John Winniford</t>
+          <t>Jim Carman</t>
         </is>
       </c>
       <c r="B221" s="6" t="inlineStr">
         <is>
-          <t>The Signorelli Company</t>
+          <t>Howard Hughes Holdings Inc.</t>
         </is>
       </c>
       <c r="C221" s="6" t="inlineStr">
         <is>
-          <t>President, Homebuilding, The Signorelli Company</t>
+          <t>President, Texas Region</t>
         </is>
       </c>
       <c r="D221" s="7" t="inlineStr">
@@ -24381,12 +24420,12 @@
       </c>
       <c r="G221" s="6" t="inlineStr">
         <is>
-          <t>The Woodlands HQ / Fort Bend, Liberty</t>
+          <t>The Woodlands HQ / Harris, Montgomery</t>
         </is>
       </c>
       <c r="H221" s="6" t="inlineStr">
         <is>
-          <t>23,000+ paper lots in pipeline</t>
+          <t>1,802 residential acres left to sell</t>
         </is>
       </c>
       <c r="I221" s="8" t="inlineStr">
@@ -24394,62 +24433,71 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J221" s="9" t="inlineStr"/>
+      <c r="J221" s="9" t="inlineStr">
+        <is>
+          <t>Three communities on one metro's edge, 1,802 residential acres still to sell.</t>
+        </is>
+      </c>
       <c r="K221" s="8" t="inlineStr">
         <is>
-          <t>Partly</t>
-        </is>
-      </c>
-      <c r="L221" s="9" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L221" s="9" t="inlineStr">
+        <is>
+          <t>It sells finished lots. The builder who buys them buys the wall.</t>
+        </is>
+      </c>
       <c r="M221" s="8" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N221" s="9" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N221" s="9" t="inlineStr">
+        <is>
+          <t>Financed and opened Greater Houston's first mass timber office building, with low-carbon concrete in the same structure.</t>
+        </is>
+      </c>
       <c r="O221" s="8" t="inlineStr">
         <is>
-          <t>Partly</t>
-        </is>
-      </c>
-      <c r="P221" s="10" t="inlineStr"/>
-      <c r="Q221" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=John%20Winniford%20The%20Signorelli%20Company","search")</f>
-        <v/>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P221" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/carmanjim/</t>
+        </is>
+      </c>
+      <c r="Q221" s="6" t="inlineStr"/>
       <c r="R221" s="11">
         <f>IF(P221="","ADD LINKEDIN","ok")</f>
         <v/>
       </c>
       <c r="S221" s="6" t="inlineStr">
         <is>
-          <t>https://www.signorellicompany.com/</t>
+          <t>https://www.howardhughes.com/</t>
         </is>
       </c>
       <c r="T221" s="9" t="inlineStr">
         <is>
-          <t>Sells lots, but owns First America Homes, which holds all three counts. One president runs both.</t>
+          <t>1,802 residential acres left to sell across three communities, and it paid to put up Greater Houston's first mass timber office. It sells lots, so the builder buys the wall.</t>
         </is>
       </c>
       <c r="U221" s="6" t="inlineStr"/>
       <c r="V221" s="9" t="inlineStr">
         <is>
-          <t>President, Homebuilding. The same person who runs First America, which Signorelli owns, so a single approach reaches both the land position and the builder.</t>
-        </is>
-      </c>
-      <c r="W221" s="6" t="inlineStr">
-        <is>
-          <t>https://www.signorellicompany.com/our-leadership/34/john-winniford</t>
-        </is>
-      </c>
+          <t>Profile opened. President, Texas Region at Howard Hughes Communities. Greater Houston. His own feed carries Bridgeland's number nine national ranking at 500 home sales by mid-2026 and the 83-acre Toro District with the Houston Texans headquarters.</t>
+        </is>
+      </c>
+      <c r="W221" s="6" t="inlineStr"/>
       <c r="X221" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/signorelli-company</t>
+          <t>https://www.linkedin.com/company/the-howard-hughes-corporation</t>
         </is>
       </c>
       <c r="Y221" s="6" t="inlineStr">
         <is>
-          <t>https://www.signorellicompany.com/our-leadership</t>
+          <t>https://investor.howardhughes.com/governance/leadership</t>
         </is>
       </c>
       <c r="Z221" s="6" t="inlineStr"/>
@@ -24457,7 +24505,7 @@
     <row r="222">
       <c r="A222" s="12" t="inlineStr">
         <is>
-          <t>David O'Reilly</t>
+          <t>Stephen Sams</t>
         </is>
       </c>
       <c r="B222" s="12" t="inlineStr">
@@ -24467,7 +24515,7 @@
       </c>
       <c r="C222" s="12" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Senior Vice President, Master Planned Communities, Residential Development, Houston Region</t>
         </is>
       </c>
       <c r="D222" s="13" t="inlineStr">
@@ -24476,7 +24524,7 @@
         </is>
       </c>
       <c r="E222" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F222" s="12" t="inlineStr">
         <is>
@@ -24490,7 +24538,7 @@
       </c>
       <c r="H222" s="12" t="inlineStr">
         <is>
-          <t>$900M Pershing Square investment, 46.9%</t>
+          <t>1,802 residential acres left to sell</t>
         </is>
       </c>
       <c r="I222" s="14" t="inlineStr">
@@ -24498,29 +24546,38 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J222" s="15" t="inlineStr"/>
+      <c r="J222" s="15" t="inlineStr">
+        <is>
+          <t>Three communities on one metro's edge, 1,802 residential acres still to sell.</t>
+        </is>
+      </c>
       <c r="K222" s="14" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L222" s="15" t="inlineStr"/>
+      <c r="L222" s="15" t="inlineStr">
+        <is>
+          <t>It sells finished lots. The builder who buys them buys the wall.</t>
+        </is>
+      </c>
       <c r="M222" s="14" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N222" s="15" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N222" s="15" t="inlineStr">
+        <is>
+          <t>Financed and opened Greater Houston's first mass timber office building, with low-carbon concrete in the same structure.</t>
+        </is>
+      </c>
       <c r="O222" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="P222" s="10" t="inlineStr"/>
-      <c r="Q222" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=David%20O%27Reilly%20Howard%20Hughes%20Holdings%20Inc.","search")</f>
-        <v/>
-      </c>
+      <c r="Q222" s="12" t="inlineStr"/>
       <c r="R222" s="16">
         <f>IF(P222="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -24532,18 +24589,22 @@
       </c>
       <c r="T222" s="15" t="inlineStr">
         <is>
-          <t>11,400 acres and $900M from Pershing Square, but it sells lots, so the builder buys the wall rather than Howard Hughes.</t>
-        </is>
-      </c>
-      <c r="U222" s="12" t="inlineStr"/>
+          <t>1,802 residential acres left to sell across three communities, and it paid to put up Greater Houston's first mass timber office. It sells lots, so the builder buys the wall.</t>
+        </is>
+      </c>
+      <c r="U222" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
       <c r="V222" s="15" t="inlineStr">
         <is>
-          <t>Chief Executive Officer on Howard Hughes's own leadership page.</t>
+          <t>Named in the firm's own April 2022 appointment release, reporting to Jim Carman and covering The Woodlands, Bridgeland and The Woodlands Hills. No later source confirms he still holds it.</t>
         </is>
       </c>
       <c r="W222" s="12" t="inlineStr">
         <is>
-          <t>https://investor.howardhughes.com/governance/leadership</t>
+          <t>https://www.bridgeland.com/the-howard-hughes-corporation-appoints-stephen-sams-as-senior-vice-president-mpc-of-residential-development-in-the-houston-region/</t>
         </is>
       </c>
       <c r="X222" s="12" t="inlineStr">
@@ -24561,17 +24622,17 @@
     <row r="223">
       <c r="A223" s="6" t="inlineStr">
         <is>
-          <t>Bill Ackman</t>
+          <t>Danny Signorelli</t>
         </is>
       </c>
       <c r="B223" s="6" t="inlineStr">
         <is>
-          <t>Howard Hughes Holdings Inc.</t>
+          <t>The Signorelli Company</t>
         </is>
       </c>
       <c r="C223" s="6" t="inlineStr">
         <is>
-          <t>Executive Chairman of the Board</t>
+          <t>Founder and Chief Executive Officer</t>
         </is>
       </c>
       <c r="D223" s="7" t="inlineStr">
@@ -24580,7 +24641,7 @@
         </is>
       </c>
       <c r="E223" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F223" s="6" t="inlineStr">
         <is>
@@ -24589,12 +24650,12 @@
       </c>
       <c r="G223" s="6" t="inlineStr">
         <is>
-          <t>The Woodlands HQ / Harris, Montgomery</t>
+          <t>The Woodlands HQ / Fort Bend, Liberty</t>
         </is>
       </c>
       <c r="H223" s="6" t="inlineStr">
         <is>
-          <t>$900M Pershing Square investment, 46.9%</t>
+          <t>23,000+ paper lots in pipeline</t>
         </is>
       </c>
       <c r="I223" s="8" t="inlineStr">
@@ -24602,62 +24663,71 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J223" s="9" t="inlineStr"/>
+      <c r="J223" s="9" t="inlineStr">
+        <is>
+          <t>More than 16 masterplans and over 23,000 paper lots in pipeline.</t>
+        </is>
+      </c>
       <c r="K223" s="8" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L223" s="9" t="inlineStr"/>
+          <t>Partly</t>
+        </is>
+      </c>
+      <c r="L223" s="9" t="inlineStr">
+        <is>
+          <t>It sells lots, but it owns First America Homes, and one president runs both.</t>
+        </is>
+      </c>
       <c r="M223" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N223" s="9" t="inlineStr"/>
+      <c r="N223" s="9" t="inlineStr">
+        <is>
+          <t>Nothing on record about how anything inside its communities is built.</t>
+        </is>
+      </c>
       <c r="O223" s="8" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P223" s="10" t="inlineStr"/>
-      <c r="Q223" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Bill%20Ackman%20Howard%20Hughes%20Holdings%20Inc.","search")</f>
-        <v/>
-      </c>
+          <t>Partly</t>
+        </is>
+      </c>
+      <c r="P223" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/danny-signorelli-6284461b/</t>
+        </is>
+      </c>
+      <c r="Q223" s="6" t="inlineStr"/>
       <c r="R223" s="11">
         <f>IF(P223="","ADD LINKEDIN","ok")</f>
         <v/>
       </c>
       <c r="S223" s="6" t="inlineStr">
         <is>
-          <t>https://www.howardhughes.com/</t>
+          <t>https://www.signorellicompany.com/</t>
         </is>
       </c>
       <c r="T223" s="9" t="inlineStr">
         <is>
-          <t>11,400 acres and $900M from Pershing Square, but it sells lots, so the builder buys the wall rather than Howard Hughes.</t>
+          <t>Sells lots, but owns First America Homes, which holds all three counts. One president runs both.</t>
         </is>
       </c>
       <c r="U223" s="6" t="inlineStr"/>
       <c r="V223" s="9" t="inlineStr">
         <is>
-          <t>Executive Chairman on Howard Hughes's own leadership page.</t>
-        </is>
-      </c>
-      <c r="W223" s="6" t="inlineStr">
-        <is>
-          <t>https://investor.howardhughes.com/governance/leadership</t>
-        </is>
-      </c>
+          <t>CEO, President, The Signorelli Company. Greater Houston.</t>
+        </is>
+      </c>
+      <c r="W223" s="6" t="inlineStr"/>
       <c r="X223" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/the-howard-hughes-corporation</t>
+          <t>https://www.linkedin.com/company/signorelli-company</t>
         </is>
       </c>
       <c r="Y223" s="6" t="inlineStr">
         <is>
-          <t>https://investor.howardhughes.com/governance/leadership</t>
+          <t>https://www.signorellicompany.com/our-leadership</t>
         </is>
       </c>
       <c r="Z223" s="6" t="inlineStr"/>
@@ -24665,17 +24735,17 @@
     <row r="224">
       <c r="A224" s="12" t="inlineStr">
         <is>
-          <t>Ryan Israel</t>
+          <t>Jeff Dewese</t>
         </is>
       </c>
       <c r="B224" s="12" t="inlineStr">
         <is>
-          <t>Howard Hughes Holdings Inc.</t>
+          <t>The Signorelli Company</t>
         </is>
       </c>
       <c r="C224" s="12" t="inlineStr">
         <is>
-          <t>Chief Investment Officer</t>
+          <t>President, Land Division</t>
         </is>
       </c>
       <c r="D224" s="13" t="inlineStr">
@@ -24684,7 +24754,7 @@
         </is>
       </c>
       <c r="E224" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F224" s="12" t="inlineStr">
         <is>
@@ -24693,12 +24763,12 @@
       </c>
       <c r="G224" s="12" t="inlineStr">
         <is>
-          <t>The Woodlands HQ / Harris, Montgomery</t>
+          <t>The Woodlands HQ / Fort Bend, Liberty</t>
         </is>
       </c>
       <c r="H224" s="12" t="inlineStr">
         <is>
-          <t>$900M Pershing Square investment, 46.9%</t>
+          <t>23,000+ paper lots in pipeline</t>
         </is>
       </c>
       <c r="I224" s="14" t="inlineStr">
@@ -24706,27 +24776,39 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J224" s="15" t="inlineStr"/>
+      <c r="J224" s="15" t="inlineStr">
+        <is>
+          <t>More than 16 masterplans and over 23,000 paper lots in pipeline.</t>
+        </is>
+      </c>
       <c r="K224" s="14" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L224" s="15" t="inlineStr"/>
+          <t>Partly</t>
+        </is>
+      </c>
+      <c r="L224" s="15" t="inlineStr">
+        <is>
+          <t>It sells lots, but it owns First America Homes, and one president runs both.</t>
+        </is>
+      </c>
       <c r="M224" s="14" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N224" s="15" t="inlineStr"/>
+      <c r="N224" s="15" t="inlineStr">
+        <is>
+          <t>Nothing on record about how anything inside its communities is built.</t>
+        </is>
+      </c>
       <c r="O224" s="14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Partly</t>
         </is>
       </c>
       <c r="P224" s="10" t="inlineStr"/>
       <c r="Q224" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Ryan%20Israel%20Howard%20Hughes%20Holdings%20Inc.","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Jeff%20Dewese%20The%20Signorelli%20Company","search")</f>
         <v/>
       </c>
       <c r="R224" s="16">
@@ -24735,33 +24817,33 @@
       </c>
       <c r="S224" s="12" t="inlineStr">
         <is>
-          <t>https://www.howardhughes.com/</t>
+          <t>https://www.signorellicompany.com/</t>
         </is>
       </c>
       <c r="T224" s="15" t="inlineStr">
         <is>
-          <t>11,400 acres and $900M from Pershing Square, but it sells lots, so the builder buys the wall rather than Howard Hughes.</t>
+          <t>Sells lots, but owns First America Homes, which holds all three counts. One president runs both.</t>
         </is>
       </c>
       <c r="U224" s="12" t="inlineStr"/>
       <c r="V224" s="15" t="inlineStr">
         <is>
-          <t>Chief Investment Officer on Howard Hughes's own leadership page.</t>
+          <t>Signorelli's own bio page. President, Land Division, overseeing land acquisition, planning and construction management for Granger Pines, Cielo and Austin Point.</t>
         </is>
       </c>
       <c r="W224" s="12" t="inlineStr">
         <is>
-          <t>https://investor.howardhughes.com/governance/leadership</t>
+          <t>https://www.signorellicompany.com/our-leadership/15/jeff-dewese</t>
         </is>
       </c>
       <c r="X224" s="12" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/the-howard-hughes-corporation</t>
+          <t>https://www.linkedin.com/company/signorelli-company</t>
         </is>
       </c>
       <c r="Y224" s="12" t="inlineStr">
         <is>
-          <t>https://investor.howardhughes.com/governance/leadership</t>
+          <t>https://www.signorellicompany.com/our-leadership</t>
         </is>
       </c>
       <c r="Z224" s="12" t="inlineStr"/>
@@ -24769,17 +24851,17 @@
     <row r="225">
       <c r="A225" s="6" t="inlineStr">
         <is>
-          <t>Jim Carman</t>
+          <t>Harry Dinham</t>
         </is>
       </c>
       <c r="B225" s="6" t="inlineStr">
         <is>
-          <t>Howard Hughes Holdings Inc.</t>
+          <t>The Signorelli Company</t>
         </is>
       </c>
       <c r="C225" s="6" t="inlineStr">
         <is>
-          <t>President, Houston Region</t>
+          <t>Chief Financial Officer</t>
         </is>
       </c>
       <c r="D225" s="7" t="inlineStr">
@@ -24788,7 +24870,7 @@
         </is>
       </c>
       <c r="E225" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F225" s="6" t="inlineStr">
         <is>
@@ -24797,12 +24879,12 @@
       </c>
       <c r="G225" s="6" t="inlineStr">
         <is>
-          <t>The Woodlands HQ / Harris, Montgomery</t>
+          <t>The Woodlands HQ / Fort Bend, Liberty</t>
         </is>
       </c>
       <c r="H225" s="6" t="inlineStr">
         <is>
-          <t>$900M Pershing Square investment, 46.9%</t>
+          <t>23,000+ paper lots in pipeline</t>
         </is>
       </c>
       <c r="I225" s="8" t="inlineStr">
@@ -24810,59 +24892,74 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J225" s="9" t="inlineStr"/>
+      <c r="J225" s="9" t="inlineStr">
+        <is>
+          <t>More than 16 masterplans and over 23,000 paper lots in pipeline.</t>
+        </is>
+      </c>
       <c r="K225" s="8" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L225" s="9" t="inlineStr"/>
+          <t>Partly</t>
+        </is>
+      </c>
+      <c r="L225" s="9" t="inlineStr">
+        <is>
+          <t>It sells lots, but it owns First America Homes, and one president runs both.</t>
+        </is>
+      </c>
       <c r="M225" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N225" s="9" t="inlineStr"/>
+      <c r="N225" s="9" t="inlineStr">
+        <is>
+          <t>Nothing on record about how anything inside its communities is built.</t>
+        </is>
+      </c>
       <c r="O225" s="8" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P225" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/carmanjim/</t>
-        </is>
-      </c>
-      <c r="Q225" s="6" t="inlineStr"/>
+          <t>Partly</t>
+        </is>
+      </c>
+      <c r="P225" s="10" t="inlineStr"/>
+      <c r="Q225" s="6">
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Harry%20Dinham%20The%20Signorelli%20Company","search")</f>
+        <v/>
+      </c>
       <c r="R225" s="11">
         <f>IF(P225="","ADD LINKEDIN","ok")</f>
         <v/>
       </c>
       <c r="S225" s="6" t="inlineStr">
         <is>
-          <t>https://www.howardhughes.com/</t>
+          <t>https://www.signorellicompany.com/</t>
         </is>
       </c>
       <c r="T225" s="9" t="inlineStr">
         <is>
-          <t>11,400 acres and $900M from Pershing Square, but it sells lots, so the builder buys the wall rather than Howard Hughes.</t>
+          <t>Sells lots, but owns First America Homes, which holds all three counts. One president runs both.</t>
         </is>
       </c>
       <c r="U225" s="6" t="inlineStr"/>
       <c r="V225" s="9" t="inlineStr">
         <is>
-          <t>Profile opened. President, Texas Region at Howard Hughes Communities. Greater Houston. His own feed carries Bridgeland's number nine national ranking at 500 home sales by mid-2026 and the 83-acre Toro District with the Houston Texans headquarters.</t>
-        </is>
-      </c>
-      <c r="W225" s="6" t="inlineStr"/>
+          <t>Signorelli's own bio page. Chief Financial Officer on the executive leadership team.</t>
+        </is>
+      </c>
+      <c r="W225" s="6" t="inlineStr">
+        <is>
+          <t>https://www.signorellicompany.com/our-leadership/30/harry-dinham</t>
+        </is>
+      </c>
       <c r="X225" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/the-howard-hughes-corporation</t>
+          <t>https://www.linkedin.com/company/signorelli-company</t>
         </is>
       </c>
       <c r="Y225" s="6" t="inlineStr">
         <is>
-          <t>https://investor.howardhughes.com/governance/leadership</t>
+          <t>https://www.signorellicompany.com/our-leadership</t>
         </is>
       </c>
       <c r="Z225" s="6" t="inlineStr"/>
@@ -24870,17 +24967,17 @@
     <row r="226">
       <c r="A226" s="12" t="inlineStr">
         <is>
-          <t>Alan Brende</t>
+          <t>John Winniford</t>
         </is>
       </c>
       <c r="B226" s="12" t="inlineStr">
         <is>
-          <t>Land Tejas</t>
+          <t>The Signorelli Company</t>
         </is>
       </c>
       <c r="C226" s="12" t="inlineStr">
         <is>
-          <t>Co-President, Land Tejas</t>
+          <t>President, Homebuilding, The Signorelli Company</t>
         </is>
       </c>
       <c r="D226" s="13" t="inlineStr">
@@ -24889,7 +24986,7 @@
         </is>
       </c>
       <c r="E226" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F226" s="12" t="inlineStr">
         <is>
@@ -24898,12 +24995,12 @@
       </c>
       <c r="G226" s="12" t="inlineStr">
         <is>
-          <t>Houston / Katy, Harris-Waller</t>
+          <t>The Woodlands HQ / Fort Bend, Liberty</t>
         </is>
       </c>
       <c r="H226" s="12" t="inlineStr">
         <is>
-          <t>Sunterra, 2,303 acres in Katy, fifteen builders</t>
+          <t>23,000+ paper lots in pipeline</t>
         </is>
       </c>
       <c r="I226" s="14" t="inlineStr">
@@ -24911,27 +25008,39 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J226" s="15" t="inlineStr"/>
+      <c r="J226" s="15" t="inlineStr">
+        <is>
+          <t>More than 16 masterplans and over 23,000 paper lots in pipeline.</t>
+        </is>
+      </c>
       <c r="K226" s="14" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L226" s="15" t="inlineStr"/>
+          <t>Partly</t>
+        </is>
+      </c>
+      <c r="L226" s="15" t="inlineStr">
+        <is>
+          <t>It sells lots, but it owns First America Homes, and one president runs both.</t>
+        </is>
+      </c>
       <c r="M226" s="14" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N226" s="15" t="inlineStr"/>
+      <c r="N226" s="15" t="inlineStr">
+        <is>
+          <t>Nothing on record about how anything inside its communities is built.</t>
+        </is>
+      </c>
       <c r="O226" s="14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Partly</t>
         </is>
       </c>
       <c r="P226" s="10" t="inlineStr"/>
       <c r="Q226" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Alan%20Brende%20Land%20Tejas","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=John%20Winniford%20The%20Signorelli%20Company","search")</f>
         <v/>
       </c>
       <c r="R226" s="16">
@@ -24940,33 +25049,33 @@
       </c>
       <c r="S226" s="12" t="inlineStr">
         <is>
-          <t>https://landtejas.com/</t>
+          <t>https://www.signorellicompany.com/</t>
         </is>
       </c>
       <c r="T226" s="15" t="inlineStr">
         <is>
-          <t>Sells lots. Sunterra carries 2,303 acres and 15 builders.</t>
+          <t>Sells lots, but owns First America Homes, which holds all three counts. One president runs both.</t>
         </is>
       </c>
       <c r="U226" s="12" t="inlineStr"/>
       <c r="V226" s="15" t="inlineStr">
         <is>
-          <t>Co-President.</t>
+          <t>President, Homebuilding. The same person who runs First America, which Signorelli owns, so a single approach reaches both the land position and the builder.</t>
         </is>
       </c>
       <c r="W226" s="12" t="inlineStr">
         <is>
-          <t>https://landtejas.com/about-us/our-leadership/</t>
+          <t>https://www.signorellicompany.com/our-leadership/34/john-winniford</t>
         </is>
       </c>
       <c r="X226" s="12" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/land-tejas-companies</t>
+          <t>https://www.linkedin.com/company/signorelli-company</t>
         </is>
       </c>
       <c r="Y226" s="12" t="inlineStr">
         <is>
-          <t>https://landtejas.com/about-us/our-leadership/</t>
+          <t>https://www.signorellicompany.com/our-leadership</t>
         </is>
       </c>
       <c r="Z226" s="12" t="inlineStr"/>
@@ -24974,7 +25083,7 @@
     <row r="227">
       <c r="A227" s="6" t="inlineStr">
         <is>
-          <t>Melanie Ohl</t>
+          <t>Alan Brende</t>
         </is>
       </c>
       <c r="B227" s="6" t="inlineStr">
@@ -25015,19 +25124,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J227" s="9" t="inlineStr"/>
+      <c r="J227" s="9" t="inlineStr">
+        <is>
+          <t>Sunterra alone is 2,303 acres in Katy with fifteen builders inside it.</t>
+        </is>
+      </c>
       <c r="K227" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L227" s="9" t="inlineStr"/>
+      <c r="L227" s="9" t="inlineStr">
+        <is>
+          <t>It sells lots. Fifteen builders buy the wall.</t>
+        </is>
+      </c>
       <c r="M227" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N227" s="9" t="inlineStr"/>
+      <c r="N227" s="9" t="inlineStr">
+        <is>
+          <t>Nothing on record about construction method.</t>
+        </is>
+      </c>
       <c r="O227" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -25035,7 +25156,7 @@
       </c>
       <c r="P227" s="10" t="inlineStr"/>
       <c r="Q227" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Melanie%20Ohl%20Land%20Tejas","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Alan%20Brende%20Land%20Tejas","search")</f>
         <v/>
       </c>
       <c r="R227" s="11">
@@ -25078,17 +25199,17 @@
     <row r="228">
       <c r="A228" s="12" t="inlineStr">
         <is>
-          <t>Fred Caldwell</t>
+          <t>Melanie Ohl</t>
         </is>
       </c>
       <c r="B228" s="12" t="inlineStr">
         <is>
-          <t>Caldwell Companies</t>
+          <t>Land Tejas</t>
         </is>
       </c>
       <c r="C228" s="12" t="inlineStr">
         <is>
-          <t>Chief Executive Officer, Caldwell Companies</t>
+          <t>Co-President, Land Tejas</t>
         </is>
       </c>
       <c r="D228" s="13" t="inlineStr">
@@ -25106,12 +25227,12 @@
       </c>
       <c r="G228" s="12" t="inlineStr">
         <is>
-          <t>Cypress / Montgomery, Harris</t>
+          <t>Houston / Katy, Harris-Waller</t>
         </is>
       </c>
       <c r="H228" s="12" t="inlineStr">
         <is>
-          <t>Towne Lake and The Highlands, about 4,000 homes</t>
+          <t>Sunterra, 2,303 acres in Katy, fifteen builders</t>
         </is>
       </c>
       <c r="I228" s="14" t="inlineStr">
@@ -25119,27 +25240,39 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J228" s="15" t="inlineStr"/>
+      <c r="J228" s="15" t="inlineStr">
+        <is>
+          <t>Sunterra alone is 2,303 acres in Katy with fifteen builders inside it.</t>
+        </is>
+      </c>
       <c r="K228" s="14" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L228" s="15" t="inlineStr"/>
+      <c r="L228" s="15" t="inlineStr">
+        <is>
+          <t>It sells lots. Fifteen builders buy the wall.</t>
+        </is>
+      </c>
       <c r="M228" s="14" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N228" s="15" t="inlineStr"/>
+      <c r="N228" s="15" t="inlineStr">
+        <is>
+          <t>Nothing on record about construction method.</t>
+        </is>
+      </c>
       <c r="O228" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P228" s="10" t="inlineStr"/>
       <c r="Q228" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Fred%20Caldwell%20Caldwell%20Companies","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Melanie%20Ohl%20Land%20Tejas","search")</f>
         <v/>
       </c>
       <c r="R228" s="16">
@@ -25148,33 +25281,33 @@
       </c>
       <c r="S228" s="12" t="inlineStr">
         <is>
-          <t>https://caldwellcos.com/</t>
+          <t>https://landtejas.com/</t>
         </is>
       </c>
       <c r="T228" s="15" t="inlineStr">
         <is>
-          <t>Sells lots. Towne Lake and The Highlands carry 4,000 homes across 12 builders.</t>
+          <t>Sells lots. Sunterra carries 2,303 acres and 15 builders.</t>
         </is>
       </c>
       <c r="U228" s="12" t="inlineStr"/>
       <c r="V228" s="15" t="inlineStr">
         <is>
-          <t>Chief Executive Officer.</t>
+          <t>Co-President.</t>
         </is>
       </c>
       <c r="W228" s="12" t="inlineStr">
         <is>
-          <t>https://caldwellcos.com/our-team</t>
+          <t>https://landtejas.com/about-us/our-leadership/</t>
         </is>
       </c>
       <c r="X228" s="12" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/caldwell-companies</t>
+          <t>https://www.linkedin.com/company/land-tejas-companies</t>
         </is>
       </c>
       <c r="Y228" s="12" t="inlineStr">
         <is>
-          <t>https://caldwellcos.com/our-team</t>
+          <t>https://landtejas.com/about-us/our-leadership/</t>
         </is>
       </c>
       <c r="Z228" s="12" t="inlineStr"/>
@@ -25182,17 +25315,17 @@
     <row r="229">
       <c r="A229" s="6" t="inlineStr">
         <is>
-          <t>Michael J. Smith</t>
+          <t>Fred Caldwell</t>
         </is>
       </c>
       <c r="B229" s="6" t="inlineStr">
         <is>
-          <t>Johnson Development Corp</t>
+          <t>Caldwell Companies</t>
         </is>
       </c>
       <c r="C229" s="6" t="inlineStr">
         <is>
-          <t>President and Chief Executive Officer, Johnson Development</t>
+          <t>Chief Executive Officer, Caldwell Companies</t>
         </is>
       </c>
       <c r="D229" s="7" t="inlineStr">
@@ -25210,12 +25343,12 @@
       </c>
       <c r="G229" s="6" t="inlineStr">
         <is>
-          <t>Houston / Fort Bend, Montgomery</t>
+          <t>Cypress / Montgomery, Harris</t>
         </is>
       </c>
       <c r="H229" s="6" t="inlineStr">
         <is>
-          <t>Fourteen concurrent Houston masterplans</t>
+          <t>Towne Lake and The Highlands, about 4,000 homes</t>
         </is>
       </c>
       <c r="I229" s="8" t="inlineStr">
@@ -25223,19 +25356,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J229" s="9" t="inlineStr"/>
+      <c r="J229" s="9" t="inlineStr">
+        <is>
+          <t>Towne Lake and The Highlands carry about 4,000 planned homes across 12 builders.</t>
+        </is>
+      </c>
       <c r="K229" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L229" s="9" t="inlineStr"/>
+      <c r="L229" s="9" t="inlineStr">
+        <is>
+          <t>It sells lots and does not pour walls.</t>
+        </is>
+      </c>
       <c r="M229" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N229" s="9" t="inlineStr"/>
+      <c r="N229" s="9" t="inlineStr">
+        <is>
+          <t>Publishes no construction-method content.</t>
+        </is>
+      </c>
       <c r="O229" s="8" t="inlineStr">
         <is>
           <t>No</t>
@@ -25243,7 +25388,7 @@
       </c>
       <c r="P229" s="10" t="inlineStr"/>
       <c r="Q229" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Michael%20J.%20Smith%20Johnson%20Development%20Corp","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Fred%20Caldwell%20Caldwell%20Companies","search")</f>
         <v/>
       </c>
       <c r="R229" s="11">
@@ -25252,33 +25397,33 @@
       </c>
       <c r="S229" s="6" t="inlineStr">
         <is>
-          <t>https://www.johnsondevelopment.com/</t>
+          <t>https://caldwellcos.com/</t>
         </is>
       </c>
       <c r="T229" s="9" t="inlineStr">
         <is>
-          <t>Sells lots across 14 Houston masterplans. Buys no walls.</t>
+          <t>Sells lots. Towne Lake and The Highlands carry 4,000 homes across 12 builders.</t>
         </is>
       </c>
       <c r="U229" s="6" t="inlineStr"/>
       <c r="V229" s="9" t="inlineStr">
         <is>
-          <t>President and Chief Executive Officer.</t>
+          <t>Chief Executive Officer.</t>
         </is>
       </c>
       <c r="W229" s="6" t="inlineStr">
         <is>
-          <t>https://www.johnsondevelopment.com/our-leaders</t>
+          <t>https://caldwellcos.com/our-team</t>
         </is>
       </c>
       <c r="X229" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/the-johnson-development-corp</t>
+          <t>https://www.linkedin.com/company/caldwell-companies</t>
         </is>
       </c>
       <c r="Y229" s="6" t="inlineStr">
         <is>
-          <t>https://www.johnsondevelopment.com/our-leaders</t>
+          <t>https://caldwellcos.com/our-team</t>
         </is>
       </c>
       <c r="Z229" s="6" t="inlineStr"/>
@@ -25286,17 +25431,17 @@
     <row r="230">
       <c r="A230" s="12" t="inlineStr">
         <is>
-          <t>Alan Bauer</t>
+          <t>Michael J. Smith</t>
         </is>
       </c>
       <c r="B230" s="12" t="inlineStr">
         <is>
-          <t>Newland Communities</t>
+          <t>Johnson Development Corp</t>
         </is>
       </c>
       <c r="C230" s="12" t="inlineStr">
         <is>
-          <t>Senior Vice President and Houston Division Manager, Newland (2019)</t>
+          <t>President and Chief Executive Officer, Johnson Development</t>
         </is>
       </c>
       <c r="D230" s="13" t="inlineStr">
@@ -25314,32 +25459,44 @@
       </c>
       <c r="G230" s="12" t="inlineStr">
         <is>
-          <t>San Diego HQ / Katy, Harris</t>
+          <t>Houston / Fort Bend, Montgomery</t>
         </is>
       </c>
       <c r="H230" s="12" t="inlineStr">
         <is>
-          <t>Elyson, 3,600 acres in Katy</t>
+          <t>Fourteen concurrent Houston masterplans</t>
         </is>
       </c>
       <c r="I230" s="14" t="inlineStr">
         <is>
-          <t>Partly</t>
-        </is>
-      </c>
-      <c r="J230" s="15" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J230" s="15" t="inlineStr">
+        <is>
+          <t>Fourteen concurrent Houston masterplans.</t>
+        </is>
+      </c>
       <c r="K230" s="14" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L230" s="15" t="inlineStr"/>
+      <c r="L230" s="15" t="inlineStr">
+        <is>
+          <t>It sells lots across all fourteen. The builders inside buy the wall.</t>
+        </is>
+      </c>
       <c r="M230" s="14" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N230" s="15" t="inlineStr"/>
+      <c r="N230" s="15" t="inlineStr">
+        <is>
+          <t>Publishes no construction-method content.</t>
+        </is>
+      </c>
       <c r="O230" s="14" t="inlineStr">
         <is>
           <t>No</t>
@@ -25347,7 +25504,7 @@
       </c>
       <c r="P230" s="10" t="inlineStr"/>
       <c r="Q230" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Alan%20Bauer%20Newland%20Communities","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Michael%20J.%20Smith%20Johnson%20Development%20Corp","search")</f>
         <v/>
       </c>
       <c r="R230" s="16">
@@ -25356,70 +25513,74 @@
       </c>
       <c r="S230" s="12" t="inlineStr">
         <is>
-          <t>https://newlandco.com/</t>
+          <t>https://www.johnsondevelopment.com/</t>
         </is>
       </c>
       <c r="T230" s="15" t="inlineStr">
         <is>
-          <t>3,600-acre Elyson, but Newland has been absorbed into Brookfield Residential and no longer publishes its own leadership. The one Houston name on record is from 2019.</t>
+          <t>Sells lots across 14 Houston masterplans. Buys no walls.</t>
         </is>
       </c>
       <c r="U230" s="12" t="inlineStr"/>
       <c r="V230" s="15" t="inlineStr">
         <is>
-          <t>Senior Vice President and Division Manager for Newland's Houston division, per the West Houston Association board announcement. Dated 2019 and unconfirmed since, because Newland no longer publishes its own leadership.</t>
+          <t>President and Chief Executive Officer.</t>
         </is>
       </c>
       <c r="W230" s="12" t="inlineStr">
         <is>
-          <t>https://www.westhouston.org/2019/01/18/welcome-to-the-2019-board-or-directors/</t>
+          <t>https://www.johnsondevelopment.com/our-leaders</t>
         </is>
       </c>
       <c r="X230" s="12" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/newland-communities-llc</t>
-        </is>
-      </c>
-      <c r="Y230" s="12" t="inlineStr"/>
+          <t>https://www.linkedin.com/company/the-johnson-development-corp</t>
+        </is>
+      </c>
+      <c r="Y230" s="12" t="inlineStr">
+        <is>
+          <t>https://www.johnsondevelopment.com/our-leaders</t>
+        </is>
+      </c>
       <c r="Z230" s="12" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="6" t="inlineStr">
         <is>
-          <t>George Kopecky</t>
+          <t>Alan Bauer</t>
         </is>
       </c>
       <c r="B231" s="6" t="inlineStr">
         <is>
-          <t>GreenEco Builders</t>
+          <t>Newland Communities</t>
         </is>
       </c>
       <c r="C231" s="6" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Senior Vice President and Houston Division Manager, Newland (2019)</t>
         </is>
       </c>
       <c r="D231" s="7" t="inlineStr">
         <is>
-          <t>Already working with ICON</t>
+          <t>Masterplan owner</t>
         </is>
       </c>
       <c r="E231" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F231" s="6" t="inlineStr">
         <is>
-          <t>Buys walls</t>
+          <t>Sells lots</t>
         </is>
       </c>
       <c r="G231" s="6" t="inlineStr">
         <is>
-          <t>Tavola, New Caney</t>
+          <t>San Diego HQ / Katy, Harris</t>
         </is>
       </c>
       <c r="H231" s="6" t="inlineStr">
         <is>
-          <t>Orders windows per home to keep adopting newer products</t>
+          <t>Elyson, 3,600 acres in Katy</t>
         </is>
       </c>
       <c r="I231" s="8" t="inlineStr">
@@ -25429,27 +25590,27 @@
       </c>
       <c r="J231" s="9" t="inlineStr">
         <is>
-          <t>One confirmed community, Tavola in New Caney. The footprint is small.</t>
+          <t>One Houston community, Elyson, at 3,600 acres in Katy.</t>
         </is>
       </c>
       <c r="K231" s="8" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L231" s="9" t="inlineStr">
         <is>
-          <t>Owned by Rausch Coleman Homes since 2020, and Lennar completed its purchase of Rausch Coleman on 10 February 2025. No volume figure is published for the brand; purchasing sits with the parent.</t>
+          <t>It sells lots, and the platform now sits inside Brookfield Residential.</t>
         </is>
       </c>
       <c r="M231" s="8" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N231" s="9" t="inlineStr">
         <is>
-          <t>It orders windows per home rather than per community specifically so it can adopt newer energy products as they appear. That is a procurement habit built for method change.</t>
+          <t>Nothing on record about construction method.</t>
         </is>
       </c>
       <c r="O231" s="8" t="inlineStr">
@@ -25457,51 +25618,58 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P231" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/george-kopecky-7ba08a26/</t>
-        </is>
-      </c>
-      <c r="Q231" s="6" t="inlineStr"/>
+      <c r="P231" s="10" t="inlineStr"/>
+      <c r="Q231" s="6">
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Alan%20Bauer%20Newland%20Communities","search")</f>
+        <v/>
+      </c>
       <c r="R231" s="11">
         <f>IF(P231="","ADD LINKEDIN","ok")</f>
         <v/>
       </c>
       <c r="S231" s="6" t="inlineStr">
         <is>
-          <t>https://greenecobuilders.com/</t>
+          <t>https://newlandco.com/</t>
         </is>
       </c>
       <c r="T231" s="9" t="inlineStr">
         <is>
-          <t>Orders windows per home rather than per community so it can adopt newer products. Owned by Rausch Coleman Homes, which Lennar bought in February 2025.</t>
+          <t>3,600-acre Elyson, but Newland has been absorbed into Brookfield Residential and no longer publishes its own leadership. The one Houston name on record is from 2019.</t>
         </is>
       </c>
       <c r="U231" s="6" t="inlineStr"/>
       <c r="V231" s="9" t="inlineStr">
         <is>
-          <t>Indexed title reads George Kopecky, President at GreenEco Builders. Named as the firm's principal in trade coverage of the 2020 sale to Rausch Coleman.</t>
-        </is>
-      </c>
-      <c r="W231" s="6" t="inlineStr"/>
-      <c r="X231" s="6" t="inlineStr"/>
+          <t>Senior Vice President and Division Manager for Newland's Houston division, per the West Houston Association board announcement. Dated 2019 and unconfirmed since, because Newland no longer publishes its own leadership.</t>
+        </is>
+      </c>
+      <c r="W231" s="6" t="inlineStr">
+        <is>
+          <t>https://www.westhouston.org/2019/01/18/welcome-to-the-2019-board-or-directors/</t>
+        </is>
+      </c>
+      <c r="X231" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/newland-communities-llc</t>
+        </is>
+      </c>
       <c r="Y231" s="6" t="inlineStr"/>
       <c r="Z231" s="6" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="12" t="inlineStr">
         <is>
-          <t>Michael Reamer</t>
+          <t>George Kopecky</t>
         </is>
       </c>
       <c r="B232" s="12" t="inlineStr">
         <is>
-          <t>Friendswood Development Company</t>
+          <t>GreenEco Builders</t>
         </is>
       </c>
       <c r="C232" s="12" t="inlineStr">
         <is>
-          <t>President, Friendswood Development Company</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D232" s="13" t="inlineStr">
@@ -25510,21 +25678,21 @@
         </is>
       </c>
       <c r="E232" s="14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F232" s="12" t="inlineStr">
         <is>
-          <t>Sells lots</t>
+          <t>Buys walls</t>
         </is>
       </c>
       <c r="G232" s="12" t="inlineStr">
         <is>
-          <t>Houston / Montgomery, Galveston</t>
+          <t>Tavola, New Caney</t>
         </is>
       </c>
       <c r="H232" s="12" t="inlineStr">
         <is>
-          <t>Sells lots inside its own masterplans; Lennar builds</t>
+          <t>Orders windows per home to keep adopting newer products</t>
         </is>
       </c>
       <c r="I232" s="14" t="inlineStr">
@@ -25534,17 +25702,17 @@
       </c>
       <c r="J232" s="15" t="inlineStr">
         <is>
-          <t>Sells lots inside its own masterplans. Lennar builds the houses.</t>
+          <t>One confirmed community, Tavola in New Caney. The footprint is small.</t>
         </is>
       </c>
       <c r="K232" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partly</t>
         </is>
       </c>
       <c r="L232" s="15" t="inlineStr">
         <is>
-          <t>Sells lots, wholly owned by Lennar, so the route is Lennar.</t>
+          <t>Owned by Rausch Coleman Homes since 2020, and Lennar completed its purchase of Rausch Coleman on 10 February 2025. No volume figure is published for the brand; purchasing sits with the parent.</t>
         </is>
       </c>
       <c r="M232" s="14" t="inlineStr">
@@ -25554,121 +25722,122 @@
       </c>
       <c r="N232" s="15" t="inlineStr">
         <is>
-          <t>The parent, Lennar, built a hundred printed homes with ICON at Wolf Ranch. Friendswood itself buys no walls.</t>
+          <t>It orders windows per home rather than per community specifically so it can adopt newer energy products as they appear. That is a procurement habit built for method change.</t>
         </is>
       </c>
       <c r="O232" s="14" t="inlineStr">
         <is>
-          <t>Partly</t>
-        </is>
-      </c>
-      <c r="P232" s="10" t="inlineStr"/>
-      <c r="Q232" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Michael%20Reamer%20Friendswood%20Development%20Company","search")</f>
-        <v/>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P232" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/george-kopecky-7ba08a26/</t>
+        </is>
+      </c>
+      <c r="Q232" s="12" t="inlineStr"/>
       <c r="R232" s="16">
         <f>IF(P232="","ADD LINKEDIN","ok")</f>
         <v/>
       </c>
       <c r="S232" s="12" t="inlineStr">
         <is>
-          <t>https://friendswooddevelopment.com/</t>
+          <t>https://greenecobuilders.com/</t>
         </is>
       </c>
       <c r="T232" s="15" t="inlineStr">
         <is>
-          <t>Sells lots, wholly owned by Lennar since 2000. Lennar built a hundred printed homes with ICON at Wolf Ranch.</t>
+          <t>Orders windows per home rather than per community so it can adopt newer products. Owned by Rausch Coleman Homes, which Lennar bought in February 2025.</t>
         </is>
       </c>
       <c r="U232" s="12" t="inlineStr"/>
       <c r="V232" s="15" t="inlineStr">
         <is>
-          <t>President.</t>
-        </is>
-      </c>
-      <c r="W232" s="12" t="inlineStr">
-        <is>
-          <t>https://friendswooddevelopment.com/people</t>
-        </is>
-      </c>
-      <c r="X232" s="12" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/friendswood-development-company</t>
-        </is>
-      </c>
-      <c r="Y232" s="12" t="inlineStr">
-        <is>
-          <t>https://friendswooddevelopment.com/people</t>
-        </is>
-      </c>
+          <t>Indexed title reads George Kopecky, President at GreenEco Builders. Named as the firm's principal in trade coverage of the 2020 sale to Rausch Coleman.</t>
+        </is>
+      </c>
+      <c r="W232" s="12" t="inlineStr"/>
+      <c r="X232" s="12" t="inlineStr"/>
+      <c r="Y232" s="12" t="inlineStr"/>
       <c r="Z232" s="12" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="6" t="inlineStr">
         <is>
-          <t>Steven D. Alvis</t>
+          <t>Michael Reamer</t>
         </is>
       </c>
       <c r="B233" s="6" t="inlineStr">
         <is>
-          <t>NewQuest Properties</t>
+          <t>Friendswood Development Company</t>
         </is>
       </c>
       <c r="C233" s="6" t="inlineStr">
         <is>
-          <t>Co-Founder and Managing Partner</t>
+          <t>President, Friendswood Development Company</t>
         </is>
       </c>
       <c r="D233" s="7" t="inlineStr">
         <is>
-          <t>Off deck, screened out</t>
+          <t>Already working with ICON</t>
         </is>
       </c>
       <c r="E233" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F233" s="6" t="inlineStr">
         <is>
-          <t>Buys walls</t>
+          <t>Sells lots</t>
         </is>
       </c>
       <c r="G233" s="6" t="inlineStr">
         <is>
-          <t>Houston HQ / Fort Bend, Brazoria</t>
+          <t>Houston / Montgomery, Galveston</t>
         </is>
       </c>
       <c r="H233" s="6" t="inlineStr">
         <is>
-          <t>$3.1B portfolio, 12M sf managed</t>
+          <t>Sells lots inside its own masterplans; Lennar builds</t>
         </is>
       </c>
       <c r="I233" s="8" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J233" s="9" t="inlineStr"/>
+          <t>Partly</t>
+        </is>
+      </c>
+      <c r="J233" s="9" t="inlineStr">
+        <is>
+          <t>Sells lots inside its own masterplans. Lennar builds the houses.</t>
+        </is>
+      </c>
       <c r="K233" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L233" s="9" t="inlineStr"/>
+      <c r="L233" s="9" t="inlineStr">
+        <is>
+          <t>Sells lots, wholly owned by Lennar, so the route is Lennar.</t>
+        </is>
+      </c>
       <c r="M233" s="8" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N233" s="9" t="inlineStr"/>
+          <t>Partly</t>
+        </is>
+      </c>
+      <c r="N233" s="9" t="inlineStr">
+        <is>
+          <t>The parent, Lennar, built a hundred printed homes with ICON at Wolf Ranch. Friendswood itself buys no walls.</t>
+        </is>
+      </c>
       <c r="O233" s="8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Partly</t>
         </is>
       </c>
       <c r="P233" s="10" t="inlineStr"/>
       <c r="Q233" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Steven%20D.%20Alvis%20NewQuest%20Properties","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Michael%20Reamer%20Friendswood%20Development%20Company","search")</f>
         <v/>
       </c>
       <c r="R233" s="11">
@@ -25677,33 +25846,33 @@
       </c>
       <c r="S233" s="6" t="inlineStr">
         <is>
-          <t>https://www.newquest.com/</t>
+          <t>https://friendswooddevelopment.com/</t>
         </is>
       </c>
       <c r="T233" s="9" t="inlineStr">
         <is>
-          <t>$3.1B portfolio and a repeated Town Center format. Retail shells compete against tilt-wall, not stick framing.</t>
+          <t>Sells lots, wholly owned by Lennar since 2000. Lennar built a hundred printed homes with ICON at Wolf Ranch.</t>
         </is>
       </c>
       <c r="U233" s="6" t="inlineStr"/>
       <c r="V233" s="9" t="inlineStr">
         <is>
-          <t>Co-Founder and Managing Partner.</t>
+          <t>President.</t>
         </is>
       </c>
       <c r="W233" s="6" t="inlineStr">
         <is>
-          <t>https://www.newquest.com/about-us/leadership/</t>
+          <t>https://friendswooddevelopment.com/people</t>
         </is>
       </c>
       <c r="X233" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/newquest-properties</t>
+          <t>https://www.linkedin.com/company/friendswood-development-company</t>
         </is>
       </c>
       <c r="Y233" s="6" t="inlineStr">
         <is>
-          <t>https://www.newquest.com/about-us/leadership/</t>
+          <t>https://friendswooddevelopment.com/people</t>
         </is>
       </c>
       <c r="Z233" s="6" t="inlineStr"/>
@@ -25711,7 +25880,7 @@
     <row r="234">
       <c r="A234" s="12" t="inlineStr">
         <is>
-          <t>Jay K. Sears</t>
+          <t>Steven D. Alvis</t>
         </is>
       </c>
       <c r="B234" s="12" t="inlineStr">
@@ -25772,7 +25941,7 @@
       </c>
       <c r="P234" s="10" t="inlineStr"/>
       <c r="Q234" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Jay%20K.%20Sears%20NewQuest%20Properties","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Steven%20D.%20Alvis%20NewQuest%20Properties","search")</f>
         <v/>
       </c>
       <c r="R234" s="16">
@@ -25815,7 +25984,7 @@
     <row r="235">
       <c r="A235" s="6" t="inlineStr">
         <is>
-          <t>Austin Alvis</t>
+          <t>Jay K. Sears</t>
         </is>
       </c>
       <c r="B235" s="6" t="inlineStr">
@@ -25825,7 +25994,7 @@
       </c>
       <c r="C235" s="6" t="inlineStr">
         <is>
-          <t>President and Chief Development Officer</t>
+          <t>Co-Founder and Managing Partner</t>
         </is>
       </c>
       <c r="D235" s="7" t="inlineStr">
@@ -25876,7 +26045,7 @@
       </c>
       <c r="P235" s="10" t="inlineStr"/>
       <c r="Q235" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Austin%20Alvis%20NewQuest%20Properties","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Jay%20K.%20Sears%20NewQuest%20Properties","search")</f>
         <v/>
       </c>
       <c r="R235" s="11">
@@ -25896,7 +26065,7 @@
       <c r="U235" s="6" t="inlineStr"/>
       <c r="V235" s="9" t="inlineStr">
         <is>
-          <t>President and Chief Development Officer.</t>
+          <t>Co-Founder and Managing Partner.</t>
         </is>
       </c>
       <c r="W235" s="6" t="inlineStr">
@@ -25919,7 +26088,7 @@
     <row r="236">
       <c r="A236" s="12" t="inlineStr">
         <is>
-          <t>Jeff Horton</t>
+          <t>Austin Alvis</t>
         </is>
       </c>
       <c r="B236" s="12" t="inlineStr">
@@ -25929,7 +26098,7 @@
       </c>
       <c r="C236" s="12" t="inlineStr">
         <is>
-          <t>Chief Operating Officer and Head of Capital Markets</t>
+          <t>President and Chief Development Officer</t>
         </is>
       </c>
       <c r="D236" s="13" t="inlineStr">
@@ -25980,7 +26149,7 @@
       </c>
       <c r="P236" s="10" t="inlineStr"/>
       <c r="Q236" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Jeff%20Horton%20NewQuest%20Properties","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Austin%20Alvis%20NewQuest%20Properties","search")</f>
         <v/>
       </c>
       <c r="R236" s="16">
@@ -26000,7 +26169,7 @@
       <c r="U236" s="12" t="inlineStr"/>
       <c r="V236" s="15" t="inlineStr">
         <is>
-          <t>Chief Operating Officer and Head of Capital Markets.</t>
+          <t>President and Chief Development Officer.</t>
         </is>
       </c>
       <c r="W236" s="12" t="inlineStr">
@@ -26023,17 +26192,17 @@
     <row r="237">
       <c r="A237" s="6" t="inlineStr">
         <is>
-          <t>K. Alan Hassenflu</t>
+          <t>Jeff Horton</t>
         </is>
       </c>
       <c r="B237" s="6" t="inlineStr">
         <is>
-          <t>Fidelis Realty Partners</t>
+          <t>NewQuest Properties</t>
         </is>
       </c>
       <c r="C237" s="6" t="inlineStr">
         <is>
-          <t>Chairman and Chief Executive Officer</t>
+          <t>Chief Operating Officer and Head of Capital Markets</t>
         </is>
       </c>
       <c r="D237" s="7" t="inlineStr">
@@ -26051,12 +26220,12 @@
       </c>
       <c r="G237" s="6" t="inlineStr">
         <is>
-          <t>Houston HQ / Brazoria, Montgomery</t>
+          <t>Houston HQ / Fort Bend, Brazoria</t>
         </is>
       </c>
       <c r="H237" s="6" t="inlineStr">
         <is>
-          <t>26M sf, ~100 properties, 12 states</t>
+          <t>$3.1B portfolio, 12M sf managed</t>
         </is>
       </c>
       <c r="I237" s="8" t="inlineStr">
@@ -26079,12 +26248,12 @@
       <c r="N237" s="9" t="inlineStr"/>
       <c r="O237" s="8" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P237" s="10" t="inlineStr"/>
       <c r="Q237" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=K.%20Alan%20Hassenflu%20Fidelis%20Realty%20Partners","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Jeff%20Horton%20NewQuest%20Properties","search")</f>
         <v/>
       </c>
       <c r="R237" s="11">
@@ -26093,33 +26262,33 @@
       </c>
       <c r="S237" s="6" t="inlineStr">
         <is>
-          <t>https://www.frpltd.com/</t>
+          <t>https://www.newquest.com/</t>
         </is>
       </c>
       <c r="T237" s="9" t="inlineStr">
         <is>
-          <t>Two land positions in target counties within 24 months. Every purchase price is undisclosed.</t>
+          <t>$3.1B portfolio and a repeated Town Center format. Retail shells compete against tilt-wall, not stick framing.</t>
         </is>
       </c>
       <c r="U237" s="6" t="inlineStr"/>
       <c r="V237" s="9" t="inlineStr">
         <is>
-          <t>President and Chief Executive Officer, a founder in 2003, formerly senior managing director at Trammell Crow.</t>
+          <t>Chief Operating Officer and Head of Capital Markets.</t>
         </is>
       </c>
       <c r="W237" s="6" t="inlineStr">
         <is>
-          <t>https://www.frpltd.com/about-fidelis/mission-values</t>
+          <t>https://www.newquest.com/about-us/leadership/</t>
         </is>
       </c>
       <c r="X237" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/fidelis-realty-partners</t>
+          <t>https://www.linkedin.com/company/newquest-properties</t>
         </is>
       </c>
       <c r="Y237" s="6" t="inlineStr">
         <is>
-          <t>https://www.frpltd.com/about-fidelis/mission-values</t>
+          <t>https://www.newquest.com/about-us/leadership/</t>
         </is>
       </c>
       <c r="Z237" s="6" t="inlineStr"/>
@@ -26127,7 +26296,7 @@
     <row r="238">
       <c r="A238" s="12" t="inlineStr">
         <is>
-          <t>Glenn Airola</t>
+          <t>K. Alan Hassenflu</t>
         </is>
       </c>
       <c r="B238" s="12" t="inlineStr">
@@ -26137,7 +26306,7 @@
       </c>
       <c r="C238" s="12" t="inlineStr">
         <is>
-          <t>Co-President and Chief Operating Officer</t>
+          <t>Chairman and Chief Executive Officer</t>
         </is>
       </c>
       <c r="D238" s="13" t="inlineStr">
@@ -26188,7 +26357,7 @@
       </c>
       <c r="P238" s="10" t="inlineStr"/>
       <c r="Q238" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Glenn%20Airola%20Fidelis%20Realty%20Partners","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=K.%20Alan%20Hassenflu%20Fidelis%20Realty%20Partners","search")</f>
         <v/>
       </c>
       <c r="R238" s="16">
@@ -26208,7 +26377,7 @@
       <c r="U238" s="12" t="inlineStr"/>
       <c r="V238" s="15" t="inlineStr">
         <is>
-          <t>Executive Vice President, General Counsel and Chief Administrative Officer since 2007.</t>
+          <t>President and Chief Executive Officer, a founder in 2003, formerly senior managing director at Trammell Crow.</t>
         </is>
       </c>
       <c r="W238" s="12" t="inlineStr">
@@ -26231,7 +26400,7 @@
     <row r="239">
       <c r="A239" s="6" t="inlineStr">
         <is>
-          <t>R. Carson Wilson IV</t>
+          <t>Glenn Airola</t>
         </is>
       </c>
       <c r="B239" s="6" t="inlineStr">
@@ -26241,7 +26410,7 @@
       </c>
       <c r="C239" s="6" t="inlineStr">
         <is>
-          <t>Executive Vice President of Leasing, Construction and Development, Fidelis Realty Partners</t>
+          <t>Co-President and Chief Operating Officer</t>
         </is>
       </c>
       <c r="D239" s="7" t="inlineStr">
@@ -26290,12 +26459,11 @@
           <t>Partly</t>
         </is>
       </c>
-      <c r="P239" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/r-carson-wilson-iv-9b7525292/</t>
-        </is>
-      </c>
-      <c r="Q239" s="6" t="inlineStr"/>
+      <c r="P239" s="10" t="inlineStr"/>
+      <c r="Q239" s="6">
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Glenn%20Airola%20Fidelis%20Realty%20Partners","search")</f>
+        <v/>
+      </c>
       <c r="R239" s="11">
         <f>IF(P239="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -26310,17 +26478,17 @@
           <t>Two land positions in target counties within 24 months. Every purchase price is undisclosed.</t>
         </is>
       </c>
-      <c r="U239" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="U239" s="6" t="inlineStr"/>
       <c r="V239" s="9" t="inlineStr">
         <is>
-          <t>Executive Vice President - Leasing, Construction and Development at Fidelis Realty Partners. Greater Houston. One title covers all three, so the person who signs the lease also owns the build.</t>
-        </is>
-      </c>
-      <c r="W239" s="6" t="inlineStr"/>
+          <t>Executive Vice President, General Counsel and Chief Administrative Officer since 2007.</t>
+        </is>
+      </c>
+      <c r="W239" s="6" t="inlineStr">
+        <is>
+          <t>https://www.frpltd.com/about-fidelis/mission-values</t>
+        </is>
+      </c>
       <c r="X239" s="6" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/fidelis-realty-partners</t>
@@ -26336,17 +26504,17 @@
     <row r="240">
       <c r="A240" s="12" t="inlineStr">
         <is>
-          <t>Brandt Bowden</t>
+          <t>R. Carson Wilson IV</t>
         </is>
       </c>
       <c r="B240" s="12" t="inlineStr">
         <is>
-          <t>The Hanover Company</t>
+          <t>Fidelis Realty Partners</t>
         </is>
       </c>
       <c r="C240" s="12" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Executive Vice President of Leasing, Construction and Development, Fidelis Realty Partners</t>
         </is>
       </c>
       <c r="D240" s="13" t="inlineStr">
@@ -26364,12 +26532,12 @@
       </c>
       <c r="G240" s="12" t="inlineStr">
         <is>
-          <t>Houston HQ, Harris County</t>
+          <t>Houston HQ / Brazoria, Montgomery</t>
         </is>
       </c>
       <c r="H240" s="12" t="inlineStr">
         <is>
-          <t>19 markets, in-house construction arm</t>
+          <t>26M sf, ~100 properties, 12 states</t>
         </is>
       </c>
       <c r="I240" s="14" t="inlineStr">
@@ -26395,40 +26563,45 @@
           <t>Partly</t>
         </is>
       </c>
-      <c r="P240" s="10" t="inlineStr"/>
-      <c r="Q240" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Brandt%20Bowden%20The%20Hanover%20Company","search")</f>
-        <v/>
-      </c>
+      <c r="P240" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/r-carson-wilson-iv-9b7525292/</t>
+        </is>
+      </c>
+      <c r="Q240" s="12" t="inlineStr"/>
       <c r="R240" s="16">
         <f>IF(P240="","ADD LINKEDIN","ok")</f>
         <v/>
       </c>
       <c r="S240" s="12" t="inlineStr">
         <is>
-          <t>https://www.hanoverco.com/</t>
+          <t>https://www.frpltd.com/</t>
         </is>
       </c>
       <c r="T240" s="15" t="inlineStr">
         <is>
-          <t>An in-house construction arm and a Houston HQ since 1982, but no Houston project could be sourced.</t>
-        </is>
-      </c>
-      <c r="U240" s="12" t="inlineStr"/>
+          <t>Two land positions in target counties within 24 months. Every purchase price is undisclosed.</t>
+        </is>
+      </c>
+      <c r="U240" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
       <c r="V240" s="15" t="inlineStr">
         <is>
-          <t>Chief Executive Officer of Hanover, overseeing capital, development and construction, previously chief investment officer.</t>
-        </is>
-      </c>
-      <c r="W240" s="12" t="inlineStr">
-        <is>
-          <t>https://knowledge.uli.org/en/people/b/b/brandt-bowden-f34f</t>
-        </is>
-      </c>
-      <c r="X240" s="12" t="inlineStr"/>
+          <t>Executive Vice President - Leasing, Construction and Development at Fidelis Realty Partners. Greater Houston. One title covers all three, so the person who signs the lease also owns the build.</t>
+        </is>
+      </c>
+      <c r="W240" s="12" t="inlineStr"/>
+      <c r="X240" s="12" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/fidelis-realty-partners</t>
+        </is>
+      </c>
       <c r="Y240" s="12" t="inlineStr">
         <is>
-          <t>https://www.hanoverco.com/leadership</t>
+          <t>https://www.frpltd.com/about-fidelis/mission-values</t>
         </is>
       </c>
       <c r="Z240" s="12" t="inlineStr"/>
@@ -26436,7 +26609,7 @@
     <row r="241">
       <c r="A241" s="6" t="inlineStr">
         <is>
-          <t>Murry Bowden</t>
+          <t>Brandt Bowden</t>
         </is>
       </c>
       <c r="B241" s="6" t="inlineStr">
@@ -26446,7 +26619,7 @@
       </c>
       <c r="C241" s="6" t="inlineStr">
         <is>
-          <t>Founder and Executive Chairman</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="D241" s="7" t="inlineStr">
@@ -26497,7 +26670,7 @@
       </c>
       <c r="P241" s="10" t="inlineStr"/>
       <c r="Q241" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Murry%20Bowden%20The%20Hanover%20Company","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Brandt%20Bowden%20The%20Hanover%20Company","search")</f>
         <v/>
       </c>
       <c r="R241" s="11">
@@ -26517,12 +26690,12 @@
       <c r="U241" s="6" t="inlineStr"/>
       <c r="V241" s="9" t="inlineStr">
         <is>
-          <t>Founder, Chairman and Chief Executive Officer, responsible for strategy and investment decisions.</t>
+          <t>Chief Executive Officer of Hanover, overseeing capital, development and construction, previously chief investment officer.</t>
         </is>
       </c>
       <c r="W241" s="6" t="inlineStr">
         <is>
-          <t>https://www.nmhc.org/meetings/meetings-pages/meeting-materials/j-murry-bowden-biography/</t>
+          <t>https://knowledge.uli.org/en/people/b/b/brandt-bowden-f34f</t>
         </is>
       </c>
       <c r="X241" s="6" t="inlineStr"/>
@@ -26536,7 +26709,7 @@
     <row r="242">
       <c r="A242" s="12" t="inlineStr">
         <is>
-          <t>John Nash</t>
+          <t>Murry Bowden</t>
         </is>
       </c>
       <c r="B242" s="12" t="inlineStr">
@@ -26546,7 +26719,7 @@
       </c>
       <c r="C242" s="12" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Founder and Executive Chairman</t>
         </is>
       </c>
       <c r="D242" s="13" t="inlineStr">
@@ -26597,7 +26770,7 @@
       </c>
       <c r="P242" s="10" t="inlineStr"/>
       <c r="Q242" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=John%20Nash%20The%20Hanover%20Company","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Murry%20Bowden%20The%20Hanover%20Company","search")</f>
         <v/>
       </c>
       <c r="R242" s="16">
@@ -26617,12 +26790,12 @@
       <c r="U242" s="12" t="inlineStr"/>
       <c r="V242" s="15" t="inlineStr">
         <is>
-          <t>President. Thirty-three years with Hanover, twenty-three of them as president, per the McCombs alumni network.</t>
+          <t>Founder, Chairman and Chief Executive Officer, responsible for strategy and investment decisions.</t>
         </is>
       </c>
       <c r="W242" s="12" t="inlineStr">
         <is>
-          <t>https://www.hanoverco.com/leadership</t>
+          <t>https://www.nmhc.org/meetings/meetings-pages/meeting-materials/j-murry-bowden-biography/</t>
         </is>
       </c>
       <c r="X242" s="12" t="inlineStr"/>
@@ -26636,7 +26809,7 @@
     <row r="243">
       <c r="A243" s="6" t="inlineStr">
         <is>
-          <t>John Garibaldi</t>
+          <t>John Nash</t>
         </is>
       </c>
       <c r="B243" s="6" t="inlineStr">
@@ -26646,7 +26819,7 @@
       </c>
       <c r="C243" s="6" t="inlineStr">
         <is>
-          <t>President, Multifamily</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D243" s="7" t="inlineStr">
@@ -26697,7 +26870,7 @@
       </c>
       <c r="P243" s="10" t="inlineStr"/>
       <c r="Q243" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=John%20Garibaldi%20The%20Hanover%20Company","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=John%20Nash%20The%20Hanover%20Company","search")</f>
         <v/>
       </c>
       <c r="R243" s="11">
@@ -26717,7 +26890,7 @@
       <c r="U243" s="6" t="inlineStr"/>
       <c r="V243" s="9" t="inlineStr">
         <is>
-          <t>President, Multifamily. Twenty-five years with the firm, starting as a development partner in Houston in 1999.</t>
+          <t>President. Thirty-three years with Hanover, twenty-three of them as president, per the McCombs alumni network.</t>
         </is>
       </c>
       <c r="W243" s="6" t="inlineStr">
@@ -26736,7 +26909,7 @@
     <row r="244">
       <c r="A244" s="12" t="inlineStr">
         <is>
-          <t>Thomas Knutson</t>
+          <t>John Garibaldi</t>
         </is>
       </c>
       <c r="B244" s="12" t="inlineStr">
@@ -26746,7 +26919,7 @@
       </c>
       <c r="C244" s="12" t="inlineStr">
         <is>
-          <t>President of Construction, The Hanover Company</t>
+          <t>President, Multifamily</t>
         </is>
       </c>
       <c r="D244" s="13" t="inlineStr">
@@ -26795,12 +26968,11 @@
           <t>Partly</t>
         </is>
       </c>
-      <c r="P244" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/thomas-knutson-a741898/</t>
-        </is>
-      </c>
-      <c r="Q244" s="12" t="inlineStr"/>
+      <c r="P244" s="10" t="inlineStr"/>
+      <c r="Q244" s="12">
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=John%20Garibaldi%20The%20Hanover%20Company","search")</f>
+        <v/>
+      </c>
       <c r="R244" s="16">
         <f>IF(P244="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -26815,17 +26987,17 @@
           <t>An in-house construction arm and a Houston HQ since 1982, but no Houston project could be sourced.</t>
         </is>
       </c>
-      <c r="U244" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="U244" s="12" t="inlineStr"/>
       <c r="V244" s="15" t="inlineStr">
         <is>
-          <t>President - Construction at The Hanover Company. Houston, Texas. Hanover builds its own work, so this is the head of the in-house contractor.</t>
-        </is>
-      </c>
-      <c r="W244" s="12" t="inlineStr"/>
+          <t>President, Multifamily. Twenty-five years with the firm, starting as a development partner in Houston in 1999.</t>
+        </is>
+      </c>
+      <c r="W244" s="12" t="inlineStr">
+        <is>
+          <t>https://www.hanoverco.com/leadership</t>
+        </is>
+      </c>
       <c r="X244" s="12" t="inlineStr"/>
       <c r="Y244" s="12" t="inlineStr">
         <is>
@@ -26837,7 +27009,7 @@
     <row r="245">
       <c r="A245" s="6" t="inlineStr">
         <is>
-          <t>Mark Wood</t>
+          <t>Thomas Knutson</t>
         </is>
       </c>
       <c r="B245" s="6" t="inlineStr">
@@ -26847,7 +27019,7 @@
       </c>
       <c r="C245" s="6" t="inlineStr">
         <is>
-          <t>Vice President of Construction, The Hanover Company</t>
+          <t>President of Construction, The Hanover Company</t>
         </is>
       </c>
       <c r="D245" s="7" t="inlineStr">
@@ -26898,7 +27070,7 @@
       </c>
       <c r="P245" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/mark-wood-49713011/</t>
+          <t>https://www.linkedin.com/in/thomas-knutson-a741898/</t>
         </is>
       </c>
       <c r="Q245" s="6" t="inlineStr"/>
@@ -26923,7 +27095,7 @@
       </c>
       <c r="V245" s="9" t="inlineStr">
         <is>
-          <t>Vice President - Construction at The Hanover Company. Houston, Texas.</t>
+          <t>President - Construction at The Hanover Company. Houston, Texas. Hanover builds its own work, so this is the head of the in-house contractor.</t>
         </is>
       </c>
       <c r="W245" s="6" t="inlineStr"/>
@@ -26938,7 +27110,7 @@
     <row r="246">
       <c r="A246" s="12" t="inlineStr">
         <is>
-          <t>Mike Wright</t>
+          <t>Mark Wood</t>
         </is>
       </c>
       <c r="B246" s="12" t="inlineStr">
@@ -26948,7 +27120,7 @@
       </c>
       <c r="C246" s="12" t="inlineStr">
         <is>
-          <t>Vice President of Preconstruction and Estimating, The Hanover Company</t>
+          <t>Vice President of Construction, The Hanover Company</t>
         </is>
       </c>
       <c r="D246" s="13" t="inlineStr">
@@ -26999,7 +27171,7 @@
       </c>
       <c r="P246" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/mike-wright-7795a8b/</t>
+          <t>https://www.linkedin.com/in/mark-wood-49713011/</t>
         </is>
       </c>
       <c r="Q246" s="12" t="inlineStr"/>
@@ -27024,7 +27196,7 @@
       </c>
       <c r="V246" s="15" t="inlineStr">
         <is>
-          <t>Vice President of Preconstruction &amp; Estimating at The Hanover Company. Katy, Texas. Preconstruction is where an unfamiliar wall system gets priced or dismissed, so this is the first real test of a printed assembly.</t>
+          <t>Vice President - Construction at The Hanover Company. Houston, Texas.</t>
         </is>
       </c>
       <c r="W246" s="12" t="inlineStr"/>
@@ -27039,17 +27211,17 @@
     <row r="247">
       <c r="A247" s="6" t="inlineStr">
         <is>
-          <t>Jeff Read</t>
+          <t>Mike Wright</t>
         </is>
       </c>
       <c r="B247" s="6" t="inlineStr">
         <is>
-          <t>Read King</t>
+          <t>The Hanover Company</t>
         </is>
       </c>
       <c r="C247" s="6" t="inlineStr">
         <is>
-          <t>Principal and Co-Founder</t>
+          <t>Vice President of Preconstruction and Estimating, The Hanover Company</t>
         </is>
       </c>
       <c r="D247" s="7" t="inlineStr">
@@ -27067,12 +27239,12 @@
       </c>
       <c r="G247" s="6" t="inlineStr">
         <is>
-          <t>Houston HQ / Fort Bend, Harris</t>
+          <t>Houston HQ, Harris County</t>
         </is>
       </c>
       <c r="H247" s="6" t="inlineStr">
         <is>
-          <t>36 freestanding ER centres, 100+ build-to-suit</t>
+          <t>19 markets, in-house construction arm</t>
         </is>
       </c>
       <c r="I247" s="8" t="inlineStr">
@@ -27095,47 +27267,44 @@
       <c r="N247" s="9" t="inlineStr"/>
       <c r="O247" s="8" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P247" s="10" t="inlineStr"/>
-      <c r="Q247" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Jeff%20Read%20Read%20King","search")</f>
-        <v/>
-      </c>
+          <t>Partly</t>
+        </is>
+      </c>
+      <c r="P247" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mike-wright-7795a8b/</t>
+        </is>
+      </c>
+      <c r="Q247" s="6" t="inlineStr"/>
       <c r="R247" s="11">
         <f>IF(P247="","ADD LINKEDIN","ok")</f>
         <v/>
       </c>
       <c r="S247" s="6" t="inlineStr">
         <is>
-          <t>https://read-king.com/</t>
+          <t>https://www.hanoverco.com/</t>
         </is>
       </c>
       <c r="T247" s="9" t="inlineStr">
         <is>
-          <t>36 freestanding emergency centres and over 100 build-to-suits, the most repeated small-commercial format screened.</t>
-        </is>
-      </c>
-      <c r="U247" s="6" t="inlineStr"/>
+          <t>An in-house construction arm and a Houston HQ since 1982, but no Houston project could be sourced.</t>
+        </is>
+      </c>
+      <c r="U247" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
       <c r="V247" s="9" t="inlineStr">
         <is>
-          <t>Principal.</t>
-        </is>
-      </c>
-      <c r="W247" s="6" t="inlineStr">
-        <is>
-          <t>https://www.read-king.com/team</t>
-        </is>
-      </c>
-      <c r="X247" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/read-king-inc-</t>
-        </is>
-      </c>
+          <t>Vice President of Preconstruction &amp; Estimating at The Hanover Company. Katy, Texas. Preconstruction is where an unfamiliar wall system gets priced or dismissed, so this is the first real test of a printed assembly.</t>
+        </is>
+      </c>
+      <c r="W247" s="6" t="inlineStr"/>
+      <c r="X247" s="6" t="inlineStr"/>
       <c r="Y247" s="6" t="inlineStr">
         <is>
-          <t>https://www.read-king.com/team</t>
+          <t>https://www.hanoverco.com/leadership</t>
         </is>
       </c>
       <c r="Z247" s="6" t="inlineStr"/>
@@ -27143,7 +27312,7 @@
     <row r="248">
       <c r="A248" s="12" t="inlineStr">
         <is>
-          <t>Ewing King</t>
+          <t>Jeff Read</t>
         </is>
       </c>
       <c r="B248" s="12" t="inlineStr">
@@ -27153,7 +27322,7 @@
       </c>
       <c r="C248" s="12" t="inlineStr">
         <is>
-          <t>Principal</t>
+          <t>Principal and Co-Founder</t>
         </is>
       </c>
       <c r="D248" s="13" t="inlineStr">
@@ -27204,7 +27373,7 @@
       </c>
       <c r="P248" s="10" t="inlineStr"/>
       <c r="Q248" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Ewing%20King%20Read%20King","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Jeff%20Read%20Read%20King","search")</f>
         <v/>
       </c>
       <c r="R248" s="16">
@@ -27247,7 +27416,7 @@
     <row r="249">
       <c r="A249" s="6" t="inlineStr">
         <is>
-          <t>Blake Allen</t>
+          <t>Ewing King</t>
         </is>
       </c>
       <c r="B249" s="6" t="inlineStr">
@@ -27257,7 +27426,7 @@
       </c>
       <c r="C249" s="6" t="inlineStr">
         <is>
-          <t>Chief Financial Officer</t>
+          <t>Principal</t>
         </is>
       </c>
       <c r="D249" s="7" t="inlineStr">
@@ -27308,7 +27477,7 @@
       </c>
       <c r="P249" s="10" t="inlineStr"/>
       <c r="Q249" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Blake%20Allen%20Read%20King","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Ewing%20King%20Read%20King","search")</f>
         <v/>
       </c>
       <c r="R249" s="11">
@@ -27328,7 +27497,7 @@
       <c r="U249" s="6" t="inlineStr"/>
       <c r="V249" s="9" t="inlineStr">
         <is>
-          <t>Chief Financial Officer.</t>
+          <t>Principal.</t>
         </is>
       </c>
       <c r="W249" s="6" t="inlineStr">
@@ -27351,7 +27520,7 @@
     <row r="250">
       <c r="A250" s="12" t="inlineStr">
         <is>
-          <t>Telisia Amaning</t>
+          <t>Blake Allen</t>
         </is>
       </c>
       <c r="B250" s="12" t="inlineStr">
@@ -27361,7 +27530,7 @@
       </c>
       <c r="C250" s="12" t="inlineStr">
         <is>
-          <t>Chief Operating Officer</t>
+          <t>Chief Financial Officer</t>
         </is>
       </c>
       <c r="D250" s="13" t="inlineStr">
@@ -27410,12 +27579,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P250" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/telisiaamaning/</t>
-        </is>
-      </c>
-      <c r="Q250" s="12" t="inlineStr"/>
+      <c r="P250" s="10" t="inlineStr"/>
+      <c r="Q250" s="12">
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Blake%20Allen%20Read%20King","search")</f>
+        <v/>
+      </c>
       <c r="R250" s="16">
         <f>IF(P250="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -27433,10 +27601,14 @@
       <c r="U250" s="12" t="inlineStr"/>
       <c r="V250" s="15" t="inlineStr">
         <is>
-          <t>Chief Operating Officer, READ KING. Houston, Texas.</t>
-        </is>
-      </c>
-      <c r="W250" s="12" t="inlineStr"/>
+          <t>Chief Financial Officer.</t>
+        </is>
+      </c>
+      <c r="W250" s="12" t="inlineStr">
+        <is>
+          <t>https://www.read-king.com/team</t>
+        </is>
+      </c>
       <c r="X250" s="12" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/read-king-inc-</t>
@@ -27452,17 +27624,17 @@
     <row r="251">
       <c r="A251" s="6" t="inlineStr">
         <is>
-          <t>Alex Jessett</t>
+          <t>Telisia Amaning</t>
         </is>
       </c>
       <c r="B251" s="6" t="inlineStr">
         <is>
-          <t>Camden Property Trust</t>
+          <t>Read King</t>
         </is>
       </c>
       <c r="C251" s="6" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Chief Operating Officer</t>
         </is>
       </c>
       <c r="D251" s="7" t="inlineStr">
@@ -27480,17 +27652,17 @@
       </c>
       <c r="G251" s="6" t="inlineStr">
         <is>
-          <t>Houston HQ / Fort Bend, Montgomery</t>
+          <t>Houston HQ / Fort Bend, Harris</t>
         </is>
       </c>
       <c r="H251" s="6" t="inlineStr">
         <is>
-          <t>$155M into 389 BTR homes</t>
+          <t>36 freestanding ER centres, 100+ build-to-suit</t>
         </is>
       </c>
       <c r="I251" s="8" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J251" s="9" t="inlineStr"/>
@@ -27508,47 +27680,44 @@
       <c r="N251" s="9" t="inlineStr"/>
       <c r="O251" s="8" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P251" s="10" t="inlineStr"/>
-      <c r="Q251" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Alex%20Jessett%20Camden%20Property%20Trust","search")</f>
-        <v/>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P251" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/telisiaamaning/</t>
+        </is>
+      </c>
+      <c r="Q251" s="6" t="inlineStr"/>
       <c r="R251" s="11">
         <f>IF(P251="","ADD LINKEDIN","ok")</f>
         <v/>
       </c>
       <c r="S251" s="6" t="inlineStr">
         <is>
-          <t>https://www.camdenliving.com/</t>
+          <t>https://read-king.com/</t>
         </is>
       </c>
       <c r="T251" s="9" t="inlineStr">
         <is>
-          <t>$155M into 389 build-to-rent homes, Houston HQ, holds long term. Figures date to 2022.</t>
+          <t>36 freestanding emergency centres and over 100 build-to-suits, the most repeated small-commercial format screened.</t>
         </is>
       </c>
       <c r="U251" s="6" t="inlineStr"/>
       <c r="V251" s="9" t="inlineStr">
         <is>
-          <t>Chief Executive Officer, previously President and Chief Financial Officer, at Camden since 1999.</t>
-        </is>
-      </c>
-      <c r="W251" s="6" t="inlineStr">
-        <is>
-          <t>https://investors.camdenliving.com/investors/governance/board-of-directors/default.aspx</t>
-        </is>
-      </c>
+          <t>Chief Operating Officer, READ KING. Houston, Texas.</t>
+        </is>
+      </c>
+      <c r="W251" s="6" t="inlineStr"/>
       <c r="X251" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/camden-property-trust</t>
+          <t>https://www.linkedin.com/company/read-king-inc-</t>
         </is>
       </c>
       <c r="Y251" s="6" t="inlineStr">
         <is>
-          <t>https://investors.camdenliving.com/investors/governance/board-of-directors/default.aspx</t>
+          <t>https://www.read-king.com/team</t>
         </is>
       </c>
       <c r="Z251" s="6" t="inlineStr"/>
@@ -27556,7 +27725,7 @@
     <row r="252">
       <c r="A252" s="12" t="inlineStr">
         <is>
-          <t>Richard J. Campo</t>
+          <t>Alex Jessett</t>
         </is>
       </c>
       <c r="B252" s="12" t="inlineStr">
@@ -27566,7 +27735,7 @@
       </c>
       <c r="C252" s="12" t="inlineStr">
         <is>
-          <t>Executive Chairman of the Board of Trust Managers</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="D252" s="13" t="inlineStr">
@@ -27617,7 +27786,7 @@
       </c>
       <c r="P252" s="10" t="inlineStr"/>
       <c r="Q252" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Richard%20J.%20Campo%20Camden%20Property%20Trust","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Alex%20Jessett%20Camden%20Property%20Trust","search")</f>
         <v/>
       </c>
       <c r="R252" s="16">
@@ -27637,7 +27806,7 @@
       <c r="U252" s="12" t="inlineStr"/>
       <c r="V252" s="15" t="inlineStr">
         <is>
-          <t>Executive Chairman, chief executive from the 1993 listing until 2026.</t>
+          <t>Chief Executive Officer, previously President and Chief Financial Officer, at Camden since 1999.</t>
         </is>
       </c>
       <c r="W252" s="12" t="inlineStr">
@@ -27660,7 +27829,7 @@
     <row r="253">
       <c r="A253" s="6" t="inlineStr">
         <is>
-          <t>Michael Eilertsen</t>
+          <t>Richard J. Campo</t>
         </is>
       </c>
       <c r="B253" s="6" t="inlineStr">
@@ -27670,7 +27839,7 @@
       </c>
       <c r="C253" s="6" t="inlineStr">
         <is>
-          <t>Vice President of Construction, Camden Property Trust</t>
+          <t>Executive Chairman of the Board of Trust Managers</t>
         </is>
       </c>
       <c r="D253" s="7" t="inlineStr">
@@ -27719,12 +27888,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P253" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/michael-eilertsen-68a59911/</t>
-        </is>
-      </c>
-      <c r="Q253" s="6" t="inlineStr"/>
+      <c r="P253" s="10" t="inlineStr"/>
+      <c r="Q253" s="6">
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Richard%20J.%20Campo%20Camden%20Property%20Trust","search")</f>
+        <v/>
+      </c>
       <c r="R253" s="11">
         <f>IF(P253="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -27739,17 +27907,17 @@
           <t>$155M into 389 build-to-rent homes, Houston HQ, holds long term. Figures date to 2022.</t>
         </is>
       </c>
-      <c r="U253" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="U253" s="6" t="inlineStr"/>
       <c r="V253" s="9" t="inlineStr">
         <is>
-          <t>Vice President Of Construction at Camden Property Trust. Houston, Texas.</t>
-        </is>
-      </c>
-      <c r="W253" s="6" t="inlineStr"/>
+          <t>Executive Chairman, chief executive from the 1993 listing until 2026.</t>
+        </is>
+      </c>
+      <c r="W253" s="6" t="inlineStr">
+        <is>
+          <t>https://investors.camdenliving.com/investors/governance/board-of-directors/default.aspx</t>
+        </is>
+      </c>
       <c r="X253" s="6" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/camden-property-trust</t>
@@ -27765,17 +27933,17 @@
     <row r="254">
       <c r="A254" s="12" t="inlineStr">
         <is>
-          <t>Bob Faith</t>
+          <t>Michael Eilertsen</t>
         </is>
       </c>
       <c r="B254" s="12" t="inlineStr">
         <is>
-          <t>Greystar (Summerwell)</t>
+          <t>Camden Property Trust</t>
         </is>
       </c>
       <c r="C254" s="12" t="inlineStr">
         <is>
-          <t>Founder, Chairman and Chief Executive Officer</t>
+          <t>Vice President of Construction, Camden Property Trust</t>
         </is>
       </c>
       <c r="D254" s="13" t="inlineStr">
@@ -27793,12 +27961,12 @@
       </c>
       <c r="G254" s="12" t="inlineStr">
         <is>
-          <t>Charleston HQ / Katy, Harris-Waller</t>
+          <t>Houston HQ / Fort Bend, Montgomery</t>
         </is>
       </c>
       <c r="H254" s="12" t="inlineStr">
         <is>
-          <t>Summerwell: 10,000+ homes, 50 properties</t>
+          <t>$155M into 389 BTR homes</t>
         </is>
       </c>
       <c r="I254" s="14" t="inlineStr">
@@ -27824,44 +27992,45 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P254" s="10" t="inlineStr"/>
-      <c r="Q254" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Bob%20Faith%20Greystar","search")</f>
-        <v/>
-      </c>
+      <c r="P254" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/michael-eilertsen-68a59911/</t>
+        </is>
+      </c>
+      <c r="Q254" s="12" t="inlineStr"/>
       <c r="R254" s="16">
         <f>IF(P254="","ADD LINKEDIN","ok")</f>
         <v/>
       </c>
       <c r="S254" s="12" t="inlineStr">
         <is>
-          <t>https://www.greystar.com/</t>
+          <t>https://www.camdenliving.com/</t>
         </is>
       </c>
       <c r="T254" s="15" t="inlineStr">
         <is>
-          <t>156 units inside Sunterra, a Houston-based development director, and a 10,000-home national brand. Costs withheld.</t>
-        </is>
-      </c>
-      <c r="U254" s="12" t="inlineStr"/>
+          <t>$155M into 389 build-to-rent homes, Houston HQ, holds long term. Figures date to 2022.</t>
+        </is>
+      </c>
+      <c r="U254" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
       <c r="V254" s="15" t="inlineStr">
         <is>
-          <t>Founder, Chairman and Chief Executive Officer on Greystar's own bio page.</t>
-        </is>
-      </c>
-      <c r="W254" s="12" t="inlineStr">
-        <is>
-          <t>https://www.greystar.com/contact-us/our-people/bob-faith</t>
-        </is>
-      </c>
+          <t>Vice President Of Construction at Camden Property Trust. Houston, Texas.</t>
+        </is>
+      </c>
+      <c r="W254" s="12" t="inlineStr"/>
       <c r="X254" s="12" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/greystar</t>
+          <t>https://www.linkedin.com/company/camden-property-trust</t>
         </is>
       </c>
       <c r="Y254" s="12" t="inlineStr">
         <is>
-          <t>https://www.greystar.com/business/about-greystar/our-leadership</t>
+          <t>https://investors.camdenliving.com/investors/governance/board-of-directors/default.aspx</t>
         </is>
       </c>
       <c r="Z254" s="12" t="inlineStr"/>
@@ -27869,7 +28038,7 @@
     <row r="255">
       <c r="A255" s="6" t="inlineStr">
         <is>
-          <t>Brian Herwald</t>
+          <t>Bob Faith</t>
         </is>
       </c>
       <c r="B255" s="6" t="inlineStr">
@@ -27879,7 +28048,7 @@
       </c>
       <c r="C255" s="6" t="inlineStr">
         <is>
-          <t>Managing Director of Development, Houston</t>
+          <t>Founder, Chairman and Chief Executive Officer</t>
         </is>
       </c>
       <c r="D255" s="7" t="inlineStr">
@@ -27930,7 +28099,7 @@
       </c>
       <c r="P255" s="10" t="inlineStr"/>
       <c r="Q255" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Brian%20Herwald%20Greystar","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Bob%20Faith%20Greystar","search")</f>
         <v/>
       </c>
       <c r="R255" s="11">
@@ -27950,12 +28119,12 @@
       <c r="U255" s="6" t="inlineStr"/>
       <c r="V255" s="9" t="inlineStr">
         <is>
-          <t>Managing Director of Development, quoted on Greystar's first Houston logistics project.</t>
+          <t>Founder, Chairman and Chief Executive Officer on Greystar's own bio page.</t>
         </is>
       </c>
       <c r="W255" s="6" t="inlineStr">
         <is>
-          <t>https://www.greystar.com/business/about-greystar/newsroom/greystar-completes-first-logistics-project-in-houston</t>
+          <t>https://www.greystar.com/contact-us/our-people/bob-faith</t>
         </is>
       </c>
       <c r="X255" s="6" t="inlineStr">
@@ -27973,17 +28142,17 @@
     <row r="256">
       <c r="A256" s="12" t="inlineStr">
         <is>
-          <t>Brian Dinerstein</t>
+          <t>Brian Herwald</t>
         </is>
       </c>
       <c r="B256" s="12" t="inlineStr">
         <is>
-          <t>The Dinerstein Companies</t>
+          <t>Greystar (Summerwell)</t>
         </is>
       </c>
       <c r="C256" s="12" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Managing Director of Development, Houston</t>
         </is>
       </c>
       <c r="D256" s="13" t="inlineStr">
@@ -28001,12 +28170,12 @@
       </c>
       <c r="G256" s="12" t="inlineStr">
         <is>
-          <t>Houston HQ / Fort Bend</t>
+          <t>Charleston HQ / Katy, Harris-Waller</t>
         </is>
       </c>
       <c r="H256" s="12" t="inlineStr">
         <is>
-          <t>186 BTR homes, Harrison Street JV</t>
+          <t>Summerwell: 10,000+ homes, 50 properties</t>
         </is>
       </c>
       <c r="I256" s="14" t="inlineStr">
@@ -28034,7 +28203,7 @@
       </c>
       <c r="P256" s="10" t="inlineStr"/>
       <c r="Q256" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Brian%20Dinerstein%20The%20Dinerstein%20Companies","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Brian%20Herwald%20Greystar","search")</f>
         <v/>
       </c>
       <c r="R256" s="16">
@@ -28043,33 +28212,33 @@
       </c>
       <c r="S256" s="12" t="inlineStr">
         <is>
-          <t>https://www.dinersteincos.com/</t>
+          <t>https://www.greystar.com/</t>
         </is>
       </c>
       <c r="T256" s="15" t="inlineStr">
         <is>
-          <t>186 build-to-rent homes with Harrison Street and 70 years in Houston. Launch coverage is amenities only.</t>
+          <t>156 units inside Sunterra, a Houston-based development director, and a 10,000-home national brand. Costs withheld.</t>
         </is>
       </c>
       <c r="U256" s="12" t="inlineStr"/>
       <c r="V256" s="15" t="inlineStr">
         <is>
-          <t>The firm's own bio page. Chief Executive Officer of a developer and operator with $4.3 billion under management.</t>
+          <t>Managing Director of Development, quoted on Greystar's first Houston logistics project.</t>
         </is>
       </c>
       <c r="W256" s="12" t="inlineStr">
         <is>
-          <t>https://www.dinersteincos.com/team/brian-dinerstein</t>
+          <t>https://www.greystar.com/business/about-greystar/newsroom/greystar-completes-first-logistics-project-in-houston</t>
         </is>
       </c>
       <c r="X256" s="12" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/the-dinerstein-companies/</t>
+          <t>https://www.linkedin.com/company/greystar</t>
         </is>
       </c>
       <c r="Y256" s="12" t="inlineStr">
         <is>
-          <t>https://www.dinersteincos.com/about-us</t>
+          <t>https://www.greystar.com/business/about-greystar/our-leadership</t>
         </is>
       </c>
       <c r="Z256" s="12" t="inlineStr"/>
@@ -28077,7 +28246,7 @@
     <row r="257">
       <c r="A257" s="6" t="inlineStr">
         <is>
-          <t>Jack Dinerstein</t>
+          <t>Brian Dinerstein</t>
         </is>
       </c>
       <c r="B257" s="6" t="inlineStr">
@@ -28087,7 +28256,7 @@
       </c>
       <c r="C257" s="6" t="inlineStr">
         <is>
-          <t>Executive Chairman</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="D257" s="7" t="inlineStr">
@@ -28136,12 +28305,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P257" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/jack-dinerstein-4215073/</t>
-        </is>
-      </c>
-      <c r="Q257" s="6" t="inlineStr"/>
+      <c r="P257" s="10" t="inlineStr"/>
+      <c r="Q257" s="6">
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Brian%20Dinerstein%20The%20Dinerstein%20Companies","search")</f>
+        <v/>
+      </c>
       <c r="R257" s="11">
         <f>IF(P257="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -28159,10 +28327,14 @@
       <c r="U257" s="6" t="inlineStr"/>
       <c r="V257" s="9" t="inlineStr">
         <is>
-          <t>Owner, Dinerstein Companies. Houston, Texas.</t>
-        </is>
-      </c>
-      <c r="W257" s="6" t="inlineStr"/>
+          <t>The firm's own bio page. Chief Executive Officer of a developer and operator with $4.3 billion under management.</t>
+        </is>
+      </c>
+      <c r="W257" s="6" t="inlineStr">
+        <is>
+          <t>https://www.dinersteincos.com/team/brian-dinerstein</t>
+        </is>
+      </c>
       <c r="X257" s="6" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/the-dinerstein-companies/</t>
@@ -28178,7 +28350,7 @@
     <row r="258">
       <c r="A258" s="12" t="inlineStr">
         <is>
-          <t>Brad Dinerstein</t>
+          <t>Jack Dinerstein</t>
         </is>
       </c>
       <c r="B258" s="12" t="inlineStr">
@@ -28188,7 +28360,7 @@
       </c>
       <c r="C258" s="12" t="inlineStr">
         <is>
-          <t>Managing Partner of Development and Design</t>
+          <t>Executive Chairman</t>
         </is>
       </c>
       <c r="D258" s="13" t="inlineStr">
@@ -28237,11 +28409,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P258" s="10" t="inlineStr"/>
-      <c r="Q258" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Brad%20Dinerstein%20The%20Dinerstein%20Companies","search")</f>
-        <v/>
-      </c>
+      <c r="P258" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jack-dinerstein-4215073/</t>
+        </is>
+      </c>
+      <c r="Q258" s="12" t="inlineStr"/>
       <c r="R258" s="16">
         <f>IF(P258="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -28259,14 +28432,10 @@
       <c r="U258" s="12" t="inlineStr"/>
       <c r="V258" s="15" t="inlineStr">
         <is>
-          <t>Managing Partner of Development and Design.</t>
-        </is>
-      </c>
-      <c r="W258" s="12" t="inlineStr">
-        <is>
-          <t>https://www.dinersteincos.com/about-us</t>
-        </is>
-      </c>
+          <t>Owner, Dinerstein Companies. Houston, Texas.</t>
+        </is>
+      </c>
+      <c r="W258" s="12" t="inlineStr"/>
       <c r="X258" s="12" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/the-dinerstein-companies/</t>
@@ -28282,7 +28451,7 @@
     <row r="259">
       <c r="A259" s="6" t="inlineStr">
         <is>
-          <t>John Caltagirone</t>
+          <t>Brad Dinerstein</t>
         </is>
       </c>
       <c r="B259" s="6" t="inlineStr">
@@ -28292,7 +28461,7 @@
       </c>
       <c r="C259" s="6" t="inlineStr">
         <is>
-          <t>President and Partner</t>
+          <t>Managing Partner of Development and Design</t>
         </is>
       </c>
       <c r="D259" s="7" t="inlineStr">
@@ -28343,7 +28512,7 @@
       </c>
       <c r="P259" s="10" t="inlineStr"/>
       <c r="Q259" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=John%20Caltagirone%20The%20Dinerstein%20Companies","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Brad%20Dinerstein%20The%20Dinerstein%20Companies","search")</f>
         <v/>
       </c>
       <c r="R259" s="11">
@@ -28363,7 +28532,7 @@
       <c r="U259" s="6" t="inlineStr"/>
       <c r="V259" s="9" t="inlineStr">
         <is>
-          <t>President and Partner.</t>
+          <t>Managing Partner of Development and Design.</t>
         </is>
       </c>
       <c r="W259" s="6" t="inlineStr">
@@ -28386,17 +28555,17 @@
     <row r="260">
       <c r="A260" s="12" t="inlineStr">
         <is>
-          <t>Jason Baker</t>
+          <t>John Caltagirone</t>
         </is>
       </c>
       <c r="B260" s="12" t="inlineStr">
         <is>
-          <t>Baker Katz</t>
+          <t>The Dinerstein Companies</t>
         </is>
       </c>
       <c r="C260" s="12" t="inlineStr">
         <is>
-          <t>Leads the tenant representation team, Baker Katz</t>
+          <t>President and Partner</t>
         </is>
       </c>
       <c r="D260" s="13" t="inlineStr">
@@ -28414,10 +28583,14 @@
       </c>
       <c r="G260" s="12" t="inlineStr">
         <is>
-          <t>Houston / Harris, Galveston</t>
-        </is>
-      </c>
-      <c r="H260" s="12" t="inlineStr"/>
+          <t>Houston HQ / Fort Bend</t>
+        </is>
+      </c>
+      <c r="H260" s="12" t="inlineStr">
+        <is>
+          <t>186 BTR homes, Harrison Street JV</t>
+        </is>
+      </c>
       <c r="I260" s="14" t="inlineStr">
         <is>
           <t>Partly</t>
@@ -28438,12 +28611,12 @@
       <c r="N260" s="15" t="inlineStr"/>
       <c r="O260" s="14" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P260" s="10" t="inlineStr"/>
       <c r="Q260" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Jason%20Baker%20Baker%20Katz","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=John%20Caltagirone%20The%20Dinerstein%20Companies","search")</f>
         <v/>
       </c>
       <c r="R260" s="16">
@@ -28452,33 +28625,33 @@
       </c>
       <c r="S260" s="12" t="inlineStr">
         <is>
-          <t>https://bakerkatz.com/</t>
+          <t>https://www.dinersteincos.com/</t>
         </is>
       </c>
       <c r="T260" s="15" t="inlineStr">
         <is>
-          <t>More than 80 retail projects, but recent Houston activity is buying existing centres rather than building.</t>
+          <t>186 build-to-rent homes with Harrison Street and 70 years in Houston. Launch coverage is amenities only.</t>
         </is>
       </c>
       <c r="U260" s="12" t="inlineStr"/>
       <c r="V260" s="15" t="inlineStr">
         <is>
-          <t>Leads the tenant representation team, with more than twenty-five years in Houston retail. The page carries bios without formal titles.</t>
+          <t>President and Partner.</t>
         </is>
       </c>
       <c r="W260" s="12" t="inlineStr">
         <is>
-          <t>https://bakerkatz.com/about-us/</t>
+          <t>https://www.dinersteincos.com/about-us</t>
         </is>
       </c>
       <c r="X260" s="12" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/baker-katz</t>
+          <t>https://www.linkedin.com/company/the-dinerstein-companies/</t>
         </is>
       </c>
       <c r="Y260" s="12" t="inlineStr">
         <is>
-          <t>https://bakerkatz.com/about-us/</t>
+          <t>https://www.dinersteincos.com/about-us</t>
         </is>
       </c>
       <c r="Z260" s="12" t="inlineStr"/>
@@ -28486,7 +28659,7 @@
     <row r="261">
       <c r="A261" s="6" t="inlineStr">
         <is>
-          <t>Kenneth Katz</t>
+          <t>Jason Baker</t>
         </is>
       </c>
       <c r="B261" s="6" t="inlineStr">
@@ -28496,7 +28669,7 @@
       </c>
       <c r="C261" s="6" t="inlineStr">
         <is>
-          <t>Leads the investment and development practice, Baker Katz</t>
+          <t>Leads the tenant representation team, Baker Katz</t>
         </is>
       </c>
       <c r="D261" s="7" t="inlineStr">
@@ -28543,7 +28716,7 @@
       </c>
       <c r="P261" s="10" t="inlineStr"/>
       <c r="Q261" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Kenneth%20Katz%20Baker%20Katz","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Jason%20Baker%20Baker%20Katz","search")</f>
         <v/>
       </c>
       <c r="R261" s="11">
@@ -28563,7 +28736,7 @@
       <c r="U261" s="6" t="inlineStr"/>
       <c r="V261" s="9" t="inlineStr">
         <is>
-          <t>Leads the real estate investment and development practice, covering ground-up development and redevelopment.</t>
+          <t>Leads the tenant representation team, with more than twenty-five years in Houston retail. The page carries bios without formal titles.</t>
         </is>
       </c>
       <c r="W261" s="6" t="inlineStr">
@@ -28586,7 +28759,7 @@
     <row r="262">
       <c r="A262" s="12" t="inlineStr">
         <is>
-          <t>Martin Mendoza</t>
+          <t>Kenneth Katz</t>
         </is>
       </c>
       <c r="B262" s="12" t="inlineStr">
@@ -28596,7 +28769,7 @@
       </c>
       <c r="C262" s="12" t="inlineStr">
         <is>
-          <t>Oversees design and construction, Baker Katz</t>
+          <t>Leads the investment and development practice, Baker Katz</t>
         </is>
       </c>
       <c r="D262" s="13" t="inlineStr">
@@ -28643,7 +28816,7 @@
       </c>
       <c r="P262" s="10" t="inlineStr"/>
       <c r="Q262" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Martin%20Mendoza%20Baker%20Katz","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Kenneth%20Katz%20Baker%20Katz","search")</f>
         <v/>
       </c>
       <c r="R262" s="16">
@@ -28660,14 +28833,10 @@
           <t>More than 80 retail projects, but recent Houston activity is buying existing centres rather than building.</t>
         </is>
       </c>
-      <c r="U262" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="U262" s="12" t="inlineStr"/>
       <c r="V262" s="15" t="inlineStr">
         <is>
-          <t>Joined in August 2024 responsible for overseeing design and construction phases. The page gives no title, so the function rather than the rank is what places him here.</t>
+          <t>Leads the real estate investment and development practice, covering ground-up development and redevelopment.</t>
         </is>
       </c>
       <c r="W262" s="12" t="inlineStr">
@@ -28690,17 +28859,17 @@
     <row r="263">
       <c r="A263" s="6" t="inlineStr">
         <is>
-          <t>Bob Sellingsloh</t>
+          <t>Martin Mendoza</t>
         </is>
       </c>
       <c r="B263" s="6" t="inlineStr">
         <is>
-          <t>Wulfe &amp; Co.</t>
+          <t>Baker Katz</t>
         </is>
       </c>
       <c r="C263" s="6" t="inlineStr">
         <is>
-          <t>President and Principal, Wulfe &amp; Co.</t>
+          <t>Oversees design and construction, Baker Katz</t>
         </is>
       </c>
       <c r="D263" s="7" t="inlineStr">
@@ -28718,7 +28887,7 @@
       </c>
       <c r="G263" s="6" t="inlineStr">
         <is>
-          <t>Post Oak / Harris, Galveston</t>
+          <t>Houston / Harris, Galveston</t>
         </is>
       </c>
       <c r="H263" s="6" t="inlineStr"/>
@@ -28742,12 +28911,12 @@
       <c r="N263" s="9" t="inlineStr"/>
       <c r="O263" s="8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partly</t>
         </is>
       </c>
       <c r="P263" s="10" t="inlineStr"/>
       <c r="Q263" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Bob%20Sellingsloh%20Wulfe%20%26%20Co.","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Martin%20Mendoza%20Baker%20Katz","search")</f>
         <v/>
       </c>
       <c r="R263" s="11">
@@ -28756,33 +28925,37 @@
       </c>
       <c r="S263" s="6" t="inlineStr">
         <is>
-          <t>https://www.wulfe.com/</t>
+          <t>https://bakerkatz.com/</t>
         </is>
       </c>
       <c r="T263" s="9" t="inlineStr">
         <is>
-          <t>7.2M sf across nine centres. Current activity is leasing and management, not ground-up.</t>
-        </is>
-      </c>
-      <c r="U263" s="6" t="inlineStr"/>
+          <t>More than 80 retail projects, but recent Houston activity is buying existing centres rather than building.</t>
+        </is>
+      </c>
+      <c r="U263" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
       <c r="V263" s="9" t="inlineStr">
         <is>
-          <t>President and Principal, listed first under leadership. Ed Wulfe no longer appears on the leadership page.</t>
+          <t>Joined in August 2024 responsible for overseeing design and construction phases. The page gives no title, so the function rather than the rank is what places him here.</t>
         </is>
       </c>
       <c r="W263" s="6" t="inlineStr">
         <is>
-          <t>https://www.wulfe.com/people</t>
+          <t>https://bakerkatz.com/about-us/</t>
         </is>
       </c>
       <c r="X263" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/wulfe</t>
+          <t>https://www.linkedin.com/company/baker-katz</t>
         </is>
       </c>
       <c r="Y263" s="6" t="inlineStr">
         <is>
-          <t>https://www.wulfe.com/people</t>
+          <t>https://bakerkatz.com/about-us/</t>
         </is>
       </c>
       <c r="Z263" s="6" t="inlineStr"/>
@@ -28790,7 +28963,7 @@
     <row r="264">
       <c r="A264" s="12" t="inlineStr">
         <is>
-          <t>Tammy Smith</t>
+          <t>Bob Sellingsloh</t>
         </is>
       </c>
       <c r="B264" s="12" t="inlineStr">
@@ -28800,7 +28973,7 @@
       </c>
       <c r="C264" s="12" t="inlineStr">
         <is>
-          <t>Director of Construction, Wulfe &amp; Co.</t>
+          <t>President and Principal, Wulfe &amp; Co.</t>
         </is>
       </c>
       <c r="D264" s="13" t="inlineStr">
@@ -28847,7 +29020,7 @@
       </c>
       <c r="P264" s="10" t="inlineStr"/>
       <c r="Q264" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Tammy%20Smith%20Wulfe%20%26%20Co.","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Bob%20Sellingsloh%20Wulfe%20%26%20Co.","search")</f>
         <v/>
       </c>
       <c r="R264" s="16">
@@ -28864,42 +29037,142 @@
           <t>7.2M sf across nine centres. Current activity is leasing and management, not ground-up.</t>
         </is>
       </c>
-      <c r="U264" s="12" t="inlineStr">
+      <c r="U264" s="12" t="inlineStr"/>
+      <c r="V264" s="15" t="inlineStr">
+        <is>
+          <t>President and Principal, listed first under leadership. Ed Wulfe no longer appears on the leadership page.</t>
+        </is>
+      </c>
+      <c r="W264" s="12" t="inlineStr">
+        <is>
+          <t>https://www.wulfe.com/people</t>
+        </is>
+      </c>
+      <c r="X264" s="12" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wulfe</t>
+        </is>
+      </c>
+      <c r="Y264" s="12" t="inlineStr">
+        <is>
+          <t>https://www.wulfe.com/people</t>
+        </is>
+      </c>
+      <c r="Z264" s="12" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="6" t="inlineStr">
+        <is>
+          <t>Tammy Smith</t>
+        </is>
+      </c>
+      <c r="B265" s="6" t="inlineStr">
+        <is>
+          <t>Wulfe &amp; Co.</t>
+        </is>
+      </c>
+      <c r="C265" s="6" t="inlineStr">
+        <is>
+          <t>Director of Construction, Wulfe &amp; Co.</t>
+        </is>
+      </c>
+      <c r="D265" s="7" t="inlineStr">
+        <is>
+          <t>Off deck, screened out</t>
+        </is>
+      </c>
+      <c r="E265" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F265" s="6" t="inlineStr">
+        <is>
+          <t>Buys walls</t>
+        </is>
+      </c>
+      <c r="G265" s="6" t="inlineStr">
+        <is>
+          <t>Post Oak / Harris, Galveston</t>
+        </is>
+      </c>
+      <c r="H265" s="6" t="inlineStr"/>
+      <c r="I265" s="8" t="inlineStr">
+        <is>
+          <t>Partly</t>
+        </is>
+      </c>
+      <c r="J265" s="9" t="inlineStr"/>
+      <c r="K265" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L265" s="9" t="inlineStr"/>
+      <c r="M265" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N265" s="9" t="inlineStr"/>
+      <c r="O265" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P265" s="10" t="inlineStr"/>
+      <c r="Q265" s="6">
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Tammy%20Smith%20Wulfe%20%26%20Co.","search")</f>
+        <v/>
+      </c>
+      <c r="R265" s="11">
+        <f>IF(P265="","ADD LINKEDIN","ok")</f>
+        <v/>
+      </c>
+      <c r="S265" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wulfe.com/</t>
+        </is>
+      </c>
+      <c r="T265" s="9" t="inlineStr">
+        <is>
+          <t>7.2M sf across nine centres. Current activity is leasing and management, not ground-up.</t>
+        </is>
+      </c>
+      <c r="U265" s="6" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="V264" s="15" t="inlineStr">
+      <c r="V265" s="9" t="inlineStr">
         <is>
           <t>Director of Construction.</t>
         </is>
       </c>
-      <c r="W264" s="12" t="inlineStr">
+      <c r="W265" s="6" t="inlineStr">
         <is>
           <t>https://www.wulfe.com/people</t>
         </is>
       </c>
-      <c r="X264" s="12" t="inlineStr">
+      <c r="X265" s="6" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/wulfe</t>
         </is>
       </c>
-      <c r="Y264" s="12" t="inlineStr">
+      <c r="Y265" s="6" t="inlineStr">
         <is>
           <t>https://www.wulfe.com/people</t>
         </is>
       </c>
-      <c r="Z264" s="12" t="inlineStr"/>
-    </row>
-    <row r="266">
-      <c r="A266" s="17" t="inlineStr">
-        <is>
-          <t>NOTE. A filled LinkedIn cell means the profile was opened or the search result read and the headline named the firm; column W records what was read. Where that test failed the cell is left empty rather than guessed, because a fabricated slug passes visual inspection and then fails in front of the person it names. Column Q searches for the empty ones in your own session. Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Capital is a qualifier, not a count. Source: ICON Greater Houston screen, build 46, 2026-09-11.</t>
+      <c r="Z265" s="6" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="17" t="inlineStr">
+        <is>
+          <t>NOTE. A filled LinkedIn cell means the profile was opened or the search result read and the headline named the firm; column W records what was read. Where that test failed the cell is left empty rather than guessed, because a fabricated slug passes visual inspection and then fails in front of the person it names. Column Q searches for the empty ones in your own session. Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Capital is a qualifier, not a count. Source: ICON Greater Houston screen, build 48, 2026-09-11.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:Z264"/>
+  <autoFilter ref="A6:Z265"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/ICON_Greater_Houston_Rolodex.xlsx
+++ b/docs/ICON_Greater_Houston_Rolodex.xlsx
@@ -582,7 +582,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated from houston-data.json · build 48 · 2026-09-11 · public render. Do not hand-edit the HTML deck; it regenerates from the same file.</t>
+          <t>Generated from houston-data.json · build 49 · 2026-09-11 · public render. Do not hand-edit the HTML deck; it regenerates from the same file.</t>
         </is>
       </c>
     </row>
@@ -986,11 +986,7 @@
         </is>
       </c>
       <c r="U8" s="12" t="inlineStr"/>
-      <c r="V8" s="15" t="inlineStr">
-        <is>
-          <t>Co-founder.</t>
-        </is>
-      </c>
+      <c r="V8" s="15" t="inlineStr"/>
       <c r="W8" s="12" t="inlineStr">
         <is>
           <t>https://colekleinbuilders.com/about/</t>
@@ -3053,11 +3049,7 @@
         </is>
       </c>
       <c r="U26" s="12" t="inlineStr"/>
-      <c r="V26" s="15" t="inlineStr">
-        <is>
-          <t>Division President, First America Homes. Houston, Texas.</t>
-        </is>
-      </c>
+      <c r="V26" s="15" t="inlineStr"/>
       <c r="W26" s="12" t="inlineStr"/>
       <c r="X26" s="12" t="inlineStr">
         <is>
@@ -3405,7 +3397,7 @@
       </c>
       <c r="V29" s="9" t="inlineStr">
         <is>
-          <t>Indexed title reads Bruce Hendren, Stylecraft. The firm's team page lists him as Vice President of Pre-Construction. Team page lists Bruce Hendren, Vice President of Pre-Construction.</t>
+          <t>Indexed title reads Bruce Hendren, Stylecraft. The firm's team page lists him as Vice President of Pre-Construction.</t>
         </is>
       </c>
       <c r="W29" s="6" t="inlineStr">
@@ -4608,11 +4600,7 @@
         </is>
       </c>
       <c r="U40" s="12" t="inlineStr"/>
-      <c r="V40" s="15" t="inlineStr">
-        <is>
-          <t>Executive Vice President and Chief Operating Officer.</t>
-        </is>
-      </c>
+      <c r="V40" s="15" t="inlineStr"/>
       <c r="W40" s="12" t="inlineStr">
         <is>
           <t>https://suebausa.com/about-us/</t>
@@ -9368,11 +9356,7 @@
         </is>
       </c>
       <c r="U83" s="6" t="inlineStr"/>
-      <c r="V83" s="9" t="inlineStr">
-        <is>
-          <t>Team page: Co-President.</t>
-        </is>
-      </c>
+      <c r="V83" s="9" t="inlineStr"/>
       <c r="W83" s="6" t="inlineStr">
         <is>
           <t>https://jamestownestatehomes.com/team/katy-hawes/</t>
@@ -9476,11 +9460,7 @@
         </is>
       </c>
       <c r="U84" s="12" t="inlineStr"/>
-      <c r="V84" s="15" t="inlineStr">
-        <is>
-          <t>Team page: Co-President.</t>
-        </is>
-      </c>
+      <c r="V84" s="15" t="inlineStr"/>
       <c r="W84" s="12" t="inlineStr">
         <is>
           <t>https://jamestownestatehomes.com/team/matt-norris/</t>
@@ -10459,7 +10439,7 @@
       <c r="U93" s="6" t="inlineStr"/>
       <c r="V93" s="9" t="inlineStr">
         <is>
-          <t>Indexed title reads Matthew Zaist, President and CEO at Risewell Homes. Confirmed on the firm's team page. Executive team page: President and Chief Executive Officer.</t>
+          <t>Indexed title reads Matthew Zaist, President and CEO at Risewell Homes. Confirmed on the firm's team page.</t>
         </is>
       </c>
       <c r="W93" s="6" t="inlineStr">
@@ -11423,11 +11403,7 @@
         </is>
       </c>
       <c r="U102" s="12" t="inlineStr"/>
-      <c r="V102" s="15" t="inlineStr">
-        <is>
-          <t>Managing Member.</t>
-        </is>
-      </c>
+      <c r="V102" s="15" t="inlineStr"/>
       <c r="W102" s="12" t="inlineStr">
         <is>
           <t>https://rskrealestatepartners.com/our-team/</t>
@@ -11659,11 +11635,7 @@
         </is>
       </c>
       <c r="U104" s="12" t="inlineStr"/>
-      <c r="V104" s="15" t="inlineStr">
-        <is>
-          <t>Vice President of Development.</t>
-        </is>
-      </c>
+      <c r="V104" s="15" t="inlineStr"/>
       <c r="W104" s="12" t="inlineStr">
         <is>
           <t>https://rskrealestatepartners.com/our-team/</t>
@@ -18445,11 +18417,7 @@
         </is>
       </c>
       <c r="U168" s="12" t="inlineStr"/>
-      <c r="V168" s="15" t="inlineStr">
-        <is>
-          <t>Managing Principal at Radom Capital.</t>
-        </is>
-      </c>
+      <c r="V168" s="15" t="inlineStr"/>
       <c r="W168" s="12" t="inlineStr"/>
       <c r="X168" s="12" t="inlineStr">
         <is>
@@ -19786,11 +19754,7 @@
         </is>
       </c>
       <c r="U180" s="12" t="inlineStr"/>
-      <c r="V180" s="15" t="inlineStr">
-        <is>
-          <t>Executive Vice President and General Counsel.</t>
-        </is>
-      </c>
+      <c r="V180" s="15" t="inlineStr"/>
       <c r="W180" s="12" t="inlineStr">
         <is>
           <t>https://www.midway.team/our-people</t>
@@ -20020,11 +19984,7 @@
         </is>
       </c>
       <c r="U182" s="12" t="inlineStr"/>
-      <c r="V182" s="15" t="inlineStr">
-        <is>
-          <t>Executive Vice President, Midway. Houston, Texas.</t>
-        </is>
-      </c>
+      <c r="V182" s="15" t="inlineStr"/>
       <c r="W182" s="12" t="inlineStr"/>
       <c r="X182" s="12" t="inlineStr">
         <is>
@@ -20132,11 +20092,7 @@
         </is>
       </c>
       <c r="U183" s="6" t="inlineStr"/>
-      <c r="V183" s="9" t="inlineStr">
-        <is>
-          <t>Team page: Founder and Managing Principal.</t>
-        </is>
-      </c>
+      <c r="V183" s="9" t="inlineStr"/>
       <c r="W183" s="6" t="inlineStr">
         <is>
           <t>https://www.pagewood.com/team</t>
@@ -20243,7 +20199,7 @@
       <c r="U184" s="12" t="inlineStr"/>
       <c r="V184" s="15" t="inlineStr">
         <is>
-          <t>Indexed title reads Mathew Volz, Managing Principal at Pagewood. The firm's team page spells the name Mat. Team page: Managing Principal.</t>
+          <t>Indexed title reads Mathew Volz, Managing Principal at Pagewood. The firm's team page spells the name Mat.</t>
         </is>
       </c>
       <c r="W184" s="12" t="inlineStr">
@@ -20349,11 +20305,7 @@
         </is>
       </c>
       <c r="U185" s="6" t="inlineStr"/>
-      <c r="V185" s="9" t="inlineStr">
-        <is>
-          <t>Team page: Senior Construction Manager.</t>
-        </is>
-      </c>
+      <c r="V185" s="9" t="inlineStr"/>
       <c r="W185" s="6" t="inlineStr">
         <is>
           <t>https://www.pagewood.com/team</t>
@@ -20458,11 +20410,7 @@
         </is>
       </c>
       <c r="U186" s="12" t="inlineStr"/>
-      <c r="V186" s="15" t="inlineStr">
-        <is>
-          <t>Linked from conceptneighborhood.com/team, which lists him as Managing Partner, Projects and Finance. Team page: Managing Partner, Projects and Finance.</t>
-        </is>
-      </c>
+      <c r="V186" s="15" t="inlineStr"/>
       <c r="W186" s="12" t="inlineStr">
         <is>
           <t>https://www.conceptneighborhood.com/team</t>
@@ -20567,11 +20515,7 @@
         </is>
       </c>
       <c r="U187" s="6" t="inlineStr"/>
-      <c r="V187" s="9" t="inlineStr">
-        <is>
-          <t>Linked from conceptneighborhood.com/team, which lists him as Managing Partner, Brokerage and Placemaking. Team page: Managing Partner, Brokerage and Placemaking.</t>
-        </is>
-      </c>
+      <c r="V187" s="9" t="inlineStr"/>
       <c r="W187" s="6" t="inlineStr">
         <is>
           <t>https://www.conceptneighborhood.com/team</t>
@@ -20676,11 +20620,7 @@
         </is>
       </c>
       <c r="U188" s="12" t="inlineStr"/>
-      <c r="V188" s="15" t="inlineStr">
-        <is>
-          <t>Linked from conceptneighborhood.com/team, which lists him as Partner, Design and Placemaking. Team page: Partner, Design and Placemaking.</t>
-        </is>
-      </c>
+      <c r="V188" s="15" t="inlineStr"/>
       <c r="W188" s="12" t="inlineStr">
         <is>
           <t>https://www.conceptneighborhood.com/team</t>
@@ -20785,11 +20725,7 @@
         </is>
       </c>
       <c r="U189" s="6" t="inlineStr"/>
-      <c r="V189" s="9" t="inlineStr">
-        <is>
-          <t>Linked from conceptneighborhood.com/team, which lists him as Managing Partner, Projects and Legal. Team page: Managing Partner, Projects and Legal.</t>
-        </is>
-      </c>
+      <c r="V189" s="9" t="inlineStr"/>
       <c r="W189" s="6" t="inlineStr">
         <is>
           <t>https://www.conceptneighborhood.com/team</t>
@@ -21938,11 +21874,7 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="V199" s="9" t="inlineStr">
-        <is>
-          <t>Vice President of Purchasing, M/I Homes - Houston. Houston, Texas.</t>
-        </is>
-      </c>
+      <c r="V199" s="9" t="inlineStr"/>
       <c r="W199" s="6" t="inlineStr"/>
       <c r="X199" s="6" t="inlineStr">
         <is>
@@ -22279,11 +22211,7 @@
         </is>
       </c>
       <c r="U202" s="12" t="inlineStr"/>
-      <c r="V202" s="15" t="inlineStr">
-        <is>
-          <t>President and Chief Executive Officer.</t>
-        </is>
-      </c>
+      <c r="V202" s="15" t="inlineStr"/>
       <c r="W202" s="12" t="inlineStr">
         <is>
           <t>https://www.ashtonwoods.com/corporate-info</t>
@@ -22511,11 +22439,7 @@
         </is>
       </c>
       <c r="U204" s="12" t="inlineStr"/>
-      <c r="V204" s="15" t="inlineStr">
-        <is>
-          <t>Chief Operating Officer.</t>
-        </is>
-      </c>
+      <c r="V204" s="15" t="inlineStr"/>
       <c r="W204" s="12" t="inlineStr">
         <is>
           <t>https://www.ashtonwoods.com/corporate-info</t>
@@ -23548,11 +23472,7 @@
         </is>
       </c>
       <c r="U213" s="6" t="inlineStr"/>
-      <c r="V213" s="9" t="inlineStr">
-        <is>
-          <t>Chief Executive Officer on Perry's own page.</t>
-        </is>
-      </c>
+      <c r="V213" s="9" t="inlineStr"/>
       <c r="W213" s="6" t="inlineStr">
         <is>
           <t>https://www.perryhomes.com/about-perry-homes</t>
@@ -25174,11 +25094,7 @@
         </is>
       </c>
       <c r="U227" s="6" t="inlineStr"/>
-      <c r="V227" s="9" t="inlineStr">
-        <is>
-          <t>Co-President.</t>
-        </is>
-      </c>
+      <c r="V227" s="9" t="inlineStr"/>
       <c r="W227" s="6" t="inlineStr">
         <is>
           <t>https://landtejas.com/about-us/our-leadership/</t>
@@ -25290,11 +25206,7 @@
         </is>
       </c>
       <c r="U228" s="12" t="inlineStr"/>
-      <c r="V228" s="15" t="inlineStr">
-        <is>
-          <t>Co-President.</t>
-        </is>
-      </c>
+      <c r="V228" s="15" t="inlineStr"/>
       <c r="W228" s="12" t="inlineStr">
         <is>
           <t>https://landtejas.com/about-us/our-leadership/</t>
@@ -25406,11 +25318,7 @@
         </is>
       </c>
       <c r="U229" s="6" t="inlineStr"/>
-      <c r="V229" s="9" t="inlineStr">
-        <is>
-          <t>Chief Executive Officer.</t>
-        </is>
-      </c>
+      <c r="V229" s="9" t="inlineStr"/>
       <c r="W229" s="6" t="inlineStr">
         <is>
           <t>https://caldwellcos.com/our-team</t>
@@ -25522,11 +25430,7 @@
         </is>
       </c>
       <c r="U230" s="12" t="inlineStr"/>
-      <c r="V230" s="15" t="inlineStr">
-        <is>
-          <t>President and Chief Executive Officer.</t>
-        </is>
-      </c>
+      <c r="V230" s="15" t="inlineStr"/>
       <c r="W230" s="12" t="inlineStr">
         <is>
           <t>https://www.johnsondevelopment.com/our-leaders</t>
@@ -25855,11 +25759,7 @@
         </is>
       </c>
       <c r="U233" s="6" t="inlineStr"/>
-      <c r="V233" s="9" t="inlineStr">
-        <is>
-          <t>President.</t>
-        </is>
-      </c>
+      <c r="V233" s="9" t="inlineStr"/>
       <c r="W233" s="6" t="inlineStr">
         <is>
           <t>https://friendswooddevelopment.com/people</t>
@@ -25959,11 +25859,7 @@
         </is>
       </c>
       <c r="U234" s="12" t="inlineStr"/>
-      <c r="V234" s="15" t="inlineStr">
-        <is>
-          <t>Co-Founder and Managing Partner.</t>
-        </is>
-      </c>
+      <c r="V234" s="15" t="inlineStr"/>
       <c r="W234" s="12" t="inlineStr">
         <is>
           <t>https://www.newquest.com/about-us/leadership/</t>
@@ -26063,11 +25959,7 @@
         </is>
       </c>
       <c r="U235" s="6" t="inlineStr"/>
-      <c r="V235" s="9" t="inlineStr">
-        <is>
-          <t>Co-Founder and Managing Partner.</t>
-        </is>
-      </c>
+      <c r="V235" s="9" t="inlineStr"/>
       <c r="W235" s="6" t="inlineStr">
         <is>
           <t>https://www.newquest.com/about-us/leadership/</t>
@@ -26167,11 +26059,7 @@
         </is>
       </c>
       <c r="U236" s="12" t="inlineStr"/>
-      <c r="V236" s="15" t="inlineStr">
-        <is>
-          <t>President and Chief Development Officer.</t>
-        </is>
-      </c>
+      <c r="V236" s="15" t="inlineStr"/>
       <c r="W236" s="12" t="inlineStr">
         <is>
           <t>https://www.newquest.com/about-us/leadership/</t>
@@ -26271,11 +26159,7 @@
         </is>
       </c>
       <c r="U237" s="6" t="inlineStr"/>
-      <c r="V237" s="9" t="inlineStr">
-        <is>
-          <t>Chief Operating Officer and Head of Capital Markets.</t>
-        </is>
-      </c>
+      <c r="V237" s="9" t="inlineStr"/>
       <c r="W237" s="6" t="inlineStr">
         <is>
           <t>https://www.newquest.com/about-us/leadership/</t>
@@ -27391,11 +27275,7 @@
         </is>
       </c>
       <c r="U248" s="12" t="inlineStr"/>
-      <c r="V248" s="15" t="inlineStr">
-        <is>
-          <t>Principal.</t>
-        </is>
-      </c>
+      <c r="V248" s="15" t="inlineStr"/>
       <c r="W248" s="12" t="inlineStr">
         <is>
           <t>https://www.read-king.com/team</t>
@@ -27495,11 +27375,7 @@
         </is>
       </c>
       <c r="U249" s="6" t="inlineStr"/>
-      <c r="V249" s="9" t="inlineStr">
-        <is>
-          <t>Principal.</t>
-        </is>
-      </c>
+      <c r="V249" s="9" t="inlineStr"/>
       <c r="W249" s="6" t="inlineStr">
         <is>
           <t>https://www.read-king.com/team</t>
@@ -27599,11 +27475,7 @@
         </is>
       </c>
       <c r="U250" s="12" t="inlineStr"/>
-      <c r="V250" s="15" t="inlineStr">
-        <is>
-          <t>Chief Financial Officer.</t>
-        </is>
-      </c>
+      <c r="V250" s="15" t="inlineStr"/>
       <c r="W250" s="12" t="inlineStr">
         <is>
           <t>https://www.read-king.com/team</t>
@@ -28530,11 +28402,7 @@
         </is>
       </c>
       <c r="U259" s="6" t="inlineStr"/>
-      <c r="V259" s="9" t="inlineStr">
-        <is>
-          <t>Managing Partner of Development and Design.</t>
-        </is>
-      </c>
+      <c r="V259" s="9" t="inlineStr"/>
       <c r="W259" s="6" t="inlineStr">
         <is>
           <t>https://www.dinersteincos.com/about-us</t>
@@ -28634,11 +28502,7 @@
         </is>
       </c>
       <c r="U260" s="12" t="inlineStr"/>
-      <c r="V260" s="15" t="inlineStr">
-        <is>
-          <t>President and Partner.</t>
-        </is>
-      </c>
+      <c r="V260" s="15" t="inlineStr"/>
       <c r="W260" s="12" t="inlineStr">
         <is>
           <t>https://www.dinersteincos.com/about-us</t>
@@ -29142,11 +29006,7 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="V265" s="9" t="inlineStr">
-        <is>
-          <t>Director of Construction.</t>
-        </is>
-      </c>
+      <c r="V265" s="9" t="inlineStr"/>
       <c r="W265" s="6" t="inlineStr">
         <is>
           <t>https://www.wulfe.com/people</t>
@@ -29167,7 +29027,7 @@
     <row r="267">
       <c r="A267" s="17" t="inlineStr">
         <is>
-          <t>NOTE. A filled LinkedIn cell means the profile was opened or the search result read and the headline named the firm; column W records what was read. Where that test failed the cell is left empty rather than guessed, because a fabricated slug passes visual inspection and then fails in front of the person it names. Column Q searches for the empty ones in your own session. Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Capital is a qualifier, not a count. Source: ICON Greater Houston screen, build 48, 2026-09-11.</t>
+          <t>NOTE. A filled LinkedIn cell means the profile was opened or the search result read and the headline named the firm; column W records what was read. Where that test failed the cell is left empty rather than guessed, because a fabricated slug passes visual inspection and then fails in front of the person it names. Column Q searches for the empty ones in your own session. Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Capital is a qualifier, not a count. Source: ICON Greater Houston screen, build 49, 2026-09-11.</t>
         </is>
       </c>
     </row>

--- a/docs/ICON_Greater_Houston_Rolodex.xlsx
+++ b/docs/ICON_Greater_Houston_Rolodex.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Permits" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Contacts'!$A$6:$Z$283</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Contacts'!$A$6:$Z$282</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z285"/>
+  <dimension ref="A1:Z284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>COUNTA($A$7:$A$283)</f>
+        <f>COUNTA($A$7:$A$282)</f>
         <v/>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="D3" s="3">
-        <f>COUNTIF($R$7:$R$283,"ok")</f>
+        <f>COUNTIF($R$7:$R$282,"ok")</f>
         <v/>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="F3" s="3">
-        <f>COUNTIF($R$7:$R$283,"ADD LINKEDIN")</f>
+        <f>COUNTIF($R$7:$R$282,"ADD LINKEDIN")</f>
         <v/>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="H3" s="3">
-        <f>SUMPRODUCT((COUNTIF(OFFSET($B$7,ROW($B$7:$B$283)-ROW($B$7),0,1,1),$B$7:$B$283)&gt;0)*($D$7:$D$283="Strong target")/COUNTIF($B$7:$B$283,$B$7:$B$283&amp;""))</f>
+        <f>SUMPRODUCT((COUNTIF(OFFSET($B$7,ROW($B$7:$B$282)-ROW($B$7),0,1,1),$B$7:$B$282)&gt;0)*($D$7:$D$282="Strong target")/COUNTIF($B$7:$B$282,$B$7:$B$282&amp;""))</f>
         <v/>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="J3" s="3">
-        <f>COUNTIF($V$7:$V$283,"YES")</f>
+        <f>COUNTIF($V$7:$V$282,"YES")</f>
         <v/>
       </c>
     </row>
@@ -9555,7 +9555,7 @@
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>Director, Imagination Homes; Division President, David Weekley Homes</t>
+          <t>Director, Imagination Homes</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
@@ -18546,7 +18546,7 @@
     <row r="172">
       <c r="A172" s="12" t="inlineStr">
         <is>
-          <t>Joshua Cantu</t>
+          <t>Cullen Burton</t>
         </is>
       </c>
       <c r="B172" s="12" t="inlineStr">
@@ -18556,7 +18556,7 @@
       </c>
       <c r="C172" s="12" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D172" s="13" t="inlineStr">
@@ -18618,10 +18618,7 @@
         </is>
       </c>
       <c r="P172" s="10" t="inlineStr"/>
-      <c r="Q172" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Joshua%20Cantu%20Burton%20Construction","search")</f>
-        <v/>
-      </c>
+      <c r="Q172" s="12" t="inlineStr"/>
       <c r="R172" s="16">
         <f>IF(P172="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -18636,13 +18633,17 @@
           <t>Twenty-two years old, a tilt-up award in 2024 and multifamily in the published portfolio. The founder is on the firm's own page; the chief executive is not.</t>
         </is>
       </c>
-      <c r="U172" s="12" t="inlineStr"/>
-      <c r="V172" s="15" t="inlineStr">
-        <is>
-          <t>Headline reads Director at Burton Construction. Houston, Texas.</t>
-        </is>
-      </c>
-      <c r="W172" s="12" t="inlineStr"/>
+      <c r="U172" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="V172" s="15" t="inlineStr"/>
+      <c r="W172" s="12" t="inlineStr">
+        <is>
+          <t>https://burtonconstruction.com/leadership/</t>
+        </is>
+      </c>
       <c r="X172" s="12" t="inlineStr"/>
       <c r="Y172" s="12" t="inlineStr"/>
       <c r="Z172" s="12" t="inlineStr"/>
@@ -18650,17 +18651,17 @@
     <row r="173">
       <c r="A173" s="6" t="inlineStr">
         <is>
-          <t>Cullen Burton</t>
+          <t>J. Cameron Guinn</t>
         </is>
       </c>
       <c r="B173" s="6" t="inlineStr">
         <is>
-          <t>Burton Construction</t>
+          <t>HTX Concrete</t>
         </is>
       </c>
       <c r="C173" s="6" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Vice President, Business Development</t>
         </is>
       </c>
       <c r="D173" s="7" t="inlineStr">
@@ -18678,12 +18679,12 @@
       </c>
       <c r="G173" s="6" t="inlineStr">
         <is>
-          <t>Houston, with Austin, San Antonio and Phoenix</t>
+          <t>Houston, working Harris, Fort Bend and Brazoria</t>
         </is>
       </c>
       <c r="H173" s="6" t="inlineStr">
         <is>
-          <t>Founded 2004, with multifamily in its published portfolio</t>
+          <t>Names a garden-style multifamily project on its own site</t>
         </is>
       </c>
       <c r="I173" s="8" t="inlineStr">
@@ -18693,7 +18694,7 @@
       </c>
       <c r="J173" s="9" t="inlineStr">
         <is>
-          <t>Commercial and multifamily work across four metros. The buildings differ project to project.</t>
+          <t>Commercial shells and paving across the metro. The published square footages are weighted to paving rather than to wall.</t>
         </is>
       </c>
       <c r="K173" s="8" t="inlineStr">
@@ -18703,7 +18704,7 @@
       </c>
       <c r="L173" s="9" t="inlineStr">
         <is>
-          <t>No revenue, crew count or project size is published. On the bands, a firm with no published figure is a Partly.</t>
+          <t>No annual volume is published. The one published wall figure is 12,000 square feet of tilt wall against 155,000 gross square feet of paving on the same job.</t>
         </is>
       </c>
       <c r="M173" s="8" t="inlineStr">
@@ -18713,7 +18714,7 @@
       </c>
       <c r="N173" s="9" t="inlineStr">
         <is>
-          <t>No method statement on record. The tilt-up award is for execution.</t>
+          <t>No method statement on record.</t>
         </is>
       </c>
       <c r="O173" s="8" t="inlineStr">
@@ -18721,7 +18722,11 @@
           <t>Partly</t>
         </is>
       </c>
-      <c r="P173" s="10" t="inlineStr"/>
+      <c r="P173" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/j-cameron-guinn-2047686/</t>
+        </is>
+      </c>
       <c r="Q173" s="6" t="inlineStr"/>
       <c r="R173" s="11">
         <f>IF(P173="","ADD LINKEDIN","ok")</f>
@@ -18729,25 +18734,21 @@
       </c>
       <c r="S173" s="6" t="inlineStr">
         <is>
-          <t>https://burtonconstruction.com/</t>
+          <t>https://htxconcrete.com/</t>
         </is>
       </c>
       <c r="T173" s="9" t="inlineStr">
         <is>
-          <t>Twenty-two years old, a tilt-up award in 2024 and multifamily in the published portfolio. The founder is on the firm's own page; the chief executive is not.</t>
-        </is>
-      </c>
-      <c r="U173" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="V173" s="9" t="inlineStr"/>
-      <c r="W173" s="6" t="inlineStr">
-        <is>
-          <t>https://burtonconstruction.com/leadership/</t>
-        </is>
-      </c>
+          <t>One of two contractors screened that names an actual multifamily project on its own site. The published work is paving-heavy.</t>
+        </is>
+      </c>
+      <c r="U173" s="6" t="inlineStr"/>
+      <c r="V173" s="9" t="inlineStr">
+        <is>
+          <t>Headline reads Vice President Business Development at HTX Concrete. Houston, Texas.</t>
+        </is>
+      </c>
+      <c r="W173" s="6" t="inlineStr"/>
       <c r="X173" s="6" t="inlineStr"/>
       <c r="Y173" s="6" t="inlineStr"/>
       <c r="Z173" s="6" t="inlineStr"/>
@@ -18755,7 +18756,7 @@
     <row r="174">
       <c r="A174" s="12" t="inlineStr">
         <is>
-          <t>J. Cameron Guinn</t>
+          <t>Tony Le</t>
         </is>
       </c>
       <c r="B174" s="12" t="inlineStr">
@@ -18765,7 +18766,7 @@
       </c>
       <c r="C174" s="12" t="inlineStr">
         <is>
-          <t>Vice President, Business Development</t>
+          <t>Chief Estimator</t>
         </is>
       </c>
       <c r="D174" s="13" t="inlineStr">
@@ -18828,7 +18829,7 @@
       </c>
       <c r="P174" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/j-cameron-guinn-2047686/</t>
+          <t>https://www.linkedin.com/in/tony-le-81ba0032/</t>
         </is>
       </c>
       <c r="Q174" s="12" t="inlineStr"/>
@@ -18849,7 +18850,7 @@
       <c r="U174" s="12" t="inlineStr"/>
       <c r="V174" s="15" t="inlineStr">
         <is>
-          <t>Headline reads Vice President Business Development at HTX Concrete. Houston, Texas.</t>
+          <t>Headline reads Chief Estimator at HTX Concrete. Houston, Texas.</t>
         </is>
       </c>
       <c r="W174" s="12" t="inlineStr"/>
@@ -18860,17 +18861,17 @@
     <row r="175">
       <c r="A175" s="6" t="inlineStr">
         <is>
-          <t>Tony Le</t>
+          <t>Trent Mitchell</t>
         </is>
       </c>
       <c r="B175" s="6" t="inlineStr">
         <is>
-          <t>HTX Concrete</t>
+          <t>Silver Spur Concrete Contractors</t>
         </is>
       </c>
       <c r="C175" s="6" t="inlineStr">
         <is>
-          <t>Chief Estimator</t>
+          <t>Owner, named on the firm's own about page, after eighteen years selling ready-mix to the largest general contractors in Houston</t>
         </is>
       </c>
       <c r="D175" s="7" t="inlineStr">
@@ -18888,12 +18889,12 @@
       </c>
       <c r="G175" s="6" t="inlineStr">
         <is>
-          <t>Houston, working Harris, Fort Bend and Brazoria</t>
+          <t>Tomball and north Houston, Harris and Montgomery</t>
         </is>
       </c>
       <c r="H175" s="6" t="inlineStr">
         <is>
-          <t>Names a garden-style multifamily project on its own site</t>
+          <t>Publishes a custom residential concrete line</t>
         </is>
       </c>
       <c r="I175" s="8" t="inlineStr">
@@ -18903,7 +18904,7 @@
       </c>
       <c r="J175" s="9" t="inlineStr">
         <is>
-          <t>Commercial shells and paving across the metro. The published square footages are weighted to paving rather than to wall.</t>
+          <t>Commercial concrete and metal buildings recurring across the north side of the metro.</t>
         </is>
       </c>
       <c r="K175" s="8" t="inlineStr">
@@ -18913,7 +18914,7 @@
       </c>
       <c r="L175" s="9" t="inlineStr">
         <is>
-          <t>No annual volume is published. The one published wall figure is 12,000 square feet of tilt wall against 155,000 gross square feet of paving on the same job.</t>
+          <t>No crew count, revenue or project size is published anywhere on the site. On the bands, a firm with no published figure is a Partly.</t>
         </is>
       </c>
       <c r="M175" s="8" t="inlineStr">
@@ -18931,32 +18932,31 @@
           <t>Partly</t>
         </is>
       </c>
-      <c r="P175" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/tony-le-81ba0032/</t>
-        </is>
-      </c>
-      <c r="Q175" s="6" t="inlineStr"/>
+      <c r="P175" s="10" t="inlineStr"/>
+      <c r="Q175" s="6">
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Trent%20Mitchell%20Silver%20Spur%20Concrete%20Contractors","search")</f>
+        <v/>
+      </c>
       <c r="R175" s="11">
         <f>IF(P175="","ADD LINKEDIN","ok")</f>
         <v/>
       </c>
       <c r="S175" s="6" t="inlineStr">
         <is>
-          <t>https://htxconcrete.com/</t>
+          <t>https://silverspurconcrete.com/</t>
         </is>
       </c>
       <c r="T175" s="9" t="inlineStr">
         <is>
-          <t>One of two contractors screened that names an actual multifamily project on its own site. The published work is paving-heavy.</t>
-        </is>
-      </c>
-      <c r="U175" s="6" t="inlineStr"/>
-      <c r="V175" s="9" t="inlineStr">
-        <is>
-          <t>Headline reads Chief Estimator at HTX Concrete. Houston, Texas.</t>
-        </is>
-      </c>
+          <t>The only contractor screened that pairs tilt-wall with a published residential concrete line, including engineered slabs.</t>
+        </is>
+      </c>
+      <c r="U175" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="V175" s="9" t="inlineStr"/>
       <c r="W175" s="6" t="inlineStr"/>
       <c r="X175" s="6" t="inlineStr"/>
       <c r="Y175" s="6" t="inlineStr"/>
@@ -18965,50 +18965,50 @@
     <row r="176">
       <c r="A176" s="12" t="inlineStr">
         <is>
-          <t>Trent Mitchell</t>
+          <t>Scott Arnoldy</t>
         </is>
       </c>
       <c r="B176" s="12" t="inlineStr">
         <is>
-          <t>Silver Spur Concrete Contractors</t>
+          <t>Triten Real Estate Partners</t>
         </is>
       </c>
       <c r="C176" s="12" t="inlineStr">
         <is>
-          <t>Owner, named on the firm's own about page, after eighteen years selling ready-mix to the largest general contractors in Houston</t>
+          <t>Chief Executive Officer, Founder</t>
         </is>
       </c>
       <c r="D176" s="13" t="inlineStr">
         <is>
-          <t>Builds the wall, not the house</t>
+          <t>Creative project, hybrid job</t>
         </is>
       </c>
       <c r="E176" s="14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F176" s="12" t="inlineStr">
         <is>
-          <t>Builds the wall</t>
+          <t>Buys walls</t>
         </is>
       </c>
       <c r="G176" s="12" t="inlineStr">
         <is>
-          <t>Tomball and north Houston, Harris and Montgomery</t>
+          <t>East End / Fort Bend, Harris County</t>
         </is>
       </c>
       <c r="H176" s="12" t="inlineStr">
         <is>
-          <t>Publishes a custom residential concrete line</t>
+          <t>341 units at The Mill, 294 more under construction at Aliana</t>
         </is>
       </c>
       <c r="I176" s="14" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J176" s="15" t="inlineStr">
         <is>
-          <t>Commercial concrete and metal buildings recurring across the north side of the metro.</t>
+          <t>341 units at The Mill, 294 more under construction at Aliana.</t>
         </is>
       </c>
       <c r="K176" s="14" t="inlineStr">
@@ -19018,17 +19018,17 @@
       </c>
       <c r="L176" s="15" t="inlineStr">
         <is>
-          <t>No crew count, revenue or project size is published anywhere on the site. On the bands, a firm with no published figure is a Partly.</t>
+          <t>The Landing at Aliana is 294 units of three-storey garden-style housing on one Fort Bend site. That is the repeating low-rise the band covers.</t>
         </is>
       </c>
       <c r="M176" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partly</t>
         </is>
       </c>
       <c r="N176" s="15" t="inlineStr">
         <is>
-          <t>No method statement on record.</t>
+          <t>It expected to use cross-laminated timber on a six-storey office building at The Mill in 2021, contingent on retail leasing. The building is not in its own portfolio entry and no source shows it was built.</t>
         </is>
       </c>
       <c r="O176" s="14" t="inlineStr">
@@ -19036,40 +19036,49 @@
           <t>Partly</t>
         </is>
       </c>
-      <c r="P176" s="10" t="inlineStr"/>
-      <c r="Q176" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Trent%20Mitchell%20Silver%20Spur%20Concrete%20Contractors","search")</f>
-        <v/>
-      </c>
+      <c r="P176" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/scottarnoldy/</t>
+        </is>
+      </c>
+      <c r="Q176" s="12" t="inlineStr"/>
       <c r="R176" s="16">
         <f>IF(P176="","ADD LINKEDIN","ok")</f>
         <v/>
       </c>
       <c r="S176" s="12" t="inlineStr">
         <is>
-          <t>https://silverspurconcrete.com/</t>
+          <t>https://www.tritenre.com/</t>
         </is>
       </c>
       <c r="T176" s="15" t="inlineStr">
         <is>
-          <t>The only contractor screened that pairs tilt-wall with a published residential concrete line, including engineered slabs.</t>
-        </is>
-      </c>
-      <c r="U176" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="V176" s="15" t="inlineStr"/>
+          <t>Financed a cross-laminated timber frame at The Mill. 294 units at Aliana land in Titan's first delivery window.</t>
+        </is>
+      </c>
+      <c r="U176" s="12" t="inlineStr"/>
+      <c r="V176" s="15" t="inlineStr">
+        <is>
+          <t>Founder and CEO, Triten Real Estate Partners. Houston, Texas.</t>
+        </is>
+      </c>
       <c r="W176" s="12" t="inlineStr"/>
-      <c r="X176" s="12" t="inlineStr"/>
-      <c r="Y176" s="12" t="inlineStr"/>
+      <c r="X176" s="12" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/triten-real-estate-partners</t>
+        </is>
+      </c>
+      <c r="Y176" s="12" t="inlineStr">
+        <is>
+          <t>https://www.tritenre.com/team</t>
+        </is>
+      </c>
       <c r="Z176" s="12" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="6" t="inlineStr">
         <is>
-          <t>Scott Arnoldy</t>
+          <t>Larry Sloan</t>
         </is>
       </c>
       <c r="B177" s="6" t="inlineStr">
@@ -19079,7 +19088,7 @@
       </c>
       <c r="C177" s="6" t="inlineStr">
         <is>
-          <t>Chief Executive Officer, Founder</t>
+          <t>Partner, Chief Development Officer</t>
         </is>
       </c>
       <c r="D177" s="7" t="inlineStr">
@@ -19142,7 +19151,7 @@
       </c>
       <c r="P177" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/scottarnoldy/</t>
+          <t>https://www.linkedin.com/in/larry-sloan-894204b/</t>
         </is>
       </c>
       <c r="Q177" s="6" t="inlineStr"/>
@@ -19163,7 +19172,7 @@
       <c r="U177" s="6" t="inlineStr"/>
       <c r="V177" s="9" t="inlineStr">
         <is>
-          <t>Founder and CEO, Triten Real Estate Partners. Houston, Texas.</t>
+          <t>Chief Development Officer (CDO) at Triten Real Estate Partners. Houston, Texas. The same person who left Midway as EVP of investment and development in November 2023.</t>
         </is>
       </c>
       <c r="W177" s="6" t="inlineStr"/>
@@ -19182,7 +19191,7 @@
     <row r="178">
       <c r="A178" s="12" t="inlineStr">
         <is>
-          <t>Larry Sloan</t>
+          <t>Brent Ozenbaugh</t>
         </is>
       </c>
       <c r="B178" s="12" t="inlineStr">
@@ -19192,7 +19201,7 @@
       </c>
       <c r="C178" s="12" t="inlineStr">
         <is>
-          <t>Partner, Chief Development Officer</t>
+          <t>Partner, Chief Operating Officer</t>
         </is>
       </c>
       <c r="D178" s="13" t="inlineStr">
@@ -19255,7 +19264,7 @@
       </c>
       <c r="P178" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/larry-sloan-894204b/</t>
+          <t>https://www.linkedin.com/in/brent-ozenbaugh-b99872/</t>
         </is>
       </c>
       <c r="Q178" s="12" t="inlineStr"/>
@@ -19276,7 +19285,7 @@
       <c r="U178" s="12" t="inlineStr"/>
       <c r="V178" s="15" t="inlineStr">
         <is>
-          <t>Chief Development Officer (CDO) at Triten Real Estate Partners. Houston, Texas. The same person who left Midway as EVP of investment and development in November 2023.</t>
+          <t>COO at Triten Real Estate Partners. Greater Houston.</t>
         </is>
       </c>
       <c r="W178" s="12" t="inlineStr"/>
@@ -19295,7 +19304,7 @@
     <row r="179">
       <c r="A179" s="6" t="inlineStr">
         <is>
-          <t>Brent Ozenbaugh</t>
+          <t>Carter Bechtol</t>
         </is>
       </c>
       <c r="B179" s="6" t="inlineStr">
@@ -19305,7 +19314,7 @@
       </c>
       <c r="C179" s="6" t="inlineStr">
         <is>
-          <t>Partner, Chief Operating Officer</t>
+          <t>Partner, Head of Triten Residential</t>
         </is>
       </c>
       <c r="D179" s="7" t="inlineStr">
@@ -19366,12 +19375,11 @@
           <t>Partly</t>
         </is>
       </c>
-      <c r="P179" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/brent-ozenbaugh-b99872/</t>
-        </is>
-      </c>
-      <c r="Q179" s="6" t="inlineStr"/>
+      <c r="P179" s="10" t="inlineStr"/>
+      <c r="Q179" s="6">
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Carter%20Bechtol%20Triten%20Real%20Estate%20Partners","search")</f>
+        <v/>
+      </c>
       <c r="R179" s="11">
         <f>IF(P179="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -19389,10 +19397,14 @@
       <c r="U179" s="6" t="inlineStr"/>
       <c r="V179" s="9" t="inlineStr">
         <is>
-          <t>COO at Triten Real Estate Partners. Greater Houston.</t>
-        </is>
-      </c>
-      <c r="W179" s="6" t="inlineStr"/>
+          <t>Triten's own bio page. Partner, Head of Triten Residential. The residential platform is the part of Triten that would buy a repeated wall.</t>
+        </is>
+      </c>
+      <c r="W179" s="6" t="inlineStr">
+        <is>
+          <t>https://www.tritenre.com/team/carter-becthol</t>
+        </is>
+      </c>
       <c r="X179" s="6" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/triten-real-estate-partners</t>
@@ -19408,17 +19420,17 @@
     <row r="180">
       <c r="A180" s="12" t="inlineStr">
         <is>
-          <t>Carter Bechtol</t>
+          <t>Steve Radom</t>
         </is>
       </c>
       <c r="B180" s="12" t="inlineStr">
         <is>
-          <t>Triten Real Estate Partners</t>
+          <t>Radom Capital</t>
         </is>
       </c>
       <c r="C180" s="12" t="inlineStr">
         <is>
-          <t>Partner, Head of Triten Residential</t>
+          <t>Managing Principal</t>
         </is>
       </c>
       <c r="D180" s="13" t="inlineStr">
@@ -19427,7 +19439,7 @@
         </is>
       </c>
       <c r="E180" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F180" s="12" t="inlineStr">
         <is>
@@ -19436,87 +19448,80 @@
       </c>
       <c r="G180" s="12" t="inlineStr">
         <is>
-          <t>East End / Fort Bend, Harris County</t>
+          <t>Heights / Montrose, Harris County</t>
         </is>
       </c>
       <c r="H180" s="12" t="inlineStr">
         <is>
-          <t>341 units at The Mill, 294 more under construction at Aliana</t>
+          <t>$104.75M Montrose Collective financing</t>
         </is>
       </c>
       <c r="I180" s="14" t="inlineStr">
         <is>
+          <t>Partly</t>
+        </is>
+      </c>
+      <c r="J180" s="15" t="inlineStr">
+        <is>
+          <t>Fifteen projects in one district, 218 units at Clock Tower.</t>
+        </is>
+      </c>
+      <c r="K180" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L180" s="15" t="inlineStr">
+        <is>
+          <t>Adaptive reuse and retail. Every project is its own building.</t>
+        </is>
+      </c>
+      <c r="M180" s="14" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="J180" s="15" t="inlineStr">
-        <is>
-          <t>341 units at The Mill, 294 more under construction at Aliana.</t>
-        </is>
-      </c>
-      <c r="K180" s="14" t="inlineStr">
-        <is>
-          <t>Partly</t>
-        </is>
-      </c>
-      <c r="L180" s="15" t="inlineStr">
-        <is>
-          <t>The Landing at Aliana is 294 units of three-storey garden-style housing on one Fort Bend site. That is the repeating low-rise the band covers.</t>
-        </is>
-      </c>
-      <c r="M180" s="14" t="inlineStr">
-        <is>
-          <t>Partly</t>
-        </is>
-      </c>
       <c r="N180" s="15" t="inlineStr">
         <is>
-          <t>It expected to use cross-laminated timber on a six-storey office building at The Mill in 2021, contingent on retail leasing. The building is not in its own portfolio entry and no source shows it was built.</t>
+          <t>Commissioned Michael Hsu for Montrose Collective, four-street frontage, $104.75M financed.</t>
         </is>
       </c>
       <c r="O180" s="14" t="inlineStr">
         <is>
-          <t>Partly</t>
-        </is>
-      </c>
-      <c r="P180" s="10" t="inlineStr"/>
-      <c r="Q180" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Carter%20Bechtol%20Triten%20Real%20Estate%20Partners","search")</f>
-        <v/>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P180" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/steveradom/</t>
+        </is>
+      </c>
+      <c r="Q180" s="12" t="inlineStr"/>
       <c r="R180" s="16">
         <f>IF(P180="","ADD LINKEDIN","ok")</f>
         <v/>
       </c>
       <c r="S180" s="12" t="inlineStr">
         <is>
-          <t>https://www.tritenre.com/</t>
+          <t>https://www.radomcapital.com/</t>
         </is>
       </c>
       <c r="T180" s="15" t="inlineStr">
         <is>
-          <t>Financed a cross-laminated timber frame at The Mill. 294 units at Aliana land in Titan's first delivery window.</t>
+          <t>Michael Hsu at Montrose Collective, $104.75M financed. Fifteen projects in one district, so volume is concentrated rather than deep.</t>
         </is>
       </c>
       <c r="U180" s="12" t="inlineStr"/>
-      <c r="V180" s="15" t="inlineStr">
-        <is>
-          <t>Triten's own bio page. Partner, Head of Triten Residential. The residential platform is the part of Triten that would buy a repeated wall.</t>
-        </is>
-      </c>
-      <c r="W180" s="12" t="inlineStr">
-        <is>
-          <t>https://www.tritenre.com/team/carter-becthol</t>
-        </is>
-      </c>
+      <c r="V180" s="15" t="inlineStr"/>
+      <c r="W180" s="12" t="inlineStr"/>
       <c r="X180" s="12" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/triten-real-estate-partners</t>
+          <t>https://www.linkedin.com/company/radom-capital-llc</t>
         </is>
       </c>
       <c r="Y180" s="12" t="inlineStr">
         <is>
-          <t>https://www.tritenre.com/team</t>
+          <t>https://www.radomcapital.com/team</t>
         </is>
       </c>
       <c r="Z180" s="12" t="inlineStr"/>
@@ -19524,7 +19529,7 @@
     <row r="181">
       <c r="A181" s="6" t="inlineStr">
         <is>
-          <t>Steve Radom</t>
+          <t>Barton Kelly</t>
         </is>
       </c>
       <c r="B181" s="6" t="inlineStr">
@@ -19534,7 +19539,7 @@
       </c>
       <c r="C181" s="6" t="inlineStr">
         <is>
-          <t>Managing Principal</t>
+          <t>Principal</t>
         </is>
       </c>
       <c r="D181" s="7" t="inlineStr">
@@ -19597,7 +19602,7 @@
       </c>
       <c r="P181" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/steveradom/</t>
+          <t>https://www.linkedin.com/in/bartonk/</t>
         </is>
       </c>
       <c r="Q181" s="6" t="inlineStr"/>
@@ -19616,7 +19621,11 @@
         </is>
       </c>
       <c r="U181" s="6" t="inlineStr"/>
-      <c r="V181" s="9" t="inlineStr"/>
+      <c r="V181" s="9" t="inlineStr">
+        <is>
+          <t>Vice President at Radom Capital LLC, Houston. Barton Kelly's LinkedIn headline reads Vice President at Radom Capital; the firm's own team page lists him as Principal. The titles conflict.</t>
+        </is>
+      </c>
       <c r="W181" s="6" t="inlineStr"/>
       <c r="X181" s="6" t="inlineStr">
         <is>
@@ -19633,7 +19642,7 @@
     <row r="182">
       <c r="A182" s="12" t="inlineStr">
         <is>
-          <t>Barton Kelly</t>
+          <t>Evan Peterson</t>
         </is>
       </c>
       <c r="B182" s="12" t="inlineStr">
@@ -19706,7 +19715,7 @@
       </c>
       <c r="P182" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/bartonk/</t>
+          <t>https://www.linkedin.com/in/evan-peterson-19656548/</t>
         </is>
       </c>
       <c r="Q182" s="12" t="inlineStr"/>
@@ -19727,7 +19736,7 @@
       <c r="U182" s="12" t="inlineStr"/>
       <c r="V182" s="15" t="inlineStr">
         <is>
-          <t>Vice President at Radom Capital LLC, Houston. Barton Kelly's LinkedIn headline reads Vice President at Radom Capital; the firm's own team page lists him as Principal. The titles conflict.</t>
+          <t>Principal at Radom Capital LLC. Houston, Texas.</t>
         </is>
       </c>
       <c r="W182" s="12" t="inlineStr"/>
@@ -19746,17 +19755,17 @@
     <row r="183">
       <c r="A183" s="6" t="inlineStr">
         <is>
-          <t>Evan Peterson</t>
+          <t>Jon Deal</t>
         </is>
       </c>
       <c r="B183" s="6" t="inlineStr">
         <is>
-          <t>Radom Capital</t>
+          <t>The Deal Company (Sawyer Yards)</t>
         </is>
       </c>
       <c r="C183" s="6" t="inlineStr">
         <is>
-          <t>Principal</t>
+          <t>Founder and Chief Executive Officer</t>
         </is>
       </c>
       <c r="D183" s="7" t="inlineStr">
@@ -19774,12 +19783,12 @@
       </c>
       <c r="G183" s="6" t="inlineStr">
         <is>
-          <t>Heights / Montrose, Harris County</t>
+          <t>Washington Corridor, Harris County</t>
         </is>
       </c>
       <c r="H183" s="6" t="inlineStr">
         <is>
-          <t>$104.75M Montrose Collective financing</t>
+          <t>55 acres, 27 buildings, 2M+ sf</t>
         </is>
       </c>
       <c r="I183" s="8" t="inlineStr">
@@ -19789,7 +19798,7 @@
       </c>
       <c r="J183" s="9" t="inlineStr">
         <is>
-          <t>Fifteen projects in one district, 218 units at Clock Tower.</t>
+          <t>27 buildings across 55 acres since 2005.</t>
         </is>
       </c>
       <c r="K183" s="8" t="inlineStr">
@@ -19799,7 +19808,7 @@
       </c>
       <c r="L183" s="9" t="inlineStr">
         <is>
-          <t>Adaptive reuse and retail. Every project is its own building.</t>
+          <t>Converting industrial buildings leaves almost no new wall to print.</t>
         </is>
       </c>
       <c r="M183" s="8" t="inlineStr">
@@ -19809,49 +19818,48 @@
       </c>
       <c r="N183" s="9" t="inlineStr">
         <is>
-          <t>Commissioned Michael Hsu for Montrose Collective, four-street frontage, $104.75M financed.</t>
+          <t>Twenty years of building inside awkward industrial structures.</t>
         </is>
       </c>
       <c r="O183" s="8" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P183" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/evan-peterson-19656548/</t>
-        </is>
-      </c>
-      <c r="Q183" s="6" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P183" s="10" t="inlineStr"/>
+      <c r="Q183" s="6">
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Jon%20Deal%20The%20Deal%20Company","search")</f>
+        <v/>
+      </c>
       <c r="R183" s="11">
         <f>IF(P183="","ADD LINKEDIN","ok")</f>
         <v/>
       </c>
       <c r="S183" s="6" t="inlineStr">
         <is>
-          <t>https://www.radomcapital.com/</t>
+          <t>https://www.dealco.net/</t>
         </is>
       </c>
       <c r="T183" s="9" t="inlineStr">
         <is>
-          <t>Michael Hsu at Montrose Collective, $104.75M financed. Fifteen projects in one district, so volume is concentrated rather than deep.</t>
+          <t>Twenty years converting industrial buildings, 27 of them. Adaptive reuse leaves little new wall to print.</t>
         </is>
       </c>
       <c r="U183" s="6" t="inlineStr"/>
       <c r="V183" s="9" t="inlineStr">
         <is>
-          <t>Principal at Radom Capital LLC. Houston, Texas.</t>
-        </is>
-      </c>
-      <c r="W183" s="6" t="inlineStr"/>
-      <c r="X183" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/radom-capital-llc</t>
-        </is>
-      </c>
+          <t>Founder and Chief Executive Officer, and co-developer of Sawyer Yards.</t>
+        </is>
+      </c>
+      <c r="W183" s="6" t="inlineStr">
+        <is>
+          <t>https://www.dealco.net/about/</t>
+        </is>
+      </c>
+      <c r="X183" s="6" t="inlineStr"/>
       <c r="Y183" s="6" t="inlineStr">
         <is>
-          <t>https://www.radomcapital.com/team</t>
+          <t>https://www.dealco.net/about/</t>
         </is>
       </c>
       <c r="Z183" s="6" t="inlineStr"/>
@@ -19859,17 +19867,17 @@
     <row r="184">
       <c r="A184" s="12" t="inlineStr">
         <is>
-          <t>Jon Deal</t>
+          <t>Dougal A. Cameron</t>
         </is>
       </c>
       <c r="B184" s="12" t="inlineStr">
         <is>
-          <t>The Deal Company (Sawyer Yards)</t>
+          <t>Cameron Management</t>
         </is>
       </c>
       <c r="C184" s="12" t="inlineStr">
         <is>
-          <t>Founder and Chief Executive Officer</t>
+          <t>President and Owner</t>
         </is>
       </c>
       <c r="D184" s="13" t="inlineStr">
@@ -19878,7 +19886,7 @@
         </is>
       </c>
       <c r="E184" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F184" s="12" t="inlineStr">
         <is>
@@ -19887,22 +19895,22 @@
       </c>
       <c r="G184" s="12" t="inlineStr">
         <is>
-          <t>Washington Corridor, Harris County</t>
+          <t>Downtown Houston, Harris County</t>
         </is>
       </c>
       <c r="H184" s="12" t="inlineStr">
         <is>
-          <t>55 acres, 27 buildings, 2M+ sf</t>
+          <t>$50M conversion, up to 100 units</t>
         </is>
       </c>
       <c r="I184" s="14" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J184" s="15" t="inlineStr">
         <is>
-          <t>27 buildings across 55 acres since 2005.</t>
+          <t>Two towers, one conversion each. Nothing repeats.</t>
         </is>
       </c>
       <c r="K184" s="14" t="inlineStr">
@@ -19912,7 +19920,7 @@
       </c>
       <c r="L184" s="15" t="inlineStr">
         <is>
-          <t>Converting industrial buildings leaves almost no new wall to print.</t>
+          <t>Converting two 1927 and 1941 office towers to residential. No new exterior wall.</t>
         </is>
       </c>
       <c r="M184" s="14" t="inlineStr">
@@ -19922,17 +19930,17 @@
       </c>
       <c r="N184" s="15" t="inlineStr">
         <is>
-          <t>Twenty years of building inside awkward industrial structures.</t>
+          <t>It is taking on a $50 million conversion of two landmark towers from 1927 and 1941, which is a harder build than anything a printer would be asked to do.</t>
         </is>
       </c>
       <c r="O184" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partly</t>
         </is>
       </c>
       <c r="P184" s="10" t="inlineStr"/>
       <c r="Q184" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Jon%20Deal%20The%20Deal%20Company","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Dougal%20A.%20Cameron%20Cameron%20Management","search")</f>
         <v/>
       </c>
       <c r="R184" s="16">
@@ -19941,29 +19949,33 @@
       </c>
       <c r="S184" s="12" t="inlineStr">
         <is>
-          <t>https://www.dealco.net/</t>
+          <t>https://cameronmanagement.com/</t>
         </is>
       </c>
       <c r="T184" s="15" t="inlineStr">
         <is>
-          <t>Twenty years converting industrial buildings, 27 of them. Adaptive reuse leaves little new wall to print.</t>
+          <t>Interior conversion of a 1927 tower. Willing to take on a hard build, but almost no new exterior wall.</t>
         </is>
       </c>
       <c r="U184" s="12" t="inlineStr"/>
       <c r="V184" s="15" t="inlineStr">
         <is>
-          <t>Founder and Chief Executive Officer, and co-developer of Sawyer Yards.</t>
+          <t>President. Founded the firm in 1995 after asset and project management at Hines.</t>
         </is>
       </c>
       <c r="W184" s="12" t="inlineStr">
         <is>
-          <t>https://www.dealco.net/about/</t>
-        </is>
-      </c>
-      <c r="X184" s="12" t="inlineStr"/>
+          <t>https://cameronmanagement.com/team_member/dougal-a-cameron</t>
+        </is>
+      </c>
+      <c r="X184" s="12" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cameron-management</t>
+        </is>
+      </c>
       <c r="Y184" s="12" t="inlineStr">
         <is>
-          <t>https://www.dealco.net/about/</t>
+          <t>https://cameronmanagement.com/about</t>
         </is>
       </c>
       <c r="Z184" s="12" t="inlineStr"/>
@@ -19971,7 +19983,7 @@
     <row r="185">
       <c r="A185" s="6" t="inlineStr">
         <is>
-          <t>Dougal A. Cameron</t>
+          <t>William T. Dom</t>
         </is>
       </c>
       <c r="B185" s="6" t="inlineStr">
@@ -19981,7 +19993,7 @@
       </c>
       <c r="C185" s="6" t="inlineStr">
         <is>
-          <t>President and Owner</t>
+          <t>Chief Operating Officer</t>
         </is>
       </c>
       <c r="D185" s="7" t="inlineStr">
@@ -20044,7 +20056,7 @@
       </c>
       <c r="P185" s="10" t="inlineStr"/>
       <c r="Q185" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Dougal%20A.%20Cameron%20Cameron%20Management","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=William%20T.%20Dom%20Cameron%20Management","search")</f>
         <v/>
       </c>
       <c r="R185" s="11">
@@ -20064,12 +20076,12 @@
       <c r="U185" s="6" t="inlineStr"/>
       <c r="V185" s="9" t="inlineStr">
         <is>
-          <t>President. Founded the firm in 1995 after asset and project management at Hines.</t>
+          <t>Chief Operating Officer and partner since 2000, formerly an asset manager at Hines.</t>
         </is>
       </c>
       <c r="W185" s="6" t="inlineStr">
         <is>
-          <t>https://cameronmanagement.com/team_member/dougal-a-cameron</t>
+          <t>https://cameronmanagement.com/team_member/william-t-ted-dom</t>
         </is>
       </c>
       <c r="X185" s="6" t="inlineStr">
@@ -20087,17 +20099,17 @@
     <row r="186">
       <c r="A186" s="12" t="inlineStr">
         <is>
-          <t>William T. Dom</t>
+          <t>Jim Lemming</t>
         </is>
       </c>
       <c r="B186" s="12" t="inlineStr">
         <is>
-          <t>Cameron Management</t>
+          <t>Partners in Building</t>
         </is>
       </c>
       <c r="C186" s="12" t="inlineStr">
         <is>
-          <t>Chief Operating Officer</t>
+          <t>Chairman, formerly President and Chief Executive Officer until June 2026</t>
         </is>
       </c>
       <c r="D186" s="13" t="inlineStr">
@@ -20115,12 +20127,12 @@
       </c>
       <c r="G186" s="12" t="inlineStr">
         <is>
-          <t>Downtown Houston, Harris County</t>
+          <t>Houston, build on your lot</t>
         </is>
       </c>
       <c r="H186" s="12" t="inlineStr">
         <is>
-          <t>$50M conversion, up to 100 units</t>
+          <t>More than 300 homes a year in Texas and Tennessee</t>
         </is>
       </c>
       <c r="I186" s="14" t="inlineStr">
@@ -20130,27 +20142,27 @@
       </c>
       <c r="J186" s="15" t="inlineStr">
         <is>
-          <t>Two towers, one conversion each. Nothing repeats.</t>
+          <t>Build on your lot, one-of-a-kind by its own description. There is no plan set to repeat.</t>
         </is>
       </c>
       <c r="K186" s="14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L186" s="15" t="inlineStr">
+        <is>
+          <t>More than 300 homes a year on the firm's own count, across Texas and Tennessee.</t>
+        </is>
+      </c>
+      <c r="M186" s="14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L186" s="15" t="inlineStr">
-        <is>
-          <t>Converting two 1927 and 1941 office towers to residential. No new exterior wall.</t>
-        </is>
-      </c>
-      <c r="M186" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="N186" s="15" t="inlineStr">
         <is>
-          <t>It is taking on a $50 million conversion of two landmark towers from 1927 and 1941, which is a harder build than anything a printer would be asked to do.</t>
+          <t>No method evidence.</t>
         </is>
       </c>
       <c r="O186" s="14" t="inlineStr">
@@ -20160,7 +20172,7 @@
       </c>
       <c r="P186" s="10" t="inlineStr"/>
       <c r="Q186" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=William%20T.%20Dom%20Cameron%20Management","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Jim%20Lemming%20Partners%20in%20Building","search")</f>
         <v/>
       </c>
       <c r="R186" s="16">
@@ -20169,41 +20181,33 @@
       </c>
       <c r="S186" s="12" t="inlineStr">
         <is>
-          <t>https://cameronmanagement.com/</t>
+          <t>https://partnersinbuilding.com/</t>
         </is>
       </c>
       <c r="T186" s="15" t="inlineStr">
         <is>
-          <t>Interior conversion of a 1927 tower. Willing to take on a hard build, but almost no new exterior wall.</t>
+          <t>More than 300 homes a year and a vice president of purchasing. Every house is one-of-a-kind. The presidency passed from Jim to Chris Lemming in June 2026.</t>
         </is>
       </c>
       <c r="U186" s="12" t="inlineStr"/>
       <c r="V186" s="15" t="inlineStr">
         <is>
-          <t>Chief Operating Officer and partner since 2000, formerly an asset manager at Hines.</t>
+          <t>HousingWire, 15 June 2026: President and CEO Jim Lemming will transition to chairman, and his son Chris Lemming will assume the presidency.</t>
         </is>
       </c>
       <c r="W186" s="12" t="inlineStr">
         <is>
-          <t>https://cameronmanagement.com/team_member/william-t-ted-dom</t>
-        </is>
-      </c>
-      <c r="X186" s="12" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/cameron-management</t>
-        </is>
-      </c>
-      <c r="Y186" s="12" t="inlineStr">
-        <is>
-          <t>https://cameronmanagement.com/about</t>
-        </is>
-      </c>
+          <t>https://www.housingwire.com/articles/partners-building-succession-plan/</t>
+        </is>
+      </c>
+      <c r="X186" s="12" t="inlineStr"/>
+      <c r="Y186" s="12" t="inlineStr"/>
       <c r="Z186" s="12" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="6" t="inlineStr">
         <is>
-          <t>Jim Lemming</t>
+          <t>Dewey Hennessee</t>
         </is>
       </c>
       <c r="B187" s="6" t="inlineStr">
@@ -20213,7 +20217,7 @@
       </c>
       <c r="C187" s="6" t="inlineStr">
         <is>
-          <t>Chairman, formerly President and Chief Executive Officer until June 2026</t>
+          <t>Vice President of Purchasing</t>
         </is>
       </c>
       <c r="D187" s="7" t="inlineStr">
@@ -20274,11 +20278,12 @@
           <t>Partly</t>
         </is>
       </c>
-      <c r="P187" s="10" t="inlineStr"/>
-      <c r="Q187" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Jim%20Lemming%20Partners%20in%20Building","search")</f>
-        <v/>
-      </c>
+      <c r="P187" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dewey-hennessee-gmb-caps-cgp-95418531</t>
+        </is>
+      </c>
+      <c r="Q187" s="6" t="inlineStr"/>
       <c r="R187" s="11">
         <f>IF(P187="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -20293,17 +20298,17 @@
           <t>More than 300 homes a year and a vice president of purchasing. Every house is one-of-a-kind. The presidency passed from Jim to Chris Lemming in June 2026.</t>
         </is>
       </c>
-      <c r="U187" s="6" t="inlineStr"/>
+      <c r="U187" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
       <c r="V187" s="9" t="inlineStr">
         <is>
-          <t>HousingWire, 15 June 2026: President and CEO Jim Lemming will transition to chairman, and his son Chris Lemming will assume the presidency.</t>
-        </is>
-      </c>
-      <c r="W187" s="6" t="inlineStr">
-        <is>
-          <t>https://www.housingwire.com/articles/partners-building-succession-plan/</t>
-        </is>
-      </c>
+          <t>Indexed title reads Dewey Hennessee GMB CAPS CGP, Partners in Building. The title on file comes from the first pass and is not repeated in the index entry.</t>
+        </is>
+      </c>
+      <c r="W187" s="6" t="inlineStr"/>
       <c r="X187" s="6" t="inlineStr"/>
       <c r="Y187" s="6" t="inlineStr"/>
       <c r="Z187" s="6" t="inlineStr"/>
@@ -20311,7 +20316,7 @@
     <row r="188">
       <c r="A188" s="12" t="inlineStr">
         <is>
-          <t>Dewey Hennessee</t>
+          <t>Chris Lemming</t>
         </is>
       </c>
       <c r="B188" s="12" t="inlineStr">
@@ -20321,7 +20326,7 @@
       </c>
       <c r="C188" s="12" t="inlineStr">
         <is>
-          <t>Vice President of Purchasing</t>
+          <t>President, since June 2026</t>
         </is>
       </c>
       <c r="D188" s="13" t="inlineStr">
@@ -20382,12 +20387,11 @@
           <t>Partly</t>
         </is>
       </c>
-      <c r="P188" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/dewey-hennessee-gmb-caps-cgp-95418531</t>
-        </is>
-      </c>
-      <c r="Q188" s="12" t="inlineStr"/>
+      <c r="P188" s="10" t="inlineStr"/>
+      <c r="Q188" s="12">
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Chris%20Lemming%20Partners%20in%20Building","search")</f>
+        <v/>
+      </c>
       <c r="R188" s="16">
         <f>IF(P188="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -20402,17 +20406,17 @@
           <t>More than 300 homes a year and a vice president of purchasing. Every house is one-of-a-kind. The presidency passed from Jim to Chris Lemming in June 2026.</t>
         </is>
       </c>
-      <c r="U188" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="U188" s="12" t="inlineStr"/>
       <c r="V188" s="15" t="inlineStr">
         <is>
-          <t>Indexed title reads Dewey Hennessee GMB CAPS CGP, Partners in Building. The title on file comes from the first pass and is not repeated in the index entry.</t>
-        </is>
-      </c>
-      <c r="W188" s="12" t="inlineStr"/>
+          <t>HousingWire, 15 June 2026: Chris Lemming assumes the presidency after an eighteen-month succession.</t>
+        </is>
+      </c>
+      <c r="W188" s="12" t="inlineStr">
+        <is>
+          <t>https://www.housingwire.com/articles/partners-building-succession-plan/</t>
+        </is>
+      </c>
       <c r="X188" s="12" t="inlineStr"/>
       <c r="Y188" s="12" t="inlineStr"/>
       <c r="Z188" s="12" t="inlineStr"/>
@@ -20420,17 +20424,17 @@
     <row r="189">
       <c r="A189" s="6" t="inlineStr">
         <is>
-          <t>Chris Lemming</t>
+          <t>Dan Braun</t>
         </is>
       </c>
       <c r="B189" s="6" t="inlineStr">
         <is>
-          <t>Partners in Building</t>
+          <t>Braun Enterprises</t>
         </is>
       </c>
       <c r="C189" s="6" t="inlineStr">
         <is>
-          <t>President, since June 2026</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D189" s="7" t="inlineStr">
@@ -20439,7 +20443,7 @@
         </is>
       </c>
       <c r="E189" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F189" s="6" t="inlineStr">
         <is>
@@ -20448,79 +20452,76 @@
       </c>
       <c r="G189" s="6" t="inlineStr">
         <is>
-          <t>Houston, build on your lot</t>
+          <t>Houston, San Antonio and Austin</t>
         </is>
       </c>
       <c r="H189" s="6" t="inlineStr">
         <is>
-          <t>More than 300 homes a year in Texas and Tennessee</t>
+          <t>Ground-up retail in the Heights and small flex industrial</t>
         </is>
       </c>
       <c r="I189" s="8" t="inlineStr">
         <is>
+          <t>Partly</t>
+        </is>
+      </c>
+      <c r="J189" s="9" t="inlineStr">
+        <is>
+          <t>Small retail buildings repeated across three cities, which is more repetition than anyone else in this category.</t>
+        </is>
+      </c>
+      <c r="K189" s="8" t="inlineStr">
+        <is>
+          <t>Partly</t>
+        </is>
+      </c>
+      <c r="L189" s="9" t="inlineStr">
+        <is>
+          <t>Retail shells at 20,000 to 25,000 square feet. A printed wall competes with tilt-wall here, not with stick framing.</t>
+        </is>
+      </c>
+      <c r="M189" s="8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J189" s="9" t="inlineStr">
-        <is>
-          <t>Build on your lot, one-of-a-kind by its own description. There is no plan set to repeat.</t>
-        </is>
-      </c>
-      <c r="K189" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L189" s="9" t="inlineStr">
-        <is>
-          <t>More than 300 homes a year on the firm's own count, across Texas and Tennessee.</t>
-        </is>
-      </c>
-      <c r="M189" s="8" t="inlineStr">
+      <c r="N189" s="9" t="inlineStr">
+        <is>
+          <t>No method evidence on record.</t>
+        </is>
+      </c>
+      <c r="O189" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N189" s="9" t="inlineStr">
-        <is>
-          <t>No method evidence.</t>
-        </is>
-      </c>
-      <c r="O189" s="8" t="inlineStr">
-        <is>
-          <t>Partly</t>
-        </is>
-      </c>
-      <c r="P189" s="10" t="inlineStr"/>
-      <c r="Q189" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Chris%20Lemming%20Partners%20in%20Building","search")</f>
-        <v/>
-      </c>
+      <c r="P189" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dan-braun-36451a15/</t>
+        </is>
+      </c>
+      <c r="Q189" s="6" t="inlineStr"/>
       <c r="R189" s="11">
         <f>IF(P189="","ADD LINKEDIN","ok")</f>
         <v/>
       </c>
       <c r="S189" s="6" t="inlineStr">
         <is>
-          <t>https://partnersinbuilding.com/</t>
+          <t>https://braunenterprises.com/</t>
         </is>
       </c>
       <c r="T189" s="9" t="inlineStr">
         <is>
-          <t>More than 300 homes a year and a vice president of purchasing. Every house is one-of-a-kind. The presidency passed from Jim to Chris Lemming in June 2026.</t>
+          <t>Builds new rather than converting: small-format ground-up retail in the Heights.</t>
         </is>
       </c>
       <c r="U189" s="6" t="inlineStr"/>
       <c r="V189" s="9" t="inlineStr">
         <is>
-          <t>HousingWire, 15 June 2026: Chris Lemming assumes the presidency after an eighteen-month succession.</t>
-        </is>
-      </c>
-      <c r="W189" s="6" t="inlineStr">
-        <is>
-          <t>https://www.housingwire.com/articles/partners-building-succession-plan/</t>
-        </is>
-      </c>
+          <t>Indexed title reads Dan Braun, President at Braun Enterprises. The firm's team page returns a 404, so this is the only link.</t>
+        </is>
+      </c>
+      <c r="W189" s="6" t="inlineStr"/>
       <c r="X189" s="6" t="inlineStr"/>
       <c r="Y189" s="6" t="inlineStr"/>
       <c r="Z189" s="6" t="inlineStr"/>
@@ -20528,17 +20529,17 @@
     <row r="190">
       <c r="A190" s="12" t="inlineStr">
         <is>
-          <t>Dan Braun</t>
+          <t>Bradley Freels</t>
         </is>
       </c>
       <c r="B190" s="12" t="inlineStr">
         <is>
-          <t>Braun Enterprises</t>
+          <t>Midway</t>
         </is>
       </c>
       <c r="C190" s="12" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Chairman and Chief Executive Officer</t>
         </is>
       </c>
       <c r="D190" s="13" t="inlineStr">
@@ -20556,12 +20557,12 @@
       </c>
       <c r="G190" s="12" t="inlineStr">
         <is>
-          <t>Houston, San Antonio and Austin</t>
+          <t>Houston HQ / East End, Harris County</t>
         </is>
       </c>
       <c r="H190" s="12" t="inlineStr">
         <is>
-          <t>Ground-up retail in the Heights and small flex industrial</t>
+          <t>East River: 150 acres, 60 city blocks</t>
         </is>
       </c>
       <c r="I190" s="14" t="inlineStr">
@@ -20571,69 +20572,80 @@
       </c>
       <c r="J190" s="15" t="inlineStr">
         <is>
-          <t>Small retail buildings repeated across three cities, which is more repetition than anyone else in this category.</t>
+          <t>East River is 60 city blocks on one site, phased over decades.</t>
         </is>
       </c>
       <c r="K190" s="14" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L190" s="15" t="inlineStr">
         <is>
-          <t>Retail shells at 20,000 to 25,000 square feet. A printed wall competes with tilt-wall here, not with stick framing.</t>
+          <t>Sixty blocks of mixed-use. The buildings are one-offs, whatever the acreage.</t>
         </is>
       </c>
       <c r="M190" s="14" t="inlineStr">
         <is>
+          <t>Partly</t>
+        </is>
+      </c>
+      <c r="N190" s="15" t="inlineStr">
+        <is>
+          <t>District-scale design ambition, but no specific method precedent was found.</t>
+        </is>
+      </c>
+      <c r="O190" s="14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N190" s="15" t="inlineStr">
-        <is>
-          <t>No method evidence on record.</t>
-        </is>
-      </c>
-      <c r="O190" s="14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P190" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/dan-braun-36451a15/</t>
-        </is>
-      </c>
-      <c r="Q190" s="12" t="inlineStr"/>
+      <c r="P190" s="10" t="inlineStr"/>
+      <c r="Q190" s="12">
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Bradley%20Freels%20Midway","search")</f>
+        <v/>
+      </c>
       <c r="R190" s="16">
         <f>IF(P190="","ADD LINKEDIN","ok")</f>
         <v/>
       </c>
       <c r="S190" s="12" t="inlineStr">
         <is>
-          <t>https://braunenterprises.com/</t>
+          <t>https://www.midway.team/</t>
         </is>
       </c>
       <c r="T190" s="15" t="inlineStr">
         <is>
-          <t>Builds new rather than converting: small-format ground-up retail in the Heights.</t>
+          <t>East River is 60 blocks on one site, and Midway kept sole development control after selling out of the Parkway joint venture in December 2024.</t>
         </is>
       </c>
       <c r="U190" s="12" t="inlineStr"/>
       <c r="V190" s="15" t="inlineStr">
         <is>
-          <t>Indexed title reads Dan Braun, President at Braun Enterprises. The firm's team page returns a 404, so this is the only link.</t>
-        </is>
-      </c>
-      <c r="W190" s="12" t="inlineStr"/>
-      <c r="X190" s="12" t="inlineStr"/>
-      <c r="Y190" s="12" t="inlineStr"/>
+          <t>Chairman and Chief Executive Officer on Midway's own people page. He has no findable LinkedIn profile, so this is the citation.</t>
+        </is>
+      </c>
+      <c r="W190" s="12" t="inlineStr">
+        <is>
+          <t>https://www.midway.team/our-people</t>
+        </is>
+      </c>
+      <c r="X190" s="12" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/midway</t>
+        </is>
+      </c>
+      <c r="Y190" s="12" t="inlineStr">
+        <is>
+          <t>https://www.midway.team/our-people</t>
+        </is>
+      </c>
       <c r="Z190" s="12" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="6" t="inlineStr">
         <is>
-          <t>Bradley Freels</t>
+          <t>David Hightower</t>
         </is>
       </c>
       <c r="B191" s="6" t="inlineStr">
@@ -20643,7 +20655,7 @@
       </c>
       <c r="C191" s="6" t="inlineStr">
         <is>
-          <t>Chairman and Chief Executive Officer</t>
+          <t>Executive Vice President</t>
         </is>
       </c>
       <c r="D191" s="7" t="inlineStr">
@@ -20704,11 +20716,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P191" s="10" t="inlineStr"/>
-      <c r="Q191" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Bradley%20Freels%20Midway","search")</f>
-        <v/>
-      </c>
+      <c r="P191" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dahightower/</t>
+        </is>
+      </c>
+      <c r="Q191" s="6" t="inlineStr"/>
       <c r="R191" s="11">
         <f>IF(P191="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -20726,14 +20739,10 @@
       <c r="U191" s="6" t="inlineStr"/>
       <c r="V191" s="9" t="inlineStr">
         <is>
-          <t>Chairman and Chief Executive Officer on Midway's own people page. He has no findable LinkedIn profile, so this is the citation.</t>
-        </is>
-      </c>
-      <c r="W191" s="6" t="inlineStr">
-        <is>
-          <t>https://www.midway.team/our-people</t>
-        </is>
-      </c>
+          <t>Executive Vice President, Development at Midway Companies. Houston, Texas.</t>
+        </is>
+      </c>
+      <c r="W191" s="6" t="inlineStr"/>
       <c r="X191" s="6" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/midway</t>
@@ -20749,7 +20758,7 @@
     <row r="192">
       <c r="A192" s="12" t="inlineStr">
         <is>
-          <t>David Hightower</t>
+          <t>Clark Thompson</t>
         </is>
       </c>
       <c r="B192" s="12" t="inlineStr">
@@ -20759,7 +20768,7 @@
       </c>
       <c r="C192" s="12" t="inlineStr">
         <is>
-          <t>Executive Vice President</t>
+          <t>Executive Vice President and General Counsel</t>
         </is>
       </c>
       <c r="D192" s="13" t="inlineStr">
@@ -20820,12 +20829,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P192" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/dahightower/</t>
-        </is>
-      </c>
-      <c r="Q192" s="12" t="inlineStr"/>
+      <c r="P192" s="10" t="inlineStr"/>
+      <c r="Q192" s="12">
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Clark%20Thompson%20Midway","search")</f>
+        <v/>
+      </c>
       <c r="R192" s="16">
         <f>IF(P192="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -20841,12 +20849,12 @@
         </is>
       </c>
       <c r="U192" s="12" t="inlineStr"/>
-      <c r="V192" s="15" t="inlineStr">
-        <is>
-          <t>Executive Vice President, Development at Midway Companies. Houston, Texas.</t>
-        </is>
-      </c>
-      <c r="W192" s="12" t="inlineStr"/>
+      <c r="V192" s="15" t="inlineStr"/>
+      <c r="W192" s="12" t="inlineStr">
+        <is>
+          <t>https://www.midway.team/our-people</t>
+        </is>
+      </c>
       <c r="X192" s="12" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/midway</t>
@@ -20862,7 +20870,7 @@
     <row r="193">
       <c r="A193" s="6" t="inlineStr">
         <is>
-          <t>Clark Thompson</t>
+          <t>Rob Sigler</t>
         </is>
       </c>
       <c r="B193" s="6" t="inlineStr">
@@ -20872,7 +20880,7 @@
       </c>
       <c r="C193" s="6" t="inlineStr">
         <is>
-          <t>Executive Vice President and General Counsel</t>
+          <t>Executive Vice President, Construction, Investment and Development, Midway</t>
         </is>
       </c>
       <c r="D193" s="7" t="inlineStr">
@@ -20933,11 +20941,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P193" s="10" t="inlineStr"/>
-      <c r="Q193" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Clark%20Thompson%20Midway","search")</f>
-        <v/>
-      </c>
+      <c r="P193" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/robsigler/</t>
+        </is>
+      </c>
+      <c r="Q193" s="6" t="inlineStr"/>
       <c r="R193" s="11">
         <f>IF(P193="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -20952,13 +20961,17 @@
           <t>East River is 60 blocks on one site, and Midway kept sole development control after selling out of the Parkway joint venture in December 2024.</t>
         </is>
       </c>
-      <c r="U193" s="6" t="inlineStr"/>
-      <c r="V193" s="9" t="inlineStr"/>
-      <c r="W193" s="6" t="inlineStr">
-        <is>
-          <t>https://www.midway.team/our-people</t>
-        </is>
-      </c>
+      <c r="U193" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="V193" s="9" t="inlineStr">
+        <is>
+          <t>Profile opened. Company line reads Midway. Headline is Executive Vice President Construction, Investment &amp; Development, and his feed carries Midway and East River posts. He also shared Kirksey's mass-timber progress at San Jacinto College, CLT floor panels going in, which is a personal record of interest in an alternative structural system.</t>
+        </is>
+      </c>
+      <c r="W193" s="6" t="inlineStr"/>
       <c r="X193" s="6" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/midway</t>
@@ -20974,7 +20987,7 @@
     <row r="194">
       <c r="A194" s="12" t="inlineStr">
         <is>
-          <t>Rob Sigler</t>
+          <t>Anna Deans</t>
         </is>
       </c>
       <c r="B194" s="12" t="inlineStr">
@@ -20984,7 +20997,7 @@
       </c>
       <c r="C194" s="12" t="inlineStr">
         <is>
-          <t>Executive Vice President, Construction, Investment and Development, Midway</t>
+          <t>Executive Vice President, Midway</t>
         </is>
       </c>
       <c r="D194" s="13" t="inlineStr">
@@ -21047,7 +21060,7 @@
       </c>
       <c r="P194" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/robsigler/</t>
+          <t>https://www.linkedin.com/in/anna-deans-bbbab03/</t>
         </is>
       </c>
       <c r="Q194" s="12" t="inlineStr"/>
@@ -21065,16 +21078,8 @@
           <t>East River is 60 blocks on one site, and Midway kept sole development control after selling out of the Parkway joint venture in December 2024.</t>
         </is>
       </c>
-      <c r="U194" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="V194" s="15" t="inlineStr">
-        <is>
-          <t>Profile opened. Company line reads Midway. Headline is Executive Vice President Construction, Investment &amp; Development, and his feed carries Midway and East River posts. He also shared Kirksey's mass-timber progress at San Jacinto College, CLT floor panels going in, which is a personal record of interest in an alternative structural system.</t>
-        </is>
-      </c>
+      <c r="U194" s="12" t="inlineStr"/>
+      <c r="V194" s="15" t="inlineStr"/>
       <c r="W194" s="12" t="inlineStr"/>
       <c r="X194" s="12" t="inlineStr">
         <is>
@@ -21091,17 +21096,17 @@
     <row r="195">
       <c r="A195" s="6" t="inlineStr">
         <is>
-          <t>Anna Deans</t>
+          <t>Paul Coonrod</t>
         </is>
       </c>
       <c r="B195" s="6" t="inlineStr">
         <is>
-          <t>Midway</t>
+          <t>Pagewood</t>
         </is>
       </c>
       <c r="C195" s="6" t="inlineStr">
         <is>
-          <t>Executive Vice President, Midway</t>
+          <t>Founder and Managing Principal</t>
         </is>
       </c>
       <c r="D195" s="7" t="inlineStr">
@@ -21110,7 +21115,7 @@
         </is>
       </c>
       <c r="E195" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F195" s="6" t="inlineStr">
         <is>
@@ -21119,12 +21124,12 @@
       </c>
       <c r="G195" s="6" t="inlineStr">
         <is>
-          <t>Houston HQ / East End, Harris County</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="H195" s="6" t="inlineStr">
         <is>
-          <t>East River: 150 acres, 60 city blocks</t>
+          <t>East Blocks phase one, 30,000 sf across two warehouses</t>
         </is>
       </c>
       <c r="I195" s="8" t="inlineStr">
@@ -21134,7 +21139,7 @@
       </c>
       <c r="J195" s="9" t="inlineStr">
         <is>
-          <t>East River is 60 city blocks on one site, phased over decades.</t>
+          <t>Ten blocks under one plan is concentration, but every building is its own problem.</t>
         </is>
       </c>
       <c r="K195" s="8" t="inlineStr">
@@ -21144,63 +21149,58 @@
       </c>
       <c r="L195" s="9" t="inlineStr">
         <is>
-          <t>Sixty blocks of mixed-use. The buildings are one-offs, whatever the acreage.</t>
+          <t>The phase-one programme is retail, office and parking rather than repeated units.</t>
         </is>
       </c>
       <c r="M195" s="8" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N195" s="9" t="inlineStr">
         <is>
-          <t>District-scale design ambition, but no specific method precedent was found.</t>
+          <t>It chose to keep eighty-year-old warehouses that would have been cheaper to demolish. The partner said so on the record.</t>
         </is>
       </c>
       <c r="O195" s="8" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P195" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/anna-deans-bbbab03/</t>
-        </is>
-      </c>
-      <c r="Q195" s="6" t="inlineStr"/>
+          <t>Partly</t>
+        </is>
+      </c>
+      <c r="P195" s="10" t="inlineStr"/>
+      <c r="Q195" s="6">
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Paul%20Coonrod%20Pagewood","search")</f>
+        <v/>
+      </c>
       <c r="R195" s="11">
         <f>IF(P195="","ADD LINKEDIN","ok")</f>
         <v/>
       </c>
       <c r="S195" s="6" t="inlineStr">
         <is>
-          <t>https://www.midway.team/</t>
+          <t>https://www.pagewood.com/</t>
         </is>
       </c>
       <c r="T195" s="9" t="inlineStr">
         <is>
-          <t>East River is 60 blocks on one site, and Midway kept sole development control after selling out of the Parkway joint venture in December 2024.</t>
+          <t>Ten contiguous EaDo blocks, 513,000 square feet in phase one, Gensler on design and SWA on landscape. It builds ground-up industrial elsewhere, so it is not conversion-only.</t>
         </is>
       </c>
       <c r="U195" s="6" t="inlineStr"/>
       <c r="V195" s="9" t="inlineStr"/>
-      <c r="W195" s="6" t="inlineStr"/>
-      <c r="X195" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/midway</t>
-        </is>
-      </c>
-      <c r="Y195" s="6" t="inlineStr">
-        <is>
-          <t>https://www.midway.team/our-people</t>
-        </is>
-      </c>
+      <c r="W195" s="6" t="inlineStr">
+        <is>
+          <t>https://www.pagewood.com/team</t>
+        </is>
+      </c>
+      <c r="X195" s="6" t="inlineStr"/>
+      <c r="Y195" s="6" t="inlineStr"/>
       <c r="Z195" s="6" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="12" t="inlineStr">
         <is>
-          <t>Paul Coonrod</t>
+          <t>Mat Volz</t>
         </is>
       </c>
       <c r="B196" s="12" t="inlineStr">
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C196" s="12" t="inlineStr">
         <is>
-          <t>Founder and Managing Principal</t>
+          <t>Managing Principal</t>
         </is>
       </c>
       <c r="D196" s="13" t="inlineStr">
@@ -21271,11 +21271,12 @@
           <t>Partly</t>
         </is>
       </c>
-      <c r="P196" s="10" t="inlineStr"/>
-      <c r="Q196" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Paul%20Coonrod%20Pagewood","search")</f>
-        <v/>
-      </c>
+      <c r="P196" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mathew-volz-14684850/</t>
+        </is>
+      </c>
+      <c r="Q196" s="12" t="inlineStr"/>
       <c r="R196" s="16">
         <f>IF(P196="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -21291,7 +21292,11 @@
         </is>
       </c>
       <c r="U196" s="12" t="inlineStr"/>
-      <c r="V196" s="15" t="inlineStr"/>
+      <c r="V196" s="15" t="inlineStr">
+        <is>
+          <t>Indexed title reads Mathew Volz, Managing Principal at Pagewood. The firm's team page spells the name Mat.</t>
+        </is>
+      </c>
       <c r="W196" s="12" t="inlineStr">
         <is>
           <t>https://www.pagewood.com/team</t>
@@ -21304,7 +21309,7 @@
     <row r="197">
       <c r="A197" s="6" t="inlineStr">
         <is>
-          <t>Mat Volz</t>
+          <t>Preston Luster</t>
         </is>
       </c>
       <c r="B197" s="6" t="inlineStr">
@@ -21314,7 +21319,7 @@
       </c>
       <c r="C197" s="6" t="inlineStr">
         <is>
-          <t>Managing Principal</t>
+          <t>Senior Construction Manager</t>
         </is>
       </c>
       <c r="D197" s="7" t="inlineStr">
@@ -21375,12 +21380,11 @@
           <t>Partly</t>
         </is>
       </c>
-      <c r="P197" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/mathew-volz-14684850/</t>
-        </is>
-      </c>
-      <c r="Q197" s="6" t="inlineStr"/>
+      <c r="P197" s="10" t="inlineStr"/>
+      <c r="Q197" s="6">
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Preston%20Luster%20Pagewood","search")</f>
+        <v/>
+      </c>
       <c r="R197" s="11">
         <f>IF(P197="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -21396,11 +21400,7 @@
         </is>
       </c>
       <c r="U197" s="6" t="inlineStr"/>
-      <c r="V197" s="9" t="inlineStr">
-        <is>
-          <t>Indexed title reads Mathew Volz, Managing Principal at Pagewood. The firm's team page spells the name Mat.</t>
-        </is>
-      </c>
+      <c r="V197" s="9" t="inlineStr"/>
       <c r="W197" s="6" t="inlineStr">
         <is>
           <t>https://www.pagewood.com/team</t>
@@ -21413,17 +21413,17 @@
     <row r="198">
       <c r="A198" s="12" t="inlineStr">
         <is>
-          <t>Preston Luster</t>
+          <t>David Kelley</t>
         </is>
       </c>
       <c r="B198" s="12" t="inlineStr">
         <is>
-          <t>Pagewood</t>
+          <t>Concept Neighborhood</t>
         </is>
       </c>
       <c r="C198" s="12" t="inlineStr">
         <is>
-          <t>Senior Construction Manager</t>
+          <t>Managing Partner, Projects and Finance</t>
         </is>
       </c>
       <c r="D198" s="13" t="inlineStr">
@@ -21441,22 +21441,22 @@
       </c>
       <c r="G198" s="12" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>East End, Harris</t>
         </is>
       </c>
       <c r="H198" s="12" t="inlineStr">
         <is>
-          <t>East Blocks phase one, 30,000 sf across two warehouses</t>
+          <t>17 acres at The Plant, Second Ward</t>
         </is>
       </c>
       <c r="I198" s="14" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J198" s="15" t="inlineStr">
         <is>
-          <t>Ten blocks under one plan is concentration, but every building is its own problem.</t>
+          <t>Four blocks of eighty-year-old industrial buildings, each one different. There is no plan to repeat.</t>
         </is>
       </c>
       <c r="K198" s="14" t="inlineStr">
@@ -21466,48 +21466,49 @@
       </c>
       <c r="L198" s="15" t="inlineStr">
         <is>
-          <t>The phase-one programme is retail, office and parking rather than repeated units.</t>
+          <t>Conversion work leaves little new wall. A printed element would have to be an addition rather than the building.</t>
         </is>
       </c>
       <c r="M198" s="14" t="inlineStr">
         <is>
+          <t>Partly</t>
+        </is>
+      </c>
+      <c r="N198" s="15" t="inlineStr">
+        <is>
+          <t>They restored an 1890s building to open Axelrad and took a National Register industrial basilica on at The Factory. This is a team that chooses the harder build on purpose.</t>
+        </is>
+      </c>
+      <c r="O198" s="14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N198" s="15" t="inlineStr">
-        <is>
-          <t>It chose to keep eighty-year-old warehouses that would have been cheaper to demolish. The partner said so on the record.</t>
-        </is>
-      </c>
-      <c r="O198" s="14" t="inlineStr">
-        <is>
-          <t>Partly</t>
-        </is>
-      </c>
-      <c r="P198" s="10" t="inlineStr"/>
-      <c r="Q198" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Preston%20Luster%20Pagewood","search")</f>
-        <v/>
-      </c>
+      <c r="P198" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/david-kelley-275240105/</t>
+        </is>
+      </c>
+      <c r="Q198" s="12" t="inlineStr"/>
       <c r="R198" s="16">
         <f>IF(P198="","ADD LINKEDIN","ok")</f>
         <v/>
       </c>
       <c r="S198" s="12" t="inlineStr">
         <is>
-          <t>https://www.pagewood.com/</t>
+          <t>https://www.conceptneighborhood.com/</t>
         </is>
       </c>
       <c r="T198" s="15" t="inlineStr">
         <is>
-          <t>Ten contiguous EaDo blocks, 513,000 square feet in phase one, Gensler on design and SWA on landscape. It builds ground-up industrial elsewhere, so it is not conversion-only.</t>
+          <t>The only firm screened whose founders operate hospitality themselves rather than leasing to operators. Seventeen acres of industrial conversion in the East End.</t>
         </is>
       </c>
       <c r="U198" s="12" t="inlineStr"/>
       <c r="V198" s="15" t="inlineStr"/>
       <c r="W198" s="12" t="inlineStr">
         <is>
-          <t>https://www.pagewood.com/team</t>
+          <t>https://www.conceptneighborhood.com/team</t>
         </is>
       </c>
       <c r="X198" s="12" t="inlineStr"/>
@@ -21517,7 +21518,7 @@
     <row r="199">
       <c r="A199" s="6" t="inlineStr">
         <is>
-          <t>David Kelley</t>
+          <t>Jeffrey Kaplan</t>
         </is>
       </c>
       <c r="B199" s="6" t="inlineStr">
@@ -21527,7 +21528,7 @@
       </c>
       <c r="C199" s="6" t="inlineStr">
         <is>
-          <t>Managing Partner, Projects and Finance</t>
+          <t>Managing Partner, Brokerage and Placemaking, co-founder of Axelrad</t>
         </is>
       </c>
       <c r="D199" s="7" t="inlineStr">
@@ -21590,7 +21591,7 @@
       </c>
       <c r="P199" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/david-kelley-275240105/</t>
+          <t>https://www.linkedin.com/in/jeffrey-kaplan-71190150/</t>
         </is>
       </c>
       <c r="Q199" s="6" t="inlineStr"/>
@@ -21622,7 +21623,7 @@
     <row r="200">
       <c r="A200" s="12" t="inlineStr">
         <is>
-          <t>Jeffrey Kaplan</t>
+          <t>Monte Large</t>
         </is>
       </c>
       <c r="B200" s="12" t="inlineStr">
@@ -21632,7 +21633,7 @@
       </c>
       <c r="C200" s="12" t="inlineStr">
         <is>
-          <t>Managing Partner, Brokerage and Placemaking, co-founder of Axelrad</t>
+          <t>Partner, Design and Placemaking</t>
         </is>
       </c>
       <c r="D200" s="13" t="inlineStr">
@@ -21695,7 +21696,7 @@
       </c>
       <c r="P200" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/jeffrey-kaplan-71190150/</t>
+          <t>https://www.linkedin.com/in/montelarge/</t>
         </is>
       </c>
       <c r="Q200" s="12" t="inlineStr"/>
@@ -21727,7 +21728,7 @@
     <row r="201">
       <c r="A201" s="6" t="inlineStr">
         <is>
-          <t>Monte Large</t>
+          <t>Jeremy Roberts</t>
         </is>
       </c>
       <c r="B201" s="6" t="inlineStr">
@@ -21737,7 +21738,7 @@
       </c>
       <c r="C201" s="6" t="inlineStr">
         <is>
-          <t>Partner, Design and Placemaking</t>
+          <t>Managing Partner, Projects and Legal</t>
         </is>
       </c>
       <c r="D201" s="7" t="inlineStr">
@@ -21800,7 +21801,7 @@
       </c>
       <c r="P201" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/montelarge/</t>
+          <t>https://www.linkedin.com/in/jeremyaaronroberts/</t>
         </is>
       </c>
       <c r="Q201" s="6" t="inlineStr"/>
@@ -21832,17 +21833,17 @@
     <row r="202">
       <c r="A202" s="12" t="inlineStr">
         <is>
-          <t>Jeremy Roberts</t>
+          <t>Randolph Wile</t>
         </is>
       </c>
       <c r="B202" s="12" t="inlineStr">
         <is>
-          <t>Concept Neighborhood</t>
+          <t>Wile Interests</t>
         </is>
       </c>
       <c r="C202" s="12" t="inlineStr">
         <is>
-          <t>Managing Partner, Projects and Legal</t>
+          <t>Founder and President</t>
         </is>
       </c>
       <c r="D202" s="13" t="inlineStr">
@@ -21860,42 +21861,42 @@
       </c>
       <c r="G202" s="12" t="inlineStr">
         <is>
-          <t>East End, Harris</t>
+          <t>Houston and Katy</t>
         </is>
       </c>
       <c r="H202" s="12" t="inlineStr">
         <is>
-          <t>17 acres at The Plant, Second Ward</t>
+          <t>Ground-up in Katy, adaptive reuse in EaDo</t>
         </is>
       </c>
       <c r="I202" s="14" t="inlineStr">
         <is>
+          <t>Partly</t>
+        </is>
+      </c>
+      <c r="J202" s="15" t="inlineStr">
+        <is>
+          <t>Two quite different programmes in two submarkets. No repeated unit.</t>
+        </is>
+      </c>
+      <c r="K202" s="14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J202" s="15" t="inlineStr">
-        <is>
-          <t>Four blocks of eighty-year-old industrial buildings, each one different. There is no plan to repeat.</t>
-        </is>
-      </c>
-      <c r="K202" s="14" t="inlineStr">
+      <c r="L202" s="15" t="inlineStr">
+        <is>
+          <t>Medical office and retail shells rather than houses.</t>
+        </is>
+      </c>
+      <c r="M202" s="14" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L202" s="15" t="inlineStr">
-        <is>
-          <t>Conversion work leaves little new wall. A printed element would have to be an addition rather than the building.</t>
-        </is>
-      </c>
-      <c r="M202" s="14" t="inlineStr">
-        <is>
-          <t>Partly</t>
-        </is>
-      </c>
       <c r="N202" s="15" t="inlineStr">
         <is>
-          <t>They restored an 1890s building to open Axelrad and took a National Register industrial basilica on at The Factory. This is a team that chooses the harder build on purpose.</t>
+          <t>Its president is the one quoted explaining why the firm kept the old warehouses instead of clearing the site.</t>
         </is>
       </c>
       <c r="O202" s="14" t="inlineStr">
@@ -21905,7 +21906,7 @@
       </c>
       <c r="P202" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/jeremyaaronroberts/</t>
+          <t>https://www.linkedin.com/in/randolph-wile/</t>
         </is>
       </c>
       <c r="Q202" s="12" t="inlineStr"/>
@@ -21915,19 +21916,23 @@
       </c>
       <c r="S202" s="12" t="inlineStr">
         <is>
-          <t>https://www.conceptneighborhood.com/</t>
+          <t>https://www.wileinterests.com/</t>
         </is>
       </c>
       <c r="T202" s="15" t="inlineStr">
         <is>
-          <t>The only firm screened whose founders operate hospitality themselves rather than leasing to operators. Seventeen acres of industrial conversion in the East End.</t>
+          <t>Ground-up medical and retail in Katy, conversion in EaDo.</t>
         </is>
       </c>
       <c r="U202" s="12" t="inlineStr"/>
-      <c r="V202" s="15" t="inlineStr"/>
+      <c r="V202" s="15" t="inlineStr">
+        <is>
+          <t>Indexed title reads Randolph Wile, Wile Interests, Inc. The Real Deal, November 2023, quotes Wile Interests president Randolph Wile.</t>
+        </is>
+      </c>
       <c r="W202" s="12" t="inlineStr">
         <is>
-          <t>https://www.conceptneighborhood.com/team</t>
+          <t>https://therealdeal.com/texas/houston/2023/11/13/pagewood-wile-to-convert-eado-houston-warehouses/</t>
         </is>
       </c>
       <c r="X202" s="12" t="inlineStr"/>
@@ -21937,26 +21942,26 @@
     <row r="203">
       <c r="A203" s="6" t="inlineStr">
         <is>
-          <t>Randolph Wile</t>
+          <t>Paul J. Romanowski</t>
         </is>
       </c>
       <c r="B203" s="6" t="inlineStr">
         <is>
-          <t>Wile Interests</t>
+          <t>D.R. Horton, Inc.</t>
         </is>
       </c>
       <c r="C203" s="6" t="inlineStr">
         <is>
-          <t>Founder and President</t>
+          <t>President and Chief Executive Officer</t>
         </is>
       </c>
       <c r="D203" s="7" t="inlineStr">
         <is>
-          <t>Creative project, hybrid job</t>
+          <t>National scale, pilot not purchase</t>
         </is>
       </c>
       <c r="E203" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F203" s="6" t="inlineStr">
         <is>
@@ -21965,78 +21970,73 @@
       </c>
       <c r="G203" s="6" t="inlineStr">
         <is>
-          <t>Houston and Katy</t>
+          <t>Arlington HQ / Sugar Land, Richmond, Conroe</t>
         </is>
       </c>
       <c r="H203" s="6" t="inlineStr">
         <is>
-          <t>Ground-up in Katy, adaptive reuse in EaDo</t>
+          <t>372 Houston permits in August 2026, first in the metro</t>
         </is>
       </c>
       <c r="I203" s="8" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J203" s="9" t="inlineStr">
         <is>
-          <t>Two quite different programmes in two submarkets. No repeated unit.</t>
+          <t>65 Houston communities and 668 standing homes at one time, on a national plan library.</t>
         </is>
       </c>
       <c r="K203" s="8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partly</t>
         </is>
       </c>
       <c r="L203" s="9" t="inlineStr">
         <is>
-          <t>Medical office and retail shells rather than houses.</t>
+          <t>84,863 closings a year is far above the band one or two printers cover, so the first order is a pilot inside one division rather than a purchase.</t>
         </is>
       </c>
       <c r="M203" s="8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N203" s="9" t="inlineStr">
         <is>
-          <t>Its president is the one quoted explaining why the firm kept the old warehouses instead of clearing the site.</t>
+          <t>Strategic investment in Apis Cor, March 2024, amount undisclosed. It is the only equity position in a printed wall system on this deck.</t>
         </is>
       </c>
       <c r="O203" s="8" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P203" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/randolph-wile/</t>
-        </is>
-      </c>
-      <c r="Q203" s="6" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P203" s="10" t="inlineStr"/>
+      <c r="Q203" s="6">
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Paul%20J.%20Romanowski%20D.R.%20Horton%2C%20Inc.","search")</f>
+        <v/>
+      </c>
       <c r="R203" s="11">
         <f>IF(P203="","ADD LINKEDIN","ok")</f>
         <v/>
       </c>
       <c r="S203" s="6" t="inlineStr">
         <is>
-          <t>https://www.wileinterests.com/</t>
+          <t>https://www.drhorton.com/texas/houston</t>
         </is>
       </c>
       <c r="T203" s="9" t="inlineStr">
         <is>
-          <t>Ground-up medical and retail in Katy, conversion in EaDo.</t>
+          <t>It has already bought equity in a printed wall system, and it builds more houses in Houston than anyone else.</t>
         </is>
       </c>
       <c r="U203" s="6" t="inlineStr"/>
-      <c r="V203" s="9" t="inlineStr">
-        <is>
-          <t>Indexed title reads Randolph Wile, Wile Interests, Inc. The Real Deal, November 2023, quotes Wile Interests president Randolph Wile.</t>
-        </is>
-      </c>
+      <c r="V203" s="9" t="inlineStr"/>
       <c r="W203" s="6" t="inlineStr">
         <is>
-          <t>https://therealdeal.com/texas/houston/2023/11/13/pagewood-wile-to-convert-eado-houston-warehouses/</t>
+          <t>https://investor.drhorton.com/corporate-governance/executive-officers</t>
         </is>
       </c>
       <c r="X203" s="6" t="inlineStr"/>
@@ -22046,7 +22046,7 @@
     <row r="204">
       <c r="A204" s="12" t="inlineStr">
         <is>
-          <t>Paul J. Romanowski</t>
+          <t>Michael J. Murray</t>
         </is>
       </c>
       <c r="B204" s="12" t="inlineStr">
@@ -22056,7 +22056,7 @@
       </c>
       <c r="C204" s="12" t="inlineStr">
         <is>
-          <t>President and Chief Executive Officer</t>
+          <t>Executive Vice President and Chief Operating Officer</t>
         </is>
       </c>
       <c r="D204" s="13" t="inlineStr">
@@ -22119,7 +22119,7 @@
       </c>
       <c r="P204" s="10" t="inlineStr"/>
       <c r="Q204" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Paul%20J.%20Romanowski%20D.R.%20Horton%2C%20Inc.","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Michael%20J.%20Murray%20D.R.%20Horton%2C%20Inc.","search")</f>
         <v/>
       </c>
       <c r="R204" s="16">
@@ -22150,7 +22150,7 @@
     <row r="205">
       <c r="A205" s="6" t="inlineStr">
         <is>
-          <t>Michael J. Murray</t>
+          <t>Brad Conlon</t>
         </is>
       </c>
       <c r="B205" s="6" t="inlineStr">
@@ -22160,7 +22160,7 @@
       </c>
       <c r="C205" s="6" t="inlineStr">
         <is>
-          <t>Executive Vice President and Chief Operating Officer</t>
+          <t>Senior Vice President of Business Development</t>
         </is>
       </c>
       <c r="D205" s="7" t="inlineStr">
@@ -22223,7 +22223,7 @@
       </c>
       <c r="P205" s="10" t="inlineStr"/>
       <c r="Q205" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Michael%20J.%20Murray%20D.R.%20Horton%2C%20Inc.","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Brad%20Conlon%20D.R.%20Horton%2C%20Inc.","search")</f>
         <v/>
       </c>
       <c r="R205" s="11">
@@ -22240,11 +22240,19 @@
           <t>It has already bought equity in a printed wall system, and it builds more houses in Houston than anyone else.</t>
         </is>
       </c>
-      <c r="U205" s="6" t="inlineStr"/>
-      <c r="V205" s="9" t="inlineStr"/>
+      <c r="U205" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="V205" s="9" t="inlineStr">
+        <is>
+          <t>The seat that spoke for the company on the Apis Cor investment. He is not one of the four executive officers, so this sits below the officer tier.</t>
+        </is>
+      </c>
       <c r="W205" s="6" t="inlineStr">
         <is>
-          <t>https://investor.drhorton.com/corporate-governance/executive-officers</t>
+          <t>https://www.prnewswire.com/news-releases/apis-cor-a-manufacturer-of-construction-3d-printing-robots-announces-strategic-investment-by-dr-horton-302084850.html</t>
         </is>
       </c>
       <c r="X205" s="6" t="inlineStr"/>
@@ -22254,17 +22262,17 @@
     <row r="206">
       <c r="A206" s="12" t="inlineStr">
         <is>
-          <t>Brad Conlon</t>
+          <t>Saun Sullivan</t>
         </is>
       </c>
       <c r="B206" s="12" t="inlineStr">
         <is>
-          <t>D.R. Horton, Inc.</t>
+          <t>DSLD Homes</t>
         </is>
       </c>
       <c r="C206" s="12" t="inlineStr">
         <is>
-          <t>Senior Vice President of Business Development</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="D206" s="13" t="inlineStr">
@@ -22273,7 +22281,7 @@
         </is>
       </c>
       <c r="E206" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F206" s="12" t="inlineStr">
         <is>
@@ -22282,12 +22290,12 @@
       </c>
       <c r="G206" s="12" t="inlineStr">
         <is>
-          <t>Arlington HQ / Sugar Land, Richmond, Conroe</t>
+          <t>Baton Rouge HQ / Bonney, Magnolia, Montgomery</t>
         </is>
       </c>
       <c r="H206" s="12" t="inlineStr">
         <is>
-          <t>372 Houston permits in August 2026, first in the metro</t>
+          <t>3,989 closings in 2025, three Houston communities</t>
         </is>
       </c>
       <c r="I206" s="14" t="inlineStr">
@@ -22297,7 +22305,7 @@
       </c>
       <c r="J206" s="15" t="inlineStr">
         <is>
-          <t>65 Houston communities and 668 standing homes at one time, on a national plan library.</t>
+          <t>Three Houston communities drawn from a plan library that runs across six states.</t>
         </is>
       </c>
       <c r="K206" s="14" t="inlineStr">
@@ -22307,17 +22315,17 @@
       </c>
       <c r="L206" s="15" t="inlineStr">
         <is>
-          <t>84,863 closings a year is far above the band one or two printers cover, so the first order is a pilot inside one division rather than a purchase.</t>
+          <t>3,989 closings a year sits above the band one or two printers cover. The Houston division is three communities of it.</t>
         </is>
       </c>
       <c r="M206" s="14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N206" s="15" t="inlineStr">
         <is>
-          <t>Strategic investment in Apis Cor, March 2024, amount undisclosed. It is the only equity position in a printed wall system on this deck.</t>
+          <t>Nothing on record. Its about page names energy efficiency and structural excellence and no method.</t>
         </is>
       </c>
       <c r="O206" s="14" t="inlineStr">
@@ -22327,7 +22335,7 @@
       </c>
       <c r="P206" s="10" t="inlineStr"/>
       <c r="Q206" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Brad%20Conlon%20D.R.%20Horton%2C%20Inc.","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Saun%20Sullivan%20DSLD%20Homes","search")</f>
         <v/>
       </c>
       <c r="R206" s="16">
@@ -22336,27 +22344,19 @@
       </c>
       <c r="S206" s="12" t="inlineStr">
         <is>
-          <t>https://www.drhorton.com/texas/houston</t>
+          <t>https://www.dsldhomes.com/</t>
         </is>
       </c>
       <c r="T206" s="15" t="inlineStr">
         <is>
-          <t>It has already bought equity in a printed wall system, and it builds more houses in Houston than anyone else.</t>
-        </is>
-      </c>
-      <c r="U206" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="V206" s="15" t="inlineStr">
-        <is>
-          <t>The seat that spoke for the company on the Apis Cor investment. He is not one of the four executive officers, so this sits below the officer tier.</t>
-        </is>
-      </c>
+          <t>Three Houston communities opened out of a 120-community plan library, and a build-to-rent line inside it.</t>
+        </is>
+      </c>
+      <c r="U206" s="12" t="inlineStr"/>
+      <c r="V206" s="15" t="inlineStr"/>
       <c r="W206" s="12" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/apis-cor-a-manufacturer-of-construction-3d-printing-robots-announces-strategic-investment-by-dr-horton-302084850.html</t>
+          <t>https://www.builderonline.com/firms/dsld-homes/</t>
         </is>
       </c>
       <c r="X206" s="12" t="inlineStr"/>
@@ -22366,12 +22366,12 @@
     <row r="207">
       <c r="A207" s="6" t="inlineStr">
         <is>
-          <t>Saun Sullivan</t>
+          <t>Jay Brown</t>
         </is>
       </c>
       <c r="B207" s="6" t="inlineStr">
         <is>
-          <t>DSLD Homes</t>
+          <t>David Weekley Homes</t>
         </is>
       </c>
       <c r="C207" s="6" t="inlineStr">
@@ -22394,12 +22394,12 @@
       </c>
       <c r="G207" s="6" t="inlineStr">
         <is>
-          <t>Baton Rouge HQ / Bonney, Magnolia, Montgomery</t>
+          <t>Houston HQ, Harris County</t>
         </is>
       </c>
       <c r="H207" s="6" t="inlineStr">
         <is>
-          <t>3,989 closings in 2025, three Houston communities</t>
+          <t>125,000+ homes, 19 markets, Houston HQ</t>
         </is>
       </c>
       <c r="I207" s="8" t="inlineStr">
@@ -22409,68 +22409,77 @@
       </c>
       <c r="J207" s="9" t="inlineStr">
         <is>
-          <t>Three Houston communities drawn from a plan library that runs across six states.</t>
+          <t>Houston is the firm's home market and it builds across the metro.</t>
         </is>
       </c>
       <c r="K207" s="8" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L207" s="9" t="inlineStr">
         <is>
-          <t>3,989 closings a year sits above the band one or two printers cover. The Houston division is three communities of it.</t>
+          <t>A national builder with a national supply chain.</t>
         </is>
       </c>
       <c r="M207" s="8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partly</t>
         </is>
       </c>
       <c r="N207" s="9" t="inlineStr">
         <is>
-          <t>Nothing on record. Its about page names energy efficiency and structural excellence and no method.</t>
+          <t>Its 2026 preferred-partner list names cladding, roofing, weather barrier, structural connectors and engineered framing. That is the envelope, and it is a supply-chain commitment rather than a method.</t>
         </is>
       </c>
       <c r="O207" s="8" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P207" s="10" t="inlineStr"/>
-      <c r="Q207" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Saun%20Sullivan%20DSLD%20Homes","search")</f>
-        <v/>
-      </c>
+          <t>Partly</t>
+        </is>
+      </c>
+      <c r="P207" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jay-brown-14305a12/</t>
+        </is>
+      </c>
+      <c r="Q207" s="6" t="inlineStr"/>
       <c r="R207" s="11">
         <f>IF(P207="","ADD LINKEDIN","ok")</f>
         <v/>
       </c>
       <c r="S207" s="6" t="inlineStr">
         <is>
-          <t>https://www.dsldhomes.com/</t>
+          <t>https://www.davidweekleyhomes.com/</t>
         </is>
       </c>
       <c r="T207" s="9" t="inlineStr">
         <is>
-          <t>Three Houston communities opened out of a 120-community plan library, and a build-to-rent line inside it.</t>
+          <t>125,000 homes, Houston HQ, 50 years. Its supplier recognition covers insulation and fire-stopping, not the envelope.</t>
         </is>
       </c>
       <c r="U207" s="6" t="inlineStr"/>
-      <c r="V207" s="9" t="inlineStr"/>
-      <c r="W207" s="6" t="inlineStr">
-        <is>
-          <t>https://www.builderonline.com/firms/dsld-homes/</t>
-        </is>
-      </c>
-      <c r="X207" s="6" t="inlineStr"/>
-      <c r="Y207" s="6" t="inlineStr"/>
+      <c r="V207" s="9" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer at David Weekley Homes. Houston, Texas.</t>
+        </is>
+      </c>
+      <c r="W207" s="6" t="inlineStr"/>
+      <c r="X207" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/david-weekley-homes</t>
+        </is>
+      </c>
+      <c r="Y207" s="6" t="inlineStr">
+        <is>
+          <t>https://www.davidweekleyhomes.com/about-us/meet-the-team</t>
+        </is>
+      </c>
       <c r="Z207" s="6" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="12" t="inlineStr">
         <is>
-          <t>Jay Brown</t>
+          <t>Chris Weekley</t>
         </is>
       </c>
       <c r="B208" s="12" t="inlineStr">
@@ -22480,7 +22489,7 @@
       </c>
       <c r="C208" s="12" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>President and Vice Chairman</t>
         </is>
       </c>
       <c r="D208" s="13" t="inlineStr">
@@ -22541,12 +22550,11 @@
           <t>Partly</t>
         </is>
       </c>
-      <c r="P208" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/jay-brown-14305a12/</t>
-        </is>
-      </c>
-      <c r="Q208" s="12" t="inlineStr"/>
+      <c r="P208" s="10" t="inlineStr"/>
+      <c r="Q208" s="12">
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Chris%20Weekley%20David%20Weekley%20Homes","search")</f>
+        <v/>
+      </c>
       <c r="R208" s="16">
         <f>IF(P208="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -22564,10 +22572,14 @@
       <c r="U208" s="12" t="inlineStr"/>
       <c r="V208" s="15" t="inlineStr">
         <is>
-          <t>Chief Executive Officer at David Weekley Homes. Houston, Texas.</t>
-        </is>
-      </c>
-      <c r="W208" s="12" t="inlineStr"/>
+          <t>President and Vice Chairman. The firm's own page credits him with innovation and developer relationships, which is the brief a printed wall would land in.</t>
+        </is>
+      </c>
+      <c r="W208" s="12" t="inlineStr">
+        <is>
+          <t>https://www.davidweekleyhomes.com/about-us/meet-the-team</t>
+        </is>
+      </c>
       <c r="X208" s="12" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/david-weekley-homes</t>
@@ -22583,7 +22595,7 @@
     <row r="209">
       <c r="A209" s="6" t="inlineStr">
         <is>
-          <t>Chris Weekley</t>
+          <t>David Weekley</t>
         </is>
       </c>
       <c r="B209" s="6" t="inlineStr">
@@ -22593,7 +22605,7 @@
       </c>
       <c r="C209" s="6" t="inlineStr">
         <is>
-          <t>President and Vice Chairman</t>
+          <t>Chairman and Founder</t>
         </is>
       </c>
       <c r="D209" s="7" t="inlineStr">
@@ -22656,7 +22668,7 @@
       </c>
       <c r="P209" s="10" t="inlineStr"/>
       <c r="Q209" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Chris%20Weekley%20David%20Weekley%20Homes","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=David%20Weekley%20David%20Weekley%20Homes","search")</f>
         <v/>
       </c>
       <c r="R209" s="11">
@@ -22676,7 +22688,7 @@
       <c r="U209" s="6" t="inlineStr"/>
       <c r="V209" s="9" t="inlineStr">
         <is>
-          <t>President and Vice Chairman. The firm's own page credits him with innovation and developer relationships, which is the brief a printed wall would land in.</t>
+          <t>Chairman, who started the company in 1976 at twenty-three.</t>
         </is>
       </c>
       <c r="W209" s="6" t="inlineStr">
@@ -22699,7 +22711,7 @@
     <row r="210">
       <c r="A210" s="12" t="inlineStr">
         <is>
-          <t>David Weekley</t>
+          <t>John Schiegg</t>
         </is>
       </c>
       <c r="B210" s="12" t="inlineStr">
@@ -22709,7 +22721,7 @@
       </c>
       <c r="C210" s="12" t="inlineStr">
         <is>
-          <t>Chairman and Founder</t>
+          <t>Vice President of Purchasing and Supply Chain, David Weekley Homes</t>
         </is>
       </c>
       <c r="D210" s="13" t="inlineStr">
@@ -22770,11 +22782,12 @@
           <t>Partly</t>
         </is>
       </c>
-      <c r="P210" s="10" t="inlineStr"/>
-      <c r="Q210" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=David%20Weekley%20David%20Weekley%20Homes","search")</f>
-        <v/>
-      </c>
+      <c r="P210" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/john-schiegg-7593996/</t>
+        </is>
+      </c>
+      <c r="Q210" s="12" t="inlineStr"/>
       <c r="R210" s="16">
         <f>IF(P210="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -22789,15 +22802,19 @@
           <t>125,000 homes, Houston HQ, 50 years. Its supplier recognition covers insulation and fire-stopping, not the envelope.</t>
         </is>
       </c>
-      <c r="U210" s="12" t="inlineStr"/>
+      <c r="U210" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
       <c r="V210" s="15" t="inlineStr">
         <is>
-          <t>Chairman, who started the company in 1976 at twenty-three.</t>
+          <t>Profile opened. Company line reads David Weekley Homes, Houston, Texas. He owns purchasing and supply chain for the largest privately held builder in the country.</t>
         </is>
       </c>
       <c r="W210" s="12" t="inlineStr">
         <is>
-          <t>https://www.davidweekleyhomes.com/about-us/meet-the-team</t>
+          <t>https://www.prnewswire.com/news-releases/david-weekley-homes-announces-2026-national-preferred-partners-302809074.html</t>
         </is>
       </c>
       <c r="X210" s="12" t="inlineStr">
@@ -22815,7 +22832,7 @@
     <row r="211">
       <c r="A211" s="6" t="inlineStr">
         <is>
-          <t>John Schiegg</t>
+          <t>Ladd Fargo</t>
         </is>
       </c>
       <c r="B211" s="6" t="inlineStr">
@@ -22825,7 +22842,7 @@
       </c>
       <c r="C211" s="6" t="inlineStr">
         <is>
-          <t>Vice President of Purchasing and Supply Chain, David Weekley Homes</t>
+          <t>Chief Operating Officer, David Weekley Homes</t>
         </is>
       </c>
       <c r="D211" s="7" t="inlineStr">
@@ -22888,7 +22905,7 @@
       </c>
       <c r="P211" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/john-schiegg-7593996/</t>
+          <t>https://www.linkedin.com/in/ladd-fargo-241a47259/</t>
         </is>
       </c>
       <c r="Q211" s="6" t="inlineStr"/>
@@ -22906,21 +22923,9 @@
           <t>125,000 homes, Houston HQ, 50 years. Its supplier recognition covers insulation and fire-stopping, not the envelope.</t>
         </is>
       </c>
-      <c r="U211" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="V211" s="9" t="inlineStr">
-        <is>
-          <t>Profile opened. Company line reads David Weekley Homes, Houston, Texas. He owns purchasing and supply chain for the largest privately held builder in the country.</t>
-        </is>
-      </c>
-      <c r="W211" s="6" t="inlineStr">
-        <is>
-          <t>https://www.prnewswire.com/news-releases/david-weekley-homes-announces-2026-national-preferred-partners-302809074.html</t>
-        </is>
-      </c>
+      <c r="U211" s="6" t="inlineStr"/>
+      <c r="V211" s="9" t="inlineStr"/>
+      <c r="W211" s="6" t="inlineStr"/>
       <c r="X211" s="6" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/david-weekley-homes</t>
@@ -22936,17 +22941,17 @@
     <row r="212">
       <c r="A212" s="12" t="inlineStr">
         <is>
-          <t>Ladd Fargo</t>
+          <t>Eric Lipar</t>
         </is>
       </c>
       <c r="B212" s="12" t="inlineStr">
         <is>
-          <t>David Weekley Homes</t>
+          <t>LGI Homes, Inc.</t>
         </is>
       </c>
       <c r="C212" s="12" t="inlineStr">
         <is>
-          <t>Chief Operating Officer, David Weekley Homes</t>
+          <t>Chief Executive Officer and Chairman of the Board</t>
         </is>
       </c>
       <c r="D212" s="13" t="inlineStr">
@@ -22955,7 +22960,7 @@
         </is>
       </c>
       <c r="E212" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F212" s="12" t="inlineStr">
         <is>
@@ -22964,12 +22969,12 @@
       </c>
       <c r="G212" s="12" t="inlineStr">
         <is>
-          <t>Houston HQ, Harris County</t>
+          <t>The Woodlands HQ, Montgomery County</t>
         </is>
       </c>
       <c r="H212" s="12" t="inlineStr">
         <is>
-          <t>125,000+ homes, 19 markets, Houston HQ</t>
+          <t>153 active selling communities, 36 markets, 21 states</t>
         </is>
       </c>
       <c r="I212" s="14" t="inlineStr">
@@ -22979,7 +22984,7 @@
       </c>
       <c r="J212" s="15" t="inlineStr">
         <is>
-          <t>Houston is the firm's home market and it builds across the metro.</t>
+          <t>153 active selling communities on one systematic plan set.</t>
         </is>
       </c>
       <c r="K212" s="14" t="inlineStr">
@@ -22989,55 +22994,58 @@
       </c>
       <c r="L212" s="15" t="inlineStr">
         <is>
-          <t>A national builder with a national supply chain.</t>
+          <t>Thousands of closings a year across 36 markets in 21 states.</t>
         </is>
       </c>
       <c r="M212" s="14" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N212" s="15" t="inlineStr">
         <is>
-          <t>Its 2026 preferred-partner list names cladding, roofing, weather barrier, structural connectors and engineered framing. That is the envelope, and it is a supply-chain commitment rather than a method.</t>
+          <t>Nothing on record.</t>
         </is>
       </c>
       <c r="O212" s="14" t="inlineStr">
         <is>
-          <t>Partly</t>
-        </is>
-      </c>
-      <c r="P212" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/ladd-fargo-241a47259/</t>
-        </is>
-      </c>
-      <c r="Q212" s="12" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P212" s="10" t="inlineStr"/>
+      <c r="Q212" s="12">
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Eric%20Lipar%20LGI%20Homes%2C%20Inc.","search")</f>
+        <v/>
+      </c>
       <c r="R212" s="16">
         <f>IF(P212="","ADD LINKEDIN","ok")</f>
         <v/>
       </c>
       <c r="S212" s="12" t="inlineStr">
         <is>
-          <t>https://www.davidweekleyhomes.com/</t>
+          <t>https://www.lgihomes.com/</t>
         </is>
       </c>
       <c r="T212" s="15" t="inlineStr">
         <is>
-          <t>125,000 homes, Houston HQ, 50 years. Its supplier recognition covers insulation and fire-stopping, not the envelope.</t>
+          <t>The most standardised product here, headquartered in the metro. Its Q2 2026 call mentions method, labour and cycle time zero times.</t>
         </is>
       </c>
       <c r="U212" s="12" t="inlineStr"/>
       <c r="V212" s="15" t="inlineStr"/>
-      <c r="W212" s="12" t="inlineStr"/>
+      <c r="W212" s="12" t="inlineStr">
+        <is>
+          <t>https://investor.lgihomes.com/corporate-governance/management</t>
+        </is>
+      </c>
       <c r="X212" s="12" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/david-weekley-homes</t>
+          <t>https://www.linkedin.com/company/lgi-homes</t>
         </is>
       </c>
       <c r="Y212" s="12" t="inlineStr">
         <is>
-          <t>https://www.davidweekleyhomes.com/about-us/meet-the-team</t>
+          <t>https://investor.lgihomes.com/corporate-governance/management</t>
         </is>
       </c>
       <c r="Z212" s="12" t="inlineStr"/>
@@ -23045,7 +23053,7 @@
     <row r="213">
       <c r="A213" s="6" t="inlineStr">
         <is>
-          <t>Eric Lipar</t>
+          <t>Mike Snider</t>
         </is>
       </c>
       <c r="B213" s="6" t="inlineStr">
@@ -23055,7 +23063,7 @@
       </c>
       <c r="C213" s="6" t="inlineStr">
         <is>
-          <t>Chief Executive Officer and Chairman of the Board</t>
+          <t>President and Chief Operating Officer</t>
         </is>
       </c>
       <c r="D213" s="7" t="inlineStr">
@@ -23118,7 +23126,7 @@
       </c>
       <c r="P213" s="10" t="inlineStr"/>
       <c r="Q213" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Eric%20Lipar%20LGI%20Homes%2C%20Inc.","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Mike%20Snider%20LGI%20Homes%2C%20Inc.","search")</f>
         <v/>
       </c>
       <c r="R213" s="11">
@@ -23157,7 +23165,7 @@
     <row r="214">
       <c r="A214" s="12" t="inlineStr">
         <is>
-          <t>Mike Snider</t>
+          <t>Charles Merdian</t>
         </is>
       </c>
       <c r="B214" s="12" t="inlineStr">
@@ -23167,7 +23175,7 @@
       </c>
       <c r="C214" s="12" t="inlineStr">
         <is>
-          <t>President and Chief Operating Officer</t>
+          <t>Chief Financial Officer and Treasurer</t>
         </is>
       </c>
       <c r="D214" s="13" t="inlineStr">
@@ -23230,7 +23238,7 @@
       </c>
       <c r="P214" s="10" t="inlineStr"/>
       <c r="Q214" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Mike%20Snider%20LGI%20Homes%2C%20Inc.","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Charles%20Merdian%20LGI%20Homes%2C%20Inc.","search")</f>
         <v/>
       </c>
       <c r="R214" s="16">
@@ -23269,7 +23277,7 @@
     <row r="215">
       <c r="A215" s="6" t="inlineStr">
         <is>
-          <t>Charles Merdian</t>
+          <t>Chuck Collier</t>
         </is>
       </c>
       <c r="B215" s="6" t="inlineStr">
@@ -23279,7 +23287,7 @@
       </c>
       <c r="C215" s="6" t="inlineStr">
         <is>
-          <t>Chief Financial Officer and Treasurer</t>
+          <t>Vice President of Construction, Houston, LGI Homes</t>
         </is>
       </c>
       <c r="D215" s="7" t="inlineStr">
@@ -23340,11 +23348,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P215" s="10" t="inlineStr"/>
-      <c r="Q215" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Charles%20Merdian%20LGI%20Homes%2C%20Inc.","search")</f>
-        <v/>
-      </c>
+      <c r="P215" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/chuck-collier-48286829/</t>
+        </is>
+      </c>
+      <c r="Q215" s="6" t="inlineStr"/>
       <c r="R215" s="11">
         <f>IF(P215="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -23359,13 +23368,17 @@
           <t>The most standardised product here, headquartered in the metro. Its Q2 2026 call mentions method, labour and cycle time zero times.</t>
         </is>
       </c>
-      <c r="U215" s="6" t="inlineStr"/>
-      <c r="V215" s="9" t="inlineStr"/>
-      <c r="W215" s="6" t="inlineStr">
-        <is>
-          <t>https://investor.lgihomes.com/corporate-governance/management</t>
-        </is>
-      </c>
+      <c r="U215" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="V215" s="9" t="inlineStr">
+        <is>
+          <t>VP of Construction, Houston, LGI Homes, stated in his own headline. Location shows only United States.</t>
+        </is>
+      </c>
+      <c r="W215" s="6" t="inlineStr"/>
       <c r="X215" s="6" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/lgi-homes</t>
@@ -23381,7 +23394,7 @@
     <row r="216">
       <c r="A216" s="12" t="inlineStr">
         <is>
-          <t>Chuck Collier</t>
+          <t>Kyle Hanna</t>
         </is>
       </c>
       <c r="B216" s="12" t="inlineStr">
@@ -23391,7 +23404,7 @@
       </c>
       <c r="C216" s="12" t="inlineStr">
         <is>
-          <t>Vice President of Construction, Houston, LGI Homes</t>
+          <t>Vice President of Purchasing, LGI Homes</t>
         </is>
       </c>
       <c r="D216" s="13" t="inlineStr">
@@ -23454,7 +23467,7 @@
       </c>
       <c r="P216" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/chuck-collier-48286829/</t>
+          <t>https://www.linkedin.com/in/kylemhanna/</t>
         </is>
       </c>
       <c r="Q216" s="12" t="inlineStr"/>
@@ -23479,7 +23492,7 @@
       </c>
       <c r="V216" s="15" t="inlineStr">
         <is>
-          <t>VP of Construction, Houston, LGI Homes, stated in his own headline. Location shows only United States.</t>
+          <t>Vice President of Purchasing at LGI Homes. Conroe, Texas, which is the head office. The construction vice presidents sit in the markets, Austin, San Antonio, Nashville, Denver, Seattle; purchasing is the one that sits in Greater Houston.</t>
         </is>
       </c>
       <c r="W216" s="12" t="inlineStr"/>
@@ -23498,17 +23511,17 @@
     <row r="217">
       <c r="A217" s="6" t="inlineStr">
         <is>
-          <t>Kyle Hanna</t>
+          <t>Bob Schottenstein</t>
         </is>
       </c>
       <c r="B217" s="6" t="inlineStr">
         <is>
-          <t>LGI Homes, Inc.</t>
+          <t>M/I Homes, Inc.</t>
         </is>
       </c>
       <c r="C217" s="6" t="inlineStr">
         <is>
-          <t>Vice President of Purchasing, LGI Homes</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="D217" s="7" t="inlineStr">
@@ -23526,12 +23539,12 @@
       </c>
       <c r="G217" s="6" t="inlineStr">
         <is>
-          <t>The Woodlands HQ, Montgomery County</t>
+          <t>Columbus HQ / Liberty, Harris</t>
         </is>
       </c>
       <c r="H217" s="6" t="inlineStr">
         <is>
-          <t>153 active selling communities, 36 markets, 21 states</t>
+          <t>3 Houston land deals in 6 months</t>
         </is>
       </c>
       <c r="I217" s="8" t="inlineStr">
@@ -23541,7 +23554,7 @@
       </c>
       <c r="J217" s="9" t="inlineStr">
         <is>
-          <t>153 active selling communities on one systematic plan set.</t>
+          <t>1,000 homes at Trinity Landing, three Houston land deals in six months.</t>
         </is>
       </c>
       <c r="K217" s="8" t="inlineStr">
@@ -23551,7 +23564,7 @@
       </c>
       <c r="L217" s="9" t="inlineStr">
         <is>
-          <t>Thousands of closings a year across 36 markets in 21 states.</t>
+          <t>A national builder, bought centrally, however good the Houston division is.</t>
         </is>
       </c>
       <c r="M217" s="8" t="inlineStr">
@@ -23561,7 +23574,7 @@
       </c>
       <c r="N217" s="9" t="inlineStr">
         <is>
-          <t>Nothing on record.</t>
+          <t>The CEO cites shorter cycle time but not what enabled it.</t>
         </is>
       </c>
       <c r="O217" s="8" t="inlineStr">
@@ -23569,45 +23582,44 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P217" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/kylemhanna/</t>
-        </is>
-      </c>
-      <c r="Q217" s="6" t="inlineStr"/>
+      <c r="P217" s="10" t="inlineStr"/>
+      <c r="Q217" s="6">
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Bob%20Schottenstein%20M/I%20Homes%2C%20Inc.","search")</f>
+        <v/>
+      </c>
       <c r="R217" s="11">
         <f>IF(P217="","ADD LINKEDIN","ok")</f>
         <v/>
       </c>
       <c r="S217" s="6" t="inlineStr">
         <is>
-          <t>https://www.lgihomes.com/</t>
+          <t>https://www.mihomes.com/</t>
         </is>
       </c>
       <c r="T217" s="9" t="inlineStr">
         <is>
-          <t>The most standardised product here, headquartered in the metro. Its Q2 2026 call mentions method, labour and cycle time zero times.</t>
-        </is>
-      </c>
-      <c r="U217" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+          <t>1,000 homes at Trinity Landing and three Houston land deals in six months under a named division president.</t>
+        </is>
+      </c>
+      <c r="U217" s="6" t="inlineStr"/>
       <c r="V217" s="9" t="inlineStr">
         <is>
-          <t>Vice President of Purchasing at LGI Homes. Conroe, Texas, which is the head office. The construction vice presidents sit in the markets, Austin, San Antonio, Nashville, Denver, Seattle; purchasing is the one that sits in Greater Houston.</t>
-        </is>
-      </c>
-      <c r="W217" s="6" t="inlineStr"/>
+          <t>Chairman, and Chief Executive Officer since January 2004, on M/I's own officers page.</t>
+        </is>
+      </c>
+      <c r="W217" s="6" t="inlineStr">
+        <is>
+          <t>https://investors.mihomes.com/investor-relations/officers-directors/default.aspx</t>
+        </is>
+      </c>
       <c r="X217" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/lgi-homes</t>
+          <t>https://www.linkedin.com/company/mihomes/</t>
         </is>
       </c>
       <c r="Y217" s="6" t="inlineStr">
         <is>
-          <t>https://investor.lgihomes.com/corporate-governance/management</t>
+          <t>https://investors.mihomes.com/investor-relations/officers-directors/default.aspx</t>
         </is>
       </c>
       <c r="Z217" s="6" t="inlineStr"/>
@@ -23615,7 +23627,7 @@
     <row r="218">
       <c r="A218" s="12" t="inlineStr">
         <is>
-          <t>Bob Schottenstein</t>
+          <t>Jay McManus</t>
         </is>
       </c>
       <c r="B218" s="12" t="inlineStr">
@@ -23625,7 +23637,7 @@
       </c>
       <c r="C218" s="12" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Houston Division President</t>
         </is>
       </c>
       <c r="D218" s="13" t="inlineStr">
@@ -23688,7 +23700,7 @@
       </c>
       <c r="P218" s="10" t="inlineStr"/>
       <c r="Q218" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Bob%20Schottenstein%20M/I%20Homes%2C%20Inc.","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Jay%20McManus%20M/I%20Homes%2C%20Inc.","search")</f>
         <v/>
       </c>
       <c r="R218" s="16">
@@ -23708,12 +23720,12 @@
       <c r="U218" s="12" t="inlineStr"/>
       <c r="V218" s="15" t="inlineStr">
         <is>
-          <t>Chairman, and Chief Executive Officer since January 2004, on M/I's own officers page.</t>
+          <t>Named Houston division president for M/I Homes in trade coverage of the division's expansion. M/I's own site names corporate officers only.</t>
         </is>
       </c>
       <c r="W218" s="12" t="inlineStr">
         <is>
-          <t>https://investors.mihomes.com/investor-relations/officers-directors/default.aspx</t>
+          <t>https://houstonagentmagazine.com/2021/08/23/m-i-homes-to-double-presence-in-houston-area/</t>
         </is>
       </c>
       <c r="X218" s="12" t="inlineStr">
@@ -23731,7 +23743,7 @@
     <row r="219">
       <c r="A219" s="6" t="inlineStr">
         <is>
-          <t>Jay McManus</t>
+          <t>Patrick Mayhan</t>
         </is>
       </c>
       <c r="B219" s="6" t="inlineStr">
@@ -23741,7 +23753,7 @@
       </c>
       <c r="C219" s="6" t="inlineStr">
         <is>
-          <t>Houston Division President</t>
+          <t>Vice President of Purchasing, M/I Homes</t>
         </is>
       </c>
       <c r="D219" s="7" t="inlineStr">
@@ -23802,11 +23814,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P219" s="10" t="inlineStr"/>
-      <c r="Q219" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Jay%20McManus%20M/I%20Homes%2C%20Inc.","search")</f>
-        <v/>
-      </c>
+      <c r="P219" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/patrick-mayhan-5591478/</t>
+        </is>
+      </c>
+      <c r="Q219" s="6" t="inlineStr"/>
       <c r="R219" s="11">
         <f>IF(P219="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -23821,17 +23834,17 @@
           <t>1,000 homes at Trinity Landing and three Houston land deals in six months under a named division president.</t>
         </is>
       </c>
-      <c r="U219" s="6" t="inlineStr"/>
+      <c r="U219" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
       <c r="V219" s="9" t="inlineStr">
         <is>
-          <t>Named Houston division president for M/I Homes in trade coverage of the division's expansion. M/I's own site names corporate officers only.</t>
-        </is>
-      </c>
-      <c r="W219" s="6" t="inlineStr">
-        <is>
-          <t>https://houstonagentmagazine.com/2021/08/23/m-i-homes-to-double-presence-in-houston-area/</t>
-        </is>
-      </c>
+          <t>Vice President of Purchasing at M/I Homes, Inc. Houston, Texas. M/I lists two purchasing vice presidents in Houston; his title carries the corporate entity and Randy Barras's carries the Houston division.</t>
+        </is>
+      </c>
+      <c r="W219" s="6" t="inlineStr"/>
       <c r="X219" s="6" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/mihomes/</t>
@@ -23847,7 +23860,7 @@
     <row r="220">
       <c r="A220" s="12" t="inlineStr">
         <is>
-          <t>Patrick Mayhan</t>
+          <t>Randy Barras</t>
         </is>
       </c>
       <c r="B220" s="12" t="inlineStr">
@@ -23857,7 +23870,7 @@
       </c>
       <c r="C220" s="12" t="inlineStr">
         <is>
-          <t>Vice President of Purchasing, M/I Homes</t>
+          <t>Vice President of Purchasing, M/I Homes Houston</t>
         </is>
       </c>
       <c r="D220" s="13" t="inlineStr">
@@ -23920,7 +23933,7 @@
       </c>
       <c r="P220" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/patrick-mayhan-5591478/</t>
+          <t>https://www.linkedin.com/in/rbarras/</t>
         </is>
       </c>
       <c r="Q220" s="12" t="inlineStr"/>
@@ -23943,11 +23956,7 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="V220" s="15" t="inlineStr">
-        <is>
-          <t>Vice President of Purchasing at M/I Homes, Inc. Houston, Texas. M/I lists two purchasing vice presidents in Houston; his title carries the corporate entity and Randy Barras's carries the Houston division.</t>
-        </is>
-      </c>
+      <c r="V220" s="15" t="inlineStr"/>
       <c r="W220" s="12" t="inlineStr"/>
       <c r="X220" s="12" t="inlineStr">
         <is>
@@ -23964,17 +23973,17 @@
     <row r="221">
       <c r="A221" s="6" t="inlineStr">
         <is>
-          <t>Randy Barras</t>
+          <t>Darin Rowe</t>
         </is>
       </c>
       <c r="B221" s="6" t="inlineStr">
         <is>
-          <t>M/I Homes, Inc.</t>
+          <t>Taylor Morrison Home Corporation</t>
         </is>
       </c>
       <c r="C221" s="6" t="inlineStr">
         <is>
-          <t>Vice President of Purchasing, M/I Homes Houston</t>
+          <t>National President, Build-to-Rent</t>
         </is>
       </c>
       <c r="D221" s="7" t="inlineStr">
@@ -23992,12 +24001,12 @@
       </c>
       <c r="G221" s="6" t="inlineStr">
         <is>
-          <t>Columbus HQ / Liberty, Harris</t>
+          <t>Scottsdale HQ / Harris County</t>
         </is>
       </c>
       <c r="H221" s="6" t="inlineStr">
         <is>
-          <t>3 Houston land deals in 6 months</t>
+          <t>240-home Houston BTR community</t>
         </is>
       </c>
       <c r="I221" s="8" t="inlineStr">
@@ -24007,7 +24016,7 @@
       </c>
       <c r="J221" s="9" t="inlineStr">
         <is>
-          <t>1,000 homes at Trinity Landing, three Houston land deals in six months.</t>
+          <t>A 240-home Houston build-to-rent community and a dedicated brand.</t>
         </is>
       </c>
       <c r="K221" s="8" t="inlineStr">
@@ -24017,7 +24026,7 @@
       </c>
       <c r="L221" s="9" t="inlineStr">
         <is>
-          <t>A national builder, bought centrally, however good the Houston division is.</t>
+          <t>A national builder with a national build-to-rent brand.</t>
         </is>
       </c>
       <c r="M221" s="8" t="inlineStr">
@@ -24027,7 +24036,7 @@
       </c>
       <c r="N221" s="9" t="inlineStr">
         <is>
-          <t>The CEO cites shorter cycle time but not what enabled it.</t>
+          <t>Its Yardly retrospective cites input costs with no method detail.</t>
         </is>
       </c>
       <c r="O221" s="8" t="inlineStr">
@@ -24035,41 +24044,44 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P221" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/rbarras/</t>
-        </is>
-      </c>
-      <c r="Q221" s="6" t="inlineStr"/>
+      <c r="P221" s="10" t="inlineStr"/>
+      <c r="Q221" s="6">
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Darin%20Rowe%20Taylor%20Morrison%20Home%20Corporation","search")</f>
+        <v/>
+      </c>
       <c r="R221" s="11">
         <f>IF(P221="","ADD LINKEDIN","ok")</f>
         <v/>
       </c>
       <c r="S221" s="6" t="inlineStr">
         <is>
-          <t>https://www.mihomes.com/</t>
+          <t>https://www.taylormorrison.com/</t>
         </is>
       </c>
       <c r="T221" s="9" t="inlineStr">
         <is>
-          <t>1,000 homes at Trinity Landing and three Houston land deals in six months under a named division president.</t>
-        </is>
-      </c>
-      <c r="U221" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="V221" s="9" t="inlineStr"/>
-      <c r="W221" s="6" t="inlineStr"/>
+          <t>A 240-home Houston build-to-rent community and a dedicated brand. The division president role dates to 2018 and is unconfirmed.</t>
+        </is>
+      </c>
+      <c r="U221" s="6" t="inlineStr"/>
+      <c r="V221" s="9" t="inlineStr">
+        <is>
+          <t>Build-to-Rent President, quoted on the launch of the Yardly brand. National, not Houston.</t>
+        </is>
+      </c>
+      <c r="W221" s="6" t="inlineStr">
+        <is>
+          <t>https://newsroom.taylormorrison.com/2022-11-14-Taylor-Morrison-Unveils-New-Build-To-Rent-Brand,-Yardly</t>
+        </is>
+      </c>
       <c r="X221" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/mihomes/</t>
+          <t>https://www.linkedin.com/company/taylor-morrison</t>
         </is>
       </c>
       <c r="Y221" s="6" t="inlineStr">
         <is>
-          <t>https://investors.mihomes.com/investor-relations/officers-directors/default.aspx</t>
+          <t>https://newsroom.taylormorrison.com/Leadership</t>
         </is>
       </c>
       <c r="Z221" s="6" t="inlineStr"/>
@@ -24077,7 +24089,7 @@
     <row r="222">
       <c r="A222" s="12" t="inlineStr">
         <is>
-          <t>Darin Rowe</t>
+          <t>Amy Rino</t>
         </is>
       </c>
       <c r="B222" s="12" t="inlineStr">
@@ -24087,7 +24099,7 @@
       </c>
       <c r="C222" s="12" t="inlineStr">
         <is>
-          <t>National President, Build-to-Rent</t>
+          <t>Chief Customer Officer, Taylor Morrison, Scottsdale (2026); ex-Houston Division President</t>
         </is>
       </c>
       <c r="D222" s="13" t="inlineStr">
@@ -24148,11 +24160,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P222" s="10" t="inlineStr"/>
-      <c r="Q222" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Darin%20Rowe%20Taylor%20Morrison%20Home%20Corporation","search")</f>
-        <v/>
-      </c>
+      <c r="P222" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/amy-rino-5152b111/</t>
+        </is>
+      </c>
+      <c r="Q222" s="12" t="inlineStr"/>
       <c r="R222" s="16">
         <f>IF(P222="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -24170,14 +24183,10 @@
       <c r="U222" s="12" t="inlineStr"/>
       <c r="V222" s="15" t="inlineStr">
         <is>
-          <t>Build-to-Rent President, quoted on the launch of the Yardly brand. National, not Houston.</t>
-        </is>
-      </c>
-      <c r="W222" s="12" t="inlineStr">
-        <is>
-          <t>https://newsroom.taylormorrison.com/2022-11-14-Taylor-Morrison-Unveils-New-Build-To-Rent-Brand,-Yardly</t>
-        </is>
-      </c>
+          <t>Amy Rino is now Chief Customer Officer at Taylor Morrison in Scottsdale, not Houston division president. No current Houston division leader is identified.</t>
+        </is>
+      </c>
+      <c r="W222" s="12" t="inlineStr"/>
       <c r="X222" s="12" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/taylor-morrison</t>
@@ -24193,17 +24202,17 @@
     <row r="223">
       <c r="A223" s="6" t="inlineStr">
         <is>
-          <t>Amy Rino</t>
+          <t>Ken Balogh</t>
         </is>
       </c>
       <c r="B223" s="6" t="inlineStr">
         <is>
-          <t>Taylor Morrison Home Corporation</t>
+          <t>Ashton Woods Homes</t>
         </is>
       </c>
       <c r="C223" s="6" t="inlineStr">
         <is>
-          <t>Chief Customer Officer, Taylor Morrison, Scottsdale (2026); ex-Houston Division President</t>
+          <t>President and Chief Executive Officer</t>
         </is>
       </c>
       <c r="D223" s="7" t="inlineStr">
@@ -24221,12 +24230,12 @@
       </c>
       <c r="G223" s="6" t="inlineStr">
         <is>
-          <t>Scottsdale HQ / Harris County</t>
+          <t>Alpharetta HQ / Harris, Fort Bend</t>
         </is>
       </c>
       <c r="H223" s="6" t="inlineStr">
         <is>
-          <t>240-home Houston BTR community</t>
+          <t>14+ named Houston communities</t>
         </is>
       </c>
       <c r="I223" s="8" t="inlineStr">
@@ -24236,7 +24245,7 @@
       </c>
       <c r="J223" s="9" t="inlineStr">
         <is>
-          <t>A 240-home Houston build-to-rent community and a dedicated brand.</t>
+          <t>Fourteen named Houston communities.</t>
         </is>
       </c>
       <c r="K223" s="8" t="inlineStr">
@@ -24246,7 +24255,7 @@
       </c>
       <c r="L223" s="9" t="inlineStr">
         <is>
-          <t>A national builder with a national build-to-rent brand.</t>
+          <t>A national builder with a corporate purchasing function.</t>
         </is>
       </c>
       <c r="M223" s="8" t="inlineStr">
@@ -24256,49 +24265,48 @@
       </c>
       <c r="N223" s="9" t="inlineStr">
         <is>
-          <t>Its Yardly retrospective cites input costs with no method detail.</t>
+          <t>No firm-specific method evidence found.</t>
         </is>
       </c>
       <c r="O223" s="8" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P223" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/amy-rino-5152b111/</t>
-        </is>
-      </c>
-      <c r="Q223" s="6" t="inlineStr"/>
+          <t>Partly</t>
+        </is>
+      </c>
+      <c r="P223" s="10" t="inlineStr"/>
+      <c r="Q223" s="6">
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Ken%20Balogh%20Ashton%20Woods%20Homes","search")</f>
+        <v/>
+      </c>
       <c r="R223" s="11">
         <f>IF(P223="","ADD LINKEDIN","ok")</f>
         <v/>
       </c>
       <c r="S223" s="6" t="inlineStr">
         <is>
-          <t>https://www.taylormorrison.com/</t>
+          <t>https://www.ashtonwoods.com/</t>
         </is>
       </c>
       <c r="T223" s="9" t="inlineStr">
         <is>
-          <t>A 240-home Houston build-to-rent community and a dedicated brand. The division president role dates to 2018 and is unconfirmed.</t>
+          <t>14 named Houston communities and a Texas regional president.</t>
         </is>
       </c>
       <c r="U223" s="6" t="inlineStr"/>
-      <c r="V223" s="9" t="inlineStr">
-        <is>
-          <t>Amy Rino is now Chief Customer Officer at Taylor Morrison in Scottsdale, not Houston division president. No current Houston division leader is identified.</t>
-        </is>
-      </c>
-      <c r="W223" s="6" t="inlineStr"/>
+      <c r="V223" s="9" t="inlineStr"/>
+      <c r="W223" s="6" t="inlineStr">
+        <is>
+          <t>https://www.ashtonwoods.com/corporate-info</t>
+        </is>
+      </c>
       <c r="X223" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/taylor-morrison</t>
+          <t>https://www.linkedin.com/company/ashton-woods-homes</t>
         </is>
       </c>
       <c r="Y223" s="6" t="inlineStr">
         <is>
-          <t>https://newsroom.taylormorrison.com/Leadership</t>
+          <t>https://www.ashtonwoods.com/corporate-info</t>
         </is>
       </c>
       <c r="Z223" s="6" t="inlineStr"/>
@@ -24306,7 +24314,7 @@
     <row r="224">
       <c r="A224" s="12" t="inlineStr">
         <is>
-          <t>Ken Balogh</t>
+          <t>Lindsay Motley</t>
         </is>
       </c>
       <c r="B224" s="12" t="inlineStr">
@@ -24316,7 +24324,7 @@
       </c>
       <c r="C224" s="12" t="inlineStr">
         <is>
-          <t>President and Chief Executive Officer</t>
+          <t>Regional President</t>
         </is>
       </c>
       <c r="D224" s="13" t="inlineStr">
@@ -24379,7 +24387,7 @@
       </c>
       <c r="P224" s="10" t="inlineStr"/>
       <c r="Q224" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Ken%20Balogh%20Ashton%20Woods%20Homes","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Lindsay%20Motley%20Ashton%20Woods%20Homes","search")</f>
         <v/>
       </c>
       <c r="R224" s="16">
@@ -24397,7 +24405,11 @@
         </is>
       </c>
       <c r="U224" s="12" t="inlineStr"/>
-      <c r="V224" s="15" t="inlineStr"/>
+      <c r="V224" s="15" t="inlineStr">
+        <is>
+          <t>Regional President. The firm's own announcement names her Austin division president.</t>
+        </is>
+      </c>
       <c r="W224" s="12" t="inlineStr">
         <is>
           <t>https://www.ashtonwoods.com/corporate-info</t>
@@ -24418,7 +24430,7 @@
     <row r="225">
       <c r="A225" s="6" t="inlineStr">
         <is>
-          <t>Lindsay Motley</t>
+          <t>Ryan Lewis</t>
         </is>
       </c>
       <c r="B225" s="6" t="inlineStr">
@@ -24428,7 +24440,7 @@
       </c>
       <c r="C225" s="6" t="inlineStr">
         <is>
-          <t>Regional President</t>
+          <t>Chief Operating Officer</t>
         </is>
       </c>
       <c r="D225" s="7" t="inlineStr">
@@ -24491,7 +24503,7 @@
       </c>
       <c r="P225" s="10" t="inlineStr"/>
       <c r="Q225" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Lindsay%20Motley%20Ashton%20Woods%20Homes","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Ryan%20Lewis%20Ashton%20Woods%20Homes","search")</f>
         <v/>
       </c>
       <c r="R225" s="11">
@@ -24509,11 +24521,7 @@
         </is>
       </c>
       <c r="U225" s="6" t="inlineStr"/>
-      <c r="V225" s="9" t="inlineStr">
-        <is>
-          <t>Regional President. The firm's own announcement names her Austin division president.</t>
-        </is>
-      </c>
+      <c r="V225" s="9" t="inlineStr"/>
       <c r="W225" s="6" t="inlineStr">
         <is>
           <t>https://www.ashtonwoods.com/corporate-info</t>
@@ -24534,7 +24542,7 @@
     <row r="226">
       <c r="A226" s="12" t="inlineStr">
         <is>
-          <t>Ryan Lewis</t>
+          <t>Adam Weaver</t>
         </is>
       </c>
       <c r="B226" s="12" t="inlineStr">
@@ -24544,7 +24552,7 @@
       </c>
       <c r="C226" s="12" t="inlineStr">
         <is>
-          <t>Chief Operating Officer</t>
+          <t>Senior Vice President of Purchasing</t>
         </is>
       </c>
       <c r="D226" s="13" t="inlineStr">
@@ -24606,10 +24614,7 @@
         </is>
       </c>
       <c r="P226" s="10" t="inlineStr"/>
-      <c r="Q226" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Ryan%20Lewis%20Ashton%20Woods%20Homes","search")</f>
-        <v/>
-      </c>
+      <c r="Q226" s="12" t="inlineStr"/>
       <c r="R226" s="16">
         <f>IF(P226="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -24624,7 +24629,11 @@
           <t>14 named Houston communities and a Texas regional president.</t>
         </is>
       </c>
-      <c r="U226" s="12" t="inlineStr"/>
+      <c r="U226" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
       <c r="V226" s="15" t="inlineStr"/>
       <c r="W226" s="12" t="inlineStr">
         <is>
@@ -24646,7 +24655,7 @@
     <row r="227">
       <c r="A227" s="6" t="inlineStr">
         <is>
-          <t>Adam Weaver</t>
+          <t>Ken Newman</t>
         </is>
       </c>
       <c r="B227" s="6" t="inlineStr">
@@ -24656,7 +24665,7 @@
       </c>
       <c r="C227" s="6" t="inlineStr">
         <is>
-          <t>Senior Vice President of Purchasing</t>
+          <t>Senior Vice President of Construction Operations</t>
         </is>
       </c>
       <c r="D227" s="7" t="inlineStr">
@@ -24759,17 +24768,17 @@
     <row r="228">
       <c r="A228" s="12" t="inlineStr">
         <is>
-          <t>Ken Newman</t>
+          <t>Kathy Britton</t>
         </is>
       </c>
       <c r="B228" s="12" t="inlineStr">
         <is>
-          <t>Ashton Woods Homes</t>
+          <t>Perry Homes</t>
         </is>
       </c>
       <c r="C228" s="12" t="inlineStr">
         <is>
-          <t>Senior Vice President of Construction Operations</t>
+          <t>Owner and Executive Chair</t>
         </is>
       </c>
       <c r="D228" s="13" t="inlineStr">
@@ -24787,12 +24796,12 @@
       </c>
       <c r="G228" s="12" t="inlineStr">
         <is>
-          <t>Alpharetta HQ / Harris, Fort Bend</t>
+          <t>Houston HQ, Harris County</t>
         </is>
       </c>
       <c r="H228" s="12" t="inlineStr">
         <is>
-          <t>14+ named Houston communities</t>
+          <t>120+ communities, 65,000+ homes sold</t>
         </is>
       </c>
       <c r="I228" s="14" t="inlineStr">
@@ -24802,7 +24811,7 @@
       </c>
       <c r="J228" s="15" t="inlineStr">
         <is>
-          <t>Fourteen named Houston communities.</t>
+          <t>More than 120 communities and 65,000 homes, locally owned.</t>
         </is>
       </c>
       <c r="K228" s="14" t="inlineStr">
@@ -24812,7 +24821,7 @@
       </c>
       <c r="L228" s="15" t="inlineStr">
         <is>
-          <t>A national builder with a corporate purchasing function.</t>
+          <t>120 communities and thousands of closings a year, bought centrally.</t>
         </is>
       </c>
       <c r="M228" s="14" t="inlineStr">
@@ -24822,7 +24831,7 @@
       </c>
       <c r="N228" s="15" t="inlineStr">
         <is>
-          <t>No firm-specific method evidence found.</t>
+          <t>Its own published definition of innovation is smart-home features and floor plans.</t>
         </is>
       </c>
       <c r="O228" s="14" t="inlineStr">
@@ -24831,40 +24840,43 @@
         </is>
       </c>
       <c r="P228" s="10" t="inlineStr"/>
-      <c r="Q228" s="12" t="inlineStr"/>
+      <c r="Q228" s="12">
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Kathy%20Britton%20Perry%20Homes","search")</f>
+        <v/>
+      </c>
       <c r="R228" s="16">
         <f>IF(P228="","ADD LINKEDIN","ok")</f>
         <v/>
       </c>
       <c r="S228" s="12" t="inlineStr">
         <is>
-          <t>https://www.ashtonwoods.com/</t>
+          <t>https://www.perryhomes.com/</t>
         </is>
       </c>
       <c r="T228" s="15" t="inlineStr">
         <is>
-          <t>14 named Houston communities and a Texas regional president.</t>
-        </is>
-      </c>
-      <c r="U228" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="V228" s="15" t="inlineStr"/>
+          <t>120 communities and local ownership. Its published innovation page covers smart-home features and floor plans.</t>
+        </is>
+      </c>
+      <c r="U228" s="12" t="inlineStr"/>
+      <c r="V228" s="15" t="inlineStr">
+        <is>
+          <t>Perry's own page: Owner and Executive Chair, having succeeded her father Bob Perry as chief executive.</t>
+        </is>
+      </c>
       <c r="W228" s="12" t="inlineStr">
         <is>
-          <t>https://www.ashtonwoods.com/corporate-info</t>
+          <t>https://www.perryhomes.com/about-perry-homes</t>
         </is>
       </c>
       <c r="X228" s="12" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/ashton-woods-homes</t>
+          <t>https://www.linkedin.com/company/perry-homes</t>
         </is>
       </c>
       <c r="Y228" s="12" t="inlineStr">
         <is>
-          <t>https://www.ashtonwoods.com/corporate-info</t>
+          <t>https://www.perryhomes.com/about-perry-homes</t>
         </is>
       </c>
       <c r="Z228" s="12" t="inlineStr"/>
@@ -24872,7 +24884,7 @@
     <row r="229">
       <c r="A229" s="6" t="inlineStr">
         <is>
-          <t>Kathy Britton</t>
+          <t>Todd Chachere</t>
         </is>
       </c>
       <c r="B229" s="6" t="inlineStr">
@@ -24882,7 +24894,7 @@
       </c>
       <c r="C229" s="6" t="inlineStr">
         <is>
-          <t>Owner and Executive Chair</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="D229" s="7" t="inlineStr">
@@ -24945,7 +24957,7 @@
       </c>
       <c r="P229" s="10" t="inlineStr"/>
       <c r="Q229" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Kathy%20Britton%20Perry%20Homes","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Todd%20Chachere%20Perry%20Homes","search")</f>
         <v/>
       </c>
       <c r="R229" s="11">
@@ -24963,11 +24975,7 @@
         </is>
       </c>
       <c r="U229" s="6" t="inlineStr"/>
-      <c r="V229" s="9" t="inlineStr">
-        <is>
-          <t>Perry's own page: Owner and Executive Chair, having succeeded her father Bob Perry as chief executive.</t>
-        </is>
-      </c>
+      <c r="V229" s="9" t="inlineStr"/>
       <c r="W229" s="6" t="inlineStr">
         <is>
           <t>https://www.perryhomes.com/about-perry-homes</t>
@@ -24988,17 +24996,17 @@
     <row r="230">
       <c r="A230" s="12" t="inlineStr">
         <is>
-          <t>Todd Chachere</t>
+          <t>Ronny Salameh</t>
         </is>
       </c>
       <c r="B230" s="12" t="inlineStr">
         <is>
-          <t>Perry Homes</t>
+          <t>Brightland Homes</t>
         </is>
       </c>
       <c r="C230" s="12" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>President and Chief Executive Officer, The DRB Group</t>
         </is>
       </c>
       <c r="D230" s="13" t="inlineStr">
@@ -25016,22 +25024,22 @@
       </c>
       <c r="G230" s="12" t="inlineStr">
         <is>
-          <t>Houston HQ, Harris County</t>
+          <t>Addison HQ / Montgomery, Harris</t>
         </is>
       </c>
       <c r="H230" s="12" t="inlineStr">
         <is>
-          <t>120+ communities, 65,000+ homes sold</t>
+          <t>110 communities, 17,000+ homes delivered</t>
         </is>
       </c>
       <c r="I230" s="14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Partly</t>
         </is>
       </c>
       <c r="J230" s="15" t="inlineStr">
         <is>
-          <t>More than 120 communities and 65,000 homes, locally owned.</t>
+          <t>110 active communities.</t>
         </is>
       </c>
       <c r="K230" s="14" t="inlineStr">
@@ -25041,7 +25049,7 @@
       </c>
       <c r="L230" s="15" t="inlineStr">
         <is>
-          <t>120 communities and thousands of closings a year, bought centrally.</t>
+          <t>110 communities inside the DRB platform, bought by a parent that has put capital into wood.</t>
         </is>
       </c>
       <c r="M230" s="14" t="inlineStr">
@@ -25051,7 +25059,7 @@
       </c>
       <c r="N230" s="15" t="inlineStr">
         <is>
-          <t>Its own published definition of innovation is smart-home features and floor plans.</t>
+          <t>Owner Sumitomo Forestry is a timber group, which may cut against a concrete wall.</t>
         </is>
       </c>
       <c r="O230" s="14" t="inlineStr">
@@ -25061,7 +25069,7 @@
       </c>
       <c r="P230" s="10" t="inlineStr"/>
       <c r="Q230" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Todd%20Chachere%20Perry%20Homes","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Ronny%20Salameh%20Brightland%20Homes","search")</f>
         <v/>
       </c>
       <c r="R230" s="16">
@@ -25070,29 +25078,33 @@
       </c>
       <c r="S230" s="12" t="inlineStr">
         <is>
-          <t>https://www.perryhomes.com/</t>
+          <t>https://www.brightlandhomes.com/</t>
         </is>
       </c>
       <c r="T230" s="15" t="inlineStr">
         <is>
-          <t>120 communities and local ownership. Its published innovation page covers smart-home features and floor plans.</t>
+          <t>110 communities, but parent Sumitomo Forestry bought a sawmill and is integrating wood framing across the platform Brightland sits in.</t>
         </is>
       </c>
       <c r="U230" s="12" t="inlineStr"/>
-      <c r="V230" s="15" t="inlineStr"/>
+      <c r="V230" s="15" t="inlineStr">
+        <is>
+          <t>President and Chief Executive Officer of The DRB Group, which has owned Brightland since April 2025.</t>
+        </is>
+      </c>
       <c r="W230" s="12" t="inlineStr">
         <is>
-          <t>https://www.perryhomes.com/about-perry-homes</t>
+          <t>https://www.drbgroup.com/about</t>
         </is>
       </c>
       <c r="X230" s="12" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/perry-homes</t>
+          <t>https://www.linkedin.com/company/brightlandhomes</t>
         </is>
       </c>
       <c r="Y230" s="12" t="inlineStr">
         <is>
-          <t>https://www.perryhomes.com/about-perry-homes</t>
+          <t>https://www.drbgroup.com/about</t>
         </is>
       </c>
       <c r="Z230" s="12" t="inlineStr"/>
@@ -25100,7 +25112,7 @@
     <row r="231">
       <c r="A231" s="6" t="inlineStr">
         <is>
-          <t>Ronny Salameh</t>
+          <t>Young Nam</t>
         </is>
       </c>
       <c r="B231" s="6" t="inlineStr">
@@ -25110,7 +25122,7 @@
       </c>
       <c r="C231" s="6" t="inlineStr">
         <is>
-          <t>President and Chief Executive Officer, The DRB Group</t>
+          <t>Senior Vice President of Purchasing, The DRB Group</t>
         </is>
       </c>
       <c r="D231" s="7" t="inlineStr">
@@ -25171,11 +25183,12 @@
           <t>Partly</t>
         </is>
       </c>
-      <c r="P231" s="10" t="inlineStr"/>
-      <c r="Q231" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Ronny%20Salameh%20Brightland%20Homes","search")</f>
-        <v/>
-      </c>
+      <c r="P231" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/young-nam-78b36229/</t>
+        </is>
+      </c>
+      <c r="Q231" s="6" t="inlineStr"/>
       <c r="R231" s="11">
         <f>IF(P231="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -25190,10 +25203,14 @@
           <t>110 communities, but parent Sumitomo Forestry bought a sawmill and is integrating wood framing across the platform Brightland sits in.</t>
         </is>
       </c>
-      <c r="U231" s="6" t="inlineStr"/>
+      <c r="U231" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
       <c r="V231" s="9" t="inlineStr">
         <is>
-          <t>President and Chief Executive Officer of The DRB Group, which has owned Brightland since April 2025.</t>
+          <t>Senior Vice President of Supply Chain, Bethesda, Maryland. The DRB Group's own leadership page lists a Young Nam as SVP of Purchasing, and DRB is headquartered in the Maryland suburbs. Senior Vice President of Purchasing at The DRB Group. Brightland publishes no leadership of its own, so the person who buys for the platform Brightland sits inside is the contact.</t>
         </is>
       </c>
       <c r="W231" s="6" t="inlineStr">
@@ -25216,50 +25233,50 @@
     <row r="232">
       <c r="A232" s="12" t="inlineStr">
         <is>
-          <t>Young Nam</t>
+          <t>David O'Reilly</t>
         </is>
       </c>
       <c r="B232" s="12" t="inlineStr">
         <is>
-          <t>Brightland Homes</t>
+          <t>Howard Hughes Holdings Inc.</t>
         </is>
       </c>
       <c r="C232" s="12" t="inlineStr">
         <is>
-          <t>Senior Vice President of Purchasing, The DRB Group</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="D232" s="13" t="inlineStr">
         <is>
-          <t>National scale, pilot not purchase</t>
+          <t>Masterplan owner</t>
         </is>
       </c>
       <c r="E232" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F232" s="12" t="inlineStr">
         <is>
-          <t>Buys walls</t>
+          <t>Sells lots</t>
         </is>
       </c>
       <c r="G232" s="12" t="inlineStr">
         <is>
-          <t>Addison HQ / Montgomery, Harris</t>
+          <t>The Woodlands HQ / Harris, Montgomery</t>
         </is>
       </c>
       <c r="H232" s="12" t="inlineStr">
         <is>
-          <t>110 communities, 17,000+ homes delivered</t>
+          <t>1,802 residential acres left to sell</t>
         </is>
       </c>
       <c r="I232" s="14" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J232" s="15" t="inlineStr">
         <is>
-          <t>110 active communities.</t>
+          <t>Three communities on one metro's edge, 1,802 residential acres still to sell.</t>
         </is>
       </c>
       <c r="K232" s="14" t="inlineStr">
@@ -25269,67 +25286,58 @@
       </c>
       <c r="L232" s="15" t="inlineStr">
         <is>
-          <t>110 communities inside the DRB platform, bought by a parent that has put capital into wood.</t>
+          <t>It sells finished lots. The builder who buys them buys the wall.</t>
         </is>
       </c>
       <c r="M232" s="14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N232" s="15" t="inlineStr">
         <is>
-          <t>Owner Sumitomo Forestry is a timber group, which may cut against a concrete wall.</t>
+          <t>It financed and opened Greater Houston's first mass timber office building, with low-carbon concrete in the same structure.</t>
         </is>
       </c>
       <c r="O232" s="14" t="inlineStr">
         <is>
-          <t>Partly</t>
-        </is>
-      </c>
-      <c r="P232" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/young-nam-78b36229/</t>
-        </is>
-      </c>
-      <c r="Q232" s="12" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P232" s="10" t="inlineStr"/>
+      <c r="Q232" s="12">
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=David%20O%27Reilly%20Howard%20Hughes%20Holdings%20Inc.","search")</f>
+        <v/>
+      </c>
       <c r="R232" s="16">
         <f>IF(P232="","ADD LINKEDIN","ok")</f>
         <v/>
       </c>
       <c r="S232" s="12" t="inlineStr">
         <is>
-          <t>https://www.brightlandhomes.com/</t>
+          <t>https://www.howardhughes.com/</t>
         </is>
       </c>
       <c r="T232" s="15" t="inlineStr">
         <is>
-          <t>110 communities, but parent Sumitomo Forestry bought a sawmill and is integrating wood framing across the platform Brightland sits in.</t>
-        </is>
-      </c>
-      <c r="U232" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="V232" s="15" t="inlineStr">
-        <is>
-          <t>Senior Vice President of Supply Chain, Bethesda, Maryland. The DRB Group's own leadership page lists a Young Nam as SVP of Purchasing, and DRB is headquartered in the Maryland suburbs. Senior Vice President of Purchasing at The DRB Group. Brightland publishes no leadership of its own, so the person who buys for the platform Brightland sits inside is the contact.</t>
-        </is>
-      </c>
+          <t>1,802 residential acres left to sell across three communities, and it paid to put up Greater Houston's first mass timber office. It sells lots, so the builder buys the wall.</t>
+        </is>
+      </c>
+      <c r="U232" s="12" t="inlineStr"/>
+      <c r="V232" s="15" t="inlineStr"/>
       <c r="W232" s="12" t="inlineStr">
         <is>
-          <t>https://www.drbgroup.com/about</t>
+          <t>https://investor.howardhughes.com/governance/leadership</t>
         </is>
       </c>
       <c r="X232" s="12" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/brightlandhomes</t>
+          <t>https://www.linkedin.com/company/the-howard-hughes-corporation</t>
         </is>
       </c>
       <c r="Y232" s="12" t="inlineStr">
         <is>
-          <t>https://www.drbgroup.com/about</t>
+          <t>https://investor.howardhughes.com/governance/leadership</t>
         </is>
       </c>
       <c r="Z232" s="12" t="inlineStr"/>
@@ -25337,7 +25345,7 @@
     <row r="233">
       <c r="A233" s="6" t="inlineStr">
         <is>
-          <t>David O'Reilly</t>
+          <t>Bill Ackman</t>
         </is>
       </c>
       <c r="B233" s="6" t="inlineStr">
@@ -25347,7 +25355,7 @@
       </c>
       <c r="C233" s="6" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Executive Chairman of the Board</t>
         </is>
       </c>
       <c r="D233" s="7" t="inlineStr">
@@ -25410,7 +25418,7 @@
       </c>
       <c r="P233" s="10" t="inlineStr"/>
       <c r="Q233" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=David%20O%27Reilly%20Howard%20Hughes%20Holdings%20Inc.","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Bill%20Ackman%20Howard%20Hughes%20Holdings%20Inc.","search")</f>
         <v/>
       </c>
       <c r="R233" s="11">
@@ -25449,7 +25457,7 @@
     <row r="234">
       <c r="A234" s="12" t="inlineStr">
         <is>
-          <t>Bill Ackman</t>
+          <t>Ryan Israel</t>
         </is>
       </c>
       <c r="B234" s="12" t="inlineStr">
@@ -25459,7 +25467,7 @@
       </c>
       <c r="C234" s="12" t="inlineStr">
         <is>
-          <t>Executive Chairman of the Board</t>
+          <t>Chief Investment Officer</t>
         </is>
       </c>
       <c r="D234" s="13" t="inlineStr">
@@ -25522,7 +25530,7 @@
       </c>
       <c r="P234" s="10" t="inlineStr"/>
       <c r="Q234" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Bill%20Ackman%20Howard%20Hughes%20Holdings%20Inc.","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Ryan%20Israel%20Howard%20Hughes%20Holdings%20Inc.","search")</f>
         <v/>
       </c>
       <c r="R234" s="16">
@@ -25561,7 +25569,7 @@
     <row r="235">
       <c r="A235" s="6" t="inlineStr">
         <is>
-          <t>Ryan Israel</t>
+          <t>Jim Carman</t>
         </is>
       </c>
       <c r="B235" s="6" t="inlineStr">
@@ -25571,7 +25579,7 @@
       </c>
       <c r="C235" s="6" t="inlineStr">
         <is>
-          <t>Chief Investment Officer</t>
+          <t>President, Texas Region</t>
         </is>
       </c>
       <c r="D235" s="7" t="inlineStr">
@@ -25632,11 +25640,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P235" s="10" t="inlineStr"/>
-      <c r="Q235" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Ryan%20Israel%20Howard%20Hughes%20Holdings%20Inc.","search")</f>
-        <v/>
-      </c>
+      <c r="P235" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/carmanjim/</t>
+        </is>
+      </c>
+      <c r="Q235" s="6" t="inlineStr"/>
       <c r="R235" s="11">
         <f>IF(P235="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -25652,12 +25661,12 @@
         </is>
       </c>
       <c r="U235" s="6" t="inlineStr"/>
-      <c r="V235" s="9" t="inlineStr"/>
-      <c r="W235" s="6" t="inlineStr">
-        <is>
-          <t>https://investor.howardhughes.com/governance/leadership</t>
-        </is>
-      </c>
+      <c r="V235" s="9" t="inlineStr">
+        <is>
+          <t>Profile opened. President, Texas Region at Howard Hughes Communities. Greater Houston. His own feed carries Bridgeland's number nine national ranking at 500 home sales by mid-2026 and the 83-acre Toro District with the Houston Texans headquarters.</t>
+        </is>
+      </c>
+      <c r="W235" s="6" t="inlineStr"/>
       <c r="X235" s="6" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/the-howard-hughes-corporation</t>
@@ -25673,17 +25682,17 @@
     <row r="236">
       <c r="A236" s="12" t="inlineStr">
         <is>
-          <t>Jim Carman</t>
+          <t>Fred Balda</t>
         </is>
       </c>
       <c r="B236" s="12" t="inlineStr">
         <is>
-          <t>Howard Hughes Holdings Inc.</t>
+          <t>Hillwood Communities</t>
         </is>
       </c>
       <c r="C236" s="12" t="inlineStr">
         <is>
-          <t>President, Texas Region</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D236" s="13" t="inlineStr">
@@ -25701,12 +25710,12 @@
       </c>
       <c r="G236" s="12" t="inlineStr">
         <is>
-          <t>The Woodlands HQ / Harris, Montgomery</t>
+          <t>Dallas HQ / Manvel, Pearland, League City</t>
         </is>
       </c>
       <c r="H236" s="12" t="inlineStr">
         <is>
-          <t>1,802 residential acres left to sell</t>
+          <t>Three Houston masterplans, 700 acres at Legacy alone</t>
         </is>
       </c>
       <c r="I236" s="14" t="inlineStr">
@@ -25716,7 +25725,7 @@
       </c>
       <c r="J236" s="15" t="inlineStr">
         <is>
-          <t>Three communities on one metro's edge, 1,802 residential acres still to sell.</t>
+          <t>Three concurrent Houston masterplans, 700 acres at Legacy alone.</t>
         </is>
       </c>
       <c r="K236" s="14" t="inlineStr">
@@ -25726,67 +25735,58 @@
       </c>
       <c r="L236" s="15" t="inlineStr">
         <is>
-          <t>It sells finished lots. The builder who buys them buys the wall.</t>
+          <t>It develops lots and sells them to vertical builders. It does not pour walls.</t>
         </is>
       </c>
       <c r="M236" s="14" t="inlineStr">
         <is>
+          <t>Partly</t>
+        </is>
+      </c>
+      <c r="N236" s="15" t="inlineStr">
+        <is>
+          <t>A hundred printed homes were built inside one of its own communities. Hillwood developed the ground. Lennar bought the printing.</t>
+        </is>
+      </c>
+      <c r="O236" s="14" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N236" s="15" t="inlineStr">
-        <is>
-          <t>It financed and opened Greater Houston's first mass timber office building, with low-carbon concrete in the same structure.</t>
-        </is>
-      </c>
-      <c r="O236" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P236" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/carmanjim/</t>
-        </is>
-      </c>
-      <c r="Q236" s="12" t="inlineStr"/>
+      <c r="P236" s="10" t="inlineStr"/>
+      <c r="Q236" s="12">
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Fred%20Balda%20Hillwood%20Communities","search")</f>
+        <v/>
+      </c>
       <c r="R236" s="16">
         <f>IF(P236="","ADD LINKEDIN","ok")</f>
         <v/>
       </c>
       <c r="S236" s="12" t="inlineStr">
         <is>
-          <t>https://www.howardhughes.com/</t>
+          <t>https://www.hillwoodcommunities.com/</t>
         </is>
       </c>
       <c r="T236" s="15" t="inlineStr">
         <is>
-          <t>1,802 residential acres left to sell across three communities, and it paid to put up Greater Houston's first mass timber office. It sells lots, so the builder buys the wall.</t>
+          <t>It is the land developer of Wolf Ranch, and it runs three Houston masterplans with a Houston general manager named.</t>
         </is>
       </c>
       <c r="U236" s="12" t="inlineStr"/>
-      <c r="V236" s="15" t="inlineStr">
-        <is>
-          <t>Profile opened. President, Texas Region at Howard Hughes Communities. Greater Houston. His own feed carries Bridgeland's number nine national ranking at 500 home sales by mid-2026 and the 83-acre Toro District with the Houston Texans headquarters.</t>
-        </is>
-      </c>
-      <c r="W236" s="12" t="inlineStr"/>
-      <c r="X236" s="12" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/the-howard-hughes-corporation</t>
-        </is>
-      </c>
-      <c r="Y236" s="12" t="inlineStr">
-        <is>
-          <t>https://investor.howardhughes.com/governance/leadership</t>
-        </is>
-      </c>
+      <c r="V236" s="15" t="inlineStr"/>
+      <c r="W236" s="12" t="inlineStr">
+        <is>
+          <t>https://www.hillwoodcommunities.com/leadership/</t>
+        </is>
+      </c>
+      <c r="X236" s="12" t="inlineStr"/>
+      <c r="Y236" s="12" t="inlineStr"/>
       <c r="Z236" s="12" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="6" t="inlineStr">
         <is>
-          <t>Fred Balda</t>
+          <t>Russell Bynum</t>
         </is>
       </c>
       <c r="B237" s="6" t="inlineStr">
@@ -25796,7 +25796,7 @@
       </c>
       <c r="C237" s="6" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Senior Vice President, General Manager, Houston MSA</t>
         </is>
       </c>
       <c r="D237" s="7" t="inlineStr">
@@ -25859,7 +25859,7 @@
       </c>
       <c r="P237" s="10" t="inlineStr"/>
       <c r="Q237" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Fred%20Balda%20Hillwood%20Communities","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Russell%20Bynum%20Hillwood%20Communities","search")</f>
         <v/>
       </c>
       <c r="R237" s="11">
@@ -25876,7 +25876,11 @@
           <t>It is the land developer of Wolf Ranch, and it runs three Houston masterplans with a Houston general manager named.</t>
         </is>
       </c>
-      <c r="U237" s="6" t="inlineStr"/>
+      <c r="U237" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
       <c r="V237" s="9" t="inlineStr"/>
       <c r="W237" s="6" t="inlineStr">
         <is>
@@ -25890,7 +25894,7 @@
     <row r="238">
       <c r="A238" s="12" t="inlineStr">
         <is>
-          <t>Russell Bynum</t>
+          <t>Mark Meyer</t>
         </is>
       </c>
       <c r="B238" s="12" t="inlineStr">
@@ -25900,7 +25904,7 @@
       </c>
       <c r="C238" s="12" t="inlineStr">
         <is>
-          <t>Senior Vice President, General Manager, Houston MSA</t>
+          <t>Senior Vice President, Planning and Innovation</t>
         </is>
       </c>
       <c r="D238" s="13" t="inlineStr">
@@ -25963,7 +25967,7 @@
       </c>
       <c r="P238" s="10" t="inlineStr"/>
       <c r="Q238" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Russell%20Bynum%20Hillwood%20Communities","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Mark%20Meyer%20Hillwood%20Communities","search")</f>
         <v/>
       </c>
       <c r="R238" s="16">
@@ -25980,11 +25984,7 @@
           <t>It is the land developer of Wolf Ranch, and it runs three Houston masterplans with a Houston general manager named.</t>
         </is>
       </c>
-      <c r="U238" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="U238" s="12" t="inlineStr"/>
       <c r="V238" s="15" t="inlineStr"/>
       <c r="W238" s="12" t="inlineStr">
         <is>
@@ -25998,7 +25998,7 @@
     <row r="239">
       <c r="A239" s="6" t="inlineStr">
         <is>
-          <t>Mark Meyer</t>
+          <t>Patrick Cowden</t>
         </is>
       </c>
       <c r="B239" s="6" t="inlineStr">
@@ -26008,7 +26008,7 @@
       </c>
       <c r="C239" s="6" t="inlineStr">
         <is>
-          <t>Senior Vice President, Planning and Innovation</t>
+          <t>Senior Vice President, Development</t>
         </is>
       </c>
       <c r="D239" s="7" t="inlineStr">
@@ -26071,7 +26071,7 @@
       </c>
       <c r="P239" s="10" t="inlineStr"/>
       <c r="Q239" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Mark%20Meyer%20Hillwood%20Communities","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Patrick%20Cowden%20Hillwood%20Communities","search")</f>
         <v/>
       </c>
       <c r="R239" s="11">
@@ -26102,17 +26102,17 @@
     <row r="240">
       <c r="A240" s="12" t="inlineStr">
         <is>
-          <t>Patrick Cowden</t>
+          <t>Danny Signorelli</t>
         </is>
       </c>
       <c r="B240" s="12" t="inlineStr">
         <is>
-          <t>Hillwood Communities</t>
+          <t>The Signorelli Company</t>
         </is>
       </c>
       <c r="C240" s="12" t="inlineStr">
         <is>
-          <t>Senior Vice President, Development</t>
+          <t>Founder and Chief Executive Officer</t>
         </is>
       </c>
       <c r="D240" s="13" t="inlineStr">
@@ -26130,12 +26130,12 @@
       </c>
       <c r="G240" s="12" t="inlineStr">
         <is>
-          <t>Dallas HQ / Manvel, Pearland, League City</t>
+          <t>The Woodlands HQ / Fort Bend, Liberty</t>
         </is>
       </c>
       <c r="H240" s="12" t="inlineStr">
         <is>
-          <t>Three Houston masterplans, 700 acres at Legacy alone</t>
+          <t>23,000+ paper lots in pipeline</t>
         </is>
       </c>
       <c r="I240" s="14" t="inlineStr">
@@ -26145,68 +26145,77 @@
       </c>
       <c r="J240" s="15" t="inlineStr">
         <is>
-          <t>Three concurrent Houston masterplans, 700 acres at Legacy alone.</t>
+          <t>More than 16 masterplans and over 23,000 paper lots in pipeline.</t>
         </is>
       </c>
       <c r="K240" s="14" t="inlineStr">
         <is>
+          <t>Partly</t>
+        </is>
+      </c>
+      <c r="L240" s="15" t="inlineStr">
+        <is>
+          <t>It sells lots, but it owns First America Homes, and one president runs both.</t>
+        </is>
+      </c>
+      <c r="M240" s="14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L240" s="15" t="inlineStr">
-        <is>
-          <t>It develops lots and sells them to vertical builders. It does not pour walls.</t>
-        </is>
-      </c>
-      <c r="M240" s="14" t="inlineStr">
-        <is>
-          <t>Partly</t>
-        </is>
-      </c>
       <c r="N240" s="15" t="inlineStr">
         <is>
-          <t>A hundred printed homes were built inside one of its own communities. Hillwood developed the ground. Lennar bought the printing.</t>
+          <t>Nothing on record about how anything inside its communities is built.</t>
         </is>
       </c>
       <c r="O240" s="14" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P240" s="10" t="inlineStr"/>
-      <c r="Q240" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Patrick%20Cowden%20Hillwood%20Communities","search")</f>
-        <v/>
-      </c>
+          <t>Partly</t>
+        </is>
+      </c>
+      <c r="P240" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/danny-signorelli-6284461b/</t>
+        </is>
+      </c>
+      <c r="Q240" s="12" t="inlineStr"/>
       <c r="R240" s="16">
         <f>IF(P240="","ADD LINKEDIN","ok")</f>
         <v/>
       </c>
       <c r="S240" s="12" t="inlineStr">
         <is>
-          <t>https://www.hillwoodcommunities.com/</t>
+          <t>https://www.signorellicompany.com/</t>
         </is>
       </c>
       <c r="T240" s="15" t="inlineStr">
         <is>
-          <t>It is the land developer of Wolf Ranch, and it runs three Houston masterplans with a Houston general manager named.</t>
+          <t>Sells lots, but owns First America Homes, which holds all three counts. One president runs both.</t>
         </is>
       </c>
       <c r="U240" s="12" t="inlineStr"/>
-      <c r="V240" s="15" t="inlineStr"/>
-      <c r="W240" s="12" t="inlineStr">
-        <is>
-          <t>https://www.hillwoodcommunities.com/leadership/</t>
-        </is>
-      </c>
-      <c r="X240" s="12" t="inlineStr"/>
-      <c r="Y240" s="12" t="inlineStr"/>
+      <c r="V240" s="15" t="inlineStr">
+        <is>
+          <t>CEO, President, The Signorelli Company. Greater Houston.</t>
+        </is>
+      </c>
+      <c r="W240" s="12" t="inlineStr"/>
+      <c r="X240" s="12" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/signorelli-company</t>
+        </is>
+      </c>
+      <c r="Y240" s="12" t="inlineStr">
+        <is>
+          <t>https://www.signorellicompany.com/our-leadership</t>
+        </is>
+      </c>
       <c r="Z240" s="12" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="6" t="inlineStr">
         <is>
-          <t>Danny Signorelli</t>
+          <t>Jeff Dewese</t>
         </is>
       </c>
       <c r="B241" s="6" t="inlineStr">
@@ -26216,7 +26225,7 @@
       </c>
       <c r="C241" s="6" t="inlineStr">
         <is>
-          <t>Founder and Chief Executive Officer</t>
+          <t>President, Land Division</t>
         </is>
       </c>
       <c r="D241" s="7" t="inlineStr">
@@ -26277,12 +26286,11 @@
           <t>Partly</t>
         </is>
       </c>
-      <c r="P241" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/danny-signorelli-6284461b/</t>
-        </is>
-      </c>
-      <c r="Q241" s="6" t="inlineStr"/>
+      <c r="P241" s="10" t="inlineStr"/>
+      <c r="Q241" s="6">
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Jeff%20Dewese%20The%20Signorelli%20Company","search")</f>
+        <v/>
+      </c>
       <c r="R241" s="11">
         <f>IF(P241="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -26300,10 +26308,14 @@
       <c r="U241" s="6" t="inlineStr"/>
       <c r="V241" s="9" t="inlineStr">
         <is>
-          <t>CEO, President, The Signorelli Company. Greater Houston.</t>
-        </is>
-      </c>
-      <c r="W241" s="6" t="inlineStr"/>
+          <t>Signorelli's own bio page. President, Land Division, overseeing land acquisition, planning and construction management for Granger Pines, Cielo and Austin Point.</t>
+        </is>
+      </c>
+      <c r="W241" s="6" t="inlineStr">
+        <is>
+          <t>https://www.signorellicompany.com/our-leadership/15/jeff-dewese</t>
+        </is>
+      </c>
       <c r="X241" s="6" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/signorelli-company</t>
@@ -26319,7 +26331,7 @@
     <row r="242">
       <c r="A242" s="12" t="inlineStr">
         <is>
-          <t>Jeff Dewese</t>
+          <t>Harry Dinham</t>
         </is>
       </c>
       <c r="B242" s="12" t="inlineStr">
@@ -26329,7 +26341,7 @@
       </c>
       <c r="C242" s="12" t="inlineStr">
         <is>
-          <t>President, Land Division</t>
+          <t>Chief Financial Officer</t>
         </is>
       </c>
       <c r="D242" s="13" t="inlineStr">
@@ -26392,7 +26404,7 @@
       </c>
       <c r="P242" s="10" t="inlineStr"/>
       <c r="Q242" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Jeff%20Dewese%20The%20Signorelli%20Company","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Harry%20Dinham%20The%20Signorelli%20Company","search")</f>
         <v/>
       </c>
       <c r="R242" s="16">
@@ -26412,12 +26424,12 @@
       <c r="U242" s="12" t="inlineStr"/>
       <c r="V242" s="15" t="inlineStr">
         <is>
-          <t>Signorelli's own bio page. President, Land Division, overseeing land acquisition, planning and construction management for Granger Pines, Cielo and Austin Point.</t>
+          <t>Signorelli's own bio page. Chief Financial Officer on the executive leadership team.</t>
         </is>
       </c>
       <c r="W242" s="12" t="inlineStr">
         <is>
-          <t>https://www.signorellicompany.com/our-leadership/15/jeff-dewese</t>
+          <t>https://www.signorellicompany.com/our-leadership/30/harry-dinham</t>
         </is>
       </c>
       <c r="X242" s="12" t="inlineStr">
@@ -26435,7 +26447,7 @@
     <row r="243">
       <c r="A243" s="6" t="inlineStr">
         <is>
-          <t>Harry Dinham</t>
+          <t>John Winniford</t>
         </is>
       </c>
       <c r="B243" s="6" t="inlineStr">
@@ -26445,7 +26457,7 @@
       </c>
       <c r="C243" s="6" t="inlineStr">
         <is>
-          <t>Chief Financial Officer</t>
+          <t>President, Homebuilding, The Signorelli Company</t>
         </is>
       </c>
       <c r="D243" s="7" t="inlineStr">
@@ -26508,7 +26520,7 @@
       </c>
       <c r="P243" s="10" t="inlineStr"/>
       <c r="Q243" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Harry%20Dinham%20The%20Signorelli%20Company","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=John%20Winniford%20The%20Signorelli%20Company","search")</f>
         <v/>
       </c>
       <c r="R243" s="11">
@@ -26528,12 +26540,12 @@
       <c r="U243" s="6" t="inlineStr"/>
       <c r="V243" s="9" t="inlineStr">
         <is>
-          <t>Signorelli's own bio page. Chief Financial Officer on the executive leadership team.</t>
+          <t>President, Homebuilding. The same person who runs First America, which Signorelli owns, so a single approach reaches both the land position and the builder.</t>
         </is>
       </c>
       <c r="W243" s="6" t="inlineStr">
         <is>
-          <t>https://www.signorellicompany.com/our-leadership/30/harry-dinham</t>
+          <t>https://www.signorellicompany.com/our-leadership/34/john-winniford</t>
         </is>
       </c>
       <c r="X243" s="6" t="inlineStr">
@@ -26551,17 +26563,17 @@
     <row r="244">
       <c r="A244" s="12" t="inlineStr">
         <is>
-          <t>John Winniford</t>
+          <t>Fred Caldwell</t>
         </is>
       </c>
       <c r="B244" s="12" t="inlineStr">
         <is>
-          <t>The Signorelli Company</t>
+          <t>Caldwell Companies</t>
         </is>
       </c>
       <c r="C244" s="12" t="inlineStr">
         <is>
-          <t>President, Homebuilding, The Signorelli Company</t>
+          <t>Chief Executive Officer, Caldwell Companies</t>
         </is>
       </c>
       <c r="D244" s="13" t="inlineStr">
@@ -26579,12 +26591,12 @@
       </c>
       <c r="G244" s="12" t="inlineStr">
         <is>
-          <t>The Woodlands HQ / Fort Bend, Liberty</t>
+          <t>Cypress / Montgomery, Harris</t>
         </is>
       </c>
       <c r="H244" s="12" t="inlineStr">
         <is>
-          <t>23,000+ paper lots in pipeline</t>
+          <t>Towne Lake and The Highlands, more than 4,000 homes at The Highlands alone</t>
         </is>
       </c>
       <c r="I244" s="14" t="inlineStr">
@@ -26594,7 +26606,7 @@
       </c>
       <c r="J244" s="15" t="inlineStr">
         <is>
-          <t>More than 16 masterplans and over 23,000 paper lots in pipeline.</t>
+          <t>The Highlands alone carries more than 4,000 planned homes across thirteen builders, and Towne Lake is a second community.</t>
         </is>
       </c>
       <c r="K244" s="14" t="inlineStr">
@@ -26604,7 +26616,7 @@
       </c>
       <c r="L244" s="15" t="inlineStr">
         <is>
-          <t>It sells lots, but it owns First America Homes, and one president runs both.</t>
+          <t>It sells lots, and through Caldwell Homes it also builds. The wall decision exists inside the group.</t>
         </is>
       </c>
       <c r="M244" s="14" t="inlineStr">
@@ -26614,17 +26626,17 @@
       </c>
       <c r="N244" s="15" t="inlineStr">
         <is>
-          <t>Nothing on record about how anything inside its communities is built.</t>
+          <t>Caldwell Companies publishes no construction-method content. Caldwell Homes, its own division, is screened separately on this deck.</t>
         </is>
       </c>
       <c r="O244" s="14" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P244" s="10" t="inlineStr"/>
       <c r="Q244" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=John%20Winniford%20The%20Signorelli%20Company","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Fred%20Caldwell%20Caldwell%20Companies","search")</f>
         <v/>
       </c>
       <c r="R244" s="16">
@@ -26633,33 +26645,29 @@
       </c>
       <c r="S244" s="12" t="inlineStr">
         <is>
-          <t>https://www.signorellicompany.com/</t>
+          <t>https://caldwellcos.com/</t>
         </is>
       </c>
       <c r="T244" s="15" t="inlineStr">
         <is>
-          <t>Sells lots, but owns First America Homes, which holds all three counts. One president runs both.</t>
+          <t>Sells lots. Towne Lake and The Highlands carry 4,000 homes across 12 builders.</t>
         </is>
       </c>
       <c r="U244" s="12" t="inlineStr"/>
-      <c r="V244" s="15" t="inlineStr">
-        <is>
-          <t>President, Homebuilding. The same person who runs First America, which Signorelli owns, so a single approach reaches both the land position and the builder.</t>
-        </is>
-      </c>
+      <c r="V244" s="15" t="inlineStr"/>
       <c r="W244" s="12" t="inlineStr">
         <is>
-          <t>https://www.signorellicompany.com/our-leadership/34/john-winniford</t>
+          <t>https://caldwellcos.com/our-team</t>
         </is>
       </c>
       <c r="X244" s="12" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/signorelli-company</t>
+          <t>https://www.linkedin.com/company/caldwell-companies</t>
         </is>
       </c>
       <c r="Y244" s="12" t="inlineStr">
         <is>
-          <t>https://www.signorellicompany.com/our-leadership</t>
+          <t>https://caldwellcos.com/our-team</t>
         </is>
       </c>
       <c r="Z244" s="12" t="inlineStr"/>
@@ -26667,17 +26675,17 @@
     <row r="245">
       <c r="A245" s="6" t="inlineStr">
         <is>
-          <t>Fred Caldwell</t>
+          <t>Alan Brende</t>
         </is>
       </c>
       <c r="B245" s="6" t="inlineStr">
         <is>
-          <t>Caldwell Companies</t>
+          <t>Land Tejas</t>
         </is>
       </c>
       <c r="C245" s="6" t="inlineStr">
         <is>
-          <t>Chief Executive Officer, Caldwell Companies</t>
+          <t>Co-President, Land Tejas</t>
         </is>
       </c>
       <c r="D245" s="7" t="inlineStr">
@@ -26686,7 +26694,7 @@
         </is>
       </c>
       <c r="E245" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F245" s="6" t="inlineStr">
         <is>
@@ -26695,12 +26703,12 @@
       </c>
       <c r="G245" s="6" t="inlineStr">
         <is>
-          <t>Cypress / Montgomery, Harris</t>
+          <t>Houston / Katy, Harris-Waller</t>
         </is>
       </c>
       <c r="H245" s="6" t="inlineStr">
         <is>
-          <t>Towne Lake and The Highlands, more than 4,000 homes at The Highlands alone</t>
+          <t>Sunterra in Katy, eighteen builders inside it</t>
         </is>
       </c>
       <c r="I245" s="8" t="inlineStr">
@@ -26710,17 +26718,17 @@
       </c>
       <c r="J245" s="9" t="inlineStr">
         <is>
-          <t>The Highlands alone carries more than 4,000 planned homes across thirteen builders, and Towne Lake is a second community.</t>
+          <t>Sunterra carries eighteen builders inside one community.</t>
         </is>
       </c>
       <c r="K245" s="8" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L245" s="9" t="inlineStr">
         <is>
-          <t>It sells lots, and through Caldwell Homes it also builds. The wall decision exists inside the group.</t>
+          <t>It sells lots. Eighteen builders buy the wall.</t>
         </is>
       </c>
       <c r="M245" s="8" t="inlineStr">
@@ -26730,17 +26738,17 @@
       </c>
       <c r="N245" s="9" t="inlineStr">
         <is>
-          <t>Caldwell Companies publishes no construction-method content. Caldwell Homes, its own division, is screened separately on this deck.</t>
+          <t>Nothing on record about construction method.</t>
         </is>
       </c>
       <c r="O245" s="8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P245" s="10" t="inlineStr"/>
       <c r="Q245" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Fred%20Caldwell%20Caldwell%20Companies","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Alan%20Brende%20Land%20Tejas","search")</f>
         <v/>
       </c>
       <c r="R245" s="11">
@@ -26749,29 +26757,29 @@
       </c>
       <c r="S245" s="6" t="inlineStr">
         <is>
-          <t>https://caldwellcos.com/</t>
+          <t>https://landtejas.com/</t>
         </is>
       </c>
       <c r="T245" s="9" t="inlineStr">
         <is>
-          <t>Sells lots. Towne Lake and The Highlands carry 4,000 homes across 12 builders.</t>
+          <t>Sells lots. Sunterra carries 2,303 acres and 15 builders.</t>
         </is>
       </c>
       <c r="U245" s="6" t="inlineStr"/>
       <c r="V245" s="9" t="inlineStr"/>
       <c r="W245" s="6" t="inlineStr">
         <is>
-          <t>https://caldwellcos.com/our-team</t>
+          <t>https://landtejas.com/about-us/our-leadership/</t>
         </is>
       </c>
       <c r="X245" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/caldwell-companies</t>
+          <t>https://www.linkedin.com/company/land-tejas-companies</t>
         </is>
       </c>
       <c r="Y245" s="6" t="inlineStr">
         <is>
-          <t>https://caldwellcos.com/our-team</t>
+          <t>https://landtejas.com/about-us/our-leadership/</t>
         </is>
       </c>
       <c r="Z245" s="6" t="inlineStr"/>
@@ -26779,7 +26787,7 @@
     <row r="246">
       <c r="A246" s="12" t="inlineStr">
         <is>
-          <t>Alan Brende</t>
+          <t>Melanie Ohl</t>
         </is>
       </c>
       <c r="B246" s="12" t="inlineStr">
@@ -26852,7 +26860,7 @@
       </c>
       <c r="P246" s="10" t="inlineStr"/>
       <c r="Q246" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Alan%20Brende%20Land%20Tejas","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Melanie%20Ohl%20Land%20Tejas","search")</f>
         <v/>
       </c>
       <c r="R246" s="16">
@@ -26891,17 +26899,17 @@
     <row r="247">
       <c r="A247" s="6" t="inlineStr">
         <is>
-          <t>Melanie Ohl</t>
+          <t>Michael J. Smith</t>
         </is>
       </c>
       <c r="B247" s="6" t="inlineStr">
         <is>
-          <t>Land Tejas</t>
+          <t>Johnson Development Corp</t>
         </is>
       </c>
       <c r="C247" s="6" t="inlineStr">
         <is>
-          <t>Co-President, Land Tejas</t>
+          <t>President and Chief Executive Officer, Johnson Development</t>
         </is>
       </c>
       <c r="D247" s="7" t="inlineStr">
@@ -26919,12 +26927,12 @@
       </c>
       <c r="G247" s="6" t="inlineStr">
         <is>
-          <t>Houston / Katy, Harris-Waller</t>
+          <t>Houston / Fort Bend, Montgomery</t>
         </is>
       </c>
       <c r="H247" s="6" t="inlineStr">
         <is>
-          <t>Sunterra in Katy, eighteen builders inside it</t>
+          <t>Fifteen concurrent Houston masterplans</t>
         </is>
       </c>
       <c r="I247" s="8" t="inlineStr">
@@ -26934,7 +26942,7 @@
       </c>
       <c r="J247" s="9" t="inlineStr">
         <is>
-          <t>Sunterra carries eighteen builders inside one community.</t>
+          <t>Fifteen concurrent Houston masterplans, by its own count.</t>
         </is>
       </c>
       <c r="K247" s="8" t="inlineStr">
@@ -26944,7 +26952,7 @@
       </c>
       <c r="L247" s="9" t="inlineStr">
         <is>
-          <t>It sells lots. Eighteen builders buy the wall.</t>
+          <t>It sells lots and does not pour walls.</t>
         </is>
       </c>
       <c r="M247" s="8" t="inlineStr">
@@ -26954,17 +26962,17 @@
       </c>
       <c r="N247" s="9" t="inlineStr">
         <is>
-          <t>Nothing on record about construction method.</t>
+          <t>Johnson Development publishes no construction-method content.</t>
         </is>
       </c>
       <c r="O247" s="8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P247" s="10" t="inlineStr"/>
       <c r="Q247" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Melanie%20Ohl%20Land%20Tejas","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Michael%20J.%20Smith%20Johnson%20Development%20Corp","search")</f>
         <v/>
       </c>
       <c r="R247" s="11">
@@ -26973,29 +26981,29 @@
       </c>
       <c r="S247" s="6" t="inlineStr">
         <is>
-          <t>https://landtejas.com/</t>
+          <t>https://www.johnsondevelopment.com/</t>
         </is>
       </c>
       <c r="T247" s="9" t="inlineStr">
         <is>
-          <t>Sells lots. Sunterra carries 2,303 acres and 15 builders.</t>
+          <t>Sells lots across 14 Houston masterplans. Buys no walls.</t>
         </is>
       </c>
       <c r="U247" s="6" t="inlineStr"/>
       <c r="V247" s="9" t="inlineStr"/>
       <c r="W247" s="6" t="inlineStr">
         <is>
-          <t>https://landtejas.com/about-us/our-leadership/</t>
+          <t>https://www.johnsondevelopment.com/our-leaders</t>
         </is>
       </c>
       <c r="X247" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/land-tejas-companies</t>
+          <t>https://www.linkedin.com/company/the-johnson-development-corp</t>
         </is>
       </c>
       <c r="Y247" s="6" t="inlineStr">
         <is>
-          <t>https://landtejas.com/about-us/our-leadership/</t>
+          <t>https://www.johnsondevelopment.com/our-leaders</t>
         </is>
       </c>
       <c r="Z247" s="6" t="inlineStr"/>
@@ -27003,17 +27011,17 @@
     <row r="248">
       <c r="A248" s="12" t="inlineStr">
         <is>
-          <t>Michael J. Smith</t>
+          <t>Alan Bauer</t>
         </is>
       </c>
       <c r="B248" s="12" t="inlineStr">
         <is>
-          <t>Johnson Development Corp</t>
+          <t>Newland Communities</t>
         </is>
       </c>
       <c r="C248" s="12" t="inlineStr">
         <is>
-          <t>President and Chief Executive Officer, Johnson Development</t>
+          <t>Senior Vice President and Houston Division Manager, Newland (2019)</t>
         </is>
       </c>
       <c r="D248" s="13" t="inlineStr">
@@ -27031,22 +27039,22 @@
       </c>
       <c r="G248" s="12" t="inlineStr">
         <is>
-          <t>Houston / Fort Bend, Montgomery</t>
+          <t>San Diego HQ / Katy, Harris</t>
         </is>
       </c>
       <c r="H248" s="12" t="inlineStr">
         <is>
-          <t>Fifteen concurrent Houston masterplans</t>
+          <t>Elyson, 3,600 acres in Katy</t>
         </is>
       </c>
       <c r="I248" s="14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Partly</t>
         </is>
       </c>
       <c r="J248" s="15" t="inlineStr">
         <is>
-          <t>Fifteen concurrent Houston masterplans, by its own count.</t>
+          <t>One Houston community, Elyson, at 3,600 acres in Katy.</t>
         </is>
       </c>
       <c r="K248" s="14" t="inlineStr">
@@ -27056,7 +27064,7 @@
       </c>
       <c r="L248" s="15" t="inlineStr">
         <is>
-          <t>It sells lots and does not pour walls.</t>
+          <t>It sells lots, and the platform now sits inside Brookfield Residential.</t>
         </is>
       </c>
       <c r="M248" s="14" t="inlineStr">
@@ -27066,7 +27074,7 @@
       </c>
       <c r="N248" s="15" t="inlineStr">
         <is>
-          <t>Johnson Development publishes no construction-method content.</t>
+          <t>Nothing on record about construction method.</t>
         </is>
       </c>
       <c r="O248" s="14" t="inlineStr">
@@ -27076,7 +27084,7 @@
       </c>
       <c r="P248" s="10" t="inlineStr"/>
       <c r="Q248" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Michael%20J.%20Smith%20Johnson%20Development%20Corp","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Alan%20Bauer%20Newland%20Communities","search")</f>
         <v/>
       </c>
       <c r="R248" s="16">
@@ -27085,56 +27093,56 @@
       </c>
       <c r="S248" s="12" t="inlineStr">
         <is>
-          <t>https://www.johnsondevelopment.com/</t>
+          <t>https://newlandco.com/</t>
         </is>
       </c>
       <c r="T248" s="15" t="inlineStr">
         <is>
-          <t>Sells lots across 14 Houston masterplans. Buys no walls.</t>
+          <t>3,600-acre Elyson, but Newland has been absorbed into Brookfield Residential and no longer publishes its own leadership. The one Houston name on record is from 2019.</t>
         </is>
       </c>
       <c r="U248" s="12" t="inlineStr"/>
-      <c r="V248" s="15" t="inlineStr"/>
+      <c r="V248" s="15" t="inlineStr">
+        <is>
+          <t>Senior Vice President and Division Manager for Newland's Houston division, per the West Houston Association board announcement. Dated 2019 and unconfirmed since, because Newland no longer publishes its own leadership.</t>
+        </is>
+      </c>
       <c r="W248" s="12" t="inlineStr">
         <is>
-          <t>https://www.johnsondevelopment.com/our-leaders</t>
+          <t>https://www.westhouston.org/2019/01/18/welcome-to-the-2019-board-or-directors/</t>
         </is>
       </c>
       <c r="X248" s="12" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/the-johnson-development-corp</t>
-        </is>
-      </c>
-      <c r="Y248" s="12" t="inlineStr">
-        <is>
-          <t>https://www.johnsondevelopment.com/our-leaders</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/company/newland-communities-llc</t>
+        </is>
+      </c>
+      <c r="Y248" s="12" t="inlineStr"/>
       <c r="Z248" s="12" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="6" t="inlineStr">
         <is>
-          <t>Alan Bauer</t>
+          <t>Michael Reamer</t>
         </is>
       </c>
       <c r="B249" s="6" t="inlineStr">
         <is>
-          <t>Newland Communities</t>
+          <t>Friendswood Development Company</t>
         </is>
       </c>
       <c r="C249" s="6" t="inlineStr">
         <is>
-          <t>Senior Vice President and Houston Division Manager, Newland (2019)</t>
+          <t>President, Friendswood Development Company</t>
         </is>
       </c>
       <c r="D249" s="7" t="inlineStr">
         <is>
-          <t>Masterplan owner</t>
+          <t>Already working with ICON</t>
         </is>
       </c>
       <c r="E249" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F249" s="6" t="inlineStr">
         <is>
@@ -27143,12 +27151,12 @@
       </c>
       <c r="G249" s="6" t="inlineStr">
         <is>
-          <t>San Diego HQ / Katy, Harris</t>
+          <t>Houston / Montgomery, Galveston</t>
         </is>
       </c>
       <c r="H249" s="6" t="inlineStr">
         <is>
-          <t>Elyson, 3,600 acres in Katy</t>
+          <t>Sells lots inside its own masterplans; Lennar builds</t>
         </is>
       </c>
       <c r="I249" s="8" t="inlineStr">
@@ -27158,7 +27166,7 @@
       </c>
       <c r="J249" s="9" t="inlineStr">
         <is>
-          <t>One Houston community, Elyson, at 3,600 acres in Katy.</t>
+          <t>Sells lots inside its own masterplans. Lennar builds the houses.</t>
         </is>
       </c>
       <c r="K249" s="8" t="inlineStr">
@@ -27168,27 +27176,27 @@
       </c>
       <c r="L249" s="9" t="inlineStr">
         <is>
-          <t>It sells lots, and the platform now sits inside Brookfield Residential.</t>
+          <t>Sells lots, wholly owned by Lennar, so the route is Lennar.</t>
         </is>
       </c>
       <c r="M249" s="8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partly</t>
         </is>
       </c>
       <c r="N249" s="9" t="inlineStr">
         <is>
-          <t>Nothing on record about construction method.</t>
+          <t>The parent, Lennar, built a hundred printed homes with ICON at Wolf Ranch. Friendswood itself buys no walls.</t>
         </is>
       </c>
       <c r="O249" s="8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partly</t>
         </is>
       </c>
       <c r="P249" s="10" t="inlineStr"/>
       <c r="Q249" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Alan%20Bauer%20Newland%20Communities","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Michael%20Reamer%20Friendswood%20Development%20Company","search")</f>
         <v/>
       </c>
       <c r="R249" s="11">
@@ -27197,47 +27205,47 @@
       </c>
       <c r="S249" s="6" t="inlineStr">
         <is>
-          <t>https://newlandco.com/</t>
+          <t>https://friendswooddevelopment.com/</t>
         </is>
       </c>
       <c r="T249" s="9" t="inlineStr">
         <is>
-          <t>3,600-acre Elyson, but Newland has been absorbed into Brookfield Residential and no longer publishes its own leadership. The one Houston name on record is from 2019.</t>
+          <t>Sells lots, wholly owned by Lennar since 2000. Lennar built a hundred printed homes with ICON at Wolf Ranch.</t>
         </is>
       </c>
       <c r="U249" s="6" t="inlineStr"/>
-      <c r="V249" s="9" t="inlineStr">
-        <is>
-          <t>Senior Vice President and Division Manager for Newland's Houston division, per the West Houston Association board announcement. Dated 2019 and unconfirmed since, because Newland no longer publishes its own leadership.</t>
-        </is>
-      </c>
+      <c r="V249" s="9" t="inlineStr"/>
       <c r="W249" s="6" t="inlineStr">
         <is>
-          <t>https://www.westhouston.org/2019/01/18/welcome-to-the-2019-board-or-directors/</t>
+          <t>https://friendswooddevelopment.com/people</t>
         </is>
       </c>
       <c r="X249" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/newland-communities-llc</t>
-        </is>
-      </c>
-      <c r="Y249" s="6" t="inlineStr"/>
+          <t>https://www.linkedin.com/company/friendswood-development-company</t>
+        </is>
+      </c>
+      <c r="Y249" s="6" t="inlineStr">
+        <is>
+          <t>https://friendswooddevelopment.com/people</t>
+        </is>
+      </c>
       <c r="Z249" s="6" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="12" t="inlineStr">
         <is>
-          <t>Michael Reamer</t>
+          <t>George Kopecky</t>
         </is>
       </c>
       <c r="B250" s="12" t="inlineStr">
         <is>
-          <t>Friendswood Development Company</t>
+          <t>GreenEco Builders</t>
         </is>
       </c>
       <c r="C250" s="12" t="inlineStr">
         <is>
-          <t>President, Friendswood Development Company</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D250" s="13" t="inlineStr">
@@ -27250,17 +27258,17 @@
       </c>
       <c r="F250" s="12" t="inlineStr">
         <is>
-          <t>Sells lots</t>
+          <t>Buys walls</t>
         </is>
       </c>
       <c r="G250" s="12" t="inlineStr">
         <is>
-          <t>Houston / Montgomery, Galveston</t>
+          <t>Tavola, New Caney</t>
         </is>
       </c>
       <c r="H250" s="12" t="inlineStr">
         <is>
-          <t>Sells lots inside its own masterplans; Lennar builds</t>
+          <t>Owned by Rausch Coleman, which Lennar bought in February 2025</t>
         </is>
       </c>
       <c r="I250" s="14" t="inlineStr">
@@ -27270,95 +27278,84 @@
       </c>
       <c r="J250" s="15" t="inlineStr">
         <is>
-          <t>Sells lots inside its own masterplans. Lennar builds the houses.</t>
+          <t>One confirmed community, Tavola in New Caney. The footprint is small.</t>
         </is>
       </c>
       <c r="K250" s="14" t="inlineStr">
         <is>
+          <t>Partly</t>
+        </is>
+      </c>
+      <c r="L250" s="15" t="inlineStr">
+        <is>
+          <t>No volume figure is published for the Houston operation.</t>
+        </is>
+      </c>
+      <c r="M250" s="14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L250" s="15" t="inlineStr">
-        <is>
-          <t>Sells lots, wholly owned by Lennar, so the route is Lennar.</t>
-        </is>
-      </c>
-      <c r="M250" s="14" t="inlineStr">
-        <is>
-          <t>Partly</t>
-        </is>
-      </c>
       <c r="N250" s="15" t="inlineStr">
         <is>
-          <t>The parent, Lennar, built a hundred printed homes with ICON at Wolf Ranch. Friendswood itself buys no walls.</t>
+          <t>Nothing on record. The energy-product claims this card used to carry came from a page that no longer exists.</t>
         </is>
       </c>
       <c r="O250" s="14" t="inlineStr">
         <is>
-          <t>Partly</t>
-        </is>
-      </c>
-      <c r="P250" s="10" t="inlineStr"/>
-      <c r="Q250" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Michael%20Reamer%20Friendswood%20Development%20Company","search")</f>
-        <v/>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P250" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/george-kopecky-7ba08a26/</t>
+        </is>
+      </c>
+      <c r="Q250" s="12" t="inlineStr"/>
       <c r="R250" s="16">
         <f>IF(P250="","ADD LINKEDIN","ok")</f>
         <v/>
       </c>
-      <c r="S250" s="12" t="inlineStr">
-        <is>
-          <t>https://friendswooddevelopment.com/</t>
-        </is>
-      </c>
+      <c r="S250" s="12" t="inlineStr"/>
       <c r="T250" s="15" t="inlineStr">
         <is>
-          <t>Sells lots, wholly owned by Lennar since 2000. Lennar built a hundred printed homes with ICON at Wolf Ranch.</t>
+          <t>Orders windows per home rather than per community so it can adopt newer products. Owned by Rausch Coleman Homes, which Lennar bought in February 2025.</t>
         </is>
       </c>
       <c r="U250" s="12" t="inlineStr"/>
-      <c r="V250" s="15" t="inlineStr"/>
-      <c r="W250" s="12" t="inlineStr">
-        <is>
-          <t>https://friendswooddevelopment.com/people</t>
-        </is>
-      </c>
-      <c r="X250" s="12" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/friendswood-development-company</t>
-        </is>
-      </c>
-      <c r="Y250" s="12" t="inlineStr">
-        <is>
-          <t>https://friendswooddevelopment.com/people</t>
-        </is>
-      </c>
+      <c r="V250" s="15" t="inlineStr">
+        <is>
+          <t>Indexed title reads George Kopecky, President at GreenEco Builders. Named as the firm's principal in trade coverage of the 2020 sale to Rausch Coleman.</t>
+        </is>
+      </c>
+      <c r="W250" s="12" t="inlineStr"/>
+      <c r="X250" s="12" t="inlineStr"/>
+      <c r="Y250" s="12" t="inlineStr"/>
       <c r="Z250" s="12" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="6" t="inlineStr">
         <is>
-          <t>George Kopecky</t>
+          <t>Steven D. Alvis</t>
         </is>
       </c>
       <c r="B251" s="6" t="inlineStr">
         <is>
-          <t>GreenEco Builders</t>
+          <t>NewQuest Properties</t>
         </is>
       </c>
       <c r="C251" s="6" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Co-Founder and Managing Partner</t>
         </is>
       </c>
       <c r="D251" s="7" t="inlineStr">
         <is>
-          <t>Already working with ICON</t>
+          <t>Off deck, screened out</t>
         </is>
       </c>
       <c r="E251" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F251" s="6" t="inlineStr">
         <is>
@@ -27367,80 +27364,79 @@
       </c>
       <c r="G251" s="6" t="inlineStr">
         <is>
-          <t>Tavola, New Caney</t>
+          <t>Houston HQ / Fort Bend, Brazoria</t>
         </is>
       </c>
       <c r="H251" s="6" t="inlineStr">
         <is>
-          <t>Owned by Rausch Coleman, which Lennar bought in February 2025</t>
+          <t>$3.1B portfolio, 12M sf managed</t>
         </is>
       </c>
       <c r="I251" s="8" t="inlineStr">
         <is>
-          <t>Partly</t>
-        </is>
-      </c>
-      <c r="J251" s="9" t="inlineStr">
-        <is>
-          <t>One confirmed community, Tavola in New Caney. The footprint is small.</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J251" s="9" t="inlineStr"/>
       <c r="K251" s="8" t="inlineStr">
         <is>
-          <t>Partly</t>
-        </is>
-      </c>
-      <c r="L251" s="9" t="inlineStr">
-        <is>
-          <t>No volume figure is published for the Houston operation.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L251" s="9" t="inlineStr"/>
       <c r="M251" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N251" s="9" t="inlineStr">
-        <is>
-          <t>Nothing on record. The energy-product claims this card used to carry came from a page that no longer exists.</t>
-        </is>
-      </c>
+      <c r="N251" s="9" t="inlineStr"/>
       <c r="O251" s="8" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P251" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/george-kopecky-7ba08a26/</t>
-        </is>
-      </c>
-      <c r="Q251" s="6" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P251" s="10" t="inlineStr"/>
+      <c r="Q251" s="6">
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Steven%20D.%20Alvis%20NewQuest%20Properties","search")</f>
+        <v/>
+      </c>
       <c r="R251" s="11">
         <f>IF(P251="","ADD LINKEDIN","ok")</f>
         <v/>
       </c>
-      <c r="S251" s="6" t="inlineStr"/>
+      <c r="S251" s="6" t="inlineStr">
+        <is>
+          <t>https://www.newquest.com/</t>
+        </is>
+      </c>
       <c r="T251" s="9" t="inlineStr">
         <is>
-          <t>Orders windows per home rather than per community so it can adopt newer products. Owned by Rausch Coleman Homes, which Lennar bought in February 2025.</t>
+          <t>$3.1B portfolio and a repeated Town Center format. Retail shells compete against tilt-wall, not stick framing.</t>
         </is>
       </c>
       <c r="U251" s="6" t="inlineStr"/>
-      <c r="V251" s="9" t="inlineStr">
-        <is>
-          <t>Indexed title reads George Kopecky, President at GreenEco Builders. Named as the firm's principal in trade coverage of the 2020 sale to Rausch Coleman.</t>
-        </is>
-      </c>
-      <c r="W251" s="6" t="inlineStr"/>
-      <c r="X251" s="6" t="inlineStr"/>
-      <c r="Y251" s="6" t="inlineStr"/>
+      <c r="V251" s="9" t="inlineStr"/>
+      <c r="W251" s="6" t="inlineStr">
+        <is>
+          <t>https://www.newquest.com/about-us/leadership/</t>
+        </is>
+      </c>
+      <c r="X251" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/newquest-properties</t>
+        </is>
+      </c>
+      <c r="Y251" s="6" t="inlineStr">
+        <is>
+          <t>https://www.newquest.com/about-us/leadership/</t>
+        </is>
+      </c>
       <c r="Z251" s="6" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="12" t="inlineStr">
         <is>
-          <t>Steven D. Alvis</t>
+          <t>Jay K. Sears</t>
         </is>
       </c>
       <c r="B252" s="12" t="inlineStr">
@@ -27501,7 +27497,7 @@
       </c>
       <c r="P252" s="10" t="inlineStr"/>
       <c r="Q252" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Steven%20D.%20Alvis%20NewQuest%20Properties","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Jay%20K.%20Sears%20NewQuest%20Properties","search")</f>
         <v/>
       </c>
       <c r="R252" s="16">
@@ -27540,7 +27536,7 @@
     <row r="253">
       <c r="A253" s="6" t="inlineStr">
         <is>
-          <t>Jay K. Sears</t>
+          <t>Austin Alvis</t>
         </is>
       </c>
       <c r="B253" s="6" t="inlineStr">
@@ -27550,7 +27546,7 @@
       </c>
       <c r="C253" s="6" t="inlineStr">
         <is>
-          <t>Co-Founder and Managing Partner</t>
+          <t>President and Chief Development Officer</t>
         </is>
       </c>
       <c r="D253" s="7" t="inlineStr">
@@ -27601,7 +27597,7 @@
       </c>
       <c r="P253" s="10" t="inlineStr"/>
       <c r="Q253" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Jay%20K.%20Sears%20NewQuest%20Properties","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Austin%20Alvis%20NewQuest%20Properties","search")</f>
         <v/>
       </c>
       <c r="R253" s="11">
@@ -27640,7 +27636,7 @@
     <row r="254">
       <c r="A254" s="12" t="inlineStr">
         <is>
-          <t>Austin Alvis</t>
+          <t>Jeff Horton</t>
         </is>
       </c>
       <c r="B254" s="12" t="inlineStr">
@@ -27650,7 +27646,7 @@
       </c>
       <c r="C254" s="12" t="inlineStr">
         <is>
-          <t>President and Chief Development Officer</t>
+          <t>Chief Operating Officer and Head of Capital Markets</t>
         </is>
       </c>
       <c r="D254" s="13" t="inlineStr">
@@ -27701,7 +27697,7 @@
       </c>
       <c r="P254" s="10" t="inlineStr"/>
       <c r="Q254" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Austin%20Alvis%20NewQuest%20Properties","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Jeff%20Horton%20NewQuest%20Properties","search")</f>
         <v/>
       </c>
       <c r="R254" s="16">
@@ -27740,17 +27736,17 @@
     <row r="255">
       <c r="A255" s="6" t="inlineStr">
         <is>
-          <t>Jeff Horton</t>
+          <t>K. Alan Hassenflu</t>
         </is>
       </c>
       <c r="B255" s="6" t="inlineStr">
         <is>
-          <t>NewQuest Properties</t>
+          <t>Fidelis Realty Partners</t>
         </is>
       </c>
       <c r="C255" s="6" t="inlineStr">
         <is>
-          <t>Chief Operating Officer and Head of Capital Markets</t>
+          <t>President and Chief Executive Officer</t>
         </is>
       </c>
       <c r="D255" s="7" t="inlineStr">
@@ -27768,12 +27764,12 @@
       </c>
       <c r="G255" s="6" t="inlineStr">
         <is>
-          <t>Houston HQ / Fort Bend, Brazoria</t>
+          <t>Houston HQ / Brazoria, Montgomery</t>
         </is>
       </c>
       <c r="H255" s="6" t="inlineStr">
         <is>
-          <t>$3.1B portfolio, 12M sf managed</t>
+          <t>26M sf, ~100 properties, 12 states</t>
         </is>
       </c>
       <c r="I255" s="8" t="inlineStr">
@@ -27796,12 +27792,12 @@
       <c r="N255" s="9" t="inlineStr"/>
       <c r="O255" s="8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Partly</t>
         </is>
       </c>
       <c r="P255" s="10" t="inlineStr"/>
       <c r="Q255" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Jeff%20Horton%20NewQuest%20Properties","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=K.%20Alan%20Hassenflu%20Fidelis%20Realty%20Partners","search")</f>
         <v/>
       </c>
       <c r="R255" s="11">
@@ -27810,29 +27806,33 @@
       </c>
       <c r="S255" s="6" t="inlineStr">
         <is>
-          <t>https://www.newquest.com/</t>
+          <t>https://www.frpltd.com/</t>
         </is>
       </c>
       <c r="T255" s="9" t="inlineStr">
         <is>
-          <t>$3.1B portfolio and a repeated Town Center format. Retail shells compete against tilt-wall, not stick framing.</t>
+          <t>Two land positions in target counties within 24 months. Every purchase price is undisclosed.</t>
         </is>
       </c>
       <c r="U255" s="6" t="inlineStr"/>
-      <c r="V255" s="9" t="inlineStr"/>
+      <c r="V255" s="9" t="inlineStr">
+        <is>
+          <t>President and Chief Executive Officer, a founder in 2003, formerly senior managing director at Trammell Crow.</t>
+        </is>
+      </c>
       <c r="W255" s="6" t="inlineStr">
         <is>
-          <t>https://www.newquest.com/about-us/leadership/</t>
+          <t>https://www.frpltd.com/about-fidelis/mission-values</t>
         </is>
       </c>
       <c r="X255" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/newquest-properties</t>
+          <t>https://www.linkedin.com/company/fidelis-realty-partners</t>
         </is>
       </c>
       <c r="Y255" s="6" t="inlineStr">
         <is>
-          <t>https://www.newquest.com/about-us/leadership/</t>
+          <t>https://www.frpltd.com/about-fidelis/mission-values</t>
         </is>
       </c>
       <c r="Z255" s="6" t="inlineStr"/>
@@ -27840,7 +27840,7 @@
     <row r="256">
       <c r="A256" s="12" t="inlineStr">
         <is>
-          <t>K. Alan Hassenflu</t>
+          <t>Glenn Airola</t>
         </is>
       </c>
       <c r="B256" s="12" t="inlineStr">
@@ -27850,7 +27850,7 @@
       </c>
       <c r="C256" s="12" t="inlineStr">
         <is>
-          <t>President and Chief Executive Officer</t>
+          <t>Executive Vice President, General Counsel and Chief Administrative Officer</t>
         </is>
       </c>
       <c r="D256" s="13" t="inlineStr">
@@ -27901,7 +27901,7 @@
       </c>
       <c r="P256" s="10" t="inlineStr"/>
       <c r="Q256" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=K.%20Alan%20Hassenflu%20Fidelis%20Realty%20Partners","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Glenn%20Airola%20Fidelis%20Realty%20Partners","search")</f>
         <v/>
       </c>
       <c r="R256" s="16">
@@ -27919,11 +27919,7 @@
         </is>
       </c>
       <c r="U256" s="12" t="inlineStr"/>
-      <c r="V256" s="15" t="inlineStr">
-        <is>
-          <t>President and Chief Executive Officer, a founder in 2003, formerly senior managing director at Trammell Crow.</t>
-        </is>
-      </c>
+      <c r="V256" s="15" t="inlineStr"/>
       <c r="W256" s="12" t="inlineStr">
         <is>
           <t>https://www.frpltd.com/about-fidelis/mission-values</t>
@@ -27944,7 +27940,7 @@
     <row r="257">
       <c r="A257" s="6" t="inlineStr">
         <is>
-          <t>Glenn Airola</t>
+          <t>R. Carson Wilson IV</t>
         </is>
       </c>
       <c r="B257" s="6" t="inlineStr">
@@ -27954,7 +27950,7 @@
       </c>
       <c r="C257" s="6" t="inlineStr">
         <is>
-          <t>Executive Vice President, General Counsel and Chief Administrative Officer</t>
+          <t>Vice President, Leasing</t>
         </is>
       </c>
       <c r="D257" s="7" t="inlineStr">
@@ -28003,11 +27999,12 @@
           <t>Partly</t>
         </is>
       </c>
-      <c r="P257" s="10" t="inlineStr"/>
-      <c r="Q257" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Glenn%20Airola%20Fidelis%20Realty%20Partners","search")</f>
-        <v/>
-      </c>
+      <c r="P257" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/r-carson-wilson-iv-9b7525292/</t>
+        </is>
+      </c>
+      <c r="Q257" s="6" t="inlineStr"/>
       <c r="R257" s="11">
         <f>IF(P257="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -28022,13 +28019,17 @@
           <t>Two land positions in target counties within 24 months. Every purchase price is undisclosed.</t>
         </is>
       </c>
-      <c r="U257" s="6" t="inlineStr"/>
-      <c r="V257" s="9" t="inlineStr"/>
-      <c r="W257" s="6" t="inlineStr">
-        <is>
-          <t>https://www.frpltd.com/about-fidelis/mission-values</t>
-        </is>
-      </c>
+      <c r="U257" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="V257" s="9" t="inlineStr">
+        <is>
+          <t>Executive Vice President - Leasing, Construction and Development at Fidelis Realty Partners. Greater Houston. One title covers all three, so the person who signs the lease also owns the build.</t>
+        </is>
+      </c>
+      <c r="W257" s="6" t="inlineStr"/>
       <c r="X257" s="6" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/fidelis-realty-partners</t>
@@ -28044,17 +28045,17 @@
     <row r="258">
       <c r="A258" s="12" t="inlineStr">
         <is>
-          <t>R. Carson Wilson IV</t>
+          <t>Brandt Bowden</t>
         </is>
       </c>
       <c r="B258" s="12" t="inlineStr">
         <is>
-          <t>Fidelis Realty Partners</t>
+          <t>The Hanover Company</t>
         </is>
       </c>
       <c r="C258" s="12" t="inlineStr">
         <is>
-          <t>Vice President, Leasing</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="D258" s="13" t="inlineStr">
@@ -28072,12 +28073,12 @@
       </c>
       <c r="G258" s="12" t="inlineStr">
         <is>
-          <t>Houston HQ / Brazoria, Montgomery</t>
+          <t>Houston HQ, Harris County</t>
         </is>
       </c>
       <c r="H258" s="12" t="inlineStr">
         <is>
-          <t>26M sf, ~100 properties, 12 states</t>
+          <t>19 markets, in-house construction arm</t>
         </is>
       </c>
       <c r="I258" s="14" t="inlineStr">
@@ -28103,45 +28104,40 @@
           <t>Partly</t>
         </is>
       </c>
-      <c r="P258" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/r-carson-wilson-iv-9b7525292/</t>
-        </is>
-      </c>
-      <c r="Q258" s="12" t="inlineStr"/>
+      <c r="P258" s="10" t="inlineStr"/>
+      <c r="Q258" s="12">
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Brandt%20Bowden%20The%20Hanover%20Company","search")</f>
+        <v/>
+      </c>
       <c r="R258" s="16">
         <f>IF(P258="","ADD LINKEDIN","ok")</f>
         <v/>
       </c>
       <c r="S258" s="12" t="inlineStr">
         <is>
-          <t>https://www.frpltd.com/</t>
+          <t>https://www.hanoverco.com/</t>
         </is>
       </c>
       <c r="T258" s="15" t="inlineStr">
         <is>
-          <t>Two land positions in target counties within 24 months. Every purchase price is undisclosed.</t>
-        </is>
-      </c>
-      <c r="U258" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+          <t>An in-house construction arm and a Houston HQ since 1982, but no Houston project could be sourced.</t>
+        </is>
+      </c>
+      <c r="U258" s="12" t="inlineStr"/>
       <c r="V258" s="15" t="inlineStr">
         <is>
-          <t>Executive Vice President - Leasing, Construction and Development at Fidelis Realty Partners. Greater Houston. One title covers all three, so the person who signs the lease also owns the build.</t>
-        </is>
-      </c>
-      <c r="W258" s="12" t="inlineStr"/>
-      <c r="X258" s="12" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/fidelis-realty-partners</t>
-        </is>
-      </c>
+          <t>Chief Executive Officer of Hanover, overseeing capital, development and construction, previously chief investment officer.</t>
+        </is>
+      </c>
+      <c r="W258" s="12" t="inlineStr">
+        <is>
+          <t>https://knowledge.uli.org/en/people/b/b/brandt-bowden-f34f</t>
+        </is>
+      </c>
+      <c r="X258" s="12" t="inlineStr"/>
       <c r="Y258" s="12" t="inlineStr">
         <is>
-          <t>https://www.frpltd.com/about-fidelis/mission-values</t>
+          <t>https://www.hanoverco.com/leadership</t>
         </is>
       </c>
       <c r="Z258" s="12" t="inlineStr"/>
@@ -28149,7 +28145,7 @@
     <row r="259">
       <c r="A259" s="6" t="inlineStr">
         <is>
-          <t>Brandt Bowden</t>
+          <t>Murry Bowden</t>
         </is>
       </c>
       <c r="B259" s="6" t="inlineStr">
@@ -28159,7 +28155,7 @@
       </c>
       <c r="C259" s="6" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Founder and Executive Chairman</t>
         </is>
       </c>
       <c r="D259" s="7" t="inlineStr">
@@ -28210,7 +28206,7 @@
       </c>
       <c r="P259" s="10" t="inlineStr"/>
       <c r="Q259" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Brandt%20Bowden%20The%20Hanover%20Company","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Murry%20Bowden%20The%20Hanover%20Company","search")</f>
         <v/>
       </c>
       <c r="R259" s="11">
@@ -28230,12 +28226,12 @@
       <c r="U259" s="6" t="inlineStr"/>
       <c r="V259" s="9" t="inlineStr">
         <is>
-          <t>Chief Executive Officer of Hanover, overseeing capital, development and construction, previously chief investment officer.</t>
+          <t>Founder, Chairman and Chief Executive Officer, responsible for strategy and investment decisions.</t>
         </is>
       </c>
       <c r="W259" s="6" t="inlineStr">
         <is>
-          <t>https://knowledge.uli.org/en/people/b/b/brandt-bowden-f34f</t>
+          <t>https://www.nmhc.org/meetings/meetings-pages/meeting-materials/j-murry-bowden-biography/</t>
         </is>
       </c>
       <c r="X259" s="6" t="inlineStr"/>
@@ -28249,7 +28245,7 @@
     <row r="260">
       <c r="A260" s="12" t="inlineStr">
         <is>
-          <t>Murry Bowden</t>
+          <t>John Nash</t>
         </is>
       </c>
       <c r="B260" s="12" t="inlineStr">
@@ -28259,7 +28255,7 @@
       </c>
       <c r="C260" s="12" t="inlineStr">
         <is>
-          <t>Founder and Executive Chairman</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D260" s="13" t="inlineStr">
@@ -28310,7 +28306,7 @@
       </c>
       <c r="P260" s="10" t="inlineStr"/>
       <c r="Q260" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Murry%20Bowden%20The%20Hanover%20Company","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=John%20Nash%20The%20Hanover%20Company","search")</f>
         <v/>
       </c>
       <c r="R260" s="16">
@@ -28330,12 +28326,12 @@
       <c r="U260" s="12" t="inlineStr"/>
       <c r="V260" s="15" t="inlineStr">
         <is>
-          <t>Founder, Chairman and Chief Executive Officer, responsible for strategy and investment decisions.</t>
+          <t>President. Thirty-three years with Hanover, twenty-three of them as president, per the McCombs alumni network.</t>
         </is>
       </c>
       <c r="W260" s="12" t="inlineStr">
         <is>
-          <t>https://www.nmhc.org/meetings/meetings-pages/meeting-materials/j-murry-bowden-biography/</t>
+          <t>https://www.hanoverco.com/leadership</t>
         </is>
       </c>
       <c r="X260" s="12" t="inlineStr"/>
@@ -28349,7 +28345,7 @@
     <row r="261">
       <c r="A261" s="6" t="inlineStr">
         <is>
-          <t>John Nash</t>
+          <t>John Garibaldi</t>
         </is>
       </c>
       <c r="B261" s="6" t="inlineStr">
@@ -28359,7 +28355,7 @@
       </c>
       <c r="C261" s="6" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>President, Multifamily</t>
         </is>
       </c>
       <c r="D261" s="7" t="inlineStr">
@@ -28410,7 +28406,7 @@
       </c>
       <c r="P261" s="10" t="inlineStr"/>
       <c r="Q261" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=John%20Nash%20The%20Hanover%20Company","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=John%20Garibaldi%20The%20Hanover%20Company","search")</f>
         <v/>
       </c>
       <c r="R261" s="11">
@@ -28430,7 +28426,7 @@
       <c r="U261" s="6" t="inlineStr"/>
       <c r="V261" s="9" t="inlineStr">
         <is>
-          <t>President. Thirty-three years with Hanover, twenty-three of them as president, per the McCombs alumni network.</t>
+          <t>President, Multifamily. Twenty-five years with the firm, starting as a development partner in Houston in 1999.</t>
         </is>
       </c>
       <c r="W261" s="6" t="inlineStr">
@@ -28449,7 +28445,7 @@
     <row r="262">
       <c r="A262" s="12" t="inlineStr">
         <is>
-          <t>John Garibaldi</t>
+          <t>Thomas Knutson</t>
         </is>
       </c>
       <c r="B262" s="12" t="inlineStr">
@@ -28459,7 +28455,7 @@
       </c>
       <c r="C262" s="12" t="inlineStr">
         <is>
-          <t>President, Multifamily</t>
+          <t>President of Construction, The Hanover Company</t>
         </is>
       </c>
       <c r="D262" s="13" t="inlineStr">
@@ -28508,11 +28504,12 @@
           <t>Partly</t>
         </is>
       </c>
-      <c r="P262" s="10" t="inlineStr"/>
-      <c r="Q262" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=John%20Garibaldi%20The%20Hanover%20Company","search")</f>
-        <v/>
-      </c>
+      <c r="P262" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/thomas-knutson-a741898/</t>
+        </is>
+      </c>
+      <c r="Q262" s="12" t="inlineStr"/>
       <c r="R262" s="16">
         <f>IF(P262="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -28527,17 +28524,17 @@
           <t>An in-house construction arm and a Houston HQ since 1982, but no Houston project could be sourced.</t>
         </is>
       </c>
-      <c r="U262" s="12" t="inlineStr"/>
+      <c r="U262" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
       <c r="V262" s="15" t="inlineStr">
         <is>
-          <t>President, Multifamily. Twenty-five years with the firm, starting as a development partner in Houston in 1999.</t>
-        </is>
-      </c>
-      <c r="W262" s="12" t="inlineStr">
-        <is>
-          <t>https://www.hanoverco.com/leadership</t>
-        </is>
-      </c>
+          <t>President - Construction at The Hanover Company. Houston, Texas. Hanover builds its own work, so this is the head of the in-house contractor.</t>
+        </is>
+      </c>
+      <c r="W262" s="12" t="inlineStr"/>
       <c r="X262" s="12" t="inlineStr"/>
       <c r="Y262" s="12" t="inlineStr">
         <is>
@@ -28549,7 +28546,7 @@
     <row r="263">
       <c r="A263" s="6" t="inlineStr">
         <is>
-          <t>Thomas Knutson</t>
+          <t>Mike Wright</t>
         </is>
       </c>
       <c r="B263" s="6" t="inlineStr">
@@ -28559,7 +28556,7 @@
       </c>
       <c r="C263" s="6" t="inlineStr">
         <is>
-          <t>President of Construction, The Hanover Company</t>
+          <t>Vice President of Preconstruction and Estimating, The Hanover Company</t>
         </is>
       </c>
       <c r="D263" s="7" t="inlineStr">
@@ -28610,7 +28607,7 @@
       </c>
       <c r="P263" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/thomas-knutson-a741898/</t>
+          <t>https://www.linkedin.com/in/mike-wright-7795a8b/</t>
         </is>
       </c>
       <c r="Q263" s="6" t="inlineStr"/>
@@ -28635,7 +28632,7 @@
       </c>
       <c r="V263" s="9" t="inlineStr">
         <is>
-          <t>President - Construction at The Hanover Company. Houston, Texas. Hanover builds its own work, so this is the head of the in-house contractor.</t>
+          <t>Vice President of Preconstruction &amp; Estimating at The Hanover Company. Katy, Texas. Preconstruction is where an unfamiliar wall system gets priced or dismissed, so this is the first real test of a printed assembly.</t>
         </is>
       </c>
       <c r="W263" s="6" t="inlineStr"/>
@@ -28650,17 +28647,17 @@
     <row r="264">
       <c r="A264" s="12" t="inlineStr">
         <is>
-          <t>Mike Wright</t>
+          <t>Jeff Read</t>
         </is>
       </c>
       <c r="B264" s="12" t="inlineStr">
         <is>
-          <t>The Hanover Company</t>
+          <t>Read King</t>
         </is>
       </c>
       <c r="C264" s="12" t="inlineStr">
         <is>
-          <t>Vice President of Preconstruction and Estimating, The Hanover Company</t>
+          <t>Principal and Co-Founder</t>
         </is>
       </c>
       <c r="D264" s="13" t="inlineStr">
@@ -28678,12 +28675,12 @@
       </c>
       <c r="G264" s="12" t="inlineStr">
         <is>
-          <t>Houston HQ, Harris County</t>
+          <t>Houston HQ / Fort Bend, Harris</t>
         </is>
       </c>
       <c r="H264" s="12" t="inlineStr">
         <is>
-          <t>19 markets, in-house construction arm</t>
+          <t>36 freestanding ER centres, 100+ build-to-suit</t>
         </is>
       </c>
       <c r="I264" s="14" t="inlineStr">
@@ -28706,44 +28703,43 @@
       <c r="N264" s="15" t="inlineStr"/>
       <c r="O264" s="14" t="inlineStr">
         <is>
-          <t>Partly</t>
-        </is>
-      </c>
-      <c r="P264" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/mike-wright-7795a8b/</t>
-        </is>
-      </c>
-      <c r="Q264" s="12" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P264" s="10" t="inlineStr"/>
+      <c r="Q264" s="12">
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Jeff%20Read%20Read%20King","search")</f>
+        <v/>
+      </c>
       <c r="R264" s="16">
         <f>IF(P264="","ADD LINKEDIN","ok")</f>
         <v/>
       </c>
       <c r="S264" s="12" t="inlineStr">
         <is>
-          <t>https://www.hanoverco.com/</t>
+          <t>https://read-king.com/</t>
         </is>
       </c>
       <c r="T264" s="15" t="inlineStr">
         <is>
-          <t>An in-house construction arm and a Houston HQ since 1982, but no Houston project could be sourced.</t>
-        </is>
-      </c>
-      <c r="U264" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="V264" s="15" t="inlineStr">
-        <is>
-          <t>Vice President of Preconstruction &amp; Estimating at The Hanover Company. Katy, Texas. Preconstruction is where an unfamiliar wall system gets priced or dismissed, so this is the first real test of a printed assembly.</t>
-        </is>
-      </c>
-      <c r="W264" s="12" t="inlineStr"/>
-      <c r="X264" s="12" t="inlineStr"/>
+          <t>36 freestanding emergency centres and over 100 build-to-suits, the most repeated small-commercial format screened.</t>
+        </is>
+      </c>
+      <c r="U264" s="12" t="inlineStr"/>
+      <c r="V264" s="15" t="inlineStr"/>
+      <c r="W264" s="12" t="inlineStr">
+        <is>
+          <t>https://www.read-king.com/team</t>
+        </is>
+      </c>
+      <c r="X264" s="12" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/read-king-inc-</t>
+        </is>
+      </c>
       <c r="Y264" s="12" t="inlineStr">
         <is>
-          <t>https://www.hanoverco.com/leadership</t>
+          <t>https://www.read-king.com/team</t>
         </is>
       </c>
       <c r="Z264" s="12" t="inlineStr"/>
@@ -28751,7 +28747,7 @@
     <row r="265">
       <c r="A265" s="6" t="inlineStr">
         <is>
-          <t>Jeff Read</t>
+          <t>Ewing King</t>
         </is>
       </c>
       <c r="B265" s="6" t="inlineStr">
@@ -28761,7 +28757,7 @@
       </c>
       <c r="C265" s="6" t="inlineStr">
         <is>
-          <t>Principal and Co-Founder</t>
+          <t>Principal</t>
         </is>
       </c>
       <c r="D265" s="7" t="inlineStr">
@@ -28812,7 +28808,7 @@
       </c>
       <c r="P265" s="10" t="inlineStr"/>
       <c r="Q265" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Jeff%20Read%20Read%20King","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Ewing%20King%20Read%20King","search")</f>
         <v/>
       </c>
       <c r="R265" s="11">
@@ -28851,7 +28847,7 @@
     <row r="266">
       <c r="A266" s="12" t="inlineStr">
         <is>
-          <t>Ewing King</t>
+          <t>Blake Allen</t>
         </is>
       </c>
       <c r="B266" s="12" t="inlineStr">
@@ -28861,7 +28857,7 @@
       </c>
       <c r="C266" s="12" t="inlineStr">
         <is>
-          <t>Principal</t>
+          <t>Chief Financial Officer</t>
         </is>
       </c>
       <c r="D266" s="13" t="inlineStr">
@@ -28912,7 +28908,7 @@
       </c>
       <c r="P266" s="10" t="inlineStr"/>
       <c r="Q266" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Ewing%20King%20Read%20King","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Blake%20Allen%20Read%20King","search")</f>
         <v/>
       </c>
       <c r="R266" s="16">
@@ -28951,7 +28947,7 @@
     <row r="267">
       <c r="A267" s="6" t="inlineStr">
         <is>
-          <t>Blake Allen</t>
+          <t>Telisia Amaning</t>
         </is>
       </c>
       <c r="B267" s="6" t="inlineStr">
@@ -28961,7 +28957,7 @@
       </c>
       <c r="C267" s="6" t="inlineStr">
         <is>
-          <t>Chief Financial Officer</t>
+          <t>Chief Operating Officer</t>
         </is>
       </c>
       <c r="D267" s="7" t="inlineStr">
@@ -29010,11 +29006,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="P267" s="10" t="inlineStr"/>
-      <c r="Q267" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Blake%20Allen%20Read%20King","search")</f>
-        <v/>
-      </c>
+      <c r="P267" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/telisiaamaning/</t>
+        </is>
+      </c>
+      <c r="Q267" s="6" t="inlineStr"/>
       <c r="R267" s="11">
         <f>IF(P267="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -29030,12 +29027,12 @@
         </is>
       </c>
       <c r="U267" s="6" t="inlineStr"/>
-      <c r="V267" s="9" t="inlineStr"/>
-      <c r="W267" s="6" t="inlineStr">
-        <is>
-          <t>https://www.read-king.com/team</t>
-        </is>
-      </c>
+      <c r="V267" s="9" t="inlineStr">
+        <is>
+          <t>Chief Operating Officer, READ KING. Houston, Texas.</t>
+        </is>
+      </c>
+      <c r="W267" s="6" t="inlineStr"/>
       <c r="X267" s="6" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/read-king-inc-</t>
@@ -29051,17 +29048,17 @@
     <row r="268">
       <c r="A268" s="12" t="inlineStr">
         <is>
-          <t>Telisia Amaning</t>
+          <t>Alex Jessett</t>
         </is>
       </c>
       <c r="B268" s="12" t="inlineStr">
         <is>
-          <t>Read King</t>
+          <t>Camden Property Trust</t>
         </is>
       </c>
       <c r="C268" s="12" t="inlineStr">
         <is>
-          <t>Chief Operating Officer</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="D268" s="13" t="inlineStr">
@@ -29079,17 +29076,17 @@
       </c>
       <c r="G268" s="12" t="inlineStr">
         <is>
-          <t>Houston HQ / Fort Bend, Harris</t>
+          <t>Houston HQ / Fort Bend, Montgomery</t>
         </is>
       </c>
       <c r="H268" s="12" t="inlineStr">
         <is>
-          <t>36 freestanding ER centres, 100+ build-to-suit</t>
+          <t>$155M into 389 BTR homes</t>
         </is>
       </c>
       <c r="I268" s="14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Partly</t>
         </is>
       </c>
       <c r="J268" s="15" t="inlineStr"/>
@@ -29107,44 +29104,47 @@
       <c r="N268" s="15" t="inlineStr"/>
       <c r="O268" s="14" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P268" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/telisiaamaning/</t>
-        </is>
-      </c>
-      <c r="Q268" s="12" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P268" s="10" t="inlineStr"/>
+      <c r="Q268" s="12">
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Alex%20Jessett%20Camden%20Property%20Trust","search")</f>
+        <v/>
+      </c>
       <c r="R268" s="16">
         <f>IF(P268="","ADD LINKEDIN","ok")</f>
         <v/>
       </c>
       <c r="S268" s="12" t="inlineStr">
         <is>
-          <t>https://read-king.com/</t>
+          <t>https://www.camdenliving.com/</t>
         </is>
       </c>
       <c r="T268" s="15" t="inlineStr">
         <is>
-          <t>36 freestanding emergency centres and over 100 build-to-suits, the most repeated small-commercial format screened.</t>
+          <t>$155M into 389 build-to-rent homes, Houston HQ, holds long term. Figures date to 2022.</t>
         </is>
       </c>
       <c r="U268" s="12" t="inlineStr"/>
       <c r="V268" s="15" t="inlineStr">
         <is>
-          <t>Chief Operating Officer, READ KING. Houston, Texas.</t>
-        </is>
-      </c>
-      <c r="W268" s="12" t="inlineStr"/>
+          <t>Chief Executive Officer, previously President and Chief Financial Officer, at Camden since 1999.</t>
+        </is>
+      </c>
+      <c r="W268" s="12" t="inlineStr">
+        <is>
+          <t>https://investors.camdenliving.com/investors/governance/board-of-directors/default.aspx</t>
+        </is>
+      </c>
       <c r="X268" s="12" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/read-king-inc-</t>
+          <t>https://www.linkedin.com/company/camden-property-trust</t>
         </is>
       </c>
       <c r="Y268" s="12" t="inlineStr">
         <is>
-          <t>https://www.read-king.com/team</t>
+          <t>https://investors.camdenliving.com/investors/governance/board-of-directors/default.aspx</t>
         </is>
       </c>
       <c r="Z268" s="12" t="inlineStr"/>
@@ -29152,7 +29152,7 @@
     <row r="269">
       <c r="A269" s="6" t="inlineStr">
         <is>
-          <t>Alex Jessett</t>
+          <t>Richard J. Campo</t>
         </is>
       </c>
       <c r="B269" s="6" t="inlineStr">
@@ -29162,7 +29162,7 @@
       </c>
       <c r="C269" s="6" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Executive Chairman of the Board of Trust Managers</t>
         </is>
       </c>
       <c r="D269" s="7" t="inlineStr">
@@ -29213,7 +29213,7 @@
       </c>
       <c r="P269" s="10" t="inlineStr"/>
       <c r="Q269" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Alex%20Jessett%20Camden%20Property%20Trust","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Richard%20J.%20Campo%20Camden%20Property%20Trust","search")</f>
         <v/>
       </c>
       <c r="R269" s="11">
@@ -29233,7 +29233,7 @@
       <c r="U269" s="6" t="inlineStr"/>
       <c r="V269" s="9" t="inlineStr">
         <is>
-          <t>Chief Executive Officer, previously President and Chief Financial Officer, at Camden since 1999.</t>
+          <t>Executive Chairman, chief executive from the 1993 listing until 2026.</t>
         </is>
       </c>
       <c r="W269" s="6" t="inlineStr">
@@ -29256,7 +29256,7 @@
     <row r="270">
       <c r="A270" s="12" t="inlineStr">
         <is>
-          <t>Richard J. Campo</t>
+          <t>Michael Eilertsen</t>
         </is>
       </c>
       <c r="B270" s="12" t="inlineStr">
@@ -29266,7 +29266,7 @@
       </c>
       <c r="C270" s="12" t="inlineStr">
         <is>
-          <t>Executive Chairman of the Board of Trust Managers</t>
+          <t>Vice President of Construction, Camden Property Trust</t>
         </is>
       </c>
       <c r="D270" s="13" t="inlineStr">
@@ -29315,11 +29315,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P270" s="10" t="inlineStr"/>
-      <c r="Q270" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Richard%20J.%20Campo%20Camden%20Property%20Trust","search")</f>
-        <v/>
-      </c>
+      <c r="P270" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/michael-eilertsen-68a59911/</t>
+        </is>
+      </c>
+      <c r="Q270" s="12" t="inlineStr"/>
       <c r="R270" s="16">
         <f>IF(P270="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -29334,17 +29335,13 @@
           <t>$155M into 389 build-to-rent homes, Houston HQ, holds long term. Figures date to 2022.</t>
         </is>
       </c>
-      <c r="U270" s="12" t="inlineStr"/>
-      <c r="V270" s="15" t="inlineStr">
-        <is>
-          <t>Executive Chairman, chief executive from the 1993 listing until 2026.</t>
-        </is>
-      </c>
-      <c r="W270" s="12" t="inlineStr">
-        <is>
-          <t>https://investors.camdenliving.com/investors/governance/board-of-directors/default.aspx</t>
-        </is>
-      </c>
+      <c r="U270" s="12" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="V270" s="15" t="inlineStr"/>
+      <c r="W270" s="12" t="inlineStr"/>
       <c r="X270" s="12" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/camden-property-trust</t>
@@ -29360,17 +29357,17 @@
     <row r="271">
       <c r="A271" s="6" t="inlineStr">
         <is>
-          <t>Michael Eilertsen</t>
+          <t>Bob Faith</t>
         </is>
       </c>
       <c r="B271" s="6" t="inlineStr">
         <is>
-          <t>Camden Property Trust</t>
+          <t>Greystar (Summerwell)</t>
         </is>
       </c>
       <c r="C271" s="6" t="inlineStr">
         <is>
-          <t>Vice President of Construction, Camden Property Trust</t>
+          <t>Founder, Chairman and Chief Executive Officer</t>
         </is>
       </c>
       <c r="D271" s="7" t="inlineStr">
@@ -29388,12 +29385,12 @@
       </c>
       <c r="G271" s="6" t="inlineStr">
         <is>
-          <t>Houston HQ / Fort Bend, Montgomery</t>
+          <t>Charleston HQ / Katy, Harris-Waller</t>
         </is>
       </c>
       <c r="H271" s="6" t="inlineStr">
         <is>
-          <t>$155M into 389 BTR homes</t>
+          <t>Summerwell: 10,000+ homes, 50 properties</t>
         </is>
       </c>
       <c r="I271" s="8" t="inlineStr">
@@ -29419,41 +29416,40 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P271" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/michael-eilertsen-68a59911/</t>
-        </is>
-      </c>
-      <c r="Q271" s="6" t="inlineStr"/>
+      <c r="P271" s="10" t="inlineStr"/>
+      <c r="Q271" s="6">
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Bob%20Faith%20Greystar","search")</f>
+        <v/>
+      </c>
       <c r="R271" s="11">
         <f>IF(P271="","ADD LINKEDIN","ok")</f>
         <v/>
       </c>
       <c r="S271" s="6" t="inlineStr">
         <is>
-          <t>https://www.camdenliving.com/</t>
+          <t>https://www.greystar.com/</t>
         </is>
       </c>
       <c r="T271" s="9" t="inlineStr">
         <is>
-          <t>$155M into 389 build-to-rent homes, Houston HQ, holds long term. Figures date to 2022.</t>
-        </is>
-      </c>
-      <c r="U271" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+          <t>156 units inside Sunterra, a Houston-based development director, and a 10,000-home national brand. Costs withheld.</t>
+        </is>
+      </c>
+      <c r="U271" s="6" t="inlineStr"/>
       <c r="V271" s="9" t="inlineStr"/>
-      <c r="W271" s="6" t="inlineStr"/>
+      <c r="W271" s="6" t="inlineStr">
+        <is>
+          <t>https://www.greystar.com/contact-us/our-people/bob-faith</t>
+        </is>
+      </c>
       <c r="X271" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/camden-property-trust</t>
+          <t>https://www.linkedin.com/company/greystar</t>
         </is>
       </c>
       <c r="Y271" s="6" t="inlineStr">
         <is>
-          <t>https://investors.camdenliving.com/investors/governance/board-of-directors/default.aspx</t>
+          <t>https://www.greystar.com/business/about-greystar/our-leadership</t>
         </is>
       </c>
       <c r="Z271" s="6" t="inlineStr"/>
@@ -29461,7 +29457,7 @@
     <row r="272">
       <c r="A272" s="12" t="inlineStr">
         <is>
-          <t>Bob Faith</t>
+          <t>Brian Herwald</t>
         </is>
       </c>
       <c r="B272" s="12" t="inlineStr">
@@ -29471,7 +29467,7 @@
       </c>
       <c r="C272" s="12" t="inlineStr">
         <is>
-          <t>Founder, Chairman and Chief Executive Officer</t>
+          <t>Managing Director of Development, Houston</t>
         </is>
       </c>
       <c r="D272" s="13" t="inlineStr">
@@ -29522,7 +29518,7 @@
       </c>
       <c r="P272" s="10" t="inlineStr"/>
       <c r="Q272" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Bob%20Faith%20Greystar","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Brian%20Herwald%20Greystar","search")</f>
         <v/>
       </c>
       <c r="R272" s="16">
@@ -29540,10 +29536,14 @@
         </is>
       </c>
       <c r="U272" s="12" t="inlineStr"/>
-      <c r="V272" s="15" t="inlineStr"/>
+      <c r="V272" s="15" t="inlineStr">
+        <is>
+          <t>Managing Director of Development, quoted on Greystar's first Houston logistics project.</t>
+        </is>
+      </c>
       <c r="W272" s="12" t="inlineStr">
         <is>
-          <t>https://www.greystar.com/contact-us/our-people/bob-faith</t>
+          <t>https://www.greystar.com/business/about-greystar/newsroom/greystar-completes-first-logistics-project-in-houston</t>
         </is>
       </c>
       <c r="X272" s="12" t="inlineStr">
@@ -29561,17 +29561,17 @@
     <row r="273">
       <c r="A273" s="6" t="inlineStr">
         <is>
-          <t>Brian Herwald</t>
+          <t>Brian Dinerstein</t>
         </is>
       </c>
       <c r="B273" s="6" t="inlineStr">
         <is>
-          <t>Greystar (Summerwell)</t>
+          <t>The Dinerstein Companies</t>
         </is>
       </c>
       <c r="C273" s="6" t="inlineStr">
         <is>
-          <t>Managing Director of Development, Houston</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="D273" s="7" t="inlineStr">
@@ -29589,12 +29589,12 @@
       </c>
       <c r="G273" s="6" t="inlineStr">
         <is>
-          <t>Charleston HQ / Katy, Harris-Waller</t>
+          <t>Houston HQ / Fort Bend</t>
         </is>
       </c>
       <c r="H273" s="6" t="inlineStr">
         <is>
-          <t>Summerwell: 10,000+ homes, 50 properties</t>
+          <t>186 BTR homes, Harrison Street JV</t>
         </is>
       </c>
       <c r="I273" s="8" t="inlineStr">
@@ -29622,7 +29622,7 @@
       </c>
       <c r="P273" s="10" t="inlineStr"/>
       <c r="Q273" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Brian%20Herwald%20Greystar","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Brian%20Dinerstein%20The%20Dinerstein%20Companies","search")</f>
         <v/>
       </c>
       <c r="R273" s="11">
@@ -29631,33 +29631,33 @@
       </c>
       <c r="S273" s="6" t="inlineStr">
         <is>
-          <t>https://www.greystar.com/</t>
+          <t>https://www.dinersteincos.com/</t>
         </is>
       </c>
       <c r="T273" s="9" t="inlineStr">
         <is>
-          <t>156 units inside Sunterra, a Houston-based development director, and a 10,000-home national brand. Costs withheld.</t>
+          <t>186 build-to-rent homes with Harrison Street and 70 years in Houston. Launch coverage is amenities only.</t>
         </is>
       </c>
       <c r="U273" s="6" t="inlineStr"/>
       <c r="V273" s="9" t="inlineStr">
         <is>
-          <t>Managing Director of Development, quoted on Greystar's first Houston logistics project.</t>
+          <t>The firm's own bio page. Chief Executive Officer of a developer and operator with $4.3 billion under management.</t>
         </is>
       </c>
       <c r="W273" s="6" t="inlineStr">
         <is>
-          <t>https://www.greystar.com/business/about-greystar/newsroom/greystar-completes-first-logistics-project-in-houston</t>
+          <t>https://www.dinersteincos.com/team/brian-dinerstein</t>
         </is>
       </c>
       <c r="X273" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/greystar</t>
+          <t>https://www.linkedin.com/company/the-dinerstein-companies/</t>
         </is>
       </c>
       <c r="Y273" s="6" t="inlineStr">
         <is>
-          <t>https://www.greystar.com/business/about-greystar/our-leadership</t>
+          <t>https://www.dinersteincos.com/about-us</t>
         </is>
       </c>
       <c r="Z273" s="6" t="inlineStr"/>
@@ -29665,7 +29665,7 @@
     <row r="274">
       <c r="A274" s="12" t="inlineStr">
         <is>
-          <t>Brian Dinerstein</t>
+          <t>Jack Dinerstein</t>
         </is>
       </c>
       <c r="B274" s="12" t="inlineStr">
@@ -29675,7 +29675,7 @@
       </c>
       <c r="C274" s="12" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Executive Chairman</t>
         </is>
       </c>
       <c r="D274" s="13" t="inlineStr">
@@ -29724,11 +29724,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P274" s="10" t="inlineStr"/>
-      <c r="Q274" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Brian%20Dinerstein%20The%20Dinerstein%20Companies","search")</f>
-        <v/>
-      </c>
+      <c r="P274" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jack-dinerstein-4215073/</t>
+        </is>
+      </c>
+      <c r="Q274" s="12" t="inlineStr"/>
       <c r="R274" s="16">
         <f>IF(P274="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -29746,14 +29747,10 @@
       <c r="U274" s="12" t="inlineStr"/>
       <c r="V274" s="15" t="inlineStr">
         <is>
-          <t>The firm's own bio page. Chief Executive Officer of a developer and operator with $4.3 billion under management.</t>
-        </is>
-      </c>
-      <c r="W274" s="12" t="inlineStr">
-        <is>
-          <t>https://www.dinersteincos.com/team/brian-dinerstein</t>
-        </is>
-      </c>
+          <t>Owner, Dinerstein Companies. Houston, Texas.</t>
+        </is>
+      </c>
+      <c r="W274" s="12" t="inlineStr"/>
       <c r="X274" s="12" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/the-dinerstein-companies/</t>
@@ -29769,7 +29766,7 @@
     <row r="275">
       <c r="A275" s="6" t="inlineStr">
         <is>
-          <t>Jack Dinerstein</t>
+          <t>Brad Dinerstein</t>
         </is>
       </c>
       <c r="B275" s="6" t="inlineStr">
@@ -29779,7 +29776,7 @@
       </c>
       <c r="C275" s="6" t="inlineStr">
         <is>
-          <t>Executive Chairman</t>
+          <t>Managing Partner of Development and Design</t>
         </is>
       </c>
       <c r="D275" s="7" t="inlineStr">
@@ -29828,12 +29825,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P275" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/jack-dinerstein-4215073/</t>
-        </is>
-      </c>
-      <c r="Q275" s="6" t="inlineStr"/>
+      <c r="P275" s="10" t="inlineStr"/>
+      <c r="Q275" s="6">
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Brad%20Dinerstein%20The%20Dinerstein%20Companies","search")</f>
+        <v/>
+      </c>
       <c r="R275" s="11">
         <f>IF(P275="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -29849,12 +29845,12 @@
         </is>
       </c>
       <c r="U275" s="6" t="inlineStr"/>
-      <c r="V275" s="9" t="inlineStr">
-        <is>
-          <t>Owner, Dinerstein Companies. Houston, Texas.</t>
-        </is>
-      </c>
-      <c r="W275" s="6" t="inlineStr"/>
+      <c r="V275" s="9" t="inlineStr"/>
+      <c r="W275" s="6" t="inlineStr">
+        <is>
+          <t>https://www.dinersteincos.com/about-us</t>
+        </is>
+      </c>
       <c r="X275" s="6" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/the-dinerstein-companies/</t>
@@ -29870,7 +29866,7 @@
     <row r="276">
       <c r="A276" s="12" t="inlineStr">
         <is>
-          <t>Brad Dinerstein</t>
+          <t>John Caltagirone</t>
         </is>
       </c>
       <c r="B276" s="12" t="inlineStr">
@@ -29880,7 +29876,7 @@
       </c>
       <c r="C276" s="12" t="inlineStr">
         <is>
-          <t>Managing Partner of Development and Design</t>
+          <t>President and Partner</t>
         </is>
       </c>
       <c r="D276" s="13" t="inlineStr">
@@ -29931,7 +29927,7 @@
       </c>
       <c r="P276" s="10" t="inlineStr"/>
       <c r="Q276" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Brad%20Dinerstein%20The%20Dinerstein%20Companies","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=John%20Caltagirone%20The%20Dinerstein%20Companies","search")</f>
         <v/>
       </c>
       <c r="R276" s="16">
@@ -29970,17 +29966,17 @@
     <row r="277">
       <c r="A277" s="6" t="inlineStr">
         <is>
-          <t>John Caltagirone</t>
+          <t>Jason Baker</t>
         </is>
       </c>
       <c r="B277" s="6" t="inlineStr">
         <is>
-          <t>The Dinerstein Companies</t>
+          <t>Baker Katz</t>
         </is>
       </c>
       <c r="C277" s="6" t="inlineStr">
         <is>
-          <t>President and Partner</t>
+          <t>Leads the tenant representation team, Baker Katz</t>
         </is>
       </c>
       <c r="D277" s="7" t="inlineStr">
@@ -29998,14 +29994,10 @@
       </c>
       <c r="G277" s="6" t="inlineStr">
         <is>
-          <t>Houston HQ / Fort Bend</t>
-        </is>
-      </c>
-      <c r="H277" s="6" t="inlineStr">
-        <is>
-          <t>186 BTR homes, Harrison Street JV</t>
-        </is>
-      </c>
+          <t>Houston / Harris, Galveston</t>
+        </is>
+      </c>
+      <c r="H277" s="6" t="inlineStr"/>
       <c r="I277" s="8" t="inlineStr">
         <is>
           <t>Partly</t>
@@ -30026,12 +30018,12 @@
       <c r="N277" s="9" t="inlineStr"/>
       <c r="O277" s="8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Partly</t>
         </is>
       </c>
       <c r="P277" s="10" t="inlineStr"/>
       <c r="Q277" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=John%20Caltagirone%20The%20Dinerstein%20Companies","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Jason%20Baker%20Baker%20Katz","search")</f>
         <v/>
       </c>
       <c r="R277" s="11">
@@ -30040,29 +30032,33 @@
       </c>
       <c r="S277" s="6" t="inlineStr">
         <is>
-          <t>https://www.dinersteincos.com/</t>
+          <t>https://bakerkatz.com/</t>
         </is>
       </c>
       <c r="T277" s="9" t="inlineStr">
         <is>
-          <t>186 build-to-rent homes with Harrison Street and 70 years in Houston. Launch coverage is amenities only.</t>
+          <t>More than 80 retail projects, but recent Houston activity is buying existing centres rather than building.</t>
         </is>
       </c>
       <c r="U277" s="6" t="inlineStr"/>
-      <c r="V277" s="9" t="inlineStr"/>
+      <c r="V277" s="9" t="inlineStr">
+        <is>
+          <t>Leads the tenant representation team, with more than twenty-five years in Houston retail. The page carries bios without formal titles.</t>
+        </is>
+      </c>
       <c r="W277" s="6" t="inlineStr">
         <is>
-          <t>https://www.dinersteincos.com/about-us</t>
+          <t>https://bakerkatz.com/about-us/</t>
         </is>
       </c>
       <c r="X277" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/the-dinerstein-companies/</t>
+          <t>https://www.linkedin.com/company/baker-katz</t>
         </is>
       </c>
       <c r="Y277" s="6" t="inlineStr">
         <is>
-          <t>https://www.dinersteincos.com/about-us</t>
+          <t>https://bakerkatz.com/about-us/</t>
         </is>
       </c>
       <c r="Z277" s="6" t="inlineStr"/>
@@ -30070,7 +30066,7 @@
     <row r="278">
       <c r="A278" s="12" t="inlineStr">
         <is>
-          <t>Jason Baker</t>
+          <t>Kenneth Katz</t>
         </is>
       </c>
       <c r="B278" s="12" t="inlineStr">
@@ -30080,7 +30076,7 @@
       </c>
       <c r="C278" s="12" t="inlineStr">
         <is>
-          <t>Leads the tenant representation team, Baker Katz</t>
+          <t>Leads the investment and development practice, Baker Katz</t>
         </is>
       </c>
       <c r="D278" s="13" t="inlineStr">
@@ -30127,7 +30123,7 @@
       </c>
       <c r="P278" s="10" t="inlineStr"/>
       <c r="Q278" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Jason%20Baker%20Baker%20Katz","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Kenneth%20Katz%20Baker%20Katz","search")</f>
         <v/>
       </c>
       <c r="R278" s="16">
@@ -30147,7 +30143,7 @@
       <c r="U278" s="12" t="inlineStr"/>
       <c r="V278" s="15" t="inlineStr">
         <is>
-          <t>Leads the tenant representation team, with more than twenty-five years in Houston retail. The page carries bios without formal titles.</t>
+          <t>Leads the real estate investment and development practice, covering ground-up development and redevelopment.</t>
         </is>
       </c>
       <c r="W278" s="12" t="inlineStr">
@@ -30170,7 +30166,7 @@
     <row r="279">
       <c r="A279" s="6" t="inlineStr">
         <is>
-          <t>Kenneth Katz</t>
+          <t>Martin Mendoza</t>
         </is>
       </c>
       <c r="B279" s="6" t="inlineStr">
@@ -30180,7 +30176,7 @@
       </c>
       <c r="C279" s="6" t="inlineStr">
         <is>
-          <t>Leads the investment and development practice, Baker Katz</t>
+          <t>Oversees design and construction, Baker Katz</t>
         </is>
       </c>
       <c r="D279" s="7" t="inlineStr">
@@ -30227,7 +30223,7 @@
       </c>
       <c r="P279" s="10" t="inlineStr"/>
       <c r="Q279" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Kenneth%20Katz%20Baker%20Katz","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Martin%20Mendoza%20Baker%20Katz","search")</f>
         <v/>
       </c>
       <c r="R279" s="11">
@@ -30244,10 +30240,14 @@
           <t>More than 80 retail projects, but recent Houston activity is buying existing centres rather than building.</t>
         </is>
       </c>
-      <c r="U279" s="6" t="inlineStr"/>
+      <c r="U279" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
       <c r="V279" s="9" t="inlineStr">
         <is>
-          <t>Leads the real estate investment and development practice, covering ground-up development and redevelopment.</t>
+          <t>Joined in August 2024 responsible for overseeing design and construction phases. The page gives no title, so the function rather than the rank is what places him here.</t>
         </is>
       </c>
       <c r="W279" s="6" t="inlineStr">
@@ -30270,17 +30270,17 @@
     <row r="280">
       <c r="A280" s="12" t="inlineStr">
         <is>
-          <t>Martin Mendoza</t>
+          <t>Bob Sellingsloh</t>
         </is>
       </c>
       <c r="B280" s="12" t="inlineStr">
         <is>
-          <t>Baker Katz</t>
+          <t>Wulfe &amp; Co.</t>
         </is>
       </c>
       <c r="C280" s="12" t="inlineStr">
         <is>
-          <t>Oversees design and construction, Baker Katz</t>
+          <t>President and Principal, Wulfe &amp; Co.</t>
         </is>
       </c>
       <c r="D280" s="13" t="inlineStr">
@@ -30298,7 +30298,7 @@
       </c>
       <c r="G280" s="12" t="inlineStr">
         <is>
-          <t>Houston / Harris, Galveston</t>
+          <t>Post Oak / Harris, Galveston</t>
         </is>
       </c>
       <c r="H280" s="12" t="inlineStr"/>
@@ -30322,12 +30322,12 @@
       <c r="N280" s="15" t="inlineStr"/>
       <c r="O280" s="14" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P280" s="10" t="inlineStr"/>
       <c r="Q280" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Martin%20Mendoza%20Baker%20Katz","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Bob%20Sellingsloh%20Wulfe%20%26%20Co.","search")</f>
         <v/>
       </c>
       <c r="R280" s="16">
@@ -30336,37 +30336,33 @@
       </c>
       <c r="S280" s="12" t="inlineStr">
         <is>
-          <t>https://bakerkatz.com/</t>
+          <t>https://www.wulfe.com/</t>
         </is>
       </c>
       <c r="T280" s="15" t="inlineStr">
         <is>
-          <t>More than 80 retail projects, but recent Houston activity is buying existing centres rather than building.</t>
-        </is>
-      </c>
-      <c r="U280" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+          <t>7.2M sf across nine centres. Current activity is leasing and management, not ground-up.</t>
+        </is>
+      </c>
+      <c r="U280" s="12" t="inlineStr"/>
       <c r="V280" s="15" t="inlineStr">
         <is>
-          <t>Joined in August 2024 responsible for overseeing design and construction phases. The page gives no title, so the function rather than the rank is what places him here.</t>
+          <t>President and Principal, listed first under leadership. Ed Wulfe no longer appears on the leadership page.</t>
         </is>
       </c>
       <c r="W280" s="12" t="inlineStr">
         <is>
-          <t>https://bakerkatz.com/about-us/</t>
+          <t>https://www.wulfe.com/people</t>
         </is>
       </c>
       <c r="X280" s="12" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/baker-katz</t>
+          <t>https://www.linkedin.com/company/wulfe</t>
         </is>
       </c>
       <c r="Y280" s="12" t="inlineStr">
         <is>
-          <t>https://bakerkatz.com/about-us/</t>
+          <t>https://www.wulfe.com/people</t>
         </is>
       </c>
       <c r="Z280" s="12" t="inlineStr"/>
@@ -30374,7 +30370,7 @@
     <row r="281">
       <c r="A281" s="6" t="inlineStr">
         <is>
-          <t>Bob Sellingsloh</t>
+          <t>Tammy Smith</t>
         </is>
       </c>
       <c r="B281" s="6" t="inlineStr">
@@ -30384,7 +30380,7 @@
       </c>
       <c r="C281" s="6" t="inlineStr">
         <is>
-          <t>President and Principal, Wulfe &amp; Co.</t>
+          <t>Director of Construction, Wulfe &amp; Co.</t>
         </is>
       </c>
       <c r="D281" s="7" t="inlineStr">
@@ -30431,7 +30427,7 @@
       </c>
       <c r="P281" s="10" t="inlineStr"/>
       <c r="Q281" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Bob%20Sellingsloh%20Wulfe%20%26%20Co.","search")</f>
+        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Tammy%20Smith%20Wulfe%20%26%20Co.","search")</f>
         <v/>
       </c>
       <c r="R281" s="11">
@@ -30448,12 +30444,12 @@
           <t>7.2M sf across nine centres. Current activity is leasing and management, not ground-up.</t>
         </is>
       </c>
-      <c r="U281" s="6" t="inlineStr"/>
-      <c r="V281" s="9" t="inlineStr">
-        <is>
-          <t>President and Principal, listed first under leadership. Ed Wulfe no longer appears on the leadership page.</t>
-        </is>
-      </c>
+      <c r="U281" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="V281" s="9" t="inlineStr"/>
       <c r="W281" s="6" t="inlineStr">
         <is>
           <t>https://www.wulfe.com/people</t>
@@ -30474,17 +30470,17 @@
     <row r="282">
       <c r="A282" s="12" t="inlineStr">
         <is>
-          <t>Tammy Smith</t>
+          <t>Vinod Ramani</t>
         </is>
       </c>
       <c r="B282" s="12" t="inlineStr">
         <is>
-          <t>Wulfe &amp; Co.</t>
+          <t>Urban Living</t>
         </is>
       </c>
       <c r="C282" s="12" t="inlineStr">
         <is>
-          <t>Director of Construction, Wulfe &amp; Co.</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="D282" s="13" t="inlineStr">
@@ -30493,7 +30489,7 @@
         </is>
       </c>
       <c r="E282" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F282" s="12" t="inlineStr">
         <is>
@@ -30502,185 +30498,85 @@
       </c>
       <c r="G282" s="12" t="inlineStr">
         <is>
-          <t>Post Oak / Harris, Galveston</t>
-        </is>
-      </c>
-      <c r="H282" s="12" t="inlineStr"/>
+          <t>Inner-loop Houston, Harris County</t>
+        </is>
+      </c>
+      <c r="H282" s="12" t="inlineStr">
+        <is>
+          <t>Its own domain no longer resolves to a site</t>
+        </is>
+      </c>
       <c r="I282" s="14" t="inlineStr">
         <is>
-          <t>Partly</t>
-        </is>
-      </c>
-      <c r="J282" s="15" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J282" s="15" t="inlineStr">
+        <is>
+          <t>Nothing is published. The firm's own site is a parked domain.</t>
+        </is>
+      </c>
       <c r="K282" s="14" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L282" s="15" t="inlineStr"/>
+      <c r="L282" s="15" t="inlineStr">
+        <is>
+          <t>No community, unit count or volume figure survives on any page the deck can cite.</t>
+        </is>
+      </c>
       <c r="M282" s="14" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N282" s="15" t="inlineStr"/>
+      <c r="N282" s="15" t="inlineStr">
+        <is>
+          <t>Nothing on record.</t>
+        </is>
+      </c>
       <c r="O282" s="14" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P282" s="10" t="inlineStr"/>
-      <c r="Q282" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Tammy%20Smith%20Wulfe%20%26%20Co.","search")</f>
-        <v/>
-      </c>
+      <c r="P282" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/vinod-ramani-4a46788/</t>
+        </is>
+      </c>
+      <c r="Q282" s="12" t="inlineStr"/>
       <c r="R282" s="16">
         <f>IF(P282="","ADD LINKEDIN","ok")</f>
         <v/>
       </c>
-      <c r="S282" s="12" t="inlineStr">
-        <is>
-          <t>https://www.wulfe.com/</t>
-        </is>
-      </c>
+      <c r="S282" s="12" t="inlineStr"/>
       <c r="T282" s="15" t="inlineStr">
         <is>
-          <t>7.2M sf across nine centres. Current activity is leasing and management, not ground-up.</t>
-        </is>
-      </c>
-      <c r="U282" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="V282" s="15" t="inlineStr"/>
-      <c r="W282" s="12" t="inlineStr">
-        <is>
-          <t>https://www.wulfe.com/people</t>
-        </is>
-      </c>
-      <c r="X282" s="12" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/wulfe</t>
-        </is>
-      </c>
-      <c r="Y282" s="12" t="inlineStr">
-        <is>
-          <t>https://www.wulfe.com/people</t>
-        </is>
-      </c>
+          <t>Attached townhome production, the product type a printed party wall serves. The owner is held on a LinkedIn headline alone; the firm's own site publishes nobody.</t>
+        </is>
+      </c>
+      <c r="U282" s="12" t="inlineStr"/>
+      <c r="V282" s="15" t="inlineStr">
+        <is>
+          <t>Indexed title reads Vinod Ramani, Urban Living.</t>
+        </is>
+      </c>
+      <c r="W282" s="12" t="inlineStr"/>
+      <c r="X282" s="12" t="inlineStr"/>
+      <c r="Y282" s="12" t="inlineStr"/>
       <c r="Z282" s="12" t="inlineStr"/>
     </row>
-    <row r="283">
-      <c r="A283" s="6" t="inlineStr">
-        <is>
-          <t>Vinod Ramani</t>
-        </is>
-      </c>
-      <c r="B283" s="6" t="inlineStr">
-        <is>
-          <t>Urban Living</t>
-        </is>
-      </c>
-      <c r="C283" s="6" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="D283" s="7" t="inlineStr">
-        <is>
-          <t>Off deck, screened out</t>
-        </is>
-      </c>
-      <c r="E283" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F283" s="6" t="inlineStr">
-        <is>
-          <t>Buys walls</t>
-        </is>
-      </c>
-      <c r="G283" s="6" t="inlineStr">
-        <is>
-          <t>Inner-loop Houston, Harris County</t>
-        </is>
-      </c>
-      <c r="H283" s="6" t="inlineStr">
-        <is>
-          <t>Its own domain no longer resolves to a site</t>
-        </is>
-      </c>
-      <c r="I283" s="8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J283" s="9" t="inlineStr">
-        <is>
-          <t>Nothing is published. The firm's own site is a parked domain.</t>
-        </is>
-      </c>
-      <c r="K283" s="8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L283" s="9" t="inlineStr">
-        <is>
-          <t>No community, unit count or volume figure survives on any page the deck can cite.</t>
-        </is>
-      </c>
-      <c r="M283" s="8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N283" s="9" t="inlineStr">
-        <is>
-          <t>Nothing on record.</t>
-        </is>
-      </c>
-      <c r="O283" s="8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P283" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/vinod-ramani-4a46788/</t>
-        </is>
-      </c>
-      <c r="Q283" s="6" t="inlineStr"/>
-      <c r="R283" s="11">
-        <f>IF(P283="","ADD LINKEDIN","ok")</f>
-        <v/>
-      </c>
-      <c r="S283" s="6" t="inlineStr"/>
-      <c r="T283" s="9" t="inlineStr">
-        <is>
-          <t>Attached townhome production, the product type a printed party wall serves. The owner is held on a LinkedIn headline alone; the firm's own site publishes nobody.</t>
-        </is>
-      </c>
-      <c r="U283" s="6" t="inlineStr"/>
-      <c r="V283" s="9" t="inlineStr">
-        <is>
-          <t>Indexed title reads Vinod Ramani, Urban Living.</t>
-        </is>
-      </c>
-      <c r="W283" s="6" t="inlineStr"/>
-      <c r="X283" s="6" t="inlineStr"/>
-      <c r="Y283" s="6" t="inlineStr"/>
-      <c r="Z283" s="6" t="inlineStr"/>
-    </row>
-    <row r="285">
-      <c r="A285" s="17" t="inlineStr">
+    <row r="284">
+      <c r="A284" s="17" t="inlineStr">
         <is>
           <t>NOTE. A filled LinkedIn cell means the profile was opened or the search result read and the headline named the firm; column W records what was read. Where that test failed the cell is left empty rather than guessed, because a fabricated slug passes visual inspection and then fails in front of the person it names. Column Q searches for the empty ones in your own session. Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Capital is a qualifier, not a count. Source: ICON Greater Houston screen, build 53, 2026-09-11.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:Z283"/>
+  <autoFilter ref="A6:Z282"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/ICON_Greater_Houston_Rolodex.xlsx
+++ b/docs/ICON_Greater_Houston_Rolodex.xlsx
@@ -582,7 +582,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated from houston-data.json · build 53 · 2026-09-11 · public render. Do not hand-edit the HTML deck; it regenerates from the same file.</t>
+          <t>Generated from houston-data.json · build 55 · 2026-09-11 · public render. Do not hand-edit the HTML deck; it regenerates from the same file.</t>
         </is>
       </c>
     </row>
@@ -21149,7 +21149,7 @@
       </c>
       <c r="L195" s="9" t="inlineStr">
         <is>
-          <t>The phase-one programme is retail, office and parking rather than repeated units.</t>
+          <t>Phase one is two warehouses of the same size, done twice. The rest of the district is one-offs, and the build-to-rent line is not in Houston.</t>
         </is>
       </c>
       <c r="M195" s="8" t="inlineStr">
@@ -21253,7 +21253,7 @@
       </c>
       <c r="L196" s="15" t="inlineStr">
         <is>
-          <t>The phase-one programme is retail, office and parking rather than repeated units.</t>
+          <t>Phase one is two warehouses of the same size, done twice. The rest of the district is one-offs, and the build-to-rent line is not in Houston.</t>
         </is>
       </c>
       <c r="M196" s="14" t="inlineStr">
@@ -21362,7 +21362,7 @@
       </c>
       <c r="L197" s="9" t="inlineStr">
         <is>
-          <t>The phase-one programme is retail, office and parking rather than repeated units.</t>
+          <t>Phase one is two warehouses of the same size, done twice. The rest of the district is one-offs, and the build-to-rent line is not in Houston.</t>
         </is>
       </c>
       <c r="M197" s="8" t="inlineStr">
@@ -24801,7 +24801,7 @@
       </c>
       <c r="H228" s="12" t="inlineStr">
         <is>
-          <t>120+ communities, 65,000+ homes sold</t>
+          <t>Four Texas markets and five in Florida, no volume published</t>
         </is>
       </c>
       <c r="I228" s="14" t="inlineStr">
@@ -24811,7 +24811,7 @@
       </c>
       <c r="J228" s="15" t="inlineStr">
         <is>
-          <t>More than 120 communities and 65,000 homes, locally owned.</t>
+          <t>Nine markets across two states on one plan library.</t>
         </is>
       </c>
       <c r="K228" s="14" t="inlineStr">
@@ -24821,7 +24821,7 @@
       </c>
       <c r="L228" s="15" t="inlineStr">
         <is>
-          <t>120 communities and thousands of closings a year, bought centrally.</t>
+          <t>Nine markets across two states. The volume is far above what one or two printers cover, and it is bought centrally.</t>
         </is>
       </c>
       <c r="M228" s="14" t="inlineStr">
@@ -24917,7 +24917,7 @@
       </c>
       <c r="H229" s="6" t="inlineStr">
         <is>
-          <t>120+ communities, 65,000+ homes sold</t>
+          <t>Four Texas markets and five in Florida, no volume published</t>
         </is>
       </c>
       <c r="I229" s="8" t="inlineStr">
@@ -24927,7 +24927,7 @@
       </c>
       <c r="J229" s="9" t="inlineStr">
         <is>
-          <t>More than 120 communities and 65,000 homes, locally owned.</t>
+          <t>Nine markets across two states on one plan library.</t>
         </is>
       </c>
       <c r="K229" s="8" t="inlineStr">
@@ -24937,7 +24937,7 @@
       </c>
       <c r="L229" s="9" t="inlineStr">
         <is>
-          <t>120 communities and thousands of closings a year, bought centrally.</t>
+          <t>Nine markets across two states. The volume is far above what one or two printers cover, and it is bought centrally.</t>
         </is>
       </c>
       <c r="M229" s="8" t="inlineStr">
@@ -30571,7 +30571,7 @@
     <row r="284">
       <c r="A284" s="17" t="inlineStr">
         <is>
-          <t>NOTE. A filled LinkedIn cell means the profile was opened or the search result read and the headline named the firm; column W records what was read. Where that test failed the cell is left empty rather than guessed, because a fabricated slug passes visual inspection and then fails in front of the person it names. Column Q searches for the empty ones in your own session. Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Capital is a qualifier, not a count. Source: ICON Greater Houston screen, build 53, 2026-09-11.</t>
+          <t>NOTE. A filled LinkedIn cell means the profile was opened or the search result read and the headline named the firm; column W records what was read. Where that test failed the cell is left empty rather than guessed, because a fabricated slug passes visual inspection and then fails in front of the person it names. Column Q searches for the empty ones in your own session. Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Capital is a qualifier, not a count. Source: ICON Greater Houston screen, build 55, 2026-09-11.</t>
         </is>
       </c>
     </row>

--- a/docs/ICON_Greater_Houston_Rolodex.xlsx
+++ b/docs/ICON_Greater_Houston_Rolodex.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Permits" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Contacts'!$A$6:$Z$282</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Contacts'!$A$6:$AC$282</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z284"/>
+  <dimension ref="A1:AC284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -570,6 +570,9 @@
     <col width="42" customWidth="1" min="24" max="24"/>
     <col width="42" customWidth="1" min="25" max="25"/>
     <col width="70" customWidth="1" min="26" max="26"/>
+    <col width="18" customWidth="1" min="27" max="27"/>
+    <col width="26" customWidth="1" min="28" max="28"/>
+    <col width="46" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -582,7 +585,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated from houston-data.json · build 55 · 2026-09-11 · public render. Do not hand-edit the HTML deck; it regenerates from the same file.</t>
+          <t>Generated from houston-data.json · build 56 · 2026-09-11 · public render. Do not hand-edit the HTML deck; it regenerates from the same file.</t>
         </is>
       </c>
     </row>
@@ -636,7 +639,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>LEGEND. Column Q is a one-click LinkedIn people search for that name at that firm, run in your own signed-in session. Paste the profile URL into the shaded cell in column P and column R flips from ADD LINKEDIN to ok, with the counters in row 3 updating live. Every other column is generated and is overwritten on the next build. Column V marks the people who can change a wall specification, a vice president or director of construction or the head of purchasing; filter it to YES for the call list. Column W is the evidence behind the name, column X the firm's own page that names them, and columns Y and Z the company's LinkedIn and leadership pages. Example: https://www.linkedin.com/in/jane-doe-1a2b3c4d/</t>
+          <t>LEGEND. Column Q is a one-click LinkedIn people search for that name at that firm, run in your own signed-in session. Paste the profile URL into the shaded cell in column P and column R flips from ADD LINKEDIN to ok, with the counters in row 3 updating live. Every other column is generated and is overwritten on the next build. Column V marks the people who can change a wall specification, a vice president or director of construction or the head of purchasing; filter it to YES for the call list. Column W is the evidence behind the name, column X the firm's own page that names them, and columns Y and Z the company's LinkedIn and leadership pages. Columns AB to AD carry the firm's main line, the words the page uses for it, and the page it is published on. The number is the firm's, not the person's, so it repeats down every row for that firm. A firm whose own pages publish no number has all three cells empty. Example: https://www.linkedin.com/in/jane-doe-1a2b3c4d/</t>
         </is>
       </c>
     </row>
@@ -769,6 +772,21 @@
       <c r="Z6" s="5" t="inlineStr">
         <is>
           <t>Latest press</t>
+        </is>
+      </c>
+      <c r="AA6" s="5" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="AB6" s="5" t="inlineStr">
+        <is>
+          <t>Phone label</t>
+        </is>
+      </c>
+      <c r="AC6" s="5" t="inlineStr">
+        <is>
+          <t>Phone source</t>
         </is>
       </c>
     </row>
@@ -891,6 +909,9 @@
           <t>2026-02 The Architect's Newspaper. Zuri Gardens, a 3D-printed Texas community, shows promise for attainable housing  https://www.archpaper.com/2026/02/zuri-gardens-3d-printed-texas-community/</t>
         </is>
       </c>
+      <c r="AA7" s="6" t="inlineStr"/>
+      <c r="AB7" s="6" t="inlineStr"/>
+      <c r="AC7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
@@ -1007,6 +1028,9 @@
           <t>2026-02 The Architect's Newspaper. Zuri Gardens, a 3D-printed Texas community, shows promise for attainable housing  https://www.archpaper.com/2026/02/zuri-gardens-3d-printed-texas-community/</t>
         </is>
       </c>
+      <c r="AA8" s="12" t="inlineStr"/>
+      <c r="AB8" s="12" t="inlineStr"/>
+      <c r="AC8" s="12" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -1119,6 +1143,9 @@
           <t>2026-04-30 Intelligent Build.tech. Partnership to develop an innovative 3D-printed residential community  https://www.intelligentbuild.tech/2026/04/30/partnership-to-develop-an-innovative-3d-printed-residential-community/</t>
         </is>
       </c>
+      <c r="AA9" s="6" t="inlineStr"/>
+      <c r="AB9" s="6" t="inlineStr"/>
+      <c r="AC9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
@@ -1231,6 +1258,9 @@
           <t>2026-04-22 Homes.com. Houston's 3D-printed housing push grows with two new developments  https://www.homes.com/news/houstons-3d-printed-housing-push-grows-with-two-new-developments/647676272/</t>
         </is>
       </c>
+      <c r="AA10" s="12" t="inlineStr"/>
+      <c r="AB10" s="12" t="inlineStr"/>
+      <c r="AC10" s="12" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -1346,6 +1376,21 @@
       <c r="Z11" s="6" t="inlineStr">
         <is>
           <t>2026-04-25 Houston Chronicle. Why Houston's booming build-to-rent sector could slow  https://www.houstonchronicle.com/business/article/houston-build-to-rent-housing-21293194.php</t>
+        </is>
+      </c>
+      <c r="AA11" s="6" t="inlineStr">
+        <is>
+          <t>(713) 219-9400</t>
+        </is>
+      </c>
+      <c r="AB11" s="6" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="AC11" s="6" t="inlineStr">
+        <is>
+          <t>https://wanbridge.com/</t>
         </is>
       </c>
     </row>
@@ -1461,6 +1506,21 @@
           <t>2026-04-25 Houston Chronicle. Why Houston's booming build-to-rent sector could slow  https://www.houstonchronicle.com/business/article/houston-build-to-rent-housing-21293194.php</t>
         </is>
       </c>
+      <c r="AA12" s="12" t="inlineStr">
+        <is>
+          <t>(713) 219-9400</t>
+        </is>
+      </c>
+      <c r="AB12" s="12" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="AC12" s="12" t="inlineStr">
+        <is>
+          <t>https://wanbridge.com/</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -1578,6 +1638,21 @@
           <t>2026-04-25 Houston Chronicle. Why Houston's booming build-to-rent sector could slow  https://www.houstonchronicle.com/business/article/houston-build-to-rent-housing-21293194.php</t>
         </is>
       </c>
+      <c r="AA13" s="6" t="inlineStr">
+        <is>
+          <t>(713) 219-9400</t>
+        </is>
+      </c>
+      <c r="AB13" s="6" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="AC13" s="6" t="inlineStr">
+        <is>
+          <t>https://wanbridge.com/</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
@@ -1691,6 +1766,21 @@
           <t>2026-04-25 Houston Chronicle. Why Houston's booming build-to-rent sector could slow  https://www.houstonchronicle.com/business/article/houston-build-to-rent-housing-21293194.php</t>
         </is>
       </c>
+      <c r="AA14" s="12" t="inlineStr">
+        <is>
+          <t>(713) 219-9400</t>
+        </is>
+      </c>
+      <c r="AB14" s="12" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="AC14" s="12" t="inlineStr">
+        <is>
+          <t>https://wanbridge.com/</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -1795,6 +1885,13 @@
       <c r="X15" s="6" t="inlineStr"/>
       <c r="Y15" s="6" t="inlineStr"/>
       <c r="Z15" s="6" t="inlineStr"/>
+      <c r="AA15" s="6" t="inlineStr"/>
+      <c r="AB15" s="6" t="inlineStr"/>
+      <c r="AC15" s="6" t="inlineStr">
+        <is>
+          <t>https://www.caldwellhomes.com/</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
@@ -1899,6 +1996,13 @@
       <c r="X16" s="12" t="inlineStr"/>
       <c r="Y16" s="12" t="inlineStr"/>
       <c r="Z16" s="12" t="inlineStr"/>
+      <c r="AA16" s="12" t="inlineStr"/>
+      <c r="AB16" s="12" t="inlineStr"/>
+      <c r="AC16" s="12" t="inlineStr">
+        <is>
+          <t>https://www.caldwellhomes.com/</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -2003,6 +2107,13 @@
       <c r="X17" s="6" t="inlineStr"/>
       <c r="Y17" s="6" t="inlineStr"/>
       <c r="Z17" s="6" t="inlineStr"/>
+      <c r="AA17" s="6" t="inlineStr"/>
+      <c r="AB17" s="6" t="inlineStr"/>
+      <c r="AC17" s="6" t="inlineStr">
+        <is>
+          <t>https://www.caldwellhomes.com/</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
@@ -2111,6 +2222,13 @@
       <c r="X18" s="12" t="inlineStr"/>
       <c r="Y18" s="12" t="inlineStr"/>
       <c r="Z18" s="12" t="inlineStr"/>
+      <c r="AA18" s="12" t="inlineStr"/>
+      <c r="AB18" s="12" t="inlineStr"/>
+      <c r="AC18" s="12" t="inlineStr">
+        <is>
+          <t>https://www.caldwellhomes.com/</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -2215,6 +2333,13 @@
       <c r="X19" s="6" t="inlineStr"/>
       <c r="Y19" s="6" t="inlineStr"/>
       <c r="Z19" s="6" t="inlineStr"/>
+      <c r="AA19" s="6" t="inlineStr"/>
+      <c r="AB19" s="6" t="inlineStr"/>
+      <c r="AC19" s="6" t="inlineStr">
+        <is>
+          <t>https://www.caldwellhomes.com/</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
@@ -2328,6 +2453,17 @@
         </is>
       </c>
       <c r="Z20" s="12" t="inlineStr"/>
+      <c r="AA20" s="12" t="inlineStr">
+        <is>
+          <t>(713) 961-3877</t>
+        </is>
+      </c>
+      <c r="AB20" s="12" t="inlineStr"/>
+      <c r="AC20" s="12" t="inlineStr">
+        <is>
+          <t>https://intownhomes.com/</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -2441,6 +2577,17 @@
           <t>2013-10-30 Boxer Property. Boxer Announces Executive Leadership Changes, which is where the current titles come from and which puts engineering and construction under the president  https://www.boxerproperty.com/blog/roles-responsibilities-evolve-executives/</t>
         </is>
       </c>
+      <c r="AA21" s="6" t="inlineStr">
+        <is>
+          <t>(713) 777-7368</t>
+        </is>
+      </c>
+      <c r="AB21" s="6" t="inlineStr"/>
+      <c r="AC21" s="6" t="inlineStr">
+        <is>
+          <t>https://www.boxerproperty.com/</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
@@ -2552,6 +2699,17 @@
       <c r="Z22" s="12" t="inlineStr">
         <is>
           <t>2013-10-30 Boxer Property. Boxer Announces Executive Leadership Changes, which is where the current titles come from and which puts engineering and construction under the president  https://www.boxerproperty.com/blog/roles-responsibilities-evolve-executives/</t>
+        </is>
+      </c>
+      <c r="AA22" s="12" t="inlineStr">
+        <is>
+          <t>(713) 777-7368</t>
+        </is>
+      </c>
+      <c r="AB22" s="12" t="inlineStr"/>
+      <c r="AC22" s="12" t="inlineStr">
+        <is>
+          <t>https://www.boxerproperty.com/</t>
         </is>
       </c>
     </row>
@@ -2658,6 +2816,17 @@
           <t>2013-10-30 Boxer Property. Boxer Announces Executive Leadership Changes, which is where the current titles come from and which puts engineering and construction under the president  https://www.boxerproperty.com/blog/roles-responsibilities-evolve-executives/</t>
         </is>
       </c>
+      <c r="AA23" s="6" t="inlineStr">
+        <is>
+          <t>(713) 777-7368</t>
+        </is>
+      </c>
+      <c r="AB23" s="6" t="inlineStr"/>
+      <c r="AC23" s="6" t="inlineStr">
+        <is>
+          <t>https://www.boxerproperty.com/</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
@@ -2762,6 +2931,17 @@
           <t>2013-10-30 Boxer Property. Boxer Announces Executive Leadership Changes, which is where the current titles come from and which puts engineering and construction under the president  https://www.boxerproperty.com/blog/roles-responsibilities-evolve-executives/</t>
         </is>
       </c>
+      <c r="AA24" s="12" t="inlineStr">
+        <is>
+          <t>(713) 777-7368</t>
+        </is>
+      </c>
+      <c r="AB24" s="12" t="inlineStr"/>
+      <c r="AC24" s="12" t="inlineStr">
+        <is>
+          <t>https://www.boxerproperty.com/</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -2870,6 +3050,17 @@
       <c r="X25" s="6" t="inlineStr"/>
       <c r="Y25" s="6" t="inlineStr"/>
       <c r="Z25" s="6" t="inlineStr"/>
+      <c r="AA25" s="6" t="inlineStr">
+        <is>
+          <t>(512) 334-6775</t>
+        </is>
+      </c>
+      <c r="AB25" s="6" t="inlineStr"/>
+      <c r="AC25" s="6" t="inlineStr">
+        <is>
+          <t>https://www.brohnhomes.com/</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
@@ -2986,6 +3177,21 @@
         </is>
       </c>
       <c r="Z26" s="12" t="inlineStr"/>
+      <c r="AA26" s="12" t="inlineStr">
+        <is>
+          <t>(888) 885-5653</t>
+        </is>
+      </c>
+      <c r="AB26" s="12" t="inlineStr">
+        <is>
+          <t>warranty service</t>
+        </is>
+      </c>
+      <c r="AC26" s="12" t="inlineStr">
+        <is>
+          <t>https://www.centurycommunities.com/</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -3099,6 +3305,21 @@
         </is>
       </c>
       <c r="Z27" s="6" t="inlineStr"/>
+      <c r="AA27" s="6" t="inlineStr">
+        <is>
+          <t>(888) 885-5653</t>
+        </is>
+      </c>
+      <c r="AB27" s="6" t="inlineStr">
+        <is>
+          <t>warranty service</t>
+        </is>
+      </c>
+      <c r="AC27" s="6" t="inlineStr">
+        <is>
+          <t>https://www.centurycommunities.com/</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
@@ -3219,6 +3440,17 @@
           <t>2026-08-10 CEOWORLD magazine. Danny Signorelli Leads First America Homes Expansion Across Houston and Texas  https://ceoworld.biz/2026/08/10/danny-signorelli-leads-first-america-homes-expansion-across-houston-and-texas/</t>
         </is>
       </c>
+      <c r="AA28" s="12" t="inlineStr">
+        <is>
+          <t>(713) 897-8986</t>
+        </is>
+      </c>
+      <c r="AB28" s="12" t="inlineStr"/>
+      <c r="AC28" s="12" t="inlineStr">
+        <is>
+          <t>https://www.firstamericahomes.com/</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -3336,6 +3568,17 @@
           <t>2026-08-10 CEOWORLD magazine. Danny Signorelli Leads First America Homes Expansion Across Houston and Texas  https://ceoworld.biz/2026/08/10/danny-signorelli-leads-first-america-homes-expansion-across-houston-and-texas/</t>
         </is>
       </c>
+      <c r="AA29" s="6" t="inlineStr">
+        <is>
+          <t>(713) 897-8986</t>
+        </is>
+      </c>
+      <c r="AB29" s="6" t="inlineStr"/>
+      <c r="AC29" s="6" t="inlineStr">
+        <is>
+          <t>https://www.firstamericahomes.com/</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
@@ -3457,6 +3700,17 @@
           <t>2026-08-10 CEOWORLD magazine. Danny Signorelli Leads First America Homes Expansion Across Houston and Texas  https://ceoworld.biz/2026/08/10/danny-signorelli-leads-first-america-homes-expansion-across-houston-and-texas/</t>
         </is>
       </c>
+      <c r="AA30" s="12" t="inlineStr">
+        <is>
+          <t>(713) 897-8986</t>
+        </is>
+      </c>
+      <c r="AB30" s="12" t="inlineStr"/>
+      <c r="AC30" s="12" t="inlineStr">
+        <is>
+          <t>https://www.firstamericahomes.com/</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -3570,6 +3824,21 @@
           <t>2026-07-24 Builder Magazine. How Stylecraft Is Building Bigger While Staying Local  https://www.builderonline.com/builder-100/leadership/how-stylecraft-is-building-bigger-while-staying-local/</t>
         </is>
       </c>
+      <c r="AA31" s="6" t="inlineStr">
+        <is>
+          <t>(979) 200-4552</t>
+        </is>
+      </c>
+      <c r="AB31" s="6" t="inlineStr">
+        <is>
+          <t>office</t>
+        </is>
+      </c>
+      <c r="AC31" s="6" t="inlineStr">
+        <is>
+          <t>https://www.stylecraft.com/</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
@@ -3686,6 +3955,21 @@
           <t>2026-07-24 Builder Magazine. How Stylecraft Is Building Bigger While Staying Local  https://www.builderonline.com/builder-100/leadership/how-stylecraft-is-building-bigger-while-staying-local/</t>
         </is>
       </c>
+      <c r="AA32" s="12" t="inlineStr">
+        <is>
+          <t>(979) 200-4552</t>
+        </is>
+      </c>
+      <c r="AB32" s="12" t="inlineStr">
+        <is>
+          <t>office</t>
+        </is>
+      </c>
+      <c r="AC32" s="12" t="inlineStr">
+        <is>
+          <t>https://www.stylecraft.com/</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -3803,6 +4087,21 @@
           <t>2026-07-24 Builder Magazine. How Stylecraft Is Building Bigger While Staying Local  https://www.builderonline.com/builder-100/leadership/how-stylecraft-is-building-bigger-while-staying-local/</t>
         </is>
       </c>
+      <c r="AA33" s="6" t="inlineStr">
+        <is>
+          <t>(979) 200-4552</t>
+        </is>
+      </c>
+      <c r="AB33" s="6" t="inlineStr">
+        <is>
+          <t>office</t>
+        </is>
+      </c>
+      <c r="AC33" s="6" t="inlineStr">
+        <is>
+          <t>https://www.stylecraft.com/</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
@@ -3914,6 +4213,21 @@
       <c r="Z34" s="12" t="inlineStr">
         <is>
           <t>2026-07-24 Builder Magazine. How Stylecraft Is Building Bigger While Staying Local  https://www.builderonline.com/builder-100/leadership/how-stylecraft-is-building-bigger-while-staying-local/</t>
+        </is>
+      </c>
+      <c r="AA34" s="12" t="inlineStr">
+        <is>
+          <t>(979) 200-4552</t>
+        </is>
+      </c>
+      <c r="AB34" s="12" t="inlineStr">
+        <is>
+          <t>office</t>
+        </is>
+      </c>
+      <c r="AC34" s="12" t="inlineStr">
+        <is>
+          <t>https://www.stylecraft.com/</t>
         </is>
       </c>
     </row>
@@ -4020,6 +4334,17 @@
       <c r="X35" s="6" t="inlineStr"/>
       <c r="Y35" s="6" t="inlineStr"/>
       <c r="Z35" s="6" t="inlineStr"/>
+      <c r="AA35" s="6" t="inlineStr">
+        <is>
+          <t>(346) 212-2153</t>
+        </is>
+      </c>
+      <c r="AB35" s="6" t="inlineStr"/>
+      <c r="AC35" s="6" t="inlineStr">
+        <is>
+          <t>https://www.tionahomes.com/</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
@@ -4120,6 +4445,17 @@
       <c r="X36" s="12" t="inlineStr"/>
       <c r="Y36" s="12" t="inlineStr"/>
       <c r="Z36" s="12" t="inlineStr"/>
+      <c r="AA36" s="12" t="inlineStr">
+        <is>
+          <t>(346) 212-2153</t>
+        </is>
+      </c>
+      <c r="AB36" s="12" t="inlineStr"/>
+      <c r="AC36" s="12" t="inlineStr">
+        <is>
+          <t>https://www.tionahomes.com/</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -4220,6 +4556,17 @@
       <c r="X37" s="6" t="inlineStr"/>
       <c r="Y37" s="6" t="inlineStr"/>
       <c r="Z37" s="6" t="inlineStr"/>
+      <c r="AA37" s="6" t="inlineStr">
+        <is>
+          <t>(346) 212-2153</t>
+        </is>
+      </c>
+      <c r="AB37" s="6" t="inlineStr"/>
+      <c r="AC37" s="6" t="inlineStr">
+        <is>
+          <t>https://www.tionahomes.com/</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
@@ -4324,6 +4671,17 @@
       <c r="X38" s="12" t="inlineStr"/>
       <c r="Y38" s="12" t="inlineStr"/>
       <c r="Z38" s="12" t="inlineStr"/>
+      <c r="AA38" s="12" t="inlineStr">
+        <is>
+          <t>(832) 224-3603</t>
+        </is>
+      </c>
+      <c r="AB38" s="12" t="inlineStr"/>
+      <c r="AC38" s="12" t="inlineStr">
+        <is>
+          <t>https://www.auradwellings.com/</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -4437,6 +4795,17 @@
         </is>
       </c>
       <c r="Z39" s="6" t="inlineStr"/>
+      <c r="AA39" s="6" t="inlineStr">
+        <is>
+          <t>(713) 961-3588</t>
+        </is>
+      </c>
+      <c r="AB39" s="6" t="inlineStr"/>
+      <c r="AC39" s="6" t="inlineStr">
+        <is>
+          <t>https://suebausa.com/</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
@@ -4549,6 +4918,17 @@
         </is>
       </c>
       <c r="Z40" s="12" t="inlineStr"/>
+      <c r="AA40" s="12" t="inlineStr">
+        <is>
+          <t>(713) 961-3588</t>
+        </is>
+      </c>
+      <c r="AB40" s="12" t="inlineStr"/>
+      <c r="AC40" s="12" t="inlineStr">
+        <is>
+          <t>https://suebausa.com/</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -4666,6 +5046,17 @@
         </is>
       </c>
       <c r="Z41" s="6" t="inlineStr"/>
+      <c r="AA41" s="6" t="inlineStr">
+        <is>
+          <t>(713) 961-3588</t>
+        </is>
+      </c>
+      <c r="AB41" s="6" t="inlineStr"/>
+      <c r="AC41" s="6" t="inlineStr">
+        <is>
+          <t>https://suebausa.com/</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
@@ -4783,6 +5174,9 @@
           <t>Builder Magazine. Chesmar Homes, with the note that Sekisui House U.S. is the 2026 Builder of the Year  https://www.builderonline.com/organization/chesmar-homes/</t>
         </is>
       </c>
+      <c r="AA42" s="12" t="inlineStr"/>
+      <c r="AB42" s="12" t="inlineStr"/>
+      <c r="AC42" s="12" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -4896,6 +5290,9 @@
           <t>Builder Magazine. Chesmar Homes, with the note that Sekisui House U.S. is the 2026 Builder of the Year  https://www.builderonline.com/organization/chesmar-homes/</t>
         </is>
       </c>
+      <c r="AA43" s="6" t="inlineStr"/>
+      <c r="AB43" s="6" t="inlineStr"/>
+      <c r="AC43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
@@ -5013,6 +5410,9 @@
           <t>Builder Magazine. Chesmar Homes, with the note that Sekisui House U.S. is the 2026 Builder of the Year  https://www.builderonline.com/organization/chesmar-homes/</t>
         </is>
       </c>
+      <c r="AA44" s="12" t="inlineStr"/>
+      <c r="AB44" s="12" t="inlineStr"/>
+      <c r="AC44" s="12" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -5121,6 +5521,17 @@
       <c r="X45" s="6" t="inlineStr"/>
       <c r="Y45" s="6" t="inlineStr"/>
       <c r="Z45" s="6" t="inlineStr"/>
+      <c r="AA45" s="6" t="inlineStr">
+        <is>
+          <t>(713) 789-8004</t>
+        </is>
+      </c>
+      <c r="AB45" s="6" t="inlineStr"/>
+      <c r="AC45" s="6" t="inlineStr">
+        <is>
+          <t>https://www.jpatrickhomes.com/</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
@@ -5230,6 +5641,17 @@
       <c r="X46" s="12" t="inlineStr"/>
       <c r="Y46" s="12" t="inlineStr"/>
       <c r="Z46" s="12" t="inlineStr"/>
+      <c r="AA46" s="12" t="inlineStr">
+        <is>
+          <t>(713) 789-8004</t>
+        </is>
+      </c>
+      <c r="AB46" s="12" t="inlineStr"/>
+      <c r="AC46" s="12" t="inlineStr">
+        <is>
+          <t>https://www.jpatrickhomes.com/</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -5338,6 +5760,21 @@
       <c r="X47" s="6" t="inlineStr"/>
       <c r="Y47" s="6" t="inlineStr"/>
       <c r="Z47" s="6" t="inlineStr"/>
+      <c r="AA47" s="6" t="inlineStr">
+        <is>
+          <t>(281) 482-5864</t>
+        </is>
+      </c>
+      <c r="AB47" s="6" t="inlineStr">
+        <is>
+          <t>office</t>
+        </is>
+      </c>
+      <c r="AC47" s="6" t="inlineStr">
+        <is>
+          <t>https://www.cervellehomes.com/</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
@@ -5446,6 +5883,21 @@
       <c r="X48" s="12" t="inlineStr"/>
       <c r="Y48" s="12" t="inlineStr"/>
       <c r="Z48" s="12" t="inlineStr"/>
+      <c r="AA48" s="12" t="inlineStr">
+        <is>
+          <t>(281) 482-5864</t>
+        </is>
+      </c>
+      <c r="AB48" s="12" t="inlineStr">
+        <is>
+          <t>office</t>
+        </is>
+      </c>
+      <c r="AC48" s="12" t="inlineStr">
+        <is>
+          <t>https://www.cervellehomes.com/</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
@@ -5558,6 +6010,17 @@
       <c r="X49" s="6" t="inlineStr"/>
       <c r="Y49" s="6" t="inlineStr"/>
       <c r="Z49" s="6" t="inlineStr"/>
+      <c r="AA49" s="6" t="inlineStr">
+        <is>
+          <t>(281) 407-6466</t>
+        </is>
+      </c>
+      <c r="AB49" s="6" t="inlineStr"/>
+      <c r="AC49" s="6" t="inlineStr">
+        <is>
+          <t>https://www.clayresidential.com/</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
@@ -5666,6 +6129,17 @@
       <c r="X50" s="12" t="inlineStr"/>
       <c r="Y50" s="12" t="inlineStr"/>
       <c r="Z50" s="12" t="inlineStr"/>
+      <c r="AA50" s="12" t="inlineStr">
+        <is>
+          <t>(888) 904-7172</t>
+        </is>
+      </c>
+      <c r="AB50" s="12" t="inlineStr"/>
+      <c r="AC50" s="12" t="inlineStr">
+        <is>
+          <t>https://www.myaltahomes.com/</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -5774,6 +6248,17 @@
       <c r="X51" s="6" t="inlineStr"/>
       <c r="Y51" s="6" t="inlineStr"/>
       <c r="Z51" s="6" t="inlineStr"/>
+      <c r="AA51" s="6" t="inlineStr">
+        <is>
+          <t>(888) 904-7172</t>
+        </is>
+      </c>
+      <c r="AB51" s="6" t="inlineStr"/>
+      <c r="AC51" s="6" t="inlineStr">
+        <is>
+          <t>https://www.myaltahomes.com/</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
@@ -5882,6 +6367,17 @@
       <c r="X52" s="12" t="inlineStr"/>
       <c r="Y52" s="12" t="inlineStr"/>
       <c r="Z52" s="12" t="inlineStr"/>
+      <c r="AA52" s="12" t="inlineStr">
+        <is>
+          <t>(888) 904-7172</t>
+        </is>
+      </c>
+      <c r="AB52" s="12" t="inlineStr"/>
+      <c r="AC52" s="12" t="inlineStr">
+        <is>
+          <t>https://www.myaltahomes.com/</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
@@ -5982,6 +6478,9 @@
       </c>
       <c r="Y53" s="6" t="inlineStr"/>
       <c r="Z53" s="6" t="inlineStr"/>
+      <c r="AA53" s="6" t="inlineStr"/>
+      <c r="AB53" s="6" t="inlineStr"/>
+      <c r="AC53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
@@ -6091,6 +6590,9 @@
       </c>
       <c r="Y54" s="12" t="inlineStr"/>
       <c r="Z54" s="12" t="inlineStr"/>
+      <c r="AA54" s="12" t="inlineStr"/>
+      <c r="AB54" s="12" t="inlineStr"/>
+      <c r="AC54" s="12" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
@@ -6195,6 +6697,17 @@
       <c r="X55" s="6" t="inlineStr"/>
       <c r="Y55" s="6" t="inlineStr"/>
       <c r="Z55" s="6" t="inlineStr"/>
+      <c r="AA55" s="6" t="inlineStr">
+        <is>
+          <t>(888) 498-6815</t>
+        </is>
+      </c>
+      <c r="AB55" s="6" t="inlineStr"/>
+      <c r="AC55" s="6" t="inlineStr">
+        <is>
+          <t>https://www.longlakeltd.com/</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
@@ -6300,6 +6813,17 @@
       <c r="X56" s="12" t="inlineStr"/>
       <c r="Y56" s="12" t="inlineStr"/>
       <c r="Z56" s="12" t="inlineStr"/>
+      <c r="AA56" s="12" t="inlineStr">
+        <is>
+          <t>(888) 498-6815</t>
+        </is>
+      </c>
+      <c r="AB56" s="12" t="inlineStr"/>
+      <c r="AC56" s="12" t="inlineStr">
+        <is>
+          <t>https://www.longlakeltd.com/</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
@@ -6401,6 +6925,17 @@
       <c r="X57" s="6" t="inlineStr"/>
       <c r="Y57" s="6" t="inlineStr"/>
       <c r="Z57" s="6" t="inlineStr"/>
+      <c r="AA57" s="6" t="inlineStr">
+        <is>
+          <t>(888) 498-6815</t>
+        </is>
+      </c>
+      <c r="AB57" s="6" t="inlineStr"/>
+      <c r="AC57" s="6" t="inlineStr">
+        <is>
+          <t>https://www.longlakeltd.com/</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
@@ -6509,6 +7044,17 @@
       <c r="X58" s="12" t="inlineStr"/>
       <c r="Y58" s="12" t="inlineStr"/>
       <c r="Z58" s="12" t="inlineStr"/>
+      <c r="AA58" s="12" t="inlineStr">
+        <is>
+          <t>(888) 498-6815</t>
+        </is>
+      </c>
+      <c r="AB58" s="12" t="inlineStr"/>
+      <c r="AC58" s="12" t="inlineStr">
+        <is>
+          <t>https://www.longlakeltd.com/</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
@@ -6622,6 +7168,21 @@
         </is>
       </c>
       <c r="Z59" s="6" t="inlineStr"/>
+      <c r="AA59" s="6" t="inlineStr">
+        <is>
+          <t>(833) 684-6527</t>
+        </is>
+      </c>
+      <c r="AB59" s="6" t="inlineStr">
+        <is>
+          <t>warranty</t>
+        </is>
+      </c>
+      <c r="AC59" s="6" t="inlineStr">
+        <is>
+          <t>https://www.meritagehomes.com/company/contact</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="12" t="inlineStr">
@@ -6734,6 +7295,21 @@
         </is>
       </c>
       <c r="Z60" s="12" t="inlineStr"/>
+      <c r="AA60" s="12" t="inlineStr">
+        <is>
+          <t>(833) 684-6527</t>
+        </is>
+      </c>
+      <c r="AB60" s="12" t="inlineStr">
+        <is>
+          <t>warranty</t>
+        </is>
+      </c>
+      <c r="AC60" s="12" t="inlineStr">
+        <is>
+          <t>https://www.meritagehomes.com/company/contact</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
@@ -6846,6 +7422,21 @@
         </is>
       </c>
       <c r="Z61" s="6" t="inlineStr"/>
+      <c r="AA61" s="6" t="inlineStr">
+        <is>
+          <t>(833) 684-6527</t>
+        </is>
+      </c>
+      <c r="AB61" s="6" t="inlineStr">
+        <is>
+          <t>warranty</t>
+        </is>
+      </c>
+      <c r="AC61" s="6" t="inlineStr">
+        <is>
+          <t>https://www.meritagehomes.com/company/contact</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
@@ -6939,6 +7530,17 @@
       <c r="X62" s="12" t="inlineStr"/>
       <c r="Y62" s="12" t="inlineStr"/>
       <c r="Z62" s="12" t="inlineStr"/>
+      <c r="AA62" s="12" t="inlineStr">
+        <is>
+          <t>(877) 552-3727</t>
+        </is>
+      </c>
+      <c r="AB62" s="12" t="inlineStr"/>
+      <c r="AC62" s="12" t="inlineStr">
+        <is>
+          <t>https://www.smithdouglas.com/</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
@@ -7051,6 +7653,17 @@
         </is>
       </c>
       <c r="Z63" s="6" t="inlineStr"/>
+      <c r="AA63" s="6" t="inlineStr">
+        <is>
+          <t>(888) 234-9451</t>
+        </is>
+      </c>
+      <c r="AB63" s="6" t="inlineStr"/>
+      <c r="AC63" s="6" t="inlineStr">
+        <is>
+          <t>https://www.camillocompanies.com/</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="12" t="inlineStr">
@@ -7163,6 +7776,17 @@
         </is>
       </c>
       <c r="Z64" s="12" t="inlineStr"/>
+      <c r="AA64" s="12" t="inlineStr">
+        <is>
+          <t>(888) 234-9451</t>
+        </is>
+      </c>
+      <c r="AB64" s="12" t="inlineStr"/>
+      <c r="AC64" s="12" t="inlineStr">
+        <is>
+          <t>https://www.camillocompanies.com/</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
@@ -7275,6 +7899,17 @@
         </is>
       </c>
       <c r="Z65" s="6" t="inlineStr"/>
+      <c r="AA65" s="6" t="inlineStr">
+        <is>
+          <t>(888) 234-9451</t>
+        </is>
+      </c>
+      <c r="AB65" s="6" t="inlineStr"/>
+      <c r="AC65" s="6" t="inlineStr">
+        <is>
+          <t>https://www.camillocompanies.com/</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="12" t="inlineStr">
@@ -7387,6 +8022,17 @@
         </is>
       </c>
       <c r="Z66" s="12" t="inlineStr"/>
+      <c r="AA66" s="12" t="inlineStr">
+        <is>
+          <t>(888) 234-9451</t>
+        </is>
+      </c>
+      <c r="AB66" s="12" t="inlineStr"/>
+      <c r="AC66" s="12" t="inlineStr">
+        <is>
+          <t>https://www.camillocompanies.com/</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
@@ -7499,6 +8145,17 @@
         </is>
       </c>
       <c r="Z67" s="6" t="inlineStr"/>
+      <c r="AA67" s="6" t="inlineStr">
+        <is>
+          <t>(713) 600-7000</t>
+        </is>
+      </c>
+      <c r="AB67" s="6" t="inlineStr"/>
+      <c r="AC67" s="6" t="inlineStr">
+        <is>
+          <t>https://www.c-rock.com/</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="12" t="inlineStr">
@@ -7612,6 +8269,17 @@
         </is>
       </c>
       <c r="Z68" s="12" t="inlineStr"/>
+      <c r="AA68" s="12" t="inlineStr">
+        <is>
+          <t>(713) 600-7000</t>
+        </is>
+      </c>
+      <c r="AB68" s="12" t="inlineStr"/>
+      <c r="AC68" s="12" t="inlineStr">
+        <is>
+          <t>https://www.c-rock.com/</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
@@ -7728,6 +8396,21 @@
         </is>
       </c>
       <c r="Z69" s="6" t="inlineStr"/>
+      <c r="AA69" s="6" t="inlineStr">
+        <is>
+          <t>(480) 428-8994</t>
+        </is>
+      </c>
+      <c r="AB69" s="6" t="inlineStr">
+        <is>
+          <t>published in the privacy notice</t>
+        </is>
+      </c>
+      <c r="AC69" s="6" t="inlineStr">
+        <is>
+          <t>https://www.christophertodd.com/</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="12" t="inlineStr">
@@ -7844,6 +8527,21 @@
         </is>
       </c>
       <c r="Z70" s="12" t="inlineStr"/>
+      <c r="AA70" s="12" t="inlineStr">
+        <is>
+          <t>(480) 428-8994</t>
+        </is>
+      </c>
+      <c r="AB70" s="12" t="inlineStr">
+        <is>
+          <t>published in the privacy notice</t>
+        </is>
+      </c>
+      <c r="AC70" s="12" t="inlineStr">
+        <is>
+          <t>https://www.christophertodd.com/</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
@@ -7948,6 +8646,21 @@
       <c r="X71" s="6" t="inlineStr"/>
       <c r="Y71" s="6" t="inlineStr"/>
       <c r="Z71" s="6" t="inlineStr"/>
+      <c r="AA71" s="6" t="inlineStr">
+        <is>
+          <t>(281) 915-9791</t>
+        </is>
+      </c>
+      <c r="AB71" s="6" t="inlineStr">
+        <is>
+          <t>Greater Houston</t>
+        </is>
+      </c>
+      <c r="AC71" s="6" t="inlineStr">
+        <is>
+          <t>https://www.everlastinghomesgroup.com/</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="12" t="inlineStr">
@@ -8052,6 +8765,21 @@
       <c r="X72" s="12" t="inlineStr"/>
       <c r="Y72" s="12" t="inlineStr"/>
       <c r="Z72" s="12" t="inlineStr"/>
+      <c r="AA72" s="12" t="inlineStr">
+        <is>
+          <t>(281) 915-9791</t>
+        </is>
+      </c>
+      <c r="AB72" s="12" t="inlineStr">
+        <is>
+          <t>Greater Houston</t>
+        </is>
+      </c>
+      <c r="AC72" s="12" t="inlineStr">
+        <is>
+          <t>https://www.everlastinghomesgroup.com/</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
@@ -8145,6 +8873,9 @@
       <c r="X73" s="6" t="inlineStr"/>
       <c r="Y73" s="6" t="inlineStr"/>
       <c r="Z73" s="6" t="inlineStr"/>
+      <c r="AA73" s="6" t="inlineStr"/>
+      <c r="AB73" s="6" t="inlineStr"/>
+      <c r="AC73" s="6" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="12" t="inlineStr">
@@ -8249,6 +8980,17 @@
       <c r="X74" s="12" t="inlineStr"/>
       <c r="Y74" s="12" t="inlineStr"/>
       <c r="Z74" s="12" t="inlineStr"/>
+      <c r="AA74" s="12" t="inlineStr">
+        <is>
+          <t>(832) 265-7353</t>
+        </is>
+      </c>
+      <c r="AB74" s="12" t="inlineStr"/>
+      <c r="AC74" s="12" t="inlineStr">
+        <is>
+          <t>https://www.nautiluscustomhomes.com/</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
@@ -8349,6 +9091,17 @@
       <c r="X75" s="6" t="inlineStr"/>
       <c r="Y75" s="6" t="inlineStr"/>
       <c r="Z75" s="6" t="inlineStr"/>
+      <c r="AA75" s="6" t="inlineStr">
+        <is>
+          <t>(832) 265-7353</t>
+        </is>
+      </c>
+      <c r="AB75" s="6" t="inlineStr"/>
+      <c r="AC75" s="6" t="inlineStr">
+        <is>
+          <t>https://www.nautiluscustomhomes.com/</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="12" t="inlineStr">
@@ -8442,6 +9195,21 @@
       <c r="X76" s="12" t="inlineStr"/>
       <c r="Y76" s="12" t="inlineStr"/>
       <c r="Z76" s="12" t="inlineStr"/>
+      <c r="AA76" s="12" t="inlineStr">
+        <is>
+          <t>(409) 256-4888</t>
+        </is>
+      </c>
+      <c r="AB76" s="12" t="inlineStr">
+        <is>
+          <t>office</t>
+        </is>
+      </c>
+      <c r="AC76" s="12" t="inlineStr">
+        <is>
+          <t>https://seaside-construction.com/</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
@@ -8546,6 +9314,17 @@
       <c r="X77" s="6" t="inlineStr"/>
       <c r="Y77" s="6" t="inlineStr"/>
       <c r="Z77" s="6" t="inlineStr"/>
+      <c r="AA77" s="6" t="inlineStr">
+        <is>
+          <t>(346) 263-0547</t>
+        </is>
+      </c>
+      <c r="AB77" s="6" t="inlineStr"/>
+      <c r="AC77" s="6" t="inlineStr">
+        <is>
+          <t>https://www.tilsonhomes.com/</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="12" t="inlineStr">
@@ -8651,6 +9430,17 @@
       <c r="X78" s="12" t="inlineStr"/>
       <c r="Y78" s="12" t="inlineStr"/>
       <c r="Z78" s="12" t="inlineStr"/>
+      <c r="AA78" s="12" t="inlineStr">
+        <is>
+          <t>(281) 240-1551</t>
+        </is>
+      </c>
+      <c r="AB78" s="12" t="inlineStr"/>
+      <c r="AC78" s="12" t="inlineStr">
+        <is>
+          <t>https://www.westin-homes.com/</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
@@ -8760,6 +9550,17 @@
       <c r="X79" s="6" t="inlineStr"/>
       <c r="Y79" s="6" t="inlineStr"/>
       <c r="Z79" s="6" t="inlineStr"/>
+      <c r="AA79" s="6" t="inlineStr">
+        <is>
+          <t>(281) 240-1551</t>
+        </is>
+      </c>
+      <c r="AB79" s="6" t="inlineStr"/>
+      <c r="AC79" s="6" t="inlineStr">
+        <is>
+          <t>https://www.westin-homes.com/</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="12" t="inlineStr">
@@ -8876,6 +9677,17 @@
         </is>
       </c>
       <c r="Z80" s="12" t="inlineStr"/>
+      <c r="AA80" s="12" t="inlineStr">
+        <is>
+          <t>(713) 864-8099</t>
+        </is>
+      </c>
+      <c r="AB80" s="12" t="inlineStr"/>
+      <c r="AC80" s="12" t="inlineStr">
+        <is>
+          <t>https://avenuecdc.org/</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
@@ -8989,6 +9801,17 @@
         </is>
       </c>
       <c r="Z81" s="6" t="inlineStr"/>
+      <c r="AA81" s="6" t="inlineStr">
+        <is>
+          <t>(713) 864-8099</t>
+        </is>
+      </c>
+      <c r="AB81" s="6" t="inlineStr"/>
+      <c r="AC81" s="6" t="inlineStr">
+        <is>
+          <t>https://avenuecdc.org/</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="12" t="inlineStr">
@@ -9102,6 +9925,17 @@
         </is>
       </c>
       <c r="Z82" s="12" t="inlineStr"/>
+      <c r="AA82" s="12" t="inlineStr">
+        <is>
+          <t>(713) 864-8099</t>
+        </is>
+      </c>
+      <c r="AB82" s="12" t="inlineStr"/>
+      <c r="AC82" s="12" t="inlineStr">
+        <is>
+          <t>https://avenuecdc.org/</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
@@ -9211,6 +10045,17 @@
         </is>
       </c>
       <c r="Z83" s="6" t="inlineStr"/>
+      <c r="AA83" s="6" t="inlineStr">
+        <is>
+          <t>(713) 864-8099</t>
+        </is>
+      </c>
+      <c r="AB83" s="6" t="inlineStr"/>
+      <c r="AC83" s="6" t="inlineStr">
+        <is>
+          <t>https://avenuecdc.org/</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="12" t="inlineStr">
@@ -9324,6 +10169,17 @@
         </is>
       </c>
       <c r="Z84" s="12" t="inlineStr"/>
+      <c r="AA84" s="12" t="inlineStr">
+        <is>
+          <t>(713) 864-8099</t>
+        </is>
+      </c>
+      <c r="AB84" s="12" t="inlineStr"/>
+      <c r="AC84" s="12" t="inlineStr">
+        <is>
+          <t>https://avenuecdc.org/</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
@@ -9432,6 +10288,9 @@
       <c r="X85" s="6" t="inlineStr"/>
       <c r="Y85" s="6" t="inlineStr"/>
       <c r="Z85" s="6" t="inlineStr"/>
+      <c r="AA85" s="6" t="inlineStr"/>
+      <c r="AB85" s="6" t="inlineStr"/>
+      <c r="AC85" s="6" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="12" t="inlineStr">
@@ -9541,6 +10400,9 @@
       <c r="X86" s="12" t="inlineStr"/>
       <c r="Y86" s="12" t="inlineStr"/>
       <c r="Z86" s="12" t="inlineStr"/>
+      <c r="AA86" s="12" t="inlineStr"/>
+      <c r="AB86" s="12" t="inlineStr"/>
+      <c r="AC86" s="12" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
@@ -9649,6 +10511,17 @@
       <c r="X87" s="6" t="inlineStr"/>
       <c r="Y87" s="6" t="inlineStr"/>
       <c r="Z87" s="6" t="inlineStr"/>
+      <c r="AA87" s="6" t="inlineStr">
+        <is>
+          <t>(866) 510-2449</t>
+        </is>
+      </c>
+      <c r="AB87" s="6" t="inlineStr"/>
+      <c r="AC87" s="6" t="inlineStr">
+        <is>
+          <t>https://imaginationhomes.com/</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="12" t="inlineStr">
@@ -9758,6 +10631,17 @@
       <c r="X88" s="12" t="inlineStr"/>
       <c r="Y88" s="12" t="inlineStr"/>
       <c r="Z88" s="12" t="inlineStr"/>
+      <c r="AA88" s="12" t="inlineStr">
+        <is>
+          <t>(832) 858-0755</t>
+        </is>
+      </c>
+      <c r="AB88" s="12" t="inlineStr"/>
+      <c r="AC88" s="12" t="inlineStr">
+        <is>
+          <t>https://jamestownestatehomes.com/</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
@@ -9862,6 +10746,17 @@
       <c r="X89" s="6" t="inlineStr"/>
       <c r="Y89" s="6" t="inlineStr"/>
       <c r="Z89" s="6" t="inlineStr"/>
+      <c r="AA89" s="6" t="inlineStr">
+        <is>
+          <t>(832) 858-0755</t>
+        </is>
+      </c>
+      <c r="AB89" s="6" t="inlineStr"/>
+      <c r="AC89" s="6" t="inlineStr">
+        <is>
+          <t>https://jamestownestatehomes.com/</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="12" t="inlineStr">
@@ -9966,6 +10861,17 @@
       <c r="X90" s="12" t="inlineStr"/>
       <c r="Y90" s="12" t="inlineStr"/>
       <c r="Z90" s="12" t="inlineStr"/>
+      <c r="AA90" s="12" t="inlineStr">
+        <is>
+          <t>(832) 858-0755</t>
+        </is>
+      </c>
+      <c r="AB90" s="12" t="inlineStr"/>
+      <c r="AC90" s="12" t="inlineStr">
+        <is>
+          <t>https://jamestownestatehomes.com/</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
@@ -10071,6 +10977,17 @@
       <c r="X91" s="6" t="inlineStr"/>
       <c r="Y91" s="6" t="inlineStr"/>
       <c r="Z91" s="6" t="inlineStr"/>
+      <c r="AA91" s="6" t="inlineStr">
+        <is>
+          <t>(281) 609-8310</t>
+        </is>
+      </c>
+      <c r="AB91" s="6" t="inlineStr"/>
+      <c r="AC91" s="6" t="inlineStr">
+        <is>
+          <t>https://kendallhomes.net/</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="12" t="inlineStr">
@@ -10184,6 +11101,21 @@
       <c r="X92" s="12" t="inlineStr"/>
       <c r="Y92" s="12" t="inlineStr"/>
       <c r="Z92" s="12" t="inlineStr"/>
+      <c r="AA92" s="12" t="inlineStr">
+        <is>
+          <t>(713) 864-9190</t>
+        </is>
+      </c>
+      <c r="AB92" s="12" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="AC92" s="12" t="inlineStr">
+        <is>
+          <t>https://www.sandcastlehouston.com/</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
@@ -10293,6 +11225,21 @@
       <c r="X93" s="6" t="inlineStr"/>
       <c r="Y93" s="6" t="inlineStr"/>
       <c r="Z93" s="6" t="inlineStr"/>
+      <c r="AA93" s="6" t="inlineStr">
+        <is>
+          <t>(713) 864-9190</t>
+        </is>
+      </c>
+      <c r="AB93" s="6" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="AC93" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sandcastlehouston.com/</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="12" t="inlineStr">
@@ -10398,6 +11345,21 @@
       <c r="X94" s="12" t="inlineStr"/>
       <c r="Y94" s="12" t="inlineStr"/>
       <c r="Z94" s="12" t="inlineStr"/>
+      <c r="AA94" s="12" t="inlineStr">
+        <is>
+          <t>(713) 864-9190</t>
+        </is>
+      </c>
+      <c r="AB94" s="12" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="AC94" s="12" t="inlineStr">
+        <is>
+          <t>https://www.sandcastlehouston.com/</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
@@ -10499,6 +11461,21 @@
       <c r="X95" s="6" t="inlineStr"/>
       <c r="Y95" s="6" t="inlineStr"/>
       <c r="Z95" s="6" t="inlineStr"/>
+      <c r="AA95" s="6" t="inlineStr">
+        <is>
+          <t>(713) 864-9190</t>
+        </is>
+      </c>
+      <c r="AB95" s="6" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="AC95" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sandcastlehouston.com/</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="12" t="inlineStr">
@@ -10599,6 +11576,21 @@
       <c r="X96" s="12" t="inlineStr"/>
       <c r="Y96" s="12" t="inlineStr"/>
       <c r="Z96" s="12" t="inlineStr"/>
+      <c r="AA96" s="12" t="inlineStr">
+        <is>
+          <t>(713) 489-7738</t>
+        </is>
+      </c>
+      <c r="AB96" s="12" t="inlineStr">
+        <is>
+          <t>the Westway Park office</t>
+        </is>
+      </c>
+      <c r="AC96" s="12" t="inlineStr">
+        <is>
+          <t>https://www.tricoasthomes.com/</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
@@ -10699,6 +11691,21 @@
       <c r="X97" s="6" t="inlineStr"/>
       <c r="Y97" s="6" t="inlineStr"/>
       <c r="Z97" s="6" t="inlineStr"/>
+      <c r="AA97" s="6" t="inlineStr">
+        <is>
+          <t>(713) 489-7738</t>
+        </is>
+      </c>
+      <c r="AB97" s="6" t="inlineStr">
+        <is>
+          <t>the Westway Park office</t>
+        </is>
+      </c>
+      <c r="AC97" s="6" t="inlineStr">
+        <is>
+          <t>https://www.tricoasthomes.com/</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="12" t="inlineStr">
@@ -10808,6 +11815,21 @@
       <c r="X98" s="12" t="inlineStr"/>
       <c r="Y98" s="12" t="inlineStr"/>
       <c r="Z98" s="12" t="inlineStr"/>
+      <c r="AA98" s="12" t="inlineStr">
+        <is>
+          <t>(713) 489-7738</t>
+        </is>
+      </c>
+      <c r="AB98" s="12" t="inlineStr">
+        <is>
+          <t>the Westway Park office</t>
+        </is>
+      </c>
+      <c r="AC98" s="12" t="inlineStr">
+        <is>
+          <t>https://www.tricoasthomes.com/</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
@@ -10920,6 +11942,21 @@
         </is>
       </c>
       <c r="Z99" s="6" t="inlineStr"/>
+      <c r="AA99" s="6" t="inlineStr">
+        <is>
+          <t>(972) 385-4100</t>
+        </is>
+      </c>
+      <c r="AB99" s="6" t="inlineStr">
+        <is>
+          <t>Dallas office</t>
+        </is>
+      </c>
+      <c r="AC99" s="6" t="inlineStr">
+        <is>
+          <t>https://provident.net/</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="12" t="inlineStr">
@@ -11036,6 +12073,21 @@
         </is>
       </c>
       <c r="Z100" s="12" t="inlineStr"/>
+      <c r="AA100" s="12" t="inlineStr">
+        <is>
+          <t>(972) 385-4100</t>
+        </is>
+      </c>
+      <c r="AB100" s="12" t="inlineStr">
+        <is>
+          <t>Dallas office</t>
+        </is>
+      </c>
+      <c r="AC100" s="12" t="inlineStr">
+        <is>
+          <t>https://provident.net/</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
@@ -11145,6 +12197,17 @@
       <c r="X101" s="6" t="inlineStr"/>
       <c r="Y101" s="6" t="inlineStr"/>
       <c r="Z101" s="6" t="inlineStr"/>
+      <c r="AA101" s="6" t="inlineStr">
+        <is>
+          <t>(888) 827-4421</t>
+        </is>
+      </c>
+      <c r="AB101" s="6" t="inlineStr"/>
+      <c r="AC101" s="6" t="inlineStr">
+        <is>
+          <t>https://risewellhomes.com/</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="12" t="inlineStr">
@@ -11254,6 +12317,17 @@
       <c r="X102" s="12" t="inlineStr"/>
       <c r="Y102" s="12" t="inlineStr"/>
       <c r="Z102" s="12" t="inlineStr"/>
+      <c r="AA102" s="12" t="inlineStr">
+        <is>
+          <t>(888) 827-4421</t>
+        </is>
+      </c>
+      <c r="AB102" s="12" t="inlineStr"/>
+      <c r="AC102" s="12" t="inlineStr">
+        <is>
+          <t>https://risewellhomes.com/</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
@@ -11363,6 +12437,21 @@
       </c>
       <c r="Y103" s="6" t="inlineStr"/>
       <c r="Z103" s="6" t="inlineStr"/>
+      <c r="AA103" s="6" t="inlineStr">
+        <is>
+          <t>(713) 903-2596</t>
+        </is>
+      </c>
+      <c r="AB103" s="6" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
+      </c>
+      <c r="AC103" s="6" t="inlineStr">
+        <is>
+          <t>https://www.coventryhomes.com/connect/</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="12" t="inlineStr">
@@ -11471,6 +12560,21 @@
       <c r="X104" s="12" t="inlineStr"/>
       <c r="Y104" s="12" t="inlineStr"/>
       <c r="Z104" s="12" t="inlineStr"/>
+      <c r="AA104" s="12" t="inlineStr">
+        <is>
+          <t>(713) 346-0200</t>
+        </is>
+      </c>
+      <c r="AB104" s="12" t="inlineStr">
+        <is>
+          <t>office</t>
+        </is>
+      </c>
+      <c r="AC104" s="12" t="inlineStr">
+        <is>
+          <t>https://newmarkhomes.com/</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
@@ -11576,6 +12680,21 @@
       <c r="X105" s="6" t="inlineStr"/>
       <c r="Y105" s="6" t="inlineStr"/>
       <c r="Z105" s="6" t="inlineStr"/>
+      <c r="AA105" s="6" t="inlineStr">
+        <is>
+          <t>(281) 664-7255</t>
+        </is>
+      </c>
+      <c r="AB105" s="6" t="inlineStr">
+        <is>
+          <t>Houston design studio</t>
+        </is>
+      </c>
+      <c r="AC105" s="6" t="inlineStr">
+        <is>
+          <t>https://sitterlehomes.com/contact/</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="12" t="inlineStr">
@@ -11681,6 +12800,21 @@
       <c r="X106" s="12" t="inlineStr"/>
       <c r="Y106" s="12" t="inlineStr"/>
       <c r="Z106" s="12" t="inlineStr"/>
+      <c r="AA106" s="12" t="inlineStr">
+        <is>
+          <t>(281) 664-7255</t>
+        </is>
+      </c>
+      <c r="AB106" s="12" t="inlineStr">
+        <is>
+          <t>Houston design studio</t>
+        </is>
+      </c>
+      <c r="AC106" s="12" t="inlineStr">
+        <is>
+          <t>https://sitterlehomes.com/contact/</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
@@ -11786,6 +12920,21 @@
       <c r="X107" s="6" t="inlineStr"/>
       <c r="Y107" s="6" t="inlineStr"/>
       <c r="Z107" s="6" t="inlineStr"/>
+      <c r="AA107" s="6" t="inlineStr">
+        <is>
+          <t>(281) 664-7255</t>
+        </is>
+      </c>
+      <c r="AB107" s="6" t="inlineStr">
+        <is>
+          <t>Houston design studio</t>
+        </is>
+      </c>
+      <c r="AC107" s="6" t="inlineStr">
+        <is>
+          <t>https://sitterlehomes.com/contact/</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="12" t="inlineStr">
@@ -11898,6 +13047,9 @@
         </is>
       </c>
       <c r="Z108" s="12" t="inlineStr"/>
+      <c r="AA108" s="12" t="inlineStr"/>
+      <c r="AB108" s="12" t="inlineStr"/>
+      <c r="AC108" s="12" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
@@ -12010,6 +13162,9 @@
         </is>
       </c>
       <c r="Z109" s="6" t="inlineStr"/>
+      <c r="AA109" s="6" t="inlineStr"/>
+      <c r="AB109" s="6" t="inlineStr"/>
+      <c r="AC109" s="6" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="12" t="inlineStr">
@@ -12123,6 +13278,9 @@
         </is>
       </c>
       <c r="Z110" s="12" t="inlineStr"/>
+      <c r="AA110" s="12" t="inlineStr"/>
+      <c r="AB110" s="12" t="inlineStr"/>
+      <c r="AC110" s="12" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
@@ -12232,6 +13390,9 @@
         </is>
       </c>
       <c r="Z111" s="6" t="inlineStr"/>
+      <c r="AA111" s="6" t="inlineStr"/>
+      <c r="AB111" s="6" t="inlineStr"/>
+      <c r="AC111" s="6" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="12" t="inlineStr">
@@ -12341,6 +13502,9 @@
         </is>
       </c>
       <c r="Z112" s="12" t="inlineStr"/>
+      <c r="AA112" s="12" t="inlineStr"/>
+      <c r="AB112" s="12" t="inlineStr"/>
+      <c r="AC112" s="12" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="6" t="inlineStr">
@@ -12446,6 +13610,17 @@
       <c r="X113" s="6" t="inlineStr"/>
       <c r="Y113" s="6" t="inlineStr"/>
       <c r="Z113" s="6" t="inlineStr"/>
+      <c r="AA113" s="6" t="inlineStr">
+        <is>
+          <t>(832) 653-3600</t>
+        </is>
+      </c>
+      <c r="AB113" s="6" t="inlineStr"/>
+      <c r="AC113" s="6" t="inlineStr">
+        <is>
+          <t>https://www.ravennahomes.com/</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="12" t="inlineStr">
@@ -12554,6 +13729,21 @@
       <c r="X114" s="12" t="inlineStr"/>
       <c r="Y114" s="12" t="inlineStr"/>
       <c r="Z114" s="12" t="inlineStr"/>
+      <c r="AA114" s="12" t="inlineStr">
+        <is>
+          <t>(832) 264-6282</t>
+        </is>
+      </c>
+      <c r="AB114" s="12" t="inlineStr">
+        <is>
+          <t>office</t>
+        </is>
+      </c>
+      <c r="AC114" s="12" t="inlineStr">
+        <is>
+          <t>https://icfconstructors.com/</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="6" t="inlineStr">
@@ -12663,6 +13853,17 @@
       <c r="X115" s="6" t="inlineStr"/>
       <c r="Y115" s="6" t="inlineStr"/>
       <c r="Z115" s="6" t="inlineStr"/>
+      <c r="AA115" s="6" t="inlineStr">
+        <is>
+          <t>(281) 784-3070</t>
+        </is>
+      </c>
+      <c r="AB115" s="6" t="inlineStr"/>
+      <c r="AC115" s="6" t="inlineStr">
+        <is>
+          <t>https://www.botellobuilders.com/contact-us/</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="12" t="inlineStr">
@@ -12772,6 +13973,17 @@
       <c r="X116" s="12" t="inlineStr"/>
       <c r="Y116" s="12" t="inlineStr"/>
       <c r="Z116" s="12" t="inlineStr"/>
+      <c r="AA116" s="12" t="inlineStr">
+        <is>
+          <t>(281) 784-3070</t>
+        </is>
+      </c>
+      <c r="AB116" s="12" t="inlineStr"/>
+      <c r="AC116" s="12" t="inlineStr">
+        <is>
+          <t>https://www.botellobuilders.com/contact-us/</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="6" t="inlineStr">
@@ -12876,6 +14088,17 @@
       <c r="X117" s="6" t="inlineStr"/>
       <c r="Y117" s="6" t="inlineStr"/>
       <c r="Z117" s="6" t="inlineStr"/>
+      <c r="AA117" s="6" t="inlineStr">
+        <is>
+          <t>(281) 784-3070</t>
+        </is>
+      </c>
+      <c r="AB117" s="6" t="inlineStr"/>
+      <c r="AC117" s="6" t="inlineStr">
+        <is>
+          <t>https://www.botellobuilders.com/contact-us/</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="12" t="inlineStr">
@@ -12985,6 +14208,21 @@
       <c r="X118" s="12" t="inlineStr"/>
       <c r="Y118" s="12" t="inlineStr"/>
       <c r="Z118" s="12" t="inlineStr"/>
+      <c r="AA118" s="12" t="inlineStr">
+        <is>
+          <t>(713) 983-8002</t>
+        </is>
+      </c>
+      <c r="AB118" s="12" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
+      </c>
+      <c r="AC118" s="12" t="inlineStr">
+        <is>
+          <t>https://www.keystoneconcrete.com/</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="6" t="inlineStr">
@@ -13094,6 +14332,21 @@
       <c r="X119" s="6" t="inlineStr"/>
       <c r="Y119" s="6" t="inlineStr"/>
       <c r="Z119" s="6" t="inlineStr"/>
+      <c r="AA119" s="6" t="inlineStr">
+        <is>
+          <t>(713) 983-8002</t>
+        </is>
+      </c>
+      <c r="AB119" s="6" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
+      </c>
+      <c r="AC119" s="6" t="inlineStr">
+        <is>
+          <t>https://www.keystoneconcrete.com/</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="12" t="inlineStr">
@@ -13203,6 +14456,21 @@
       <c r="X120" s="12" t="inlineStr"/>
       <c r="Y120" s="12" t="inlineStr"/>
       <c r="Z120" s="12" t="inlineStr"/>
+      <c r="AA120" s="12" t="inlineStr">
+        <is>
+          <t>(713) 681-2626</t>
+        </is>
+      </c>
+      <c r="AB120" s="12" t="inlineStr">
+        <is>
+          <t>commercial, Judiway Street</t>
+        </is>
+      </c>
+      <c r="AC120" s="12" t="inlineStr">
+        <is>
+          <t>https://www.marekbros.com/houston/</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="6" t="inlineStr">
@@ -13307,6 +14575,21 @@
       <c r="X121" s="6" t="inlineStr"/>
       <c r="Y121" s="6" t="inlineStr"/>
       <c r="Z121" s="6" t="inlineStr"/>
+      <c r="AA121" s="6" t="inlineStr">
+        <is>
+          <t>(713) 681-2626</t>
+        </is>
+      </c>
+      <c r="AB121" s="6" t="inlineStr">
+        <is>
+          <t>commercial, Judiway Street</t>
+        </is>
+      </c>
+      <c r="AC121" s="6" t="inlineStr">
+        <is>
+          <t>https://www.marekbros.com/houston/</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="12" t="inlineStr">
@@ -13411,6 +14694,21 @@
       <c r="X122" s="12" t="inlineStr"/>
       <c r="Y122" s="12" t="inlineStr"/>
       <c r="Z122" s="12" t="inlineStr"/>
+      <c r="AA122" s="12" t="inlineStr">
+        <is>
+          <t>(713) 681-2626</t>
+        </is>
+      </c>
+      <c r="AB122" s="12" t="inlineStr">
+        <is>
+          <t>commercial, Judiway Street</t>
+        </is>
+      </c>
+      <c r="AC122" s="12" t="inlineStr">
+        <is>
+          <t>https://www.marekbros.com/houston/</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="6" t="inlineStr">
@@ -13511,6 +14809,21 @@
       <c r="X123" s="6" t="inlineStr"/>
       <c r="Y123" s="6" t="inlineStr"/>
       <c r="Z123" s="6" t="inlineStr"/>
+      <c r="AA123" s="6" t="inlineStr">
+        <is>
+          <t>(713) 681-2626</t>
+        </is>
+      </c>
+      <c r="AB123" s="6" t="inlineStr">
+        <is>
+          <t>commercial, Judiway Street</t>
+        </is>
+      </c>
+      <c r="AC123" s="6" t="inlineStr">
+        <is>
+          <t>https://www.marekbros.com/houston/</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="12" t="inlineStr">
@@ -13624,6 +14937,17 @@
           <t>2025-03 Construction In Focus. CIVE, Construction and Design at their Finest  https://constructioninfocus.com/2025/03/cive-construction-and-design-at-their-finest/</t>
         </is>
       </c>
+      <c r="AA124" s="12" t="inlineStr">
+        <is>
+          <t>(281) 870-8727</t>
+        </is>
+      </c>
+      <c r="AB124" s="12" t="inlineStr"/>
+      <c r="AC124" s="12" t="inlineStr">
+        <is>
+          <t>https://cive.com/</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="6" t="inlineStr">
@@ -13737,6 +15061,17 @@
           <t>2025-03 Construction In Focus. CIVE, Construction and Design at their Finest  https://constructioninfocus.com/2025/03/cive-construction-and-design-at-their-finest/</t>
         </is>
       </c>
+      <c r="AA125" s="6" t="inlineStr">
+        <is>
+          <t>(281) 870-8727</t>
+        </is>
+      </c>
+      <c r="AB125" s="6" t="inlineStr"/>
+      <c r="AC125" s="6" t="inlineStr">
+        <is>
+          <t>https://cive.com/</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="12" t="inlineStr">
@@ -13843,6 +15178,17 @@
       <c r="Z126" s="12" t="inlineStr">
         <is>
           <t>2025-03 Construction In Focus. CIVE, Construction and Design at their Finest  https://constructioninfocus.com/2025/03/cive-construction-and-design-at-their-finest/</t>
+        </is>
+      </c>
+      <c r="AA126" s="12" t="inlineStr">
+        <is>
+          <t>(281) 870-8727</t>
+        </is>
+      </c>
+      <c r="AB126" s="12" t="inlineStr"/>
+      <c r="AC126" s="12" t="inlineStr">
+        <is>
+          <t>https://cive.com/</t>
         </is>
       </c>
     </row>
@@ -13945,6 +15291,17 @@
       <c r="X127" s="6" t="inlineStr"/>
       <c r="Y127" s="6" t="inlineStr"/>
       <c r="Z127" s="6" t="inlineStr"/>
+      <c r="AA127" s="6" t="inlineStr">
+        <is>
+          <t>(713) 914-9200</t>
+        </is>
+      </c>
+      <c r="AB127" s="6" t="inlineStr"/>
+      <c r="AC127" s="6" t="inlineStr">
+        <is>
+          <t>https://www.blazerbuilding.com/</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="12" t="inlineStr">
@@ -14045,6 +15402,17 @@
       <c r="X128" s="12" t="inlineStr"/>
       <c r="Y128" s="12" t="inlineStr"/>
       <c r="Z128" s="12" t="inlineStr"/>
+      <c r="AA128" s="12" t="inlineStr">
+        <is>
+          <t>(713) 914-9200</t>
+        </is>
+      </c>
+      <c r="AB128" s="12" t="inlineStr"/>
+      <c r="AC128" s="12" t="inlineStr">
+        <is>
+          <t>https://www.blazerbuilding.com/</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="6" t="inlineStr">
@@ -14145,6 +15513,17 @@
       <c r="X129" s="6" t="inlineStr"/>
       <c r="Y129" s="6" t="inlineStr"/>
       <c r="Z129" s="6" t="inlineStr"/>
+      <c r="AA129" s="6" t="inlineStr">
+        <is>
+          <t>(713) 914-9200</t>
+        </is>
+      </c>
+      <c r="AB129" s="6" t="inlineStr"/>
+      <c r="AC129" s="6" t="inlineStr">
+        <is>
+          <t>https://www.blazerbuilding.com/</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="12" t="inlineStr">
@@ -14245,6 +15624,17 @@
       <c r="X130" s="12" t="inlineStr"/>
       <c r="Y130" s="12" t="inlineStr"/>
       <c r="Z130" s="12" t="inlineStr"/>
+      <c r="AA130" s="12" t="inlineStr">
+        <is>
+          <t>(713) 914-9200</t>
+        </is>
+      </c>
+      <c r="AB130" s="12" t="inlineStr"/>
+      <c r="AC130" s="12" t="inlineStr">
+        <is>
+          <t>https://www.blazerbuilding.com/</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="6" t="inlineStr">
@@ -14353,6 +15743,17 @@
       <c r="X131" s="6" t="inlineStr"/>
       <c r="Y131" s="6" t="inlineStr"/>
       <c r="Z131" s="6" t="inlineStr"/>
+      <c r="AA131" s="6" t="inlineStr">
+        <is>
+          <t>(713) 375-2380</t>
+        </is>
+      </c>
+      <c r="AB131" s="6" t="inlineStr"/>
+      <c r="AC131" s="6" t="inlineStr">
+        <is>
+          <t>https://grecostructures.com/contact/</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="12" t="inlineStr">
@@ -14453,6 +15854,17 @@
       <c r="X132" s="12" t="inlineStr"/>
       <c r="Y132" s="12" t="inlineStr"/>
       <c r="Z132" s="12" t="inlineStr"/>
+      <c r="AA132" s="12" t="inlineStr">
+        <is>
+          <t>(713) 375-2380</t>
+        </is>
+      </c>
+      <c r="AB132" s="12" t="inlineStr"/>
+      <c r="AC132" s="12" t="inlineStr">
+        <is>
+          <t>https://grecostructures.com/contact/</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="6" t="inlineStr">
@@ -14558,6 +15970,17 @@
       <c r="X133" s="6" t="inlineStr"/>
       <c r="Y133" s="6" t="inlineStr"/>
       <c r="Z133" s="6" t="inlineStr"/>
+      <c r="AA133" s="6" t="inlineStr">
+        <is>
+          <t>(713) 375-2380</t>
+        </is>
+      </c>
+      <c r="AB133" s="6" t="inlineStr"/>
+      <c r="AC133" s="6" t="inlineStr">
+        <is>
+          <t>https://grecostructures.com/contact/</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="12" t="inlineStr">
@@ -14663,6 +16086,17 @@
       <c r="X134" s="12" t="inlineStr"/>
       <c r="Y134" s="12" t="inlineStr"/>
       <c r="Z134" s="12" t="inlineStr"/>
+      <c r="AA134" s="12" t="inlineStr">
+        <is>
+          <t>(713) 375-2380</t>
+        </is>
+      </c>
+      <c r="AB134" s="12" t="inlineStr"/>
+      <c r="AC134" s="12" t="inlineStr">
+        <is>
+          <t>https://grecostructures.com/contact/</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="6" t="inlineStr">
@@ -14767,6 +16201,9 @@
           <t>2026 Engineering News-Record. ENR 2026 Top 400 Contractors, where the firm is ranked 72  https://www.enr.com/toplists/2026-Top-400-Contractors-1</t>
         </is>
       </c>
+      <c r="AA135" s="6" t="inlineStr"/>
+      <c r="AB135" s="6" t="inlineStr"/>
+      <c r="AC135" s="6" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="12" t="inlineStr">
@@ -14871,6 +16308,9 @@
           <t>2026 Engineering News-Record. ENR 2026 Top 400 Contractors, where the firm is ranked 72  https://www.enr.com/toplists/2026-Top-400-Contractors-1</t>
         </is>
       </c>
+      <c r="AA136" s="12" t="inlineStr"/>
+      <c r="AB136" s="12" t="inlineStr"/>
+      <c r="AC136" s="12" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="6" t="inlineStr">
@@ -14975,6 +16415,9 @@
           <t>2026 Engineering News-Record. ENR 2026 Top 400 Contractors, where the firm is ranked 72  https://www.enr.com/toplists/2026-Top-400-Contractors-1</t>
         </is>
       </c>
+      <c r="AA137" s="6" t="inlineStr"/>
+      <c r="AB137" s="6" t="inlineStr"/>
+      <c r="AC137" s="6" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="12" t="inlineStr">
@@ -15088,6 +16531,9 @@
           <t>2026 Engineering News-Record. ENR 2026 Top 400 Contractors, where the firm is ranked 72  https://www.enr.com/toplists/2026-Top-400-Contractors-1</t>
         </is>
       </c>
+      <c r="AA138" s="12" t="inlineStr"/>
+      <c r="AB138" s="12" t="inlineStr"/>
+      <c r="AC138" s="12" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
@@ -15197,6 +16643,9 @@
           <t>2026 Engineering News-Record. ENR 2026 Top 400 Contractors, where the firm is ranked 72  https://www.enr.com/toplists/2026-Top-400-Contractors-1</t>
         </is>
       </c>
+      <c r="AA139" s="6" t="inlineStr"/>
+      <c r="AB139" s="6" t="inlineStr"/>
+      <c r="AC139" s="6" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="12" t="inlineStr">
@@ -15305,6 +16754,17 @@
       <c r="X140" s="12" t="inlineStr"/>
       <c r="Y140" s="12" t="inlineStr"/>
       <c r="Z140" s="12" t="inlineStr"/>
+      <c r="AA140" s="12" t="inlineStr">
+        <is>
+          <t>(713) 852-6500</t>
+        </is>
+      </c>
+      <c r="AB140" s="12" t="inlineStr"/>
+      <c r="AC140" s="12" t="inlineStr">
+        <is>
+          <t>https://www.oriongroupholdingsinc.com/</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
@@ -15414,6 +16874,17 @@
       <c r="X141" s="6" t="inlineStr"/>
       <c r="Y141" s="6" t="inlineStr"/>
       <c r="Z141" s="6" t="inlineStr"/>
+      <c r="AA141" s="6" t="inlineStr">
+        <is>
+          <t>(832) 663-6800</t>
+        </is>
+      </c>
+      <c r="AB141" s="6" t="inlineStr"/>
+      <c r="AC141" s="6" t="inlineStr">
+        <is>
+          <t>https://www.encoreconcrete.com/</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="12" t="inlineStr">
@@ -15523,6 +16994,17 @@
       <c r="X142" s="12" t="inlineStr"/>
       <c r="Y142" s="12" t="inlineStr"/>
       <c r="Z142" s="12" t="inlineStr"/>
+      <c r="AA142" s="12" t="inlineStr">
+        <is>
+          <t>(832) 663-6800</t>
+        </is>
+      </c>
+      <c r="AB142" s="12" t="inlineStr"/>
+      <c r="AC142" s="12" t="inlineStr">
+        <is>
+          <t>https://www.encoreconcrete.com/</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="6" t="inlineStr">
@@ -15623,6 +17105,21 @@
       <c r="X143" s="6" t="inlineStr"/>
       <c r="Y143" s="6" t="inlineStr"/>
       <c r="Z143" s="6" t="inlineStr"/>
+      <c r="AA143" s="6" t="inlineStr">
+        <is>
+          <t>(281) 207-0700</t>
+        </is>
+      </c>
+      <c r="AB143" s="6" t="inlineStr">
+        <is>
+          <t>Houston, at Katy</t>
+        </is>
+      </c>
+      <c r="AC143" s="6" t="inlineStr">
+        <is>
+          <t>https://rino-con.com/</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="12" t="inlineStr">
@@ -15723,6 +17220,21 @@
       <c r="X144" s="12" t="inlineStr"/>
       <c r="Y144" s="12" t="inlineStr"/>
       <c r="Z144" s="12" t="inlineStr"/>
+      <c r="AA144" s="12" t="inlineStr">
+        <is>
+          <t>(281) 207-0700</t>
+        </is>
+      </c>
+      <c r="AB144" s="12" t="inlineStr">
+        <is>
+          <t>Houston, at Katy</t>
+        </is>
+      </c>
+      <c r="AC144" s="12" t="inlineStr">
+        <is>
+          <t>https://rino-con.com/</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="6" t="inlineStr">
@@ -15823,6 +17335,21 @@
       <c r="X145" s="6" t="inlineStr"/>
       <c r="Y145" s="6" t="inlineStr"/>
       <c r="Z145" s="6" t="inlineStr"/>
+      <c r="AA145" s="6" t="inlineStr">
+        <is>
+          <t>(281) 207-0700</t>
+        </is>
+      </c>
+      <c r="AB145" s="6" t="inlineStr">
+        <is>
+          <t>Houston, at Katy</t>
+        </is>
+      </c>
+      <c r="AC145" s="6" t="inlineStr">
+        <is>
+          <t>https://rino-con.com/</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="12" t="inlineStr">
@@ -15928,6 +17455,21 @@
       <c r="X146" s="12" t="inlineStr"/>
       <c r="Y146" s="12" t="inlineStr"/>
       <c r="Z146" s="12" t="inlineStr"/>
+      <c r="AA146" s="12" t="inlineStr">
+        <is>
+          <t>(281) 207-0700</t>
+        </is>
+      </c>
+      <c r="AB146" s="12" t="inlineStr">
+        <is>
+          <t>Houston, at Katy</t>
+        </is>
+      </c>
+      <c r="AC146" s="12" t="inlineStr">
+        <is>
+          <t>https://rino-con.com/</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="6" t="inlineStr">
@@ -16033,6 +17575,21 @@
       <c r="X147" s="6" t="inlineStr"/>
       <c r="Y147" s="6" t="inlineStr"/>
       <c r="Z147" s="6" t="inlineStr"/>
+      <c r="AA147" s="6" t="inlineStr">
+        <is>
+          <t>(281) 207-0700</t>
+        </is>
+      </c>
+      <c r="AB147" s="6" t="inlineStr">
+        <is>
+          <t>Houston, at Katy</t>
+        </is>
+      </c>
+      <c r="AC147" s="6" t="inlineStr">
+        <is>
+          <t>https://rino-con.com/</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="12" t="inlineStr">
@@ -16142,6 +17699,21 @@
       <c r="X148" s="12" t="inlineStr"/>
       <c r="Y148" s="12" t="inlineStr"/>
       <c r="Z148" s="12" t="inlineStr"/>
+      <c r="AA148" s="12" t="inlineStr">
+        <is>
+          <t>(281) 405-9557</t>
+        </is>
+      </c>
+      <c r="AB148" s="12" t="inlineStr">
+        <is>
+          <t>office</t>
+        </is>
+      </c>
+      <c r="AC148" s="12" t="inlineStr">
+        <is>
+          <t>https://www.texasamconcrete.com/</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="6" t="inlineStr">
@@ -16243,6 +17815,21 @@
       <c r="X149" s="6" t="inlineStr"/>
       <c r="Y149" s="6" t="inlineStr"/>
       <c r="Z149" s="6" t="inlineStr"/>
+      <c r="AA149" s="6" t="inlineStr">
+        <is>
+          <t>(281) 405-9557</t>
+        </is>
+      </c>
+      <c r="AB149" s="6" t="inlineStr">
+        <is>
+          <t>office</t>
+        </is>
+      </c>
+      <c r="AC149" s="6" t="inlineStr">
+        <is>
+          <t>https://www.texasamconcrete.com/</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="12" t="inlineStr">
@@ -16344,6 +17931,21 @@
       <c r="X150" s="12" t="inlineStr"/>
       <c r="Y150" s="12" t="inlineStr"/>
       <c r="Z150" s="12" t="inlineStr"/>
+      <c r="AA150" s="12" t="inlineStr">
+        <is>
+          <t>(281) 405-9557</t>
+        </is>
+      </c>
+      <c r="AB150" s="12" t="inlineStr">
+        <is>
+          <t>office</t>
+        </is>
+      </c>
+      <c r="AC150" s="12" t="inlineStr">
+        <is>
+          <t>https://www.texasamconcrete.com/</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="6" t="inlineStr">
@@ -16453,6 +18055,21 @@
       <c r="X151" s="6" t="inlineStr"/>
       <c r="Y151" s="6" t="inlineStr"/>
       <c r="Z151" s="6" t="inlineStr"/>
+      <c r="AA151" s="6" t="inlineStr">
+        <is>
+          <t>(800) 539-2224</t>
+        </is>
+      </c>
+      <c r="AB151" s="6" t="inlineStr">
+        <is>
+          <t>headquarters</t>
+        </is>
+      </c>
+      <c r="AC151" s="6" t="inlineStr">
+        <is>
+          <t>https://bakerconstruction.com/</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="12" t="inlineStr">
@@ -16554,6 +18171,21 @@
       <c r="X152" s="12" t="inlineStr"/>
       <c r="Y152" s="12" t="inlineStr"/>
       <c r="Z152" s="12" t="inlineStr"/>
+      <c r="AA152" s="12" t="inlineStr">
+        <is>
+          <t>(800) 539-2224</t>
+        </is>
+      </c>
+      <c r="AB152" s="12" t="inlineStr">
+        <is>
+          <t>headquarters</t>
+        </is>
+      </c>
+      <c r="AC152" s="12" t="inlineStr">
+        <is>
+          <t>https://bakerconstruction.com/</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="6" t="inlineStr">
@@ -16655,6 +18287,21 @@
       <c r="X153" s="6" t="inlineStr"/>
       <c r="Y153" s="6" t="inlineStr"/>
       <c r="Z153" s="6" t="inlineStr"/>
+      <c r="AA153" s="6" t="inlineStr">
+        <is>
+          <t>(800) 539-2224</t>
+        </is>
+      </c>
+      <c r="AB153" s="6" t="inlineStr">
+        <is>
+          <t>headquarters</t>
+        </is>
+      </c>
+      <c r="AC153" s="6" t="inlineStr">
+        <is>
+          <t>https://bakerconstruction.com/</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="12" t="inlineStr">
@@ -16760,6 +18407,17 @@
       <c r="X154" s="12" t="inlineStr"/>
       <c r="Y154" s="12" t="inlineStr"/>
       <c r="Z154" s="12" t="inlineStr"/>
+      <c r="AA154" s="12" t="inlineStr">
+        <is>
+          <t>(813) 397-6100</t>
+        </is>
+      </c>
+      <c r="AB154" s="12" t="inlineStr"/>
+      <c r="AC154" s="12" t="inlineStr">
+        <is>
+          <t>https://leolaconstruction.com/houston/</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="6" t="inlineStr">
@@ -16871,6 +18529,21 @@
       <c r="Z155" s="6" t="inlineStr">
         <is>
           <t>2026-07-21 Construction Owners. Arch-Con Tops Out 330-Unit Artis Montrose Apartment Project  https://www.constructionowners.com/news/arch-con-reaches-topping-out-milestone-on-330-unit-artis-montrose-apartment-project</t>
+        </is>
+      </c>
+      <c r="AA155" s="6" t="inlineStr">
+        <is>
+          <t>(713) 533-1900</t>
+        </is>
+      </c>
+      <c r="AB155" s="6" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
+      </c>
+      <c r="AC155" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arch-con.com/contact-us/</t>
         </is>
       </c>
     </row>
@@ -16979,6 +18652,21 @@
       <c r="Z156" s="12" t="inlineStr">
         <is>
           <t>2026-07-21 Construction Owners. Arch-Con Tops Out 330-Unit Artis Montrose Apartment Project  https://www.constructionowners.com/news/arch-con-reaches-topping-out-milestone-on-330-unit-artis-montrose-apartment-project</t>
+        </is>
+      </c>
+      <c r="AA156" s="12" t="inlineStr">
+        <is>
+          <t>(713) 533-1900</t>
+        </is>
+      </c>
+      <c r="AB156" s="12" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
+      </c>
+      <c r="AC156" s="12" t="inlineStr">
+        <is>
+          <t>https://www.arch-con.com/contact-us/</t>
         </is>
       </c>
     </row>
@@ -17085,6 +18773,21 @@
           <t>2026-07-21 Construction Owners. Arch-Con Tops Out 330-Unit Artis Montrose Apartment Project  https://www.constructionowners.com/news/arch-con-reaches-topping-out-milestone-on-330-unit-artis-montrose-apartment-project</t>
         </is>
       </c>
+      <c r="AA157" s="6" t="inlineStr">
+        <is>
+          <t>(713) 533-1900</t>
+        </is>
+      </c>
+      <c r="AB157" s="6" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
+      </c>
+      <c r="AC157" s="6" t="inlineStr">
+        <is>
+          <t>https://www.arch-con.com/contact-us/</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="12" t="inlineStr">
@@ -17193,6 +18896,21 @@
           <t>2026-07-21 Construction Owners. Arch-Con Tops Out 330-Unit Artis Montrose Apartment Project  https://www.constructionowners.com/news/arch-con-reaches-topping-out-milestone-on-330-unit-artis-montrose-apartment-project</t>
         </is>
       </c>
+      <c r="AA158" s="12" t="inlineStr">
+        <is>
+          <t>(713) 533-1900</t>
+        </is>
+      </c>
+      <c r="AB158" s="12" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
+      </c>
+      <c r="AC158" s="12" t="inlineStr">
+        <is>
+          <t>https://www.arch-con.com/contact-us/</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="6" t="inlineStr">
@@ -17302,6 +19020,17 @@
       <c r="X159" s="6" t="inlineStr"/>
       <c r="Y159" s="6" t="inlineStr"/>
       <c r="Z159" s="6" t="inlineStr"/>
+      <c r="AA159" s="6" t="inlineStr">
+        <is>
+          <t>(281) 272-7900</t>
+        </is>
+      </c>
+      <c r="AB159" s="6" t="inlineStr"/>
+      <c r="AC159" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bcshouston.com/</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="12" t="inlineStr">
@@ -17411,6 +19140,17 @@
       <c r="X160" s="12" t="inlineStr"/>
       <c r="Y160" s="12" t="inlineStr"/>
       <c r="Z160" s="12" t="inlineStr"/>
+      <c r="AA160" s="12" t="inlineStr">
+        <is>
+          <t>(281) 272-7900</t>
+        </is>
+      </c>
+      <c r="AB160" s="12" t="inlineStr"/>
+      <c r="AC160" s="12" t="inlineStr">
+        <is>
+          <t>https://www.bcshouston.com/</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="6" t="inlineStr">
@@ -17516,6 +19256,17 @@
       <c r="X161" s="6" t="inlineStr"/>
       <c r="Y161" s="6" t="inlineStr"/>
       <c r="Z161" s="6" t="inlineStr"/>
+      <c r="AA161" s="6" t="inlineStr">
+        <is>
+          <t>(281) 272-7900</t>
+        </is>
+      </c>
+      <c r="AB161" s="6" t="inlineStr"/>
+      <c r="AC161" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bcshouston.com/</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="12" t="inlineStr">
@@ -17617,6 +19368,21 @@
       <c r="X162" s="12" t="inlineStr"/>
       <c r="Y162" s="12" t="inlineStr"/>
       <c r="Z162" s="12" t="inlineStr"/>
+      <c r="AA162" s="12" t="inlineStr">
+        <is>
+          <t>(713) 681-1100</t>
+        </is>
+      </c>
+      <c r="AB162" s="12" t="inlineStr">
+        <is>
+          <t>office</t>
+        </is>
+      </c>
+      <c r="AC162" s="12" t="inlineStr">
+        <is>
+          <t>https://www.mldeer.com/</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="6" t="inlineStr">
@@ -17718,6 +19484,21 @@
       <c r="X163" s="6" t="inlineStr"/>
       <c r="Y163" s="6" t="inlineStr"/>
       <c r="Z163" s="6" t="inlineStr"/>
+      <c r="AA163" s="6" t="inlineStr">
+        <is>
+          <t>(713) 681-1100</t>
+        </is>
+      </c>
+      <c r="AB163" s="6" t="inlineStr">
+        <is>
+          <t>office</t>
+        </is>
+      </c>
+      <c r="AC163" s="6" t="inlineStr">
+        <is>
+          <t>https://www.mldeer.com/</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="12" t="inlineStr">
@@ -17823,6 +19604,21 @@
       <c r="X164" s="12" t="inlineStr"/>
       <c r="Y164" s="12" t="inlineStr"/>
       <c r="Z164" s="12" t="inlineStr"/>
+      <c r="AA164" s="12" t="inlineStr">
+        <is>
+          <t>(713) 681-1100</t>
+        </is>
+      </c>
+      <c r="AB164" s="12" t="inlineStr">
+        <is>
+          <t>office</t>
+        </is>
+      </c>
+      <c r="AC164" s="12" t="inlineStr">
+        <is>
+          <t>https://www.mldeer.com/</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="6" t="inlineStr">
@@ -17923,6 +19719,17 @@
       <c r="X165" s="6" t="inlineStr"/>
       <c r="Y165" s="6" t="inlineStr"/>
       <c r="Z165" s="6" t="inlineStr"/>
+      <c r="AA165" s="6" t="inlineStr">
+        <is>
+          <t>(713) 477-6660</t>
+        </is>
+      </c>
+      <c r="AB165" s="6" t="inlineStr"/>
+      <c r="AC165" s="6" t="inlineStr">
+        <is>
+          <t>https://tandtconstruction.com/</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="12" t="inlineStr">
@@ -18023,6 +19830,17 @@
       <c r="X166" s="12" t="inlineStr"/>
       <c r="Y166" s="12" t="inlineStr"/>
       <c r="Z166" s="12" t="inlineStr"/>
+      <c r="AA166" s="12" t="inlineStr">
+        <is>
+          <t>(713) 477-6660</t>
+        </is>
+      </c>
+      <c r="AB166" s="12" t="inlineStr"/>
+      <c r="AC166" s="12" t="inlineStr">
+        <is>
+          <t>https://tandtconstruction.com/</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="6" t="inlineStr">
@@ -18123,6 +19941,17 @@
       <c r="X167" s="6" t="inlineStr"/>
       <c r="Y167" s="6" t="inlineStr"/>
       <c r="Z167" s="6" t="inlineStr"/>
+      <c r="AA167" s="6" t="inlineStr">
+        <is>
+          <t>(713) 477-6660</t>
+        </is>
+      </c>
+      <c r="AB167" s="6" t="inlineStr"/>
+      <c r="AC167" s="6" t="inlineStr">
+        <is>
+          <t>https://tandtconstruction.com/</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="12" t="inlineStr">
@@ -18223,6 +20052,17 @@
       <c r="X168" s="12" t="inlineStr"/>
       <c r="Y168" s="12" t="inlineStr"/>
       <c r="Z168" s="12" t="inlineStr"/>
+      <c r="AA168" s="12" t="inlineStr">
+        <is>
+          <t>(281) 227-8225</t>
+        </is>
+      </c>
+      <c r="AB168" s="12" t="inlineStr"/>
+      <c r="AC168" s="12" t="inlineStr">
+        <is>
+          <t>https://andradeconstructioncompanies.com/</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="6" t="inlineStr">
@@ -18328,6 +20168,17 @@
       <c r="X169" s="6" t="inlineStr"/>
       <c r="Y169" s="6" t="inlineStr"/>
       <c r="Z169" s="6" t="inlineStr"/>
+      <c r="AA169" s="6" t="inlineStr">
+        <is>
+          <t>(281) 227-8225</t>
+        </is>
+      </c>
+      <c r="AB169" s="6" t="inlineStr"/>
+      <c r="AC169" s="6" t="inlineStr">
+        <is>
+          <t>https://andradeconstructioncompanies.com/</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="12" t="inlineStr">
@@ -18433,6 +20284,17 @@
       <c r="X170" s="12" t="inlineStr"/>
       <c r="Y170" s="12" t="inlineStr"/>
       <c r="Z170" s="12" t="inlineStr"/>
+      <c r="AA170" s="12" t="inlineStr">
+        <is>
+          <t>(281) 227-8225</t>
+        </is>
+      </c>
+      <c r="AB170" s="12" t="inlineStr"/>
+      <c r="AC170" s="12" t="inlineStr">
+        <is>
+          <t>https://andradeconstructioncompanies.com/</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="6" t="inlineStr">
@@ -18542,6 +20404,21 @@
       <c r="X171" s="6" t="inlineStr"/>
       <c r="Y171" s="6" t="inlineStr"/>
       <c r="Z171" s="6" t="inlineStr"/>
+      <c r="AA171" s="6" t="inlineStr">
+        <is>
+          <t>(281) 313-5055</t>
+        </is>
+      </c>
+      <c r="AB171" s="6" t="inlineStr">
+        <is>
+          <t>Houston office</t>
+        </is>
+      </c>
+      <c r="AC171" s="6" t="inlineStr">
+        <is>
+          <t>https://burtonconstruction.com/</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="12" t="inlineStr">
@@ -18647,6 +20524,21 @@
       <c r="X172" s="12" t="inlineStr"/>
       <c r="Y172" s="12" t="inlineStr"/>
       <c r="Z172" s="12" t="inlineStr"/>
+      <c r="AA172" s="12" t="inlineStr">
+        <is>
+          <t>(281) 313-5055</t>
+        </is>
+      </c>
+      <c r="AB172" s="12" t="inlineStr">
+        <is>
+          <t>Houston office</t>
+        </is>
+      </c>
+      <c r="AC172" s="12" t="inlineStr">
+        <is>
+          <t>https://burtonconstruction.com/</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="6" t="inlineStr">
@@ -18752,6 +20644,17 @@
       <c r="X173" s="6" t="inlineStr"/>
       <c r="Y173" s="6" t="inlineStr"/>
       <c r="Z173" s="6" t="inlineStr"/>
+      <c r="AA173" s="6" t="inlineStr">
+        <is>
+          <t>(832) 930-7739</t>
+        </is>
+      </c>
+      <c r="AB173" s="6" t="inlineStr"/>
+      <c r="AC173" s="6" t="inlineStr">
+        <is>
+          <t>https://htxconcrete.com/</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="12" t="inlineStr">
@@ -18857,6 +20760,17 @@
       <c r="X174" s="12" t="inlineStr"/>
       <c r="Y174" s="12" t="inlineStr"/>
       <c r="Z174" s="12" t="inlineStr"/>
+      <c r="AA174" s="12" t="inlineStr">
+        <is>
+          <t>(832) 930-7739</t>
+        </is>
+      </c>
+      <c r="AB174" s="12" t="inlineStr"/>
+      <c r="AC174" s="12" t="inlineStr">
+        <is>
+          <t>https://htxconcrete.com/</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="6" t="inlineStr">
@@ -18961,6 +20875,17 @@
       <c r="X175" s="6" t="inlineStr"/>
       <c r="Y175" s="6" t="inlineStr"/>
       <c r="Z175" s="6" t="inlineStr"/>
+      <c r="AA175" s="6" t="inlineStr">
+        <is>
+          <t>(713) 482-7712</t>
+        </is>
+      </c>
+      <c r="AB175" s="6" t="inlineStr"/>
+      <c r="AC175" s="6" t="inlineStr">
+        <is>
+          <t>https://silverspurconcrete.com/</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="12" t="inlineStr">
@@ -19074,6 +20999,17 @@
         </is>
       </c>
       <c r="Z176" s="12" t="inlineStr"/>
+      <c r="AA176" s="12" t="inlineStr">
+        <is>
+          <t>(832) 214-5000</t>
+        </is>
+      </c>
+      <c r="AB176" s="12" t="inlineStr"/>
+      <c r="AC176" s="12" t="inlineStr">
+        <is>
+          <t>https://www.tritenre.com/</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="6" t="inlineStr">
@@ -19187,6 +21123,17 @@
         </is>
       </c>
       <c r="Z177" s="6" t="inlineStr"/>
+      <c r="AA177" s="6" t="inlineStr">
+        <is>
+          <t>(832) 214-5000</t>
+        </is>
+      </c>
+      <c r="AB177" s="6" t="inlineStr"/>
+      <c r="AC177" s="6" t="inlineStr">
+        <is>
+          <t>https://www.tritenre.com/</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="12" t="inlineStr">
@@ -19300,6 +21247,17 @@
         </is>
       </c>
       <c r="Z178" s="12" t="inlineStr"/>
+      <c r="AA178" s="12" t="inlineStr">
+        <is>
+          <t>(832) 214-5000</t>
+        </is>
+      </c>
+      <c r="AB178" s="12" t="inlineStr"/>
+      <c r="AC178" s="12" t="inlineStr">
+        <is>
+          <t>https://www.tritenre.com/</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="6" t="inlineStr">
@@ -19416,6 +21374,17 @@
         </is>
       </c>
       <c r="Z179" s="6" t="inlineStr"/>
+      <c r="AA179" s="6" t="inlineStr">
+        <is>
+          <t>(832) 214-5000</t>
+        </is>
+      </c>
+      <c r="AB179" s="6" t="inlineStr"/>
+      <c r="AC179" s="6" t="inlineStr">
+        <is>
+          <t>https://www.tritenre.com/</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="12" t="inlineStr">
@@ -19525,6 +21494,17 @@
         </is>
       </c>
       <c r="Z180" s="12" t="inlineStr"/>
+      <c r="AA180" s="12" t="inlineStr">
+        <is>
+          <t>(713) 783-4444</t>
+        </is>
+      </c>
+      <c r="AB180" s="12" t="inlineStr"/>
+      <c r="AC180" s="12" t="inlineStr">
+        <is>
+          <t>https://www.radomcapital.com/</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="6" t="inlineStr">
@@ -19638,6 +21618,17 @@
         </is>
       </c>
       <c r="Z181" s="6" t="inlineStr"/>
+      <c r="AA181" s="6" t="inlineStr">
+        <is>
+          <t>(713) 783-4444</t>
+        </is>
+      </c>
+      <c r="AB181" s="6" t="inlineStr"/>
+      <c r="AC181" s="6" t="inlineStr">
+        <is>
+          <t>https://www.radomcapital.com/</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="12" t="inlineStr">
@@ -19751,6 +21742,17 @@
         </is>
       </c>
       <c r="Z182" s="12" t="inlineStr"/>
+      <c r="AA182" s="12" t="inlineStr">
+        <is>
+          <t>(713) 783-4444</t>
+        </is>
+      </c>
+      <c r="AB182" s="12" t="inlineStr"/>
+      <c r="AC182" s="12" t="inlineStr">
+        <is>
+          <t>https://www.radomcapital.com/</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="6" t="inlineStr">
@@ -19863,6 +21865,21 @@
         </is>
       </c>
       <c r="Z183" s="6" t="inlineStr"/>
+      <c r="AA183" s="6" t="inlineStr">
+        <is>
+          <t>(713) 993-9823</t>
+        </is>
+      </c>
+      <c r="AB183" s="6" t="inlineStr">
+        <is>
+          <t>office</t>
+        </is>
+      </c>
+      <c r="AC183" s="6" t="inlineStr">
+        <is>
+          <t>https://www.dealco.net/</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="12" t="inlineStr">
@@ -19979,6 +21996,17 @@
         </is>
       </c>
       <c r="Z184" s="12" t="inlineStr"/>
+      <c r="AA184" s="12" t="inlineStr">
+        <is>
+          <t>(713) 224-1663</t>
+        </is>
+      </c>
+      <c r="AB184" s="12" t="inlineStr"/>
+      <c r="AC184" s="12" t="inlineStr">
+        <is>
+          <t>https://cameronmanagement.com/contact</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="6" t="inlineStr">
@@ -20095,6 +22123,17 @@
         </is>
       </c>
       <c r="Z185" s="6" t="inlineStr"/>
+      <c r="AA185" s="6" t="inlineStr">
+        <is>
+          <t>(713) 224-1663</t>
+        </is>
+      </c>
+      <c r="AB185" s="6" t="inlineStr"/>
+      <c r="AC185" s="6" t="inlineStr">
+        <is>
+          <t>https://cameronmanagement.com/contact</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="12" t="inlineStr">
@@ -20203,6 +22242,21 @@
       <c r="X186" s="12" t="inlineStr"/>
       <c r="Y186" s="12" t="inlineStr"/>
       <c r="Z186" s="12" t="inlineStr"/>
+      <c r="AA186" s="12" t="inlineStr">
+        <is>
+          <t>(713) 937-1121</t>
+        </is>
+      </c>
+      <c r="AB186" s="12" t="inlineStr">
+        <is>
+          <t>Houston office, corporate</t>
+        </is>
+      </c>
+      <c r="AC186" s="12" t="inlineStr">
+        <is>
+          <t>https://partnersinbuilding.com/</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="6" t="inlineStr">
@@ -20312,6 +22366,21 @@
       <c r="X187" s="6" t="inlineStr"/>
       <c r="Y187" s="6" t="inlineStr"/>
       <c r="Z187" s="6" t="inlineStr"/>
+      <c r="AA187" s="6" t="inlineStr">
+        <is>
+          <t>(713) 937-1121</t>
+        </is>
+      </c>
+      <c r="AB187" s="6" t="inlineStr">
+        <is>
+          <t>Houston office, corporate</t>
+        </is>
+      </c>
+      <c r="AC187" s="6" t="inlineStr">
+        <is>
+          <t>https://partnersinbuilding.com/</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="12" t="inlineStr">
@@ -20420,6 +22489,21 @@
       <c r="X188" s="12" t="inlineStr"/>
       <c r="Y188" s="12" t="inlineStr"/>
       <c r="Z188" s="12" t="inlineStr"/>
+      <c r="AA188" s="12" t="inlineStr">
+        <is>
+          <t>(713) 937-1121</t>
+        </is>
+      </c>
+      <c r="AB188" s="12" t="inlineStr">
+        <is>
+          <t>Houston office, corporate</t>
+        </is>
+      </c>
+      <c r="AC188" s="12" t="inlineStr">
+        <is>
+          <t>https://partnersinbuilding.com/</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="6" t="inlineStr">
@@ -20525,6 +22609,17 @@
       <c r="X189" s="6" t="inlineStr"/>
       <c r="Y189" s="6" t="inlineStr"/>
       <c r="Z189" s="6" t="inlineStr"/>
+      <c r="AA189" s="6" t="inlineStr">
+        <is>
+          <t>(713) 541-0066</t>
+        </is>
+      </c>
+      <c r="AB189" s="6" t="inlineStr"/>
+      <c r="AC189" s="6" t="inlineStr">
+        <is>
+          <t>https://braunenterprises.com/</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="12" t="inlineStr">
@@ -20641,6 +22736,17 @@
         </is>
       </c>
       <c r="Z190" s="12" t="inlineStr"/>
+      <c r="AA190" s="12" t="inlineStr">
+        <is>
+          <t>(713) 629-5200</t>
+        </is>
+      </c>
+      <c r="AB190" s="12" t="inlineStr"/>
+      <c r="AC190" s="12" t="inlineStr">
+        <is>
+          <t>https://www.midway.team/contact</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="6" t="inlineStr">
@@ -20754,6 +22860,17 @@
         </is>
       </c>
       <c r="Z191" s="6" t="inlineStr"/>
+      <c r="AA191" s="6" t="inlineStr">
+        <is>
+          <t>(713) 629-5200</t>
+        </is>
+      </c>
+      <c r="AB191" s="6" t="inlineStr"/>
+      <c r="AC191" s="6" t="inlineStr">
+        <is>
+          <t>https://www.midway.team/contact</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="12" t="inlineStr">
@@ -20866,6 +22983,17 @@
         </is>
       </c>
       <c r="Z192" s="12" t="inlineStr"/>
+      <c r="AA192" s="12" t="inlineStr">
+        <is>
+          <t>(713) 629-5200</t>
+        </is>
+      </c>
+      <c r="AB192" s="12" t="inlineStr"/>
+      <c r="AC192" s="12" t="inlineStr">
+        <is>
+          <t>https://www.midway.team/contact</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="6" t="inlineStr">
@@ -20983,6 +23111,17 @@
         </is>
       </c>
       <c r="Z193" s="6" t="inlineStr"/>
+      <c r="AA193" s="6" t="inlineStr">
+        <is>
+          <t>(713) 629-5200</t>
+        </is>
+      </c>
+      <c r="AB193" s="6" t="inlineStr"/>
+      <c r="AC193" s="6" t="inlineStr">
+        <is>
+          <t>https://www.midway.team/contact</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="12" t="inlineStr">
@@ -21092,6 +23231,17 @@
         </is>
       </c>
       <c r="Z194" s="12" t="inlineStr"/>
+      <c r="AA194" s="12" t="inlineStr">
+        <is>
+          <t>(713) 629-5200</t>
+        </is>
+      </c>
+      <c r="AB194" s="12" t="inlineStr"/>
+      <c r="AC194" s="12" t="inlineStr">
+        <is>
+          <t>https://www.midway.team/contact</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="6" t="inlineStr">
@@ -21196,6 +23346,17 @@
       <c r="X195" s="6" t="inlineStr"/>
       <c r="Y195" s="6" t="inlineStr"/>
       <c r="Z195" s="6" t="inlineStr"/>
+      <c r="AA195" s="6" t="inlineStr">
+        <is>
+          <t>(713) 804-4000</t>
+        </is>
+      </c>
+      <c r="AB195" s="6" t="inlineStr"/>
+      <c r="AC195" s="6" t="inlineStr">
+        <is>
+          <t>https://www.pagewood.com/</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="12" t="inlineStr">
@@ -21305,6 +23466,17 @@
       <c r="X196" s="12" t="inlineStr"/>
       <c r="Y196" s="12" t="inlineStr"/>
       <c r="Z196" s="12" t="inlineStr"/>
+      <c r="AA196" s="12" t="inlineStr">
+        <is>
+          <t>(713) 804-4000</t>
+        </is>
+      </c>
+      <c r="AB196" s="12" t="inlineStr"/>
+      <c r="AC196" s="12" t="inlineStr">
+        <is>
+          <t>https://www.pagewood.com/</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="6" t="inlineStr">
@@ -21409,6 +23581,17 @@
       <c r="X197" s="6" t="inlineStr"/>
       <c r="Y197" s="6" t="inlineStr"/>
       <c r="Z197" s="6" t="inlineStr"/>
+      <c r="AA197" s="6" t="inlineStr">
+        <is>
+          <t>(713) 804-4000</t>
+        </is>
+      </c>
+      <c r="AB197" s="6" t="inlineStr"/>
+      <c r="AC197" s="6" t="inlineStr">
+        <is>
+          <t>https://www.pagewood.com/</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="12" t="inlineStr">
@@ -21514,6 +23697,17 @@
       <c r="X198" s="12" t="inlineStr"/>
       <c r="Y198" s="12" t="inlineStr"/>
       <c r="Z198" s="12" t="inlineStr"/>
+      <c r="AA198" s="12" t="inlineStr">
+        <is>
+          <t>(713) 821-7052</t>
+        </is>
+      </c>
+      <c r="AB198" s="12" t="inlineStr"/>
+      <c r="AC198" s="12" t="inlineStr">
+        <is>
+          <t>https://www.conceptneighborhood.com/</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="6" t="inlineStr">
@@ -21619,6 +23813,17 @@
       <c r="X199" s="6" t="inlineStr"/>
       <c r="Y199" s="6" t="inlineStr"/>
       <c r="Z199" s="6" t="inlineStr"/>
+      <c r="AA199" s="6" t="inlineStr">
+        <is>
+          <t>(713) 821-7052</t>
+        </is>
+      </c>
+      <c r="AB199" s="6" t="inlineStr"/>
+      <c r="AC199" s="6" t="inlineStr">
+        <is>
+          <t>https://www.conceptneighborhood.com/</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="12" t="inlineStr">
@@ -21724,6 +23929,17 @@
       <c r="X200" s="12" t="inlineStr"/>
       <c r="Y200" s="12" t="inlineStr"/>
       <c r="Z200" s="12" t="inlineStr"/>
+      <c r="AA200" s="12" t="inlineStr">
+        <is>
+          <t>(713) 821-7052</t>
+        </is>
+      </c>
+      <c r="AB200" s="12" t="inlineStr"/>
+      <c r="AC200" s="12" t="inlineStr">
+        <is>
+          <t>https://www.conceptneighborhood.com/</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="6" t="inlineStr">
@@ -21829,6 +24045,17 @@
       <c r="X201" s="6" t="inlineStr"/>
       <c r="Y201" s="6" t="inlineStr"/>
       <c r="Z201" s="6" t="inlineStr"/>
+      <c r="AA201" s="6" t="inlineStr">
+        <is>
+          <t>(713) 821-7052</t>
+        </is>
+      </c>
+      <c r="AB201" s="6" t="inlineStr"/>
+      <c r="AC201" s="6" t="inlineStr">
+        <is>
+          <t>https://www.conceptneighborhood.com/</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="12" t="inlineStr">
@@ -21938,6 +24165,9 @@
       <c r="X202" s="12" t="inlineStr"/>
       <c r="Y202" s="12" t="inlineStr"/>
       <c r="Z202" s="12" t="inlineStr"/>
+      <c r="AA202" s="12" t="inlineStr"/>
+      <c r="AB202" s="12" t="inlineStr"/>
+      <c r="AC202" s="12" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="6" t="inlineStr">
@@ -22042,6 +24272,13 @@
       <c r="X203" s="6" t="inlineStr"/>
       <c r="Y203" s="6" t="inlineStr"/>
       <c r="Z203" s="6" t="inlineStr"/>
+      <c r="AA203" s="6" t="inlineStr"/>
+      <c r="AB203" s="6" t="inlineStr"/>
+      <c r="AC203" s="6" t="inlineStr">
+        <is>
+          <t>https://www.drhorton.com/contact-us-page</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="12" t="inlineStr">
@@ -22146,6 +24383,13 @@
       <c r="X204" s="12" t="inlineStr"/>
       <c r="Y204" s="12" t="inlineStr"/>
       <c r="Z204" s="12" t="inlineStr"/>
+      <c r="AA204" s="12" t="inlineStr"/>
+      <c r="AB204" s="12" t="inlineStr"/>
+      <c r="AC204" s="12" t="inlineStr">
+        <is>
+          <t>https://www.drhorton.com/contact-us-page</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="6" t="inlineStr">
@@ -22258,6 +24502,13 @@
       <c r="X205" s="6" t="inlineStr"/>
       <c r="Y205" s="6" t="inlineStr"/>
       <c r="Z205" s="6" t="inlineStr"/>
+      <c r="AA205" s="6" t="inlineStr"/>
+      <c r="AB205" s="6" t="inlineStr"/>
+      <c r="AC205" s="6" t="inlineStr">
+        <is>
+          <t>https://www.drhorton.com/contact-us-page</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="12" t="inlineStr">
@@ -22362,6 +24613,21 @@
       <c r="X206" s="12" t="inlineStr"/>
       <c r="Y206" s="12" t="inlineStr"/>
       <c r="Z206" s="12" t="inlineStr"/>
+      <c r="AA206" s="12" t="inlineStr">
+        <is>
+          <t>(844) 767-2713</t>
+        </is>
+      </c>
+      <c r="AB206" s="12" t="inlineStr">
+        <is>
+          <t>main office, Baton Rouge</t>
+        </is>
+      </c>
+      <c r="AC206" s="12" t="inlineStr">
+        <is>
+          <t>https://www.dsldhomes.com/</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="6" t="inlineStr">
@@ -22475,6 +24741,17 @@
         </is>
       </c>
       <c r="Z207" s="6" t="inlineStr"/>
+      <c r="AA207" s="6" t="inlineStr">
+        <is>
+          <t>(844) 777-3717</t>
+        </is>
+      </c>
+      <c r="AB207" s="6" t="inlineStr"/>
+      <c r="AC207" s="6" t="inlineStr">
+        <is>
+          <t>https://www.davidweekleyhomes.com/</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="12" t="inlineStr">
@@ -22591,6 +24868,17 @@
         </is>
       </c>
       <c r="Z208" s="12" t="inlineStr"/>
+      <c r="AA208" s="12" t="inlineStr">
+        <is>
+          <t>(844) 777-3717</t>
+        </is>
+      </c>
+      <c r="AB208" s="12" t="inlineStr"/>
+      <c r="AC208" s="12" t="inlineStr">
+        <is>
+          <t>https://www.davidweekleyhomes.com/</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="6" t="inlineStr">
@@ -22707,6 +24995,17 @@
         </is>
       </c>
       <c r="Z209" s="6" t="inlineStr"/>
+      <c r="AA209" s="6" t="inlineStr">
+        <is>
+          <t>(844) 777-3717</t>
+        </is>
+      </c>
+      <c r="AB209" s="6" t="inlineStr"/>
+      <c r="AC209" s="6" t="inlineStr">
+        <is>
+          <t>https://www.davidweekleyhomes.com/</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="12" t="inlineStr">
@@ -22828,6 +25127,17 @@
         </is>
       </c>
       <c r="Z210" s="12" t="inlineStr"/>
+      <c r="AA210" s="12" t="inlineStr">
+        <is>
+          <t>(844) 777-3717</t>
+        </is>
+      </c>
+      <c r="AB210" s="12" t="inlineStr"/>
+      <c r="AC210" s="12" t="inlineStr">
+        <is>
+          <t>https://www.davidweekleyhomes.com/</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="6" t="inlineStr">
@@ -22937,6 +25247,17 @@
         </is>
       </c>
       <c r="Z211" s="6" t="inlineStr"/>
+      <c r="AA211" s="6" t="inlineStr">
+        <is>
+          <t>(844) 777-3717</t>
+        </is>
+      </c>
+      <c r="AB211" s="6" t="inlineStr"/>
+      <c r="AC211" s="6" t="inlineStr">
+        <is>
+          <t>https://www.davidweekleyhomes.com/</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="12" t="inlineStr">
@@ -23049,6 +25370,9 @@
         </is>
       </c>
       <c r="Z212" s="12" t="inlineStr"/>
+      <c r="AA212" s="12" t="inlineStr"/>
+      <c r="AB212" s="12" t="inlineStr"/>
+      <c r="AC212" s="12" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="6" t="inlineStr">
@@ -23161,6 +25485,9 @@
         </is>
       </c>
       <c r="Z213" s="6" t="inlineStr"/>
+      <c r="AA213" s="6" t="inlineStr"/>
+      <c r="AB213" s="6" t="inlineStr"/>
+      <c r="AC213" s="6" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="12" t="inlineStr">
@@ -23273,6 +25600,9 @@
         </is>
       </c>
       <c r="Z214" s="12" t="inlineStr"/>
+      <c r="AA214" s="12" t="inlineStr"/>
+      <c r="AB214" s="12" t="inlineStr"/>
+      <c r="AC214" s="12" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="6" t="inlineStr">
@@ -23390,6 +25720,9 @@
         </is>
       </c>
       <c r="Z215" s="6" t="inlineStr"/>
+      <c r="AA215" s="6" t="inlineStr"/>
+      <c r="AB215" s="6" t="inlineStr"/>
+      <c r="AC215" s="6" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="12" t="inlineStr">
@@ -23507,6 +25840,9 @@
         </is>
       </c>
       <c r="Z216" s="12" t="inlineStr"/>
+      <c r="AA216" s="12" t="inlineStr"/>
+      <c r="AB216" s="12" t="inlineStr"/>
+      <c r="AC216" s="12" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="6" t="inlineStr">
@@ -23623,6 +25959,9 @@
         </is>
       </c>
       <c r="Z217" s="6" t="inlineStr"/>
+      <c r="AA217" s="6" t="inlineStr"/>
+      <c r="AB217" s="6" t="inlineStr"/>
+      <c r="AC217" s="6" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="12" t="inlineStr">
@@ -23739,6 +26078,9 @@
         </is>
       </c>
       <c r="Z218" s="12" t="inlineStr"/>
+      <c r="AA218" s="12" t="inlineStr"/>
+      <c r="AB218" s="12" t="inlineStr"/>
+      <c r="AC218" s="12" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="6" t="inlineStr">
@@ -23856,6 +26198,9 @@
         </is>
       </c>
       <c r="Z219" s="6" t="inlineStr"/>
+      <c r="AA219" s="6" t="inlineStr"/>
+      <c r="AB219" s="6" t="inlineStr"/>
+      <c r="AC219" s="6" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="12" t="inlineStr">
@@ -23969,6 +26314,9 @@
         </is>
       </c>
       <c r="Z220" s="12" t="inlineStr"/>
+      <c r="AA220" s="12" t="inlineStr"/>
+      <c r="AB220" s="12" t="inlineStr"/>
+      <c r="AC220" s="12" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="6" t="inlineStr">
@@ -24085,6 +26433,13 @@
         </is>
       </c>
       <c r="Z221" s="6" t="inlineStr"/>
+      <c r="AA221" s="6" t="inlineStr"/>
+      <c r="AB221" s="6" t="inlineStr"/>
+      <c r="AC221" s="6" t="inlineStr">
+        <is>
+          <t>https://www.taylormorrison.com/contact-us</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="12" t="inlineStr">
@@ -24198,6 +26553,13 @@
         </is>
       </c>
       <c r="Z222" s="12" t="inlineStr"/>
+      <c r="AA222" s="12" t="inlineStr"/>
+      <c r="AB222" s="12" t="inlineStr"/>
+      <c r="AC222" s="12" t="inlineStr">
+        <is>
+          <t>https://www.taylormorrison.com/contact-us</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="6" t="inlineStr">
@@ -24310,6 +26672,21 @@
         </is>
       </c>
       <c r="Z223" s="6" t="inlineStr"/>
+      <c r="AA223" s="6" t="inlineStr">
+        <is>
+          <t>(770) 998-9663</t>
+        </is>
+      </c>
+      <c r="AB223" s="6" t="inlineStr">
+        <is>
+          <t>corporate headquarters, Alpharetta, Georgia</t>
+        </is>
+      </c>
+      <c r="AC223" s="6" t="inlineStr">
+        <is>
+          <t>https://www.ashtonwoods.com/corporate-info</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="12" t="inlineStr">
@@ -24426,6 +26803,21 @@
         </is>
       </c>
       <c r="Z224" s="12" t="inlineStr"/>
+      <c r="AA224" s="12" t="inlineStr">
+        <is>
+          <t>(770) 998-9663</t>
+        </is>
+      </c>
+      <c r="AB224" s="12" t="inlineStr">
+        <is>
+          <t>corporate headquarters, Alpharetta, Georgia</t>
+        </is>
+      </c>
+      <c r="AC224" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ashtonwoods.com/corporate-info</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="6" t="inlineStr">
@@ -24538,6 +26930,21 @@
         </is>
       </c>
       <c r="Z225" s="6" t="inlineStr"/>
+      <c r="AA225" s="6" t="inlineStr">
+        <is>
+          <t>(770) 998-9663</t>
+        </is>
+      </c>
+      <c r="AB225" s="6" t="inlineStr">
+        <is>
+          <t>corporate headquarters, Alpharetta, Georgia</t>
+        </is>
+      </c>
+      <c r="AC225" s="6" t="inlineStr">
+        <is>
+          <t>https://www.ashtonwoods.com/corporate-info</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="12" t="inlineStr">
@@ -24651,6 +27058,21 @@
         </is>
       </c>
       <c r="Z226" s="12" t="inlineStr"/>
+      <c r="AA226" s="12" t="inlineStr">
+        <is>
+          <t>(770) 998-9663</t>
+        </is>
+      </c>
+      <c r="AB226" s="12" t="inlineStr">
+        <is>
+          <t>corporate headquarters, Alpharetta, Georgia</t>
+        </is>
+      </c>
+      <c r="AC226" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ashtonwoods.com/corporate-info</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="6" t="inlineStr">
@@ -24764,6 +27186,21 @@
         </is>
       </c>
       <c r="Z227" s="6" t="inlineStr"/>
+      <c r="AA227" s="6" t="inlineStr">
+        <is>
+          <t>(770) 998-9663</t>
+        </is>
+      </c>
+      <c r="AB227" s="6" t="inlineStr">
+        <is>
+          <t>corporate headquarters, Alpharetta, Georgia</t>
+        </is>
+      </c>
+      <c r="AC227" s="6" t="inlineStr">
+        <is>
+          <t>https://www.ashtonwoods.com/corporate-info</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="12" t="inlineStr">
@@ -24880,6 +27317,17 @@
         </is>
       </c>
       <c r="Z228" s="12" t="inlineStr"/>
+      <c r="AA228" s="12" t="inlineStr">
+        <is>
+          <t>(800) 247-3779</t>
+        </is>
+      </c>
+      <c r="AB228" s="12" t="inlineStr"/>
+      <c r="AC228" s="12" t="inlineStr">
+        <is>
+          <t>https://www.perryhomes.com/contact-us</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="6" t="inlineStr">
@@ -24992,6 +27440,17 @@
         </is>
       </c>
       <c r="Z229" s="6" t="inlineStr"/>
+      <c r="AA229" s="6" t="inlineStr">
+        <is>
+          <t>(800) 247-3779</t>
+        </is>
+      </c>
+      <c r="AB229" s="6" t="inlineStr"/>
+      <c r="AC229" s="6" t="inlineStr">
+        <is>
+          <t>https://www.perryhomes.com/contact-us</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="12" t="inlineStr">
@@ -25108,6 +27567,21 @@
         </is>
       </c>
       <c r="Z230" s="12" t="inlineStr"/>
+      <c r="AA230" s="12" t="inlineStr">
+        <is>
+          <t>(281) 201-6961</t>
+        </is>
+      </c>
+      <c r="AB230" s="12" t="inlineStr">
+        <is>
+          <t>Houston office, published by DRB Homes</t>
+        </is>
+      </c>
+      <c r="AC230" s="12" t="inlineStr">
+        <is>
+          <t>https://www.drbhomes.com/drbhomes/contact/contact-us</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="6" t="inlineStr">
@@ -25229,6 +27703,21 @@
         </is>
       </c>
       <c r="Z231" s="6" t="inlineStr"/>
+      <c r="AA231" s="6" t="inlineStr">
+        <is>
+          <t>(281) 201-6961</t>
+        </is>
+      </c>
+      <c r="AB231" s="6" t="inlineStr">
+        <is>
+          <t>Houston office, published by DRB Homes</t>
+        </is>
+      </c>
+      <c r="AC231" s="6" t="inlineStr">
+        <is>
+          <t>https://www.drbhomes.com/drbhomes/contact/contact-us</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="12" t="inlineStr">
@@ -25341,6 +27830,17 @@
         </is>
       </c>
       <c r="Z232" s="12" t="inlineStr"/>
+      <c r="AA232" s="12" t="inlineStr">
+        <is>
+          <t>(281) 929-7700</t>
+        </is>
+      </c>
+      <c r="AB232" s="12" t="inlineStr"/>
+      <c r="AC232" s="12" t="inlineStr">
+        <is>
+          <t>https://www.howardhughes.com/contact/</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="6" t="inlineStr">
@@ -25453,6 +27953,17 @@
         </is>
       </c>
       <c r="Z233" s="6" t="inlineStr"/>
+      <c r="AA233" s="6" t="inlineStr">
+        <is>
+          <t>(281) 929-7700</t>
+        </is>
+      </c>
+      <c r="AB233" s="6" t="inlineStr"/>
+      <c r="AC233" s="6" t="inlineStr">
+        <is>
+          <t>https://www.howardhughes.com/contact/</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="12" t="inlineStr">
@@ -25565,6 +28076,17 @@
         </is>
       </c>
       <c r="Z234" s="12" t="inlineStr"/>
+      <c r="AA234" s="12" t="inlineStr">
+        <is>
+          <t>(281) 929-7700</t>
+        </is>
+      </c>
+      <c r="AB234" s="12" t="inlineStr"/>
+      <c r="AC234" s="12" t="inlineStr">
+        <is>
+          <t>https://www.howardhughes.com/contact/</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="6" t="inlineStr">
@@ -25678,6 +28200,17 @@
         </is>
       </c>
       <c r="Z235" s="6" t="inlineStr"/>
+      <c r="AA235" s="6" t="inlineStr">
+        <is>
+          <t>(281) 929-7700</t>
+        </is>
+      </c>
+      <c r="AB235" s="6" t="inlineStr"/>
+      <c r="AC235" s="6" t="inlineStr">
+        <is>
+          <t>https://www.howardhughes.com/contact/</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="12" t="inlineStr">
@@ -25782,6 +28315,21 @@
       <c r="X236" s="12" t="inlineStr"/>
       <c r="Y236" s="12" t="inlineStr"/>
       <c r="Z236" s="12" t="inlineStr"/>
+      <c r="AA236" s="12" t="inlineStr">
+        <is>
+          <t>(214) 449-0914</t>
+        </is>
+      </c>
+      <c r="AB236" s="12" t="inlineStr">
+        <is>
+          <t>Dallas office</t>
+        </is>
+      </c>
+      <c r="AC236" s="12" t="inlineStr">
+        <is>
+          <t>https://www.hillwoodcommunities.com/</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="6" t="inlineStr">
@@ -25890,6 +28438,21 @@
       <c r="X237" s="6" t="inlineStr"/>
       <c r="Y237" s="6" t="inlineStr"/>
       <c r="Z237" s="6" t="inlineStr"/>
+      <c r="AA237" s="6" t="inlineStr">
+        <is>
+          <t>(214) 449-0914</t>
+        </is>
+      </c>
+      <c r="AB237" s="6" t="inlineStr">
+        <is>
+          <t>Dallas office</t>
+        </is>
+      </c>
+      <c r="AC237" s="6" t="inlineStr">
+        <is>
+          <t>https://www.hillwoodcommunities.com/</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="12" t="inlineStr">
@@ -25994,6 +28557,21 @@
       <c r="X238" s="12" t="inlineStr"/>
       <c r="Y238" s="12" t="inlineStr"/>
       <c r="Z238" s="12" t="inlineStr"/>
+      <c r="AA238" s="12" t="inlineStr">
+        <is>
+          <t>(214) 449-0914</t>
+        </is>
+      </c>
+      <c r="AB238" s="12" t="inlineStr">
+        <is>
+          <t>Dallas office</t>
+        </is>
+      </c>
+      <c r="AC238" s="12" t="inlineStr">
+        <is>
+          <t>https://www.hillwoodcommunities.com/</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="6" t="inlineStr">
@@ -26098,6 +28676,21 @@
       <c r="X239" s="6" t="inlineStr"/>
       <c r="Y239" s="6" t="inlineStr"/>
       <c r="Z239" s="6" t="inlineStr"/>
+      <c r="AA239" s="6" t="inlineStr">
+        <is>
+          <t>(214) 449-0914</t>
+        </is>
+      </c>
+      <c r="AB239" s="6" t="inlineStr">
+        <is>
+          <t>Dallas office</t>
+        </is>
+      </c>
+      <c r="AC239" s="6" t="inlineStr">
+        <is>
+          <t>https://www.hillwoodcommunities.com/</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="12" t="inlineStr">
@@ -26211,6 +28804,17 @@
         </is>
       </c>
       <c r="Z240" s="12" t="inlineStr"/>
+      <c r="AA240" s="12" t="inlineStr">
+        <is>
+          <t>(713) 452-1700</t>
+        </is>
+      </c>
+      <c r="AB240" s="12" t="inlineStr"/>
+      <c r="AC240" s="12" t="inlineStr">
+        <is>
+          <t>https://www.signorellicompany.com/</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="6" t="inlineStr">
@@ -26327,6 +28931,17 @@
         </is>
       </c>
       <c r="Z241" s="6" t="inlineStr"/>
+      <c r="AA241" s="6" t="inlineStr">
+        <is>
+          <t>(713) 452-1700</t>
+        </is>
+      </c>
+      <c r="AB241" s="6" t="inlineStr"/>
+      <c r="AC241" s="6" t="inlineStr">
+        <is>
+          <t>https://www.signorellicompany.com/</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="12" t="inlineStr">
@@ -26443,6 +29058,17 @@
         </is>
       </c>
       <c r="Z242" s="12" t="inlineStr"/>
+      <c r="AA242" s="12" t="inlineStr">
+        <is>
+          <t>(713) 452-1700</t>
+        </is>
+      </c>
+      <c r="AB242" s="12" t="inlineStr"/>
+      <c r="AC242" s="12" t="inlineStr">
+        <is>
+          <t>https://www.signorellicompany.com/</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="6" t="inlineStr">
@@ -26559,6 +29185,17 @@
         </is>
       </c>
       <c r="Z243" s="6" t="inlineStr"/>
+      <c r="AA243" s="6" t="inlineStr">
+        <is>
+          <t>(713) 452-1700</t>
+        </is>
+      </c>
+      <c r="AB243" s="6" t="inlineStr"/>
+      <c r="AC243" s="6" t="inlineStr">
+        <is>
+          <t>https://www.signorellicompany.com/</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="12" t="inlineStr">
@@ -26671,6 +29308,21 @@
         </is>
       </c>
       <c r="Z244" s="12" t="inlineStr"/>
+      <c r="AA244" s="12" t="inlineStr">
+        <is>
+          <t>(713) 690-0000</t>
+        </is>
+      </c>
+      <c r="AB244" s="12" t="inlineStr">
+        <is>
+          <t>Houston and Cypress</t>
+        </is>
+      </c>
+      <c r="AC244" s="12" t="inlineStr">
+        <is>
+          <t>https://caldwellcos.com/</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="6" t="inlineStr">
@@ -26783,6 +29435,17 @@
         </is>
       </c>
       <c r="Z245" s="6" t="inlineStr"/>
+      <c r="AA245" s="6" t="inlineStr">
+        <is>
+          <t>(713) 783-6702</t>
+        </is>
+      </c>
+      <c r="AB245" s="6" t="inlineStr"/>
+      <c r="AC245" s="6" t="inlineStr">
+        <is>
+          <t>https://landtejas.com/</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="12" t="inlineStr">
@@ -26895,6 +29558,17 @@
         </is>
       </c>
       <c r="Z246" s="12" t="inlineStr"/>
+      <c r="AA246" s="12" t="inlineStr">
+        <is>
+          <t>(713) 783-6702</t>
+        </is>
+      </c>
+      <c r="AB246" s="12" t="inlineStr"/>
+      <c r="AC246" s="12" t="inlineStr">
+        <is>
+          <t>https://landtejas.com/</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="6" t="inlineStr">
@@ -27007,6 +29681,17 @@
         </is>
       </c>
       <c r="Z247" s="6" t="inlineStr"/>
+      <c r="AA247" s="6" t="inlineStr">
+        <is>
+          <t>(713) 960-9977</t>
+        </is>
+      </c>
+      <c r="AB247" s="6" t="inlineStr"/>
+      <c r="AC247" s="6" t="inlineStr">
+        <is>
+          <t>https://www.johnsondevelopment.com/</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="12" t="inlineStr">
@@ -27119,6 +29804,9 @@
       </c>
       <c r="Y248" s="12" t="inlineStr"/>
       <c r="Z248" s="12" t="inlineStr"/>
+      <c r="AA248" s="12" t="inlineStr"/>
+      <c r="AB248" s="12" t="inlineStr"/>
+      <c r="AC248" s="12" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="6" t="inlineStr">
@@ -27231,6 +29919,17 @@
         </is>
       </c>
       <c r="Z249" s="6" t="inlineStr"/>
+      <c r="AA249" s="6" t="inlineStr">
+        <is>
+          <t>(281) 875-1552</t>
+        </is>
+      </c>
+      <c r="AB249" s="6" t="inlineStr"/>
+      <c r="AC249" s="6" t="inlineStr">
+        <is>
+          <t>https://friendswooddevelopment.com/contact-us</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="12" t="inlineStr">
@@ -27332,6 +30031,9 @@
       <c r="X250" s="12" t="inlineStr"/>
       <c r="Y250" s="12" t="inlineStr"/>
       <c r="Z250" s="12" t="inlineStr"/>
+      <c r="AA250" s="12" t="inlineStr"/>
+      <c r="AB250" s="12" t="inlineStr"/>
+      <c r="AC250" s="12" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="6" t="inlineStr">
@@ -27432,6 +30134,21 @@
         </is>
       </c>
       <c r="Z251" s="6" t="inlineStr"/>
+      <c r="AA251" s="6" t="inlineStr">
+        <is>
+          <t>(281) 477-4300</t>
+        </is>
+      </c>
+      <c r="AB251" s="6" t="inlineStr">
+        <is>
+          <t>contact, corporate headquarters</t>
+        </is>
+      </c>
+      <c r="AC251" s="6" t="inlineStr">
+        <is>
+          <t>https://www.newquest.com/contact-us/</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="12" t="inlineStr">
@@ -27532,6 +30249,21 @@
         </is>
       </c>
       <c r="Z252" s="12" t="inlineStr"/>
+      <c r="AA252" s="12" t="inlineStr">
+        <is>
+          <t>(281) 477-4300</t>
+        </is>
+      </c>
+      <c r="AB252" s="12" t="inlineStr">
+        <is>
+          <t>contact, corporate headquarters</t>
+        </is>
+      </c>
+      <c r="AC252" s="12" t="inlineStr">
+        <is>
+          <t>https://www.newquest.com/contact-us/</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="6" t="inlineStr">
@@ -27632,6 +30364,21 @@
         </is>
       </c>
       <c r="Z253" s="6" t="inlineStr"/>
+      <c r="AA253" s="6" t="inlineStr">
+        <is>
+          <t>(281) 477-4300</t>
+        </is>
+      </c>
+      <c r="AB253" s="6" t="inlineStr">
+        <is>
+          <t>contact, corporate headquarters</t>
+        </is>
+      </c>
+      <c r="AC253" s="6" t="inlineStr">
+        <is>
+          <t>https://www.newquest.com/contact-us/</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="12" t="inlineStr">
@@ -27732,6 +30479,21 @@
         </is>
       </c>
       <c r="Z254" s="12" t="inlineStr"/>
+      <c r="AA254" s="12" t="inlineStr">
+        <is>
+          <t>(281) 477-4300</t>
+        </is>
+      </c>
+      <c r="AB254" s="12" t="inlineStr">
+        <is>
+          <t>contact, corporate headquarters</t>
+        </is>
+      </c>
+      <c r="AC254" s="12" t="inlineStr">
+        <is>
+          <t>https://www.newquest.com/contact-us/</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="6" t="inlineStr">
@@ -27836,6 +30598,17 @@
         </is>
       </c>
       <c r="Z255" s="6" t="inlineStr"/>
+      <c r="AA255" s="6" t="inlineStr">
+        <is>
+          <t>(713) 623-6800</t>
+        </is>
+      </c>
+      <c r="AB255" s="6" t="inlineStr"/>
+      <c r="AC255" s="6" t="inlineStr">
+        <is>
+          <t>https://www.frpltd.com/</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="12" t="inlineStr">
@@ -27936,6 +30709,17 @@
         </is>
       </c>
       <c r="Z256" s="12" t="inlineStr"/>
+      <c r="AA256" s="12" t="inlineStr">
+        <is>
+          <t>(713) 623-6800</t>
+        </is>
+      </c>
+      <c r="AB256" s="12" t="inlineStr"/>
+      <c r="AC256" s="12" t="inlineStr">
+        <is>
+          <t>https://www.frpltd.com/</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="6" t="inlineStr">
@@ -28041,6 +30825,17 @@
         </is>
       </c>
       <c r="Z257" s="6" t="inlineStr"/>
+      <c r="AA257" s="6" t="inlineStr">
+        <is>
+          <t>(713) 623-6800</t>
+        </is>
+      </c>
+      <c r="AB257" s="6" t="inlineStr"/>
+      <c r="AC257" s="6" t="inlineStr">
+        <is>
+          <t>https://www.frpltd.com/</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="12" t="inlineStr">
@@ -28141,6 +30936,17 @@
         </is>
       </c>
       <c r="Z258" s="12" t="inlineStr"/>
+      <c r="AA258" s="12" t="inlineStr">
+        <is>
+          <t>(713) 267-2100</t>
+        </is>
+      </c>
+      <c r="AB258" s="12" t="inlineStr"/>
+      <c r="AC258" s="12" t="inlineStr">
+        <is>
+          <t>https://www.hanoverco.com/</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="6" t="inlineStr">
@@ -28241,6 +31047,17 @@
         </is>
       </c>
       <c r="Z259" s="6" t="inlineStr"/>
+      <c r="AA259" s="6" t="inlineStr">
+        <is>
+          <t>(713) 267-2100</t>
+        </is>
+      </c>
+      <c r="AB259" s="6" t="inlineStr"/>
+      <c r="AC259" s="6" t="inlineStr">
+        <is>
+          <t>https://www.hanoverco.com/</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="12" t="inlineStr">
@@ -28341,6 +31158,17 @@
         </is>
       </c>
       <c r="Z260" s="12" t="inlineStr"/>
+      <c r="AA260" s="12" t="inlineStr">
+        <is>
+          <t>(713) 267-2100</t>
+        </is>
+      </c>
+      <c r="AB260" s="12" t="inlineStr"/>
+      <c r="AC260" s="12" t="inlineStr">
+        <is>
+          <t>https://www.hanoverco.com/</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="6" t="inlineStr">
@@ -28441,6 +31269,17 @@
         </is>
       </c>
       <c r="Z261" s="6" t="inlineStr"/>
+      <c r="AA261" s="6" t="inlineStr">
+        <is>
+          <t>(713) 267-2100</t>
+        </is>
+      </c>
+      <c r="AB261" s="6" t="inlineStr"/>
+      <c r="AC261" s="6" t="inlineStr">
+        <is>
+          <t>https://www.hanoverco.com/</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="12" t="inlineStr">
@@ -28542,6 +31381,17 @@
         </is>
       </c>
       <c r="Z262" s="12" t="inlineStr"/>
+      <c r="AA262" s="12" t="inlineStr">
+        <is>
+          <t>(713) 267-2100</t>
+        </is>
+      </c>
+      <c r="AB262" s="12" t="inlineStr"/>
+      <c r="AC262" s="12" t="inlineStr">
+        <is>
+          <t>https://www.hanoverco.com/</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="6" t="inlineStr">
@@ -28643,6 +31493,17 @@
         </is>
       </c>
       <c r="Z263" s="6" t="inlineStr"/>
+      <c r="AA263" s="6" t="inlineStr">
+        <is>
+          <t>(713) 267-2100</t>
+        </is>
+      </c>
+      <c r="AB263" s="6" t="inlineStr"/>
+      <c r="AC263" s="6" t="inlineStr">
+        <is>
+          <t>https://www.hanoverco.com/</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="12" t="inlineStr">
@@ -28743,6 +31604,17 @@
         </is>
       </c>
       <c r="Z264" s="12" t="inlineStr"/>
+      <c r="AA264" s="12" t="inlineStr">
+        <is>
+          <t>(713) 782-9000</t>
+        </is>
+      </c>
+      <c r="AB264" s="12" t="inlineStr"/>
+      <c r="AC264" s="12" t="inlineStr">
+        <is>
+          <t>https://read-king.com/</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="6" t="inlineStr">
@@ -28843,6 +31715,17 @@
         </is>
       </c>
       <c r="Z265" s="6" t="inlineStr"/>
+      <c r="AA265" s="6" t="inlineStr">
+        <is>
+          <t>(713) 782-9000</t>
+        </is>
+      </c>
+      <c r="AB265" s="6" t="inlineStr"/>
+      <c r="AC265" s="6" t="inlineStr">
+        <is>
+          <t>https://read-king.com/</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="12" t="inlineStr">
@@ -28943,6 +31826,17 @@
         </is>
       </c>
       <c r="Z266" s="12" t="inlineStr"/>
+      <c r="AA266" s="12" t="inlineStr">
+        <is>
+          <t>(713) 782-9000</t>
+        </is>
+      </c>
+      <c r="AB266" s="12" t="inlineStr"/>
+      <c r="AC266" s="12" t="inlineStr">
+        <is>
+          <t>https://read-king.com/</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="6" t="inlineStr">
@@ -29044,6 +31938,17 @@
         </is>
       </c>
       <c r="Z267" s="6" t="inlineStr"/>
+      <c r="AA267" s="6" t="inlineStr">
+        <is>
+          <t>(713) 782-9000</t>
+        </is>
+      </c>
+      <c r="AB267" s="6" t="inlineStr"/>
+      <c r="AC267" s="6" t="inlineStr">
+        <is>
+          <t>https://read-king.com/</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="12" t="inlineStr">
@@ -29148,6 +32053,17 @@
         </is>
       </c>
       <c r="Z268" s="12" t="inlineStr"/>
+      <c r="AA268" s="12" t="inlineStr">
+        <is>
+          <t>(713) 354-2500</t>
+        </is>
+      </c>
+      <c r="AB268" s="12" t="inlineStr"/>
+      <c r="AC268" s="12" t="inlineStr">
+        <is>
+          <t>https://www.camdenliving.com/</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="6" t="inlineStr">
@@ -29252,6 +32168,17 @@
         </is>
       </c>
       <c r="Z269" s="6" t="inlineStr"/>
+      <c r="AA269" s="6" t="inlineStr">
+        <is>
+          <t>(713) 354-2500</t>
+        </is>
+      </c>
+      <c r="AB269" s="6" t="inlineStr"/>
+      <c r="AC269" s="6" t="inlineStr">
+        <is>
+          <t>https://www.camdenliving.com/</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="12" t="inlineStr">
@@ -29353,6 +32280,17 @@
         </is>
       </c>
       <c r="Z270" s="12" t="inlineStr"/>
+      <c r="AA270" s="12" t="inlineStr">
+        <is>
+          <t>(713) 354-2500</t>
+        </is>
+      </c>
+      <c r="AB270" s="12" t="inlineStr"/>
+      <c r="AC270" s="12" t="inlineStr">
+        <is>
+          <t>https://www.camdenliving.com/</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="6" t="inlineStr">
@@ -29453,6 +32391,9 @@
         </is>
       </c>
       <c r="Z271" s="6" t="inlineStr"/>
+      <c r="AA271" s="6" t="inlineStr"/>
+      <c r="AB271" s="6" t="inlineStr"/>
+      <c r="AC271" s="6" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="12" t="inlineStr">
@@ -29557,6 +32498,9 @@
         </is>
       </c>
       <c r="Z272" s="12" t="inlineStr"/>
+      <c r="AA272" s="12" t="inlineStr"/>
+      <c r="AB272" s="12" t="inlineStr"/>
+      <c r="AC272" s="12" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="6" t="inlineStr">
@@ -29661,6 +32605,9 @@
         </is>
       </c>
       <c r="Z273" s="6" t="inlineStr"/>
+      <c r="AA273" s="6" t="inlineStr"/>
+      <c r="AB273" s="6" t="inlineStr"/>
+      <c r="AC273" s="6" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="12" t="inlineStr">
@@ -29762,6 +32709,9 @@
         </is>
       </c>
       <c r="Z274" s="12" t="inlineStr"/>
+      <c r="AA274" s="12" t="inlineStr"/>
+      <c r="AB274" s="12" t="inlineStr"/>
+      <c r="AC274" s="12" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="6" t="inlineStr">
@@ -29862,6 +32812,9 @@
         </is>
       </c>
       <c r="Z275" s="6" t="inlineStr"/>
+      <c r="AA275" s="6" t="inlineStr"/>
+      <c r="AB275" s="6" t="inlineStr"/>
+      <c r="AC275" s="6" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="12" t="inlineStr">
@@ -29962,6 +32915,9 @@
         </is>
       </c>
       <c r="Z276" s="12" t="inlineStr"/>
+      <c r="AA276" s="12" t="inlineStr"/>
+      <c r="AB276" s="12" t="inlineStr"/>
+      <c r="AC276" s="12" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="6" t="inlineStr">
@@ -30062,6 +33018,17 @@
         </is>
       </c>
       <c r="Z277" s="6" t="inlineStr"/>
+      <c r="AA277" s="6" t="inlineStr">
+        <is>
+          <t>(713) 621-2900</t>
+        </is>
+      </c>
+      <c r="AB277" s="6" t="inlineStr"/>
+      <c r="AC277" s="6" t="inlineStr">
+        <is>
+          <t>https://bakerkatz.com/</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="12" t="inlineStr">
@@ -30162,6 +33129,17 @@
         </is>
       </c>
       <c r="Z278" s="12" t="inlineStr"/>
+      <c r="AA278" s="12" t="inlineStr">
+        <is>
+          <t>(713) 621-2900</t>
+        </is>
+      </c>
+      <c r="AB278" s="12" t="inlineStr"/>
+      <c r="AC278" s="12" t="inlineStr">
+        <is>
+          <t>https://bakerkatz.com/</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="6" t="inlineStr">
@@ -30266,6 +33244,17 @@
         </is>
       </c>
       <c r="Z279" s="6" t="inlineStr"/>
+      <c r="AA279" s="6" t="inlineStr">
+        <is>
+          <t>(713) 621-2900</t>
+        </is>
+      </c>
+      <c r="AB279" s="6" t="inlineStr"/>
+      <c r="AC279" s="6" t="inlineStr">
+        <is>
+          <t>https://bakerkatz.com/</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="12" t="inlineStr">
@@ -30366,6 +33355,17 @@
         </is>
       </c>
       <c r="Z280" s="12" t="inlineStr"/>
+      <c r="AA280" s="12" t="inlineStr">
+        <is>
+          <t>(713) 621-1700</t>
+        </is>
+      </c>
+      <c r="AB280" s="12" t="inlineStr"/>
+      <c r="AC280" s="12" t="inlineStr">
+        <is>
+          <t>https://www.wulfe.com/</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="6" t="inlineStr">
@@ -30466,6 +33466,17 @@
         </is>
       </c>
       <c r="Z281" s="6" t="inlineStr"/>
+      <c r="AA281" s="6" t="inlineStr">
+        <is>
+          <t>(713) 621-1700</t>
+        </is>
+      </c>
+      <c r="AB281" s="6" t="inlineStr"/>
+      <c r="AC281" s="6" t="inlineStr">
+        <is>
+          <t>https://www.wulfe.com/</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="12" t="inlineStr">
@@ -30567,16 +33578,19 @@
       <c r="X282" s="12" t="inlineStr"/>
       <c r="Y282" s="12" t="inlineStr"/>
       <c r="Z282" s="12" t="inlineStr"/>
+      <c r="AA282" s="12" t="inlineStr"/>
+      <c r="AB282" s="12" t="inlineStr"/>
+      <c r="AC282" s="12" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" s="17" t="inlineStr">
         <is>
-          <t>NOTE. A filled LinkedIn cell means the profile was opened or the search result read and the headline named the firm; column W records what was read. Where that test failed the cell is left empty rather than guessed, because a fabricated slug passes visual inspection and then fails in front of the person it names. Column Q searches for the empty ones in your own session. Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Capital is a qualifier, not a count. Source: ICON Greater Houston screen, build 55, 2026-09-11.</t>
+          <t>NOTE. A filled LinkedIn cell means the profile was opened or the search result read and the headline named the firm; column W records what was read. Where that test failed the cell is left empty rather than guessed, because a fabricated slug passes visual inspection and then fails in front of the person it names. Column Q searches for the empty ones in your own session. Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Capital is a qualifier, not a count. Source: ICON Greater Houston screen, build 56, 2026-09-11.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:Z282"/>
+  <autoFilter ref="A6:AC282"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/ICON_Greater_Houston_Rolodex.xlsx
+++ b/docs/ICON_Greater_Houston_Rolodex.xlsx
@@ -585,7 +585,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated from houston-data.json · build 56 · 2026-09-11 · public render. Do not hand-edit the HTML deck; it regenerates from the same file.</t>
+          <t>Generated from houston-data.json · build 57 · 2026-09-11 · public render. Do not hand-edit the HTML deck; it regenerates from the same file.</t>
         </is>
       </c>
     </row>
@@ -33585,7 +33585,7 @@
     <row r="284">
       <c r="A284" s="17" t="inlineStr">
         <is>
-          <t>NOTE. A filled LinkedIn cell means the profile was opened or the search result read and the headline named the firm; column W records what was read. Where that test failed the cell is left empty rather than guessed, because a fabricated slug passes visual inspection and then fails in front of the person it names. Column Q searches for the empty ones in your own session. Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Capital is a qualifier, not a count. Source: ICON Greater Houston screen, build 56, 2026-09-11.</t>
+          <t>NOTE. A filled LinkedIn cell means the profile was opened or the search result read and the headline named the firm; column W records what was read. Where that test failed the cell is left empty rather than guessed, because a fabricated slug passes visual inspection and then fails in front of the person it names. Column Q searches for the empty ones in your own session. Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Capital is a qualifier, not a count. Source: ICON Greater Houston screen, build 57, 2026-09-11.</t>
         </is>
       </c>
     </row>

--- a/docs/ICON_Greater_Houston_Rolodex.xlsx
+++ b/docs/ICON_Greater_Houston_Rolodex.xlsx
@@ -585,7 +585,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated from houston-data.json · build 57 · 2026-09-11 · public render. Do not hand-edit the HTML deck; it regenerates from the same file.</t>
+          <t>Generated from houston-data.json · build 58 · 2026-09-11 · public render. Do not hand-edit the HTML deck; it regenerates from the same file.</t>
         </is>
       </c>
     </row>
@@ -33585,7 +33585,7 @@
     <row r="284">
       <c r="A284" s="17" t="inlineStr">
         <is>
-          <t>NOTE. A filled LinkedIn cell means the profile was opened or the search result read and the headline named the firm; column W records what was read. Where that test failed the cell is left empty rather than guessed, because a fabricated slug passes visual inspection and then fails in front of the person it names. Column Q searches for the empty ones in your own session. Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Capital is a qualifier, not a count. Source: ICON Greater Houston screen, build 57, 2026-09-11.</t>
+          <t>NOTE. A filled LinkedIn cell means the profile was opened or the search result read and the headline named the firm; column W records what was read. Where that test failed the cell is left empty rather than guessed, because a fabricated slug passes visual inspection and then fails in front of the person it names. Column Q searches for the empty ones in your own session. Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Capital is a qualifier, not a count. Source: ICON Greater Houston screen, build 58, 2026-09-11.</t>
         </is>
       </c>
     </row>

--- a/docs/ICON_Greater_Houston_Rolodex.xlsx
+++ b/docs/ICON_Greater_Houston_Rolodex.xlsx
@@ -585,7 +585,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated from houston-data.json · build 58 · 2026-09-11 · public render. Do not hand-edit the HTML deck; it regenerates from the same file.</t>
+          <t>Generated from houston-data.json · build 59 · 2026-09-11 · public render. Do not hand-edit the HTML deck; it regenerates from the same file.</t>
         </is>
       </c>
     </row>
@@ -6454,29 +6454,42 @@
         </is>
       </c>
       <c r="P53" s="10" t="inlineStr"/>
-      <c r="Q53" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Jamie%20Bryant%20Houston%20Housing%20Authority","search")</f>
-        <v/>
-      </c>
+      <c r="Q53" s="6" t="inlineStr"/>
       <c r="R53" s="11">
         <f>IF(P53="","ADD LINKEDIN","ok")</f>
         <v/>
       </c>
-      <c r="S53" s="6" t="inlineStr"/>
+      <c r="S53" s="6" t="inlineStr">
+        <is>
+          <t>https://www.alliancehtx.org/</t>
+        </is>
+      </c>
       <c r="T53" s="9" t="inlineStr">
         <is>
           <t>$600M across five phases to 2032. Federal money and open procurement, but no method track record.</t>
         </is>
       </c>
       <c r="U53" s="6" t="inlineStr"/>
-      <c r="V53" s="9" t="inlineStr"/>
-      <c r="W53" s="6" t="inlineStr"/>
+      <c r="V53" s="9" t="inlineStr">
+        <is>
+          <t>Her own bio page gives the title and the February 2025 appointment.</t>
+        </is>
+      </c>
+      <c r="W53" s="6" t="inlineStr">
+        <is>
+          <t>https://www.alliancehtx.org/team-members/jamie-bryant</t>
+        </is>
+      </c>
       <c r="X53" s="6" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/houston-housing-authority</t>
         </is>
       </c>
-      <c r="Y53" s="6" t="inlineStr"/>
+      <c r="Y53" s="6" t="inlineStr">
+        <is>
+          <t>https://www.alliancehtx.org/leadership</t>
+        </is>
+      </c>
       <c r="Z53" s="6" t="inlineStr"/>
       <c r="AA53" s="6" t="inlineStr"/>
       <c r="AB53" s="6" t="inlineStr"/>
@@ -6566,7 +6579,11 @@
         <f>IF(P54="","ADD LINKEDIN","ok")</f>
         <v/>
       </c>
-      <c r="S54" s="12" t="inlineStr"/>
+      <c r="S54" s="12" t="inlineStr">
+        <is>
+          <t>https://www.alliancehtx.org/</t>
+        </is>
+      </c>
       <c r="T54" s="15" t="inlineStr">
         <is>
           <t>$600M across five phases to 2032. Federal money and open procurement, but no method track record.</t>
@@ -6579,16 +6596,24 @@
       </c>
       <c r="V54" s="15" t="inlineStr">
         <is>
-          <t>Executive VP and COO Houston Housing Authority. Houston, Texas. The operating officer over a $600 million five-phase programme, and the office that answers for delivery rather than policy.</t>
-        </is>
-      </c>
-      <c r="W54" s="12" t="inlineStr"/>
+          <t>Executive VP and COO Houston Housing Authority. Houston, Texas. The operating officer over a $600 million five-phase programme, and the office that answers for delivery rather than policy. The leadership page carries the title.</t>
+        </is>
+      </c>
+      <c r="W54" s="12" t="inlineStr">
+        <is>
+          <t>https://www.alliancehtx.org/leadership</t>
+        </is>
+      </c>
       <c r="X54" s="12" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/houston-housing-authority</t>
         </is>
       </c>
-      <c r="Y54" s="12" t="inlineStr"/>
+      <c r="Y54" s="12" t="inlineStr">
+        <is>
+          <t>https://www.alliancehtx.org/leadership</t>
+        </is>
+      </c>
       <c r="Z54" s="12" t="inlineStr"/>
       <c r="AA54" s="12" t="inlineStr"/>
       <c r="AB54" s="12" t="inlineStr"/>
@@ -8859,7 +8884,7 @@
       </c>
       <c r="S73" s="6" t="inlineStr">
         <is>
-          <t>https://livelonestar.com/</t>
+          <t>no website confirmed</t>
         </is>
       </c>
       <c r="T73" s="9" t="inlineStr">
@@ -30015,7 +30040,11 @@
         <f>IF(P250="","ADD LINKEDIN","ok")</f>
         <v/>
       </c>
-      <c r="S250" s="12" t="inlineStr"/>
+      <c r="S250" s="12" t="inlineStr">
+        <is>
+          <t>no website confirmed</t>
+        </is>
+      </c>
       <c r="T250" s="15" t="inlineStr">
         <is>
           <t>Orders windows per home rather than per community so it can adopt newer products. Owned by Rausch Coleman Homes, which Lennar bought in February 2025.</t>
@@ -33562,7 +33591,11 @@
         <f>IF(P282="","ADD LINKEDIN","ok")</f>
         <v/>
       </c>
-      <c r="S282" s="12" t="inlineStr"/>
+      <c r="S282" s="12" t="inlineStr">
+        <is>
+          <t>no website confirmed</t>
+        </is>
+      </c>
       <c r="T282" s="15" t="inlineStr">
         <is>
           <t>Attached townhome production, the product type a printed party wall serves. The owner is held on a LinkedIn headline alone; the firm's own site publishes nobody.</t>
@@ -33585,7 +33618,7 @@
     <row r="284">
       <c r="A284" s="17" t="inlineStr">
         <is>
-          <t>NOTE. A filled LinkedIn cell means the profile was opened or the search result read and the headline named the firm; column W records what was read. Where that test failed the cell is left empty rather than guessed, because a fabricated slug passes visual inspection and then fails in front of the person it names. Column Q searches for the empty ones in your own session. Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Capital is a qualifier, not a count. Source: ICON Greater Houston screen, build 58, 2026-09-11.</t>
+          <t>NOTE. A filled LinkedIn cell means the profile was opened or the search result read and the headline named the firm; column W records what was read. Where that test failed the cell is left empty rather than guessed, because a fabricated slug passes visual inspection and then fails in front of the person it names. Column Q searches for the empty ones in your own session. Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Capital is a qualifier, not a count. Source: ICON Greater Houston screen, build 59, 2026-09-11.</t>
         </is>
       </c>
     </row>

--- a/docs/ICON_Greater_Houston_Rolodex.xlsx
+++ b/docs/ICON_Greater_Houston_Rolodex.xlsx
@@ -585,7 +585,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated from houston-data.json · build 59 · 2026-09-11 · public render. Do not hand-edit the HTML deck; it regenerates from the same file.</t>
+          <t>Generated from houston-data.json · build 60 · 2026-09-11 · public render. Do not hand-edit the HTML deck; it regenerates from the same file.</t>
         </is>
       </c>
     </row>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>Co-founder and Chief Executive Officer, named in trade coverage</t>
+          <t>Co-founder and Chief Executive Officer</t>
         </is>
       </c>
       <c r="D38" s="13" t="inlineStr">
@@ -4643,10 +4643,7 @@
         </is>
       </c>
       <c r="P38" s="10" t="inlineStr"/>
-      <c r="Q38" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Rame%20Hruska%20Aura%20Dwellings%20and%20Hospitality","search")</f>
-        <v/>
-      </c>
+      <c r="Q38" s="12" t="inlineStr"/>
       <c r="R38" s="16">
         <f>IF(P38="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -4666,8 +4663,16 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="V38" s="15" t="inlineStr"/>
-      <c r="W38" s="12" t="inlineStr"/>
+      <c r="V38" s="15" t="inlineStr">
+        <is>
+          <t>Quoted in AGC Houston's Cornerstone for winter 2025 to 2026, reposted 25 February 2026, as a co-founder and chief executive of Aura Dwellings and Hospitality. The company's own site names no one.</t>
+        </is>
+      </c>
+      <c r="W38" s="12" t="inlineStr">
+        <is>
+          <t>https://www.marekbros.com/the-future-is-factory-built/</t>
+        </is>
+      </c>
       <c r="X38" s="12" t="inlineStr"/>
       <c r="Y38" s="12" t="inlineStr"/>
       <c r="Z38" s="12" t="inlineStr"/>
@@ -8581,7 +8586,7 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>Chief Executive Officer and co-founder, named in the firm's own media coverage</t>
+          <t>Chief Executive Officer and co-founder</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
@@ -8643,10 +8648,7 @@
         </is>
       </c>
       <c r="P71" s="10" t="inlineStr"/>
-      <c r="Q71" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Franck%20Boursier%20Everlasting%20Homes%20Building%20Group","search")</f>
-        <v/>
-      </c>
+      <c r="Q71" s="6" t="inlineStr"/>
       <c r="R71" s="11">
         <f>IF(P71="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -8666,8 +8668,16 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="V71" s="9" t="inlineStr"/>
-      <c r="W71" s="6" t="inlineStr"/>
+      <c r="V71" s="9" t="inlineStr">
+        <is>
+          <t>The firm's own site carries him as chief executive and a founder in the business record it publishes.</t>
+        </is>
+      </c>
+      <c r="W71" s="6" t="inlineStr">
+        <is>
+          <t>https://www.everlastinghomesgroup.com/</t>
+        </is>
+      </c>
       <c r="X71" s="6" t="inlineStr"/>
       <c r="Y71" s="6" t="inlineStr"/>
       <c r="Z71" s="6" t="inlineStr"/>
@@ -8700,7 +8710,7 @@
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>General Manager, named in trade coverage of the Braesvalley house</t>
+          <t>General Manager</t>
         </is>
       </c>
       <c r="D72" s="13" t="inlineStr">
@@ -8762,10 +8772,7 @@
         </is>
       </c>
       <c r="P72" s="10" t="inlineStr"/>
-      <c r="Q72" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=George%20Mock%20Everlasting%20Homes%20Building%20Group","search")</f>
-        <v/>
-      </c>
+      <c r="Q72" s="12" t="inlineStr"/>
       <c r="R72" s="16">
         <f>IF(P72="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -8785,8 +8792,16 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="V72" s="15" t="inlineStr"/>
-      <c r="W72" s="12" t="inlineStr"/>
+      <c r="V72" s="15" t="inlineStr">
+        <is>
+          <t>The firm's own site carries him as general manager and a founder in the business record it publishes.</t>
+        </is>
+      </c>
+      <c r="W72" s="12" t="inlineStr">
+        <is>
+          <t>https://www.everlastinghomesgroup.com/</t>
+        </is>
+      </c>
       <c r="X72" s="12" t="inlineStr"/>
       <c r="Y72" s="12" t="inlineStr"/>
       <c r="Z72" s="12" t="inlineStr"/>
@@ -8915,7 +8930,7 @@
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>Founder and Designer, named on the firm's own about page</t>
+          <t>Founder and Designer</t>
         </is>
       </c>
       <c r="D74" s="13" t="inlineStr">
@@ -8977,10 +8992,7 @@
         </is>
       </c>
       <c r="P74" s="10" t="inlineStr"/>
-      <c r="Q74" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Ker%20Thomson%20Nautilus%20Custom%20Homes","search")</f>
-        <v/>
-      </c>
+      <c r="Q74" s="12" t="inlineStr"/>
       <c r="R74" s="16">
         <f>IF(P74="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -9000,10 +9012,22 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="V74" s="15" t="inlineStr"/>
-      <c r="W74" s="12" t="inlineStr"/>
+      <c r="V74" s="15" t="inlineStr">
+        <is>
+          <t>The firm's own about page: in design and layout since the late 1990s, and in 2007 formed Nautilus's predecessor, Durable Residential Builders, out of a building-systems project with Texas A&amp;M.</t>
+        </is>
+      </c>
+      <c r="W74" s="12" t="inlineStr">
+        <is>
+          <t>https://www.nautiluscustomhomes.com/about-us</t>
+        </is>
+      </c>
       <c r="X74" s="12" t="inlineStr"/>
-      <c r="Y74" s="12" t="inlineStr"/>
+      <c r="Y74" s="12" t="inlineStr">
+        <is>
+          <t>https://www.nautiluscustomhomes.com/about-us</t>
+        </is>
+      </c>
       <c r="Z74" s="12" t="inlineStr"/>
       <c r="AA74" s="12" t="inlineStr">
         <is>
@@ -9030,7 +9054,7 @@
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>Construction lead, named on the firm's own about page</t>
+          <t>Construction lead</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
@@ -9092,10 +9116,7 @@
         </is>
       </c>
       <c r="P75" s="10" t="inlineStr"/>
-      <c r="Q75" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Jim%20Kuchenbrod%20Nautilus%20Custom%20Homes","search")</f>
-        <v/>
-      </c>
+      <c r="Q75" s="6" t="inlineStr"/>
       <c r="R75" s="11">
         <f>IF(P75="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -9111,10 +9132,22 @@
         </is>
       </c>
       <c r="U75" s="6" t="inlineStr"/>
-      <c r="V75" s="9" t="inlineStr"/>
-      <c r="W75" s="6" t="inlineStr"/>
+      <c r="V75" s="9" t="inlineStr">
+        <is>
+          <t>The firm's own about page: a navy veteran, in all aspects of residential construction for more than thirty-five years.</t>
+        </is>
+      </c>
+      <c r="W75" s="6" t="inlineStr">
+        <is>
+          <t>https://www.nautiluscustomhomes.com/about-us</t>
+        </is>
+      </c>
       <c r="X75" s="6" t="inlineStr"/>
-      <c r="Y75" s="6" t="inlineStr"/>
+      <c r="Y75" s="6" t="inlineStr">
+        <is>
+          <t>https://www.nautiluscustomhomes.com/about-us</t>
+        </is>
+      </c>
       <c r="Z75" s="6" t="inlineStr"/>
       <c r="AA75" s="6" t="inlineStr">
         <is>
@@ -13660,7 +13693,7 @@
       </c>
       <c r="C114" s="12" t="inlineStr">
         <is>
-          <t>Owner, named on the firm's own homepage as having owned and operated it since 2002</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="D114" s="13" t="inlineStr">
@@ -13722,10 +13755,7 @@
         </is>
       </c>
       <c r="P114" s="10" t="inlineStr"/>
-      <c r="Q114" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Matt%20Zetlmeisl%20ICF%20Constructors","search")</f>
-        <v/>
-      </c>
+      <c r="Q114" s="12" t="inlineStr"/>
       <c r="R114" s="16">
         <f>IF(P114="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -13747,10 +13777,14 @@
       </c>
       <c r="V114" s="15" t="inlineStr">
         <is>
-          <t>Matt Zetlmeisl has no LinkedIn profile. The firm's own site is the only source that names him.</t>
-        </is>
-      </c>
-      <c r="W114" s="12" t="inlineStr"/>
+          <t>The firm's own about page: owned and operated by Matt Zetlmeisl since 2002.</t>
+        </is>
+      </c>
+      <c r="W114" s="12" t="inlineStr">
+        <is>
+          <t>https://icfconstructors.com/about/</t>
+        </is>
+      </c>
       <c r="X114" s="12" t="inlineStr"/>
       <c r="Y114" s="12" t="inlineStr"/>
       <c r="Z114" s="12" t="inlineStr"/>
@@ -13783,7 +13817,7 @@
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>Founder, named on the firm's own site</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
@@ -13871,12 +13905,20 @@
       </c>
       <c r="V115" s="9" t="inlineStr">
         <is>
-          <t>Headline reads President at Botello Builders Corporation. Houston, Texas. The firm's own site calls him a founder and gives no title.</t>
-        </is>
-      </c>
-      <c r="W115" s="6" t="inlineStr"/>
+          <t>Headline reads President at Botello Builders Corporation. Houston, Texas. The firm's own site calls him a founder and gives no title. The firm's own site: founded in early 2007 by Eleazar, Eden and Jose Botello, starting in residential work.</t>
+        </is>
+      </c>
+      <c r="W115" s="6" t="inlineStr">
+        <is>
+          <t>https://www.botellobuilders.com/</t>
+        </is>
+      </c>
       <c r="X115" s="6" t="inlineStr"/>
-      <c r="Y115" s="6" t="inlineStr"/>
+      <c r="Y115" s="6" t="inlineStr">
+        <is>
+          <t>https://www.botellobuilders.com/</t>
+        </is>
+      </c>
       <c r="Z115" s="6" t="inlineStr"/>
       <c r="AA115" s="6" t="inlineStr">
         <is>
@@ -13903,7 +13945,7 @@
       </c>
       <c r="C116" s="12" t="inlineStr">
         <is>
-          <t>Founder, named on the firm's own site</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="D116" s="13" t="inlineStr">
@@ -13991,12 +14033,20 @@
       </c>
       <c r="V116" s="15" t="inlineStr">
         <is>
-          <t>Headline reads Operations Manager at Botello Builders Corporation. Houston, Texas.</t>
-        </is>
-      </c>
-      <c r="W116" s="12" t="inlineStr"/>
+          <t>Headline reads Operations Manager at Botello Builders Corporation. Houston, Texas. The firm's own site: founded in early 2007 by Eleazar, Eden and Jose Botello, starting in residential work.</t>
+        </is>
+      </c>
+      <c r="W116" s="12" t="inlineStr">
+        <is>
+          <t>https://www.botellobuilders.com/</t>
+        </is>
+      </c>
       <c r="X116" s="12" t="inlineStr"/>
-      <c r="Y116" s="12" t="inlineStr"/>
+      <c r="Y116" s="12" t="inlineStr">
+        <is>
+          <t>https://www.botellobuilders.com/</t>
+        </is>
+      </c>
       <c r="Z116" s="12" t="inlineStr"/>
       <c r="AA116" s="12" t="inlineStr">
         <is>
@@ -14023,7 +14073,7 @@
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>Founder, named on the firm's own site</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
@@ -14085,10 +14135,7 @@
         </is>
       </c>
       <c r="P117" s="10" t="inlineStr"/>
-      <c r="Q117" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Jose%20Botello%20Botello%20Builders","search")</f>
-        <v/>
-      </c>
+      <c r="Q117" s="6" t="inlineStr"/>
       <c r="R117" s="11">
         <f>IF(P117="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -14108,10 +14155,22 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="V117" s="9" t="inlineStr"/>
-      <c r="W117" s="6" t="inlineStr"/>
+      <c r="V117" s="9" t="inlineStr">
+        <is>
+          <t>The firm's own site: founded in early 2007 by Eleazar, Eden and Jose Botello, starting in residential work.</t>
+        </is>
+      </c>
+      <c r="W117" s="6" t="inlineStr">
+        <is>
+          <t>https://www.botellobuilders.com/</t>
+        </is>
+      </c>
       <c r="X117" s="6" t="inlineStr"/>
-      <c r="Y117" s="6" t="inlineStr"/>
+      <c r="Y117" s="6" t="inlineStr">
+        <is>
+          <t>https://www.botellobuilders.com/</t>
+        </is>
+      </c>
       <c r="Z117" s="6" t="inlineStr"/>
       <c r="AA117" s="6" t="inlineStr">
         <is>
@@ -15230,7 +15289,7 @@
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>Listed under Senior Leadership on the firm's own team page</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
@@ -15292,10 +15351,7 @@
         </is>
       </c>
       <c r="P127" s="10" t="inlineStr"/>
-      <c r="Q127" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Chris%20Richardson%20Blazer%20Building","search")</f>
-        <v/>
-      </c>
+      <c r="Q127" s="6" t="inlineStr"/>
       <c r="R127" s="11">
         <f>IF(P127="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -15311,10 +15367,22 @@
         </is>
       </c>
       <c r="U127" s="6" t="inlineStr"/>
-      <c r="V127" s="9" t="inlineStr"/>
-      <c r="W127" s="6" t="inlineStr"/>
+      <c r="V127" s="9" t="inlineStr">
+        <is>
+          <t>His own bio page on the firm's site: founded the company in 1978. The Who We Are page lists him under Senior Leadership.</t>
+        </is>
+      </c>
+      <c r="W127" s="6" t="inlineStr">
+        <is>
+          <t>https://www.blazerbuilding.com/team/chris-richardson/</t>
+        </is>
+      </c>
       <c r="X127" s="6" t="inlineStr"/>
-      <c r="Y127" s="6" t="inlineStr"/>
+      <c r="Y127" s="6" t="inlineStr">
+        <is>
+          <t>https://www.blazerbuilding.com/who-we-are/</t>
+        </is>
+      </c>
       <c r="Z127" s="6" t="inlineStr"/>
       <c r="AA127" s="6" t="inlineStr">
         <is>
@@ -15341,7 +15409,7 @@
       </c>
       <c r="C128" s="12" t="inlineStr">
         <is>
-          <t>Listed under Senior Leadership on the firm's own team page</t>
+          <t>President, Blazer Building Southwest</t>
         </is>
       </c>
       <c r="D128" s="13" t="inlineStr">
@@ -15403,10 +15471,7 @@
         </is>
       </c>
       <c r="P128" s="10" t="inlineStr"/>
-      <c r="Q128" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Chad%20Hillman%20Blazer%20Building","search")</f>
-        <v/>
-      </c>
+      <c r="Q128" s="12" t="inlineStr"/>
       <c r="R128" s="16">
         <f>IF(P128="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -15422,10 +15487,22 @@
         </is>
       </c>
       <c r="U128" s="12" t="inlineStr"/>
-      <c r="V128" s="15" t="inlineStr"/>
-      <c r="W128" s="12" t="inlineStr"/>
+      <c r="V128" s="15" t="inlineStr">
+        <is>
+          <t>His own bio page: president of Blazer Building Southwest, over operations, project management, financial oversight and relationships with owners, developers, lenders and subcontractors. Before it, vice president of construction, general superintendent and superintendent.</t>
+        </is>
+      </c>
+      <c r="W128" s="12" t="inlineStr">
+        <is>
+          <t>https://www.blazerbuilding.com/team/chad-hillman/</t>
+        </is>
+      </c>
       <c r="X128" s="12" t="inlineStr"/>
-      <c r="Y128" s="12" t="inlineStr"/>
+      <c r="Y128" s="12" t="inlineStr">
+        <is>
+          <t>https://www.blazerbuilding.com/who-we-are/</t>
+        </is>
+      </c>
       <c r="Z128" s="12" t="inlineStr"/>
       <c r="AA128" s="12" t="inlineStr">
         <is>
@@ -15452,7 +15529,7 @@
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>Listed under Senior Leadership on the firm's own team page</t>
+          <t>Business Development</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
@@ -15514,10 +15591,7 @@
         </is>
       </c>
       <c r="P129" s="10" t="inlineStr"/>
-      <c r="Q129" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Matt%20Fuqua%20Blazer%20Building","search")</f>
-        <v/>
-      </c>
+      <c r="Q129" s="6" t="inlineStr"/>
       <c r="R129" s="11">
         <f>IF(P129="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -15533,10 +15607,22 @@
         </is>
       </c>
       <c r="U129" s="6" t="inlineStr"/>
-      <c r="V129" s="9" t="inlineStr"/>
-      <c r="W129" s="6" t="inlineStr"/>
+      <c r="V129" s="9" t="inlineStr">
+        <is>
+          <t>His own bio page: business development, affordable and conventional multi-family and active adult housing, over twenty years with Blazer.</t>
+        </is>
+      </c>
+      <c r="W129" s="6" t="inlineStr">
+        <is>
+          <t>https://www.blazerbuilding.com/team/matt-fuqua/</t>
+        </is>
+      </c>
       <c r="X129" s="6" t="inlineStr"/>
-      <c r="Y129" s="6" t="inlineStr"/>
+      <c r="Y129" s="6" t="inlineStr">
+        <is>
+          <t>https://www.blazerbuilding.com/who-we-are/</t>
+        </is>
+      </c>
       <c r="Z129" s="6" t="inlineStr"/>
       <c r="AA129" s="6" t="inlineStr">
         <is>
@@ -15563,7 +15649,7 @@
       </c>
       <c r="C130" s="12" t="inlineStr">
         <is>
-          <t>Listed under Senior Leadership and Construction Supervision on the firm's own team page</t>
+          <t>Vice President of Construction</t>
         </is>
       </c>
       <c r="D130" s="13" t="inlineStr">
@@ -15625,10 +15711,7 @@
         </is>
       </c>
       <c r="P130" s="10" t="inlineStr"/>
-      <c r="Q130" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Brian%20Henderson%20Blazer%20Building","search")</f>
-        <v/>
-      </c>
+      <c r="Q130" s="12" t="inlineStr"/>
       <c r="R130" s="16">
         <f>IF(P130="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -15644,10 +15727,22 @@
         </is>
       </c>
       <c r="U130" s="12" t="inlineStr"/>
-      <c r="V130" s="15" t="inlineStr"/>
-      <c r="W130" s="12" t="inlineStr"/>
+      <c r="V130" s="15" t="inlineStr">
+        <is>
+          <t>His own bio page: joined in 2014, served as assistant superintendent and superintendent, now vice president of construction. The Who We Are page lists him under both Senior Leadership and Construction Supervision.</t>
+        </is>
+      </c>
+      <c r="W130" s="12" t="inlineStr">
+        <is>
+          <t>https://www.blazerbuilding.com/team/brian-henderson/</t>
+        </is>
+      </c>
       <c r="X130" s="12" t="inlineStr"/>
-      <c r="Y130" s="12" t="inlineStr"/>
+      <c r="Y130" s="12" t="inlineStr">
+        <is>
+          <t>https://www.blazerbuilding.com/who-we-are/</t>
+        </is>
+      </c>
       <c r="Z130" s="12" t="inlineStr"/>
       <c r="AA130" s="12" t="inlineStr">
         <is>
@@ -15674,7 +15769,7 @@
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>Senior Vice President, Self Perform Group, Satterfield and Pontikes, named on the parent's own team page as overseeing Greco Structures, Rollcon, Rocket Pumping and Westway</t>
+          <t>Senior Vice President, Self Perform Group, Satterfield and Pontikes</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
@@ -15736,10 +15831,7 @@
         </is>
       </c>
       <c r="P131" s="10" t="inlineStr"/>
-      <c r="Q131" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Trey%20Green%20Greco%20Structures","search")</f>
-        <v/>
-      </c>
+      <c r="Q131" s="6" t="inlineStr"/>
       <c r="R131" s="11">
         <f>IF(P131="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -15761,12 +15853,20 @@
       </c>
       <c r="V131" s="9" t="inlineStr">
         <is>
-          <t>Trey Green is named on Satterfield and Pontikes' own team page and returns no LinkedIn result against the parent's name.</t>
-        </is>
-      </c>
-      <c r="W131" s="6" t="inlineStr"/>
+          <t>The parent's own team page: he oversees the Self Perform group of Greco Structures, Rollcon, Rocket Pumping and Westway Construction.</t>
+        </is>
+      </c>
+      <c r="W131" s="6" t="inlineStr">
+        <is>
+          <t>https://www.satpon.com/about/team/</t>
+        </is>
+      </c>
       <c r="X131" s="6" t="inlineStr"/>
-      <c r="Y131" s="6" t="inlineStr"/>
+      <c r="Y131" s="6" t="inlineStr">
+        <is>
+          <t>https://www.satpon.com/about/team/</t>
+        </is>
+      </c>
       <c r="Z131" s="6" t="inlineStr"/>
       <c r="AA131" s="6" t="inlineStr">
         <is>
@@ -15855,10 +15955,7 @@
         </is>
       </c>
       <c r="P132" s="10" t="inlineStr"/>
-      <c r="Q132" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=George%20A.%20Pontikes%20Jr.%20Greco%20Structures","search")</f>
-        <v/>
-      </c>
+      <c r="Q132" s="12" t="inlineStr"/>
       <c r="R132" s="16">
         <f>IF(P132="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -15874,10 +15971,22 @@
         </is>
       </c>
       <c r="U132" s="12" t="inlineStr"/>
-      <c r="V132" s="15" t="inlineStr"/>
-      <c r="W132" s="12" t="inlineStr"/>
+      <c r="V132" s="15" t="inlineStr">
+        <is>
+          <t>The parent's own team page: he founded Satterfield and Pontikes with Tommy Satterfield in 1989.</t>
+        </is>
+      </c>
+      <c r="W132" s="12" t="inlineStr">
+        <is>
+          <t>https://www.satpon.com/about/team/</t>
+        </is>
+      </c>
       <c r="X132" s="12" t="inlineStr"/>
-      <c r="Y132" s="12" t="inlineStr"/>
+      <c r="Y132" s="12" t="inlineStr">
+        <is>
+          <t>https://www.satpon.com/about/team/</t>
+        </is>
+      </c>
       <c r="Z132" s="12" t="inlineStr"/>
       <c r="AA132" s="12" t="inlineStr">
         <is>
@@ -15993,7 +16102,11 @@
       </c>
       <c r="W133" s="6" t="inlineStr"/>
       <c r="X133" s="6" t="inlineStr"/>
-      <c r="Y133" s="6" t="inlineStr"/>
+      <c r="Y133" s="6" t="inlineStr">
+        <is>
+          <t>https://www.satpon.com/about/team/</t>
+        </is>
+      </c>
       <c r="Z133" s="6" t="inlineStr"/>
       <c r="AA133" s="6" t="inlineStr">
         <is>
@@ -16109,7 +16222,11 @@
       </c>
       <c r="W134" s="12" t="inlineStr"/>
       <c r="X134" s="12" t="inlineStr"/>
-      <c r="Y134" s="12" t="inlineStr"/>
+      <c r="Y134" s="12" t="inlineStr">
+        <is>
+          <t>https://www.satpon.com/about/team/</t>
+        </is>
+      </c>
       <c r="Z134" s="12" t="inlineStr"/>
       <c r="AA134" s="12" t="inlineStr">
         <is>
@@ -16136,7 +16253,7 @@
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>Founder, named on the firm's own about page</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
@@ -16198,10 +16315,7 @@
         </is>
       </c>
       <c r="P135" s="10" t="inlineStr"/>
-      <c r="Q135" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=David%20E.%20Harvey%20Sr.%20Harvey%20Cleary","search")</f>
-        <v/>
-      </c>
+      <c r="Q135" s="6" t="inlineStr"/>
       <c r="R135" s="11">
         <f>IF(P135="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -16217,10 +16331,22 @@
         </is>
       </c>
       <c r="U135" s="6" t="inlineStr"/>
-      <c r="V135" s="9" t="inlineStr"/>
-      <c r="W135" s="6" t="inlineStr"/>
+      <c r="V135" s="9" t="inlineStr">
+        <is>
+          <t>The firm's own about page: David E. Harvey, Sr. and Gerald D. Hines founded it in 1957, and Harvey was already a proponent of tiltwall.</t>
+        </is>
+      </c>
+      <c r="W135" s="6" t="inlineStr">
+        <is>
+          <t>https://www.harveycleary.com/about-us/</t>
+        </is>
+      </c>
       <c r="X135" s="6" t="inlineStr"/>
-      <c r="Y135" s="6" t="inlineStr"/>
+      <c r="Y135" s="6" t="inlineStr">
+        <is>
+          <t>https://www.harveycleary.com/about-us/</t>
+        </is>
+      </c>
       <c r="Z135" s="6" t="inlineStr">
         <is>
           <t>2026 Engineering News-Record. ENR 2026 Top 400 Contractors, where the firm is ranked 72  https://www.enr.com/toplists/2026-Top-400-Contractors-1</t>
@@ -16243,7 +16369,7 @@
       </c>
       <c r="C136" s="12" t="inlineStr">
         <is>
-          <t>Took ownership in 1987, named on the firm's own about page</t>
+          <t>Took ownership in 1987</t>
         </is>
       </c>
       <c r="D136" s="13" t="inlineStr">
@@ -16305,10 +16431,7 @@
         </is>
       </c>
       <c r="P136" s="10" t="inlineStr"/>
-      <c r="Q136" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=David%20Harvey%20Jr.%20Harvey%20Cleary","search")</f>
-        <v/>
-      </c>
+      <c r="Q136" s="12" t="inlineStr"/>
       <c r="R136" s="16">
         <f>IF(P136="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -16324,10 +16447,22 @@
         </is>
       </c>
       <c r="U136" s="12" t="inlineStr"/>
-      <c r="V136" s="15" t="inlineStr"/>
-      <c r="W136" s="12" t="inlineStr"/>
+      <c r="V136" s="15" t="inlineStr">
+        <is>
+          <t>The firm's own about page: he and Joseph Cleary both started at Harvey, in 1977 and 1976, and both took ownership in 1987, renaming it Harvey Cleary.</t>
+        </is>
+      </c>
+      <c r="W136" s="12" t="inlineStr">
+        <is>
+          <t>https://www.harveycleary.com/about-us/</t>
+        </is>
+      </c>
       <c r="X136" s="12" t="inlineStr"/>
-      <c r="Y136" s="12" t="inlineStr"/>
+      <c r="Y136" s="12" t="inlineStr">
+        <is>
+          <t>https://www.harveycleary.com/about-us/</t>
+        </is>
+      </c>
       <c r="Z136" s="12" t="inlineStr">
         <is>
           <t>2026 Engineering News-Record. ENR 2026 Top 400 Contractors, where the firm is ranked 72  https://www.enr.com/toplists/2026-Top-400-Contractors-1</t>
@@ -16350,7 +16485,7 @@
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>Took ownership in 1987, named on the firm's own about page</t>
+          <t>Took ownership in 1987</t>
         </is>
       </c>
       <c r="D137" s="7" t="inlineStr">
@@ -16412,10 +16547,7 @@
         </is>
       </c>
       <c r="P137" s="10" t="inlineStr"/>
-      <c r="Q137" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Joseph%20Cleary%20Harvey%20Cleary","search")</f>
-        <v/>
-      </c>
+      <c r="Q137" s="6" t="inlineStr"/>
       <c r="R137" s="11">
         <f>IF(P137="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -16431,10 +16563,22 @@
         </is>
       </c>
       <c r="U137" s="6" t="inlineStr"/>
-      <c r="V137" s="9" t="inlineStr"/>
-      <c r="W137" s="6" t="inlineStr"/>
+      <c r="V137" s="9" t="inlineStr">
+        <is>
+          <t>The firm's own about page: he and David Harvey, Jr. both took ownership in 1987, renaming Harvey Builders to Harvey Cleary.</t>
+        </is>
+      </c>
+      <c r="W137" s="6" t="inlineStr">
+        <is>
+          <t>https://www.harveycleary.com/about-us/</t>
+        </is>
+      </c>
       <c r="X137" s="6" t="inlineStr"/>
-      <c r="Y137" s="6" t="inlineStr"/>
+      <c r="Y137" s="6" t="inlineStr">
+        <is>
+          <t>https://www.harveycleary.com/about-us/</t>
+        </is>
+      </c>
       <c r="Z137" s="6" t="inlineStr">
         <is>
           <t>2026 Engineering News-Record. ENR 2026 Top 400 Contractors, where the firm is ranked 72  https://www.enr.com/toplists/2026-Top-400-Contractors-1</t>
@@ -16550,7 +16694,11 @@
       </c>
       <c r="W138" s="12" t="inlineStr"/>
       <c r="X138" s="12" t="inlineStr"/>
-      <c r="Y138" s="12" t="inlineStr"/>
+      <c r="Y138" s="12" t="inlineStr">
+        <is>
+          <t>https://www.harveycleary.com/about-us/</t>
+        </is>
+      </c>
       <c r="Z138" s="12" t="inlineStr">
         <is>
           <t>2026 Engineering News-Record. ENR 2026 Top 400 Contractors, where the firm is ranked 72  https://www.enr.com/toplists/2026-Top-400-Contractors-1</t>
@@ -16662,7 +16810,11 @@
       </c>
       <c r="W139" s="6" t="inlineStr"/>
       <c r="X139" s="6" t="inlineStr"/>
-      <c r="Y139" s="6" t="inlineStr"/>
+      <c r="Y139" s="6" t="inlineStr">
+        <is>
+          <t>https://www.harveycleary.com/about-us/</t>
+        </is>
+      </c>
       <c r="Z139" s="6" t="inlineStr">
         <is>
           <t>2026 Engineering News-Record. ENR 2026 Top 400 Contractors, where the firm is ranked 72  https://www.enr.com/toplists/2026-Top-400-Contractors-1</t>
@@ -16685,7 +16837,7 @@
       </c>
       <c r="C140" s="12" t="inlineStr">
         <is>
-          <t>Chief Executive Officer, Orion Group Holdings, quoted in the firm's own release of 29 January 2024</t>
+          <t>Chief Executive Officer, Orion Group Holdings</t>
         </is>
       </c>
       <c r="D140" s="13" t="inlineStr">
@@ -16747,10 +16899,7 @@
         </is>
       </c>
       <c r="P140" s="10" t="inlineStr"/>
-      <c r="Q140" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Travis%20Boone%20ORION","search")</f>
-        <v/>
-      </c>
+      <c r="Q140" s="12" t="inlineStr"/>
       <c r="R140" s="16">
         <f>IF(P140="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -16772,10 +16921,14 @@
       </c>
       <c r="V140" s="15" t="inlineStr">
         <is>
-          <t>Travis Boone runs the listed parent, not the Houston concrete business.</t>
-        </is>
-      </c>
-      <c r="W140" s="12" t="inlineStr"/>
+          <t>Quoted as chief executive in the firm's own release of 29 January 2024, announcing that TAS Concrete Construction would trade as Orion.</t>
+        </is>
+      </c>
+      <c r="W140" s="12" t="inlineStr">
+        <is>
+          <t>https://www.oriongroupholdingsinc.com/investors/press-release/2024/29-01-2024-120203346</t>
+        </is>
+      </c>
       <c r="X140" s="12" t="inlineStr"/>
       <c r="Y140" s="12" t="inlineStr"/>
       <c r="Z140" s="12" t="inlineStr"/>
@@ -17044,7 +17197,7 @@
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>Chief Executive Officer, named on the firm's own leadership page</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="D143" s="7" t="inlineStr">
@@ -17106,10 +17259,7 @@
         </is>
       </c>
       <c r="P143" s="10" t="inlineStr"/>
-      <c r="Q143" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Steve%20Salverino%20Rino%20Construction","search")</f>
-        <v/>
-      </c>
+      <c r="Q143" s="6" t="inlineStr"/>
       <c r="R143" s="11">
         <f>IF(P143="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -17125,10 +17275,22 @@
         </is>
       </c>
       <c r="U143" s="6" t="inlineStr"/>
-      <c r="V143" s="9" t="inlineStr"/>
-      <c r="W143" s="6" t="inlineStr"/>
+      <c r="V143" s="9" t="inlineStr">
+        <is>
+          <t>The firm's own leadership page carries the title.</t>
+        </is>
+      </c>
+      <c r="W143" s="6" t="inlineStr">
+        <is>
+          <t>https://rino-con.com/leadership/</t>
+        </is>
+      </c>
       <c r="X143" s="6" t="inlineStr"/>
-      <c r="Y143" s="6" t="inlineStr"/>
+      <c r="Y143" s="6" t="inlineStr">
+        <is>
+          <t>https://rino-con.com/leadership/</t>
+        </is>
+      </c>
       <c r="Z143" s="6" t="inlineStr"/>
       <c r="AA143" s="6" t="inlineStr">
         <is>
@@ -17159,7 +17321,7 @@
       </c>
       <c r="C144" s="12" t="inlineStr">
         <is>
-          <t>President, named on the firm's own leadership page</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D144" s="13" t="inlineStr">
@@ -17221,10 +17383,7 @@
         </is>
       </c>
       <c r="P144" s="10" t="inlineStr"/>
-      <c r="Q144" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Jacob%20Aswad%20Rino%20Construction","search")</f>
-        <v/>
-      </c>
+      <c r="Q144" s="12" t="inlineStr"/>
       <c r="R144" s="16">
         <f>IF(P144="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -17240,10 +17399,22 @@
         </is>
       </c>
       <c r="U144" s="12" t="inlineStr"/>
-      <c r="V144" s="15" t="inlineStr"/>
-      <c r="W144" s="12" t="inlineStr"/>
+      <c r="V144" s="15" t="inlineStr">
+        <is>
+          <t>The firm's own leadership page carries the title.</t>
+        </is>
+      </c>
+      <c r="W144" s="12" t="inlineStr">
+        <is>
+          <t>https://rino-con.com/leadership/</t>
+        </is>
+      </c>
       <c r="X144" s="12" t="inlineStr"/>
-      <c r="Y144" s="12" t="inlineStr"/>
+      <c r="Y144" s="12" t="inlineStr">
+        <is>
+          <t>https://rino-con.com/leadership/</t>
+        </is>
+      </c>
       <c r="Z144" s="12" t="inlineStr"/>
       <c r="AA144" s="12" t="inlineStr">
         <is>
@@ -17274,7 +17445,7 @@
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>Vice President, named on the firm's own leadership page</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="D145" s="7" t="inlineStr">
@@ -17336,10 +17507,7 @@
         </is>
       </c>
       <c r="P145" s="10" t="inlineStr"/>
-      <c r="Q145" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Justin%20Henderson%20Rino%20Construction","search")</f>
-        <v/>
-      </c>
+      <c r="Q145" s="6" t="inlineStr"/>
       <c r="R145" s="11">
         <f>IF(P145="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -17355,10 +17523,22 @@
         </is>
       </c>
       <c r="U145" s="6" t="inlineStr"/>
-      <c r="V145" s="9" t="inlineStr"/>
-      <c r="W145" s="6" t="inlineStr"/>
+      <c r="V145" s="9" t="inlineStr">
+        <is>
+          <t>The firm's own leadership page carries the title.</t>
+        </is>
+      </c>
+      <c r="W145" s="6" t="inlineStr">
+        <is>
+          <t>https://rino-con.com/leadership/</t>
+        </is>
+      </c>
       <c r="X145" s="6" t="inlineStr"/>
-      <c r="Y145" s="6" t="inlineStr"/>
+      <c r="Y145" s="6" t="inlineStr">
+        <is>
+          <t>https://rino-con.com/leadership/</t>
+        </is>
+      </c>
       <c r="Z145" s="6" t="inlineStr"/>
       <c r="AA145" s="6" t="inlineStr">
         <is>
@@ -17478,7 +17658,11 @@
       </c>
       <c r="W146" s="12" t="inlineStr"/>
       <c r="X146" s="12" t="inlineStr"/>
-      <c r="Y146" s="12" t="inlineStr"/>
+      <c r="Y146" s="12" t="inlineStr">
+        <is>
+          <t>https://rino-con.com/leadership/</t>
+        </is>
+      </c>
       <c r="Z146" s="12" t="inlineStr"/>
       <c r="AA146" s="12" t="inlineStr">
         <is>
@@ -17598,7 +17782,11 @@
       </c>
       <c r="W147" s="6" t="inlineStr"/>
       <c r="X147" s="6" t="inlineStr"/>
-      <c r="Y147" s="6" t="inlineStr"/>
+      <c r="Y147" s="6" t="inlineStr">
+        <is>
+          <t>https://rino-con.com/leadership/</t>
+        </is>
+      </c>
       <c r="Z147" s="6" t="inlineStr"/>
       <c r="AA147" s="6" t="inlineStr">
         <is>
@@ -19658,7 +19846,7 @@
       </c>
       <c r="C165" s="6" t="inlineStr">
         <is>
-          <t>Third generation, took leadership in 2001, named on the firm's own about page</t>
+          <t>Third generation, assumed leadership in 2001</t>
         </is>
       </c>
       <c r="D165" s="7" t="inlineStr">
@@ -19720,10 +19908,7 @@
         </is>
       </c>
       <c r="P165" s="10" t="inlineStr"/>
-      <c r="Q165" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Ryan%20Taylor%20T%26T%20Construction","search")</f>
-        <v/>
-      </c>
+      <c r="Q165" s="6" t="inlineStr"/>
       <c r="R165" s="11">
         <f>IF(P165="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -19739,10 +19924,22 @@
         </is>
       </c>
       <c r="U165" s="6" t="inlineStr"/>
-      <c r="V165" s="9" t="inlineStr"/>
-      <c r="W165" s="6" t="inlineStr"/>
+      <c r="V165" s="9" t="inlineStr">
+        <is>
+          <t>The firm's own about page: C.A. Taylor started the firm in Pasadena in 1969, his son Jeff joined and it became Taylor and Taylor, and Jeff's son Ryan joined in 1988 and assumed leadership in 2001. The page uses first names after the founder and does not print the surname beside Ryan.</t>
+        </is>
+      </c>
+      <c r="W165" s="6" t="inlineStr">
+        <is>
+          <t>https://tandtconstruction.com/about-us/</t>
+        </is>
+      </c>
       <c r="X165" s="6" t="inlineStr"/>
-      <c r="Y165" s="6" t="inlineStr"/>
+      <c r="Y165" s="6" t="inlineStr">
+        <is>
+          <t>https://tandtconstruction.com/about-us/</t>
+        </is>
+      </c>
       <c r="Z165" s="6" t="inlineStr"/>
       <c r="AA165" s="6" t="inlineStr">
         <is>
@@ -19769,7 +19966,7 @@
       </c>
       <c r="C166" s="12" t="inlineStr">
         <is>
-          <t>Second-generation co-owner, named on the firm's own about page</t>
+          <t>Second-generation co-owner</t>
         </is>
       </c>
       <c r="D166" s="13" t="inlineStr">
@@ -19831,10 +20028,7 @@
         </is>
       </c>
       <c r="P166" s="10" t="inlineStr"/>
-      <c r="Q166" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Jeff%20Taylor%20T%26T%20Construction","search")</f>
-        <v/>
-      </c>
+      <c r="Q166" s="12" t="inlineStr"/>
       <c r="R166" s="16">
         <f>IF(P166="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -19850,10 +20044,22 @@
         </is>
       </c>
       <c r="U166" s="12" t="inlineStr"/>
-      <c r="V166" s="15" t="inlineStr"/>
-      <c r="W166" s="12" t="inlineStr"/>
+      <c r="V166" s="15" t="inlineStr">
+        <is>
+          <t>The firm's own about page: Jeff and his wife Dianna continued the family business as co-owners. The page uses first names after the founder.</t>
+        </is>
+      </c>
+      <c r="W166" s="12" t="inlineStr">
+        <is>
+          <t>https://tandtconstruction.com/about-us/</t>
+        </is>
+      </c>
       <c r="X166" s="12" t="inlineStr"/>
-      <c r="Y166" s="12" t="inlineStr"/>
+      <c r="Y166" s="12" t="inlineStr">
+        <is>
+          <t>https://tandtconstruction.com/about-us/</t>
+        </is>
+      </c>
       <c r="Z166" s="12" t="inlineStr"/>
       <c r="AA166" s="12" t="inlineStr">
         <is>
@@ -19880,7 +20086,7 @@
       </c>
       <c r="C167" s="6" t="inlineStr">
         <is>
-          <t>Second-generation co-owner, named on the firm's own about page</t>
+          <t>Second-generation co-owner</t>
         </is>
       </c>
       <c r="D167" s="7" t="inlineStr">
@@ -19942,10 +20148,7 @@
         </is>
       </c>
       <c r="P167" s="10" t="inlineStr"/>
-      <c r="Q167" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Dianna%20Taylor%20T%26T%20Construction","search")</f>
-        <v/>
-      </c>
+      <c r="Q167" s="6" t="inlineStr"/>
       <c r="R167" s="11">
         <f>IF(P167="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -19961,10 +20164,22 @@
         </is>
       </c>
       <c r="U167" s="6" t="inlineStr"/>
-      <c r="V167" s="9" t="inlineStr"/>
-      <c r="W167" s="6" t="inlineStr"/>
+      <c r="V167" s="9" t="inlineStr">
+        <is>
+          <t>The firm's own about page: Jeff and his wife Dianna continued the family business as co-owners. The page uses first names after the founder.</t>
+        </is>
+      </c>
+      <c r="W167" s="6" t="inlineStr">
+        <is>
+          <t>https://tandtconstruction.com/about-us/</t>
+        </is>
+      </c>
       <c r="X167" s="6" t="inlineStr"/>
-      <c r="Y167" s="6" t="inlineStr"/>
+      <c r="Y167" s="6" t="inlineStr">
+        <is>
+          <t>https://tandtconstruction.com/about-us/</t>
+        </is>
+      </c>
       <c r="Z167" s="6" t="inlineStr"/>
       <c r="AA167" s="6" t="inlineStr">
         <is>
@@ -19991,7 +20206,7 @@
       </c>
       <c r="C168" s="12" t="inlineStr">
         <is>
-          <t>Founder, named on the firm's own about page as having started the firm in 2003</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="D168" s="13" t="inlineStr">
@@ -20053,10 +20268,7 @@
         </is>
       </c>
       <c r="P168" s="10" t="inlineStr"/>
-      <c r="Q168" s="12">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Victor%20Andrade%20Andrade%20Construction%20Companies","search")</f>
-        <v/>
-      </c>
+      <c r="Q168" s="12" t="inlineStr"/>
       <c r="R168" s="16">
         <f>IF(P168="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -20072,8 +20284,16 @@
         </is>
       </c>
       <c r="U168" s="12" t="inlineStr"/>
-      <c r="V168" s="15" t="inlineStr"/>
-      <c r="W168" s="12" t="inlineStr"/>
+      <c r="V168" s="15" t="inlineStr">
+        <is>
+          <t>The firm's own about page: founded by Victor Andrade in 2003 in residential construction, into commercial in 2013.</t>
+        </is>
+      </c>
+      <c r="W168" s="12" t="inlineStr">
+        <is>
+          <t>http://andradeconstructioncompanies.com/about-us/</t>
+        </is>
+      </c>
       <c r="X168" s="12" t="inlineStr"/>
       <c r="Y168" s="12" t="inlineStr"/>
       <c r="Z168" s="12" t="inlineStr"/>
@@ -20810,7 +21030,7 @@
       </c>
       <c r="C175" s="6" t="inlineStr">
         <is>
-          <t>Owner, named on the firm's own about page, after eighteen years selling ready-mix to the largest general contractors in Houston</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="D175" s="7" t="inlineStr">
@@ -20872,10 +21092,7 @@
         </is>
       </c>
       <c r="P175" s="10" t="inlineStr"/>
-      <c r="Q175" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Trent%20Mitchell%20Silver%20Spur%20Concrete%20Contractors","search")</f>
-        <v/>
-      </c>
+      <c r="Q175" s="6" t="inlineStr"/>
       <c r="R175" s="11">
         <f>IF(P175="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -20895,10 +21112,22 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="V175" s="9" t="inlineStr"/>
-      <c r="W175" s="6" t="inlineStr"/>
+      <c r="V175" s="9" t="inlineStr">
+        <is>
+          <t>The firm's own about page names him as owner and lists ExxonMobil World Headquarters, the Texas Children's maternity ward and Baylor College of Medicine among his commercial and industrial work.</t>
+        </is>
+      </c>
+      <c r="W175" s="6" t="inlineStr">
+        <is>
+          <t>https://www.silverspurconcrete.com/about-silver-spur-concrete-contractors/</t>
+        </is>
+      </c>
       <c r="X175" s="6" t="inlineStr"/>
-      <c r="Y175" s="6" t="inlineStr"/>
+      <c r="Y175" s="6" t="inlineStr">
+        <is>
+          <t>https://www.silverspurconcrete.com/about-silver-spur-concrete-contractors/</t>
+        </is>
+      </c>
       <c r="Z175" s="6" t="inlineStr"/>
       <c r="AA175" s="6" t="inlineStr">
         <is>
@@ -33618,7 +33847,7 @@
     <row r="284">
       <c r="A284" s="17" t="inlineStr">
         <is>
-          <t>NOTE. A filled LinkedIn cell means the profile was opened or the search result read and the headline named the firm; column W records what was read. Where that test failed the cell is left empty rather than guessed, because a fabricated slug passes visual inspection and then fails in front of the person it names. Column Q searches for the empty ones in your own session. Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Capital is a qualifier, not a count. Source: ICON Greater Houston screen, build 59, 2026-09-11.</t>
+          <t>NOTE. A filled LinkedIn cell means the profile was opened or the search result read and the headline named the firm; column W records what was read. Where that test failed the cell is left empty rather than guessed, because a fabricated slug passes visual inspection and then fails in front of the person it names. Column Q searches for the empty ones in your own session. Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Capital is a qualifier, not a count. Source: ICON Greater Houston screen, build 60, 2026-09-11.</t>
         </is>
       </c>
     </row>

--- a/docs/ICON_Greater_Houston_Rolodex.xlsx
+++ b/docs/ICON_Greater_Houston_Rolodex.xlsx
@@ -585,7 +585,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated from houston-data.json · build 60 · 2026-09-11 · public render. Do not hand-edit the HTML deck; it regenerates from the same file.</t>
+          <t>Generated from houston-data.json · build 61 · 2026-09-11 · public render. Do not hand-edit the HTML deck; it regenerates from the same file.</t>
         </is>
       </c>
     </row>
@@ -33847,7 +33847,7 @@
     <row r="284">
       <c r="A284" s="17" t="inlineStr">
         <is>
-          <t>NOTE. A filled LinkedIn cell means the profile was opened or the search result read and the headline named the firm; column W records what was read. Where that test failed the cell is left empty rather than guessed, because a fabricated slug passes visual inspection and then fails in front of the person it names. Column Q searches for the empty ones in your own session. Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Capital is a qualifier, not a count. Source: ICON Greater Houston screen, build 60, 2026-09-11.</t>
+          <t>NOTE. A filled LinkedIn cell means the profile was opened or the search result read and the headline named the firm; column W records what was read. Where that test failed the cell is left empty rather than guessed, because a fabricated slug passes visual inspection and then fails in front of the person it names. Column Q searches for the empty ones in your own session. Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Capital is a qualifier, not a count. Source: ICON Greater Houston screen, build 61, 2026-09-11.</t>
         </is>
       </c>
     </row>

--- a/docs/ICON_Greater_Houston_Rolodex.xlsx
+++ b/docs/ICON_Greater_Houston_Rolodex.xlsx
@@ -585,7 +585,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated from houston-data.json · build 63 · 2026-09-11 · public render. Do not hand-edit the HTML deck; it regenerates from the same file.</t>
+          <t>Generated from houston-data.json · build 64 · 2026-09-11 · public render. Do not hand-edit the HTML deck; it regenerates from the same file.</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="T9" s="9" t="inlineStr">
         <is>
-          <t>23 of 26 homes printed. Owner cites 50 percent faster and 5 to 7 percent cheaper. HiveASMBLD supplies it.</t>
+          <t>The owner cites 50 percent faster and 5 to 7 percent cheaper. HiveASMBLD supplies it.</t>
         </is>
       </c>
       <c r="U9" s="6" t="inlineStr"/>
@@ -1615,7 +1615,7 @@
       <c r="U13" s="6" t="inlineStr"/>
       <c r="V13" s="9" t="inlineStr">
         <is>
-          <t>The closest published seat to construction. Wan Bridge names seven leaders and none of them holds construction or purchasing.</t>
+          <t>Wan Bridge names seven leaders and none of them holds construction or purchasing.</t>
         </is>
       </c>
       <c r="W13" s="6" t="inlineStr">
@@ -10208,7 +10208,7 @@
       <c r="U84" s="12" t="inlineStr"/>
       <c r="V84" s="15" t="inlineStr">
         <is>
-          <t>The closest published seat to how the houses get built. Avenue names no construction officer.</t>
+          <t>Avenue names no construction officer on its staff page.</t>
         </is>
       </c>
       <c r="W84" s="12" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="T91" s="9" t="inlineStr">
         <is>
-          <t>More than 4,000 homes since 1993, which averages above 100 a year, across a small set of communities in one corridor. A named vice president of construction.</t>
+          <t>Above 100 homes a year on average, across a small set of communities in one corridor. A named vice president of construction.</t>
         </is>
       </c>
       <c r="U91" s="6" t="inlineStr"/>
@@ -14011,7 +14011,7 @@
       </c>
       <c r="T116" s="15" t="inlineStr">
         <is>
-          <t>The closest business model on this deck to selling printed wall: an automated plant making wall for Houston production builders, at a size one or two machines would actually cover.</t>
+          <t>An automated plant making wall for Houston production builders, at a size one or two machines would cover.</t>
         </is>
       </c>
       <c r="U116" s="12" t="inlineStr">
@@ -14135,7 +14135,7 @@
       </c>
       <c r="T117" s="9" t="inlineStr">
         <is>
-          <t>The closest business model on this deck to selling printed wall: an automated plant making wall for Houston production builders, at a size one or two machines would actually cover.</t>
+          <t>An automated plant making wall for Houston production builders, at a size one or two machines would cover.</t>
         </is>
       </c>
       <c r="U117" s="6" t="inlineStr">
@@ -14259,7 +14259,7 @@
       </c>
       <c r="T118" s="15" t="inlineStr">
         <is>
-          <t>The closest business model on this deck to selling printed wall: an automated plant making wall for Houston production builders, at a size one or two machines would actually cover.</t>
+          <t>An automated plant making wall for Houston production builders, at a size one or two machines would cover.</t>
         </is>
       </c>
       <c r="U118" s="12" t="inlineStr"/>
@@ -14379,7 +14379,7 @@
       </c>
       <c r="T119" s="9" t="inlineStr">
         <is>
-          <t>The closest business model on this deck to selling printed wall: an automated plant making wall for Houston production builders, at a size one or two machines would actually cover.</t>
+          <t>An automated plant making wall for Houston production builders, at a size one or two machines would cover.</t>
         </is>
       </c>
       <c r="U119" s="6" t="inlineStr"/>
@@ -15483,7 +15483,7 @@
       </c>
       <c r="T128" s="15" t="inlineStr">
         <is>
-          <t>The closest published language on this deck to the firm a printer would sell into: turn-key concrete, for residential production builders, in Houston.</t>
+          <t>Turn-key concrete for residential production builders in Houston, in the firm's own words.</t>
         </is>
       </c>
       <c r="U128" s="12" t="inlineStr">
@@ -15603,7 +15603,7 @@
       </c>
       <c r="T129" s="9" t="inlineStr">
         <is>
-          <t>The closest published language on this deck to the firm a printer would sell into: turn-key concrete, for residential production builders, in Houston.</t>
+          <t>Turn-key concrete for residential production builders in Houston, in the firm's own words.</t>
         </is>
       </c>
       <c r="U129" s="6" t="inlineStr"/>
@@ -16306,7 +16306,7 @@
       </c>
       <c r="N135" s="9" t="inlineStr">
         <is>
-          <t>It built and staffed a prefabrication plant producing wall panels and interior components offsite, and publishes what that saved on a hospital project. That is paying to move wall work into a factory, which is the nearest thing to the argument for a printer.</t>
+          <t>It built and staffed a prefabrication plant producing wall panels and interior components offsite, and publishes what that saved on a hospital project. That is paying to move wall work into a factory.</t>
         </is>
       </c>
       <c r="O135" s="8" t="inlineStr">
@@ -16430,7 +16430,7 @@
       </c>
       <c r="N136" s="15" t="inlineStr">
         <is>
-          <t>It built and staffed a prefabrication plant producing wall panels and interior components offsite, and publishes what that saved on a hospital project. That is paying to move wall work into a factory, which is the nearest thing to the argument for a printer.</t>
+          <t>It built and staffed a prefabrication plant producing wall panels and interior components offsite, and publishes what that saved on a hospital project. That is paying to move wall work into a factory.</t>
         </is>
       </c>
       <c r="O136" s="14" t="inlineStr">
@@ -16549,7 +16549,7 @@
       </c>
       <c r="N137" s="9" t="inlineStr">
         <is>
-          <t>It built and staffed a prefabrication plant producing wall panels and interior components offsite, and publishes what that saved on a hospital project. That is paying to move wall work into a factory, which is the nearest thing to the argument for a printer.</t>
+          <t>It built and staffed a prefabrication plant producing wall panels and interior components offsite, and publishes what that saved on a hospital project. That is paying to move wall work into a factory.</t>
         </is>
       </c>
       <c r="O137" s="8" t="inlineStr">
@@ -16668,7 +16668,7 @@
       </c>
       <c r="N138" s="15" t="inlineStr">
         <is>
-          <t>It built and staffed a prefabrication plant producing wall panels and interior components offsite, and publishes what that saved on a hospital project. That is paying to move wall work into a factory, which is the nearest thing to the argument for a printer.</t>
+          <t>It built and staffed a prefabrication plant producing wall panels and interior components offsite, and publishes what that saved on a hospital project. That is paying to move wall work into a factory.</t>
         </is>
       </c>
       <c r="O138" s="14" t="inlineStr">
@@ -16916,7 +16916,7 @@
       </c>
       <c r="T140" s="15" t="inlineStr">
         <is>
-          <t>The closest thing in Texas to a precast producer running a volumetric line, with a general manager on record wanting to widen what the plant makes.</t>
+          <t>A precast producer running a volumetric modular line, with a general manager on record wanting to widen what the plant makes.</t>
         </is>
       </c>
       <c r="U140" s="12" t="inlineStr"/>
@@ -17032,7 +17032,7 @@
       </c>
       <c r="T141" s="9" t="inlineStr">
         <is>
-          <t>The closest thing in Texas to a precast producer running a volumetric line, with a general manager on record wanting to widen what the plant makes.</t>
+          <t>A precast producer running a volumetric modular line, with a general manager on record wanting to widen what the plant makes.</t>
         </is>
       </c>
       <c r="U141" s="6" t="inlineStr">
@@ -17651,7 +17651,7 @@
       </c>
       <c r="T146" s="15" t="inlineStr">
         <is>
-          <t>The nearest thing in Greater Houston to a printing operation that already exists: a batch plant, casting beds, a QC regime and a business built on making structural wall somewhere other than the site.</t>
+          <t>A batch plant, casting beds, a quality regime, and a business built on making structural wall somewhere other than the site.</t>
         </is>
       </c>
       <c r="U146" s="12" t="inlineStr">
@@ -17771,7 +17771,7 @@
       </c>
       <c r="T147" s="9" t="inlineStr">
         <is>
-          <t>The nearest thing in Greater Houston to a printing operation that already exists: a batch plant, casting beds, a QC regime and a business built on making structural wall somewhere other than the site.</t>
+          <t>A batch plant, casting beds, a quality regime, and a business built on making structural wall somewhere other than the site.</t>
         </is>
       </c>
       <c r="U147" s="6" t="inlineStr"/>
@@ -19207,7 +19207,7 @@
       </c>
       <c r="T159" s="9" t="inlineStr">
         <is>
-          <t>The only precast producer screened whose own staffing names Houston and multifamily in the same title, which is the closest this cell gets to residential structure.</t>
+          <t>The only precast producer screened whose own staffing names Houston and multifamily in one title.</t>
         </is>
       </c>
       <c r="U159" s="6" t="inlineStr"/>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="T160" s="15" t="inlineStr">
         <is>
-          <t>The only precast producer screened whose own staffing names Houston and multifamily in the same title, which is the closest this cell gets to residential structure.</t>
+          <t>The only precast producer screened whose own staffing names Houston and multifamily in one title.</t>
         </is>
       </c>
       <c r="U160" s="12" t="inlineStr"/>
@@ -19442,7 +19442,7 @@
       </c>
       <c r="T161" s="9" t="inlineStr">
         <is>
-          <t>The only precast producer screened whose own staffing names Houston and multifamily in the same title, which is the closest this cell gets to residential structure.</t>
+          <t>The only precast producer screened whose own staffing names Houston and multifamily in one title.</t>
         </is>
       </c>
       <c r="U161" s="6" t="inlineStr"/>
@@ -19562,7 +19562,7 @@
       </c>
       <c r="T162" s="15" t="inlineStr">
         <is>
-          <t>The only precast producer screened whose own staffing names Houston and multifamily in the same title, which is the closest this cell gets to residential structure.</t>
+          <t>The only precast producer screened whose own staffing names Houston and multifamily in one title.</t>
         </is>
       </c>
       <c r="U162" s="12" t="inlineStr"/>
@@ -23070,7 +23070,7 @@
       </c>
       <c r="T191" s="9" t="inlineStr">
         <is>
-          <t>Two award-listed tilt-up jobs in Houston, one at 79 panels and 52,116 square feet of wall. Panels repeat; the buildings behind them do not.</t>
+          <t>Two award-listed tilt-up jobs in Houston. Panels repeat; the buildings behind them do not.</t>
         </is>
       </c>
       <c r="U191" s="6" t="inlineStr">
@@ -23190,7 +23190,7 @@
       </c>
       <c r="T192" s="15" t="inlineStr">
         <is>
-          <t>Two award-listed tilt-up jobs in Houston, one at 79 panels and 52,116 square feet of wall. Panels repeat; the buildings behind them do not.</t>
+          <t>Two award-listed tilt-up jobs in Houston. Panels repeat; the buildings behind them do not.</t>
         </is>
       </c>
       <c r="U192" s="12" t="inlineStr"/>
@@ -23306,7 +23306,7 @@
       </c>
       <c r="T193" s="9" t="inlineStr">
         <is>
-          <t>Two award-listed tilt-up jobs in Houston, one at 79 panels and 52,116 square feet of wall. Panels repeat; the buildings behind them do not.</t>
+          <t>Two award-listed tilt-up jobs in Houston. Panels repeat; the buildings behind them do not.</t>
         </is>
       </c>
       <c r="U193" s="6" t="inlineStr"/>
@@ -24498,7 +24498,7 @@
       </c>
       <c r="T203" s="9" t="inlineStr">
         <is>
-          <t>Named on a 61-panel job at 70 feet, with the heaviest panel at about 87 tons. That is the top of what the trade attempts here. The firm is national.</t>
+          <t>The top of what the trade attempts here. The firm is national.</t>
         </is>
       </c>
       <c r="U203" s="6" t="inlineStr">
@@ -24622,7 +24622,7 @@
       </c>
       <c r="T204" s="15" t="inlineStr">
         <is>
-          <t>Named on a 61-panel job at 70 feet, with the heaviest panel at about 87 tons. That is the top of what the trade attempts here. The firm is national.</t>
+          <t>The top of what the trade attempts here. The firm is national.</t>
         </is>
       </c>
       <c r="U204" s="12" t="inlineStr"/>
@@ -24738,7 +24738,7 @@
       </c>
       <c r="T205" s="9" t="inlineStr">
         <is>
-          <t>Named on a 61-panel job at 70 feet, with the heaviest panel at about 87 tons. That is the top of what the trade attempts here. The firm is national.</t>
+          <t>The top of what the trade attempts here. The firm is national.</t>
         </is>
       </c>
       <c r="U205" s="6" t="inlineStr"/>
@@ -24823,7 +24823,7 @@
       </c>
       <c r="L206" s="15" t="inlineStr">
         <is>
-          <t>Ten thousand slabs a year is far beyond what one or two printers would cover. A machine would be a pilot line inside a very large business.</t>
+          <t>Ten thousand slabs a year is far beyond what one or two printers would cover. A machine would be a pilot line, not a replacement for the slab business.</t>
         </is>
       </c>
       <c r="M206" s="14" t="inlineStr">
@@ -24947,7 +24947,7 @@
       </c>
       <c r="L207" s="9" t="inlineStr">
         <is>
-          <t>Ten thousand slabs a year is far beyond what one or two printers would cover. A machine would be a pilot line inside a very large business.</t>
+          <t>Ten thousand slabs a year is far beyond what one or two printers would cover. A machine would be a pilot line, not a replacement for the slab business.</t>
         </is>
       </c>
       <c r="M207" s="8" t="inlineStr">
@@ -25063,7 +25063,7 @@
       </c>
       <c r="L208" s="15" t="inlineStr">
         <is>
-          <t>Ten thousand slabs a year is far beyond what one or two printers would cover. A machine would be a pilot line inside a very large business.</t>
+          <t>Ten thousand slabs a year is far beyond what one or two printers would cover. A machine would be a pilot line, not a replacement for the slab business.</t>
         </is>
       </c>
       <c r="M208" s="14" t="inlineStr">
@@ -25224,7 +25224,7 @@
       <c r="U209" s="6" t="inlineStr"/>
       <c r="V209" s="9" t="inlineStr">
         <is>
-          <t>His profile headline names Trussway Manufacturing as a Builders FirstSource company, so it is current. An assistant general manager is below the bar this deck sets for a decision-maker, and he is the only plant-level leader the firm could be shown to have: trussway.com presents a certificate chain that fails verification through every route, so nothing on it could be read.</t>
+          <t>His profile headline names Trussway Manufacturing as a Builders FirstSource company, so it is current. An assistant general manager is below the bar this deck sets for a decision-maker. He is also the only plant-level leader the firm could be shown to have. trussway.com presents a certificate chain that fails verification through every route, so nothing on it could be read.</t>
         </is>
       </c>
       <c r="W209" s="6" t="inlineStr"/>
@@ -40578,7 +40578,7 @@
     <row r="340">
       <c r="A340" s="17" t="inlineStr">
         <is>
-          <t>NOTE. A filled LinkedIn cell means the profile was opened or the search result read and the headline named the firm; column W records what was read. Where that test failed the cell is left empty rather than guessed, because a fabricated slug passes visual inspection and then fails in front of the person it names. Column Q searches for the empty ones in your own session. Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Capital is a qualifier, not a count. Source: ICON Greater Houston screen, build 63, 2026-09-11.</t>
+          <t>NOTE. A filled LinkedIn cell means the profile was opened or the search result read and the headline named the firm; column W records what was read. Where that test failed the cell is left empty rather than guessed, because a fabricated slug passes visual inspection and then fails in front of the person it names. Column Q searches for the empty ones in your own session. Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Capital is a qualifier, not a count. Source: ICON Greater Houston screen, build 64, 2026-09-11.</t>
         </is>
       </c>
     </row>

--- a/docs/ICON_Greater_Houston_Rolodex.xlsx
+++ b/docs/ICON_Greater_Houston_Rolodex.xlsx
@@ -18263,7 +18263,7 @@
       </c>
       <c r="H155" s="6" t="inlineStr">
         <is>
-          <t>Serving the Texas market since 1988</t>
+          <t>The group's only Texas plant</t>
         </is>
       </c>
       <c r="I155" s="8" t="inlineStr">
@@ -18380,7 +18380,7 @@
       </c>
       <c r="H156" s="12" t="inlineStr">
         <is>
-          <t>Serving the Texas market since 1988</t>
+          <t>The group's only Texas plant</t>
         </is>
       </c>
       <c r="I156" s="14" t="inlineStr">
@@ -18497,7 +18497,7 @@
       </c>
       <c r="H157" s="6" t="inlineStr">
         <is>
-          <t>Serving the Texas market since 1988</t>
+          <t>The group's only Texas plant</t>
         </is>
       </c>
       <c r="I157" s="8" t="inlineStr">
@@ -20603,7 +20603,7 @@
       </c>
       <c r="H175" s="6" t="inlineStr">
         <is>
-          <t>Employee-owned, established in 2017</t>
+          <t>Employee-owned, and lists elevated multifamily as a project type</t>
         </is>
       </c>
       <c r="I175" s="8" t="inlineStr">
@@ -20720,7 +20720,7 @@
       </c>
       <c r="H176" s="12" t="inlineStr">
         <is>
-          <t>Employee-owned, established in 2017</t>
+          <t>Employee-owned, and lists elevated multifamily as a project type</t>
         </is>
       </c>
       <c r="I176" s="14" t="inlineStr">
@@ -36112,7 +36112,7 @@
       </c>
       <c r="H306" s="12" t="inlineStr">
         <is>
-          <t>More than 60 years of masterplans, and Lennar builds</t>
+          <t>Sells lots inside its own masterplans, and Lennar builds</t>
         </is>
       </c>
       <c r="I306" s="14" t="inlineStr">

--- a/docs/ICON_Greater_Houston_Rolodex.xlsx
+++ b/docs/ICON_Greater_Houston_Rolodex.xlsx
@@ -1144,7 +1144,7 @@
       </c>
       <c r="V9" s="6" t="inlineStr">
         <is>
-          <t>https://www.galvnews.com/news/printing-the-future-san-leon-project-tests-new-model-for-coastal-housing/article_e6c622f8-f6cd-47f6-ad36-ed1cac45a3d4.html</t>
+          <t>https://www.homes.com/news/houstons-3d-printed-housing-push-grows-with-two-new-developments/647676272/</t>
         </is>
       </c>
       <c r="W9" s="6" t="inlineStr"/>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="Y11" s="6" t="inlineStr">
         <is>
-          <t>2026-04-25 Houston Chronicle. Why Houston's booming build-to-rent sector could slow  https://www.houstonchronicle.com/business/article/houston-build-to-rent-housing-21293194.php</t>
+          <t>2025-11-24 Realty News Report. Build-To-Rent Boom: Dellrose, Yardly and More  https://realtynewsreport.com/build-to-rent-boom-dellrose-yardly-and-more/</t>
         </is>
       </c>
       <c r="Z11" s="6" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="Y12" s="12" t="inlineStr">
         <is>
-          <t>2026-04-25 Houston Chronicle. Why Houston's booming build-to-rent sector could slow  https://www.houstonchronicle.com/business/article/houston-build-to-rent-housing-21293194.php</t>
+          <t>2025-11-24 Realty News Report. Build-To-Rent Boom: Dellrose, Yardly and More  https://realtynewsreport.com/build-to-rent-boom-dellrose-yardly-and-more/</t>
         </is>
       </c>
       <c r="Z12" s="12" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="Y13" s="6" t="inlineStr">
         <is>
-          <t>2026-04-25 Houston Chronicle. Why Houston's booming build-to-rent sector could slow  https://www.houstonchronicle.com/business/article/houston-build-to-rent-housing-21293194.php</t>
+          <t>2025-11-24 Realty News Report. Build-To-Rent Boom: Dellrose, Yardly and More  https://realtynewsreport.com/build-to-rent-boom-dellrose-yardly-and-more/</t>
         </is>
       </c>
       <c r="Z13" s="6" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="Y14" s="12" t="inlineStr">
         <is>
-          <t>2026-04-25 Houston Chronicle. Why Houston's booming build-to-rent sector could slow  https://www.houstonchronicle.com/business/article/houston-build-to-rent-housing-21293194.php</t>
+          <t>2025-11-24 Realty News Report. Build-To-Rent Boom: Dellrose, Yardly and More  https://realtynewsreport.com/build-to-rent-boom-dellrose-yardly-and-more/</t>
         </is>
       </c>
       <c r="Z14" s="12" t="inlineStr">
@@ -19152,11 +19152,7 @@
           <t>https://www.harveycleary.com/about-us/</t>
         </is>
       </c>
-      <c r="Y162" s="12" t="inlineStr">
-        <is>
-          <t>2026 Engineering News-Record. ENR 2026 Top 400 Contractors, where the firm is ranked 72  https://www.enr.com/toplists/2026-Top-400-Contractors-1</t>
-        </is>
-      </c>
+      <c r="Y162" s="12" t="inlineStr"/>
       <c r="Z162" s="12" t="inlineStr"/>
       <c r="AA162" s="12" t="inlineStr"/>
       <c r="AB162" s="12" t="inlineStr"/>
@@ -19265,11 +19261,7 @@
           <t>https://www.harveycleary.com/about-us/</t>
         </is>
       </c>
-      <c r="Y163" s="6" t="inlineStr">
-        <is>
-          <t>2026 Engineering News-Record. ENR 2026 Top 400 Contractors, where the firm is ranked 72  https://www.enr.com/toplists/2026-Top-400-Contractors-1</t>
-        </is>
-      </c>
+      <c r="Y163" s="6" t="inlineStr"/>
       <c r="Z163" s="6" t="inlineStr"/>
       <c r="AA163" s="6" t="inlineStr"/>
       <c r="AB163" s="6" t="inlineStr"/>
@@ -19378,11 +19370,7 @@
           <t>https://www.harveycleary.com/about-us/</t>
         </is>
       </c>
-      <c r="Y164" s="12" t="inlineStr">
-        <is>
-          <t>2026 Engineering News-Record. ENR 2026 Top 400 Contractors, where the firm is ranked 72  https://www.enr.com/toplists/2026-Top-400-Contractors-1</t>
-        </is>
-      </c>
+      <c r="Y164" s="12" t="inlineStr"/>
       <c r="Z164" s="12" t="inlineStr"/>
       <c r="AA164" s="12" t="inlineStr"/>
       <c r="AB164" s="12" t="inlineStr"/>
@@ -19495,11 +19483,7 @@
           <t>https://www.harveycleary.com/about-us/</t>
         </is>
       </c>
-      <c r="Y165" s="6" t="inlineStr">
-        <is>
-          <t>2026 Engineering News-Record. ENR 2026 Top 400 Contractors, where the firm is ranked 72  https://www.enr.com/toplists/2026-Top-400-Contractors-1</t>
-        </is>
-      </c>
+      <c r="Y165" s="6" t="inlineStr"/>
       <c r="Z165" s="6" t="inlineStr"/>
       <c r="AA165" s="6" t="inlineStr"/>
       <c r="AB165" s="6" t="inlineStr"/>
@@ -19608,11 +19592,7 @@
           <t>https://www.harveycleary.com/about-us/</t>
         </is>
       </c>
-      <c r="Y166" s="12" t="inlineStr">
-        <is>
-          <t>2026 Engineering News-Record. ENR 2026 Top 400 Contractors, where the firm is ranked 72  https://www.enr.com/toplists/2026-Top-400-Contractors-1</t>
-        </is>
-      </c>
+      <c r="Y166" s="12" t="inlineStr"/>
       <c r="Z166" s="12" t="inlineStr"/>
       <c r="AA166" s="12" t="inlineStr"/>
       <c r="AB166" s="12" t="inlineStr"/>

--- a/docs/ICON_Greater_Houston_Rolodex.xlsx
+++ b/docs/ICON_Greater_Houston_Rolodex.xlsx
@@ -19152,7 +19152,11 @@
           <t>https://www.harveycleary.com/about-us/</t>
         </is>
       </c>
-      <c r="Y162" s="12" t="inlineStr"/>
+      <c r="Y162" s="12" t="inlineStr">
+        <is>
+          <t>2026 Engineering News-Record. ENR 2026 Top 400 Contractors, where the firm is ranked 72  https://www.enr.com/toplists/2026-Top-400-Contractors-1</t>
+        </is>
+      </c>
       <c r="Z162" s="12" t="inlineStr"/>
       <c r="AA162" s="12" t="inlineStr"/>
       <c r="AB162" s="12" t="inlineStr"/>
@@ -19261,7 +19265,11 @@
           <t>https://www.harveycleary.com/about-us/</t>
         </is>
       </c>
-      <c r="Y163" s="6" t="inlineStr"/>
+      <c r="Y163" s="6" t="inlineStr">
+        <is>
+          <t>2026 Engineering News-Record. ENR 2026 Top 400 Contractors, where the firm is ranked 72  https://www.enr.com/toplists/2026-Top-400-Contractors-1</t>
+        </is>
+      </c>
       <c r="Z163" s="6" t="inlineStr"/>
       <c r="AA163" s="6" t="inlineStr"/>
       <c r="AB163" s="6" t="inlineStr"/>
@@ -19370,7 +19378,11 @@
           <t>https://www.harveycleary.com/about-us/</t>
         </is>
       </c>
-      <c r="Y164" s="12" t="inlineStr"/>
+      <c r="Y164" s="12" t="inlineStr">
+        <is>
+          <t>2026 Engineering News-Record. ENR 2026 Top 400 Contractors, where the firm is ranked 72  https://www.enr.com/toplists/2026-Top-400-Contractors-1</t>
+        </is>
+      </c>
       <c r="Z164" s="12" t="inlineStr"/>
       <c r="AA164" s="12" t="inlineStr"/>
       <c r="AB164" s="12" t="inlineStr"/>
@@ -19483,7 +19495,11 @@
           <t>https://www.harveycleary.com/about-us/</t>
         </is>
       </c>
-      <c r="Y165" s="6" t="inlineStr"/>
+      <c r="Y165" s="6" t="inlineStr">
+        <is>
+          <t>2026 Engineering News-Record. ENR 2026 Top 400 Contractors, where the firm is ranked 72  https://www.enr.com/toplists/2026-Top-400-Contractors-1</t>
+        </is>
+      </c>
       <c r="Z165" s="6" t="inlineStr"/>
       <c r="AA165" s="6" t="inlineStr"/>
       <c r="AB165" s="6" t="inlineStr"/>
@@ -19592,7 +19608,11 @@
           <t>https://www.harveycleary.com/about-us/</t>
         </is>
       </c>
-      <c r="Y166" s="12" t="inlineStr"/>
+      <c r="Y166" s="12" t="inlineStr">
+        <is>
+          <t>2026 Engineering News-Record. ENR 2026 Top 400 Contractors, where the firm is ranked 72  https://www.enr.com/toplists/2026-Top-400-Contractors-1</t>
+        </is>
+      </c>
       <c r="Z166" s="12" t="inlineStr"/>
       <c r="AA166" s="12" t="inlineStr"/>
       <c r="AB166" s="12" t="inlineStr"/>

--- a/docs/ICON_Greater_Houston_Rolodex.xlsx
+++ b/docs/ICON_Greater_Houston_Rolodex.xlsx
@@ -586,7 +586,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Héctor Ibarzábal · 2026-09-24</t>
+          <t>Héctor Ibarzábal · 2026-09-26</t>
         </is>
       </c>
     </row>
@@ -36324,7 +36324,7 @@
     <row r="309">
       <c r="A309" s="17" t="inlineStr">
         <is>
-          <t>NOTE. A filled LinkedIn cell means the profile was opened or the search result read and the headline named the firm; the verification column records what was read. Where that test failed the cell is left empty rather than guessed, because a fabricated slug passes visual inspection and then fails in front of the person it names. The Find column searches for the empty ones in your own session. Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Rolodex, Greater Houston, 2026-09-24.</t>
+          <t>NOTE. A filled LinkedIn cell means the profile was opened or the search result read and the headline named the firm; the verification column records what was read. Where that test failed the cell is left empty rather than guessed, because a fabricated slug passes visual inspection and then fails in front of the person it names. The Find column searches for the empty ones in your own session. Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Rolodex, Greater Houston, 2026-09-26.</t>
         </is>
       </c>
     </row>
